--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C210C64-6B02-48F1-B41C-0CB9F9BF9D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6F50A5-D103-4A29-BAF9-74A75CCA4412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
   <si>
     <t>Dgn</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>COEFFICIENT</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
   </si>
 </sst>
 </file>
@@ -218,13 +224,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,13 +516,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" customWidth="1"/>
+    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -523,7 +530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -531,7 +538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -539,7 +546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -547,11 +554,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
@@ -559,7 +566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -567,7 +574,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -582,18 +589,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16AACB8-DCDD-4E05-8142-87FB5C31F593}">
-  <dimension ref="A1:AD29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF31"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="5" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="25.73046875" style="5" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C1" t="s">
@@ -678,2583 +685,2953 @@
         <v>12</v>
       </c>
       <c r="AD1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>1.7471860499690562E-2</v>
+      <c r="B2" s="6">
+        <v>2.1874076018055466E-2</v>
       </c>
       <c r="C2">
-        <v>3.4469968467771986E-4</v>
+        <v>2.9851592383260683E-4</v>
       </c>
       <c r="D2">
-        <v>2.4295184491415575E-6</v>
+        <v>1.1436571451653845E-6</v>
       </c>
       <c r="E2">
-        <v>-1.3509962752792642E-8</v>
+        <v>-1.5269004100319074E-9</v>
       </c>
       <c r="F2">
-        <v>-2.9994801700151595E-5</v>
+        <v>7.0108811572712801E-5</v>
       </c>
       <c r="G2">
-        <v>-4.8456786653664136E-5</v>
+        <v>-5.3716195502951547E-5</v>
       </c>
       <c r="H2">
-        <v>3.5602292080099096E-5</v>
+        <v>3.5551929797136886E-5</v>
       </c>
       <c r="I2">
-        <v>-8.8938852067183758E-5</v>
+        <v>-1.157912126447326E-4</v>
       </c>
       <c r="J2">
-        <v>-7.685592233401672E-5</v>
+        <v>-8.4266602206119507E-5</v>
       </c>
       <c r="K2">
-        <v>1.1512961108698171E-5</v>
+        <v>1.6653419729233698E-6</v>
       </c>
       <c r="L2">
-        <v>4.3824007452566172E-5</v>
+        <v>9.3407246255899836E-5</v>
       </c>
       <c r="M2">
-        <v>1.1283313509137887E-5</v>
+        <v>1.1493378519916237E-5</v>
       </c>
       <c r="N2">
-        <v>5.6310630456918802E-5</v>
+        <v>3.7889682813246553E-5</v>
       </c>
       <c r="O2">
-        <v>-3.0495321007982408E-5</v>
+        <v>-3.4554789730022793E-5</v>
       </c>
       <c r="P2">
-        <v>1.6485121100518071E-5</v>
+        <v>3.5658667633649838E-6</v>
       </c>
       <c r="Q2">
-        <v>-3.8601610935795299E-5</v>
+        <v>-1.83695481725111E-5</v>
       </c>
       <c r="R2">
-        <v>-1.7724799731967107E-5</v>
+        <v>-6.1447673540790392E-6</v>
       </c>
       <c r="S2">
-        <v>-2.4281528836900703E-5</v>
+        <v>-1.1811662601013654E-5</v>
       </c>
       <c r="T2">
-        <v>3.5170058560448974E-6</v>
+        <v>-4.1099230617279079E-6</v>
       </c>
       <c r="U2">
-        <v>-1.9610703433109654E-5</v>
+        <v>-1.3981286494577787E-5</v>
       </c>
       <c r="V2">
-        <v>-2.8351947015890952E-5</v>
+        <v>-1.9308154917156596E-5</v>
       </c>
       <c r="W2">
-        <v>-1.7903565143688481E-5</v>
+        <v>-1.523827417373022E-5</v>
       </c>
       <c r="X2">
-        <v>-6.2932608195010901E-6</v>
+        <v>-1.9452255932932666E-5</v>
       </c>
       <c r="Y2">
-        <v>1.1647246696488665E-5</v>
+        <v>6.682599706504147E-6</v>
       </c>
       <c r="Z2">
-        <v>-7.1833626879621248E-6</v>
+        <v>-8.6961027884613797E-6</v>
       </c>
       <c r="AA2">
-        <v>-1.3242873499830077E-5</v>
+        <v>-1.2886061089477157E-5</v>
       </c>
       <c r="AB2">
-        <v>-3.4063343145693693E-6</v>
+        <v>-6.669601378046875E-6</v>
       </c>
       <c r="AC2">
-        <v>-3.2189227123777386E-7</v>
+        <v>5.9861114096685321E-7</v>
       </c>
       <c r="AD2">
-        <v>-2.0780715512158302E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>1.5741945028437724E-5</v>
+      </c>
+      <c r="AE2">
+        <v>-3.3689292983417213E-5</v>
+      </c>
+      <c r="AF2">
+        <v>-1.5709920124766009E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>1.7381928613688154E-2</v>
+      <c r="B3" s="6">
+        <v>1.6910073147305599E-2</v>
       </c>
       <c r="C3">
-        <v>2.4295184491415575E-6</v>
+        <v>1.1436571451653845E-6</v>
       </c>
       <c r="D3">
-        <v>1.7269148048771281E-5</v>
+        <v>1.4364350332842051E-5</v>
       </c>
       <c r="E3">
-        <v>-1.6450841444946048E-7</v>
+        <v>-1.3724354058710353E-7</v>
       </c>
       <c r="F3">
-        <v>1.6651219340925577E-5</v>
+        <v>2.1287486995089045E-5</v>
       </c>
       <c r="G3">
-        <v>1.4123107770112179E-5</v>
+        <v>1.1025467637875621E-5</v>
       </c>
       <c r="H3">
-        <v>9.6871428450491748E-6</v>
+        <v>7.3968983355674552E-6</v>
       </c>
       <c r="I3">
-        <v>4.4236170492813187E-5</v>
+        <v>6.7295418489140408E-5</v>
       </c>
       <c r="J3">
-        <v>1.0208272606426366E-5</v>
+        <v>1.0146103675134364E-5</v>
       </c>
       <c r="K3">
-        <v>3.6932764724733487E-5</v>
+        <v>3.0353112832060981E-5</v>
       </c>
       <c r="L3">
-        <v>-5.6570157858541406E-7</v>
+        <v>-1.5306434080808589E-5</v>
       </c>
       <c r="M3">
-        <v>8.6885878173154752E-5</v>
+        <v>7.0420364325944122E-5</v>
       </c>
       <c r="N3">
-        <v>2.0684917674601538E-5</v>
+        <v>1.7168745669358801E-5</v>
       </c>
       <c r="O3">
-        <v>4.3647367269524347E-6</v>
+        <v>1.3309115479647035E-6</v>
       </c>
       <c r="P3">
-        <v>1.8100607353163279E-5</v>
+        <v>1.2745459252261099E-5</v>
       </c>
       <c r="Q3">
-        <v>4.3467145017882626E-7</v>
+        <v>1.5711506218874693E-6</v>
       </c>
       <c r="R3">
-        <v>1.627645211806295E-6</v>
+        <v>5.7271435435143632E-7</v>
       </c>
       <c r="S3">
-        <v>1.6350317054166576E-5</v>
+        <v>1.3646383607763228E-5</v>
       </c>
       <c r="T3">
-        <v>4.1459971445692779E-5</v>
+        <v>3.6198531684215224E-5</v>
       </c>
       <c r="U3">
-        <v>-5.687953819296774E-6</v>
+        <v>-1.8814284194357351E-6</v>
       </c>
       <c r="V3">
-        <v>-1.4073407875142426E-5</v>
+        <v>-8.2288069076880936E-6</v>
       </c>
       <c r="W3">
-        <v>-1.7997999608136259E-5</v>
+        <v>-1.482090114733809E-5</v>
       </c>
       <c r="X3">
-        <v>-1.809614851394841E-5</v>
+        <v>-1.2886406971670846E-5</v>
       </c>
       <c r="Y3">
-        <v>-3.125953126768938E-7</v>
+        <v>2.1846421668756831E-7</v>
       </c>
       <c r="Z3">
-        <v>-3.6333345186804788E-6</v>
+        <v>-3.104038004936691E-6</v>
       </c>
       <c r="AA3">
-        <v>-5.4659309063974479E-6</v>
+        <v>-5.0581567549761374E-6</v>
       </c>
       <c r="AB3">
-        <v>-3.6108449112757374E-6</v>
+        <v>-2.0160126882325471E-6</v>
       </c>
       <c r="AC3">
-        <v>1.1001589113463075E-7</v>
+        <v>3.7518156103585125E-7</v>
       </c>
       <c r="AD3">
-        <v>-4.4016616110077744E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+        <v>-1.7575548836117863E-7</v>
+      </c>
+      <c r="AE3">
+        <v>1.1199894597712036E-5</v>
+      </c>
+      <c r="AF3">
+        <v>-3.6926776268379638E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>-1.1810947533890744E-4</v>
+      <c r="B4" s="6">
+        <v>-1.1322421885996688E-4</v>
       </c>
       <c r="C4">
-        <v>-1.3509962752792642E-8</v>
+        <v>-1.5269004100319074E-9</v>
       </c>
       <c r="D4">
-        <v>-1.6450841444946048E-7</v>
+        <v>-1.3724354058710353E-7</v>
       </c>
       <c r="E4">
-        <v>1.6352311585416057E-9</v>
+        <v>1.3692758158211249E-9</v>
       </c>
       <c r="F4">
-        <v>-1.4282555968690068E-7</v>
+        <v>-2.1770064479994327E-7</v>
       </c>
       <c r="G4">
-        <v>-1.4563273470580167E-7</v>
+        <v>-1.1786802558761719E-7</v>
       </c>
       <c r="H4">
-        <v>-3.1422362941855789E-8</v>
+        <v>-1.4926598162995062E-8</v>
       </c>
       <c r="I4">
-        <v>-3.247210927302414E-7</v>
+        <v>-5.1639708422768484E-7</v>
       </c>
       <c r="J4">
-        <v>-3.0458896621467268E-8</v>
+        <v>-3.7601058222377137E-8</v>
       </c>
       <c r="K4">
-        <v>-3.2884613109319891E-7</v>
+        <v>-2.7312958622403518E-7</v>
       </c>
       <c r="L4">
-        <v>7.1339762301399931E-8</v>
+        <v>2.2286931216044782E-7</v>
       </c>
       <c r="M4">
-        <v>-6.9206042089966642E-7</v>
+        <v>-5.52550990769898E-7</v>
       </c>
       <c r="N4">
-        <v>-2.3136738596879015E-7</v>
+        <v>-1.9238910986303768E-7</v>
       </c>
       <c r="O4">
-        <v>-7.5535570137164516E-9</v>
+        <v>1.6745363741897949E-8</v>
       </c>
       <c r="P4">
-        <v>-1.3897510374806992E-7</v>
+        <v>-8.6904999028049701E-8</v>
       </c>
       <c r="Q4">
-        <v>-1.5656706702342341E-8</v>
+        <v>-2.4534247396819553E-8</v>
       </c>
       <c r="R4">
-        <v>-2.1789884732486552E-8</v>
+        <v>-1.0573077236194621E-8</v>
       </c>
       <c r="S4">
-        <v>-9.7106408810434712E-8</v>
+        <v>-7.8970679110126406E-8</v>
       </c>
       <c r="T4">
-        <v>-2.8023874667571718E-7</v>
+        <v>-2.4700576253227272E-7</v>
       </c>
       <c r="U4">
-        <v>8.505038219615223E-8</v>
+        <v>2.9811262373310289E-8</v>
       </c>
       <c r="V4">
-        <v>2.3554743986876129E-7</v>
+        <v>1.5728374752553908E-7</v>
       </c>
       <c r="W4">
-        <v>2.8003819889970642E-7</v>
+        <v>2.2921527888366501E-7</v>
       </c>
       <c r="X4">
-        <v>2.859890011933483E-7</v>
+        <v>2.0862451417067961E-7</v>
       </c>
       <c r="Y4">
-        <v>-3.8081024578865059E-9</v>
+        <v>-8.1968266538305633E-9</v>
       </c>
       <c r="Z4">
-        <v>2.2846286847226332E-8</v>
+        <v>1.8155915324204723E-8</v>
       </c>
       <c r="AA4">
-        <v>7.072236723403303E-8</v>
+        <v>6.0599809375043685E-8</v>
       </c>
       <c r="AB4">
-        <v>6.2457594494170826E-8</v>
+        <v>3.9198115623592033E-8</v>
       </c>
       <c r="AC4">
-        <v>-7.9695215301163053E-9</v>
+        <v>-7.1190985662936018E-9</v>
       </c>
       <c r="AD4">
-        <v>3.9363642204454033E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+        <v>-1.8019512157463056E-8</v>
+      </c>
+      <c r="AE4">
+        <v>-1.0084661403675593E-7</v>
+      </c>
+      <c r="AF4">
+        <v>3.2854761527932366E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
-        <v>-0.75692602585298641</v>
+      <c r="B5" s="6">
+        <v>-0.54449305291316275</v>
       </c>
       <c r="C5">
-        <v>-2.9994801700151595E-5</v>
+        <v>7.0108811572712801E-5</v>
       </c>
       <c r="D5">
-        <v>1.6651219340925577E-5</v>
+        <v>2.1287486995089045E-5</v>
       </c>
       <c r="E5">
-        <v>-1.4282555968690068E-7</v>
+        <v>-2.1770064479994327E-7</v>
       </c>
       <c r="F5">
-        <v>4.8410915962728944E-2</v>
+        <v>5.641189539608444E-2</v>
       </c>
       <c r="G5">
-        <v>5.7929709889895835E-4</v>
+        <v>4.9029783835324847E-4</v>
       </c>
       <c r="H5">
-        <v>6.7858669926712653E-4</v>
+        <v>4.6644843013986687E-4</v>
       </c>
       <c r="I5">
-        <v>1.0032223479822342E-3</v>
+        <v>9.322825143049196E-4</v>
       </c>
       <c r="J5">
-        <v>6.4403411179758175E-4</v>
+        <v>4.8612937149453432E-4</v>
       </c>
       <c r="K5">
-        <v>7.7633893744215798E-4</v>
+        <v>6.9754848852448582E-4</v>
       </c>
       <c r="L5">
-        <v>7.1956828324841297E-4</v>
+        <v>6.3760770972164722E-4</v>
       </c>
       <c r="M5">
-        <v>-6.3776255660283896E-4</v>
+        <v>-6.671231027621633E-4</v>
       </c>
       <c r="N5">
-        <v>-1.5625969747496953E-4</v>
+        <v>-1.0111999535728717E-4</v>
       </c>
       <c r="O5">
-        <v>-2.1191409991915385E-4</v>
+        <v>-3.9912175006452623E-4</v>
       </c>
       <c r="P5">
-        <v>-8.0867492187076939E-5</v>
+        <v>-2.3100279305889325E-4</v>
       </c>
       <c r="Q5">
-        <v>-6.318749866916773E-7</v>
+        <v>1.3159375862691937E-5</v>
       </c>
       <c r="R5">
-        <v>2.6129471047348161E-5</v>
+        <v>-7.5780101153044284E-6</v>
       </c>
       <c r="S5">
-        <v>-4.4617320318033271E-5</v>
+        <v>1.8228608777737655E-5</v>
       </c>
       <c r="T5">
-        <v>1.1466894920357019E-5</v>
+        <v>-2.7507763102295051E-4</v>
       </c>
       <c r="U5">
-        <v>7.0203204770739988E-5</v>
+        <v>2.3591377229256484E-5</v>
       </c>
       <c r="V5">
-        <v>5.9330190637222631E-5</v>
+        <v>-3.9772676508854671E-5</v>
       </c>
       <c r="W5">
-        <v>-3.9636169228579539E-5</v>
+        <v>-1.2895993894914277E-4</v>
       </c>
       <c r="X5">
-        <v>4.5841628705401295E-5</v>
+        <v>8.2629176605217156E-5</v>
       </c>
       <c r="Y5">
-        <v>-1.2469244340695436E-4</v>
+        <v>-9.8140874761658243E-5</v>
       </c>
       <c r="Z5">
-        <v>6.4781398482184521E-5</v>
+        <v>3.386067192100094E-5</v>
       </c>
       <c r="AA5">
-        <v>1.5051387712596877E-4</v>
+        <v>3.7327185859635764E-4</v>
       </c>
       <c r="AB5">
-        <v>2.4155605615208393E-4</v>
+        <v>2.8034136879408666E-4</v>
       </c>
       <c r="AC5">
-        <v>-2.1582193959812917E-5</v>
+        <v>1.7959170973855254E-5</v>
       </c>
       <c r="AD5">
-        <v>-6.1654182884119952E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+        <v>-3.0278756010854559E-4</v>
+      </c>
+      <c r="AE5">
+        <v>-6.0076710280574318E-5</v>
+      </c>
+      <c r="AF5">
+        <v>-1.0826635481383017E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
-        <v>7.5924195898022309E-2</v>
+      <c r="B6" s="6">
+        <v>0.10566422463741186</v>
       </c>
       <c r="C6">
-        <v>-4.8456786653664136E-5</v>
+        <v>-5.3716195502951547E-5</v>
       </c>
       <c r="D6">
-        <v>1.4123107770112179E-5</v>
+        <v>1.1025467637875621E-5</v>
       </c>
       <c r="E6">
-        <v>-1.4563273470580167E-7</v>
+        <v>-1.1786802558761719E-7</v>
       </c>
       <c r="F6">
-        <v>5.7929709889895835E-4</v>
+        <v>4.9029783835324847E-4</v>
       </c>
       <c r="G6">
-        <v>1.5397429129524866E-3</v>
+        <v>1.2747236705524349E-3</v>
       </c>
       <c r="H6">
-        <v>6.5603461398082213E-4</v>
+        <v>5.3451233666283607E-4</v>
       </c>
       <c r="I6">
-        <v>9.6837133790572412E-4</v>
+        <v>8.166847181305325E-4</v>
       </c>
       <c r="J6">
-        <v>8.6332550300890652E-4</v>
+        <v>7.1575309035629326E-4</v>
       </c>
       <c r="K6">
-        <v>9.259704563084818E-4</v>
+        <v>7.7410803342286335E-4</v>
       </c>
       <c r="L6">
-        <v>8.9617713760236088E-4</v>
+        <v>6.5945602784922997E-4</v>
       </c>
       <c r="M6">
-        <v>1.2287753285170891E-4</v>
+        <v>1.2305586924919661E-4</v>
       </c>
       <c r="N6">
-        <v>6.6477859922836545E-6</v>
+        <v>1.4029482074229992E-5</v>
       </c>
       <c r="O6">
-        <v>7.6569344151638074E-5</v>
+        <v>9.4025298021183911E-5</v>
       </c>
       <c r="P6">
-        <v>1.3562556172955149E-4</v>
+        <v>1.4052665274764899E-4</v>
       </c>
       <c r="Q6">
-        <v>8.5825061196614222E-5</v>
+        <v>6.7753532982014358E-5</v>
       </c>
       <c r="R6">
-        <v>9.6291734971585738E-6</v>
+        <v>1.8009631216156529E-5</v>
       </c>
       <c r="S6">
-        <v>4.4995285377654571E-5</v>
+        <v>4.4610493516168302E-5</v>
       </c>
       <c r="T6">
-        <v>2.5774875730491921E-5</v>
+        <v>-1.7358097105547648E-5</v>
       </c>
       <c r="U6">
-        <v>2.5123895869876286E-5</v>
+        <v>8.2160185616861683E-6</v>
       </c>
       <c r="V6">
-        <v>2.0488603388563273E-4</v>
+        <v>1.612450834908835E-4</v>
       </c>
       <c r="W6">
-        <v>4.9138176358450817E-4</v>
+        <v>3.8902067014318813E-4</v>
       </c>
       <c r="X6">
-        <v>6.6116837327779936E-4</v>
+        <v>6.1072752024863002E-4</v>
       </c>
       <c r="Y6">
-        <v>5.8113102953187524E-6</v>
+        <v>5.040745560277272E-6</v>
       </c>
       <c r="Z6">
-        <v>-3.0125241689514052E-5</v>
+        <v>-1.711185554365352E-5</v>
       </c>
       <c r="AA6">
-        <v>-1.0093410460025858E-8</v>
+        <v>5.5653013713087324E-6</v>
       </c>
       <c r="AB6">
-        <v>1.6989477676872364E-5</v>
+        <v>2.3969906109027966E-5</v>
       </c>
       <c r="AC6">
-        <v>1.9089802418905972E-6</v>
+        <v>1.3243172492480472E-6</v>
       </c>
       <c r="AD6">
-        <v>-1.55589952025228E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+        <v>-4.0289262114165571E-5</v>
+      </c>
+      <c r="AE6">
+        <v>1.4552064218746746E-5</v>
+      </c>
+      <c r="AF6">
+        <v>-1.2935524890365332E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B7">
-        <v>9.965675441128892E-2</v>
+      <c r="B7" s="6">
+        <v>0.10054046714898966</v>
       </c>
       <c r="C7">
-        <v>3.5602292080099096E-5</v>
+        <v>3.5551929797136886E-5</v>
       </c>
       <c r="D7">
-        <v>9.6871428450491748E-6</v>
+        <v>7.3968983355674552E-6</v>
       </c>
       <c r="E7">
-        <v>-3.1422362941855789E-8</v>
+        <v>-1.4926598162995062E-8</v>
       </c>
       <c r="F7">
-        <v>6.7858669926712653E-4</v>
+        <v>4.6644843013986687E-4</v>
       </c>
       <c r="G7">
-        <v>6.5603461398082213E-4</v>
+        <v>5.3451233666283607E-4</v>
       </c>
       <c r="H7">
-        <v>1.2745170267285777E-3</v>
+        <v>1.0658563213628608E-3</v>
       </c>
       <c r="I7">
-        <v>8.3148543705644645E-4</v>
+        <v>7.6184421891851886E-4</v>
       </c>
       <c r="J7">
-        <v>7.3679659968394786E-4</v>
+        <v>6.004771770426391E-4</v>
       </c>
       <c r="K7">
-        <v>6.9502697067806089E-4</v>
+        <v>5.6539754911426722E-4</v>
       </c>
       <c r="L7">
-        <v>7.5249566187997688E-4</v>
+        <v>6.4304128672705986E-4</v>
       </c>
       <c r="M7">
-        <v>2.3730971260161574E-4</v>
+        <v>2.2836465976456313E-4</v>
       </c>
       <c r="N7">
-        <v>-5.1469658773702423E-5</v>
+        <v>-2.187155961199316E-5</v>
       </c>
       <c r="O7">
-        <v>5.5740694027123415E-5</v>
+        <v>7.3930123593447344E-5</v>
       </c>
       <c r="P7">
-        <v>5.2047553917254958E-5</v>
+        <v>8.0476012094199794E-5</v>
       </c>
       <c r="Q7">
-        <v>9.6126119039560687E-6</v>
+        <v>2.6494805589377657E-5</v>
       </c>
       <c r="R7">
-        <v>-2.1238948742530504E-5</v>
+        <v>4.9980575492297404E-6</v>
       </c>
       <c r="S7">
-        <v>-5.2838652557854417E-5</v>
+        <v>-3.5479661536128818E-6</v>
       </c>
       <c r="T7">
-        <v>-3.1425977872665131E-5</v>
+        <v>-2.8559355109323263E-5</v>
       </c>
       <c r="U7">
-        <v>4.4560815378446416E-5</v>
+        <v>2.6873429866827936E-5</v>
       </c>
       <c r="V7">
-        <v>1.0248486911169929E-4</v>
+        <v>6.2458224815344418E-5</v>
       </c>
       <c r="W7">
-        <v>1.3468779257072976E-4</v>
+        <v>1.3334603609410352E-4</v>
       </c>
       <c r="X7">
-        <v>2.3532229800605405E-4</v>
+        <v>2.6922024676318175E-4</v>
       </c>
       <c r="Y7">
-        <v>-2.4799669389196739E-5</v>
+        <v>-1.3179829545148831E-5</v>
       </c>
       <c r="Z7">
-        <v>2.1052785955505052E-5</v>
+        <v>9.4301562577634248E-7</v>
       </c>
       <c r="AA7">
-        <v>3.7732147862168429E-5</v>
+        <v>3.0852555173356663E-5</v>
       </c>
       <c r="AB7">
-        <v>5.2037944284828122E-5</v>
+        <v>2.5619880390355398E-5</v>
       </c>
       <c r="AC7">
-        <v>-4.5405630521027794E-6</v>
+        <v>2.2968602649108813E-7</v>
       </c>
       <c r="AD7">
-        <v>-1.1635143896498528E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+        <v>-6.6171477147255206E-5</v>
+      </c>
+      <c r="AE7">
+        <v>-4.6258467120653969E-5</v>
+      </c>
+      <c r="AF7">
+        <v>-1.0706980027060419E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
-        <v>0.39295197530629727</v>
+      <c r="B8" s="6">
+        <v>-5.1888307371999377E-2</v>
       </c>
       <c r="C8">
-        <v>-8.8938852067183758E-5</v>
+        <v>-1.157912126447326E-4</v>
       </c>
       <c r="D8">
-        <v>4.4236170492813187E-5</v>
+        <v>6.7295418489140408E-5</v>
       </c>
       <c r="E8">
-        <v>-3.247210927302414E-7</v>
+        <v>-5.1639708422768484E-7</v>
       </c>
       <c r="F8">
-        <v>1.0032223479822342E-3</v>
+        <v>9.322825143049196E-4</v>
       </c>
       <c r="G8">
-        <v>9.6837133790572412E-4</v>
+        <v>8.166847181305325E-4</v>
       </c>
       <c r="H8">
-        <v>8.3148543705644645E-4</v>
+        <v>7.6184421891851886E-4</v>
       </c>
       <c r="I8">
-        <v>0.15844047255976354</v>
+        <v>3.9058570057587387E-2</v>
       </c>
       <c r="J8">
-        <v>1.0038560410826189E-3</v>
+        <v>1.0467884762483729E-3</v>
       </c>
       <c r="K8">
-        <v>1.0305938121054194E-3</v>
+        <v>9.0060118293043578E-4</v>
       </c>
       <c r="L8">
-        <v>1.0753117147408815E-3</v>
+        <v>9.8893681208381962E-4</v>
       </c>
       <c r="M8">
-        <v>4.9282370854246329E-4</v>
+        <v>6.8032633227968551E-4</v>
       </c>
       <c r="N8">
-        <v>-2.9283514022913925E-5</v>
+        <v>-8.43846968338369E-5</v>
       </c>
       <c r="O8">
-        <v>5.0661484745079873E-5</v>
+        <v>6.4942557982199632E-5</v>
       </c>
       <c r="P8">
-        <v>5.2930112342305946E-5</v>
+        <v>1.7258161309610442E-4</v>
       </c>
       <c r="Q8">
-        <v>-1.2484889016471006E-5</v>
+        <v>2.0690837516971539E-5</v>
       </c>
       <c r="R8">
-        <v>-9.4561161607925018E-5</v>
+        <v>-6.8203997263892205E-5</v>
       </c>
       <c r="S8">
-        <v>-1.8019955872715658E-4</v>
+        <v>-1.4069941960482451E-4</v>
       </c>
       <c r="T8">
-        <v>-7.1143917940326038E-5</v>
+        <v>1.0697093887855949E-4</v>
       </c>
       <c r="U8">
-        <v>8.8394357190585507E-5</v>
+        <v>1.0205244677894429E-4</v>
       </c>
       <c r="V8">
-        <v>2.6619894000028756E-4</v>
+        <v>1.8124935647922884E-4</v>
       </c>
       <c r="W8">
-        <v>6.675023678288281E-4</v>
+        <v>5.7945650349161819E-4</v>
       </c>
       <c r="X8">
-        <v>7.8517417964620788E-4</v>
+        <v>7.218447301684252E-4</v>
       </c>
       <c r="Y8">
-        <v>-7.746464724032552E-5</v>
+        <v>-9.9672813840503402E-5</v>
       </c>
       <c r="Z8">
-        <v>1.2448790341160182E-4</v>
+        <v>6.622323751116104E-6</v>
       </c>
       <c r="AA8">
-        <v>4.6878236900928E-5</v>
+        <v>4.6013995447695541E-5</v>
       </c>
       <c r="AB8">
-        <v>1.1539463242328475E-5</v>
+        <v>3.1664063028129848E-6</v>
       </c>
       <c r="AC8">
-        <v>-2.2652613101717194E-5</v>
+        <v>-5.1837457478509717E-6</v>
       </c>
       <c r="AD8">
-        <v>-2.1980252996440515E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>-1.1463574745298991E-4</v>
+      </c>
+      <c r="AE8">
+        <v>1.4392737378378517E-4</v>
+      </c>
+      <c r="AF8">
+        <v>-2.8782235208661797E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
-        <v>-1.5084848588849977E-2</v>
+      <c r="B9" s="6">
+        <v>-4.5154913358300547E-2</v>
       </c>
       <c r="C9">
-        <v>-7.685592233401672E-5</v>
+        <v>-8.4266602206119507E-5</v>
       </c>
       <c r="D9">
-        <v>1.0208272606426366E-5</v>
+        <v>1.0146103675134364E-5</v>
       </c>
       <c r="E9">
-        <v>-3.0458896621467268E-8</v>
+        <v>-3.7601058222377137E-8</v>
       </c>
       <c r="F9">
-        <v>6.4403411179758175E-4</v>
+        <v>4.8612937149453432E-4</v>
       </c>
       <c r="G9">
-        <v>8.6332550300890652E-4</v>
+        <v>7.1575309035629326E-4</v>
       </c>
       <c r="H9">
-        <v>7.3679659968394786E-4</v>
+        <v>6.004771770426391E-4</v>
       </c>
       <c r="I9">
-        <v>1.0038560410826189E-3</v>
+        <v>1.0467884762483729E-3</v>
       </c>
       <c r="J9">
-        <v>2.0984217399851106E-3</v>
+        <v>2.1174462418747124E-3</v>
       </c>
       <c r="K9">
-        <v>8.5529393069448754E-4</v>
+        <v>7.2279253788394354E-4</v>
       </c>
       <c r="L9">
-        <v>8.9968106527643426E-4</v>
+        <v>7.6773086170519797E-4</v>
       </c>
       <c r="M9">
-        <v>4.4195253553442303E-4</v>
+        <v>4.8941711499661078E-4</v>
       </c>
       <c r="N9">
-        <v>1.3257685795744069E-4</v>
+        <v>2.3197111520992697E-4</v>
       </c>
       <c r="O9">
-        <v>7.4128662664675973E-5</v>
+        <v>1.1611024357867115E-4</v>
       </c>
       <c r="P9">
-        <v>-6.6840644428518446E-7</v>
+        <v>6.9262567036752678E-5</v>
       </c>
       <c r="Q9">
-        <v>6.3544283652006302E-5</v>
+        <v>6.1067446840327018E-5</v>
       </c>
       <c r="R9">
-        <v>-1.8749805176466604E-5</v>
+        <v>-3.2779912802042861E-6</v>
       </c>
       <c r="S9">
-        <v>-1.9117219565215483E-5</v>
+        <v>1.0098727444402781E-6</v>
       </c>
       <c r="T9">
-        <v>-1.335729036162312E-5</v>
+        <v>-3.7703313695079395E-5</v>
       </c>
       <c r="U9">
-        <v>8.0735413247921077E-5</v>
+        <v>1.9904369851197389E-5</v>
       </c>
       <c r="V9">
-        <v>1.8867680076309804E-4</v>
+        <v>1.3299448873952237E-4</v>
       </c>
       <c r="W9">
-        <v>5.2330911044234051E-4</v>
+        <v>5.1167453788495548E-4</v>
       </c>
       <c r="X9">
-        <v>7.2249231921210633E-4</v>
+        <v>7.3501857717335277E-4</v>
       </c>
       <c r="Y9">
-        <v>-2.8319420335645601E-5</v>
+        <v>-1.5223236640478236E-5</v>
       </c>
       <c r="Z9">
-        <v>4.745260777046871E-5</v>
+        <v>4.6818946185943748E-5</v>
       </c>
       <c r="AA9">
-        <v>6.9045560613391647E-5</v>
+        <v>7.8084712406952732E-5</v>
       </c>
       <c r="AB9">
-        <v>6.7399779323503838E-5</v>
+        <v>5.1821549757337599E-5</v>
       </c>
       <c r="AC9">
-        <v>6.0515144080299258E-6</v>
+        <v>6.5327541532376592E-6</v>
       </c>
       <c r="AD9">
-        <v>-1.7949699590989359E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>-5.3631414669679333E-5</v>
+      </c>
+      <c r="AE9">
+        <v>6.8231935754350299E-5</v>
+      </c>
+      <c r="AF9">
+        <v>-1.7363406380741246E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B10">
-        <v>2.7713618978862944E-3</v>
+      <c r="B10" s="6">
+        <v>-5.2361669595137224E-3</v>
       </c>
       <c r="C10">
-        <v>1.1512961108698171E-5</v>
+        <v>1.6653419729233698E-6</v>
       </c>
       <c r="D10">
-        <v>3.6932764724733487E-5</v>
+        <v>3.0353112832060981E-5</v>
       </c>
       <c r="E10">
-        <v>-3.2884613109319891E-7</v>
+        <v>-2.7312958622403518E-7</v>
       </c>
       <c r="F10">
-        <v>7.7633893744215798E-4</v>
+        <v>6.9754848852448582E-4</v>
       </c>
       <c r="G10">
-        <v>9.259704563084818E-4</v>
+        <v>7.7410803342286335E-4</v>
       </c>
       <c r="H10">
-        <v>6.9502697067806089E-4</v>
+        <v>5.6539754911426722E-4</v>
       </c>
       <c r="I10">
-        <v>1.0305938121054194E-3</v>
+        <v>9.0060118293043578E-4</v>
       </c>
       <c r="J10">
-        <v>8.5529393069448754E-4</v>
+        <v>7.2279253788394354E-4</v>
       </c>
       <c r="K10">
-        <v>1.1441721271410702E-3</v>
+        <v>9.4014594642888305E-4</v>
       </c>
       <c r="L10">
-        <v>8.5722527953940029E-4</v>
+        <v>6.7040019558461429E-4</v>
       </c>
       <c r="M10">
-        <v>1.7001795839464431E-4</v>
+        <v>1.7249998231736916E-4</v>
       </c>
       <c r="N10">
-        <v>1.2351266525476202E-4</v>
+        <v>1.1358034382796231E-4</v>
       </c>
       <c r="O10">
-        <v>6.1737000103639369E-5</v>
+        <v>8.117000568748836E-5</v>
       </c>
       <c r="P10">
-        <v>8.5548235265033761E-5</v>
+        <v>1.1063489429662652E-4</v>
       </c>
       <c r="Q10">
-        <v>3.3120161476423685E-5</v>
+        <v>2.8183025715272994E-5</v>
       </c>
       <c r="R10">
-        <v>1.8230105857946263E-5</v>
+        <v>2.7661675575947565E-5</v>
       </c>
       <c r="S10">
-        <v>5.523373368797194E-5</v>
+        <v>5.8532075239809962E-5</v>
       </c>
       <c r="T10">
-        <v>2.6184620062973465E-5</v>
+        <v>-9.3680321652187806E-7</v>
       </c>
       <c r="U10">
-        <v>4.9265290693418498E-5</v>
+        <v>4.0349012503588296E-6</v>
       </c>
       <c r="V10">
-        <v>2.5068920601640946E-4</v>
+        <v>1.7464451032239773E-4</v>
       </c>
       <c r="W10">
-        <v>4.4570093925508304E-4</v>
+        <v>3.6340500527805964E-4</v>
       </c>
       <c r="X10">
-        <v>6.1770042698187531E-4</v>
+        <v>5.595040594349968E-4</v>
       </c>
       <c r="Y10">
-        <v>-1.1649044822977168E-5</v>
+        <v>-7.6692995024603189E-6</v>
       </c>
       <c r="Z10">
-        <v>5.7698711555164429E-6</v>
+        <v>3.3719310292758698E-6</v>
       </c>
       <c r="AA10">
-        <v>9.9128954024474414E-7</v>
+        <v>8.7154523924649202E-6</v>
       </c>
       <c r="AB10">
-        <v>2.9078983658546633E-5</v>
+        <v>3.1557364776549118E-5</v>
       </c>
       <c r="AC10">
-        <v>1.1234248720514231E-6</v>
+        <v>-2.6765373851791205E-7</v>
       </c>
       <c r="AD10">
-        <v>-2.233145656614254E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>-2.9004385335351134E-5</v>
+      </c>
+      <c r="AE10">
+        <v>2.8755090399975678E-5</v>
+      </c>
+      <c r="AF10">
+        <v>-1.8483312979453515E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B11">
-        <v>-0.18850003728612913</v>
+      <c r="B11" s="6">
+        <v>-0.17794564619636824</v>
       </c>
       <c r="C11">
-        <v>4.3824007452566172E-5</v>
+        <v>9.3407246255899836E-5</v>
       </c>
       <c r="D11">
-        <v>-5.6570157858541406E-7</v>
+        <v>-1.5306434080808589E-5</v>
       </c>
       <c r="E11">
-        <v>7.1339762301399931E-8</v>
+        <v>2.2286931216044782E-7</v>
       </c>
       <c r="F11">
-        <v>7.1956828324841297E-4</v>
+        <v>6.3760770972164722E-4</v>
       </c>
       <c r="G11">
-        <v>8.9617713760236088E-4</v>
+        <v>6.5945602784922997E-4</v>
       </c>
       <c r="H11">
-        <v>7.5249566187997688E-4</v>
+        <v>6.4304128672705986E-4</v>
       </c>
       <c r="I11">
-        <v>1.0753117147408815E-3</v>
+        <v>9.8893681208381962E-4</v>
       </c>
       <c r="J11">
-        <v>8.9968106527643426E-4</v>
+        <v>7.6773086170519797E-4</v>
       </c>
       <c r="K11">
-        <v>8.5722527953940029E-4</v>
+        <v>6.7040019558461429E-4</v>
       </c>
       <c r="L11">
-        <v>2.9033084429566265E-3</v>
+        <v>3.1912084596167956E-3</v>
       </c>
       <c r="M11">
-        <v>2.9427742630518572E-4</v>
+        <v>3.3745763098022151E-4</v>
       </c>
       <c r="N11">
-        <v>1.0214088276696404E-4</v>
+        <v>1.7241363828671247E-4</v>
       </c>
       <c r="O11">
-        <v>1.440283240317853E-4</v>
+        <v>1.3761849236320156E-4</v>
       </c>
       <c r="P11">
-        <v>1.0276543207785851E-4</v>
+        <v>1.2127903620431468E-4</v>
       </c>
       <c r="Q11">
-        <v>6.1460262361031769E-5</v>
+        <v>1.5073668300590102E-5</v>
       </c>
       <c r="R11">
-        <v>-2.9095822681616629E-5</v>
+        <v>-4.4250987139909194E-5</v>
       </c>
       <c r="S11">
-        <v>4.5154383622500135E-5</v>
+        <v>-2.1300620042273333E-5</v>
       </c>
       <c r="T11">
-        <v>1.3760995302645535E-4</v>
+        <v>-1.5041222732224869E-5</v>
       </c>
       <c r="U11">
-        <v>1.2168511698483244E-4</v>
+        <v>9.2245069888900624E-5</v>
       </c>
       <c r="V11">
-        <v>3.1280571116906015E-4</v>
+        <v>2.2815653864731463E-4</v>
       </c>
       <c r="W11">
-        <v>5.4092170484564949E-4</v>
+        <v>5.7900358431576084E-4</v>
       </c>
       <c r="X11">
-        <v>8.1904543504798897E-4</v>
+        <v>7.9068721815513218E-4</v>
       </c>
       <c r="Y11">
-        <v>-9.1124267502424417E-5</v>
+        <v>-1.0010507995308898E-4</v>
       </c>
       <c r="Z11">
-        <v>-7.9578593696511769E-6</v>
+        <v>3.2769022809502724E-6</v>
       </c>
       <c r="AA11">
-        <v>-4.6062305475433123E-5</v>
+        <v>4.4096105756266028E-6</v>
       </c>
       <c r="AB11">
-        <v>8.9404920027217998E-6</v>
+        <v>4.1772616336907217E-5</v>
       </c>
       <c r="AC11">
-        <v>2.1071866677422159E-6</v>
+        <v>-3.8496161507193299E-6</v>
       </c>
       <c r="AD11">
-        <v>-1.5620043054297666E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>-1.0093830540333209E-4</v>
+      </c>
+      <c r="AE11">
+        <v>-3.8256135373335989E-5</v>
+      </c>
+      <c r="AF11">
+        <v>-9.897684567244016E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B12">
-        <v>0.1693494409267369</v>
+      <c r="B12" s="6">
+        <v>0.22882671347338648</v>
       </c>
       <c r="C12">
-        <v>1.1283313509137887E-5</v>
+        <v>1.1493378519916237E-5</v>
       </c>
       <c r="D12">
-        <v>8.6885878173154752E-5</v>
+        <v>7.0420364325944122E-5</v>
       </c>
       <c r="E12">
-        <v>-6.9206042089966642E-7</v>
+        <v>-5.52550990769898E-7</v>
       </c>
       <c r="F12">
-        <v>-6.3776255660283896E-4</v>
+        <v>-6.671231027621633E-4</v>
       </c>
       <c r="G12">
-        <v>1.2287753285170891E-4</v>
+        <v>1.2305586924919661E-4</v>
       </c>
       <c r="H12">
-        <v>2.3730971260161574E-4</v>
+        <v>2.2836465976456313E-4</v>
       </c>
       <c r="I12">
-        <v>4.9282370854246329E-4</v>
+        <v>6.8032633227968551E-4</v>
       </c>
       <c r="J12">
-        <v>4.4195253553442303E-4</v>
+        <v>4.8941711499661078E-4</v>
       </c>
       <c r="K12">
-        <v>1.7001795839464431E-4</v>
+        <v>1.7249998231736916E-4</v>
       </c>
       <c r="L12">
-        <v>2.9427742630518572E-4</v>
+        <v>3.3745763098022151E-4</v>
       </c>
       <c r="M12">
-        <v>2.4628773263375347E-3</v>
+        <v>2.1985661830990887E-3</v>
       </c>
       <c r="N12">
-        <v>6.2145734611609028E-4</v>
+        <v>5.834251040412107E-4</v>
       </c>
       <c r="O12">
-        <v>4.6305667901356303E-5</v>
+        <v>2.8130691764113186E-5</v>
       </c>
       <c r="P12">
-        <v>-1.0533554918295955E-5</v>
+        <v>1.0282728513000814E-5</v>
       </c>
       <c r="Q12">
-        <v>4.7066431968171424E-6</v>
+        <v>5.3856246631920528E-6</v>
       </c>
       <c r="R12">
-        <v>-5.0345485596907553E-5</v>
+        <v>-4.0410986069276851E-5</v>
       </c>
       <c r="S12">
-        <v>2.1113513455878522E-5</v>
+        <v>1.5634486256688878E-5</v>
       </c>
       <c r="T12">
-        <v>-2.669784840277729E-5</v>
+        <v>-2.1236694296571188E-5</v>
       </c>
       <c r="U12">
-        <v>1.8623344748680071E-4</v>
+        <v>1.388670797310177E-4</v>
       </c>
       <c r="V12">
-        <v>6.0333186073440663E-4</v>
+        <v>5.3294749184469592E-4</v>
       </c>
       <c r="W12">
-        <v>8.7711961535056325E-4</v>
+        <v>8.2954096165262399E-4</v>
       </c>
       <c r="X12">
-        <v>9.8391886714822006E-4</v>
+        <v>9.119976310057766E-4</v>
       </c>
       <c r="Y12">
-        <v>-4.59493556410208E-5</v>
+        <v>-3.4438736618426058E-5</v>
       </c>
       <c r="Z12">
-        <v>-7.1708992522854958E-5</v>
+        <v>-4.0324097880234681E-5</v>
       </c>
       <c r="AA12">
-        <v>5.6456434881620816E-5</v>
+        <v>5.0308482941641315E-5</v>
       </c>
       <c r="AB12">
-        <v>7.566786134163405E-5</v>
+        <v>6.7325347410209565E-5</v>
       </c>
       <c r="AC12">
-        <v>-1.2443696482285964E-5</v>
+        <v>-4.8233395742373452E-6</v>
       </c>
       <c r="AD12">
-        <v>-3.4064766889406002E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>-1.1597601153888183E-4</v>
+      </c>
+      <c r="AE12">
+        <v>1.5171149411297291E-4</v>
+      </c>
+      <c r="AF12">
+        <v>-3.0116310722167819E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <v>-4.1304381727000801E-2</v>
+      <c r="B13" s="6">
+        <v>-2.8734027606585409E-2</v>
       </c>
       <c r="C13">
-        <v>5.6310630456918802E-5</v>
+        <v>3.7889682813246553E-5</v>
       </c>
       <c r="D13">
-        <v>2.0684917674601538E-5</v>
+        <v>1.7168745669358801E-5</v>
       </c>
       <c r="E13">
-        <v>-2.3136738596879015E-7</v>
+        <v>-1.9238910986303768E-7</v>
       </c>
       <c r="F13">
-        <v>-1.5625969747496953E-4</v>
+        <v>-1.0111999535728717E-4</v>
       </c>
       <c r="G13">
-        <v>6.6477859922836545E-6</v>
+        <v>1.4029482074229992E-5</v>
       </c>
       <c r="H13">
-        <v>-5.1469658773702423E-5</v>
+        <v>-2.187155961199316E-5</v>
       </c>
       <c r="I13">
-        <v>-2.9283514022913925E-5</v>
+        <v>-8.43846968338369E-5</v>
       </c>
       <c r="J13">
-        <v>1.3257685795744069E-4</v>
+        <v>2.3197111520992697E-4</v>
       </c>
       <c r="K13">
-        <v>1.2351266525476202E-4</v>
+        <v>1.1358034382796231E-4</v>
       </c>
       <c r="L13">
-        <v>1.0214088276696404E-4</v>
+        <v>1.7241363828671247E-4</v>
       </c>
       <c r="M13">
-        <v>6.2145734611609028E-4</v>
+        <v>5.834251040412107E-4</v>
       </c>
       <c r="N13">
-        <v>1.0558633814117249E-3</v>
+        <v>9.173513325471535E-4</v>
       </c>
       <c r="O13">
-        <v>2.1317479068237364E-5</v>
+        <v>3.5462152824107014E-5</v>
       </c>
       <c r="P13">
-        <v>-7.2423135197997716E-6</v>
+        <v>6.3777720273391219E-6</v>
       </c>
       <c r="Q13">
-        <v>3.4126131904624964E-5</v>
+        <v>1.78078647036385E-5</v>
       </c>
       <c r="R13">
-        <v>9.8332640786354282E-5</v>
+        <v>7.874560668972929E-5</v>
       </c>
       <c r="S13">
-        <v>2.1675209601894661E-4</v>
+        <v>1.5712734332446238E-4</v>
       </c>
       <c r="T13">
-        <v>2.6904788192767121E-4</v>
+        <v>1.9755704859967965E-4</v>
       </c>
       <c r="U13">
-        <v>2.2918808233293579E-5</v>
+        <v>-1.375358655762875E-5</v>
       </c>
       <c r="V13">
-        <v>3.1181249931265943E-4</v>
+        <v>2.5316097880959278E-4</v>
       </c>
       <c r="W13">
-        <v>6.534943117463088E-4</v>
+        <v>5.7746229607549457E-4</v>
       </c>
       <c r="X13">
-        <v>8.0464783959886691E-4</v>
+        <v>7.1406119885095121E-4</v>
       </c>
       <c r="Y13">
-        <v>-9.1918582762697578E-6</v>
+        <v>-1.2155994229546817E-5</v>
       </c>
       <c r="Z13">
-        <v>1.2135547101695217E-5</v>
+        <v>1.9646795530450523E-5</v>
       </c>
       <c r="AA13">
-        <v>-7.5258279043242862E-6</v>
+        <v>3.3635200080412808E-6</v>
       </c>
       <c r="AB13">
-        <v>3.1061448538532033E-7</v>
+        <v>1.2361500107295757E-5</v>
       </c>
       <c r="AC13">
-        <v>5.1507851540163367E-6</v>
+        <v>3.8127271874019116E-6</v>
       </c>
       <c r="AD13">
-        <v>-1.6376659116148766E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>-1.3809609752967548E-5</v>
+      </c>
+      <c r="AE13">
+        <v>4.1816817727777758E-5</v>
+      </c>
+      <c r="AF13">
+        <v>-1.4123336928822138E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14">
-        <v>5.5481603257131178E-3</v>
+      <c r="B14" s="6">
+        <v>-1.6727905623201611E-3</v>
       </c>
       <c r="C14">
-        <v>-3.0495321007982408E-5</v>
+        <v>-3.4554789730022793E-5</v>
       </c>
       <c r="D14">
-        <v>4.3647367269524347E-6</v>
+        <v>1.3309115479647035E-6</v>
       </c>
       <c r="E14">
-        <v>-7.5535570137164516E-9</v>
+        <v>1.6745363741897949E-8</v>
       </c>
       <c r="F14">
-        <v>-2.1191409991915385E-4</v>
+        <v>-3.9912175006452623E-4</v>
       </c>
       <c r="G14">
-        <v>7.6569344151638074E-5</v>
+        <v>9.4025298021183911E-5</v>
       </c>
       <c r="H14">
-        <v>5.5740694027123415E-5</v>
+        <v>7.3930123593447344E-5</v>
       </c>
       <c r="I14">
-        <v>5.0661484745079873E-5</v>
+        <v>6.4942557982199632E-5</v>
       </c>
       <c r="J14">
-        <v>7.4128662664675973E-5</v>
+        <v>1.1611024357867115E-4</v>
       </c>
       <c r="K14">
-        <v>6.1737000103639369E-5</v>
+        <v>8.117000568748836E-5</v>
       </c>
       <c r="L14">
-        <v>1.440283240317853E-4</v>
+        <v>1.3761849236320156E-4</v>
       </c>
       <c r="M14">
-        <v>4.6305667901356303E-5</v>
+        <v>2.8130691764113186E-5</v>
       </c>
       <c r="N14">
-        <v>2.1317479068237364E-5</v>
+        <v>3.5462152824107014E-5</v>
       </c>
       <c r="O14">
-        <v>7.4794386196144714E-4</v>
+        <v>6.2934522150186526E-4</v>
       </c>
       <c r="P14">
-        <v>6.3201297693575261E-4</v>
+        <v>5.3277216302709978E-4</v>
       </c>
       <c r="Q14">
-        <v>1.3742051058896658E-5</v>
+        <v>1.9982116899042109E-5</v>
       </c>
       <c r="R14">
-        <v>6.3453070401176686E-5</v>
+        <v>4.6483609235229806E-5</v>
       </c>
       <c r="S14">
-        <v>1.0536245065765097E-4</v>
+        <v>9.186912151973767E-5</v>
       </c>
       <c r="T14">
-        <v>1.9920600446616865E-4</v>
+        <v>1.5834570294455218E-4</v>
       </c>
       <c r="U14">
-        <v>4.8131331374545524E-5</v>
+        <v>-1.0816475358226848E-5</v>
       </c>
       <c r="V14">
-        <v>6.9848962494340304E-5</v>
+        <v>4.9234675852413744E-5</v>
       </c>
       <c r="W14">
-        <v>8.93717942027804E-5</v>
+        <v>9.9882044977447768E-5</v>
       </c>
       <c r="X14">
-        <v>2.702652556161179E-4</v>
+        <v>2.2652806341546253E-4</v>
       </c>
       <c r="Y14">
-        <v>-5.745202019215084E-7</v>
+        <v>1.4116038952588224E-6</v>
       </c>
       <c r="Z14">
-        <v>-1.0436390166290389E-5</v>
+        <v>-1.6875388168956007E-6</v>
       </c>
       <c r="AA14">
-        <v>-8.0606366586424404E-5</v>
+        <v>-6.0525083759455447E-5</v>
       </c>
       <c r="AB14">
-        <v>-3.207100310766858E-5</v>
+        <v>-3.8036209628021023E-5</v>
       </c>
       <c r="AC14">
-        <v>-2.7066710404196123E-6</v>
+        <v>-1.2668521360974E-6</v>
       </c>
       <c r="AD14">
-        <v>-9.5113405554368171E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <v>-4.7670315417004055E-5</v>
+      </c>
+      <c r="AE14">
+        <v>-2.9889627507737122E-5</v>
+      </c>
+      <c r="AF14">
+        <v>-7.8294380543485718E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B15">
-        <v>-0.12792619617646805</v>
+      <c r="B15" s="6">
+        <v>-0.11637792949605125</v>
       </c>
       <c r="C15">
-        <v>1.6485121100518071E-5</v>
+        <v>3.5658667633649838E-6</v>
       </c>
       <c r="D15">
-        <v>1.8100607353163279E-5</v>
+        <v>1.2745459252261099E-5</v>
       </c>
       <c r="E15">
-        <v>-1.3897510374806992E-7</v>
+        <v>-8.6904999028049701E-8</v>
       </c>
       <c r="F15">
-        <v>-8.0867492187076939E-5</v>
+        <v>-2.3100279305889325E-4</v>
       </c>
       <c r="G15">
-        <v>1.3562556172955149E-4</v>
+        <v>1.4052665274764899E-4</v>
       </c>
       <c r="H15">
-        <v>5.2047553917254958E-5</v>
+        <v>8.0476012094199794E-5</v>
       </c>
       <c r="I15">
-        <v>5.2930112342305946E-5</v>
+        <v>1.7258161309610442E-4</v>
       </c>
       <c r="J15">
-        <v>-6.6840644428518446E-7</v>
+        <v>6.9262567036752678E-5</v>
       </c>
       <c r="K15">
-        <v>8.5548235265033761E-5</v>
+        <v>1.1063489429662652E-4</v>
       </c>
       <c r="L15">
-        <v>1.0276543207785851E-4</v>
+        <v>1.2127903620431468E-4</v>
       </c>
       <c r="M15">
-        <v>-1.0533554918295955E-5</v>
+        <v>1.0282728513000814E-5</v>
       </c>
       <c r="N15">
-        <v>-7.2423135197997716E-6</v>
+        <v>6.3777720273391219E-6</v>
       </c>
       <c r="O15">
-        <v>6.3201297693575261E-4</v>
+        <v>5.3277216302709978E-4</v>
       </c>
       <c r="P15">
-        <v>9.8816652141149293E-4</v>
+        <v>8.2885148159012642E-4</v>
       </c>
       <c r="Q15">
-        <v>-1.0616052265107357E-5</v>
+        <v>-6.9518235784424179E-6</v>
       </c>
       <c r="R15">
-        <v>1.0038057565750926E-4</v>
+        <v>5.9127910465072602E-5</v>
       </c>
       <c r="S15">
-        <v>1.6708737659502029E-4</v>
+        <v>1.3345288736898786E-4</v>
       </c>
       <c r="T15">
-        <v>3.4036597496612148E-4</v>
+        <v>2.5719731884120769E-4</v>
       </c>
       <c r="U15">
-        <v>2.1754826164116159E-5</v>
+        <v>-2.0669582481813693E-5</v>
       </c>
       <c r="V15">
-        <v>5.7269925868806716E-5</v>
+        <v>4.7032310630458062E-5</v>
       </c>
       <c r="W15">
-        <v>1.4335301690129859E-4</v>
+        <v>1.5594186404796289E-4</v>
       </c>
       <c r="X15">
-        <v>3.252408949891934E-4</v>
+        <v>3.0208941330977634E-4</v>
       </c>
       <c r="Y15">
-        <v>3.750749272439879E-6</v>
+        <v>3.5182159059945285E-6</v>
       </c>
       <c r="Z15">
-        <v>9.7194984517920481E-6</v>
+        <v>1.3148456104460112E-5</v>
       </c>
       <c r="AA15">
-        <v>-1.1170540711789129E-4</v>
+        <v>-8.964156174115414E-5</v>
       </c>
       <c r="AB15">
-        <v>-6.2389965577039591E-5</v>
+        <v>-6.8067894548984743E-5</v>
       </c>
       <c r="AC15">
-        <v>-1.5644579949693563E-6</v>
+        <v>-1.2082071356331214E-6</v>
       </c>
       <c r="AD15">
-        <v>-1.403220276419188E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>-4.0465924059029273E-5</v>
+      </c>
+      <c r="AE15">
+        <v>-4.4105347839170782E-5</v>
+      </c>
+      <c r="AF15">
+        <v>-1.1618916288163709E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B16">
-        <v>-7.4582014073961188E-3</v>
+      <c r="B16" s="6">
+        <v>-3.0264615763201793E-3</v>
       </c>
       <c r="C16">
-        <v>-3.8601610935795299E-5</v>
+        <v>-1.83695481725111E-5</v>
       </c>
       <c r="D16">
-        <v>4.3467145017882626E-7</v>
+        <v>1.5711506218874693E-6</v>
       </c>
       <c r="E16">
-        <v>-1.5656706702342341E-8</v>
+        <v>-2.4534247396819553E-8</v>
       </c>
       <c r="F16">
-        <v>-6.318749866916773E-7</v>
+        <v>1.3159375862691937E-5</v>
       </c>
       <c r="G16">
-        <v>8.5825061196614222E-5</v>
+        <v>6.7753532982014358E-5</v>
       </c>
       <c r="H16">
-        <v>9.6126119039560687E-6</v>
+        <v>2.6494805589377657E-5</v>
       </c>
       <c r="I16">
-        <v>-1.2484889016471006E-5</v>
+        <v>2.0690837516971539E-5</v>
       </c>
       <c r="J16">
-        <v>6.3544283652006302E-5</v>
+        <v>6.1067446840327018E-5</v>
       </c>
       <c r="K16">
-        <v>3.3120161476423685E-5</v>
+        <v>2.8183025715272994E-5</v>
       </c>
       <c r="L16">
-        <v>6.1460262361031769E-5</v>
+        <v>1.5073668300590102E-5</v>
       </c>
       <c r="M16">
-        <v>4.7066431968171424E-6</v>
+        <v>5.3856246631920528E-6</v>
       </c>
       <c r="N16">
-        <v>3.4126131904624964E-5</v>
+        <v>1.78078647036385E-5</v>
       </c>
       <c r="O16">
-        <v>1.3742051058896658E-5</v>
+        <v>1.9982116899042109E-5</v>
       </c>
       <c r="P16">
-        <v>-1.0616052265107357E-5</v>
+        <v>-6.9518235784424179E-6</v>
       </c>
       <c r="Q16">
-        <v>3.6560092222287541E-3</v>
+        <v>3.078206179153508E-3</v>
       </c>
       <c r="R16">
-        <v>2.9714446627858672E-3</v>
+        <v>2.4647591333657216E-3</v>
       </c>
       <c r="S16">
-        <v>2.995874629758579E-3</v>
+        <v>2.4849603957492264E-3</v>
       </c>
       <c r="T16">
-        <v>2.9896034276769689E-3</v>
+        <v>2.4799319124073939E-3</v>
       </c>
       <c r="U16">
-        <v>-4.4002262691528432E-5</v>
+        <v>4.433926111909592E-5</v>
       </c>
       <c r="V16">
-        <v>-4.3001309074033352E-5</v>
+        <v>5.289306651788038E-6</v>
       </c>
       <c r="W16">
-        <v>-7.2348442458853917E-6</v>
+        <v>6.8487959581042769E-6</v>
       </c>
       <c r="X16">
-        <v>-5.7461587788532336E-6</v>
+        <v>2.100701636059411E-5</v>
       </c>
       <c r="Y16">
-        <v>4.345699938701562E-6</v>
+        <v>2.117072085645389E-6</v>
       </c>
       <c r="Z16">
-        <v>-4.5790092608613304E-5</v>
+        <v>-3.2036442491227514E-5</v>
       </c>
       <c r="AA16">
-        <v>2.2321246328270775E-6</v>
+        <v>-1.0666180632784008E-5</v>
       </c>
       <c r="AB16">
-        <v>1.0069743427286882E-6</v>
+        <v>-8.5215448292371137E-6</v>
       </c>
       <c r="AC16">
-        <v>2.6130965551010425E-6</v>
+        <v>4.4146921665492306E-6</v>
       </c>
       <c r="AD16">
-        <v>-2.9992981902713816E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <v>-1.8734728239342216E-6</v>
+      </c>
+      <c r="AE16">
+        <v>-2.4229861176849004E-5</v>
+      </c>
+      <c r="AF16">
+        <v>-2.5916239165677214E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B17">
-        <v>1.7639626563258987E-2</v>
+      <c r="B17" s="6">
+        <v>1.7767584210291062E-2</v>
       </c>
       <c r="C17">
-        <v>-1.7724799731967107E-5</v>
+        <v>-6.1447673540790392E-6</v>
       </c>
       <c r="D17">
-        <v>1.627645211806295E-6</v>
+        <v>5.7271435435143632E-7</v>
       </c>
       <c r="E17">
-        <v>-2.1789884732486552E-8</v>
+        <v>-1.0573077236194621E-8</v>
       </c>
       <c r="F17">
-        <v>2.6129471047348161E-5</v>
+        <v>-7.5780101153044284E-6</v>
       </c>
       <c r="G17">
-        <v>9.6291734971585738E-6</v>
+        <v>1.8009631216156529E-5</v>
       </c>
       <c r="H17">
-        <v>-2.1238948742530504E-5</v>
+        <v>4.9980575492297404E-6</v>
       </c>
       <c r="I17">
-        <v>-9.4561161607925018E-5</v>
+        <v>-6.8203997263892205E-5</v>
       </c>
       <c r="J17">
-        <v>-1.8749805176466604E-5</v>
+        <v>-3.2779912802042861E-6</v>
       </c>
       <c r="K17">
-        <v>1.8230105857946263E-5</v>
+        <v>2.7661675575947565E-5</v>
       </c>
       <c r="L17">
-        <v>-2.9095822681616629E-5</v>
+        <v>-4.4250987139909194E-5</v>
       </c>
       <c r="M17">
-        <v>-5.0345485596907553E-5</v>
+        <v>-4.0410986069276851E-5</v>
       </c>
       <c r="N17">
-        <v>9.8332640786354282E-5</v>
+        <v>7.874560668972929E-5</v>
       </c>
       <c r="O17">
-        <v>6.3453070401176686E-5</v>
+        <v>4.6483609235229806E-5</v>
       </c>
       <c r="P17">
-        <v>1.0038057565750926E-4</v>
+        <v>5.9127910465072602E-5</v>
       </c>
       <c r="Q17">
-        <v>2.9714446627858672E-3</v>
+        <v>2.4647591333657216E-3</v>
       </c>
       <c r="R17">
-        <v>3.2775383388123688E-3</v>
+        <v>2.7154512808987888E-3</v>
       </c>
       <c r="S17">
-        <v>3.0199797877742329E-3</v>
+        <v>2.506734023401771E-3</v>
       </c>
       <c r="T17">
-        <v>3.0333347176274171E-3</v>
+        <v>2.507870102597066E-3</v>
       </c>
       <c r="U17">
-        <v>-1.0087639555631808E-4</v>
+        <v>2.4467536920440747E-5</v>
       </c>
       <c r="V17">
-        <v>-1.7115661792587816E-4</v>
+        <v>-7.4555641353073833E-5</v>
       </c>
       <c r="W17">
-        <v>-1.4505285668995805E-4</v>
+        <v>-7.5538237206049502E-5</v>
       </c>
       <c r="X17">
-        <v>-1.2827309140040882E-4</v>
+        <v>-4.7356719954797899E-5</v>
       </c>
       <c r="Y17">
-        <v>1.7585199453686831E-5</v>
+        <v>1.2757373651012325E-5</v>
       </c>
       <c r="Z17">
-        <v>-1.1768744238756167E-5</v>
+        <v>-8.8683372145694026E-6</v>
       </c>
       <c r="AA17">
-        <v>-2.9312438923120594E-5</v>
+        <v>-2.6685336070746569E-5</v>
       </c>
       <c r="AB17">
-        <v>-1.5901169902214282E-5</v>
+        <v>-2.3390028136435976E-5</v>
       </c>
       <c r="AC17">
-        <v>1.4002269469135529E-6</v>
+        <v>8.0756800444292632E-7</v>
       </c>
       <c r="AD17">
-        <v>-3.0104610530649611E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <v>-1.2482152471419137E-6</v>
+      </c>
+      <c r="AE17">
+        <v>3.3046977193188873E-6</v>
+      </c>
+      <c r="AF17">
+        <v>-2.5300123538397608E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B18">
-        <v>5.3588327763666156E-2</v>
+      <c r="B18" s="6">
+        <v>7.4234264988473825E-2</v>
       </c>
       <c r="C18">
-        <v>-2.4281528836900703E-5</v>
+        <v>-1.1811662601013654E-5</v>
       </c>
       <c r="D18">
-        <v>1.6350317054166576E-5</v>
+        <v>1.3646383607763228E-5</v>
       </c>
       <c r="E18">
-        <v>-9.7106408810434712E-8</v>
+        <v>-7.8970679110126406E-8</v>
       </c>
       <c r="F18">
-        <v>-4.4617320318033271E-5</v>
+        <v>1.8228608777737655E-5</v>
       </c>
       <c r="G18">
-        <v>4.4995285377654571E-5</v>
+        <v>4.4610493516168302E-5</v>
       </c>
       <c r="H18">
-        <v>-5.2838652557854417E-5</v>
+        <v>-3.5479661536128818E-6</v>
       </c>
       <c r="I18">
-        <v>-1.8019955872715658E-4</v>
+        <v>-1.4069941960482451E-4</v>
       </c>
       <c r="J18">
-        <v>-1.9117219565215483E-5</v>
+        <v>1.0098727444402781E-6</v>
       </c>
       <c r="K18">
-        <v>5.523373368797194E-5</v>
+        <v>5.8532075239809962E-5</v>
       </c>
       <c r="L18">
-        <v>4.5154383622500135E-5</v>
+        <v>-2.1300620042273333E-5</v>
       </c>
       <c r="M18">
-        <v>2.1113513455878522E-5</v>
+        <v>1.5634486256688878E-5</v>
       </c>
       <c r="N18">
-        <v>2.1675209601894661E-4</v>
+        <v>1.5712734332446238E-4</v>
       </c>
       <c r="O18">
-        <v>1.0536245065765097E-4</v>
+        <v>9.186912151973767E-5</v>
       </c>
       <c r="P18">
-        <v>1.6708737659502029E-4</v>
+        <v>1.3345288736898786E-4</v>
       </c>
       <c r="Q18">
-        <v>2.995874629758579E-3</v>
+        <v>2.4849603957492264E-3</v>
       </c>
       <c r="R18">
-        <v>3.0199797877742329E-3</v>
+        <v>2.506734023401771E-3</v>
       </c>
       <c r="S18">
-        <v>3.4994759041610548E-3</v>
+        <v>2.8984389184299876E-3</v>
       </c>
       <c r="T18">
-        <v>3.3815273007693205E-3</v>
+        <v>2.8003534779872797E-3</v>
       </c>
       <c r="U18">
-        <v>-8.7962845326113005E-5</v>
+        <v>-2.6493501405857635E-6</v>
       </c>
       <c r="V18">
-        <v>-1.3968915017133701E-4</v>
+        <v>-6.2483699556606088E-5</v>
       </c>
       <c r="W18">
-        <v>-1.3167404671813948E-4</v>
+        <v>-1.0369238715898072E-4</v>
       </c>
       <c r="X18">
-        <v>-1.0909908728926526E-4</v>
+        <v>-5.849682456572755E-5</v>
       </c>
       <c r="Y18">
-        <v>1.8413231915007761E-5</v>
+        <v>1.5792307946028419E-5</v>
       </c>
       <c r="Z18">
-        <v>-3.2762476024829332E-5</v>
+        <v>-3.5344530999882606E-5</v>
       </c>
       <c r="AA18">
-        <v>2.8717852274097802E-6</v>
+        <v>-8.3351670455240542E-6</v>
       </c>
       <c r="AB18">
-        <v>1.3706657989752576E-5</v>
+        <v>6.5674193553907651E-6</v>
       </c>
       <c r="AC18">
-        <v>4.9722036481609491E-7</v>
+        <v>-2.0258418253910342E-6</v>
       </c>
       <c r="AD18">
-        <v>-3.834371698435592E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+        <v>6.752607974700703E-5</v>
+      </c>
+      <c r="AE18">
+        <v>-3.3611689229033317E-7</v>
+      </c>
+      <c r="AF18">
+        <v>-3.1856111227477613E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B19">
-        <v>7.7842035515172719E-3</v>
+      <c r="B19" s="6">
+        <v>2.3934022264845672E-2</v>
       </c>
       <c r="C19">
-        <v>3.5170058560448974E-6</v>
+        <v>-4.1099230617279079E-6</v>
       </c>
       <c r="D19">
-        <v>4.1459971445692779E-5</v>
+        <v>3.6198531684215224E-5</v>
       </c>
       <c r="E19">
-        <v>-2.8023874667571718E-7</v>
+        <v>-2.4700576253227272E-7</v>
       </c>
       <c r="F19">
-        <v>1.1466894920357019E-5</v>
+        <v>-2.7507763102295051E-4</v>
       </c>
       <c r="G19">
-        <v>2.5774875730491921E-5</v>
+        <v>-1.7358097105547648E-5</v>
       </c>
       <c r="H19">
-        <v>-3.1425977872665131E-5</v>
+        <v>-2.8559355109323263E-5</v>
       </c>
       <c r="I19">
-        <v>-7.1143917940326038E-5</v>
+        <v>1.0697093887855949E-4</v>
       </c>
       <c r="J19">
-        <v>-1.335729036162312E-5</v>
+        <v>-3.7703313695079395E-5</v>
       </c>
       <c r="K19">
-        <v>2.6184620062973465E-5</v>
+        <v>-9.3680321652187806E-7</v>
       </c>
       <c r="L19">
-        <v>1.3760995302645535E-4</v>
+        <v>-1.5041222732224869E-5</v>
       </c>
       <c r="M19">
-        <v>-2.669784840277729E-5</v>
+        <v>-2.1236694296571188E-5</v>
       </c>
       <c r="N19">
-        <v>2.6904788192767121E-4</v>
+        <v>1.9755704859967965E-4</v>
       </c>
       <c r="O19">
-        <v>1.9920600446616865E-4</v>
+        <v>1.5834570294455218E-4</v>
       </c>
       <c r="P19">
-        <v>3.4036597496612148E-4</v>
+        <v>2.5719731884120769E-4</v>
       </c>
       <c r="Q19">
-        <v>2.9896034276769689E-3</v>
+        <v>2.4799319124073939E-3</v>
       </c>
       <c r="R19">
-        <v>3.0333347176274171E-3</v>
+        <v>2.507870102597066E-3</v>
       </c>
       <c r="S19">
-        <v>3.3815273007693205E-3</v>
+        <v>2.8003534779872797E-3</v>
       </c>
       <c r="T19">
-        <v>4.2258901398387885E-3</v>
+        <v>3.5276159721449145E-3</v>
       </c>
       <c r="U19">
-        <v>-7.9649070402374464E-5</v>
+        <v>-4.1273467810006535E-6</v>
       </c>
       <c r="V19">
-        <v>-6.611164103573745E-5</v>
+        <v>2.8276570704542962E-5</v>
       </c>
       <c r="W19">
-        <v>-6.2646978597321365E-5</v>
+        <v>-5.1483743313882621E-5</v>
       </c>
       <c r="X19">
-        <v>-5.9206227656681066E-6</v>
+        <v>-1.2265259181800769E-5</v>
       </c>
       <c r="Y19">
-        <v>4.740866892594803E-6</v>
+        <v>2.3297135660117502E-6</v>
       </c>
       <c r="Z19">
-        <v>-3.598999923486393E-5</v>
+        <v>-3.0312525694763223E-5</v>
       </c>
       <c r="AA19">
-        <v>8.1500266957907144E-6</v>
+        <v>-2.3403420796104741E-5</v>
       </c>
       <c r="AB19">
-        <v>3.6135183751034861E-5</v>
+        <v>1.1939586542608627E-5</v>
       </c>
       <c r="AC19">
-        <v>-8.853157101686767E-6</v>
+        <v>-2.2717860644498383E-6</v>
       </c>
       <c r="AD19">
-        <v>-4.713237696354261E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+        <v>-4.6716083897256524E-5</v>
+      </c>
+      <c r="AE19">
+        <v>5.666123359223577E-5</v>
+      </c>
+      <c r="AF19">
+        <v>-3.9954826857544912E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B20">
-        <v>-1.432253830919021E-3</v>
+      <c r="B20" s="6">
+        <v>8.8140539864150338E-2</v>
       </c>
       <c r="C20">
-        <v>-1.9610703433109654E-5</v>
+        <v>-1.3981286494577787E-5</v>
       </c>
       <c r="D20">
-        <v>-5.687953819296774E-6</v>
+        <v>-1.8814284194357351E-6</v>
       </c>
       <c r="E20">
-        <v>8.505038219615223E-8</v>
+        <v>2.9811262373310289E-8</v>
       </c>
       <c r="F20">
-        <v>7.0203204770739988E-5</v>
+        <v>2.3591377229256484E-5</v>
       </c>
       <c r="G20">
-        <v>2.5123895869876286E-5</v>
+        <v>8.2160185616861683E-6</v>
       </c>
       <c r="H20">
-        <v>4.4560815378446416E-5</v>
+        <v>2.6873429866827936E-5</v>
       </c>
       <c r="I20">
-        <v>8.8394357190585507E-5</v>
+        <v>1.0205244677894429E-4</v>
       </c>
       <c r="J20">
-        <v>8.0735413247921077E-5</v>
+        <v>1.9904369851197389E-5</v>
       </c>
       <c r="K20">
-        <v>4.9265290693418498E-5</v>
+        <v>4.0349012503588296E-6</v>
       </c>
       <c r="L20">
-        <v>1.2168511698483244E-4</v>
+        <v>9.2245069888900624E-5</v>
       </c>
       <c r="M20">
-        <v>1.8623344748680071E-4</v>
+        <v>1.388670797310177E-4</v>
       </c>
       <c r="N20">
-        <v>2.2918808233293579E-5</v>
+        <v>-1.375358655762875E-5</v>
       </c>
       <c r="O20">
-        <v>4.8131331374545524E-5</v>
+        <v>-1.0816475358226848E-5</v>
       </c>
       <c r="P20">
-        <v>2.1754826164116159E-5</v>
+        <v>-2.0669582481813693E-5</v>
       </c>
       <c r="Q20">
-        <v>-4.4002262691528432E-5</v>
+        <v>4.433926111909592E-5</v>
       </c>
       <c r="R20">
-        <v>-1.0087639555631808E-4</v>
+        <v>2.4467536920440747E-5</v>
       </c>
       <c r="S20">
-        <v>-8.7962845326113005E-5</v>
+        <v>-2.6493501405857635E-6</v>
       </c>
       <c r="T20">
-        <v>-7.9649070402374464E-5</v>
+        <v>-4.1273467810006535E-6</v>
       </c>
       <c r="U20">
-        <v>1.1230038894904713E-3</v>
+        <v>9.0228050605490402E-4</v>
       </c>
       <c r="V20">
-        <v>7.3207358801855146E-4</v>
+        <v>5.1444346911600262E-4</v>
       </c>
       <c r="W20">
-        <v>7.5975323077722161E-4</v>
+        <v>5.2150389919298915E-4</v>
       </c>
       <c r="X20">
-        <v>7.961010533673507E-4</v>
+        <v>5.0432641836382235E-4</v>
       </c>
       <c r="Y20">
-        <v>-4.7274924866088596E-5</v>
+        <v>-3.3948994390590765E-5</v>
       </c>
       <c r="Z20">
-        <v>-2.1077333874939307E-5</v>
+        <v>3.5798099799764181E-5</v>
       </c>
       <c r="AA20">
-        <v>-5.5762633972294582E-6</v>
+        <v>-1.1359180208115721E-5</v>
       </c>
       <c r="AB20">
-        <v>3.9058225289171668E-6</v>
+        <v>-1.6261245216091192E-5</v>
       </c>
       <c r="AC20">
-        <v>-9.7108333139442565E-7</v>
+        <v>-9.958077716404562E-8</v>
       </c>
       <c r="AD20">
-        <v>-5.9701550402020752E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>-5.2402889968273024E-5</v>
+      </c>
+      <c r="AE20">
+        <v>2.2541418557660658E-5</v>
+      </c>
+      <c r="AF20">
+        <v>-4.7705178291751645E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B21">
-        <v>-5.8268169713516761E-2</v>
+      <c r="B21" s="6">
+        <v>1.5149212858773754E-2</v>
       </c>
       <c r="C21">
-        <v>-2.8351947015890952E-5</v>
+        <v>-1.9308154917156596E-5</v>
       </c>
       <c r="D21">
-        <v>-1.4073407875142426E-5</v>
+        <v>-8.2288069076880936E-6</v>
       </c>
       <c r="E21">
-        <v>2.3554743986876129E-7</v>
+        <v>1.5728374752553908E-7</v>
       </c>
       <c r="F21">
-        <v>5.9330190637222631E-5</v>
+        <v>-3.9772676508854671E-5</v>
       </c>
       <c r="G21">
-        <v>2.0488603388563273E-4</v>
+        <v>1.612450834908835E-4</v>
       </c>
       <c r="H21">
-        <v>1.0248486911169929E-4</v>
+        <v>6.2458224815344418E-5</v>
       </c>
       <c r="I21">
-        <v>2.6619894000028756E-4</v>
+        <v>1.8124935647922884E-4</v>
       </c>
       <c r="J21">
-        <v>1.8867680076309804E-4</v>
+        <v>1.3299448873952237E-4</v>
       </c>
       <c r="K21">
-        <v>2.5068920601640946E-4</v>
+        <v>1.7464451032239773E-4</v>
       </c>
       <c r="L21">
-        <v>3.1280571116906015E-4</v>
+        <v>2.2815653864731463E-4</v>
       </c>
       <c r="M21">
-        <v>6.0333186073440663E-4</v>
+        <v>5.3294749184469592E-4</v>
       </c>
       <c r="N21">
-        <v>3.1181249931265943E-4</v>
+        <v>2.5316097880959278E-4</v>
       </c>
       <c r="O21">
-        <v>6.9848962494340304E-5</v>
+        <v>4.9234675852413744E-5</v>
       </c>
       <c r="P21">
-        <v>5.7269925868806716E-5</v>
+        <v>4.7032310630458062E-5</v>
       </c>
       <c r="Q21">
-        <v>-4.3001309074033352E-5</v>
+        <v>5.289306651788038E-6</v>
       </c>
       <c r="R21">
-        <v>-1.7115661792587816E-4</v>
+        <v>-7.4555641353073833E-5</v>
       </c>
       <c r="S21">
-        <v>-1.3968915017133701E-4</v>
+        <v>-6.2483699556606088E-5</v>
       </c>
       <c r="T21">
-        <v>-6.611164103573745E-5</v>
+        <v>2.8276570704542962E-5</v>
       </c>
       <c r="U21">
-        <v>7.3207358801855146E-4</v>
+        <v>5.1444346911600262E-4</v>
       </c>
       <c r="V21">
-        <v>1.543177171337341E-3</v>
+        <v>1.1989553586635451E-3</v>
       </c>
       <c r="W21">
-        <v>1.2894325302710459E-3</v>
+        <v>9.9982974912145176E-4</v>
       </c>
       <c r="X21">
-        <v>1.4339579931072015E-3</v>
+        <v>1.0662174867650683E-3</v>
       </c>
       <c r="Y21">
-        <v>-8.1550957982710496E-5</v>
+        <v>-6.5177486031302298E-5</v>
       </c>
       <c r="Z21">
-        <v>-5.5788672486054048E-6</v>
+        <v>2.8073491595764246E-5</v>
       </c>
       <c r="AA21">
-        <v>-3.926421203958772E-6</v>
+        <v>-9.7789035138431154E-6</v>
       </c>
       <c r="AB21">
-        <v>-7.2228634225533772E-6</v>
+        <v>-1.0368649496181087E-5</v>
       </c>
       <c r="AC21">
-        <v>-6.8674560454065847E-6</v>
+        <v>-3.487320165542538E-6</v>
       </c>
       <c r="AD21">
-        <v>-1.1386516811092602E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+        <v>-1.0615349717230036E-4</v>
+      </c>
+      <c r="AE21">
+        <v>6.1266705022367329E-5</v>
+      </c>
+      <c r="AF21">
+        <v>-1.0131396859020566E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22">
-        <v>-5.8503194852529403E-2</v>
+      <c r="B22" s="6">
+        <v>3.9150561681355597E-2</v>
       </c>
       <c r="C22">
-        <v>-1.7903565143688481E-5</v>
+        <v>-1.523827417373022E-5</v>
       </c>
       <c r="D22">
-        <v>-1.7997999608136259E-5</v>
+        <v>-1.482090114733809E-5</v>
       </c>
       <c r="E22">
-        <v>2.8003819889970642E-7</v>
+        <v>2.2921527888366501E-7</v>
       </c>
       <c r="F22">
-        <v>-3.9636169228579539E-5</v>
+        <v>-1.2895993894914277E-4</v>
       </c>
       <c r="G22">
-        <v>4.9138176358450817E-4</v>
+        <v>3.8902067014318813E-4</v>
       </c>
       <c r="H22">
-        <v>1.3468779257072976E-4</v>
+        <v>1.3334603609410352E-4</v>
       </c>
       <c r="I22">
-        <v>6.675023678288281E-4</v>
+        <v>5.7945650349161819E-4</v>
       </c>
       <c r="J22">
-        <v>5.2330911044234051E-4</v>
+        <v>5.1167453788495548E-4</v>
       </c>
       <c r="K22">
-        <v>4.4570093925508304E-4</v>
+        <v>3.6340500527805964E-4</v>
       </c>
       <c r="L22">
-        <v>5.4092170484564949E-4</v>
+        <v>5.7900358431576084E-4</v>
       </c>
       <c r="M22">
-        <v>8.7711961535056325E-4</v>
+        <v>8.2954096165262399E-4</v>
       </c>
       <c r="N22">
-        <v>6.534943117463088E-4</v>
+        <v>5.7746229607549457E-4</v>
       </c>
       <c r="O22">
-        <v>8.93717942027804E-5</v>
+        <v>9.9882044977447768E-5</v>
       </c>
       <c r="P22">
-        <v>1.4335301690129859E-4</v>
+        <v>1.5594186404796289E-4</v>
       </c>
       <c r="Q22">
-        <v>-7.2348442458853917E-6</v>
+        <v>6.8487959581042769E-6</v>
       </c>
       <c r="R22">
-        <v>-1.4505285668995805E-4</v>
+        <v>-7.5538237206049502E-5</v>
       </c>
       <c r="S22">
-        <v>-1.3167404671813948E-4</v>
+        <v>-1.0369238715898072E-4</v>
       </c>
       <c r="T22">
-        <v>-6.2646978597321365E-5</v>
+        <v>-5.1483743313882621E-5</v>
       </c>
       <c r="U22">
-        <v>7.5975323077722161E-4</v>
+        <v>5.2150389919298915E-4</v>
       </c>
       <c r="V22">
-        <v>1.2894325302710459E-3</v>
+        <v>9.9982974912145176E-4</v>
       </c>
       <c r="W22">
-        <v>2.1762188421693904E-3</v>
+        <v>1.7410897250674383E-3</v>
       </c>
       <c r="X22">
-        <v>1.9364495606816684E-3</v>
+        <v>1.5848840601202477E-3</v>
       </c>
       <c r="Y22">
-        <v>-4.7623960717977036E-5</v>
+        <v>-5.6453861764715648E-5</v>
       </c>
       <c r="Z22">
-        <v>-2.5911424923522912E-5</v>
+        <v>3.3144177741351795E-5</v>
       </c>
       <c r="AA22">
-        <v>-3.1830909818298335E-5</v>
+        <v>-9.3644205199404709E-6</v>
       </c>
       <c r="AB22">
-        <v>-2.8686340434021457E-6</v>
+        <v>1.0712647083803331E-5</v>
       </c>
       <c r="AC22">
-        <v>-9.8535882423835843E-6</v>
+        <v>-7.5473090516145009E-6</v>
       </c>
       <c r="AD22">
-        <v>-1.6813031951556192E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+        <v>-1.5771213751342243E-4</v>
+      </c>
+      <c r="AE22">
+        <v>1.0295695236848939E-4</v>
+      </c>
+      <c r="AF22">
+        <v>-1.442498001800423E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B23">
-        <v>-2.5048746384850627E-2</v>
+      <c r="B23" s="6">
+        <v>7.1513546154983065E-2</v>
       </c>
       <c r="C23">
-        <v>-6.2932608195010901E-6</v>
+        <v>-1.9452255932932666E-5</v>
       </c>
       <c r="D23">
-        <v>-1.809614851394841E-5</v>
+        <v>-1.2886406971670846E-5</v>
       </c>
       <c r="E23">
-        <v>2.859890011933483E-7</v>
+        <v>2.0862451417067961E-7</v>
       </c>
       <c r="F23">
-        <v>4.5841628705401295E-5</v>
+        <v>8.2629176605217156E-5</v>
       </c>
       <c r="G23">
-        <v>6.6116837327779936E-4</v>
+        <v>6.1072752024863002E-4</v>
       </c>
       <c r="H23">
-        <v>2.3532229800605405E-4</v>
+        <v>2.6922024676318175E-4</v>
       </c>
       <c r="I23">
-        <v>7.8517417964620788E-4</v>
+        <v>7.218447301684252E-4</v>
       </c>
       <c r="J23">
-        <v>7.2249231921210633E-4</v>
+        <v>7.3501857717335277E-4</v>
       </c>
       <c r="K23">
-        <v>6.1770042698187531E-4</v>
+        <v>5.595040594349968E-4</v>
       </c>
       <c r="L23">
-        <v>8.1904543504798897E-4</v>
+        <v>7.9068721815513218E-4</v>
       </c>
       <c r="M23">
-        <v>9.8391886714822006E-4</v>
+        <v>9.119976310057766E-4</v>
       </c>
       <c r="N23">
-        <v>8.0464783959886691E-4</v>
+        <v>7.1406119885095121E-4</v>
       </c>
       <c r="O23">
-        <v>2.702652556161179E-4</v>
+        <v>2.2652806341546253E-4</v>
       </c>
       <c r="P23">
-        <v>3.252408949891934E-4</v>
+        <v>3.0208941330977634E-4</v>
       </c>
       <c r="Q23">
-        <v>-5.7461587788532336E-6</v>
+        <v>2.100701636059411E-5</v>
       </c>
       <c r="R23">
-        <v>-1.2827309140040882E-4</v>
+        <v>-4.7356719954797899E-5</v>
       </c>
       <c r="S23">
-        <v>-1.0909908728926526E-4</v>
+        <v>-5.849682456572755E-5</v>
       </c>
       <c r="T23">
-        <v>-5.9206227656681066E-6</v>
+        <v>-1.2265259181800769E-5</v>
       </c>
       <c r="U23">
-        <v>7.961010533673507E-4</v>
+        <v>5.0432641836382235E-4</v>
       </c>
       <c r="V23">
-        <v>1.4339579931072015E-3</v>
+        <v>1.0662174867650683E-3</v>
       </c>
       <c r="W23">
-        <v>1.9364495606816684E-3</v>
+        <v>1.5848840601202477E-3</v>
       </c>
       <c r="X23">
-        <v>2.6881786865619772E-3</v>
+        <v>2.2117515700315052E-3</v>
       </c>
       <c r="Y23">
-        <v>-7.4681090492866061E-5</v>
+        <v>-5.8782344632624868E-5</v>
       </c>
       <c r="Z23">
-        <v>-6.90795387540385E-5</v>
+        <v>3.8463700488807016E-6</v>
       </c>
       <c r="AA23">
-        <v>3.5995399121339531E-5</v>
+        <v>2.2441117131297714E-5</v>
       </c>
       <c r="AB23">
-        <v>9.6756427574099099E-5</v>
+        <v>5.852783205969464E-5</v>
       </c>
       <c r="AC23">
-        <v>-9.7392316492405707E-6</v>
+        <v>-4.0272992666790587E-6</v>
       </c>
       <c r="AD23">
-        <v>-2.2536634477345464E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>-1.6545895728900067E-4</v>
+      </c>
+      <c r="AE23">
+        <v>-8.5988906884323358E-6</v>
+      </c>
+      <c r="AF23">
+        <v>-2.0151596588177632E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B24">
-        <v>-3.7969906055846901E-2</v>
+      <c r="B24" s="6">
+        <v>-4.2449091781786984E-2</v>
       </c>
       <c r="C24">
-        <v>1.1647246696488665E-5</v>
+        <v>6.682599706504147E-6</v>
       </c>
       <c r="D24">
-        <v>-3.125953126768938E-7</v>
+        <v>2.1846421668756831E-7</v>
       </c>
       <c r="E24">
-        <v>-3.8081024578865059E-9</v>
+        <v>-8.1968266538305633E-9</v>
       </c>
       <c r="F24">
-        <v>-1.2469244340695436E-4</v>
+        <v>-9.8140874761658243E-5</v>
       </c>
       <c r="G24">
-        <v>5.8113102953187524E-6</v>
+        <v>5.040745560277272E-6</v>
       </c>
       <c r="H24">
-        <v>-2.4799669389196739E-5</v>
+        <v>-1.3179829545148831E-5</v>
       </c>
       <c r="I24">
-        <v>-7.746464724032552E-5</v>
+        <v>-9.9672813840503402E-5</v>
       </c>
       <c r="J24">
-        <v>-2.8319420335645601E-5</v>
+        <v>-1.5223236640478236E-5</v>
       </c>
       <c r="K24">
-        <v>-1.1649044822977168E-5</v>
+        <v>-7.6692995024603189E-6</v>
       </c>
       <c r="L24">
-        <v>-9.1124267502424417E-5</v>
+        <v>-1.0010507995308898E-4</v>
       </c>
       <c r="M24">
-        <v>-4.59493556410208E-5</v>
+        <v>-3.4438736618426058E-5</v>
       </c>
       <c r="N24">
-        <v>-9.1918582762697578E-6</v>
+        <v>-1.2155994229546817E-5</v>
       </c>
       <c r="O24">
-        <v>-5.745202019215084E-7</v>
+        <v>1.4116038952588224E-6</v>
       </c>
       <c r="P24">
-        <v>3.750749272439879E-6</v>
+        <v>3.5182159059945285E-6</v>
       </c>
       <c r="Q24">
-        <v>4.345699938701562E-6</v>
+        <v>2.117072085645389E-6</v>
       </c>
       <c r="R24">
-        <v>1.7585199453686831E-5</v>
+        <v>1.2757373651012325E-5</v>
       </c>
       <c r="S24">
-        <v>1.8413231915007761E-5</v>
+        <v>1.5792307946028419E-5</v>
       </c>
       <c r="T24">
-        <v>4.740866892594803E-6</v>
+        <v>2.3297135660117502E-6</v>
       </c>
       <c r="U24">
-        <v>-4.7274924866088596E-5</v>
+        <v>-3.3948994390590765E-5</v>
       </c>
       <c r="V24">
-        <v>-8.1550957982710496E-5</v>
+        <v>-6.5177486031302298E-5</v>
       </c>
       <c r="W24">
-        <v>-4.7623960717977036E-5</v>
+        <v>-5.6453861764715648E-5</v>
       </c>
       <c r="X24">
-        <v>-7.4681090492866061E-5</v>
+        <v>-5.8782344632624868E-5</v>
       </c>
       <c r="Y24">
-        <v>5.0799627194016354E-5</v>
+        <v>4.3636214899108898E-5</v>
       </c>
       <c r="Z24">
-        <v>2.2715097038470133E-5</v>
+        <v>1.2098008761402535E-5</v>
       </c>
       <c r="AA24">
-        <v>-1.8196391516843783E-5</v>
+        <v>-1.1253189458547826E-5</v>
       </c>
       <c r="AB24">
-        <v>-2.5462931566400986E-5</v>
+        <v>-1.8217334604243346E-5</v>
       </c>
       <c r="AC24">
-        <v>1.6113897047876372E-6</v>
+        <v>1.6383438324018627E-6</v>
       </c>
       <c r="AD24">
-        <v>2.3087186717192971E-5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+        <v>-4.2782382805439441E-6</v>
+      </c>
+      <c r="AE24">
+        <v>-1.5549886975636167E-5</v>
+      </c>
+      <c r="AF24">
+        <v>7.4947756806971391E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25">
-        <v>2.8206687266242949</v>
+      <c r="B25" s="6">
+        <v>2.8432923775533983</v>
       </c>
       <c r="C25">
-        <v>-7.1833626879621248E-6</v>
+        <v>-8.6961027884613797E-6</v>
       </c>
       <c r="D25">
-        <v>-3.6333345186804788E-6</v>
+        <v>-3.104038004936691E-6</v>
       </c>
       <c r="E25">
-        <v>2.2846286847226332E-8</v>
+        <v>1.8155915324204723E-8</v>
       </c>
       <c r="F25">
-        <v>6.4781398482184521E-5</v>
+        <v>3.386067192100094E-5</v>
       </c>
       <c r="G25">
-        <v>-3.0125241689514052E-5</v>
+        <v>-1.711185554365352E-5</v>
       </c>
       <c r="H25">
-        <v>2.1052785955505052E-5</v>
+        <v>9.4301562577634248E-7</v>
       </c>
       <c r="I25">
-        <v>1.2448790341160182E-4</v>
+        <v>6.622323751116104E-6</v>
       </c>
       <c r="J25">
-        <v>4.745260777046871E-5</v>
+        <v>4.6818946185943748E-5</v>
       </c>
       <c r="K25">
-        <v>5.7698711555164429E-6</v>
+        <v>3.3719310292758698E-6</v>
       </c>
       <c r="L25">
-        <v>-7.9578593696511769E-6</v>
+        <v>3.2769022809502724E-6</v>
       </c>
       <c r="M25">
-        <v>-7.1708992522854958E-5</v>
+        <v>-4.0324097880234681E-5</v>
       </c>
       <c r="N25">
-        <v>1.2135547101695217E-5</v>
+        <v>1.9646795530450523E-5</v>
       </c>
       <c r="O25">
-        <v>-1.0436390166290389E-5</v>
+        <v>-1.6875388168956007E-6</v>
       </c>
       <c r="P25">
-        <v>9.7194984517920481E-6</v>
+        <v>1.3148456104460112E-5</v>
       </c>
       <c r="Q25">
-        <v>-4.5790092608613304E-5</v>
+        <v>-3.2036442491227514E-5</v>
       </c>
       <c r="R25">
-        <v>-1.1768744238756167E-5</v>
+        <v>-8.8683372145694026E-6</v>
       </c>
       <c r="S25">
-        <v>-3.2762476024829332E-5</v>
+        <v>-3.5344530999882606E-5</v>
       </c>
       <c r="T25">
-        <v>-3.598999923486393E-5</v>
+        <v>-3.0312525694763223E-5</v>
       </c>
       <c r="U25">
-        <v>-2.1077333874939307E-5</v>
+        <v>3.5798099799764181E-5</v>
       </c>
       <c r="V25">
-        <v>-5.5788672486054048E-6</v>
+        <v>2.8073491595764246E-5</v>
       </c>
       <c r="W25">
-        <v>-2.5911424923522912E-5</v>
+        <v>3.3144177741351795E-5</v>
       </c>
       <c r="X25">
-        <v>-6.90795387540385E-5</v>
+        <v>3.8463700488807016E-6</v>
       </c>
       <c r="Y25">
-        <v>2.2715097038470133E-5</v>
+        <v>1.2098008761402535E-5</v>
       </c>
       <c r="Z25">
-        <v>6.4620624257407397E-4</v>
+        <v>5.5659569740079413E-4</v>
       </c>
       <c r="AA25">
-        <v>-4.3860425802981081E-5</v>
+        <v>-1.2693489589136656E-5</v>
       </c>
       <c r="AB25">
-        <v>-6.0059150752220415E-5</v>
+        <v>-2.223366237902518E-5</v>
       </c>
       <c r="AC25">
-        <v>5.7389437288298666E-6</v>
+        <v>4.4565162194409993E-7</v>
       </c>
       <c r="AD25">
-        <v>-3.2456043645599748E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+        <v>-5.6599157015294611E-5</v>
+      </c>
+      <c r="AE25">
+        <v>-5.5780388958842027E-5</v>
+      </c>
+      <c r="AF25">
+        <v>-2.7540579330812356E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26">
-        <v>6.7966590948947891E-3</v>
+      <c r="B26" s="6">
+        <v>4.6054897187545817E-2</v>
       </c>
       <c r="C26">
-        <v>-1.3242873499830077E-5</v>
+        <v>-1.2886061089477157E-5</v>
       </c>
       <c r="D26">
-        <v>-5.4659309063974479E-6</v>
+        <v>-5.0581567549761374E-6</v>
       </c>
       <c r="E26">
-        <v>7.072236723403303E-8</v>
+        <v>6.0599809375043685E-8</v>
       </c>
       <c r="F26">
-        <v>1.5051387712596877E-4</v>
+        <v>3.7327185859635764E-4</v>
       </c>
       <c r="G26">
-        <v>-1.0093410460025858E-8</v>
+        <v>5.5653013713087324E-6</v>
       </c>
       <c r="H26">
-        <v>3.7732147862168429E-5</v>
+        <v>3.0852555173356663E-5</v>
       </c>
       <c r="I26">
-        <v>4.6878236900928E-5</v>
+        <v>4.6013995447695541E-5</v>
       </c>
       <c r="J26">
-        <v>6.9045560613391647E-5</v>
+        <v>7.8084712406952732E-5</v>
       </c>
       <c r="K26">
-        <v>9.9128954024474414E-7</v>
+        <v>8.7154523924649202E-6</v>
       </c>
       <c r="L26">
-        <v>-4.6062305475433123E-5</v>
+        <v>4.4096105756266028E-6</v>
       </c>
       <c r="M26">
-        <v>5.6456434881620816E-5</v>
+        <v>5.0308482941641315E-5</v>
       </c>
       <c r="N26">
-        <v>-7.5258279043242862E-6</v>
+        <v>3.3635200080412808E-6</v>
       </c>
       <c r="O26">
-        <v>-8.0606366586424404E-5</v>
+        <v>-6.0525083759455447E-5</v>
       </c>
       <c r="P26">
-        <v>-1.1170540711789129E-4</v>
+        <v>-8.964156174115414E-5</v>
       </c>
       <c r="Q26">
-        <v>2.2321246328270775E-6</v>
+        <v>-1.0666180632784008E-5</v>
       </c>
       <c r="R26">
-        <v>-2.9312438923120594E-5</v>
+        <v>-2.6685336070746569E-5</v>
       </c>
       <c r="S26">
-        <v>2.8717852274097802E-6</v>
+        <v>-8.3351670455240542E-6</v>
       </c>
       <c r="T26">
-        <v>8.1500266957907144E-6</v>
+        <v>-2.3403420796104741E-5</v>
       </c>
       <c r="U26">
-        <v>-5.5762633972294582E-6</v>
+        <v>-1.1359180208115721E-5</v>
       </c>
       <c r="V26">
-        <v>-3.926421203958772E-6</v>
+        <v>-9.7789035138431154E-6</v>
       </c>
       <c r="W26">
-        <v>-3.1830909818298335E-5</v>
+        <v>-9.3644205199404709E-6</v>
       </c>
       <c r="X26">
-        <v>3.5995399121339531E-5</v>
+        <v>2.2441117131297714E-5</v>
       </c>
       <c r="Y26">
-        <v>-1.8196391516843783E-5</v>
+        <v>-1.1253189458547826E-5</v>
       </c>
       <c r="Z26">
-        <v>-4.3860425802981081E-5</v>
+        <v>-1.2693489589136656E-5</v>
       </c>
       <c r="AA26">
-        <v>6.0932158886954212E-4</v>
+        <v>5.0462464775653988E-4</v>
       </c>
       <c r="AB26">
-        <v>3.7667569243945878E-4</v>
+        <v>3.0680182026225199E-4</v>
       </c>
       <c r="AC26">
-        <v>-1.2402794569501609E-5</v>
+        <v>-6.1719740776186485E-6</v>
       </c>
       <c r="AD26">
-        <v>2.0867652028259959E-5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+        <v>2.0026607643813329E-5</v>
+      </c>
+      <c r="AE26">
+        <v>-9.9898859149052887E-6</v>
+      </c>
+      <c r="AF26">
+        <v>-3.7314142012019727E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B27">
-        <v>5.3518827608091291E-2</v>
+      <c r="B27" s="6">
+        <v>8.0151908866479049E-2</v>
       </c>
       <c r="C27">
-        <v>-3.4063343145693693E-6</v>
+        <v>-6.669601378046875E-6</v>
       </c>
       <c r="D27">
-        <v>-3.6108449112757374E-6</v>
+        <v>-2.0160126882325471E-6</v>
       </c>
       <c r="E27">
-        <v>6.2457594494170826E-8</v>
+        <v>3.9198115623592033E-8</v>
       </c>
       <c r="F27">
-        <v>2.4155605615208393E-4</v>
+        <v>2.8034136879408666E-4</v>
       </c>
       <c r="G27">
-        <v>1.6989477676872364E-5</v>
+        <v>2.3969906109027966E-5</v>
       </c>
       <c r="H27">
-        <v>5.2037944284828122E-5</v>
+        <v>2.5619880390355398E-5</v>
       </c>
       <c r="I27">
-        <v>1.1539463242328475E-5</v>
+        <v>3.1664063028129848E-6</v>
       </c>
       <c r="J27">
-        <v>6.7399779323503838E-5</v>
+        <v>5.1821549757337599E-5</v>
       </c>
       <c r="K27">
-        <v>2.9078983658546633E-5</v>
+        <v>3.1557364776549118E-5</v>
       </c>
       <c r="L27">
-        <v>8.9404920027217998E-6</v>
+        <v>4.1772616336907217E-5</v>
       </c>
       <c r="M27">
-        <v>7.566786134163405E-5</v>
+        <v>6.7325347410209565E-5</v>
       </c>
       <c r="N27">
-        <v>3.1061448538532033E-7</v>
+        <v>1.2361500107295757E-5</v>
       </c>
       <c r="O27">
-        <v>-3.207100310766858E-5</v>
+        <v>-3.8036209628021023E-5</v>
       </c>
       <c r="P27">
-        <v>-6.2389965577039591E-5</v>
+        <v>-6.8067894548984743E-5</v>
       </c>
       <c r="Q27">
-        <v>1.0069743427286882E-6</v>
+        <v>-8.5215448292371137E-6</v>
       </c>
       <c r="R27">
-        <v>-1.5901169902214282E-5</v>
+        <v>-2.3390028136435976E-5</v>
       </c>
       <c r="S27">
-        <v>1.3706657989752576E-5</v>
+        <v>6.5674193553907651E-6</v>
       </c>
       <c r="T27">
-        <v>3.6135183751034861E-5</v>
+        <v>1.1939586542608627E-5</v>
       </c>
       <c r="U27">
-        <v>3.9058225289171668E-6</v>
+        <v>-1.6261245216091192E-5</v>
       </c>
       <c r="V27">
-        <v>-7.2228634225533772E-6</v>
+        <v>-1.0368649496181087E-5</v>
       </c>
       <c r="W27">
-        <v>-2.8686340434021457E-6</v>
+        <v>1.0712647083803331E-5</v>
       </c>
       <c r="X27">
-        <v>9.6756427574099099E-5</v>
+        <v>5.852783205969464E-5</v>
       </c>
       <c r="Y27">
-        <v>-2.5462931566400986E-5</v>
+        <v>-1.8217334604243346E-5</v>
       </c>
       <c r="Z27">
-        <v>-6.0059150752220415E-5</v>
+        <v>-2.223366237902518E-5</v>
       </c>
       <c r="AA27">
-        <v>3.7667569243945878E-4</v>
+        <v>3.0680182026225199E-4</v>
       </c>
       <c r="AB27">
-        <v>5.2343112008707189E-4</v>
+        <v>4.3550692541880843E-4</v>
       </c>
       <c r="AC27">
-        <v>-1.4472019947989573E-5</v>
+        <v>-5.5476243673144356E-6</v>
       </c>
       <c r="AD27">
-        <v>-1.0244896070965313E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+        <v>1.0841063147034876E-5</v>
+      </c>
+      <c r="AE27">
+        <v>1.2817260370851903E-5</v>
+      </c>
+      <c r="AF27">
+        <v>-1.8997250344791362E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B28">
-        <v>1.357176777060916E-2</v>
+      <c r="B28" s="6">
+        <v>4.1071506049096913E-3</v>
       </c>
       <c r="C28">
-        <v>-3.2189227123777386E-7</v>
+        <v>5.9861114096685321E-7</v>
       </c>
       <c r="D28">
-        <v>1.1001589113463075E-7</v>
+        <v>3.7518156103585125E-7</v>
       </c>
       <c r="E28">
-        <v>-7.9695215301163053E-9</v>
+        <v>-7.1190985662936018E-9</v>
       </c>
       <c r="F28">
-        <v>-2.1582193959812917E-5</v>
+        <v>1.7959170973855254E-5</v>
       </c>
       <c r="G28">
-        <v>1.9089802418905972E-6</v>
+        <v>1.3243172492480472E-6</v>
       </c>
       <c r="H28">
-        <v>-4.5405630521027794E-6</v>
+        <v>2.2968602649108813E-7</v>
       </c>
       <c r="I28">
-        <v>-2.2652613101717194E-5</v>
+        <v>-5.1837457478509717E-6</v>
       </c>
       <c r="J28">
-        <v>6.0515144080299258E-6</v>
+        <v>6.5327541532376592E-6</v>
       </c>
       <c r="K28">
-        <v>1.1234248720514231E-6</v>
+        <v>-2.6765373851791205E-7</v>
       </c>
       <c r="L28">
-        <v>2.1071866677422159E-6</v>
+        <v>-3.8496161507193299E-6</v>
       </c>
       <c r="M28">
-        <v>-1.2443696482285964E-5</v>
+        <v>-4.8233395742373452E-6</v>
       </c>
       <c r="N28">
-        <v>5.1507851540163367E-6</v>
+        <v>3.8127271874019116E-6</v>
       </c>
       <c r="O28">
-        <v>-2.7066710404196123E-6</v>
+        <v>-1.2668521360974E-6</v>
       </c>
       <c r="P28">
-        <v>-1.5644579949693563E-6</v>
+        <v>-1.2082071356331214E-6</v>
       </c>
       <c r="Q28">
-        <v>2.6130965551010425E-6</v>
+        <v>4.4146921665492306E-6</v>
       </c>
       <c r="R28">
-        <v>1.4002269469135529E-6</v>
+        <v>8.0756800444292632E-7</v>
       </c>
       <c r="S28">
-        <v>4.9722036481609491E-7</v>
+        <v>-2.0258418253910342E-6</v>
       </c>
       <c r="T28">
-        <v>-8.853157101686767E-6</v>
+        <v>-2.2717860644498383E-6</v>
       </c>
       <c r="U28">
-        <v>-9.7108333139442565E-7</v>
+        <v>-9.958077716404562E-8</v>
       </c>
       <c r="V28">
-        <v>-6.8674560454065847E-6</v>
+        <v>-3.487320165542538E-6</v>
       </c>
       <c r="W28">
-        <v>-9.8535882423835843E-6</v>
+        <v>-7.5473090516145009E-6</v>
       </c>
       <c r="X28">
-        <v>-9.7392316492405707E-6</v>
+        <v>-4.0272992666790587E-6</v>
       </c>
       <c r="Y28">
-        <v>1.6113897047876372E-6</v>
+        <v>1.6383438324018627E-6</v>
       </c>
       <c r="Z28">
-        <v>5.7389437288298666E-6</v>
+        <v>4.4565162194409993E-7</v>
       </c>
       <c r="AA28">
-        <v>-1.2402794569501609E-5</v>
+        <v>-6.1719740776186485E-6</v>
       </c>
       <c r="AB28">
-        <v>-1.4472019947989573E-5</v>
+        <v>-5.5476243673144356E-6</v>
       </c>
       <c r="AC28">
-        <v>8.5142059127245173E-6</v>
+        <v>4.8647995300456807E-6</v>
       </c>
       <c r="AD28">
-        <v>-9.6137958120475717E-5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+        <v>-2.3237488894480944E-5</v>
+      </c>
+      <c r="AE28">
+        <v>-2.8455874181788892E-5</v>
+      </c>
+      <c r="AF28">
+        <v>-6.8296168672395141E-5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="6">
+        <v>0.16192703087540006</v>
+      </c>
+      <c r="C29">
+        <v>1.5741945028437724E-5</v>
+      </c>
+      <c r="D29">
+        <v>-1.7575548836117863E-7</v>
+      </c>
+      <c r="E29">
+        <v>-1.8019512157463056E-8</v>
+      </c>
+      <c r="F29">
+        <v>-3.0278756010854559E-4</v>
+      </c>
+      <c r="G29">
+        <v>-4.0289262114165571E-5</v>
+      </c>
+      <c r="H29">
+        <v>-6.6171477147255206E-5</v>
+      </c>
+      <c r="I29">
+        <v>-1.1463574745298991E-4</v>
+      </c>
+      <c r="J29">
+        <v>-5.3631414669679333E-5</v>
+      </c>
+      <c r="K29">
+        <v>-2.9004385335351134E-5</v>
+      </c>
+      <c r="L29">
+        <v>-1.0093830540333209E-4</v>
+      </c>
+      <c r="M29">
+        <v>-1.1597601153888183E-4</v>
+      </c>
+      <c r="N29">
+        <v>-1.3809609752967548E-5</v>
+      </c>
+      <c r="O29">
+        <v>-4.7670315417004055E-5</v>
+      </c>
+      <c r="P29">
+        <v>-4.0465924059029273E-5</v>
+      </c>
+      <c r="Q29">
+        <v>-1.8734728239342216E-6</v>
+      </c>
+      <c r="R29">
+        <v>-1.2482152471419137E-6</v>
+      </c>
+      <c r="S29">
+        <v>6.752607974700703E-5</v>
+      </c>
+      <c r="T29">
+        <v>-4.6716083897256524E-5</v>
+      </c>
+      <c r="U29">
+        <v>-5.2402889968273024E-5</v>
+      </c>
+      <c r="V29">
+        <v>-1.0615349717230036E-4</v>
+      </c>
+      <c r="W29">
+        <v>-1.5771213751342243E-4</v>
+      </c>
+      <c r="X29">
+        <v>-1.6545895728900067E-4</v>
+      </c>
+      <c r="Y29">
+        <v>-4.2782382805439441E-6</v>
+      </c>
+      <c r="Z29">
+        <v>-5.6599157015294611E-5</v>
+      </c>
+      <c r="AA29">
+        <v>2.0026607643813329E-5</v>
+      </c>
+      <c r="AB29">
+        <v>1.0841063147034876E-5</v>
+      </c>
+      <c r="AC29">
+        <v>-2.3237488894480944E-5</v>
+      </c>
+      <c r="AD29">
+        <v>1.6337969336835793E-3</v>
+      </c>
+      <c r="AE29">
+        <v>2.689985228118169E-4</v>
+      </c>
+      <c r="AF29">
+        <v>5.3379861089138938E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.10050018487716927</v>
+      </c>
+      <c r="C30">
+        <v>-3.3689292983417213E-5</v>
+      </c>
+      <c r="D30">
+        <v>1.1199894597712036E-5</v>
+      </c>
+      <c r="E30">
+        <v>-1.0084661403675593E-7</v>
+      </c>
+      <c r="F30">
+        <v>-6.0076710280574318E-5</v>
+      </c>
+      <c r="G30">
+        <v>1.4552064218746746E-5</v>
+      </c>
+      <c r="H30">
+        <v>-4.6258467120653969E-5</v>
+      </c>
+      <c r="I30">
+        <v>1.4392737378378517E-4</v>
+      </c>
+      <c r="J30">
+        <v>6.8231935754350299E-5</v>
+      </c>
+      <c r="K30">
+        <v>2.8755090399975678E-5</v>
+      </c>
+      <c r="L30">
+        <v>-3.8256135373335989E-5</v>
+      </c>
+      <c r="M30">
+        <v>1.5171149411297291E-4</v>
+      </c>
+      <c r="N30">
+        <v>4.1816817727777758E-5</v>
+      </c>
+      <c r="O30">
+        <v>-2.9889627507737122E-5</v>
+      </c>
+      <c r="P30">
+        <v>-4.4105347839170782E-5</v>
+      </c>
+      <c r="Q30">
+        <v>-2.4229861176849004E-5</v>
+      </c>
+      <c r="R30">
+        <v>3.3046977193188873E-6</v>
+      </c>
+      <c r="S30">
+        <v>-3.3611689229033317E-7</v>
+      </c>
+      <c r="T30">
+        <v>5.666123359223577E-5</v>
+      </c>
+      <c r="U30">
+        <v>2.2541418557660658E-5</v>
+      </c>
+      <c r="V30">
+        <v>6.1266705022367329E-5</v>
+      </c>
+      <c r="W30">
+        <v>1.0295695236848939E-4</v>
+      </c>
+      <c r="X30">
+        <v>-8.5988906884323358E-6</v>
+      </c>
+      <c r="Y30">
+        <v>-1.5549886975636167E-5</v>
+      </c>
+      <c r="Z30">
+        <v>-5.5780388958842027E-5</v>
+      </c>
+      <c r="AA30">
+        <v>-9.9898859149052887E-6</v>
+      </c>
+      <c r="AB30">
+        <v>1.2817260370851903E-5</v>
+      </c>
+      <c r="AC30">
+        <v>-2.8455874181788892E-5</v>
+      </c>
+      <c r="AD30">
+        <v>2.689985228118169E-4</v>
+      </c>
+      <c r="AE30">
+        <v>2.5047228587938702E-3</v>
+      </c>
+      <c r="AF30">
+        <v>9.2145356426145562E-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B29">
-        <v>-1.4752424918368394</v>
-      </c>
-      <c r="C29">
-        <v>-2.0780715512158302E-4</v>
-      </c>
-      <c r="D29">
-        <v>-4.4016616110077744E-4</v>
-      </c>
-      <c r="E29">
-        <v>3.9363642204454033E-6</v>
-      </c>
-      <c r="F29">
-        <v>-6.1654182884119952E-4</v>
-      </c>
-      <c r="G29">
-        <v>-1.55589952025228E-3</v>
-      </c>
-      <c r="H29">
-        <v>-1.1635143896498528E-3</v>
-      </c>
-      <c r="I29">
-        <v>-2.1980252996440515E-3</v>
-      </c>
-      <c r="J29">
-        <v>-1.7949699590989359E-3</v>
-      </c>
-      <c r="K29">
-        <v>-2.233145656614254E-3</v>
-      </c>
-      <c r="L29">
-        <v>-1.5620043054297666E-3</v>
-      </c>
-      <c r="M29">
-        <v>-3.4064766889406002E-3</v>
-      </c>
-      <c r="N29">
-        <v>-1.6376659116148766E-3</v>
-      </c>
-      <c r="O29">
-        <v>-9.5113405554368171E-4</v>
-      </c>
-      <c r="P29">
-        <v>-1.403220276419188E-3</v>
-      </c>
-      <c r="Q29">
-        <v>-2.9992981902713816E-3</v>
-      </c>
-      <c r="R29">
-        <v>-3.0104610530649611E-3</v>
-      </c>
-      <c r="S29">
-        <v>-3.834371698435592E-3</v>
-      </c>
-      <c r="T29">
-        <v>-4.713237696354261E-3</v>
-      </c>
-      <c r="U29">
-        <v>-5.9701550402020752E-4</v>
-      </c>
-      <c r="V29">
-        <v>-1.1386516811092602E-3</v>
-      </c>
-      <c r="W29">
-        <v>-1.6813031951556192E-3</v>
-      </c>
-      <c r="X29">
-        <v>-2.2536634477345464E-3</v>
-      </c>
-      <c r="Y29">
-        <v>2.3087186717192971E-5</v>
-      </c>
-      <c r="Z29">
-        <v>-3.2456043645599748E-4</v>
-      </c>
-      <c r="AA29">
-        <v>2.0867652028259959E-5</v>
-      </c>
-      <c r="AB29">
-        <v>-1.0244896070965313E-4</v>
-      </c>
-      <c r="AC29">
-        <v>-9.6137958120475717E-5</v>
-      </c>
-      <c r="AD29">
-        <v>2.087407448326627E-2</v>
+      <c r="B31" s="6">
+        <v>-1.4704270153381556</v>
+      </c>
+      <c r="C31">
+        <v>-1.5709920124766009E-4</v>
+      </c>
+      <c r="D31">
+        <v>-3.6926776268379638E-4</v>
+      </c>
+      <c r="E31">
+        <v>3.2854761527932366E-6</v>
+      </c>
+      <c r="F31">
+        <v>-1.0826635481383017E-3</v>
+      </c>
+      <c r="G31">
+        <v>-1.2935524890365332E-3</v>
+      </c>
+      <c r="H31">
+        <v>-1.0706980027060419E-3</v>
+      </c>
+      <c r="I31">
+        <v>-2.8782235208661797E-3</v>
+      </c>
+      <c r="J31">
+        <v>-1.7363406380741246E-3</v>
+      </c>
+      <c r="K31">
+        <v>-1.8483312979453515E-3</v>
+      </c>
+      <c r="L31">
+        <v>-9.897684567244016E-4</v>
+      </c>
+      <c r="M31">
+        <v>-3.0116310722167819E-3</v>
+      </c>
+      <c r="N31">
+        <v>-1.4123336928822138E-3</v>
+      </c>
+      <c r="O31">
+        <v>-7.8294380543485718E-4</v>
+      </c>
+      <c r="P31">
+        <v>-1.1618916288163709E-3</v>
+      </c>
+      <c r="Q31">
+        <v>-2.5916239165677214E-3</v>
+      </c>
+      <c r="R31">
+        <v>-2.5300123538397608E-3</v>
+      </c>
+      <c r="S31">
+        <v>-3.1856111227477613E-3</v>
+      </c>
+      <c r="T31">
+        <v>-3.9954826857544912E-3</v>
+      </c>
+      <c r="U31">
+        <v>-4.7705178291751645E-4</v>
+      </c>
+      <c r="V31">
+        <v>-1.0131396859020566E-3</v>
+      </c>
+      <c r="W31">
+        <v>-1.442498001800423E-3</v>
+      </c>
+      <c r="X31">
+        <v>-2.0151596588177632E-3</v>
+      </c>
+      <c r="Y31">
+        <v>7.4947756806971391E-6</v>
+      </c>
+      <c r="Z31">
+        <v>-2.7540579330812356E-4</v>
+      </c>
+      <c r="AA31">
+        <v>-3.7314142012019727E-5</v>
+      </c>
+      <c r="AB31">
+        <v>-1.8997250344791362E-4</v>
+      </c>
+      <c r="AC31">
+        <v>-6.8296168672395141E-5</v>
+      </c>
+      <c r="AD31">
+        <v>5.3379861089138938E-4</v>
+      </c>
+      <c r="AE31">
+        <v>9.2145356426145562E-5</v>
+      </c>
+      <c r="AF31">
+        <v>1.757195304165126E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669DD4AF-9887-4C51-91B4-546214683BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A03AF0D-98D1-4BD1-877C-1F83FAEC913D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_HO1a" sheetId="3" r:id="rId2"/>
+    <sheet name="IT_HO1a" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>Description:</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>Notes:</t>
-  </si>
-  <si>
-    <t>Have combined dhhtp_c4 and lessp_c3 into a single variable with 8 cateogries, dhhtp_c8</t>
   </si>
   <si>
     <t>REGRESSOR</t>
@@ -134,219 +131,32 @@
     <t>Constant</t>
   </si>
   <si>
-    <t>PL4</t>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
   </si>
   <si>
-    <t>PL5</t>
+    <t>ITF</t>
   </si>
   <si>
-    <t>PL6</t>
+    <t>ITG</t>
   </si>
   <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
+    <t>ITH</t>
   </si>
   <si>
-    <t>PL10</t>
+    <t>ITI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -359,266 +169,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="39">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -637,46 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="29" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="30" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="31" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="32" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="35" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="37" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="38" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,8 +525,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1026,7 +540,7 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1039,16 +553,11 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1065,83 +574,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>31</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>32</v>
       </c>
       <c r="AA1" t="s">
         <v>37</v>
@@ -1153,3347 +662,3347 @@
         <v>39</v>
       </c>
       <c r="AD1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>35</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="38">
-        <v>1.2487487083175952E-2</v>
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1.3504252829144987E-2</v>
       </c>
       <c r="C2">
-        <v>5.0985729011693E-4</v>
+        <v>1.3074330983512319E-4</v>
       </c>
       <c r="D2">
-        <v>6.4854030724188281E-6</v>
+        <v>5.2369597172460329E-7</v>
       </c>
       <c r="E2">
-        <v>-4.9808900163760097E-8</v>
+        <v>-5.5188316281469583E-9</v>
       </c>
       <c r="F2">
-        <v>-2.4743283289578686E-4</v>
+        <v>-5.2293510484548779E-5</v>
       </c>
       <c r="G2">
-        <v>-1.0541909258182646E-4</v>
+        <v>-2.8773951226953427E-5</v>
       </c>
       <c r="H2">
-        <v>3.8525010158422438E-5</v>
+        <v>2.049060763178079E-6</v>
       </c>
       <c r="I2">
-        <v>-2.1214856275671525E-4</v>
+        <v>-5.9376867387260537E-5</v>
       </c>
       <c r="J2">
-        <v>-1.7764136541972137E-4</v>
+        <v>-4.886025348730425E-5</v>
       </c>
       <c r="K2">
-        <v>-3.3658451280356341E-5</v>
+        <v>-7.3809414441387998E-6</v>
       </c>
       <c r="L2">
-        <v>1.7605670946978404E-4</v>
+        <v>3.9964503667071509E-5</v>
       </c>
       <c r="M2">
-        <v>1.0057101337731058E-4</v>
+        <v>1.7014735431539614E-5</v>
       </c>
       <c r="N2">
-        <v>9.8666199291812376E-5</v>
+        <v>2.8281966222033687E-5</v>
       </c>
       <c r="O2">
-        <v>-1.0924282851627542E-5</v>
+        <v>-4.7159146680466837E-6</v>
       </c>
       <c r="P2">
-        <v>3.1957366783621534E-5</v>
+        <v>-1.1041129590456291E-5</v>
       </c>
       <c r="Q2">
-        <v>-2.7555455138435986E-5</v>
+        <v>2.6933781714179523E-6</v>
       </c>
       <c r="R2">
-        <v>1.8024529134122181E-5</v>
+        <v>-1.7147839270421265E-6</v>
       </c>
       <c r="S2">
-        <v>3.4910458367521947E-5</v>
+        <v>-6.9245127771184097E-6</v>
       </c>
       <c r="T2">
-        <v>-2.1923498827584511E-5</v>
+        <v>-1.8168289107175546E-5</v>
       </c>
       <c r="U2">
-        <v>-1.5840744043522951E-5</v>
+        <v>-8.8323946264114176E-7</v>
       </c>
       <c r="V2">
-        <v>3.428607753602349E-7</v>
+        <v>1.7734779008110136E-6</v>
       </c>
       <c r="W2">
-        <v>-3.2138066265636529E-5</v>
+        <v>-8.896182731514779E-7</v>
       </c>
       <c r="X2">
-        <v>-2.7153992286396879E-5</v>
+        <v>-3.2711686405825264E-6</v>
       </c>
       <c r="Y2">
-        <v>8.0515421347049005E-6</v>
+        <v>1.9658349644189244E-7</v>
       </c>
       <c r="Z2">
-        <v>-1.0205046965530909E-5</v>
+        <v>-3.6361055621319477E-6</v>
       </c>
       <c r="AA2">
-        <v>-1.7689634487173019E-5</v>
+        <v>-4.3394966743498959E-6</v>
       </c>
       <c r="AB2">
-        <v>4.612929186166963E-6</v>
+        <v>-1.9601721291514337E-6</v>
       </c>
       <c r="AC2">
-        <v>-7.9311031574697379E-6</v>
+        <v>-5.1938808781731478E-6</v>
       </c>
       <c r="AD2">
-        <v>6.3496126118559745E-6</v>
+        <v>-4.6735164623377883E-6</v>
       </c>
       <c r="AE2">
-        <v>3.0977092293611811E-8</v>
+        <v>1.0721178697140799E-6</v>
       </c>
       <c r="AF2">
-        <v>3.32270419110664E-5</v>
+        <v>-2.8818153349261086E-6</v>
       </c>
       <c r="AG2">
-        <v>1.2110335424800447E-6</v>
+        <v>-7.7756611070347398E-6</v>
       </c>
       <c r="AH2">
-        <v>-4.389932419707138E-4</v>
+        <v>-7.0878618789813803E-5</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="38">
-        <v>5.3532753582598023E-3</v>
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>-1.4624467232620458E-3</v>
       </c>
       <c r="C3">
-        <v>6.4854030724188281E-6</v>
+        <v>5.2369597172460329E-7</v>
       </c>
       <c r="D3">
-        <v>2.1660384801116284E-5</v>
+        <v>6.4751302495334266E-6</v>
       </c>
       <c r="E3">
-        <v>-2.0803222121749734E-7</v>
+        <v>-6.1362317433511504E-8</v>
       </c>
       <c r="F3">
-        <v>3.9063685022342441E-5</v>
+        <v>2.2581289976085058E-5</v>
       </c>
       <c r="G3">
-        <v>2.8039615149102677E-5</v>
+        <v>3.4806240415868672E-6</v>
       </c>
       <c r="H3">
-        <v>1.6567949034397149E-5</v>
+        <v>1.6518581497577107E-6</v>
       </c>
       <c r="I3">
-        <v>6.7984836813901963E-5</v>
+        <v>7.3386124744279825E-6</v>
       </c>
       <c r="J3">
-        <v>1.6449721361476606E-5</v>
+        <v>-1.296435102801081E-6</v>
       </c>
       <c r="K3">
-        <v>3.6970493449951839E-5</v>
+        <v>9.6992839483347138E-6</v>
       </c>
       <c r="L3">
-        <v>-7.8546018753381799E-6</v>
+        <v>-3.8926088905379681E-6</v>
       </c>
       <c r="M3">
-        <v>1.2103669801985173E-4</v>
+        <v>3.7281333960987144E-5</v>
       </c>
       <c r="N3">
-        <v>2.2042337206114292E-5</v>
+        <v>3.9608067766064954E-6</v>
       </c>
       <c r="O3">
-        <v>-1.5313396933818924E-5</v>
+        <v>4.4409294069417391E-7</v>
       </c>
       <c r="P3">
-        <v>8.358582316831504E-7</v>
+        <v>-8.5145851032103213E-8</v>
       </c>
       <c r="Q3">
-        <v>-1.9218169860092027E-5</v>
+        <v>-3.4139154271193679E-6</v>
       </c>
       <c r="R3">
-        <v>-3.7207368112170017E-5</v>
+        <v>-6.6479555301813811E-6</v>
       </c>
       <c r="S3">
-        <v>-1.3260913622587542E-5</v>
+        <v>-5.2097277396713001E-6</v>
       </c>
       <c r="T3">
-        <v>1.86722563590956E-5</v>
+        <v>-3.1998874124452616E-7</v>
       </c>
       <c r="U3">
-        <v>-1.5084395861254279E-6</v>
+        <v>-1.0816350779852603E-6</v>
       </c>
       <c r="V3">
-        <v>-1.7773091032660448E-5</v>
+        <v>-7.8535629662447216E-6</v>
       </c>
       <c r="W3">
-        <v>-1.7725428851976158E-5</v>
+        <v>-9.8686119561850746E-6</v>
       </c>
       <c r="X3">
-        <v>-2.6832264878845274E-5</v>
+        <v>-1.3727119044301492E-5</v>
       </c>
       <c r="Y3">
-        <v>5.1918775570460752E-7</v>
+        <v>6.0090435756407827E-8</v>
       </c>
       <c r="Z3">
-        <v>-8.1333625158732075E-6</v>
+        <v>1.5359858545935693E-7</v>
       </c>
       <c r="AA3">
-        <v>-1.8397904489040462E-5</v>
+        <v>-1.9589762488986601E-6</v>
       </c>
       <c r="AB3">
-        <v>1.0447901649068521E-5</v>
+        <v>-3.574104141622016E-6</v>
       </c>
       <c r="AC3">
-        <v>-2.3432938846477044E-6</v>
+        <v>1.1116334129842236E-6</v>
       </c>
       <c r="AD3">
-        <v>4.5155970790922975E-6</v>
+        <v>-9.7024023133876784E-7</v>
       </c>
       <c r="AE3">
-        <v>3.6245662912667931E-7</v>
+        <v>-9.4235264822220706E-10</v>
       </c>
       <c r="AF3">
-        <v>-2.5326301482947759E-5</v>
+        <v>1.1318871457991506E-6</v>
       </c>
       <c r="AG3">
-        <v>4.5151840262410841E-6</v>
+        <v>-9.7675186082141696E-7</v>
       </c>
       <c r="AH3">
-        <v>-5.0419684697400064E-4</v>
+        <v>-1.5008058685414902E-4</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="38">
-        <v>-5.757175106583059E-5</v>
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>7.3539436665991047E-5</v>
       </c>
       <c r="C4">
-        <v>-4.9808900163760097E-8</v>
+        <v>-5.5188316281469583E-9</v>
       </c>
       <c r="D4">
-        <v>-2.0803222121749734E-7</v>
+        <v>-6.1362317433511504E-8</v>
       </c>
       <c r="E4">
-        <v>2.0808047414278053E-9</v>
+        <v>6.0476609329062718E-10</v>
       </c>
       <c r="F4">
-        <v>-3.0825181736381939E-7</v>
+        <v>-1.772235724874568E-7</v>
       </c>
       <c r="G4">
-        <v>-3.3984130975312779E-7</v>
+        <v>-4.7135138338132802E-8</v>
       </c>
       <c r="H4">
-        <v>-8.5872270288606773E-8</v>
+        <v>-1.2613758755300052E-9</v>
       </c>
       <c r="I4">
-        <v>-5.5640182834899678E-7</v>
+        <v>-3.8584690222518028E-8</v>
       </c>
       <c r="J4">
-        <v>-9.4248956200806748E-8</v>
+        <v>2.760203996049131E-8</v>
       </c>
       <c r="K4">
-        <v>-3.3710584744285328E-7</v>
+        <v>-8.7011569683774001E-8</v>
       </c>
       <c r="L4">
-        <v>1.5753064026408259E-7</v>
+        <v>5.6710127587798481E-8</v>
       </c>
       <c r="M4">
-        <v>-9.7985669002792154E-7</v>
+        <v>-2.9939195959287398E-7</v>
       </c>
       <c r="N4">
-        <v>-2.3939063866782768E-7</v>
+        <v>-5.0438824271618217E-8</v>
       </c>
       <c r="O4">
-        <v>1.6328392364650055E-7</v>
+        <v>-1.7157702169896841E-9</v>
       </c>
       <c r="P4">
-        <v>-2.9336888750264367E-8</v>
+        <v>-9.7334820705486065E-9</v>
       </c>
       <c r="Q4">
-        <v>1.9027469277679189E-7</v>
+        <v>3.5474901394343246E-8</v>
       </c>
       <c r="R4">
-        <v>4.0940823915512384E-7</v>
+        <v>7.1395067679907566E-8</v>
       </c>
       <c r="S4">
-        <v>2.158837279470273E-7</v>
+        <v>7.4644016197495944E-8</v>
       </c>
       <c r="T4">
-        <v>-2.756862630082573E-8</v>
+        <v>4.1775474556591452E-8</v>
       </c>
       <c r="U4">
-        <v>4.2763933223505174E-8</v>
+        <v>1.6943706177842E-8</v>
       </c>
       <c r="V4">
-        <v>2.4770518453236893E-7</v>
+        <v>9.7629430875929667E-8</v>
       </c>
       <c r="W4">
-        <v>2.5616557819447479E-7</v>
+        <v>1.1840764470854318E-7</v>
       </c>
       <c r="X4">
-        <v>3.2423004978606971E-7</v>
+        <v>1.4672545119740495E-7</v>
       </c>
       <c r="Y4">
-        <v>-7.5615373483454625E-9</v>
+        <v>-2.35860686816834E-9</v>
       </c>
       <c r="Z4">
-        <v>4.7555092811607297E-8</v>
+        <v>-3.2791824408925183E-9</v>
       </c>
       <c r="AA4">
-        <v>1.9060474720314273E-7</v>
+        <v>2.5715170724065201E-8</v>
       </c>
       <c r="AB4">
-        <v>-1.4672956866600413E-7</v>
+        <v>4.2508249803978106E-8</v>
       </c>
       <c r="AC4">
-        <v>1.2311374896594582E-8</v>
+        <v>-8.2456562508767621E-9</v>
       </c>
       <c r="AD4">
-        <v>-5.5003523428832741E-8</v>
+        <v>1.1581152446939951E-8</v>
       </c>
       <c r="AE4">
-        <v>-4.8959188265797088E-9</v>
+        <v>-1.2922107638907773E-9</v>
       </c>
       <c r="AF4">
-        <v>2.7862920030196577E-7</v>
+        <v>-1.0088600866191837E-8</v>
       </c>
       <c r="AG4">
-        <v>-3.6515081838127517E-8</v>
+        <v>1.2063940915487148E-8</v>
       </c>
       <c r="AH4">
-        <v>4.5094976109574447E-6</v>
+        <v>1.3442607168871279E-6</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="38">
-        <v>-0.66492794250826726</v>
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>-0.40457222940316129</v>
       </c>
       <c r="C5">
-        <v>-2.4743283289578686E-4</v>
+        <v>-5.2293510484548779E-5</v>
       </c>
       <c r="D5">
-        <v>3.9063685022342441E-5</v>
+        <v>2.2581289976085058E-5</v>
       </c>
       <c r="E5">
-        <v>-3.0825181736381939E-7</v>
+        <v>-1.772235724874568E-7</v>
       </c>
       <c r="F5">
-        <v>8.8690328609476746E-2</v>
+        <v>8.9709696963161722E-2</v>
       </c>
       <c r="G5">
-        <v>1.0515478119431003E-3</v>
+        <v>1.9719771611164083E-4</v>
       </c>
       <c r="H5">
-        <v>1.2331149964523067E-3</v>
+        <v>3.1678323712580364E-4</v>
       </c>
       <c r="I5">
-        <v>1.6809860089147251E-3</v>
+        <v>4.1062862203389955E-4</v>
       </c>
       <c r="J5">
-        <v>1.2913200070251533E-3</v>
+        <v>3.8197694762800202E-4</v>
       </c>
       <c r="K5">
-        <v>1.2886766417957731E-3</v>
+        <v>3.4872702604132189E-4</v>
       </c>
       <c r="L5">
-        <v>1.5207710018248256E-3</v>
+        <v>3.1517049503138603E-4</v>
       </c>
       <c r="M5">
-        <v>-1.4682399845287108E-5</v>
+        <v>2.5429778910367629E-4</v>
       </c>
       <c r="N5">
-        <v>1.5621787693530291E-4</v>
+        <v>1.0505917249260882E-4</v>
       </c>
       <c r="O5">
-        <v>2.0739502319431954E-4</v>
+        <v>6.7198166053607404E-5</v>
       </c>
       <c r="P5">
-        <v>1.6702388738696976E-4</v>
+        <v>5.974912630999074E-5</v>
       </c>
       <c r="Q5">
-        <v>5.7832150575601397E-5</v>
+        <v>1.8859042808223617E-5</v>
       </c>
       <c r="R5">
-        <v>-1.6557425093882347E-5</v>
+        <v>2.7831266524254261E-5</v>
       </c>
       <c r="S5">
-        <v>5.8865848806807027E-5</v>
+        <v>3.2335601107875621E-5</v>
       </c>
       <c r="T5">
-        <v>-1.2533749472519212E-5</v>
+        <v>8.3294080954246811E-5</v>
       </c>
       <c r="U5">
-        <v>1.3167381407566887E-4</v>
+        <v>-2.7399546323482926E-5</v>
       </c>
       <c r="V5">
-        <v>3.1487986948351465E-4</v>
+        <v>9.9222113475816925E-6</v>
       </c>
       <c r="W5">
-        <v>4.3253707584346994E-4</v>
+        <v>6.4620014842669914E-5</v>
       </c>
       <c r="X5">
-        <v>5.3990332216988712E-4</v>
+        <v>1.415563108633939E-4</v>
       </c>
       <c r="Y5">
-        <v>-2.1635937740960531E-4</v>
+        <v>1.4105222919395916E-5</v>
       </c>
       <c r="Z5">
-        <v>-3.0239507218456736E-5</v>
+        <v>4.0836040416890849E-5</v>
       </c>
       <c r="AA5">
-        <v>1.4686935196862243E-4</v>
+        <v>2.7520710738332291E-5</v>
       </c>
       <c r="AB5">
-        <v>-7.6569608895826194E-5</v>
+        <v>1.7468048267700332E-5</v>
       </c>
       <c r="AC5">
-        <v>-1.7238271619967905E-4</v>
+        <v>2.7112551070500519E-5</v>
       </c>
       <c r="AD5">
-        <v>-5.0332282732335636E-5</v>
+        <v>9.2553354868828543E-6</v>
       </c>
       <c r="AE5">
-        <v>-2.3914255136231141E-6</v>
+        <v>-5.1717355696032286E-7</v>
       </c>
       <c r="AF5">
-        <v>1.6239433735017184E-4</v>
+        <v>8.0886284885600202E-5</v>
       </c>
       <c r="AG5">
-        <v>1.3194007397571703E-4</v>
+        <v>-2.5996773935847185E-5</v>
       </c>
       <c r="AH5">
-        <v>-2.5091965914107684E-3</v>
+        <v>-1.1730780768807493E-3</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="38">
-        <v>-3.574969724152248E-2</v>
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>0.12347370268106453</v>
       </c>
       <c r="C6">
-        <v>-1.0541909258182646E-4</v>
+        <v>-2.8773951226953427E-5</v>
       </c>
       <c r="D6">
-        <v>2.8039615149102677E-5</v>
+        <v>3.4806240415868672E-6</v>
       </c>
       <c r="E6">
-        <v>-3.3984130975312779E-7</v>
+        <v>-4.7135138338132802E-8</v>
       </c>
       <c r="F6">
-        <v>1.0515478119431003E-3</v>
+        <v>1.9719771611164083E-4</v>
       </c>
       <c r="G6">
-        <v>1.750822412097647E-3</v>
+        <v>5.1048177322352613E-4</v>
       </c>
       <c r="H6">
-        <v>9.3290752121171373E-4</v>
+        <v>2.5352064686989296E-4</v>
       </c>
       <c r="I6">
-        <v>9.6013520493620796E-4</v>
+        <v>3.2118367260539592E-4</v>
       </c>
       <c r="J6">
-        <v>1.0256298788018166E-3</v>
+        <v>3.1933468348481616E-4</v>
       </c>
       <c r="K6">
-        <v>1.2754308078886884E-3</v>
+        <v>3.3756506819238746E-4</v>
       </c>
       <c r="L6">
-        <v>1.015254636147824E-3</v>
+        <v>2.988475705172028E-4</v>
       </c>
       <c r="M6">
-        <v>1.302547532667631E-4</v>
+        <v>6.234690696741445E-5</v>
       </c>
       <c r="N6">
-        <v>1.9813386069095985E-4</v>
+        <v>4.7945414407802503E-5</v>
       </c>
       <c r="O6">
-        <v>-2.9674475556790142E-5</v>
+        <v>1.3906508304091227E-6</v>
       </c>
       <c r="P6">
-        <v>-1.5851946490376954E-5</v>
+        <v>4.752217058899271E-6</v>
       </c>
       <c r="Q6">
-        <v>1.6464719343808849E-4</v>
+        <v>-1.0654087877799847E-5</v>
       </c>
       <c r="R6">
-        <v>3.2193064053452533E-6</v>
+        <v>2.5707758014143844E-6</v>
       </c>
       <c r="S6">
-        <v>1.1470441331172956E-4</v>
+        <v>-9.2034062069427025E-6</v>
       </c>
       <c r="T6">
-        <v>1.1051684733845332E-4</v>
+        <v>-2.6804435052867977E-6</v>
       </c>
       <c r="U6">
-        <v>-3.4383000366098766E-5</v>
+        <v>-9.9782762985754039E-6</v>
       </c>
       <c r="V6">
-        <v>3.2146133830892188E-4</v>
+        <v>9.0903697544694756E-5</v>
       </c>
       <c r="W6">
-        <v>4.8632484079167186E-4</v>
+        <v>1.4559728788384363E-4</v>
       </c>
       <c r="X6">
-        <v>6.8591481507435798E-4</v>
+        <v>2.2500113106381915E-4</v>
       </c>
       <c r="Y6">
-        <v>-3.7349350146862023E-5</v>
+        <v>-4.8937747131196482E-6</v>
       </c>
       <c r="Z6">
-        <v>-1.9885634365762668E-5</v>
+        <v>2.0006181168719984E-6</v>
       </c>
       <c r="AA6">
-        <v>1.8511991698582438E-5</v>
+        <v>-3.324037709476435E-6</v>
       </c>
       <c r="AB6">
-        <v>8.8908170665578088E-5</v>
+        <v>4.5875427446076002E-6</v>
       </c>
       <c r="AC6">
-        <v>2.5286114352692546E-5</v>
+        <v>2.5448904074594557E-6</v>
       </c>
       <c r="AD6">
-        <v>-2.8405712424238184E-5</v>
+        <v>4.4237254610635449E-6</v>
       </c>
       <c r="AE6">
-        <v>2.2080578359214394E-6</v>
+        <v>1.7070853168842565E-7</v>
       </c>
       <c r="AF6">
-        <v>-4.703733868216195E-5</v>
+        <v>-8.9875802390939827E-6</v>
       </c>
       <c r="AG6">
-        <v>2.083220296619163E-5</v>
+        <v>2.403009357269595E-6</v>
       </c>
       <c r="AH6">
-        <v>-1.9787970871808299E-3</v>
+        <v>-4.5304902641070638E-4</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="38">
-        <v>-2.6846470875708673E-2</v>
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>-6.1909169336644317E-3</v>
       </c>
       <c r="C7">
-        <v>3.8525010158422438E-5</v>
+        <v>2.049060763178079E-6</v>
       </c>
       <c r="D7">
-        <v>1.6567949034397149E-5</v>
+        <v>1.6518581497577107E-6</v>
       </c>
       <c r="E7">
-        <v>-8.5872270288606773E-8</v>
+        <v>-1.2613758755300052E-9</v>
       </c>
       <c r="F7">
-        <v>1.2331149964523067E-3</v>
+        <v>3.1678323712580364E-4</v>
       </c>
       <c r="G7">
-        <v>9.3290752121171373E-4</v>
+        <v>2.5352064686989296E-4</v>
       </c>
       <c r="H7">
-        <v>1.8935329691799666E-3</v>
+        <v>4.7583077189874821E-4</v>
       </c>
       <c r="I7">
-        <v>1.0541916959392853E-3</v>
+        <v>3.0333566553276611E-4</v>
       </c>
       <c r="J7">
-        <v>1.1270907390464925E-3</v>
+        <v>2.8740755025799406E-4</v>
       </c>
       <c r="K7">
-        <v>1.0535717612629612E-3</v>
+        <v>2.7346048280848915E-4</v>
       </c>
       <c r="L7">
-        <v>1.2010937064264285E-3</v>
+        <v>2.9201605535499671E-4</v>
       </c>
       <c r="M7">
-        <v>4.4703791866715072E-4</v>
+        <v>9.274503103923426E-5</v>
       </c>
       <c r="N7">
-        <v>9.2294129888505883E-5</v>
+        <v>3.6440535898256804E-5</v>
       </c>
       <c r="O7">
-        <v>6.4557767285431316E-5</v>
+        <v>7.535805194648551E-6</v>
       </c>
       <c r="P7">
-        <v>2.4897916565003761E-5</v>
+        <v>1.908592668736551E-5</v>
       </c>
       <c r="Q7">
-        <v>6.2037303488563411E-5</v>
+        <v>1.1079394676554403E-5</v>
       </c>
       <c r="R7">
-        <v>-8.3915241487303541E-6</v>
+        <v>1.7736600972095358E-5</v>
       </c>
       <c r="S7">
-        <v>6.3377568663052262E-5</v>
+        <v>1.0622134486376772E-5</v>
       </c>
       <c r="T7">
-        <v>-3.3214981508635541E-6</v>
+        <v>2.1576007697365902E-5</v>
       </c>
       <c r="U7">
-        <v>2.4219941243844184E-5</v>
+        <v>-1.1600367477558214E-7</v>
       </c>
       <c r="V7">
-        <v>7.3890610862375236E-5</v>
+        <v>3.3487189209837325E-5</v>
       </c>
       <c r="W7">
-        <v>1.8472645389788257E-4</v>
+        <v>5.4354381170091802E-5</v>
       </c>
       <c r="X7">
-        <v>4.724673710286998E-4</v>
+        <v>1.1919672814284108E-4</v>
       </c>
       <c r="Y7">
-        <v>-3.9699879976002196E-5</v>
+        <v>-1.8078586482805678E-6</v>
       </c>
       <c r="Z7">
-        <v>4.2808629502101054E-5</v>
+        <v>2.649117421418747E-6</v>
       </c>
       <c r="AA7">
-        <v>3.0388947663734884E-4</v>
+        <v>-8.2845262303650734E-6</v>
       </c>
       <c r="AB7">
-        <v>4.4070149807506898E-6</v>
+        <v>6.4446870364056935E-6</v>
       </c>
       <c r="AC7">
-        <v>4.0779667238832129E-5</v>
+        <v>-1.0603487745046561E-5</v>
       </c>
       <c r="AD7">
-        <v>-6.5293459625085401E-5</v>
+        <v>-4.7054978975882606E-6</v>
       </c>
       <c r="AE7">
-        <v>-2.567455903458273E-6</v>
+        <v>-3.7297964610907554E-7</v>
       </c>
       <c r="AF7">
-        <v>3.3967607555305786E-4</v>
+        <v>2.5765008242544961E-5</v>
       </c>
       <c r="AG7">
-        <v>1.5782179638358933E-4</v>
+        <v>-5.1963289915598883E-7</v>
       </c>
       <c r="AH7">
-        <v>-1.9366021769109106E-3</v>
+        <v>-4.2498415903023711E-4</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="38">
-        <v>0.96330241363388047</v>
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>-0.35386494956103293</v>
       </c>
       <c r="C8">
-        <v>-2.1214856275671525E-4</v>
+        <v>-5.9376867387260537E-5</v>
       </c>
       <c r="D8">
-        <v>6.7984836813901963E-5</v>
+        <v>7.3386124744279825E-6</v>
       </c>
       <c r="E8">
-        <v>-5.5640182834899678E-7</v>
+        <v>-3.8584690222518028E-8</v>
       </c>
       <c r="F8">
-        <v>1.6809860089147251E-3</v>
+        <v>4.1062862203389955E-4</v>
       </c>
       <c r="G8">
-        <v>9.6013520493620796E-4</v>
+        <v>3.2118367260539592E-4</v>
       </c>
       <c r="H8">
-        <v>1.0541916959392853E-3</v>
+        <v>3.0333566553276611E-4</v>
       </c>
       <c r="I8">
-        <v>0.24713787311209692</v>
+        <v>5.1940485215748421E-2</v>
       </c>
       <c r="J8">
-        <v>1.2502711347349288E-3</v>
+        <v>4.6169694109021638E-4</v>
       </c>
       <c r="K8">
-        <v>1.1468785112426483E-3</v>
+        <v>3.4036361446385734E-4</v>
       </c>
       <c r="L8">
-        <v>1.2747554776659877E-3</v>
+        <v>3.4684898504614553E-4</v>
       </c>
       <c r="M8">
-        <v>9.5444436451339791E-4</v>
+        <v>2.1461950176201428E-4</v>
       </c>
       <c r="N8">
-        <v>2.760852986160759E-4</v>
+        <v>5.3549257344034617E-5</v>
       </c>
       <c r="O8">
-        <v>-9.2978151404032395E-5</v>
+        <v>1.0989375596878915E-5</v>
       </c>
       <c r="P8">
-        <v>-1.694361713841879E-4</v>
+        <v>3.4005389912118262E-5</v>
       </c>
       <c r="Q8">
-        <v>2.0591049505648123E-5</v>
+        <v>2.9639073468858132E-5</v>
       </c>
       <c r="R8">
-        <v>1.0436404571546138E-5</v>
+        <v>1.825425299526777E-5</v>
       </c>
       <c r="S8">
-        <v>2.974429594526766E-5</v>
+        <v>4.5160250666517451E-5</v>
       </c>
       <c r="T8">
-        <v>1.3770076818322372E-4</v>
+        <v>8.316455515061785E-5</v>
       </c>
       <c r="U8">
-        <v>1.0099203508079872E-4</v>
+        <v>-1.9031941732413339E-5</v>
       </c>
       <c r="V8">
-        <v>3.7164053050896609E-4</v>
+        <v>5.0701581506823828E-5</v>
       </c>
       <c r="W8">
-        <v>5.4424387010272492E-4</v>
+        <v>1.5567129731536389E-4</v>
       </c>
       <c r="X8">
-        <v>6.2478990679459313E-4</v>
+        <v>2.3676000305362363E-4</v>
       </c>
       <c r="Y8">
-        <v>-1.791520235219863E-4</v>
+        <v>-5.0831646605438655E-6</v>
       </c>
       <c r="Z8">
-        <v>1.9066378968074667E-4</v>
+        <v>-1.7398908757316087E-5</v>
       </c>
       <c r="AA8">
-        <v>4.5996614135651115E-4</v>
+        <v>-1.8288992026923293E-5</v>
       </c>
       <c r="AB8">
-        <v>-1.1806564953034779E-4</v>
+        <v>6.7877316872757784E-7</v>
       </c>
       <c r="AC8">
-        <v>1.9614943429843598E-5</v>
+        <v>-1.2506626383148494E-5</v>
       </c>
       <c r="AD8">
-        <v>-3.7827204830434124E-5</v>
+        <v>-2.1470421357523196E-5</v>
       </c>
       <c r="AE8">
-        <v>1.2811792203293087E-5</v>
+        <v>1.6183905922981872E-6</v>
       </c>
       <c r="AF8">
-        <v>-1.7230223417134469E-4</v>
+        <v>-5.595453002764394E-5</v>
       </c>
       <c r="AG8">
-        <v>-1.2946490247114494E-4</v>
+        <v>5.456426730407517E-5</v>
       </c>
       <c r="AH8">
-        <v>-3.4975229634165482E-3</v>
+        <v>-7.4182443158430159E-4</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="38">
-        <v>-0.15121059652217747</v>
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>-8.2920860342810487E-2</v>
       </c>
       <c r="C9">
-        <v>-1.7764136541972137E-4</v>
+        <v>-4.886025348730425E-5</v>
       </c>
       <c r="D9">
-        <v>1.6449721361476606E-5</v>
+        <v>-1.296435102801081E-6</v>
       </c>
       <c r="E9">
-        <v>-9.4248956200806748E-8</v>
+        <v>2.760203996049131E-8</v>
       </c>
       <c r="F9">
-        <v>1.2913200070251533E-3</v>
+        <v>3.8197694762800202E-4</v>
       </c>
       <c r="G9">
-        <v>1.0256298788018166E-3</v>
+        <v>3.1933468348481616E-4</v>
       </c>
       <c r="H9">
-        <v>1.1270907390464925E-3</v>
+        <v>2.8740755025799406E-4</v>
       </c>
       <c r="I9">
-        <v>1.2502711347349288E-3</v>
+        <v>4.6169694109021638E-4</v>
       </c>
       <c r="J9">
-        <v>2.9211954085671447E-3</v>
+        <v>8.6770572744061867E-4</v>
       </c>
       <c r="K9">
-        <v>1.1261357875651072E-3</v>
+        <v>3.219616900548717E-4</v>
       </c>
       <c r="L9">
-        <v>1.1950131812774796E-3</v>
+        <v>3.4164332393307343E-4</v>
       </c>
       <c r="M9">
-        <v>6.0994332705733775E-4</v>
+        <v>1.4090607720262282E-4</v>
       </c>
       <c r="N9">
-        <v>3.6093354463471728E-4</v>
+        <v>9.8711298663820885E-5</v>
       </c>
       <c r="O9">
-        <v>2.5226372102594443E-5</v>
+        <v>1.0395969740821984E-5</v>
       </c>
       <c r="P9">
-        <v>-1.0500731929633737E-4</v>
+        <v>2.3325882706940973E-6</v>
       </c>
       <c r="Q9">
-        <v>1.0881890631719752E-4</v>
+        <v>1.8403820372043917E-5</v>
       </c>
       <c r="R9">
-        <v>4.2584494704953256E-5</v>
+        <v>3.1494262230363868E-5</v>
       </c>
       <c r="S9">
-        <v>3.4509861956094192E-5</v>
+        <v>3.0971071045037907E-5</v>
       </c>
       <c r="T9">
-        <v>5.8840747626688503E-5</v>
+        <v>4.6795693861346073E-5</v>
       </c>
       <c r="U9">
-        <v>8.3600379723594378E-5</v>
+        <v>-9.9815545356662094E-6</v>
       </c>
       <c r="V9">
-        <v>2.0800919217396817E-4</v>
+        <v>5.944315608214022E-5</v>
       </c>
       <c r="W9">
-        <v>5.7406931778274811E-4</v>
+        <v>1.620750621956659E-4</v>
       </c>
       <c r="X9">
-        <v>8.0977191829111408E-4</v>
+        <v>2.4718244111586392E-4</v>
       </c>
       <c r="Y9">
-        <v>-5.0371644623542834E-5</v>
+        <v>-2.0470513619803131E-6</v>
       </c>
       <c r="Z9">
-        <v>-2.0095609045942399E-5</v>
+        <v>6.2122950676191021E-6</v>
       </c>
       <c r="AA9">
-        <v>1.7189041247273453E-4</v>
+        <v>-2.7971654781780981E-5</v>
       </c>
       <c r="AB9">
-        <v>5.8821881373327103E-5</v>
+        <v>-7.9997606522520643E-6</v>
       </c>
       <c r="AC9">
-        <v>3.7500102589792906E-6</v>
+        <v>-8.1632130806928976E-6</v>
       </c>
       <c r="AD9">
-        <v>-3.8218019447430556E-5</v>
+        <v>-6.8846618448084476E-6</v>
       </c>
       <c r="AE9">
-        <v>6.781075355056696E-6</v>
+        <v>-4.3367139136056483E-7</v>
       </c>
       <c r="AF9">
-        <v>-1.2288994651668377E-5</v>
+        <v>3.2061749175081784E-5</v>
       </c>
       <c r="AG9">
-        <v>2.0085313754435229E-5</v>
+        <v>3.4793290925813907E-6</v>
       </c>
       <c r="AH9">
-        <v>-2.2024325942323745E-3</v>
+        <v>-4.684906320367502E-4</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="38">
-        <v>-0.17359470518393269</v>
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>-0.10667125015520768</v>
       </c>
       <c r="C10">
-        <v>-3.3658451280356341E-5</v>
+        <v>-7.3809414441387998E-6</v>
       </c>
       <c r="D10">
-        <v>3.6970493449951839E-5</v>
+        <v>9.6992839483347138E-6</v>
       </c>
       <c r="E10">
-        <v>-3.3710584744285328E-7</v>
+        <v>-8.7011569683774001E-8</v>
       </c>
       <c r="F10">
-        <v>1.2886766417957731E-3</v>
+        <v>3.4872702604132189E-4</v>
       </c>
       <c r="G10">
-        <v>1.2754308078886884E-3</v>
+        <v>3.3756506819238746E-4</v>
       </c>
       <c r="H10">
-        <v>1.0535717612629612E-3</v>
+        <v>2.7346048280848915E-4</v>
       </c>
       <c r="I10">
-        <v>1.1468785112426483E-3</v>
+        <v>3.4036361446385734E-4</v>
       </c>
       <c r="J10">
-        <v>1.1261357875651072E-3</v>
+        <v>3.219616900548717E-4</v>
       </c>
       <c r="K10">
-        <v>1.6350614783507979E-3</v>
+        <v>4.239205638210634E-4</v>
       </c>
       <c r="L10">
-        <v>1.1900077349596922E-3</v>
+        <v>3.1017222222191215E-4</v>
       </c>
       <c r="M10">
-        <v>1.881914719503051E-4</v>
+        <v>7.571305213158396E-5</v>
       </c>
       <c r="N10">
-        <v>2.10221685509251E-4</v>
+        <v>7.32218969994281E-5</v>
       </c>
       <c r="O10">
-        <v>1.7759470640185844E-5</v>
+        <v>5.6363101671872949E-6</v>
       </c>
       <c r="P10">
-        <v>-2.5856482314989696E-5</v>
+        <v>1.6089333802480009E-5</v>
       </c>
       <c r="Q10">
-        <v>2.9859158132289733E-5</v>
+        <v>2.4108026728469498E-5</v>
       </c>
       <c r="R10">
-        <v>1.8451252783496965E-5</v>
+        <v>3.8231072564846825E-5</v>
       </c>
       <c r="S10">
-        <v>8.1658996643294487E-5</v>
+        <v>3.8175179944273247E-5</v>
       </c>
       <c r="T10">
-        <v>5.5186444124918519E-5</v>
+        <v>3.7053637074313008E-5</v>
       </c>
       <c r="U10">
-        <v>5.2769921137823525E-5</v>
+        <v>1.1983906798044313E-5</v>
       </c>
       <c r="V10">
-        <v>4.466868135523679E-4</v>
+        <v>1.0655522925317073E-4</v>
       </c>
       <c r="W10">
-        <v>5.8373464004820316E-4</v>
+        <v>1.4969588304935945E-4</v>
       </c>
       <c r="X10">
-        <v>7.8361098591835728E-4</v>
+        <v>2.266061115396576E-4</v>
       </c>
       <c r="Y10">
-        <v>-6.529180612947682E-5</v>
+        <v>-4.5630648247887527E-6</v>
       </c>
       <c r="Z10">
-        <v>-5.821300778029295E-5</v>
+        <v>5.6161638106325883E-6</v>
       </c>
       <c r="AA10">
-        <v>9.6741080698260263E-5</v>
+        <v>-3.7089489704015264E-6</v>
       </c>
       <c r="AB10">
-        <v>1.4600923072762787E-5</v>
+        <v>6.3099480123044919E-6</v>
       </c>
       <c r="AC10">
-        <v>4.3845543146300544E-5</v>
+        <v>-3.6675078601618063E-6</v>
       </c>
       <c r="AD10">
-        <v>-1.887191945801125E-5</v>
+        <v>-4.2618954105564429E-6</v>
       </c>
       <c r="AE10">
-        <v>-4.201631069943436E-6</v>
+        <v>-9.8747954486114598E-7</v>
       </c>
       <c r="AF10">
-        <v>5.4115955237877059E-5</v>
+        <v>-2.0895247500510913E-5</v>
       </c>
       <c r="AG10">
-        <v>2.9719533482842257E-5</v>
+        <v>1.4615202039950791E-6</v>
       </c>
       <c r="AH10">
-        <v>-2.4930414776556916E-3</v>
+        <v>-7.1861823013451222E-4</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="38">
-        <v>-0.43154486684818433</v>
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>-0.3292062261013215</v>
       </c>
       <c r="C11">
-        <v>1.7605670946978404E-4</v>
+        <v>3.9964503667071509E-5</v>
       </c>
       <c r="D11">
-        <v>-7.8546018753381799E-6</v>
+        <v>-3.8926088905379681E-6</v>
       </c>
       <c r="E11">
-        <v>1.5753064026408259E-7</v>
+        <v>5.6710127587798481E-8</v>
       </c>
       <c r="F11">
-        <v>1.5207710018248256E-3</v>
+        <v>3.1517049503138603E-4</v>
       </c>
       <c r="G11">
-        <v>1.015254636147824E-3</v>
+        <v>2.988475705172028E-4</v>
       </c>
       <c r="H11">
-        <v>1.2010937064264285E-3</v>
+        <v>2.9201605535499671E-4</v>
       </c>
       <c r="I11">
-        <v>1.2747554776659877E-3</v>
+        <v>3.4684898504614553E-4</v>
       </c>
       <c r="J11">
-        <v>1.1950131812774796E-3</v>
+        <v>3.4164332393307343E-4</v>
       </c>
       <c r="K11">
-        <v>1.1900077349596922E-3</v>
+        <v>3.1017222222191215E-4</v>
       </c>
       <c r="L11">
-        <v>6.0294294484116735E-3</v>
+        <v>2.0455968398259538E-3</v>
       </c>
       <c r="M11">
-        <v>4.3452344334346136E-4</v>
+        <v>1.4714531435888967E-4</v>
       </c>
       <c r="N11">
-        <v>2.2072813586299217E-4</v>
+        <v>9.7918152113665583E-5</v>
       </c>
       <c r="O11">
-        <v>1.7413530219372237E-4</v>
+        <v>1.3988647377888685E-5</v>
       </c>
       <c r="P11">
-        <v>5.3800580307657078E-5</v>
+        <v>2.7586044206053948E-5</v>
       </c>
       <c r="Q11">
-        <v>1.0072660652707026E-4</v>
+        <v>2.3421313724183718E-5</v>
       </c>
       <c r="R11">
-        <v>3.1861013057887927E-5</v>
+        <v>3.9844426206524629E-5</v>
       </c>
       <c r="S11">
-        <v>5.749034905495369E-5</v>
+        <v>2.1630112506654246E-5</v>
       </c>
       <c r="T11">
-        <v>6.6940835592817926E-5</v>
+        <v>6.694023601781222E-5</v>
       </c>
       <c r="U11">
-        <v>1.4587059313632913E-4</v>
+        <v>4.6424473088149125E-6</v>
       </c>
       <c r="V11">
-        <v>3.5983673626866381E-4</v>
+        <v>8.0447718947168032E-5</v>
       </c>
       <c r="W11">
-        <v>5.57798561796076E-4</v>
+        <v>1.8357412454532047E-4</v>
       </c>
       <c r="X11">
-        <v>8.9737561584387433E-4</v>
+        <v>2.8526249439005265E-4</v>
       </c>
       <c r="Y11">
-        <v>-2.341532135862371E-4</v>
+        <v>-8.0477340792131682E-6</v>
       </c>
       <c r="Z11">
-        <v>-4.5275792717046738E-5</v>
+        <v>1.6392988037486328E-5</v>
       </c>
       <c r="AA11">
-        <v>-2.1940515186037843E-5</v>
+        <v>1.2367806212827535E-5</v>
       </c>
       <c r="AB11">
-        <v>-1.0920512550130761E-4</v>
+        <v>2.5633872456658571E-5</v>
       </c>
       <c r="AC11">
-        <v>-1.0800691103895562E-4</v>
+        <v>-2.0824376105935257E-6</v>
       </c>
       <c r="AD11">
-        <v>-1.5209831411845418E-4</v>
+        <v>-1.6048139598902594E-6</v>
       </c>
       <c r="AE11">
-        <v>-2.0020844927266175E-5</v>
+        <v>-6.8909094499484789E-7</v>
       </c>
       <c r="AF11">
-        <v>1.0189970461703087E-4</v>
+        <v>5.5704507373661376E-5</v>
       </c>
       <c r="AG11">
-        <v>9.6704351279939681E-5</v>
+        <v>-6.9843132750172849E-5</v>
       </c>
       <c r="AH11">
-        <v>-1.3800031623558101E-3</v>
+        <v>-4.9086118694668837E-4</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="38">
-        <v>0.12629668664812199</v>
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>0.34647898879948608</v>
       </c>
       <c r="C12">
-        <v>1.0057101337731058E-4</v>
+        <v>1.7014735431539614E-5</v>
       </c>
       <c r="D12">
-        <v>1.2103669801985173E-4</v>
+        <v>3.7281333960987144E-5</v>
       </c>
       <c r="E12">
-        <v>-9.7985669002792154E-7</v>
+        <v>-2.9939195959287398E-7</v>
       </c>
       <c r="F12">
-        <v>-1.4682399845287108E-5</v>
+        <v>2.5429778910367629E-4</v>
       </c>
       <c r="G12">
-        <v>1.302547532667631E-4</v>
+        <v>6.234690696741445E-5</v>
       </c>
       <c r="H12">
-        <v>4.4703791866715072E-4</v>
+        <v>9.274503103923426E-5</v>
       </c>
       <c r="I12">
-        <v>9.5444436451339791E-4</v>
+        <v>2.1461950176201428E-4</v>
       </c>
       <c r="J12">
-        <v>6.0994332705733775E-4</v>
+        <v>1.4090607720262282E-4</v>
       </c>
       <c r="K12">
-        <v>1.881914719503051E-4</v>
+        <v>7.571305213158396E-5</v>
       </c>
       <c r="L12">
-        <v>4.3452344334346136E-4</v>
+        <v>1.4714531435888967E-4</v>
       </c>
       <c r="M12">
-        <v>3.8395072377592041E-3</v>
+        <v>1.1014428671440749E-3</v>
       </c>
       <c r="N12">
-        <v>6.706096459341141E-4</v>
+        <v>1.9029526811052724E-4</v>
       </c>
       <c r="O12">
-        <v>-4.8615051631315876E-5</v>
+        <v>-9.2128090534217299E-7</v>
       </c>
       <c r="P12">
-        <v>-3.5313989492048552E-4</v>
+        <v>-1.5759249440377969E-5</v>
       </c>
       <c r="Q12">
-        <v>-7.6659681429089939E-5</v>
+        <v>-1.8592265257971744E-6</v>
       </c>
       <c r="R12">
-        <v>-1.3154136450195807E-4</v>
+        <v>-1.9743163237556756E-5</v>
       </c>
       <c r="S12">
-        <v>-9.5036095835912085E-5</v>
+        <v>-1.5614624692628169E-5</v>
       </c>
       <c r="T12">
-        <v>-5.5436293389776953E-5</v>
+        <v>3.3904187222866909E-5</v>
       </c>
       <c r="U12">
-        <v>5.3473035034097701E-5</v>
+        <v>1.3727052966979519E-5</v>
       </c>
       <c r="V12">
-        <v>4.988396089586726E-4</v>
+        <v>1.6873869551563297E-4</v>
       </c>
       <c r="W12">
-        <v>6.856433321663876E-4</v>
+        <v>2.5117969583884073E-4</v>
       </c>
       <c r="X12">
-        <v>6.8706747879231783E-4</v>
+        <v>2.4851316350501564E-4</v>
       </c>
       <c r="Y12">
-        <v>-4.1611690133029898E-5</v>
+        <v>-9.8107408113617473E-6</v>
       </c>
       <c r="Z12">
-        <v>-9.9796331324579078E-5</v>
+        <v>-2.8894943226470302E-6</v>
       </c>
       <c r="AA12">
-        <v>4.7475255631971702E-6</v>
+        <v>-1.5955024569933821E-5</v>
       </c>
       <c r="AB12">
-        <v>4.5800296727457413E-5</v>
+        <v>5.3026102443205683E-6</v>
       </c>
       <c r="AC12">
-        <v>-7.2491134002944911E-5</v>
+        <v>2.5263063939296327E-6</v>
       </c>
       <c r="AD12">
-        <v>-5.997029590319009E-6</v>
+        <v>-6.7055771447284635E-6</v>
       </c>
       <c r="AE12">
-        <v>1.9220223265266811E-6</v>
+        <v>-2.1175263202509185E-6</v>
       </c>
       <c r="AF12">
-        <v>-9.6390245881394256E-5</v>
+        <v>6.1113135440594947E-5</v>
       </c>
       <c r="AG12">
-        <v>-8.0860940325496811E-6</v>
+        <v>-2.7906108966132409E-5</v>
       </c>
       <c r="AH12">
-        <v>-4.2386937410304254E-3</v>
+        <v>-1.3447942845723978E-3</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="38">
-        <v>-7.6298840673617349E-2</v>
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>4.4903060818315806E-2</v>
       </c>
       <c r="C13">
-        <v>9.8666199291812376E-5</v>
+        <v>2.8281966222033687E-5</v>
       </c>
       <c r="D13">
-        <v>2.2042337206114292E-5</v>
+        <v>3.9608067766064954E-6</v>
       </c>
       <c r="E13">
-        <v>-2.3939063866782768E-7</v>
+        <v>-5.0438824271618217E-8</v>
       </c>
       <c r="F13">
-        <v>1.5621787693530291E-4</v>
+        <v>1.0505917249260882E-4</v>
       </c>
       <c r="G13">
-        <v>1.9813386069095985E-4</v>
+        <v>4.7945414407802503E-5</v>
       </c>
       <c r="H13">
-        <v>9.2294129888505883E-5</v>
+        <v>3.6440535898256804E-5</v>
       </c>
       <c r="I13">
-        <v>2.760852986160759E-4</v>
+        <v>5.3549257344034617E-5</v>
       </c>
       <c r="J13">
-        <v>3.6093354463471728E-4</v>
+        <v>9.8711298663820885E-5</v>
       </c>
       <c r="K13">
-        <v>2.10221685509251E-4</v>
+        <v>7.32218969994281E-5</v>
       </c>
       <c r="L13">
-        <v>2.2072813586299217E-4</v>
+        <v>9.7918152113665583E-5</v>
       </c>
       <c r="M13">
-        <v>6.706096459341141E-4</v>
+        <v>1.9029526811052724E-4</v>
       </c>
       <c r="N13">
-        <v>9.4573086549016444E-4</v>
+        <v>2.9399884647433725E-4</v>
       </c>
       <c r="O13">
-        <v>-3.5575292421954907E-5</v>
+        <v>-1.3344538735134892E-5</v>
       </c>
       <c r="P13">
-        <v>-9.8627559245884956E-5</v>
+        <v>-2.4759233823054853E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.9499275139665348E-5</v>
+        <v>3.9794034730246557E-5</v>
       </c>
       <c r="R13">
-        <v>-5.3898042333655168E-6</v>
+        <v>4.0078650920615861E-5</v>
       </c>
       <c r="S13">
-        <v>9.4398407177180671E-5</v>
+        <v>5.8086489467725478E-5</v>
       </c>
       <c r="T13">
-        <v>1.4641137070244529E-4</v>
+        <v>6.2715508823663133E-5</v>
       </c>
       <c r="U13">
-        <v>5.9130161145322344E-5</v>
+        <v>1.2155842200717765E-5</v>
       </c>
       <c r="V13">
-        <v>3.8877699133514306E-4</v>
+        <v>1.1109765958755105E-4</v>
       </c>
       <c r="W13">
-        <v>6.2806160884849339E-4</v>
+        <v>1.8353039397279037E-4</v>
       </c>
       <c r="X13">
-        <v>6.8831969895167579E-4</v>
+        <v>2.2448459199304969E-4</v>
       </c>
       <c r="Y13">
-        <v>-2.6599524330350141E-5</v>
+        <v>-4.5117499930005861E-6</v>
       </c>
       <c r="Z13">
-        <v>-3.5321640385382441E-5</v>
+        <v>-2.1245140825539805E-6</v>
       </c>
       <c r="AA13">
-        <v>-2.0650844614895371E-5</v>
+        <v>-2.2865778694848706E-5</v>
       </c>
       <c r="AB13">
-        <v>-2.4085914463144176E-6</v>
+        <v>-1.051932596963718E-5</v>
       </c>
       <c r="AC13">
-        <v>-3.1048504886437689E-5</v>
+        <v>-3.4170901979879383E-7</v>
       </c>
       <c r="AD13">
-        <v>-7.7963127592529219E-6</v>
+        <v>-3.9650577393336934E-7</v>
       </c>
       <c r="AE13">
-        <v>2.5838965733139215E-6</v>
+        <v>3.8339127912067575E-7</v>
       </c>
       <c r="AF13">
-        <v>-1.1326044079120866E-4</v>
+        <v>2.586454386411044E-6</v>
       </c>
       <c r="AG13">
-        <v>-5.9733467422663853E-5</v>
+        <v>1.4214948824960058E-5</v>
       </c>
       <c r="AH13">
-        <v>-1.4919844743905264E-3</v>
+        <v>-4.1002794546834617E-4</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A14" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="38">
-        <v>-0.15079621405099455</v>
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>-4.449957493928404E-2</v>
       </c>
       <c r="C14">
-        <v>-1.0924282851627542E-5</v>
+        <v>-4.7159146680466837E-6</v>
       </c>
       <c r="D14">
-        <v>-1.5313396933818924E-5</v>
+        <v>4.4409294069417391E-7</v>
       </c>
       <c r="E14">
-        <v>1.6328392364650055E-7</v>
+        <v>-1.7157702169896841E-9</v>
       </c>
       <c r="F14">
-        <v>2.0739502319431954E-4</v>
+        <v>6.7198166053607404E-5</v>
       </c>
       <c r="G14">
-        <v>-2.9674475556790142E-5</v>
+        <v>1.3906508304091227E-6</v>
       </c>
       <c r="H14">
-        <v>6.4557767285431316E-5</v>
+        <v>7.535805194648551E-6</v>
       </c>
       <c r="I14">
-        <v>-9.2978151404032395E-5</v>
+        <v>1.0989375596878915E-5</v>
       </c>
       <c r="J14">
-        <v>2.5226372102594443E-5</v>
+        <v>1.0395969740821984E-5</v>
       </c>
       <c r="K14">
-        <v>1.7759470640185844E-5</v>
+        <v>5.6363101671872949E-6</v>
       </c>
       <c r="L14">
-        <v>1.7413530219372237E-4</v>
+        <v>1.3988647377888685E-5</v>
       </c>
       <c r="M14">
-        <v>-4.8615051631315876E-5</v>
+        <v>-9.2128090534217299E-7</v>
       </c>
       <c r="N14">
-        <v>-3.5575292421954907E-5</v>
+        <v>-1.3344538735134892E-5</v>
       </c>
       <c r="O14">
-        <v>1.0341113573618817E-3</v>
+        <v>3.3870910966316649E-4</v>
       </c>
       <c r="P14">
-        <v>8.5751853544994831E-4</v>
+        <v>2.6950008593827455E-4</v>
       </c>
       <c r="Q14">
-        <v>3.1859642313753042E-6</v>
+        <v>2.7114116941996266E-5</v>
       </c>
       <c r="R14">
-        <v>2.9206197083012763E-5</v>
+        <v>1.9702771462438123E-5</v>
       </c>
       <c r="S14">
-        <v>5.0678643793409294E-5</v>
+        <v>2.8532131804511868E-5</v>
       </c>
       <c r="T14">
-        <v>6.8257525522385056E-6</v>
+        <v>3.7419295720588488E-5</v>
       </c>
       <c r="U14">
-        <v>-4.5789038649276221E-6</v>
+        <v>-7.6075407188864548E-6</v>
       </c>
       <c r="V14">
-        <v>-2.0181807083701603E-5</v>
+        <v>-4.7939474233765084E-6</v>
       </c>
       <c r="W14">
-        <v>1.0048167739524259E-4</v>
+        <v>2.1812810249503654E-6</v>
       </c>
       <c r="X14">
-        <v>2.2480254162542107E-4</v>
+        <v>2.8030007206983817E-5</v>
       </c>
       <c r="Y14">
-        <v>1.1519968285874962E-5</v>
+        <v>6.0319682123049525E-6</v>
       </c>
       <c r="Z14">
-        <v>-6.2128115490988963E-5</v>
+        <v>5.8989467334996914E-7</v>
       </c>
       <c r="AA14">
-        <v>4.094663567218344E-5</v>
+        <v>3.848608297610885E-6</v>
       </c>
       <c r="AB14">
-        <v>2.9208941476129718E-5</v>
+        <v>1.8233725849835762E-6</v>
       </c>
       <c r="AC14">
-        <v>7.5366144045245143E-6</v>
+        <v>-4.1050275336285233E-6</v>
       </c>
       <c r="AD14">
-        <v>5.376536666589865E-5</v>
+        <v>7.2606381679119695E-6</v>
       </c>
       <c r="AE14">
-        <v>1.7229577971110744E-6</v>
+        <v>2.3738712541169773E-6</v>
       </c>
       <c r="AF14">
-        <v>9.4935005273254908E-5</v>
+        <v>-4.4290345106754803E-6</v>
       </c>
       <c r="AG14">
-        <v>8.5421860749300009E-5</v>
+        <v>-1.3204542636222541E-5</v>
       </c>
       <c r="AH14">
-        <v>-6.4282798152245023E-4</v>
+        <v>-3.5650910730923276E-4</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A15" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="38">
-        <v>-0.18678273043474292</v>
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>-0.16676439736701201</v>
       </c>
       <c r="C15">
-        <v>3.1957366783621534E-5</v>
+        <v>-1.1041129590456291E-5</v>
       </c>
       <c r="D15">
-        <v>8.358582316831504E-7</v>
+        <v>-8.5145851032103213E-8</v>
       </c>
       <c r="E15">
-        <v>-2.9336888750264367E-8</v>
+        <v>-9.7334820705486065E-9</v>
       </c>
       <c r="F15">
-        <v>1.6702388738696976E-4</v>
+        <v>5.974912630999074E-5</v>
       </c>
       <c r="G15">
-        <v>-1.5851946490376954E-5</v>
+        <v>4.752217058899271E-6</v>
       </c>
       <c r="H15">
-        <v>2.4897916565003761E-5</v>
+        <v>1.908592668736551E-5</v>
       </c>
       <c r="I15">
-        <v>-1.694361713841879E-4</v>
+        <v>3.4005389912118262E-5</v>
       </c>
       <c r="J15">
-        <v>-1.0500731929633737E-4</v>
+        <v>2.3325882706940973E-6</v>
       </c>
       <c r="K15">
-        <v>-2.5856482314989696E-5</v>
+        <v>1.6089333802480009E-5</v>
       </c>
       <c r="L15">
-        <v>5.3800580307657078E-5</v>
+        <v>2.7586044206053948E-5</v>
       </c>
       <c r="M15">
-        <v>-3.5313989492048552E-4</v>
+        <v>-1.5759249440377969E-5</v>
       </c>
       <c r="N15">
-        <v>-9.8627559245884956E-5</v>
+        <v>-2.4759233823054853E-5</v>
       </c>
       <c r="O15">
-        <v>8.5751853544994831E-4</v>
+        <v>2.6950008593827455E-4</v>
       </c>
       <c r="P15">
-        <v>1.3446327426517159E-3</v>
+        <v>3.7289734615861313E-4</v>
       </c>
       <c r="Q15">
-        <v>-8.6946603838422912E-6</v>
+        <v>3.4488438346887555E-5</v>
       </c>
       <c r="R15">
-        <v>5.4346538046266786E-6</v>
+        <v>3.6350571930319906E-5</v>
       </c>
       <c r="S15">
-        <v>1.0342830134684488E-4</v>
+        <v>4.9608820155271771E-5</v>
       </c>
       <c r="T15">
-        <v>3.183919478322303E-5</v>
+        <v>7.0942016208504278E-5</v>
       </c>
       <c r="U15">
-        <v>-5.0995602545465774E-5</v>
+        <v>-1.0233838026647469E-5</v>
       </c>
       <c r="V15">
-        <v>1.5832554673048479E-5</v>
+        <v>-6.8847207128987122E-6</v>
       </c>
       <c r="W15">
-        <v>7.2218339928240211E-5</v>
+        <v>6.4576751321694312E-6</v>
       </c>
       <c r="X15">
-        <v>1.8241408358552944E-4</v>
+        <v>6.1897853913644296E-5</v>
       </c>
       <c r="Y15">
-        <v>1.8629891985236596E-5</v>
+        <v>8.4004096726731663E-6</v>
       </c>
       <c r="Z15">
-        <v>-7.9618278410355069E-5</v>
+        <v>1.2397143965766774E-5</v>
       </c>
       <c r="AA15">
-        <v>-8.8914509201160671E-5</v>
+        <v>6.550340284801066E-7</v>
       </c>
       <c r="AB15">
-        <v>-6.0230418948652989E-5</v>
+        <v>-6.709057472451575E-6</v>
       </c>
       <c r="AC15">
-        <v>-3.8375340942774648E-5</v>
+        <v>-4.2569047393710218E-6</v>
       </c>
       <c r="AD15">
-        <v>3.7479989587589673E-5</v>
+        <v>1.0144676555739075E-5</v>
       </c>
       <c r="AE15">
-        <v>7.9513890486140767E-6</v>
+        <v>1.9162699560630375E-6</v>
       </c>
       <c r="AF15">
-        <v>4.2648919476111734E-5</v>
+        <v>2.4217416537024696E-5</v>
       </c>
       <c r="AG15">
-        <v>9.1476558443811271E-5</v>
+        <v>6.9557827706025313E-6</v>
       </c>
       <c r="AH15">
-        <v>-9.2485224058497933E-4</v>
+        <v>-3.6041323162255942E-4</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A16" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="38">
-        <v>5.5929962339993144E-2</v>
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>1.0517937930640858E-4</v>
       </c>
       <c r="C16">
-        <v>-2.7555455138435986E-5</v>
+        <v>2.6933781714179523E-6</v>
       </c>
       <c r="D16">
-        <v>-1.9218169860092027E-5</v>
+        <v>-3.4139154271193679E-6</v>
       </c>
       <c r="E16">
-        <v>1.9027469277679189E-7</v>
+        <v>3.5474901394343246E-8</v>
       </c>
       <c r="F16">
-        <v>5.7832150575601397E-5</v>
+        <v>1.8859042808223617E-5</v>
       </c>
       <c r="G16">
-        <v>1.6464719343808849E-4</v>
+        <v>-1.0654087877799847E-5</v>
       </c>
       <c r="H16">
-        <v>6.2037303488563411E-5</v>
+        <v>1.1079394676554403E-5</v>
       </c>
       <c r="I16">
-        <v>2.0591049505648123E-5</v>
+        <v>2.9639073468858132E-5</v>
       </c>
       <c r="J16">
-        <v>1.0881890631719752E-4</v>
+        <v>1.8403820372043917E-5</v>
       </c>
       <c r="K16">
-        <v>2.9859158132289733E-5</v>
+        <v>2.4108026728469498E-5</v>
       </c>
       <c r="L16">
-        <v>1.0072660652707026E-4</v>
+        <v>2.3421313724183718E-5</v>
       </c>
       <c r="M16">
-        <v>-7.6659681429089939E-5</v>
+        <v>-1.8592265257971744E-6</v>
       </c>
       <c r="N16">
-        <v>-1.9499275139665348E-5</v>
+        <v>3.9794034730246557E-5</v>
       </c>
       <c r="O16">
-        <v>3.1859642313753042E-6</v>
+        <v>2.7114116941996266E-5</v>
       </c>
       <c r="P16">
-        <v>-8.6946603838422912E-6</v>
+        <v>3.4488438346887555E-5</v>
       </c>
       <c r="Q16">
-        <v>4.0084915469471337E-3</v>
+        <v>1.8646799410737287E-3</v>
       </c>
       <c r="R16">
-        <v>3.4403911098617799E-3</v>
+        <v>1.5245882145468249E-3</v>
       </c>
       <c r="S16">
-        <v>3.4336132584923537E-3</v>
+        <v>1.527524534116988E-3</v>
       </c>
       <c r="T16">
-        <v>3.4078270663167377E-3</v>
+        <v>1.5273947327473815E-3</v>
       </c>
       <c r="U16">
-        <v>-1.2588117597152354E-4</v>
+        <v>-3.9001726664155933E-5</v>
       </c>
       <c r="V16">
-        <v>-9.2762782948857037E-5</v>
+        <v>2.2726996277639338E-6</v>
       </c>
       <c r="W16">
-        <v>-5.4033641786654517E-5</v>
+        <v>7.3040099898931594E-6</v>
       </c>
       <c r="X16">
-        <v>-5.6471694608827699E-5</v>
+        <v>3.9868278689456744E-5</v>
       </c>
       <c r="Y16">
-        <v>-6.3420942375914052E-6</v>
+        <v>-2.5260294034497365E-7</v>
       </c>
       <c r="Z16">
-        <v>2.7065457217272993E-5</v>
+        <v>-1.9723961068264902E-5</v>
       </c>
       <c r="AA16">
-        <v>-8.1321952506481542E-5</v>
+        <v>-1.4396953680010792E-6</v>
       </c>
       <c r="AB16">
-        <v>-3.6292188235961809E-5</v>
+        <v>1.2628828807392551E-5</v>
       </c>
       <c r="AC16">
-        <v>-2.8108093008049825E-6</v>
+        <v>1.4353267211168926E-6</v>
       </c>
       <c r="AD16">
-        <v>7.4357286008350188E-6</v>
+        <v>5.2449842174858916E-6</v>
       </c>
       <c r="AE16">
-        <v>7.5249961743966527E-6</v>
+        <v>4.2525644552987444E-8</v>
       </c>
       <c r="AF16">
-        <v>-6.7387341905088792E-5</v>
+        <v>-6.2800149817500428E-5</v>
       </c>
       <c r="AG16">
-        <v>-3.8202984609505782E-5</v>
+        <v>6.30433020147809E-5</v>
       </c>
       <c r="AH16">
-        <v>-3.0812215633848651E-3</v>
+        <v>-1.5056309344537349E-3</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A17" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="38">
-        <v>0.14611599663638014</v>
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>0.12639060995035489</v>
       </c>
       <c r="C17">
-        <v>1.8024529134122181E-5</v>
+        <v>-1.7147839270421265E-6</v>
       </c>
       <c r="D17">
-        <v>-3.7207368112170017E-5</v>
+        <v>-6.6479555301813811E-6</v>
       </c>
       <c r="E17">
-        <v>4.0940823915512384E-7</v>
+        <v>7.1395067679907566E-8</v>
       </c>
       <c r="F17">
-        <v>-1.6557425093882347E-5</v>
+        <v>2.7831266524254261E-5</v>
       </c>
       <c r="G17">
-        <v>3.2193064053452533E-6</v>
+        <v>2.5707758014143844E-6</v>
       </c>
       <c r="H17">
-        <v>-8.3915241487303541E-6</v>
+        <v>1.7736600972095358E-5</v>
       </c>
       <c r="I17">
-        <v>1.0436404571546138E-5</v>
+        <v>1.825425299526777E-5</v>
       </c>
       <c r="J17">
-        <v>4.2584494704953256E-5</v>
+        <v>3.1494262230363868E-5</v>
       </c>
       <c r="K17">
-        <v>1.8451252783496965E-5</v>
+        <v>3.8231072564846825E-5</v>
       </c>
       <c r="L17">
-        <v>3.1861013057887927E-5</v>
+        <v>3.9844426206524629E-5</v>
       </c>
       <c r="M17">
-        <v>-1.3154136450195807E-4</v>
+        <v>-1.9743163237556756E-5</v>
       </c>
       <c r="N17">
-        <v>-5.3898042333655168E-6</v>
+        <v>4.0078650920615861E-5</v>
       </c>
       <c r="O17">
-        <v>2.9206197083012763E-5</v>
+        <v>1.9702771462438123E-5</v>
       </c>
       <c r="P17">
-        <v>5.4346538046266786E-6</v>
+        <v>3.6350571930319906E-5</v>
       </c>
       <c r="Q17">
-        <v>3.4403911098617799E-3</v>
+        <v>1.5245882145468249E-3</v>
       </c>
       <c r="R17">
-        <v>3.9163592011834079E-3</v>
+        <v>1.7055959030868803E-3</v>
       </c>
       <c r="S17">
-        <v>3.579681092796595E-3</v>
+        <v>1.5683689015724706E-3</v>
       </c>
       <c r="T17">
-        <v>3.5529897874271342E-3</v>
+        <v>1.574075363650523E-3</v>
       </c>
       <c r="U17">
-        <v>-8.7527212304665822E-5</v>
+        <v>-4.8204584041293912E-5</v>
       </c>
       <c r="V17">
-        <v>-5.3259432133181614E-5</v>
+        <v>-1.0768951972509024E-5</v>
       </c>
       <c r="W17">
-        <v>-1.8176483037295773E-5</v>
+        <v>-2.3862188827161518E-6</v>
       </c>
       <c r="X17">
-        <v>-4.31946801037527E-6</v>
+        <v>3.5363183477407373E-5</v>
       </c>
       <c r="Y17">
-        <v>-1.4434844579493559E-6</v>
+        <v>-7.797714613088234E-7</v>
       </c>
       <c r="Z17">
-        <v>3.9087850740341388E-5</v>
+        <v>-1.4058914888288859E-5</v>
       </c>
       <c r="AA17">
-        <v>-8.3701324050491129E-6</v>
+        <v>3.9067588724307962E-6</v>
       </c>
       <c r="AB17">
-        <v>-6.5249161864832598E-5</v>
+        <v>1.4714743862669088E-5</v>
       </c>
       <c r="AC17">
-        <v>-9.6954628974193374E-6</v>
+        <v>-3.2676058528164232E-6</v>
       </c>
       <c r="AD17">
-        <v>4.7125377417273399E-5</v>
+        <v>7.7917847755203324E-6</v>
       </c>
       <c r="AE17">
-        <v>-1.5207664489067278E-6</v>
+        <v>-9.3068543704272926E-7</v>
       </c>
       <c r="AF17">
-        <v>1.1248230807839148E-4</v>
+        <v>-8.0066283065696265E-5</v>
       </c>
       <c r="AG17">
-        <v>-6.1138647521071453E-5</v>
+        <v>5.4499156762441632E-5</v>
       </c>
       <c r="AH17">
-        <v>-2.8473312645004769E-3</v>
+        <v>-1.467426880663804E-3</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A18" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="38">
-        <v>0.13111754238930215</v>
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>0.11480468843037889</v>
       </c>
       <c r="C18">
-        <v>3.4910458367521947E-5</v>
+        <v>-6.9245127771184097E-6</v>
       </c>
       <c r="D18">
-        <v>-1.3260913622587542E-5</v>
+        <v>-5.2097277396713001E-6</v>
       </c>
       <c r="E18">
-        <v>2.158837279470273E-7</v>
+        <v>7.4644016197495944E-8</v>
       </c>
       <c r="F18">
-        <v>5.8865848806807027E-5</v>
+        <v>3.2335601107875621E-5</v>
       </c>
       <c r="G18">
-        <v>1.1470441331172956E-4</v>
+        <v>-9.2034062069427025E-6</v>
       </c>
       <c r="H18">
-        <v>6.3377568663052262E-5</v>
+        <v>1.0622134486376772E-5</v>
       </c>
       <c r="I18">
-        <v>2.974429594526766E-5</v>
+        <v>4.5160250666517451E-5</v>
       </c>
       <c r="J18">
-        <v>3.4509861956094192E-5</v>
+        <v>3.0971071045037907E-5</v>
       </c>
       <c r="K18">
-        <v>8.1658996643294487E-5</v>
+        <v>3.8175179944273247E-5</v>
       </c>
       <c r="L18">
-        <v>5.749034905495369E-5</v>
+        <v>2.1630112506654246E-5</v>
       </c>
       <c r="M18">
-        <v>-9.5036095835912085E-5</v>
+        <v>-1.5614624692628169E-5</v>
       </c>
       <c r="N18">
-        <v>9.4398407177180671E-5</v>
+        <v>5.8086489467725478E-5</v>
       </c>
       <c r="O18">
-        <v>5.0678643793409294E-5</v>
+        <v>2.8532131804511868E-5</v>
       </c>
       <c r="P18">
-        <v>1.0342830134684488E-4</v>
+        <v>4.9608820155271771E-5</v>
       </c>
       <c r="Q18">
-        <v>3.4336132584923537E-3</v>
+        <v>1.527524534116988E-3</v>
       </c>
       <c r="R18">
-        <v>3.579681092796595E-3</v>
+        <v>1.5683689015724706E-3</v>
       </c>
       <c r="S18">
-        <v>4.0700066228423612E-3</v>
+        <v>1.6740265772674742E-3</v>
       </c>
       <c r="T18">
-        <v>3.8293432459748549E-3</v>
+        <v>1.6412562864208558E-3</v>
       </c>
       <c r="U18">
-        <v>-9.9541216228124545E-5</v>
+        <v>-5.1256446743733761E-5</v>
       </c>
       <c r="V18">
-        <v>-1.3036468124629104E-4</v>
+        <v>-1.8996843694034353E-5</v>
       </c>
       <c r="W18">
-        <v>-1.1579194471208749E-4</v>
+        <v>-1.2788827295730362E-5</v>
       </c>
       <c r="X18">
-        <v>-1.8635472954370985E-4</v>
+        <v>1.4380440138135934E-5</v>
       </c>
       <c r="Y18">
-        <v>9.2564692295668712E-6</v>
+        <v>-8.3418091061354915E-7</v>
       </c>
       <c r="Z18">
-        <v>-1.0713185267097647E-5</v>
+        <v>-1.052086583911197E-5</v>
       </c>
       <c r="AA18">
-        <v>7.8938083454248038E-6</v>
+        <v>-1.5879676095799681E-6</v>
       </c>
       <c r="AB18">
-        <v>-2.1729824573275391E-5</v>
+        <v>1.1564449532285677E-5</v>
       </c>
       <c r="AC18">
-        <v>-3.2451264433821592E-6</v>
+        <v>-4.4404239775427219E-6</v>
       </c>
       <c r="AD18">
-        <v>7.2611698492275399E-5</v>
+        <v>9.4581630565336106E-6</v>
       </c>
       <c r="AE18">
-        <v>-3.8592124665402837E-6</v>
+        <v>-3.5445931540132572E-6</v>
       </c>
       <c r="AF18">
-        <v>2.3709313022762454E-5</v>
+        <v>-6.6937013744427891E-5</v>
       </c>
       <c r="AG18">
-        <v>-4.6591702850437263E-6</v>
+        <v>1.0965859903810769E-4</v>
       </c>
       <c r="AH18">
-        <v>-3.6697974996654451E-3</v>
+        <v>-1.5568172128593346E-3</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A19" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="38">
-        <v>0.16014029807504901</v>
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>0.13025669812307256</v>
       </c>
       <c r="C19">
-        <v>-2.1923498827584511E-5</v>
+        <v>-1.8168289107175546E-5</v>
       </c>
       <c r="D19">
-        <v>1.86722563590956E-5</v>
+        <v>-3.1998874124452616E-7</v>
       </c>
       <c r="E19">
-        <v>-2.756862630082573E-8</v>
+        <v>4.1775474556591452E-8</v>
       </c>
       <c r="F19">
-        <v>-1.2533749472519212E-5</v>
+        <v>8.3294080954246811E-5</v>
       </c>
       <c r="G19">
-        <v>1.1051684733845332E-4</v>
+        <v>-2.6804435052867977E-6</v>
       </c>
       <c r="H19">
-        <v>-3.3214981508635541E-6</v>
+        <v>2.1576007697365902E-5</v>
       </c>
       <c r="I19">
-        <v>1.3770076818322372E-4</v>
+        <v>8.316455515061785E-5</v>
       </c>
       <c r="J19">
-        <v>5.8840747626688503E-5</v>
+        <v>4.6795693861346073E-5</v>
       </c>
       <c r="K19">
-        <v>5.5186444124918519E-5</v>
+        <v>3.7053637074313008E-5</v>
       </c>
       <c r="L19">
-        <v>6.6940835592817926E-5</v>
+        <v>6.694023601781222E-5</v>
       </c>
       <c r="M19">
-        <v>-5.5436293389776953E-5</v>
+        <v>3.3904187222866909E-5</v>
       </c>
       <c r="N19">
-        <v>1.4641137070244529E-4</v>
+        <v>6.2715508823663133E-5</v>
       </c>
       <c r="O19">
-        <v>6.8257525522385056E-6</v>
+        <v>3.7419295720588488E-5</v>
       </c>
       <c r="P19">
-        <v>3.183919478322303E-5</v>
+        <v>7.0942016208504278E-5</v>
       </c>
       <c r="Q19">
-        <v>3.4078270663167377E-3</v>
+        <v>1.5273947327473815E-3</v>
       </c>
       <c r="R19">
-        <v>3.5529897874271342E-3</v>
+        <v>1.574075363650523E-3</v>
       </c>
       <c r="S19">
-        <v>3.8293432459748549E-3</v>
+        <v>1.6412562864208558E-3</v>
       </c>
       <c r="T19">
-        <v>4.9244173003207764E-3</v>
+        <v>1.9157466189749777E-3</v>
       </c>
       <c r="U19">
-        <v>-9.9696594104833826E-5</v>
+        <v>-5.3377375947653089E-5</v>
       </c>
       <c r="V19">
-        <v>-7.1008541938393584E-5</v>
+        <v>-2.2584656682524289E-5</v>
       </c>
       <c r="W19">
-        <v>-4.1083348365507149E-5</v>
+        <v>2.4686585155257366E-6</v>
       </c>
       <c r="X19">
-        <v>-8.6428748302783825E-5</v>
+        <v>2.5643365632834392E-5</v>
       </c>
       <c r="Y19">
-        <v>-9.771643842188648E-6</v>
+        <v>-9.3024835464164087E-7</v>
       </c>
       <c r="Z19">
-        <v>-1.6345882371762428E-5</v>
+        <v>2.8569430282901422E-6</v>
       </c>
       <c r="AA19">
-        <v>-1.4067172378131806E-4</v>
+        <v>4.6914780677772866E-6</v>
       </c>
       <c r="AB19">
-        <v>-8.1763655533166266E-5</v>
+        <v>2.7798213755484389E-5</v>
       </c>
       <c r="AC19">
-        <v>1.5904935439195141E-5</v>
+        <v>1.3857414005524998E-5</v>
       </c>
       <c r="AD19">
-        <v>6.9559538646721047E-5</v>
+        <v>2.1622205102609596E-5</v>
       </c>
       <c r="AE19">
-        <v>8.0584579235854132E-6</v>
+        <v>-5.6648597220772257E-6</v>
       </c>
       <c r="AF19">
-        <v>-1.4889437212913491E-4</v>
+        <v>-2.6824390461460202E-5</v>
       </c>
       <c r="AG19">
-        <v>-5.0057072073762593E-5</v>
+        <v>1.1407563614440679E-4</v>
       </c>
       <c r="AH19">
-        <v>-4.7605309573818463E-3</v>
+        <v>-1.7386154259039013E-3</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A20" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="38">
-        <v>-3.501652449415784E-2</v>
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
+        <v>-1.7707559575066509E-2</v>
       </c>
       <c r="C20">
-        <v>-1.5840744043522951E-5</v>
+        <v>-8.8323946264114176E-7</v>
       </c>
       <c r="D20">
-        <v>-1.5084395861254279E-6</v>
+        <v>-1.0816350779852603E-6</v>
       </c>
       <c r="E20">
-        <v>4.2763933223505174E-8</v>
+        <v>1.6943706177842E-8</v>
       </c>
       <c r="F20">
-        <v>1.3167381407566887E-4</v>
+        <v>-2.7399546323482926E-5</v>
       </c>
       <c r="G20">
-        <v>-3.4383000366098766E-5</v>
+        <v>-9.9782762985754039E-6</v>
       </c>
       <c r="H20">
-        <v>2.4219941243844184E-5</v>
+        <v>-1.1600367477558214E-7</v>
       </c>
       <c r="I20">
-        <v>1.0099203508079872E-4</v>
+        <v>-1.9031941732413339E-5</v>
       </c>
       <c r="J20">
-        <v>8.3600379723594378E-5</v>
+        <v>-9.9815545356662094E-6</v>
       </c>
       <c r="K20">
-        <v>5.2769921137823525E-5</v>
+        <v>1.1983906798044313E-5</v>
       </c>
       <c r="L20">
-        <v>1.4587059313632913E-4</v>
+        <v>4.6424473088149125E-6</v>
       </c>
       <c r="M20">
-        <v>5.3473035034097701E-5</v>
+        <v>1.3727052966979519E-5</v>
       </c>
       <c r="N20">
-        <v>5.9130161145322344E-5</v>
+        <v>1.2155842200717765E-5</v>
       </c>
       <c r="O20">
-        <v>-4.5789038649276221E-6</v>
+        <v>-7.6075407188864548E-6</v>
       </c>
       <c r="P20">
-        <v>-5.0995602545465774E-5</v>
+        <v>-1.0233838026647469E-5</v>
       </c>
       <c r="Q20">
-        <v>-1.2588117597152354E-4</v>
+        <v>-3.9001726664155933E-5</v>
       </c>
       <c r="R20">
-        <v>-8.7527212304665822E-5</v>
+        <v>-4.8204584041293912E-5</v>
       </c>
       <c r="S20">
-        <v>-9.9541216228124545E-5</v>
+        <v>-5.1256446743733761E-5</v>
       </c>
       <c r="T20">
-        <v>-9.9696594104833826E-5</v>
+        <v>-5.3377375947653089E-5</v>
       </c>
       <c r="U20">
-        <v>1.0158731132574252E-3</v>
+        <v>3.8044752883478148E-4</v>
       </c>
       <c r="V20">
-        <v>5.813295111976542E-4</v>
+        <v>1.8920882960664817E-4</v>
       </c>
       <c r="W20">
-        <v>5.9668071872875288E-4</v>
+        <v>2.027932675978025E-4</v>
       </c>
       <c r="X20">
-        <v>6.1220163830072384E-4</v>
+        <v>2.1291623580471463E-4</v>
       </c>
       <c r="Y20">
-        <v>-2.8338519565757787E-5</v>
+        <v>-2.2501259342218121E-5</v>
       </c>
       <c r="Z20">
-        <v>5.8393408688578349E-6</v>
+        <v>-4.6237140243578243E-6</v>
       </c>
       <c r="AA20">
-        <v>1.0656496909548584E-4</v>
+        <v>1.0119171911530556E-5</v>
       </c>
       <c r="AB20">
-        <v>-5.9276113539097266E-5</v>
+        <v>1.8817991800261997E-5</v>
       </c>
       <c r="AC20">
-        <v>-9.9821541883961143E-6</v>
+        <v>9.8166227313689419E-7</v>
       </c>
       <c r="AD20">
-        <v>-2.8203891738341996E-5</v>
+        <v>5.13361432288429E-6</v>
       </c>
       <c r="AE20">
-        <v>-4.1077524336397339E-6</v>
+        <v>-2.2444779625452416E-7</v>
       </c>
       <c r="AF20">
-        <v>9.1212932078938358E-5</v>
+        <v>1.5918157504508316E-5</v>
       </c>
       <c r="AG20">
-        <v>1.6335431158314074E-5</v>
+        <v>-4.2399603302213883E-5</v>
       </c>
       <c r="AH20">
-        <v>-4.6949757222860817E-4</v>
+        <v>-9.3509380639289486E-5</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A21" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="38">
-        <v>-4.02370351802269E-2</v>
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <v>-7.9518071915985006E-2</v>
       </c>
       <c r="C21">
-        <v>3.428607753602349E-7</v>
+        <v>1.7734779008110136E-6</v>
       </c>
       <c r="D21">
-        <v>-1.7773091032660448E-5</v>
+        <v>-7.8535629662447216E-6</v>
       </c>
       <c r="E21">
-        <v>2.4770518453236893E-7</v>
+        <v>9.7629430875929667E-8</v>
       </c>
       <c r="F21">
-        <v>3.1487986948351465E-4</v>
+        <v>9.9222113475816925E-6</v>
       </c>
       <c r="G21">
-        <v>3.2146133830892188E-4</v>
+        <v>9.0903697544694756E-5</v>
       </c>
       <c r="H21">
-        <v>7.3890610862375236E-5</v>
+        <v>3.3487189209837325E-5</v>
       </c>
       <c r="I21">
-        <v>3.7164053050896609E-4</v>
+        <v>5.0701581506823828E-5</v>
       </c>
       <c r="J21">
-        <v>2.0800919217396817E-4</v>
+        <v>5.944315608214022E-5</v>
       </c>
       <c r="K21">
-        <v>4.466868135523679E-4</v>
+        <v>1.0655522925317073E-4</v>
       </c>
       <c r="L21">
-        <v>3.5983673626866381E-4</v>
+        <v>8.0447718947168032E-5</v>
       </c>
       <c r="M21">
-        <v>4.988396089586726E-4</v>
+        <v>1.6873869551563297E-4</v>
       </c>
       <c r="N21">
-        <v>3.8877699133514306E-4</v>
+        <v>1.1109765958755105E-4</v>
       </c>
       <c r="O21">
-        <v>-2.0181807083701603E-5</v>
+        <v>-4.7939474233765084E-6</v>
       </c>
       <c r="P21">
-        <v>1.5832554673048479E-5</v>
+        <v>-6.8847207128987122E-6</v>
       </c>
       <c r="Q21">
-        <v>-9.2762782948857037E-5</v>
+        <v>2.2726996277639338E-6</v>
       </c>
       <c r="R21">
-        <v>-5.3259432133181614E-5</v>
+        <v>-1.0768951972509024E-5</v>
       </c>
       <c r="S21">
-        <v>-1.3036468124629104E-4</v>
+        <v>-1.8996843694034353E-5</v>
       </c>
       <c r="T21">
-        <v>-7.1008541938393584E-5</v>
+        <v>-2.2584656682524289E-5</v>
       </c>
       <c r="U21">
-        <v>5.813295111976542E-4</v>
+        <v>1.8920882960664817E-4</v>
       </c>
       <c r="V21">
-        <v>1.5171451200689757E-3</v>
+        <v>4.3863560396770364E-4</v>
       </c>
       <c r="W21">
-        <v>1.2648827026940685E-3</v>
+        <v>3.6388604682990752E-4</v>
       </c>
       <c r="X21">
-        <v>1.3450834890493817E-3</v>
+        <v>4.0468157361533052E-4</v>
       </c>
       <c r="Y21">
-        <v>-9.6535345479415593E-5</v>
+        <v>-1.8830466355007801E-5</v>
       </c>
       <c r="Z21">
-        <v>-2.6642680056280122E-5</v>
+        <v>1.1026948491907288E-6</v>
       </c>
       <c r="AA21">
-        <v>1.1633136887157414E-5</v>
+        <v>6.6794911045503386E-6</v>
       </c>
       <c r="AB21">
-        <v>-2.0838407905430817E-4</v>
+        <v>7.7291716222656137E-6</v>
       </c>
       <c r="AC21">
-        <v>-2.8743008927630681E-5</v>
+        <v>-4.6543314710034228E-6</v>
       </c>
       <c r="AD21">
-        <v>-1.0636340515064426E-5</v>
+        <v>-1.7775563094145976E-6</v>
       </c>
       <c r="AE21">
-        <v>-5.4006124209891068E-6</v>
+        <v>-1.2146413068034047E-6</v>
       </c>
       <c r="AF21">
-        <v>-1.4749834336640457E-5</v>
+        <v>-2.3160805360473557E-5</v>
       </c>
       <c r="AG21">
-        <v>-5.5123365420984183E-5</v>
+        <v>3.122787769808155E-6</v>
       </c>
       <c r="AH21">
-        <v>-9.8867820574509045E-4</v>
+        <v>-2.3432005834378265E-4</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A22" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="38">
-        <v>-3.881347305644745E-3</v>
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
+        <v>6.6798112001766066E-2</v>
       </c>
       <c r="C22">
-        <v>-3.2138066265636529E-5</v>
+        <v>-8.896182731514779E-7</v>
       </c>
       <c r="D22">
-        <v>-1.7725428851976158E-5</v>
+        <v>-9.8686119561850746E-6</v>
       </c>
       <c r="E22">
-        <v>2.5616557819447479E-7</v>
+        <v>1.1840764470854318E-7</v>
       </c>
       <c r="F22">
-        <v>4.3253707584346994E-4</v>
+        <v>6.4620014842669914E-5</v>
       </c>
       <c r="G22">
-        <v>4.8632484079167186E-4</v>
+        <v>1.4559728788384363E-4</v>
       </c>
       <c r="H22">
-        <v>1.8472645389788257E-4</v>
+        <v>5.4354381170091802E-5</v>
       </c>
       <c r="I22">
-        <v>5.4424387010272492E-4</v>
+        <v>1.5567129731536389E-4</v>
       </c>
       <c r="J22">
-        <v>5.7406931778274811E-4</v>
+        <v>1.620750621956659E-4</v>
       </c>
       <c r="K22">
-        <v>5.8373464004820316E-4</v>
+        <v>1.4969588304935945E-4</v>
       </c>
       <c r="L22">
-        <v>5.57798561796076E-4</v>
+        <v>1.8357412454532047E-4</v>
       </c>
       <c r="M22">
-        <v>6.856433321663876E-4</v>
+        <v>2.5117969583884073E-4</v>
       </c>
       <c r="N22">
-        <v>6.2806160884849339E-4</v>
+        <v>1.8353039397279037E-4</v>
       </c>
       <c r="O22">
-        <v>1.0048167739524259E-4</v>
+        <v>2.1812810249503654E-6</v>
       </c>
       <c r="P22">
-        <v>7.2218339928240211E-5</v>
+        <v>6.4576751321694312E-6</v>
       </c>
       <c r="Q22">
-        <v>-5.4033641786654517E-5</v>
+        <v>7.3040099898931594E-6</v>
       </c>
       <c r="R22">
-        <v>-1.8176483037295773E-5</v>
+        <v>-2.3862188827161518E-6</v>
       </c>
       <c r="S22">
-        <v>-1.1579194471208749E-4</v>
+        <v>-1.2788827295730362E-5</v>
       </c>
       <c r="T22">
-        <v>-4.1083348365507149E-5</v>
+        <v>2.4686585155257366E-6</v>
       </c>
       <c r="U22">
-        <v>5.9668071872875288E-4</v>
+        <v>2.027932675978025E-4</v>
       </c>
       <c r="V22">
-        <v>1.2648827026940685E-3</v>
+        <v>3.6388604682990752E-4</v>
       </c>
       <c r="W22">
-        <v>1.9105590169133206E-3</v>
+        <v>6.0221727416450549E-4</v>
       </c>
       <c r="X22">
-        <v>1.6423708713589138E-3</v>
+        <v>5.1600077789828557E-4</v>
       </c>
       <c r="Y22">
-        <v>-7.1103173480543353E-5</v>
+        <v>-2.1921627459282546E-5</v>
       </c>
       <c r="Z22">
-        <v>-8.2245225317856437E-6</v>
+        <v>-2.033713215092019E-6</v>
       </c>
       <c r="AA22">
-        <v>-3.3682328036077408E-5</v>
+        <v>2.059334929371837E-5</v>
       </c>
       <c r="AB22">
-        <v>-2.1461889760550736E-4</v>
+        <v>3.841321490016901E-5</v>
       </c>
       <c r="AC22">
-        <v>-3.0904589787286583E-5</v>
+        <v>-1.0339851803457952E-5</v>
       </c>
       <c r="AD22">
-        <v>-2.9126565764760052E-5</v>
+        <v>2.1846177878594077E-6</v>
       </c>
       <c r="AE22">
-        <v>-4.5520603148301633E-6</v>
+        <v>-5.1613238670847993E-7</v>
       </c>
       <c r="AF22">
-        <v>-6.8161253642254511E-5</v>
+        <v>1.7454881028803595E-5</v>
       </c>
       <c r="AG22">
-        <v>-6.0785059325890332E-5</v>
+        <v>-1.4045586543320388E-5</v>
       </c>
       <c r="AH22">
-        <v>-1.5333210253611991E-3</v>
+        <v>-3.5609678647426519E-4</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A23" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="38">
-        <v>3.805806987920729E-2</v>
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>0.18123013212916897</v>
       </c>
       <c r="C23">
-        <v>-2.7153992286396879E-5</v>
+        <v>-3.2711686405825264E-6</v>
       </c>
       <c r="D23">
-        <v>-2.6832264878845274E-5</v>
+        <v>-1.3727119044301492E-5</v>
       </c>
       <c r="E23">
-        <v>3.2423004978606971E-7</v>
+        <v>1.4672545119740495E-7</v>
       </c>
       <c r="F23">
-        <v>5.3990332216988712E-4</v>
+        <v>1.415563108633939E-4</v>
       </c>
       <c r="G23">
-        <v>6.8591481507435798E-4</v>
+        <v>2.2500113106381915E-4</v>
       </c>
       <c r="H23">
-        <v>4.724673710286998E-4</v>
+        <v>1.1919672814284108E-4</v>
       </c>
       <c r="I23">
-        <v>6.2478990679459313E-4</v>
+        <v>2.3676000305362363E-4</v>
       </c>
       <c r="J23">
-        <v>8.0977191829111408E-4</v>
+        <v>2.4718244111586392E-4</v>
       </c>
       <c r="K23">
-        <v>7.8361098591835728E-4</v>
+        <v>2.266061115396576E-4</v>
       </c>
       <c r="L23">
-        <v>8.9737561584387433E-4</v>
+        <v>2.8526249439005265E-4</v>
       </c>
       <c r="M23">
-        <v>6.8706747879231783E-4</v>
+        <v>2.4851316350501564E-4</v>
       </c>
       <c r="N23">
-        <v>6.8831969895167579E-4</v>
+        <v>2.2448459199304969E-4</v>
       </c>
       <c r="O23">
-        <v>2.2480254162542107E-4</v>
+        <v>2.8030007206983817E-5</v>
       </c>
       <c r="P23">
-        <v>1.8241408358552944E-4</v>
+        <v>6.1897853913644296E-5</v>
       </c>
       <c r="Q23">
-        <v>-5.6471694608827699E-5</v>
+        <v>3.9868278689456744E-5</v>
       </c>
       <c r="R23">
-        <v>-4.31946801037527E-6</v>
+        <v>3.5363183477407373E-5</v>
       </c>
       <c r="S23">
-        <v>-1.8635472954370985E-4</v>
+        <v>1.4380440138135934E-5</v>
       </c>
       <c r="T23">
-        <v>-8.6428748302783825E-5</v>
+        <v>2.5643365632834392E-5</v>
       </c>
       <c r="U23">
-        <v>6.1220163830072384E-4</v>
+        <v>2.1291623580471463E-4</v>
       </c>
       <c r="V23">
-        <v>1.3450834890493817E-3</v>
+        <v>4.0468157361533052E-4</v>
       </c>
       <c r="W23">
-        <v>1.6423708713589138E-3</v>
+        <v>5.1600077789828557E-4</v>
       </c>
       <c r="X23">
-        <v>2.7568481167001861E-3</v>
+        <v>8.0792500289845082E-4</v>
       </c>
       <c r="Y23">
-        <v>-1.0335704860065258E-4</v>
+        <v>-2.6172106146292215E-5</v>
       </c>
       <c r="Z23">
-        <v>1.1576144370683129E-4</v>
+        <v>4.3822429407635821E-6</v>
       </c>
       <c r="AA23">
-        <v>2.0992559469369589E-4</v>
+        <v>2.1499750650866097E-5</v>
       </c>
       <c r="AB23">
-        <v>-2.6004663333747881E-4</v>
+        <v>4.2177690617442783E-5</v>
       </c>
       <c r="AC23">
-        <v>-9.9817814837424893E-6</v>
+        <v>-1.4940669143380993E-5</v>
       </c>
       <c r="AD23">
-        <v>1.5731992713049353E-5</v>
+        <v>7.2247584668474172E-6</v>
       </c>
       <c r="AE23">
-        <v>1.5917604861093399E-7</v>
+        <v>-1.3215835730080525E-6</v>
       </c>
       <c r="AF23">
-        <v>3.1196921778907242E-4</v>
+        <v>-5.5140316404051143E-7</v>
       </c>
       <c r="AG23">
-        <v>-9.5161998228145345E-5</v>
+        <v>1.9408845130939245E-7</v>
       </c>
       <c r="AH23">
-        <v>-1.8692673049336269E-3</v>
+        <v>-4.1705401577839469E-4</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A24" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="38">
-        <v>5.664086714726675E-3</v>
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24">
+        <v>6.8112852404328086E-2</v>
       </c>
       <c r="C24">
-        <v>8.0515421347049005E-6</v>
+        <v>1.9658349644189244E-7</v>
       </c>
       <c r="D24">
-        <v>5.1918775570460752E-7</v>
+        <v>6.0090435756407827E-8</v>
       </c>
       <c r="E24">
-        <v>-7.5615373483454625E-9</v>
+        <v>-2.35860686816834E-9</v>
       </c>
       <c r="F24">
-        <v>-2.1635937740960531E-4</v>
+        <v>1.4105222919395916E-5</v>
       </c>
       <c r="G24">
-        <v>-3.7349350146862023E-5</v>
+        <v>-4.8937747131196482E-6</v>
       </c>
       <c r="H24">
-        <v>-3.9699879976002196E-5</v>
+        <v>-1.8078586482805678E-6</v>
       </c>
       <c r="I24">
-        <v>-1.791520235219863E-4</v>
+        <v>-5.0831646605438655E-6</v>
       </c>
       <c r="J24">
-        <v>-5.0371644623542834E-5</v>
+        <v>-2.0470513619803131E-6</v>
       </c>
       <c r="K24">
-        <v>-6.529180612947682E-5</v>
+        <v>-4.5630648247887527E-6</v>
       </c>
       <c r="L24">
-        <v>-2.341532135862371E-4</v>
+        <v>-8.0477340792131682E-6</v>
       </c>
       <c r="M24">
-        <v>-4.1611690133029898E-5</v>
+        <v>-9.8107408113617473E-6</v>
       </c>
       <c r="N24">
-        <v>-2.6599524330350141E-5</v>
+        <v>-4.5117499930005861E-6</v>
       </c>
       <c r="O24">
-        <v>1.1519968285874962E-5</v>
+        <v>6.0319682123049525E-6</v>
       </c>
       <c r="P24">
-        <v>1.8629891985236596E-5</v>
+        <v>8.4004096726731663E-6</v>
       </c>
       <c r="Q24">
-        <v>-6.3420942375914052E-6</v>
+        <v>-2.5260294034497365E-7</v>
       </c>
       <c r="R24">
-        <v>-1.4434844579493559E-6</v>
+        <v>-7.797714613088234E-7</v>
       </c>
       <c r="S24">
-        <v>9.2564692295668712E-6</v>
+        <v>-8.3418091061354915E-7</v>
       </c>
       <c r="T24">
-        <v>-9.771643842188648E-6</v>
+        <v>-9.3024835464164087E-7</v>
       </c>
       <c r="U24">
-        <v>-2.8338519565757787E-5</v>
+        <v>-2.2501259342218121E-5</v>
       </c>
       <c r="V24">
-        <v>-9.6535345479415593E-5</v>
+        <v>-1.8830466355007801E-5</v>
       </c>
       <c r="W24">
-        <v>-7.1103173480543353E-5</v>
+        <v>-2.1921627459282546E-5</v>
       </c>
       <c r="X24">
-        <v>-1.0335704860065258E-4</v>
+        <v>-2.6172106146292215E-5</v>
       </c>
       <c r="Y24">
-        <v>8.1698854214131981E-5</v>
+        <v>8.6177084211524257E-6</v>
       </c>
       <c r="Z24">
-        <v>2.4102877113365254E-6</v>
+        <v>3.5750556969473167E-6</v>
       </c>
       <c r="AA24">
-        <v>-7.0380238409838087E-6</v>
+        <v>2.9325199188312531E-6</v>
       </c>
       <c r="AB24">
-        <v>1.0836776883040305E-5</v>
+        <v>4.427211406228725E-6</v>
       </c>
       <c r="AC24">
-        <v>3.8725227381425674E-6</v>
+        <v>-5.1723405676291268E-8</v>
       </c>
       <c r="AD24">
-        <v>2.569093492204676E-6</v>
+        <v>1.8921581336529334E-6</v>
       </c>
       <c r="AE24">
-        <v>4.164501402546201E-6</v>
+        <v>2.0339251107063148E-7</v>
       </c>
       <c r="AF24">
-        <v>-3.6407157048884685E-5</v>
+        <v>8.8913054717165445E-7</v>
       </c>
       <c r="AG24">
-        <v>-9.7284431197457737E-6</v>
+        <v>-1.1903808266144646E-6</v>
       </c>
       <c r="AH24">
-        <v>-8.5128889759942168E-7</v>
+        <v>6.6153331256053365E-7</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A25" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="38">
-        <v>4.3881566025756431</v>
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25">
+        <v>3.1417848826428805</v>
       </c>
       <c r="C25">
-        <v>-1.0205046965530909E-5</v>
+        <v>-3.6361055621319477E-6</v>
       </c>
       <c r="D25">
-        <v>-8.1333625158732075E-6</v>
+        <v>1.5359858545935693E-7</v>
       </c>
       <c r="E25">
-        <v>4.7555092811607297E-8</v>
+        <v>-3.2791824408925183E-9</v>
       </c>
       <c r="F25">
-        <v>-3.0239507218456736E-5</v>
+        <v>4.0836040416890849E-5</v>
       </c>
       <c r="G25">
-        <v>-1.9885634365762668E-5</v>
+        <v>2.0006181168719984E-6</v>
       </c>
       <c r="H25">
-        <v>4.2808629502101054E-5</v>
+        <v>2.649117421418747E-6</v>
       </c>
       <c r="I25">
-        <v>1.9066378968074667E-4</v>
+        <v>-1.7398908757316087E-5</v>
       </c>
       <c r="J25">
-        <v>-2.0095609045942399E-5</v>
+        <v>6.2122950676191021E-6</v>
       </c>
       <c r="K25">
-        <v>-5.821300778029295E-5</v>
+        <v>5.6161638106325883E-6</v>
       </c>
       <c r="L25">
-        <v>-4.5275792717046738E-5</v>
+        <v>1.6392988037486328E-5</v>
       </c>
       <c r="M25">
-        <v>-9.9796331324579078E-5</v>
+        <v>-2.8894943226470302E-6</v>
       </c>
       <c r="N25">
-        <v>-3.5321640385382441E-5</v>
+        <v>-2.1245140825539805E-6</v>
       </c>
       <c r="O25">
-        <v>-6.2128115490988963E-5</v>
+        <v>5.8989467334996914E-7</v>
       </c>
       <c r="P25">
-        <v>-7.9618278410355069E-5</v>
+        <v>1.2397143965766774E-5</v>
       </c>
       <c r="Q25">
-        <v>2.7065457217272993E-5</v>
+        <v>-1.9723961068264902E-5</v>
       </c>
       <c r="R25">
-        <v>3.9087850740341388E-5</v>
+        <v>-1.4058914888288859E-5</v>
       </c>
       <c r="S25">
-        <v>-1.0713185267097647E-5</v>
+        <v>-1.052086583911197E-5</v>
       </c>
       <c r="T25">
-        <v>-1.6345882371762428E-5</v>
+        <v>2.8569430282901422E-6</v>
       </c>
       <c r="U25">
-        <v>5.8393408688578349E-6</v>
+        <v>-4.6237140243578243E-6</v>
       </c>
       <c r="V25">
-        <v>-2.6642680056280122E-5</v>
+        <v>1.1026948491907288E-6</v>
       </c>
       <c r="W25">
-        <v>-8.2245225317856437E-6</v>
+        <v>-2.033713215092019E-6</v>
       </c>
       <c r="X25">
-        <v>1.1576144370683129E-4</v>
+        <v>4.3822429407635821E-6</v>
       </c>
       <c r="Y25">
-        <v>2.4102877113365254E-6</v>
+        <v>3.5750556969473167E-6</v>
       </c>
       <c r="Z25">
-        <v>5.4694162233036596E-4</v>
+        <v>2.0953377745617862E-4</v>
       </c>
       <c r="AA25">
-        <v>7.3676593770786151E-5</v>
+        <v>7.2616250173916931E-6</v>
       </c>
       <c r="AB25">
-        <v>2.7738856455448524E-7</v>
+        <v>1.7287252256015832E-5</v>
       </c>
       <c r="AC25">
-        <v>1.7008787428221725E-5</v>
+        <v>3.8217488924296296E-6</v>
       </c>
       <c r="AD25">
-        <v>3.6208315899611031E-6</v>
+        <v>6.4246145243418642E-6</v>
       </c>
       <c r="AE25">
-        <v>-4.7128633799487875E-6</v>
+        <v>-1.3589861588836436E-5</v>
       </c>
       <c r="AF25">
-        <v>5.8651720196229915E-5</v>
+        <v>2.922243025756904E-5</v>
       </c>
       <c r="AG25">
-        <v>-2.3075294598929105E-5</v>
+        <v>2.9820893630451405E-5</v>
       </c>
       <c r="AH25">
-        <v>1.3243718570342974E-4</v>
+        <v>1.2283388698967174E-4</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A26" s="30" t="s">
+      <c r="A26" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="38">
-        <v>-1.1613804443431301E-2</v>
+      <c r="B26">
+        <v>1.6065555575369164E-2</v>
       </c>
       <c r="C26">
-        <v>-1.7689634487173019E-5</v>
+        <v>-4.3394966743498959E-6</v>
       </c>
       <c r="D26">
-        <v>-1.8397904489040462E-5</v>
+        <v>-1.9589762488986601E-6</v>
       </c>
       <c r="E26">
-        <v>1.9060474720314273E-7</v>
+        <v>2.5715170724065201E-8</v>
       </c>
       <c r="F26">
-        <v>1.4686935196862243E-4</v>
+        <v>2.7520710738332291E-5</v>
       </c>
       <c r="G26">
-        <v>1.8511991698582438E-5</v>
+        <v>-3.324037709476435E-6</v>
       </c>
       <c r="H26">
-        <v>3.0388947663734884E-4</v>
+        <v>-8.2845262303650734E-6</v>
       </c>
       <c r="I26">
-        <v>4.5996614135651115E-4</v>
+        <v>-1.8288992026923293E-5</v>
       </c>
       <c r="J26">
-        <v>1.7189041247273453E-4</v>
+        <v>-2.7971654781780981E-5</v>
       </c>
       <c r="K26">
-        <v>9.6741080698260263E-5</v>
+        <v>-3.7089489704015264E-6</v>
       </c>
       <c r="L26">
-        <v>-2.1940515186037843E-5</v>
+        <v>1.2367806212827535E-5</v>
       </c>
       <c r="M26">
-        <v>4.7475255631971702E-6</v>
+        <v>-1.5955024569933821E-5</v>
       </c>
       <c r="N26">
-        <v>-2.0650844614895371E-5</v>
+        <v>-2.2865778694848706E-5</v>
       </c>
       <c r="O26">
-        <v>4.094663567218344E-5</v>
+        <v>3.848608297610885E-6</v>
       </c>
       <c r="P26">
-        <v>-8.8914509201160671E-5</v>
+        <v>6.550340284801066E-7</v>
       </c>
       <c r="Q26">
-        <v>-8.1321952506481542E-5</v>
+        <v>-1.4396953680010792E-6</v>
       </c>
       <c r="R26">
-        <v>-8.3701324050491129E-6</v>
+        <v>3.9067588724307962E-6</v>
       </c>
       <c r="S26">
-        <v>7.8938083454248038E-6</v>
+        <v>-1.5879676095799681E-6</v>
       </c>
       <c r="T26">
-        <v>-1.4067172378131806E-4</v>
+        <v>4.6914780677772866E-6</v>
       </c>
       <c r="U26">
-        <v>1.0656496909548584E-4</v>
+        <v>1.0119171911530556E-5</v>
       </c>
       <c r="V26">
-        <v>1.1633136887157414E-5</v>
+        <v>6.6794911045503386E-6</v>
       </c>
       <c r="W26">
-        <v>-3.3682328036077408E-5</v>
+        <v>2.059334929371837E-5</v>
       </c>
       <c r="X26">
-        <v>2.0992559469369589E-4</v>
+        <v>2.1499750650866097E-5</v>
       </c>
       <c r="Y26">
-        <v>-7.0380238409838087E-6</v>
+        <v>2.9325199188312531E-6</v>
       </c>
       <c r="Z26">
-        <v>7.3676593770786151E-5</v>
+        <v>7.2616250173916931E-6</v>
       </c>
       <c r="AA26">
-        <v>1.3330880485569237E-3</v>
+        <v>2.6985112681929176E-4</v>
       </c>
       <c r="AB26">
-        <v>4.353340350473776E-4</v>
+        <v>1.5029682584521029E-4</v>
       </c>
       <c r="AC26">
-        <v>4.6563049386740707E-4</v>
+        <v>1.3725432769982716E-4</v>
       </c>
       <c r="AD26">
-        <v>4.3887794286015546E-4</v>
+        <v>1.4084688944421205E-4</v>
       </c>
       <c r="AE26">
-        <v>-8.2133228193059251E-6</v>
+        <v>-1.3257744861246181E-6</v>
       </c>
       <c r="AF26">
-        <v>4.7089425590331505E-4</v>
+        <v>-2.5733246683269683E-5</v>
       </c>
       <c r="AG26">
-        <v>-1.1123730411835136E-5</v>
+        <v>-5.2937272274118736E-6</v>
       </c>
       <c r="AH26">
-        <v>-1.3663071325335742E-4</v>
+        <v>-9.4588218187710652E-5</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A27" s="31" t="s">
+      <c r="A27" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="38">
-        <v>-0.11987247711523175</v>
+      <c r="B27">
+        <v>9.1407756314062935E-2</v>
       </c>
       <c r="C27">
-        <v>4.612929186166963E-6</v>
+        <v>-1.9601721291514337E-6</v>
       </c>
       <c r="D27">
-        <v>1.0447901649068521E-5</v>
+        <v>-3.574104141622016E-6</v>
       </c>
       <c r="E27">
-        <v>-1.4672956866600413E-7</v>
+        <v>4.2508249803978106E-8</v>
       </c>
       <c r="F27">
-        <v>-7.6569608895826194E-5</v>
+        <v>1.7468048267700332E-5</v>
       </c>
       <c r="G27">
-        <v>8.8908170665578088E-5</v>
+        <v>4.5875427446076002E-6</v>
       </c>
       <c r="H27">
-        <v>4.4070149807506898E-6</v>
+        <v>6.4446870364056935E-6</v>
       </c>
       <c r="I27">
-        <v>-1.1806564953034779E-4</v>
+        <v>6.7877316872757784E-7</v>
       </c>
       <c r="J27">
-        <v>5.8821881373327103E-5</v>
+        <v>-7.9997606522520643E-6</v>
       </c>
       <c r="K27">
-        <v>1.4600923072762787E-5</v>
+        <v>6.3099480123044919E-6</v>
       </c>
       <c r="L27">
-        <v>-1.0920512550130761E-4</v>
+        <v>2.5633872456658571E-5</v>
       </c>
       <c r="M27">
-        <v>4.5800296727457413E-5</v>
+        <v>5.3026102443205683E-6</v>
       </c>
       <c r="N27">
-        <v>-2.4085914463144176E-6</v>
+        <v>-1.051932596963718E-5</v>
       </c>
       <c r="O27">
-        <v>2.9208941476129718E-5</v>
+        <v>1.8233725849835762E-6</v>
       </c>
       <c r="P27">
-        <v>-6.0230418948652989E-5</v>
+        <v>-6.709057472451575E-6</v>
       </c>
       <c r="Q27">
-        <v>-3.6292188235961809E-5</v>
+        <v>1.2628828807392551E-5</v>
       </c>
       <c r="R27">
-        <v>-6.5249161864832598E-5</v>
+        <v>1.4714743862669088E-5</v>
       </c>
       <c r="S27">
-        <v>-2.1729824573275391E-5</v>
+        <v>1.1564449532285677E-5</v>
       </c>
       <c r="T27">
-        <v>-8.1763655533166266E-5</v>
+        <v>2.7798213755484389E-5</v>
       </c>
       <c r="U27">
-        <v>-5.9276113539097266E-5</v>
+        <v>1.8817991800261997E-5</v>
       </c>
       <c r="V27">
-        <v>-2.0838407905430817E-4</v>
+        <v>7.7291716222656137E-6</v>
       </c>
       <c r="W27">
-        <v>-2.1461889760550736E-4</v>
+        <v>3.841321490016901E-5</v>
       </c>
       <c r="X27">
-        <v>-2.6004663333747881E-4</v>
+        <v>4.2177690617442783E-5</v>
       </c>
       <c r="Y27">
-        <v>1.0836776883040305E-5</v>
+        <v>4.427211406228725E-6</v>
       </c>
       <c r="Z27">
-        <v>2.7738856455448524E-7</v>
+        <v>1.7287252256015832E-5</v>
       </c>
       <c r="AA27">
-        <v>4.353340350473776E-4</v>
+        <v>1.5029682584521029E-4</v>
       </c>
       <c r="AB27">
-        <v>1.7573715068071745E-3</v>
+        <v>5.0819200377334641E-4</v>
       </c>
       <c r="AC27">
-        <v>4.4855881530537361E-4</v>
+        <v>1.3770568856941515E-4</v>
       </c>
       <c r="AD27">
-        <v>4.5066720605911912E-4</v>
+        <v>1.4223390162108887E-4</v>
       </c>
       <c r="AE27">
-        <v>-1.0830828258510588E-5</v>
+        <v>-2.498780433010843E-6</v>
       </c>
       <c r="AF27">
-        <v>1.5125049528586388E-4</v>
+        <v>-2.9224949208403911E-6</v>
       </c>
       <c r="AG27">
-        <v>2.5687920337640692E-5</v>
+        <v>-1.953005834283954E-5</v>
       </c>
       <c r="AH27">
-        <v>-2.3207207920807114E-4</v>
+        <v>-8.82645934886024E-5</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A28" s="32" t="s">
+      <c r="A28" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="38">
-        <v>-6.5778258794065014E-2</v>
+      <c r="B28">
+        <v>2.7359971791403377E-2</v>
       </c>
       <c r="C28">
-        <v>-7.9311031574697379E-6</v>
+        <v>-5.1938808781731478E-6</v>
       </c>
       <c r="D28">
-        <v>-2.3432938846477044E-6</v>
+        <v>1.1116334129842236E-6</v>
       </c>
       <c r="E28">
-        <v>1.2311374896594582E-8</v>
+        <v>-8.2456562508767621E-9</v>
       </c>
       <c r="F28">
-        <v>-1.7238271619967905E-4</v>
+        <v>2.7112551070500519E-5</v>
       </c>
       <c r="G28">
-        <v>2.5286114352692546E-5</v>
+        <v>2.5448904074594557E-6</v>
       </c>
       <c r="H28">
-        <v>4.0779667238832129E-5</v>
+        <v>-1.0603487745046561E-5</v>
       </c>
       <c r="I28">
-        <v>1.9614943429843598E-5</v>
+        <v>-1.2506626383148494E-5</v>
       </c>
       <c r="J28">
-        <v>3.7500102589792906E-6</v>
+        <v>-8.1632130806928976E-6</v>
       </c>
       <c r="K28">
-        <v>4.3845543146300544E-5</v>
+        <v>-3.6675078601618063E-6</v>
       </c>
       <c r="L28">
-        <v>-1.0800691103895562E-4</v>
+        <v>-2.0824376105935257E-6</v>
       </c>
       <c r="M28">
-        <v>-7.2491134002944911E-5</v>
+        <v>2.5263063939296327E-6</v>
       </c>
       <c r="N28">
-        <v>-3.1048504886437689E-5</v>
+        <v>-3.4170901979879383E-7</v>
       </c>
       <c r="O28">
-        <v>7.5366144045245143E-6</v>
+        <v>-4.1050275336285233E-6</v>
       </c>
       <c r="P28">
-        <v>-3.8375340942774648E-5</v>
+        <v>-4.2569047393710218E-6</v>
       </c>
       <c r="Q28">
-        <v>-2.8108093008049825E-6</v>
+        <v>1.4353267211168926E-6</v>
       </c>
       <c r="R28">
-        <v>-9.6954628974193374E-6</v>
+        <v>-3.2676058528164232E-6</v>
       </c>
       <c r="S28">
-        <v>-3.2451264433821592E-6</v>
+        <v>-4.4404239775427219E-6</v>
       </c>
       <c r="T28">
-        <v>1.5904935439195141E-5</v>
+        <v>1.3857414005524998E-5</v>
       </c>
       <c r="U28">
-        <v>-9.9821541883961143E-6</v>
+        <v>9.8166227313689419E-7</v>
       </c>
       <c r="V28">
-        <v>-2.8743008927630681E-5</v>
+        <v>-4.6543314710034228E-6</v>
       </c>
       <c r="W28">
-        <v>-3.0904589787286583E-5</v>
+        <v>-1.0339851803457952E-5</v>
       </c>
       <c r="X28">
-        <v>-9.9817814837424893E-6</v>
+        <v>-1.4940669143380993E-5</v>
       </c>
       <c r="Y28">
-        <v>3.8725227381425674E-6</v>
+        <v>-5.1723405676291268E-8</v>
       </c>
       <c r="Z28">
-        <v>1.7008787428221725E-5</v>
+        <v>3.8217488924296296E-6</v>
       </c>
       <c r="AA28">
-        <v>4.6563049386740707E-4</v>
+        <v>1.3725432769982716E-4</v>
       </c>
       <c r="AB28">
-        <v>4.4855881530537361E-4</v>
+        <v>1.3770568856941515E-4</v>
       </c>
       <c r="AC28">
-        <v>9.4523226400343972E-4</v>
+        <v>2.5191019874656016E-4</v>
       </c>
       <c r="AD28">
-        <v>4.5193118042711496E-4</v>
+        <v>1.3910884727632585E-4</v>
       </c>
       <c r="AE28">
-        <v>-4.9699210799387094E-6</v>
+        <v>-8.1672673425720827E-7</v>
       </c>
       <c r="AF28">
-        <v>1.473082398504189E-5</v>
+        <v>-4.7229475915334178E-5</v>
       </c>
       <c r="AG28">
-        <v>4.7474081734393037E-5</v>
+        <v>-1.8600138674191005E-6</v>
       </c>
       <c r="AH28">
-        <v>-2.8211535403920018E-4</v>
+        <v>-1.3871459287173699E-4</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A29" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="38">
-        <v>-8.674398423029998E-3</v>
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>4.1522038801148464E-2</v>
       </c>
       <c r="C29">
-        <v>6.3496126118559745E-6</v>
+        <v>-4.6735164623377883E-6</v>
       </c>
       <c r="D29">
-        <v>4.5155970790922975E-6</v>
+        <v>-9.7024023133876784E-7</v>
       </c>
       <c r="E29">
-        <v>-5.5003523428832741E-8</v>
+        <v>1.1581152446939951E-8</v>
       </c>
       <c r="F29">
-        <v>-5.0332282732335636E-5</v>
+        <v>9.2553354868828543E-6</v>
       </c>
       <c r="G29">
-        <v>-2.8405712424238184E-5</v>
+        <v>4.4237254610635449E-6</v>
       </c>
       <c r="H29">
-        <v>-6.5293459625085401E-5</v>
+        <v>-4.7054978975882606E-6</v>
       </c>
       <c r="I29">
-        <v>-3.7827204830434124E-5</v>
+        <v>-2.1470421357523196E-5</v>
       </c>
       <c r="J29">
-        <v>-3.8218019447430556E-5</v>
+        <v>-6.8846618448084476E-6</v>
       </c>
       <c r="K29">
-        <v>-1.887191945801125E-5</v>
+        <v>-4.2618954105564429E-6</v>
       </c>
       <c r="L29">
-        <v>-1.5209831411845418E-4</v>
+        <v>-1.6048139598902594E-6</v>
       </c>
       <c r="M29">
-        <v>-5.997029590319009E-6</v>
+        <v>-6.7055771447284635E-6</v>
       </c>
       <c r="N29">
-        <v>-7.7963127592529219E-6</v>
+        <v>-3.9650577393336934E-7</v>
       </c>
       <c r="O29">
-        <v>5.376536666589865E-5</v>
+        <v>7.2606381679119695E-6</v>
       </c>
       <c r="P29">
-        <v>3.7479989587589673E-5</v>
+        <v>1.0144676555739075E-5</v>
       </c>
       <c r="Q29">
-        <v>7.4357286008350188E-6</v>
+        <v>5.2449842174858916E-6</v>
       </c>
       <c r="R29">
-        <v>4.7125377417273399E-5</v>
+        <v>7.7917847755203324E-6</v>
       </c>
       <c r="S29">
-        <v>7.2611698492275399E-5</v>
+        <v>9.4581630565336106E-6</v>
       </c>
       <c r="T29">
-        <v>6.9559538646721047E-5</v>
+        <v>2.1622205102609596E-5</v>
       </c>
       <c r="U29">
-        <v>-2.8203891738341996E-5</v>
+        <v>5.13361432288429E-6</v>
       </c>
       <c r="V29">
-        <v>-1.0636340515064426E-5</v>
+        <v>-1.7775563094145976E-6</v>
       </c>
       <c r="W29">
-        <v>-2.9126565764760052E-5</v>
+        <v>2.1846177878594077E-6</v>
       </c>
       <c r="X29">
-        <v>1.5731992713049353E-5</v>
+        <v>7.2247584668474172E-6</v>
       </c>
       <c r="Y29">
-        <v>2.569093492204676E-6</v>
+        <v>1.8921581336529334E-6</v>
       </c>
       <c r="Z29">
-        <v>3.6208315899611031E-6</v>
+        <v>6.4246145243418642E-6</v>
       </c>
       <c r="AA29">
-        <v>4.3887794286015546E-4</v>
+        <v>1.4084688944421205E-4</v>
       </c>
       <c r="AB29">
-        <v>4.5066720605911912E-4</v>
+        <v>1.4223390162108887E-4</v>
       </c>
       <c r="AC29">
-        <v>4.5193118042711496E-4</v>
+        <v>1.3910884727632585E-4</v>
       </c>
       <c r="AD29">
-        <v>7.7203388697401581E-4</v>
+        <v>2.5710771962755895E-4</v>
       </c>
       <c r="AE29">
-        <v>-2.5443289049845921E-6</v>
+        <v>-1.4351812493959365E-6</v>
       </c>
       <c r="AF29">
-        <v>8.8245702668158176E-5</v>
+        <v>-5.3380122187852115E-5</v>
       </c>
       <c r="AG29">
-        <v>1.9852876946312251E-5</v>
+        <v>2.5290956277949984E-6</v>
       </c>
       <c r="AH29">
-        <v>-5.4940718778208721E-4</v>
+        <v>-1.1723923819868153E-4</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A30" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="38">
-        <v>1.3445411150788892E-3</v>
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30">
+        <v>-5.9711881847980035E-2</v>
       </c>
       <c r="C30">
-        <v>3.0977092293611811E-8</v>
+        <v>1.0721178697140799E-6</v>
       </c>
       <c r="D30">
-        <v>3.6245662912667931E-7</v>
+        <v>-9.4235264822220706E-10</v>
       </c>
       <c r="E30">
-        <v>-4.8959188265797088E-9</v>
+        <v>-1.2922107638907773E-9</v>
       </c>
       <c r="F30">
-        <v>-2.3914255136231141E-6</v>
+        <v>-5.1717355696032286E-7</v>
       </c>
       <c r="G30">
-        <v>2.2080578359214394E-6</v>
+        <v>1.7070853168842565E-7</v>
       </c>
       <c r="H30">
-        <v>-2.567455903458273E-6</v>
+        <v>-3.7297964610907554E-7</v>
       </c>
       <c r="I30">
-        <v>1.2811792203293087E-5</v>
+        <v>1.6183905922981872E-6</v>
       </c>
       <c r="J30">
-        <v>6.781075355056696E-6</v>
+        <v>-4.3367139136056483E-7</v>
       </c>
       <c r="K30">
-        <v>-4.201631069943436E-6</v>
+        <v>-9.8747954486114598E-7</v>
       </c>
       <c r="L30">
-        <v>-2.0020844927266175E-5</v>
+        <v>-6.8909094499484789E-7</v>
       </c>
       <c r="M30">
-        <v>1.9220223265266811E-6</v>
+        <v>-2.1175263202509185E-6</v>
       </c>
       <c r="N30">
-        <v>2.5838965733139215E-6</v>
+        <v>3.8339127912067575E-7</v>
       </c>
       <c r="O30">
-        <v>1.7229577971110744E-6</v>
+        <v>2.3738712541169773E-6</v>
       </c>
       <c r="P30">
-        <v>7.9513890486140767E-6</v>
+        <v>1.9162699560630375E-6</v>
       </c>
       <c r="Q30">
-        <v>7.5249961743966527E-6</v>
+        <v>4.2525644552987444E-8</v>
       </c>
       <c r="R30">
-        <v>-1.5207664489067278E-6</v>
+        <v>-9.3068543704272926E-7</v>
       </c>
       <c r="S30">
-        <v>-3.8592124665402837E-6</v>
+        <v>-3.5445931540132572E-6</v>
       </c>
       <c r="T30">
-        <v>8.0584579235854132E-6</v>
+        <v>-5.6648597220772257E-6</v>
       </c>
       <c r="U30">
-        <v>-4.1077524336397339E-6</v>
+        <v>-2.2444779625452416E-7</v>
       </c>
       <c r="V30">
-        <v>-5.4006124209891068E-6</v>
+        <v>-1.2146413068034047E-6</v>
       </c>
       <c r="W30">
-        <v>-4.5520603148301633E-6</v>
+        <v>-5.1613238670847993E-7</v>
       </c>
       <c r="X30">
-        <v>1.5917604861093399E-7</v>
+        <v>-1.3215835730080525E-6</v>
       </c>
       <c r="Y30">
-        <v>4.164501402546201E-6</v>
+        <v>2.0339251107063148E-7</v>
       </c>
       <c r="Z30">
-        <v>-4.7128633799487875E-6</v>
+        <v>-1.3589861588836436E-5</v>
       </c>
       <c r="AA30">
-        <v>-8.2133228193059251E-6</v>
+        <v>-1.3257744861246181E-6</v>
       </c>
       <c r="AB30">
-        <v>-1.0830828258510588E-5</v>
+        <v>-2.498780433010843E-6</v>
       </c>
       <c r="AC30">
-        <v>-4.9699210799387094E-6</v>
+        <v>-8.1672673425720827E-7</v>
       </c>
       <c r="AD30">
-        <v>-2.5443289049845921E-6</v>
+        <v>-1.4351812493959365E-6</v>
       </c>
       <c r="AE30">
-        <v>1.0310720708363109E-5</v>
+        <v>3.0933732516417278E-6</v>
       </c>
       <c r="AF30">
-        <v>-3.1744352937002973E-5</v>
+        <v>-7.0960976394372945E-6</v>
       </c>
       <c r="AG30">
-        <v>-4.3743031516049635E-5</v>
+        <v>-9.9501839113295448E-6</v>
       </c>
       <c r="AH30">
-        <v>-1.7332949942120459E-4</v>
+        <v>-3.9569276772813286E-5</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A31" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="38">
-        <v>-0.20477933370971102</v>
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31">
+        <v>8.4342819310595993E-2</v>
       </c>
       <c r="C31">
-        <v>3.32270419110664E-5</v>
+        <v>-2.8818153349261086E-6</v>
       </c>
       <c r="D31">
-        <v>-2.5326301482947759E-5</v>
+        <v>1.1318871457991506E-6</v>
       </c>
       <c r="E31">
-        <v>2.7862920030196577E-7</v>
+        <v>-1.0088600866191837E-8</v>
       </c>
       <c r="F31">
-        <v>1.6239433735017184E-4</v>
+        <v>8.0886284885600202E-5</v>
       </c>
       <c r="G31">
-        <v>-4.703733868216195E-5</v>
+        <v>-8.9875802390939827E-6</v>
       </c>
       <c r="H31">
-        <v>3.3967607555305786E-4</v>
+        <v>2.5765008242544961E-5</v>
       </c>
       <c r="I31">
-        <v>-1.7230223417134469E-4</v>
+        <v>-5.595453002764394E-5</v>
       </c>
       <c r="J31">
-        <v>-1.2288994651668377E-5</v>
+        <v>3.2061749175081784E-5</v>
       </c>
       <c r="K31">
-        <v>5.4115955237877059E-5</v>
+        <v>-2.0895247500510913E-5</v>
       </c>
       <c r="L31">
-        <v>1.0189970461703087E-4</v>
+        <v>5.5704507373661376E-5</v>
       </c>
       <c r="M31">
-        <v>-9.6390245881394256E-5</v>
+        <v>6.1113135440594947E-5</v>
       </c>
       <c r="N31">
-        <v>-1.1326044079120866E-4</v>
+        <v>2.586454386411044E-6</v>
       </c>
       <c r="O31">
-        <v>9.4935005273254908E-5</v>
+        <v>-4.4290345106754803E-6</v>
       </c>
       <c r="P31">
-        <v>4.2648919476111734E-5</v>
+        <v>2.4217416537024696E-5</v>
       </c>
       <c r="Q31">
-        <v>-6.7387341905088792E-5</v>
+        <v>-6.2800149817500428E-5</v>
       </c>
       <c r="R31">
-        <v>1.1248230807839148E-4</v>
+        <v>-8.0066283065696265E-5</v>
       </c>
       <c r="S31">
-        <v>2.3709313022762454E-5</v>
+        <v>-6.6937013744427891E-5</v>
       </c>
       <c r="T31">
-        <v>-1.4889437212913491E-4</v>
+        <v>-2.6824390461460202E-5</v>
       </c>
       <c r="U31">
-        <v>9.1212932078938358E-5</v>
+        <v>1.5918157504508316E-5</v>
       </c>
       <c r="V31">
-        <v>-1.4749834336640457E-5</v>
+        <v>-2.3160805360473557E-5</v>
       </c>
       <c r="W31">
-        <v>-6.8161253642254511E-5</v>
+        <v>1.7454881028803595E-5</v>
       </c>
       <c r="X31">
-        <v>3.1196921778907242E-4</v>
+        <v>-5.5140316404051143E-7</v>
       </c>
       <c r="Y31">
-        <v>-3.6407157048884685E-5</v>
+        <v>8.8913054717165445E-7</v>
       </c>
       <c r="Z31">
-        <v>5.8651720196229915E-5</v>
+        <v>2.922243025756904E-5</v>
       </c>
       <c r="AA31">
-        <v>4.7089425590331505E-4</v>
+        <v>-2.5733246683269683E-5</v>
       </c>
       <c r="AB31">
-        <v>1.5125049528586388E-4</v>
+        <v>-2.9224949208403911E-6</v>
       </c>
       <c r="AC31">
-        <v>1.473082398504189E-5</v>
+        <v>-4.7229475915334178E-5</v>
       </c>
       <c r="AD31">
-        <v>8.8245702668158176E-5</v>
+        <v>-5.3380122187852115E-5</v>
       </c>
       <c r="AE31">
-        <v>-3.1744352937002973E-5</v>
+        <v>-7.0960976394372945E-6</v>
       </c>
       <c r="AF31">
-        <v>2.6270019578037997E-3</v>
+        <v>8.2166891796633078E-4</v>
       </c>
       <c r="AG31">
-        <v>1.9367537461665349E-4</v>
+        <v>-8.9745943598996887E-5</v>
       </c>
       <c r="AH31">
-        <v>5.8426338848886381E-4</v>
+        <v>1.2313607757889652E-4</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A32" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="38">
-        <v>-7.355362873707956E-2</v>
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>6.2189531891370692E-2</v>
       </c>
       <c r="C32">
-        <v>1.2110335424800447E-6</v>
+        <v>-7.7756611070347398E-6</v>
       </c>
       <c r="D32">
-        <v>4.5151840262410841E-6</v>
+        <v>-9.7675186082141696E-7</v>
       </c>
       <c r="E32">
-        <v>-3.6515081838127517E-8</v>
+        <v>1.2063940915487148E-8</v>
       </c>
       <c r="F32">
-        <v>1.3194007397571703E-4</v>
+        <v>-2.5996773935847185E-5</v>
       </c>
       <c r="G32">
-        <v>2.083220296619163E-5</v>
+        <v>2.403009357269595E-6</v>
       </c>
       <c r="H32">
-        <v>1.5782179638358933E-4</v>
+        <v>-5.1963289915598883E-7</v>
       </c>
       <c r="I32">
-        <v>-1.2946490247114494E-4</v>
+        <v>5.456426730407517E-5</v>
       </c>
       <c r="J32">
-        <v>2.0085313754435229E-5</v>
+        <v>3.4793290925813907E-6</v>
       </c>
       <c r="K32">
-        <v>2.9719533482842257E-5</v>
+        <v>1.4615202039950791E-6</v>
       </c>
       <c r="L32">
-        <v>9.6704351279939681E-5</v>
+        <v>-6.9843132750172849E-5</v>
       </c>
       <c r="M32">
-        <v>-8.0860940325496811E-6</v>
+        <v>-2.7906108966132409E-5</v>
       </c>
       <c r="N32">
-        <v>-5.9733467422663853E-5</v>
+        <v>1.4214948824960058E-5</v>
       </c>
       <c r="O32">
-        <v>8.5421860749300009E-5</v>
+        <v>-1.3204542636222541E-5</v>
       </c>
       <c r="P32">
-        <v>9.1476558443811271E-5</v>
+        <v>6.9557827706025313E-6</v>
       </c>
       <c r="Q32">
-        <v>-3.8202984609505782E-5</v>
+        <v>6.30433020147809E-5</v>
       </c>
       <c r="R32">
-        <v>-6.1138647521071453E-5</v>
+        <v>5.4499156762441632E-5</v>
       </c>
       <c r="S32">
-        <v>-4.6591702850437263E-6</v>
+        <v>1.0965859903810769E-4</v>
       </c>
       <c r="T32">
-        <v>-5.0057072073762593E-5</v>
+        <v>1.1407563614440679E-4</v>
       </c>
       <c r="U32">
-        <v>1.6335431158314074E-5</v>
+        <v>-4.2399603302213883E-5</v>
       </c>
       <c r="V32">
-        <v>-5.5123365420984183E-5</v>
+        <v>3.122787769808155E-6</v>
       </c>
       <c r="W32">
-        <v>-6.0785059325890332E-5</v>
+        <v>-1.4045586543320388E-5</v>
       </c>
       <c r="X32">
-        <v>-9.5161998228145345E-5</v>
+        <v>1.9408845130939245E-7</v>
       </c>
       <c r="Y32">
-        <v>-9.7284431197457737E-6</v>
+        <v>-1.1903808266144646E-6</v>
       </c>
       <c r="Z32">
-        <v>-2.3075294598929105E-5</v>
+        <v>2.9820893630451405E-5</v>
       </c>
       <c r="AA32">
-        <v>-1.1123730411835136E-5</v>
+        <v>-5.2937272274118736E-6</v>
       </c>
       <c r="AB32">
-        <v>2.5687920337640692E-5</v>
+        <v>-1.953005834283954E-5</v>
       </c>
       <c r="AC32">
-        <v>4.7474081734393037E-5</v>
+        <v>-1.8600138674191005E-6</v>
       </c>
       <c r="AD32">
-        <v>1.9852876946312251E-5</v>
+        <v>2.5290956277949984E-6</v>
       </c>
       <c r="AE32">
-        <v>-4.3743031516049635E-5</v>
+        <v>-9.9501839113295448E-6</v>
       </c>
       <c r="AF32">
-        <v>1.9367537461665349E-4</v>
+        <v>-8.9745943598996887E-5</v>
       </c>
       <c r="AG32">
-        <v>1.2483676117404231E-3</v>
+        <v>3.6982220783800794E-4</v>
       </c>
       <c r="AH32">
-        <v>4.7870682097504312E-4</v>
+        <v>6.4589659576685764E-5</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.45">
-      <c r="A33" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="38">
-        <v>-1.6938198484195555</v>
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33">
+        <v>-0.4196697950131727</v>
       </c>
       <c r="C33">
-        <v>-4.389932419707138E-4</v>
+        <v>-7.0878618789813803E-5</v>
       </c>
       <c r="D33">
-        <v>-5.0419684697400064E-4</v>
+        <v>-1.5008058685414902E-4</v>
       </c>
       <c r="E33">
-        <v>4.5094976109574447E-6</v>
+        <v>1.3442607168871279E-6</v>
       </c>
       <c r="F33">
-        <v>-2.5091965914107684E-3</v>
+        <v>-1.1730780768807493E-3</v>
       </c>
       <c r="G33">
-        <v>-1.9787970871808299E-3</v>
+        <v>-4.5304902641070638E-4</v>
       </c>
       <c r="H33">
-        <v>-1.9366021769109106E-3</v>
+        <v>-4.2498415903023711E-4</v>
       </c>
       <c r="I33">
-        <v>-3.4975229634165482E-3</v>
+        <v>-7.4182443158430159E-4</v>
       </c>
       <c r="J33">
-        <v>-2.2024325942323745E-3</v>
+        <v>-4.684906320367502E-4</v>
       </c>
       <c r="K33">
-        <v>-2.4930414776556916E-3</v>
+        <v>-7.1861823013451222E-4</v>
       </c>
       <c r="L33">
-        <v>-1.3800031623558101E-3</v>
+        <v>-4.9086118694668837E-4</v>
       </c>
       <c r="M33">
-        <v>-4.2386937410304254E-3</v>
+        <v>-1.3447942845723978E-3</v>
       </c>
       <c r="N33">
-        <v>-1.4919844743905264E-3</v>
+        <v>-4.1002794546834617E-4</v>
       </c>
       <c r="O33">
-        <v>-6.4282798152245023E-4</v>
+        <v>-3.5650910730923276E-4</v>
       </c>
       <c r="P33">
-        <v>-9.2485224058497933E-4</v>
+        <v>-3.6041323162255942E-4</v>
       </c>
       <c r="Q33">
-        <v>-3.0812215633848651E-3</v>
+        <v>-1.5056309344537349E-3</v>
       </c>
       <c r="R33">
-        <v>-2.8473312645004769E-3</v>
+        <v>-1.467426880663804E-3</v>
       </c>
       <c r="S33">
-        <v>-3.6697974996654451E-3</v>
+        <v>-1.5568172128593346E-3</v>
       </c>
       <c r="T33">
-        <v>-4.7605309573818463E-3</v>
+        <v>-1.7386154259039013E-3</v>
       </c>
       <c r="U33">
-        <v>-4.6949757222860817E-4</v>
+        <v>-9.3509380639289486E-5</v>
       </c>
       <c r="V33">
-        <v>-9.8867820574509045E-4</v>
+        <v>-2.3432005834378265E-4</v>
       </c>
       <c r="W33">
-        <v>-1.5333210253611991E-3</v>
+        <v>-3.5609678647426519E-4</v>
       </c>
       <c r="X33">
-        <v>-1.8692673049336269E-3</v>
+        <v>-4.1705401577839469E-4</v>
       </c>
       <c r="Y33">
-        <v>-8.5128889759942168E-7</v>
+        <v>6.6153331256053365E-7</v>
       </c>
       <c r="Z33">
-        <v>1.3243718570342974E-4</v>
+        <v>1.2283388698967174E-4</v>
       </c>
       <c r="AA33">
-        <v>-1.3663071325335742E-4</v>
+        <v>-9.4588218187710652E-5</v>
       </c>
       <c r="AB33">
-        <v>-2.3207207920807114E-4</v>
+        <v>-8.82645934886024E-5</v>
       </c>
       <c r="AC33">
-        <v>-2.8211535403920018E-4</v>
+        <v>-1.3871459287173699E-4</v>
       </c>
       <c r="AD33">
-        <v>-5.4940718778208721E-4</v>
+        <v>-1.1723923819868153E-4</v>
       </c>
       <c r="AE33">
-        <v>-1.7332949942120459E-4</v>
+        <v>-3.9569276772813286E-5</v>
       </c>
       <c r="AF33">
-        <v>5.8426338848886381E-4</v>
+        <v>1.2313607757889652E-4</v>
       </c>
       <c r="AG33">
-        <v>4.7870682097504312E-4</v>
+        <v>6.4589659576685764E-5</v>
       </c>
       <c r="AH33">
-        <v>2.3788177326206944E-2</v>
+        <v>7.3674307969100392E-3</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId2"/>
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
-    <sheet name="HO1a" sheetId="3" r:id="rId5"/>
+    <sheet name="UK_HO1a" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -1759,13 +1759,13 @@
         <v>95</v>
       </c>
       <c r="B5">
-        <v>0.82782877871961202</v>
+        <v>0.82789506350296693</v>
       </c>
       <c r="E5" t="s">
         <v>97</v>
       </c>
       <c r="F5">
-        <v>77649.191128168022</v>
+        <v>77729.81135527158</v>
       </c>
     </row>
     <row r="6">
@@ -1773,13 +1773,13 @@
         <v>96</v>
       </c>
       <c r="B6">
-        <v>327881</v>
+        <v>327875</v>
       </c>
       <c r="E6" t="s">
         <v>98</v>
       </c>
       <c r="F6">
-        <v>-36042.098174625928</v>
+        <v>-36026.976393268567</v>
       </c>
     </row>
   </sheetData>
@@ -1924,127 +1924,127 @@
         <v>53</v>
       </c>
       <c r="B2" s="8">
-        <v>-0.012404707560662158</v>
+        <v>-0.012547321579729693</v>
       </c>
       <c r="C2">
-        <v>0.00012771682867702324</v>
+        <v>0.00012788072474818126</v>
       </c>
       <c r="D2">
-        <v>2.4710566594854354e-007</v>
+        <v>2.6107153443071858e-007</v>
       </c>
       <c r="E2">
-        <v>7.8564666219521666e-010</v>
+        <v>7.3082024556672204e-010</v>
       </c>
       <c r="F2">
-        <v>-3.9622115409459368e-005</v>
+        <v>-3.9358928149478029e-005</v>
       </c>
       <c r="G2">
-        <v>-1.8822132446127904e-005</v>
+        <v>-1.882364922943672e-005</v>
       </c>
       <c r="H2">
-        <v>3.0765284568223453e-006</v>
+        <v>3.135120780388428e-006</v>
       </c>
       <c r="I2">
-        <v>-8.403887341005737e-005</v>
+        <v>-8.3920860752459349e-005</v>
       </c>
       <c r="J2">
-        <v>-3.4737978181363596e-005</v>
+        <v>-3.4692016537104544e-005</v>
       </c>
       <c r="K2">
-        <v>-3.613227314374941e-006</v>
+        <v>-3.6690393304229927e-006</v>
       </c>
       <c r="L2">
-        <v>4.2398014178466015e-005</v>
+        <v>4.2740461689852399e-005</v>
       </c>
       <c r="M2">
-        <v>1.8272170722163976e-005</v>
+        <v>1.8168822437532194e-005</v>
       </c>
       <c r="N2">
-        <v>2.3265075114504533e-005</v>
+        <v>2.3190569799913375e-005</v>
       </c>
       <c r="O2">
-        <v>-6.9900708171753669e-006</v>
+        <v>-7.2353725472896123e-006</v>
       </c>
       <c r="P2">
-        <v>-7.2153575104928027e-006</v>
+        <v>-7.4829875894160354e-006</v>
       </c>
       <c r="Q2">
-        <v>-7.9265977010641107e-007</v>
+        <v>-7.9122885279238301e-007</v>
       </c>
       <c r="R2">
-        <v>-1.4931568520218039e-007</v>
+        <v>-1.4508581854701788e-007</v>
       </c>
       <c r="S2">
-        <v>1.9620909277668945e-005</v>
+        <v>1.8517040194903296e-005</v>
       </c>
       <c r="T2">
-        <v>2.2175154144066791e-005</v>
+        <v>2.1433944777983996e-005</v>
       </c>
       <c r="U2">
-        <v>1.6592854556798046e-005</v>
+        <v>1.6068467230108948e-005</v>
       </c>
       <c r="V2">
-        <v>1.0049288962354983e-005</v>
+        <v>9.4897033567696436e-006</v>
       </c>
       <c r="W2">
-        <v>-2.9421948849392486e-006</v>
+        <v>-2.9612353110644452e-006</v>
       </c>
       <c r="X2">
-        <v>-2.2842023136516973e-006</v>
+        <v>-2.3093899068929268e-006</v>
       </c>
       <c r="Y2">
-        <v>-2.6122384814050417e-006</v>
+        <v>-2.5636235374156192e-006</v>
       </c>
       <c r="Z2">
-        <v>2.5651659560887277e-006</v>
+        <v>2.3035257734025374e-006</v>
       </c>
       <c r="AA2">
-        <v>-6.1480928525265669e-006</v>
+        <v>-5.9854706066210048e-006</v>
       </c>
       <c r="AB2">
-        <v>-8.3291446018805466e-006</v>
+        <v>-8.2273743438368948e-006</v>
       </c>
       <c r="AC2">
-        <v>-3.2206796953546379e-006</v>
+        <v>-3.0512157408658435e-006</v>
       </c>
       <c r="AD2">
-        <v>-2.1606636180992929e-006</v>
+        <v>-1.878729065665198e-006</v>
       </c>
       <c r="AE2">
-        <v>1.6822808489548638e-006</v>
+        <v>1.8601942434671242e-006</v>
       </c>
       <c r="AF2">
-        <v>-2.6942722493586907e-006</v>
+        <v>-2.7523960014807661e-006</v>
       </c>
       <c r="AG2">
-        <v>-7.0608282023337232e-006</v>
+        <v>-6.9703098249783688e-006</v>
       </c>
       <c r="AH2">
-        <v>1.7201627876411077e-006</v>
+        <v>1.4936291953983648e-006</v>
       </c>
       <c r="AI2">
-        <v>-1.0174540049415314e-005</v>
+        <v>-9.7779038769873102e-006</v>
       </c>
       <c r="AJ2">
-        <v>-2.985291974450226e-007</v>
+        <v>-3.1743798909241021e-007</v>
       </c>
       <c r="AK2">
-        <v>7.9851626278660644e-009</v>
+        <v>1.0252474378725544e-007</v>
       </c>
       <c r="AL2">
-        <v>1.2059758058550897e-006</v>
+        <v>6.2102916537237028e-007</v>
       </c>
       <c r="AM2">
-        <v>-6.2081679921257938e-006</v>
+        <v>-6.0272879253144178e-006</v>
       </c>
       <c r="AN2">
-        <v>-3.4747089969595519e-006</v>
+        <v>-3.6147826383296928e-006</v>
       </c>
       <c r="AO2">
-        <v>-4.4152009417706005e-006</v>
+        <v>-1.1315224187012664e-005</v>
       </c>
       <c r="AP2">
-        <v>-2.8220416855022191e-005</v>
+        <v>-2.7821092744956907e-005</v>
       </c>
     </row>
     <row r="3">
@@ -2052,127 +2052,127 @@
         <v>54</v>
       </c>
       <c r="B3" s="10">
-        <v>0.0019676824619245968</v>
+        <v>0.0020472859817201039</v>
       </c>
       <c r="C3">
-        <v>2.4710566594854354e-007</v>
+        <v>2.6107153443071858e-007</v>
       </c>
       <c r="D3">
-        <v>3.5343871383479054e-006</v>
+        <v>3.5259811505299667e-006</v>
       </c>
       <c r="E3">
-        <v>-3.3274565282014838e-008</v>
+        <v>-3.319127947999116e-008</v>
       </c>
       <c r="F3">
-        <v>1.0415271852461455e-005</v>
+        <v>1.040509943709718e-005</v>
       </c>
       <c r="G3">
-        <v>2.9713695236537236e-006</v>
+        <v>2.974512017860452e-006</v>
       </c>
       <c r="H3">
-        <v>1.0662403441242045e-006</v>
+        <v>1.040201700081031e-006</v>
       </c>
       <c r="I3">
-        <v>3.4646329188053573e-006</v>
+        <v>3.4230884546269621e-006</v>
       </c>
       <c r="J3">
-        <v>-5.8424647554752843e-007</v>
+        <v>-6.0679716057737294e-007</v>
       </c>
       <c r="K3">
-        <v>8.4076973157028939e-006</v>
+        <v>8.4195875642647749e-006</v>
       </c>
       <c r="L3">
-        <v>2.0131482338384087e-006</v>
+        <v>2.0490009476689539e-006</v>
       </c>
       <c r="M3">
-        <v>2.3912405415661292e-005</v>
+        <v>2.3673626878575388e-005</v>
       </c>
       <c r="N3">
-        <v>3.1618050327629238e-006</v>
+        <v>3.2293225804668895e-006</v>
       </c>
       <c r="O3">
-        <v>-3.4984786811638658e-007</v>
+        <v>-3.3651800074176554e-007</v>
       </c>
       <c r="P3">
-        <v>3.0682516260413246e-007</v>
+        <v>3.027666647712168e-007</v>
       </c>
       <c r="Q3">
-        <v>5.6142942080625734e-008</v>
+        <v>5.4590076078477575e-008</v>
       </c>
       <c r="R3">
-        <v>1.0915637919763319e-007</v>
+        <v>1.0922533180105159e-007</v>
       </c>
       <c r="S3">
-        <v>3.5934808847278038e-006</v>
+        <v>3.6103131531151699e-006</v>
       </c>
       <c r="T3">
-        <v>1.3716741803894554e-006</v>
+        <v>1.4551711867713814e-006</v>
       </c>
       <c r="U3">
-        <v>-1.31478285521038e-006</v>
+        <v>-1.2574434854135148e-006</v>
       </c>
       <c r="V3">
-        <v>-2.5347661302334453e-006</v>
+        <v>-2.4769981294328631e-006</v>
       </c>
       <c r="W3">
-        <v>-1.6247231660567237e-007</v>
+        <v>-1.8035534091487149e-007</v>
       </c>
       <c r="X3">
-        <v>-1.180284803827605e-006</v>
+        <v>-1.1888137516625635e-006</v>
       </c>
       <c r="Y3">
-        <v>-1.4122943374937161e-006</v>
+        <v>-1.4768776949171715e-006</v>
       </c>
       <c r="Z3">
-        <v>-9.8903734569424898e-008</v>
+        <v>-2.861537635533734e-007</v>
       </c>
       <c r="AA3">
-        <v>-8.5519710667186671e-008</v>
+        <v>-1.5003954140125943e-007</v>
       </c>
       <c r="AB3">
-        <v>1.8308282989344809e-007</v>
+        <v>9.6750197830381275e-008</v>
       </c>
       <c r="AC3">
-        <v>-3.6922932629806123e-007</v>
+        <v>-4.5639613423209734e-007</v>
       </c>
       <c r="AD3">
-        <v>-3.2691149021661699e-008</v>
+        <v>-1.1823394706229884e-007</v>
       </c>
       <c r="AE3">
-        <v>5.8235760554578036e-008</v>
+        <v>-1.2959412249870765e-008</v>
       </c>
       <c r="AF3">
-        <v>3.7249517133082162e-007</v>
+        <v>2.6971435125143941e-007</v>
       </c>
       <c r="AG3">
-        <v>1.5071944669104611e-006</v>
+        <v>1.4366065722381345e-006</v>
       </c>
       <c r="AH3">
-        <v>-1.7155527950960071e-006</v>
+        <v>-1.7348382566227951e-006</v>
       </c>
       <c r="AI3">
-        <v>3.5088428050066597e-007</v>
+        <v>3.4736910851744101e-007</v>
       </c>
       <c r="AJ3">
-        <v>1.5091311052930837e-007</v>
+        <v>1.5688245878275313e-007</v>
       </c>
       <c r="AK3">
-        <v>-5.4994028780463106e-007</v>
+        <v>-6.0799483160285996e-007</v>
       </c>
       <c r="AL3">
-        <v>-1.1482281470692416e-006</v>
+        <v>-1.4170193888767322e-006</v>
       </c>
       <c r="AM3">
-        <v>-1.0175938390587989e-007</v>
+        <v>-6.4609638909353189e-008</v>
       </c>
       <c r="AN3">
-        <v>-1.4500395939382504e-006</v>
+        <v>-1.469260996366889e-006</v>
       </c>
       <c r="AO3">
-        <v>9.3602296376210984e-007</v>
+        <v>3.3872998367661739e-007</v>
       </c>
       <c r="AP3">
-        <v>-9.8671875001025863e-005</v>
+        <v>-9.8458947539668295e-005</v>
       </c>
     </row>
     <row r="4">
@@ -2180,127 +2180,127 @@
         <v>55</v>
       </c>
       <c r="B4" s="12">
-        <v>3.1948617534905285e-005</v>
+        <v>3.1284428489710037e-005</v>
       </c>
       <c r="C4">
-        <v>7.8564666219521666e-010</v>
+        <v>7.3082024556672204e-010</v>
       </c>
       <c r="D4">
-        <v>-3.3274565282014838e-008</v>
+        <v>-3.319127947999116e-008</v>
       </c>
       <c r="E4">
-        <v>3.3347954745711541e-010</v>
+        <v>3.3266416448295071e-010</v>
       </c>
       <c r="F4">
-        <v>-7.6115572413046353e-008</v>
+        <v>-7.5887267038603062e-008</v>
       </c>
       <c r="G4">
-        <v>-3.8036972228027976e-008</v>
+        <v>-3.813419552448637e-008</v>
       </c>
       <c r="H4">
-        <v>1.0275927840878014e-009</v>
+        <v>1.2500513794468922e-009</v>
       </c>
       <c r="I4">
-        <v>-3.1842752905713831e-008</v>
+        <v>-3.1782662285910948e-008</v>
       </c>
       <c r="J4">
-        <v>1.9873034198176063e-008</v>
+        <v>2.0071365463962981e-008</v>
       </c>
       <c r="K4">
-        <v>-7.7114735826607295e-008</v>
+        <v>-7.7294683543156258e-008</v>
       </c>
       <c r="L4">
-        <v>9.1268081603663702e-010</v>
+        <v>6.5198397298494262e-010</v>
       </c>
       <c r="M4">
-        <v>-1.8654774510397871e-007</v>
+        <v>-1.8449959883008484e-007</v>
       </c>
       <c r="N4">
-        <v>-4.5230968893421547e-008</v>
+        <v>-4.568526281379137e-008</v>
       </c>
       <c r="O4">
-        <v>1.9897108183802977e-009</v>
+        <v>1.8389447355966073e-009</v>
       </c>
       <c r="P4">
-        <v>-2.1959591855770163e-008</v>
+        <v>-2.1974859052382345e-008</v>
       </c>
       <c r="Q4">
-        <v>-1.0925409364765469e-009</v>
+        <v>-1.0764623120365443e-009</v>
       </c>
       <c r="R4">
-        <v>-5.5688122932826104e-010</v>
+        <v>-5.6057026211139028e-010</v>
       </c>
       <c r="S4">
-        <v>-3.580592592226856e-008</v>
+        <v>-3.5893692030047936e-008</v>
       </c>
       <c r="T4">
-        <v>-4.4446021929114063e-009</v>
+        <v>-5.2720622825016038e-009</v>
       </c>
       <c r="U4">
-        <v>1.9109911531895145e-008</v>
+        <v>1.8621702660303102e-008</v>
       </c>
       <c r="V4">
-        <v>2.6916196714440763e-008</v>
+        <v>2.6504998988733146e-008</v>
       </c>
       <c r="W4">
-        <v>-2.6311411916055669e-009</v>
+        <v>-2.4839963851293024e-009</v>
       </c>
       <c r="X4">
-        <v>5.7090765797892343e-009</v>
+        <v>5.9060951476975856e-009</v>
       </c>
       <c r="Y4">
-        <v>1.5813547066086433e-008</v>
+        <v>1.6840048501916334e-008</v>
       </c>
       <c r="Z4">
-        <v>3.3467275454540686e-009</v>
+        <v>5.4267287881987589e-009</v>
       </c>
       <c r="AA4">
-        <v>3.6488823689211939e-009</v>
+        <v>4.5939750203273051e-009</v>
       </c>
       <c r="AB4">
-        <v>2.2560010419486656e-009</v>
+        <v>3.4325231597389311e-009</v>
       </c>
       <c r="AC4">
-        <v>4.683812022522709e-009</v>
+        <v>5.8186728297166114e-009</v>
       </c>
       <c r="AD4">
-        <v>3.3861924066573644e-009</v>
+        <v>4.5198669120779643e-009</v>
       </c>
       <c r="AE4">
-        <v>2.0050796164451299e-009</v>
+        <v>3.0747427021770088e-009</v>
       </c>
       <c r="AF4">
-        <v>-5.5020054806323124e-010</v>
+        <v>8.2796512018523817e-010</v>
       </c>
       <c r="AG4">
-        <v>-1.1446278559799904e-008</v>
+        <v>-1.0355970486476632e-008</v>
       </c>
       <c r="AH4">
-        <v>1.4842365777489208e-008</v>
+        <v>1.5604901128459016e-008</v>
       </c>
       <c r="AI4">
-        <v>3.4501885691116846e-009</v>
+        <v>3.9104818461065424e-009</v>
       </c>
       <c r="AJ4">
-        <v>-1.900508073921277e-009</v>
+        <v>-1.9644458001874094e-009</v>
       </c>
       <c r="AK4">
-        <v>3.560173271636186e-009</v>
+        <v>4.151541350872783e-009</v>
       </c>
       <c r="AL4">
-        <v>1.0019121238380966e-008</v>
+        <v>1.246790200974852e-008</v>
       </c>
       <c r="AM4">
-        <v>1.0678417267543154e-008</v>
+        <v>1.0551217249691462e-008</v>
       </c>
       <c r="AN4">
-        <v>1.6089816134282093e-008</v>
+        <v>1.6596955131367341e-008</v>
       </c>
       <c r="AO4">
-        <v>-4.803412033318179e-009</v>
+        <v>3.3415540503812032e-010</v>
       </c>
       <c r="AP4">
-        <v>8.9165088657926699e-007</v>
+        <v>8.8918417274773365e-007</v>
       </c>
     </row>
     <row r="5">
@@ -2308,127 +2308,127 @@
         <v>56</v>
       </c>
       <c r="B5" s="14">
-        <v>-0.062997026905585007</v>
+        <v>-0.061733650559734683</v>
       </c>
       <c r="C5">
-        <v>-3.9622115409459368e-005</v>
+        <v>-3.9358928149478029e-005</v>
       </c>
       <c r="D5">
-        <v>1.0415271852461455e-005</v>
+        <v>1.040509943709718e-005</v>
       </c>
       <c r="E5">
-        <v>-7.6115572413046353e-008</v>
+        <v>-7.5887267038603062e-008</v>
       </c>
       <c r="F5">
-        <v>0.014017040826427489</v>
+        <v>0.014042774896952071</v>
       </c>
       <c r="G5">
-        <v>0.00029039033650946321</v>
+        <v>0.00029078762583973651</v>
       </c>
       <c r="H5">
-        <v>0.00030084904818674979</v>
+        <v>0.00030107582711958104</v>
       </c>
       <c r="I5">
-        <v>0.00038469780076773742</v>
+        <v>0.00038456358166450116</v>
       </c>
       <c r="J5">
-        <v>0.00031929918712991383</v>
+        <v>0.00031918650137636388</v>
       </c>
       <c r="K5">
-        <v>0.00032723282056273988</v>
+        <v>0.00032746072881628349</v>
       </c>
       <c r="L5">
-        <v>0.00035005361356219597</v>
+        <v>0.00035046407028354904</v>
       </c>
       <c r="M5">
-        <v>9.3560958211929567e-006</v>
+        <v>7.4009428114694698e-006</v>
       </c>
       <c r="N5">
-        <v>4.3380156959026378e-006</v>
+        <v>4.4214792340008621e-006</v>
       </c>
       <c r="O5">
-        <v>0.00010472896223461103</v>
+        <v>0.0001053024003476495</v>
       </c>
       <c r="P5">
-        <v>0.00010940925610043067</v>
+        <v>0.00010986367446221907</v>
       </c>
       <c r="Q5">
-        <v>-5.5838321333886147e-007</v>
+        <v>-5.5058632227619628e-007</v>
       </c>
       <c r="R5">
-        <v>-5.9437942580910978e-007</v>
+        <v>-6.0560811041091787e-007</v>
       </c>
       <c r="S5">
-        <v>2.7722303480930439e-006</v>
+        <v>2.7170379921644694e-006</v>
       </c>
       <c r="T5">
-        <v>2.9511611410567001e-005</v>
+        <v>2.9826609188360979e-005</v>
       </c>
       <c r="U5">
-        <v>7.6728706811351202e-005</v>
+        <v>7.70678711128843e-005</v>
       </c>
       <c r="V5">
-        <v>0.00013283391238320177</v>
+        <v>0.00013332323715633406</v>
       </c>
       <c r="W5">
-        <v>-4.203353510195394e-006</v>
+        <v>-4.263824246065079e-006</v>
       </c>
       <c r="X5">
-        <v>4.0473386521211674e-005</v>
+        <v>4.1029776062692343e-005</v>
       </c>
       <c r="Y5">
-        <v>2.3235038603243649e-005</v>
+        <v>2.5410318695237994e-005</v>
       </c>
       <c r="Z5">
-        <v>4.2585669000465363e-005</v>
+        <v>4.4244666748914372e-005</v>
       </c>
       <c r="AA5">
-        <v>6.0798857632218413e-005</v>
+        <v>6.3082394451988085e-005</v>
       </c>
       <c r="AB5">
-        <v>6.3782716654939758e-005</v>
+        <v>6.586282011977713e-005</v>
       </c>
       <c r="AC5">
-        <v>3.6694469644645993e-005</v>
+        <v>3.8763792665232444e-005</v>
       </c>
       <c r="AD5">
-        <v>3.2152898195590197e-005</v>
+        <v>3.3906581350821768e-005</v>
       </c>
       <c r="AE5">
-        <v>4.5619095959262961e-005</v>
+        <v>4.798065596966304e-005</v>
       </c>
       <c r="AF5">
-        <v>3.2917015881726954e-005</v>
+        <v>3.5126085159460242e-005</v>
       </c>
       <c r="AG5">
-        <v>5.8581790707732729e-005</v>
+        <v>6.0647341145564614e-005</v>
       </c>
       <c r="AH5">
-        <v>-2.6695235389355022e-005</v>
+        <v>-2.4064314215068087e-005</v>
       </c>
       <c r="AI5">
-        <v>6.8854776226102087e-005</v>
+        <v>7.1280408559634646e-005</v>
       </c>
       <c r="AJ5">
-        <v>1.5645417313077337e-006</v>
+        <v>1.5738251730468475e-006</v>
       </c>
       <c r="AK5">
-        <v>1.2335767069761425e-005</v>
+        <v>1.2447682856694151e-005</v>
       </c>
       <c r="AL5">
-        <v>3.5035060547663934e-007</v>
+        <v>-5.3541140620620177e-007</v>
       </c>
       <c r="AM5">
-        <v>6.3632962067957435e-005</v>
+        <v>6.5448510151690979e-005</v>
       </c>
       <c r="AN5">
-        <v>6.7404470227266461e-005</v>
+        <v>6.9564036973654214e-005</v>
       </c>
       <c r="AO5">
-        <v>-3.5786210842447179e-005</v>
+        <v>8.468209459420187e-006</v>
       </c>
       <c r="AP5">
-        <v>-0.00075616140594718384</v>
+        <v>-0.00076007757052674028</v>
       </c>
     </row>
     <row r="6">
@@ -2436,127 +2436,127 @@
         <v>57</v>
       </c>
       <c r="B6" s="16">
-        <v>0.058392649742837886</v>
+        <v>0.058280669444391739</v>
       </c>
       <c r="C6">
-        <v>-1.8822132446127904e-005</v>
+        <v>-1.882364922943672e-005</v>
       </c>
       <c r="D6">
-        <v>2.9713695236537236e-006</v>
+        <v>2.974512017860452e-006</v>
       </c>
       <c r="E6">
-        <v>-3.8036972228027976e-008</v>
+        <v>-3.813419552448637e-008</v>
       </c>
       <c r="F6">
-        <v>0.00029039033650946321</v>
+        <v>0.00029078762583973651</v>
       </c>
       <c r="G6">
-        <v>0.0004713954058240406</v>
+        <v>0.00047165021033878887</v>
       </c>
       <c r="H6">
-        <v>0.00021486365636878263</v>
+        <v>0.00021512625599857799</v>
       </c>
       <c r="I6">
-        <v>0.0002437436457473571</v>
+        <v>0.00024395488585539365</v>
       </c>
       <c r="J6">
-        <v>0.00027803905452490054</v>
+        <v>0.00027847687402064936</v>
       </c>
       <c r="K6">
-        <v>0.00030605936621012577</v>
+        <v>0.00030637594648905728</v>
       </c>
       <c r="L6">
-        <v>0.00027721497225237504</v>
+        <v>0.00027767216828231188</v>
       </c>
       <c r="M6">
-        <v>-9.4477926175946317e-006</v>
+        <v>-8.8993269968485887e-006</v>
       </c>
       <c r="N6">
-        <v>-1.0650848754293567e-005</v>
+        <v>-1.0397388851972434e-005</v>
       </c>
       <c r="O6">
-        <v>2.2150085017403622e-005</v>
+        <v>2.1938167007050922e-005</v>
       </c>
       <c r="P6">
-        <v>2.9585222737248725e-005</v>
+        <v>2.93457003196298e-005</v>
       </c>
       <c r="Q6">
-        <v>-2.9807970842991415e-007</v>
+        <v>-2.9499764257746286e-007</v>
       </c>
       <c r="R6">
-        <v>5.7264794826078726e-008</v>
+        <v>5.2347753403825357e-008</v>
       </c>
       <c r="S6">
-        <v>1.8392438289674105e-005</v>
+        <v>1.8950085924134927e-005</v>
       </c>
       <c r="T6">
-        <v>5.8358305603613121e-005</v>
+        <v>5.8530869337245091e-005</v>
       </c>
       <c r="U6">
-        <v>0.00011518045302010784</v>
+        <v>0.00011563980312241502</v>
       </c>
       <c r="V6">
-        <v>0.0001657512579764472</v>
+        <v>0.0001662234845230217</v>
       </c>
       <c r="W6">
-        <v>-5.2105654287807544e-006</v>
+        <v>-5.2182925460248235e-006</v>
       </c>
       <c r="X6">
-        <v>-2.0211833156885605e-005</v>
+        <v>-2.0247012625917806e-005</v>
       </c>
       <c r="Y6">
-        <v>1.725544364771434e-005</v>
+        <v>1.6821231397551189e-005</v>
       </c>
       <c r="Z6">
-        <v>1.9072347298937794e-005</v>
+        <v>1.9152511835205643e-005</v>
       </c>
       <c r="AA6">
-        <v>3.3890928328997999e-005</v>
+        <v>3.3563824903551828e-005</v>
       </c>
       <c r="AB6">
-        <v>2.9451251591198656e-005</v>
+        <v>2.9113658753665766e-005</v>
       </c>
       <c r="AC6">
-        <v>2.4575656793736539e-005</v>
+        <v>2.4459194341473521e-005</v>
       </c>
       <c r="AD6">
-        <v>1.7894740527204988e-005</v>
+        <v>1.7673161332525544e-005</v>
       </c>
       <c r="AE6">
-        <v>2.1047671777806868e-005</v>
+        <v>2.0718899209248231e-005</v>
       </c>
       <c r="AF6">
-        <v>3.0844326444915985e-005</v>
+        <v>3.0580734691649473e-005</v>
       </c>
       <c r="AG6">
-        <v>2.0254408291324496e-005</v>
+        <v>1.9971919892630333e-005</v>
       </c>
       <c r="AH6">
-        <v>9.3655179721029627e-006</v>
+        <v>9.1603245672613665e-006</v>
       </c>
       <c r="AI6">
-        <v>1.8023153806085828e-005</v>
+        <v>1.7602170952127087e-005</v>
       </c>
       <c r="AJ6">
-        <v>1.4157003435898898e-006</v>
+        <v>1.4106773893571412e-006</v>
       </c>
       <c r="AK6">
-        <v>-1.1323579989716822e-005</v>
+        <v>-1.1154389961679917e-005</v>
       </c>
       <c r="AL6">
-        <v>-2.5799005592011302e-006</v>
+        <v>-1.926882591517733e-006</v>
       </c>
       <c r="AM6">
-        <v>7.4097477972990687e-006</v>
+        <v>6.9502378940695622e-006</v>
       </c>
       <c r="AN6">
-        <v>-9.1115693164547392e-006</v>
+        <v>-9.5557461050334541e-006</v>
       </c>
       <c r="AO6">
-        <v>3.1934394070982398e-007</v>
+        <v>-8.0727329784815397e-006</v>
       </c>
       <c r="AP6">
-        <v>-0.00039344498934904584</v>
+        <v>-0.00039332339225611399</v>
       </c>
     </row>
     <row r="7">
@@ -2564,127 +2564,127 @@
         <v>58</v>
       </c>
       <c r="B7" s="18">
-        <v>-0.0078664576779359126</v>
+        <v>-0.0073299585645495045</v>
       </c>
       <c r="C7">
-        <v>3.0765284568223453e-006</v>
+        <v>3.135120780388428e-006</v>
       </c>
       <c r="D7">
-        <v>1.0662403441242045e-006</v>
+        <v>1.040201700081031e-006</v>
       </c>
       <c r="E7">
-        <v>1.0275927840878014e-009</v>
+        <v>1.2500513794468922e-009</v>
       </c>
       <c r="F7">
-        <v>0.00030084904818674979</v>
+        <v>0.00030107582711958104</v>
       </c>
       <c r="G7">
-        <v>0.00021486365636878263</v>
+        <v>0.00021512625599857799</v>
       </c>
       <c r="H7">
-        <v>0.00040565748035837072</v>
+        <v>0.00040645339702684075</v>
       </c>
       <c r="I7">
-        <v>0.00024539886553194898</v>
+        <v>0.00024606985468679201</v>
       </c>
       <c r="J7">
-        <v>0.00023879216764000329</v>
+        <v>0.00023901117014001757</v>
       </c>
       <c r="K7">
-        <v>0.00023121550822325336</v>
+        <v>0.00023135950253664413</v>
       </c>
       <c r="L7">
-        <v>0.00023660589692245122</v>
+        <v>0.00023697744312051007</v>
       </c>
       <c r="M7">
-        <v>6.2770968149834794e-005</v>
+        <v>6.1941823375586538e-005</v>
       </c>
       <c r="N7">
-        <v>5.6527847556416912e-006</v>
+        <v>5.5949172224475006e-006</v>
       </c>
       <c r="O7">
-        <v>2.1790624685766378e-005</v>
+        <v>2.1516016831756829e-005</v>
       </c>
       <c r="P7">
-        <v>3.1089524885547413e-005</v>
+        <v>3.075599574824086e-005</v>
       </c>
       <c r="Q7">
-        <v>4.2237091114157776e-009</v>
+        <v>2.0023432095653418e-009</v>
       </c>
       <c r="R7">
-        <v>-2.8466623728319258e-007</v>
+        <v>-2.8846225345232835e-007</v>
       </c>
       <c r="S7">
-        <v>-9.2607492832469925e-006</v>
+        <v>-1.0102568834723701e-005</v>
       </c>
       <c r="T7">
-        <v>8.8457661546461488e-006</v>
+        <v>8.2453657084472694e-006</v>
       </c>
       <c r="U7">
-        <v>2.7564184041252638e-005</v>
+        <v>2.7065321088778022e-005</v>
       </c>
       <c r="V7">
-        <v>7.6385826322791518e-005</v>
+        <v>7.5877653170086667e-005</v>
       </c>
       <c r="W7">
-        <v>3.0680730509382997e-007</v>
+        <v>3.1052046240621893e-007</v>
       </c>
       <c r="X7">
-        <v>-1.2421676964028212e-005</v>
+        <v>-1.2473712730409556e-005</v>
       </c>
       <c r="Y7">
-        <v>1.2959913391713698e-005</v>
+        <v>1.2223847002923946e-005</v>
       </c>
       <c r="Z7">
-        <v>2.9772217288906949e-005</v>
+        <v>2.9008592422752189e-005</v>
       </c>
       <c r="AA7">
-        <v>3.7871518396302173e-005</v>
+        <v>3.7331295725158105e-005</v>
       </c>
       <c r="AB7">
-        <v>3.9594852907438307e-005</v>
+        <v>3.9202701076031289e-005</v>
       </c>
       <c r="AC7">
-        <v>4.1472015736853361e-005</v>
+        <v>4.1140396085820408e-005</v>
       </c>
       <c r="AD7">
-        <v>2.6586268515129632e-005</v>
+        <v>2.6122838509771811e-005</v>
       </c>
       <c r="AE7">
-        <v>2.8727728194853901e-005</v>
+        <v>2.819062918018544e-005</v>
       </c>
       <c r="AF7">
-        <v>4.1935567786795002e-005</v>
+        <v>4.147873628335976e-005</v>
       </c>
       <c r="AG7">
-        <v>2.8058613379705238e-005</v>
+        <v>2.7453471000079443e-005</v>
       </c>
       <c r="AH7">
-        <v>2.6351405141876389e-005</v>
+        <v>2.5912754569108509e-005</v>
       </c>
       <c r="AI7">
-        <v>2.3312730076651867e-005</v>
+        <v>2.2409646081385571e-005</v>
       </c>
       <c r="AJ7">
-        <v>1.6173194357219559e-006</v>
+        <v>1.6368308290256186e-006</v>
       </c>
       <c r="AK7">
-        <v>-2.3316837823088069e-006</v>
+        <v>-2.3988147301926446e-006</v>
       </c>
       <c r="AL7">
-        <v>-8.7386652357140472e-006</v>
+        <v>-9.3873073656590952e-006</v>
       </c>
       <c r="AM7">
-        <v>-7.771647279718557e-006</v>
+        <v>-8.433631575797539e-006</v>
       </c>
       <c r="AN7">
-        <v>1.2113688920050114e-005</v>
+        <v>1.1526790580507809e-005</v>
       </c>
       <c r="AO7">
-        <v>-9.8657449106362817e-007</v>
+        <v>-7.6326370123682531e-006</v>
       </c>
       <c r="AP7">
-        <v>-0.00035824355492082734</v>
+        <v>-0.00035631449841888856</v>
       </c>
     </row>
     <row r="8">
@@ -2692,127 +2692,127 @@
         <v>59</v>
       </c>
       <c r="B8" s="20">
-        <v>-0.24685751081588994</v>
+        <v>-0.24616059164101423</v>
       </c>
       <c r="C8">
-        <v>-8.403887341005737e-005</v>
+        <v>-8.3920860752459349e-005</v>
       </c>
       <c r="D8">
-        <v>3.4646329188053573e-006</v>
+        <v>3.4230884546269621e-006</v>
       </c>
       <c r="E8">
-        <v>-3.1842752905713831e-008</v>
+        <v>-3.1782662285910948e-008</v>
       </c>
       <c r="F8">
-        <v>0.00038469780076773742</v>
+        <v>0.00038456358166450116</v>
       </c>
       <c r="G8">
-        <v>0.0002437436457473571</v>
+        <v>0.00024395488585539365</v>
       </c>
       <c r="H8">
-        <v>0.00024539886553194898</v>
+        <v>0.00024606985468679201</v>
       </c>
       <c r="I8">
-        <v>0.032451026487207303</v>
+        <v>0.032537510279123216</v>
       </c>
       <c r="J8">
-        <v>0.00035097161805453729</v>
+        <v>0.00035123763190028227</v>
       </c>
       <c r="K8">
-        <v>0.00028801033870803303</v>
+        <v>0.00028872406982202731</v>
       </c>
       <c r="L8">
-        <v>0.0003211182755698939</v>
+        <v>0.00032229293728453141</v>
       </c>
       <c r="M8">
-        <v>-4.6337151632294828e-005</v>
+        <v>-4.6194695604229191e-005</v>
       </c>
       <c r="N8">
-        <v>0.00011378104268745546</v>
+        <v>0.00011382480355427444</v>
       </c>
       <c r="O8">
-        <v>-3.41743735627432e-005</v>
+        <v>-3.5922949152058787e-005</v>
       </c>
       <c r="P8">
-        <v>6.4027366627313607e-005</v>
+        <v>6.2082276270439176e-005</v>
       </c>
       <c r="Q8">
-        <v>2.696279328560067e-006</v>
+        <v>2.6891944035677689e-006</v>
       </c>
       <c r="R8">
-        <v>1.4352621743324586e-006</v>
+        <v>1.4166592043479909e-006</v>
       </c>
       <c r="S8">
-        <v>4.1093010093961943e-005</v>
+        <v>4.1418122986522647e-005</v>
       </c>
       <c r="T8">
-        <v>0.00014787054683602363</v>
+        <v>0.00014758614517680792</v>
       </c>
       <c r="U8">
-        <v>0.0002507147532820527</v>
+        <v>0.00025053085647868317</v>
       </c>
       <c r="V8">
-        <v>0.00021893612132088442</v>
+        <v>0.00021858548226335223</v>
       </c>
       <c r="W8">
-        <v>-8.3098323201029026e-006</v>
+        <v>-8.4119925083352442e-006</v>
       </c>
       <c r="X8">
-        <v>7.2808668529554874e-005</v>
+        <v>7.2405098850131526e-005</v>
       </c>
       <c r="Y8">
-        <v>-1.2985696311704929e-005</v>
+        <v>-1.8518886521473684e-005</v>
       </c>
       <c r="Z8">
-        <v>1.6051098532026145e-005</v>
+        <v>1.1532560900428521e-005</v>
       </c>
       <c r="AA8">
-        <v>0.00017140285409053394</v>
+        <v>0.00016697856894276706</v>
       </c>
       <c r="AB8">
-        <v>8.5378323731873036e-005</v>
+        <v>8.1372758819724659e-005</v>
       </c>
       <c r="AC8">
-        <v>-6.6492616617335845e-006</v>
+        <v>-9.9608127622214634e-006</v>
       </c>
       <c r="AD8">
-        <v>2.7186207177933301e-005</v>
+        <v>2.3916726630220741e-005</v>
       </c>
       <c r="AE8">
-        <v>0.00020692008425780031</v>
+        <v>0.00020303885685219727</v>
       </c>
       <c r="AF8">
-        <v>6.2749221625431161e-005</v>
+        <v>5.791744069693084e-005</v>
       </c>
       <c r="AG8">
-        <v>-3.1291993330550161e-006</v>
+        <v>-7.276197335241507e-006</v>
       </c>
       <c r="AH8">
-        <v>-1.2996915044699635e-005</v>
+        <v>-1.80146802374603e-005</v>
       </c>
       <c r="AI8">
-        <v>4.4014451753860031e-005</v>
+        <v>3.8792847057426592e-005</v>
       </c>
       <c r="AJ8">
-        <v>2.255681235630283e-005</v>
+        <v>2.2679259329575945e-005</v>
       </c>
       <c r="AK8">
-        <v>-0.00014228772999531669</v>
+        <v>-0.00014277536773756291</v>
       </c>
       <c r="AL8">
-        <v>-0.00014501536010140046</v>
+        <v>-0.0001454493643495981</v>
       </c>
       <c r="AM8">
-        <v>-4.2738136413975883e-005</v>
+        <v>-4.7001705974134234e-005</v>
       </c>
       <c r="AN8">
-        <v>-0.00014641317021501401</v>
+        <v>-0.00015171131348329776</v>
       </c>
       <c r="AO8">
-        <v>-6.1528399281008617e-005</v>
+        <v>-0.00010447583529184955</v>
       </c>
       <c r="AP8">
-        <v>-0.0010938037451240403</v>
+        <v>-0.0010855624412434099</v>
       </c>
     </row>
     <row r="9">
@@ -2820,127 +2820,127 @@
         <v>60</v>
       </c>
       <c r="B9" s="22">
-        <v>-0.19499215588615662</v>
+        <v>-0.19456295381846483</v>
       </c>
       <c r="C9">
-        <v>-3.4737978181363596e-005</v>
+        <v>-3.4692016537104544e-005</v>
       </c>
       <c r="D9">
-        <v>-5.8424647554752843e-007</v>
+        <v>-6.0679716057737294e-007</v>
       </c>
       <c r="E9">
-        <v>1.9873034198176063e-008</v>
+        <v>2.0071365463962981e-008</v>
       </c>
       <c r="F9">
-        <v>0.00031929918712991383</v>
+        <v>0.00031918650137636388</v>
       </c>
       <c r="G9">
-        <v>0.00027803905452490054</v>
+        <v>0.00027847687402064936</v>
       </c>
       <c r="H9">
-        <v>0.00023879216764000329</v>
+        <v>0.00023901117014001757</v>
       </c>
       <c r="I9">
-        <v>0.00035097161805453729</v>
+        <v>0.00035123763190028227</v>
       </c>
       <c r="J9">
-        <v>0.00086115519200335392</v>
+        <v>0.0008627128625342225</v>
       </c>
       <c r="K9">
-        <v>0.00029077351736433641</v>
+        <v>0.00029126334389177442</v>
       </c>
       <c r="L9">
-        <v>0.00031669183589256504</v>
+        <v>0.0003172148291226609</v>
       </c>
       <c r="M9">
-        <v>9.790734182186077e-005</v>
+        <v>9.8162379492938199e-005</v>
       </c>
       <c r="N9">
-        <v>5.0896619578384137e-005</v>
+        <v>5.1334421332998554e-005</v>
       </c>
       <c r="O9">
-        <v>2.5339764650588896e-005</v>
+        <v>2.5106817227960041e-005</v>
       </c>
       <c r="P9">
-        <v>2.904350042221365e-005</v>
+        <v>2.8797854478725409e-005</v>
       </c>
       <c r="Q9">
-        <v>-3.4275391965291708e-007</v>
+        <v>-3.4470170825956998e-007</v>
       </c>
       <c r="R9">
-        <v>-6.0324258552092622e-008</v>
+        <v>-6.2508342962404145e-008</v>
       </c>
       <c r="S9">
-        <v>4.1912547883222272e-005</v>
+        <v>4.2767062229907729e-005</v>
       </c>
       <c r="T9">
-        <v>0.0001120718134668072</v>
+        <v>0.0001129196600014647</v>
       </c>
       <c r="U9">
-        <v>0.0002043361906818934</v>
+        <v>0.00020556065281434439</v>
       </c>
       <c r="V9">
-        <v>0.00024547576578353944</v>
+        <v>0.00024647651390258501</v>
       </c>
       <c r="W9">
-        <v>-5.3972373367138426e-006</v>
+        <v>-5.4823981271316339e-006</v>
       </c>
       <c r="X9">
-        <v>-2.4202544910332347e-006</v>
+        <v>-2.5315281471237523e-006</v>
       </c>
       <c r="Y9">
-        <v>9.1969494140900446e-006</v>
+        <v>9.0658135587639245e-006</v>
       </c>
       <c r="Z9">
-        <v>3.1890012397859101e-005</v>
+        <v>3.1724283222555471e-005</v>
       </c>
       <c r="AA9">
-        <v>4.7373184465018844e-005</v>
+        <v>4.7283214122017732e-005</v>
       </c>
       <c r="AB9">
-        <v>4.8136812272764873e-005</v>
+        <v>4.8353502230760692e-005</v>
       </c>
       <c r="AC9">
-        <v>3.6026458008795377e-005</v>
+        <v>3.5960673289889608e-005</v>
       </c>
       <c r="AD9">
-        <v>2.1984808266582192e-005</v>
+        <v>2.1759754083253502e-005</v>
       </c>
       <c r="AE9">
-        <v>3.2526448353541393e-005</v>
+        <v>3.2307830672687991e-005</v>
       </c>
       <c r="AF9">
-        <v>7.3022167543804737e-005</v>
+        <v>7.2683787983176317e-005</v>
       </c>
       <c r="AG9">
-        <v>3.0231703177434861e-005</v>
+        <v>3.0007355966603794e-005</v>
       </c>
       <c r="AH9">
-        <v>2.7200665221475215e-005</v>
+        <v>2.7148690665105618e-005</v>
       </c>
       <c r="AI9">
-        <v>3.5460858449790355e-005</v>
+        <v>3.5860336554234106e-005</v>
       </c>
       <c r="AJ9">
-        <v>2.3340341326779234e-006</v>
+        <v>2.3520768482450057e-006</v>
       </c>
       <c r="AK9">
-        <v>1.1360805555929623e-005</v>
+        <v>1.1131223218453481e-005</v>
       </c>
       <c r="AL9">
-        <v>-7.9025944442600579e-006</v>
+        <v>-8.2706886212612271e-006</v>
       </c>
       <c r="AM9">
-        <v>-4.231082383534469e-005</v>
+        <v>-4.2277869584417781e-005</v>
       </c>
       <c r="AN9">
-        <v>1.0386642045536777e-005</v>
+        <v>1.0098846413304107e-005</v>
       </c>
       <c r="AO9">
-        <v>-6.97413526769939e-007</v>
+        <v>-3.8224490277561176e-006</v>
       </c>
       <c r="AP9">
-        <v>-0.00048214491719598599</v>
+        <v>-0.00048244303525332884</v>
       </c>
     </row>
     <row r="10">
@@ -2948,127 +2948,127 @@
         <v>61</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.19325155822938025</v>
+        <v>-0.19361632610613511</v>
       </c>
       <c r="C10">
-        <v>-3.613227314374941e-006</v>
+        <v>-3.6690393304229927e-006</v>
       </c>
       <c r="D10">
-        <v>8.4076973157028939e-006</v>
+        <v>8.4195875642647749e-006</v>
       </c>
       <c r="E10">
-        <v>-7.7114735826607295e-008</v>
+        <v>-7.7294683543156258e-008</v>
       </c>
       <c r="F10">
-        <v>0.00032723282056273988</v>
+        <v>0.00032746072881628349</v>
       </c>
       <c r="G10">
-        <v>0.00030605936621012577</v>
+        <v>0.00030637594648905728</v>
       </c>
       <c r="H10">
-        <v>0.00023121550822325336</v>
+        <v>0.00023135950253664413</v>
       </c>
       <c r="I10">
-        <v>0.00028801033870803303</v>
+        <v>0.00028872406982202731</v>
       </c>
       <c r="J10">
-        <v>0.00029077351736433641</v>
+        <v>0.00029126334389177442</v>
       </c>
       <c r="K10">
-        <v>0.00039977545474800591</v>
+        <v>0.00040038160410295961</v>
       </c>
       <c r="L10">
-        <v>0.00031861501215124075</v>
+        <v>0.00031922298519884815</v>
       </c>
       <c r="M10">
-        <v>2.5485816783421315e-005</v>
+        <v>2.7065594761864182e-005</v>
       </c>
       <c r="N10">
-        <v>3.9714393469787384e-005</v>
+        <v>4.0355160162869013e-005</v>
       </c>
       <c r="O10">
-        <v>2.3198993520332699e-005</v>
+        <v>2.3002017928518663e-005</v>
       </c>
       <c r="P10">
-        <v>3.2458582448817848e-005</v>
+        <v>3.2227493419709728e-005</v>
       </c>
       <c r="Q10">
-        <v>1.2547335394322806e-008</v>
+        <v>1.1676695370255133e-008</v>
       </c>
       <c r="R10">
-        <v>3.2315642246367455e-008</v>
+        <v>3.3303270018820401e-008</v>
       </c>
       <c r="S10">
-        <v>6.7184468557612536e-005</v>
+        <v>6.8387450532203417e-005</v>
       </c>
       <c r="T10">
-        <v>0.00011947447483409316</v>
+        <v>0.00012041243653630528</v>
       </c>
       <c r="U10">
-        <v>0.00016636497827888017</v>
+        <v>0.00016761802192012169</v>
       </c>
       <c r="V10">
-        <v>0.0002123554084251221</v>
+        <v>0.00021345802077399919</v>
       </c>
       <c r="W10">
-        <v>-9.4732077564624537e-006</v>
+        <v>-9.5739518070309484e-006</v>
       </c>
       <c r="X10">
-        <v>-1.6421125710056077e-005</v>
+        <v>-1.6651496044337564e-005</v>
       </c>
       <c r="Y10">
-        <v>1.8178706591986267e-005</v>
+        <v>1.7339343582152344e-005</v>
       </c>
       <c r="Z10">
-        <v>3.9679033804963261e-005</v>
+        <v>3.9175454888008693e-005</v>
       </c>
       <c r="AA10">
-        <v>5.4360154694098176e-005</v>
+        <v>5.3658533812372466e-005</v>
       </c>
       <c r="AB10">
-        <v>4.6099012975285248e-005</v>
+        <v>4.5168777664249862e-005</v>
       </c>
       <c r="AC10">
-        <v>4.4760088199863379e-005</v>
+        <v>4.4140105487325209e-005</v>
       </c>
       <c r="AD10">
-        <v>3.7900906781360821e-005</v>
+        <v>3.7205736557521105e-005</v>
       </c>
       <c r="AE10">
-        <v>3.4727777814940279e-005</v>
+        <v>3.3859352017881603e-005</v>
       </c>
       <c r="AF10">
-        <v>5.2894905662205521e-005</v>
+        <v>5.1683689392831381e-005</v>
       </c>
       <c r="AG10">
-        <v>3.9705644136841779e-005</v>
+        <v>3.8849454777251672e-005</v>
       </c>
       <c r="AH10">
-        <v>2.3826574394951692e-005</v>
+        <v>2.2869448814908768e-005</v>
       </c>
       <c r="AI10">
-        <v>2.3489999480817464e-005</v>
+        <v>2.3418212669260713e-005</v>
       </c>
       <c r="AJ10">
-        <v>9.2265018167683617e-007</v>
+        <v>9.3933704155851876e-007</v>
       </c>
       <c r="AK10">
-        <v>-9.9750936820527652e-006</v>
+        <v>-1.0164209893933878e-005</v>
       </c>
       <c r="AL10">
-        <v>-6.2837281387818613e-006</v>
+        <v>-6.0154365222669341e-006</v>
       </c>
       <c r="AM10">
-        <v>1.1205716974278964e-005</v>
+        <v>1.0961963830670093e-005</v>
       </c>
       <c r="AN10">
-        <v>-1.1552803012544277e-005</v>
+        <v>-1.2556643183163081e-005</v>
       </c>
       <c r="AO10">
-        <v>1.3321334298249351e-006</v>
+        <v>-1.5090125322283956e-005</v>
       </c>
       <c r="AP10">
-        <v>-0.00065926475285955596</v>
+        <v>-0.00065965859942462618</v>
       </c>
     </row>
     <row r="11">
@@ -3076,127 +3076,127 @@
         <v>62</v>
       </c>
       <c r="B11" s="26">
-        <v>-0.30357199009709468</v>
+        <v>-0.30313527886328301</v>
       </c>
       <c r="C11">
-        <v>4.2398014178466015e-005</v>
+        <v>4.2740461689852399e-005</v>
       </c>
       <c r="D11">
-        <v>2.0131482338384087e-006</v>
+        <v>2.0490009476689539e-006</v>
       </c>
       <c r="E11">
-        <v>9.1268081603663702e-010</v>
+        <v>6.5198397298494262e-010</v>
       </c>
       <c r="F11">
-        <v>0.00035005361356219597</v>
+        <v>0.00035046407028354904</v>
       </c>
       <c r="G11">
-        <v>0.00027721497225237504</v>
+        <v>0.00027767216828231188</v>
       </c>
       <c r="H11">
-        <v>0.00023660589692245122</v>
+        <v>0.00023697744312051007</v>
       </c>
       <c r="I11">
-        <v>0.0003211182755698939</v>
+        <v>0.00032229293728453141</v>
       </c>
       <c r="J11">
-        <v>0.00031669183589256504</v>
+        <v>0.0003172148291226609</v>
       </c>
       <c r="K11">
-        <v>0.00031861501215124075</v>
+        <v>0.00031922298519884815</v>
       </c>
       <c r="L11">
-        <v>0.00098358752542892949</v>
+        <v>0.00098503678111363071</v>
       </c>
       <c r="M11">
-        <v>4.9940146278397604e-005</v>
+        <v>5.0543186417764221e-005</v>
       </c>
       <c r="N11">
-        <v>8.6245817457639162e-005</v>
+        <v>8.6701953597710462e-005</v>
       </c>
       <c r="O11">
-        <v>1.001101182116862e-005</v>
+        <v>9.6028810829974353e-006</v>
       </c>
       <c r="P11">
-        <v>2.9367660572157173e-005</v>
+        <v>2.8853425304335901e-005</v>
       </c>
       <c r="Q11">
-        <v>-5.670419834173295e-007</v>
+        <v>-5.6321510997912226e-007</v>
       </c>
       <c r="R11">
-        <v>-7.0623293782404591e-007</v>
+        <v>-7.0757348551750777e-007</v>
       </c>
       <c r="S11">
-        <v>7.6051471368019643e-005</v>
+        <v>7.6302908815065401e-005</v>
       </c>
       <c r="T11">
-        <v>0.00017452638012326624</v>
+        <v>0.00017469733004463685</v>
       </c>
       <c r="U11">
-        <v>0.00024675337150902889</v>
+        <v>0.00024746977414980567</v>
       </c>
       <c r="V11">
-        <v>0.00030066781119384903</v>
+        <v>0.00030137075645459224</v>
       </c>
       <c r="W11">
-        <v>-1.6829613603013239e-005</v>
+        <v>-1.6963120946405926e-005</v>
       </c>
       <c r="X11">
-        <v>1.4372310015921589e-005</v>
+        <v>1.4397572078518541e-005</v>
       </c>
       <c r="Y11">
-        <v>2.7579096414877379e-005</v>
+        <v>2.8056679495844849e-005</v>
       </c>
       <c r="Z11">
-        <v>3.4916282436393164e-005</v>
+        <v>3.5056367401661568e-005</v>
       </c>
       <c r="AA11">
-        <v>3.8596885642352249e-005</v>
+        <v>3.9190129771313245e-005</v>
       </c>
       <c r="AB11">
-        <v>4.2955249127794177e-005</v>
+        <v>4.3389703833699941e-005</v>
       </c>
       <c r="AC11">
-        <v>2.359717219091617e-005</v>
+        <v>2.441745926934888e-005</v>
       </c>
       <c r="AD11">
-        <v>2.3830579479435526e-005</v>
+        <v>2.4516056335315922e-005</v>
       </c>
       <c r="AE11">
-        <v>3.3780084606018336e-005</v>
+        <v>3.4209284274083593e-005</v>
       </c>
       <c r="AF11">
-        <v>8.0656064050054575e-005</v>
+        <v>8.0781937201692729e-005</v>
       </c>
       <c r="AG11">
-        <v>2.5545709157311596e-005</v>
+        <v>2.5939269107034342e-005</v>
       </c>
       <c r="AH11">
-        <v>2.4647661078261268e-005</v>
+        <v>2.4994079830905678e-005</v>
       </c>
       <c r="AI11">
-        <v>1.7788388526727555e-005</v>
+        <v>1.9037282360267316e-005</v>
       </c>
       <c r="AJ11">
-        <v>5.2689114875636364e-006</v>
+        <v>5.2562045490779694e-006</v>
       </c>
       <c r="AK11">
-        <v>-2.7178493755894633e-005</v>
+        <v>-2.7212311970640865e-005</v>
       </c>
       <c r="AL11">
-        <v>-2.8141660298203816e-005</v>
+        <v>-2.8850179693937051e-005</v>
       </c>
       <c r="AM11">
-        <v>1.7175999031811105e-005</v>
+        <v>1.7773987431751986e-005</v>
       </c>
       <c r="AN11">
-        <v>2.8885428344414387e-005</v>
+        <v>2.8824302606118271e-005</v>
       </c>
       <c r="AO11">
-        <v>-1.947745705359769e-005</v>
+        <v>-1.9043569434301118e-005</v>
       </c>
       <c r="AP11">
-        <v>-0.00064653796293402232</v>
+        <v>-0.00064838574052548665</v>
       </c>
     </row>
     <row r="12">
@@ -3204,127 +3204,127 @@
         <v>63</v>
       </c>
       <c r="B12" s="28">
-        <v>0.092551986832530936</v>
+        <v>0.092825627804387356</v>
       </c>
       <c r="C12">
-        <v>1.8272170722163976e-005</v>
+        <v>1.8168822437532194e-005</v>
       </c>
       <c r="D12">
-        <v>2.3912405415661292e-005</v>
+        <v>2.3673626878575388e-005</v>
       </c>
       <c r="E12">
-        <v>-1.8654774510397871e-007</v>
+        <v>-1.8449959883008484e-007</v>
       </c>
       <c r="F12">
-        <v>9.3560958211929567e-006</v>
+        <v>7.4009428114694698e-006</v>
       </c>
       <c r="G12">
-        <v>-9.4477926175946317e-006</v>
+        <v>-8.8993269968485887e-006</v>
       </c>
       <c r="H12">
-        <v>6.2770968149834794e-005</v>
+        <v>6.1941823375586538e-005</v>
       </c>
       <c r="I12">
-        <v>-4.6337151632294828e-005</v>
+        <v>-4.6194695604229191e-005</v>
       </c>
       <c r="J12">
-        <v>9.790734182186077e-005</v>
+        <v>9.8162379492938199e-005</v>
       </c>
       <c r="K12">
-        <v>2.5485816783421315e-005</v>
+        <v>2.7065594761864182e-005</v>
       </c>
       <c r="L12">
-        <v>4.9940146278397604e-005</v>
+        <v>5.0543186417764221e-005</v>
       </c>
       <c r="M12">
-        <v>0.0012405887017589809</v>
+        <v>0.0012388255586401624</v>
       </c>
       <c r="N12">
-        <v>0.00016067888489198291</v>
+        <v>0.00016306113538949268</v>
       </c>
       <c r="O12">
-        <v>-1.5788981714381423e-005</v>
+        <v>-1.5553720629053519e-005</v>
       </c>
       <c r="P12">
-        <v>-4.4932452096602474e-006</v>
+        <v>-4.6474647591290613e-006</v>
       </c>
       <c r="Q12">
-        <v>-7.0875102470608846e-007</v>
+        <v>-7.792160210694949e-007</v>
       </c>
       <c r="R12">
-        <v>3.7314304019906389e-007</v>
+        <v>3.9532297634899744e-007</v>
       </c>
       <c r="S12">
-        <v>9.5815670829886191e-005</v>
+        <v>0.00010307176721410661</v>
       </c>
       <c r="T12">
-        <v>0.00018540704599922673</v>
+        <v>0.0001932237816865148</v>
       </c>
       <c r="U12">
-        <v>0.00021046038352228084</v>
+        <v>0.00021688371710355036</v>
       </c>
       <c r="V12">
-        <v>0.00020322052112371473</v>
+        <v>0.00020884502243644868</v>
       </c>
       <c r="W12">
-        <v>-1.3373376294594187e-005</v>
+        <v>-1.4026290268421811e-005</v>
       </c>
       <c r="X12">
-        <v>-5.0252868797408614e-005</v>
+        <v>-5.1518649262629734e-005</v>
       </c>
       <c r="Y12">
-        <v>1.5205075871124502e-006</v>
+        <v>-4.6377892871179803e-006</v>
       </c>
       <c r="Z12">
-        <v>2.7884088199277538e-005</v>
+        <v>2.0444658617424741e-005</v>
       </c>
       <c r="AA12">
-        <v>1.6547942943106568e-005</v>
+        <v>1.0562117758169682e-005</v>
       </c>
       <c r="AB12">
-        <v>2.3331581142452144e-005</v>
+        <v>1.731328733090099e-005</v>
       </c>
       <c r="AC12">
-        <v>2.0949157345983768e-006</v>
+        <v>-3.6712926107483138e-006</v>
       </c>
       <c r="AD12">
-        <v>1.2215716568892443e-005</v>
+        <v>6.5337293116076199e-006</v>
       </c>
       <c r="AE12">
-        <v>4.4081676531365272e-005</v>
+        <v>3.8088800263124328e-005</v>
       </c>
       <c r="AF12">
-        <v>3.3406215012167039e-005</v>
+        <v>2.6308989402662822e-005</v>
       </c>
       <c r="AG12">
-        <v>2.2601141576842991e-005</v>
+        <v>1.6539691753148834e-005</v>
       </c>
       <c r="AH12">
-        <v>-7.5971544920461383e-006</v>
+        <v>-1.3733469032988947e-005</v>
       </c>
       <c r="AI12">
-        <v>3.8221169844648232e-005</v>
+        <v>3.2704554498045669e-005</v>
       </c>
       <c r="AJ12">
-        <v>3.0302444350286345e-006</v>
+        <v>3.2718364608088947e-006</v>
       </c>
       <c r="AK12">
-        <v>-3.5781360624717149e-005</v>
+        <v>-3.799216711831233e-005</v>
       </c>
       <c r="AL12">
-        <v>-1.6341761701717682e-005</v>
+        <v>-2.0918834664780453e-005</v>
       </c>
       <c r="AM12">
-        <v>-1.7439444218795815e-005</v>
+        <v>-1.9804278269498104e-005</v>
       </c>
       <c r="AN12">
-        <v>-3.0778599111392355e-005</v>
+        <v>-3.5403584024942597e-005</v>
       </c>
       <c r="AO12">
-        <v>-2.1646718503318124e-005</v>
+        <v>-4.6047411686258612e-005</v>
       </c>
       <c r="AP12">
-        <v>-0.00095122069122997963</v>
+        <v>-0.00094498820547280805</v>
       </c>
     </row>
     <row r="13">
@@ -3332,127 +3332,127 @@
         <v>64</v>
       </c>
       <c r="B13" s="30">
-        <v>-0.01526260475451165</v>
+        <v>-0.016217397218885665</v>
       </c>
       <c r="C13">
-        <v>2.3265075114504533e-005</v>
+        <v>2.3190569799913375e-005</v>
       </c>
       <c r="D13">
-        <v>3.1618050327629238e-006</v>
+        <v>3.2293225804668895e-006</v>
       </c>
       <c r="E13">
-        <v>-4.5230968893421547e-008</v>
+        <v>-4.568526281379137e-008</v>
       </c>
       <c r="F13">
-        <v>4.3380156959026378e-006</v>
+        <v>4.4214792340008621e-006</v>
       </c>
       <c r="G13">
-        <v>-1.0650848754293567e-005</v>
+        <v>-1.0397388851972434e-005</v>
       </c>
       <c r="H13">
-        <v>5.6527847556416912e-006</v>
+        <v>5.5949172224475006e-006</v>
       </c>
       <c r="I13">
-        <v>0.00011378104268745546</v>
+        <v>0.00011382480355427444</v>
       </c>
       <c r="J13">
-        <v>5.0896619578384137e-005</v>
+        <v>5.1334421332998554e-005</v>
       </c>
       <c r="K13">
-        <v>3.9714393469787384e-005</v>
+        <v>4.0355160162869013e-005</v>
       </c>
       <c r="L13">
-        <v>8.6245817457639162e-005</v>
+        <v>8.6701953597710462e-005</v>
       </c>
       <c r="M13">
-        <v>0.00016067888489198291</v>
+        <v>0.00016306113538949268</v>
       </c>
       <c r="N13">
-        <v>0.00033349356083846207</v>
+        <v>0.00033497153210734239</v>
       </c>
       <c r="O13">
-        <v>-1.6711096899445102e-006</v>
+        <v>-1.6156746983188384e-006</v>
       </c>
       <c r="P13">
-        <v>-6.1256299862495278e-006</v>
+        <v>-5.9279040666613495e-006</v>
       </c>
       <c r="Q13">
-        <v>8.156752337244581e-007</v>
+        <v>8.2337651011318388e-007</v>
       </c>
       <c r="R13">
-        <v>1.2307875417918197e-006</v>
+        <v>1.255829100044033e-006</v>
       </c>
       <c r="S13">
-        <v>0.0001360891813695357</v>
+        <v>0.00013790270270277091</v>
       </c>
       <c r="T13">
-        <v>0.00020571394287485412</v>
+        <v>0.00020774809159567731</v>
       </c>
       <c r="U13">
-        <v>0.00025995364733303467</v>
+        <v>0.00026263938306234996</v>
       </c>
       <c r="V13">
-        <v>0.00027467588170429838</v>
+        <v>0.00027693469497704537</v>
       </c>
       <c r="W13">
-        <v>-1.7753650728944329e-005</v>
+        <v>-1.7968863313020506e-005</v>
       </c>
       <c r="X13">
-        <v>6.0877632959140213e-006</v>
+        <v>6.0459290916063712e-006</v>
       </c>
       <c r="Y13">
-        <v>-2.1869329764075655e-007</v>
+        <v>1.881929502629106e-006</v>
       </c>
       <c r="Z13">
-        <v>3.7158101353686737e-006</v>
+        <v>5.1225277545594578e-006</v>
       </c>
       <c r="AA13">
-        <v>3.9868371525026122e-006</v>
+        <v>5.7547306732661944e-006</v>
       </c>
       <c r="AB13">
-        <v>8.1641983662402888e-006</v>
+        <v>9.5454956921986025e-006</v>
       </c>
       <c r="AC13">
-        <v>4.9457814599474461e-006</v>
+        <v>6.0950655028141561e-006</v>
       </c>
       <c r="AD13">
-        <v>1.060913295726772e-007</v>
+        <v>1.2743049188284423e-006</v>
       </c>
       <c r="AE13">
-        <v>1.0079935660142819e-005</v>
+        <v>1.1487507894058186e-005</v>
       </c>
       <c r="AF13">
-        <v>1.1631357995376263e-005</v>
+        <v>1.2267559442093118e-005</v>
       </c>
       <c r="AG13">
-        <v>2.4216683648363587e-006</v>
+        <v>3.9627402472842738e-006</v>
       </c>
       <c r="AH13">
-        <v>7.0742229134413884e-006</v>
+        <v>7.9574877523093585e-006</v>
       </c>
       <c r="AI13">
-        <v>5.3788399565639399e-006</v>
+        <v>9.4080893280886835e-006</v>
       </c>
       <c r="AJ13">
-        <v>2.6266879176414622e-006</v>
+        <v>2.6034599843525184e-006</v>
       </c>
       <c r="AK13">
-        <v>-1.0806355827676414e-005</v>
+        <v>-1.1248726136713914e-005</v>
       </c>
       <c r="AL13">
-        <v>-1.6468293489840983e-005</v>
+        <v>-1.7028896508459307e-005</v>
       </c>
       <c r="AM13">
-        <v>-1.0046907095243447e-005</v>
+        <v>-7.397947347535539e-006</v>
       </c>
       <c r="AN13">
-        <v>1.4101516176364055e-005</v>
+        <v>1.5185185284556901e-005</v>
       </c>
       <c r="AO13">
-        <v>1.160966847812869e-005</v>
+        <v>1.9187239347263381e-005</v>
       </c>
       <c r="AP13">
-        <v>-0.00050292423659015553</v>
+        <v>-0.00051030646215106609</v>
       </c>
     </row>
     <row r="14">
@@ -3460,127 +3460,127 @@
         <v>65</v>
       </c>
       <c r="B14" s="32">
-        <v>-0.14685122614916066</v>
+        <v>-0.14746585553287281</v>
       </c>
       <c r="C14">
-        <v>-6.9900708171753669e-006</v>
+        <v>-7.2353725472896123e-006</v>
       </c>
       <c r="D14">
-        <v>-3.4984786811638658e-007</v>
+        <v>-3.3651800074176554e-007</v>
       </c>
       <c r="E14">
-        <v>1.9897108183802977e-009</v>
+        <v>1.8389447355966073e-009</v>
       </c>
       <c r="F14">
-        <v>0.00010472896223461103</v>
+        <v>0.0001053024003476495</v>
       </c>
       <c r="G14">
-        <v>2.2150085017403622e-005</v>
+        <v>2.1938167007050922e-005</v>
       </c>
       <c r="H14">
-        <v>2.1790624685766378e-005</v>
+        <v>2.1516016831756829e-005</v>
       </c>
       <c r="I14">
-        <v>-3.41743735627432e-005</v>
+        <v>-3.5922949152058787e-005</v>
       </c>
       <c r="J14">
-        <v>2.5339764650588896e-005</v>
+        <v>2.5106817227960041e-005</v>
       </c>
       <c r="K14">
-        <v>2.3198993520332699e-005</v>
+        <v>2.3002017928518663e-005</v>
       </c>
       <c r="L14">
-        <v>1.001101182116862e-005</v>
+        <v>9.6028810829974353e-006</v>
       </c>
       <c r="M14">
-        <v>-1.5788981714381423e-005</v>
+        <v>-1.5553720629053519e-005</v>
       </c>
       <c r="N14">
-        <v>-1.6711096899445102e-006</v>
+        <v>-1.6156746983188384e-006</v>
       </c>
       <c r="O14">
-        <v>0.00025934353853531312</v>
+        <v>0.00026002357461654484</v>
       </c>
       <c r="P14">
-        <v>0.0002179280639880592</v>
+        <v>0.00021873238050523582</v>
       </c>
       <c r="Q14">
-        <v>-9.7862702356507444e-008</v>
+        <v>-9.8295315034315554e-008</v>
       </c>
       <c r="R14">
-        <v>5.7572141785585355e-008</v>
+        <v>6.1346329277247781e-008</v>
       </c>
       <c r="S14">
-        <v>2.851013865709762e-007</v>
+        <v>1.3690693698542991e-006</v>
       </c>
       <c r="T14">
-        <v>7.3570984253988305e-007</v>
+        <v>1.4269608064544641e-006</v>
       </c>
       <c r="U14">
-        <v>2.4732574423195445e-005</v>
+        <v>2.5153322922716651e-005</v>
       </c>
       <c r="V14">
-        <v>8.4833688734686246e-005</v>
+        <v>8.5420730546135554e-005</v>
       </c>
       <c r="W14">
-        <v>3.7262527219901041e-007</v>
+        <v>4.0568246932824329e-007</v>
       </c>
       <c r="X14">
-        <v>-3.2869979142680197e-006</v>
+        <v>-3.2259668890518322e-006</v>
       </c>
       <c r="Y14">
-        <v>-1.1150416219495254e-005</v>
+        <v>-1.0961921392815153e-005</v>
       </c>
       <c r="Z14">
-        <v>-4.4744179123924961e-006</v>
+        <v>-3.7556254142177867e-006</v>
       </c>
       <c r="AA14">
-        <v>-1.6264723733069384e-005</v>
+        <v>-1.6278950981465222e-005</v>
       </c>
       <c r="AB14">
-        <v>-2.0538440933876805e-005</v>
+        <v>-2.0724285015696188e-005</v>
       </c>
       <c r="AC14">
-        <v>-1.2933124185042329e-005</v>
+        <v>-1.3082745607955688e-005</v>
       </c>
       <c r="AD14">
-        <v>-1.3956940263591715e-005</v>
+        <v>-1.4245120790307552e-005</v>
       </c>
       <c r="AE14">
-        <v>-6.1799784853872922e-006</v>
+        <v>-6.2333134071262182e-006</v>
       </c>
       <c r="AF14">
-        <v>-1.6709959874444176e-005</v>
+        <v>-1.6482766406604815e-005</v>
       </c>
       <c r="AG14">
-        <v>-1.3607000476400813e-005</v>
+        <v>-1.3431625409114417e-005</v>
       </c>
       <c r="AH14">
-        <v>-1.4976570531056447e-005</v>
+        <v>-1.4799555215242842e-005</v>
       </c>
       <c r="AI14">
-        <v>-1.9173835418372759e-006</v>
+        <v>-1.7795937795747689e-006</v>
       </c>
       <c r="AJ14">
-        <v>7.0245978427905105e-007</v>
+        <v>6.788492163280821e-007</v>
       </c>
       <c r="AK14">
-        <v>-4.5863169187086576e-006</v>
+        <v>-4.5291560255274032e-006</v>
       </c>
       <c r="AL14">
-        <v>1.1379092070620814e-005</v>
+        <v>1.2447718701449592e-005</v>
       </c>
       <c r="AM14">
-        <v>4.5725391578932935e-005</v>
+        <v>4.6125946278338737e-005</v>
       </c>
       <c r="AN14">
-        <v>1.9998802726076549e-005</v>
+        <v>2.0529676296099356e-005</v>
       </c>
       <c r="AO14">
-        <v>3.0683959162420473e-005</v>
+        <v>2.7190897407220904e-005</v>
       </c>
       <c r="AP14">
-        <v>-0.00022441621158738868</v>
+        <v>-0.00022585421420360242</v>
       </c>
     </row>
     <row r="15">
@@ -3588,127 +3588,127 @@
         <v>66</v>
       </c>
       <c r="B15" s="34">
-        <v>-0.26222922304196367</v>
+        <v>-0.26272429801462749</v>
       </c>
       <c r="C15">
-        <v>-7.2153575104928027e-006</v>
+        <v>-7.4829875894160354e-006</v>
       </c>
       <c r="D15">
-        <v>3.0682516260413246e-007</v>
+        <v>3.027666647712168e-007</v>
       </c>
       <c r="E15">
-        <v>-2.1959591855770163e-008</v>
+        <v>-2.1974859052382345e-008</v>
       </c>
       <c r="F15">
-        <v>0.00010940925610043067</v>
+        <v>0.00010986367446221907</v>
       </c>
       <c r="G15">
-        <v>2.9585222737248725e-005</v>
+        <v>2.93457003196298e-005</v>
       </c>
       <c r="H15">
-        <v>3.1089524885547413e-005</v>
+        <v>3.075599574824086e-005</v>
       </c>
       <c r="I15">
-        <v>6.4027366627313607e-005</v>
+        <v>6.2082276270439176e-005</v>
       </c>
       <c r="J15">
-        <v>2.904350042221365e-005</v>
+        <v>2.8797854478725409e-005</v>
       </c>
       <c r="K15">
-        <v>3.2458582448817848e-005</v>
+        <v>3.2227493419709728e-005</v>
       </c>
       <c r="L15">
-        <v>2.9367660572157173e-005</v>
+        <v>2.8853425304335901e-005</v>
       </c>
       <c r="M15">
-        <v>-4.4932452096602474e-006</v>
+        <v>-4.6474647591290613e-006</v>
       </c>
       <c r="N15">
-        <v>-6.1256299862495278e-006</v>
+        <v>-5.9279040666613495e-006</v>
       </c>
       <c r="O15">
-        <v>0.0002179280639880592</v>
+        <v>0.00021873238050523582</v>
       </c>
       <c r="P15">
-        <v>0.00035831751104579344</v>
+        <v>0.00035932503480700463</v>
       </c>
       <c r="Q15">
-        <v>-6.6076659076509757e-008</v>
+        <v>-6.6476113471090693e-008</v>
       </c>
       <c r="R15">
-        <v>3.9496679414350624e-007</v>
+        <v>4.003641169634019e-007</v>
       </c>
       <c r="S15">
-        <v>8.133510951057365e-006</v>
+        <v>9.2128983869631893e-006</v>
       </c>
       <c r="T15">
-        <v>2.4846686593792778e-005</v>
+        <v>2.5559094647406842e-005</v>
       </c>
       <c r="U15">
-        <v>5.1802765716279469e-005</v>
+        <v>5.2233553827668492e-005</v>
       </c>
       <c r="V15">
-        <v>0.00011691206360954677</v>
+        <v>0.00011762702812629271</v>
       </c>
       <c r="W15">
-        <v>4.411048027073517e-006</v>
+        <v>4.4440610284290586e-006</v>
       </c>
       <c r="X15">
-        <v>9.7121132376103535e-006</v>
+        <v>9.8124145438962127e-006</v>
       </c>
       <c r="Y15">
-        <v>-1.4851877609190432e-005</v>
+        <v>-1.4252319274319722e-005</v>
       </c>
       <c r="Z15">
-        <v>-7.5309284809667942e-007</v>
+        <v>2.5978551697557275e-007</v>
       </c>
       <c r="AA15">
-        <v>-1.3110318379588601e-005</v>
+        <v>-1.2671064972245006e-005</v>
       </c>
       <c r="AB15">
-        <v>-2.4281067587399416e-005</v>
+        <v>-2.4162488725263066e-005</v>
       </c>
       <c r="AC15">
-        <v>-2.8567886472008493e-005</v>
+        <v>-2.8486464029892024e-005</v>
       </c>
       <c r="AD15">
-        <v>-1.2509042616985297e-005</v>
+        <v>-1.250484049025119e-005</v>
       </c>
       <c r="AE15">
-        <v>-4.0845350809355443e-006</v>
+        <v>-3.8001402494420716e-006</v>
       </c>
       <c r="AF15">
-        <v>-9.3581187959096117e-006</v>
+        <v>-8.7971455030878301e-006</v>
       </c>
       <c r="AG15">
-        <v>-1.3834551077644458e-005</v>
+        <v>-1.331075370210338e-005</v>
       </c>
       <c r="AH15">
-        <v>-2.0694718329690681e-006</v>
+        <v>-1.3586776894978852e-006</v>
       </c>
       <c r="AI15">
-        <v>-1.5272398554458695e-005</v>
+        <v>-1.4621600892997667e-005</v>
       </c>
       <c r="AJ15">
-        <v>3.3400301616756043e-006</v>
+        <v>3.3276879194391733e-006</v>
       </c>
       <c r="AK15">
-        <v>-9.7050752742837386e-006</v>
+        <v>-9.7216222889167215e-006</v>
       </c>
       <c r="AL15">
-        <v>4.4163868431970525e-006</v>
+        <v>5.3402235887112253e-006</v>
       </c>
       <c r="AM15">
-        <v>3.6774711517777067e-005</v>
+        <v>3.7515092635861082e-005</v>
       </c>
       <c r="AN15">
-        <v>4.5076519039024244e-005</v>
+        <v>4.5984874304310914e-005</v>
       </c>
       <c r="AO15">
-        <v>2.8601821417423093e-005</v>
+        <v>2.9574302848604144e-005</v>
       </c>
       <c r="AP15">
-        <v>-0.00030096416528898717</v>
+        <v>-0.00030275701991135681</v>
       </c>
     </row>
     <row r="16">
@@ -3716,127 +3716,127 @@
         <v>67</v>
       </c>
       <c r="B16" s="36">
-        <v>0.00372251918760027</v>
+        <v>0.0037342951915878679</v>
       </c>
       <c r="C16">
-        <v>-7.9265977010641107e-007</v>
+        <v>-7.9122885279238301e-007</v>
       </c>
       <c r="D16">
-        <v>5.6142942080625734e-008</v>
+        <v>5.4590076078477575e-008</v>
       </c>
       <c r="E16">
-        <v>-1.0925409364765469e-009</v>
+        <v>-1.0764623120365443e-009</v>
       </c>
       <c r="F16">
-        <v>-5.5838321333886147e-007</v>
+        <v>-5.5058632227619628e-007</v>
       </c>
       <c r="G16">
-        <v>-2.9807970842991415e-007</v>
+        <v>-2.9499764257746286e-007</v>
       </c>
       <c r="H16">
-        <v>4.2237091114157776e-009</v>
+        <v>2.0023432095653418e-009</v>
       </c>
       <c r="I16">
-        <v>2.696279328560067e-006</v>
+        <v>2.6891944035677689e-006</v>
       </c>
       <c r="J16">
-        <v>-3.4275391965291708e-007</v>
+        <v>-3.4470170825956998e-007</v>
       </c>
       <c r="K16">
-        <v>1.2547335394322806e-008</v>
+        <v>1.1676695370255133e-008</v>
       </c>
       <c r="L16">
-        <v>-5.670419834173295e-007</v>
+        <v>-5.6321510997912226e-007</v>
       </c>
       <c r="M16">
-        <v>-7.0875102470608846e-007</v>
+        <v>-7.792160210694949e-007</v>
       </c>
       <c r="N16">
-        <v>8.156752337244581e-007</v>
+        <v>8.2337651011318388e-007</v>
       </c>
       <c r="O16">
-        <v>-9.7862702356507444e-008</v>
+        <v>-9.8295315034315554e-008</v>
       </c>
       <c r="P16">
-        <v>-6.6076659076509757e-008</v>
+        <v>-6.6476113471090693e-008</v>
       </c>
       <c r="Q16">
-        <v>3.5936255995200683e-007</v>
+        <v>3.5927253610158535e-007</v>
       </c>
       <c r="R16">
-        <v>-2.8833756136964447e-008</v>
+        <v>-2.867005135114237e-008</v>
       </c>
       <c r="S16">
-        <v>-5.2042431647729156e-007</v>
+        <v>-5.2598949307882174e-007</v>
       </c>
       <c r="T16">
-        <v>-1.0958307681945516e-006</v>
+        <v>-1.0825931602771735e-006</v>
       </c>
       <c r="U16">
-        <v>-1.1760138840438414e-006</v>
+        <v>-1.1712422641789377e-006</v>
       </c>
       <c r="V16">
-        <v>-1.1727355541984473e-006</v>
+        <v>-1.1733982462881689e-006</v>
       </c>
       <c r="W16">
-        <v>-2.9863504660210231e-008</v>
+        <v>-3.205923162381904e-008</v>
       </c>
       <c r="X16">
-        <v>4.0267716829349919e-008</v>
+        <v>3.8186779376973193e-008</v>
       </c>
       <c r="Y16">
-        <v>3.428103489969262e-008</v>
+        <v>2.7301354714099359e-008</v>
       </c>
       <c r="Z16">
-        <v>2.7142791137503425e-007</v>
+        <v>2.3884675399935194e-007</v>
       </c>
       <c r="AA16">
-        <v>1.0056600360797459e-007</v>
+        <v>9.1312201297307484e-008</v>
       </c>
       <c r="AB16">
-        <v>1.4783080081378226e-007</v>
+        <v>1.3739573166310781e-007</v>
       </c>
       <c r="AC16">
-        <v>3.4125469372067987e-007</v>
+        <v>3.271082156917113e-007</v>
       </c>
       <c r="AD16">
-        <v>9.9910454301623885e-008</v>
+        <v>8.4030241226266078e-008</v>
       </c>
       <c r="AE16">
-        <v>2.9729811760800527e-007</v>
+        <v>2.8607903899948467e-007</v>
       </c>
       <c r="AF16">
-        <v>-6.5899152548758205e-007</v>
+        <v>-6.6611041472222661e-007</v>
       </c>
       <c r="AG16">
-        <v>4.0715617083411922e-007</v>
+        <v>3.9718023545358336e-007</v>
       </c>
       <c r="AH16">
-        <v>1.8863472025965174e-007</v>
+        <v>1.851345182332464e-007</v>
       </c>
       <c r="AI16">
-        <v>-1.0377709720595437e-007</v>
+        <v>-1.2156571249125704e-007</v>
       </c>
       <c r="AJ16">
-        <v>8.8780327392359743e-008</v>
+        <v>8.8811649832477704e-008</v>
       </c>
       <c r="AK16">
-        <v>3.614481897566153e-007</v>
+        <v>3.6270036049158591e-007</v>
       </c>
       <c r="AL16">
-        <v>1.0169556615659325e-006</v>
+        <v>9.7319857190046152e-007</v>
       </c>
       <c r="AM16">
-        <v>-3.390646337551449e-007</v>
+        <v>-3.4128546557224585e-007</v>
       </c>
       <c r="AN16">
-        <v>-4.0750625793255453e-007</v>
+        <v>-4.0217974034124324e-007</v>
       </c>
       <c r="AO16">
-        <v>3.3972148556573861e-007</v>
+        <v>4.0115930129169372e-007</v>
       </c>
       <c r="AP16">
-        <v>-1.6336716856193764e-005</v>
+        <v>-1.6299109273449739e-005</v>
       </c>
     </row>
     <row r="17">
@@ -3844,127 +3844,127 @@
         <v>68</v>
       </c>
       <c r="B17" s="38">
-        <v>0.0060895178284097549</v>
+        <v>0.006103055307191115</v>
       </c>
       <c r="C17">
-        <v>-1.4931568520218039e-007</v>
+        <v>-1.4508581854701788e-007</v>
       </c>
       <c r="D17">
-        <v>1.0915637919763319e-007</v>
+        <v>1.0922533180105159e-007</v>
       </c>
       <c r="E17">
-        <v>-5.5688122932826104e-010</v>
+        <v>-5.6057026211139028e-010</v>
       </c>
       <c r="F17">
-        <v>-5.9437942580910978e-007</v>
+        <v>-6.0560811041091787e-007</v>
       </c>
       <c r="G17">
-        <v>5.7264794826078726e-008</v>
+        <v>5.2347753403825357e-008</v>
       </c>
       <c r="H17">
-        <v>-2.8466623728319258e-007</v>
+        <v>-2.8846225345232835e-007</v>
       </c>
       <c r="I17">
-        <v>1.4352621743324586e-006</v>
+        <v>1.4166592043479909e-006</v>
       </c>
       <c r="J17">
-        <v>-6.0324258552092622e-008</v>
+        <v>-6.2508342962404145e-008</v>
       </c>
       <c r="K17">
-        <v>3.2315642246367455e-008</v>
+        <v>3.3303270018820401e-008</v>
       </c>
       <c r="L17">
-        <v>-7.0623293782404591e-007</v>
+        <v>-7.0757348551750777e-007</v>
       </c>
       <c r="M17">
-        <v>3.7314304019906389e-007</v>
+        <v>3.9532297634899744e-007</v>
       </c>
       <c r="N17">
-        <v>1.2307875417918197e-006</v>
+        <v>1.255829100044033e-006</v>
       </c>
       <c r="O17">
-        <v>5.7572141785585355e-008</v>
+        <v>6.1346329277247781e-008</v>
       </c>
       <c r="P17">
-        <v>3.9496679414350624e-007</v>
+        <v>4.003641169634019e-007</v>
       </c>
       <c r="Q17">
-        <v>-2.8833756136964447e-008</v>
+        <v>-2.867005135114237e-008</v>
       </c>
       <c r="R17">
-        <v>2.8252237668071115e-007</v>
+        <v>2.8226657720447399e-007</v>
       </c>
       <c r="S17">
-        <v>-2.7335567322553209e-007</v>
+        <v>-2.1895867477506432e-007</v>
       </c>
       <c r="T17">
-        <v>-7.767729796683029e-007</v>
+        <v>-7.4671701989833667e-007</v>
       </c>
       <c r="U17">
-        <v>-8.1622216340676549e-007</v>
+        <v>-7.7886127363475663e-007</v>
       </c>
       <c r="V17">
-        <v>-1.2041490917355223e-006</v>
+        <v>-1.1614251368051405e-006</v>
       </c>
       <c r="W17">
-        <v>-5.4969417477052686e-009</v>
+        <v>-6.9983156497303587e-009</v>
       </c>
       <c r="X17">
-        <v>-3.3647742418540231e-007</v>
+        <v>-3.2857460266172808e-007</v>
       </c>
       <c r="Y17">
-        <v>4.1436961178894384e-007</v>
+        <v>4.4569342735604967e-007</v>
       </c>
       <c r="Z17">
-        <v>1.0301390441543879e-007</v>
+        <v>1.4511416240333815e-007</v>
       </c>
       <c r="AA17">
-        <v>2.6023525017693039e-007</v>
+        <v>2.8860415989162376e-007</v>
       </c>
       <c r="AB17">
-        <v>5.9871213269350256e-008</v>
+        <v>8.3898352104654422e-008</v>
       </c>
       <c r="AC17">
-        <v>3.0548915709725381e-007</v>
+        <v>3.2981006691703227e-007</v>
       </c>
       <c r="AD17">
-        <v>7.3845466651597466e-008</v>
+        <v>9.9305010931922812e-008</v>
       </c>
       <c r="AE17">
-        <v>-1.6407157547322961e-007</v>
+        <v>-1.3568759272952403e-007</v>
       </c>
       <c r="AF17">
-        <v>2.0004168872908066e-007</v>
+        <v>2.2924426976157816e-007</v>
       </c>
       <c r="AG17">
-        <v>3.880281082973266e-007</v>
+        <v>4.1791486239983743e-007</v>
       </c>
       <c r="AH17">
-        <v>3.0285608289124195e-007</v>
+        <v>3.5091433062408159e-007</v>
       </c>
       <c r="AI17">
-        <v>5.0108727619009046e-007</v>
+        <v>5.2817943229680735e-007</v>
       </c>
       <c r="AJ17">
-        <v>2.6339732187769672e-008</v>
+        <v>2.7045074420720516e-008</v>
       </c>
       <c r="AK17">
-        <v>-2.0258889907359599e-007</v>
+        <v>-2.0534660222153853e-007</v>
       </c>
       <c r="AL17">
-        <v>-4.0625088754614468e-007</v>
+        <v>-3.8593377822984748e-007</v>
       </c>
       <c r="AM17">
-        <v>3.3960255120056272e-007</v>
+        <v>3.5098759074297303e-007</v>
       </c>
       <c r="AN17">
-        <v>-1.5489468733880459e-007</v>
+        <v>-1.33727861083134e-007</v>
       </c>
       <c r="AO17">
-        <v>-6.1532563276367186e-008</v>
+        <v>2.1600337069519834e-007</v>
       </c>
       <c r="AP17">
-        <v>-1.6496895911156737e-005</v>
+        <v>-1.6582194447138253e-005</v>
       </c>
     </row>
     <row r="18">
@@ -3972,127 +3972,127 @@
         <v>69</v>
       </c>
       <c r="B18" s="40">
-        <v>0.099529137692225184</v>
+        <v>0.09548203051726574</v>
       </c>
       <c r="C18">
-        <v>1.9620909277668945e-005</v>
+        <v>1.8517040194903296e-005</v>
       </c>
       <c r="D18">
-        <v>3.5934808847278038e-006</v>
+        <v>3.6103131531151699e-006</v>
       </c>
       <c r="E18">
-        <v>-3.580592592226856e-008</v>
+        <v>-3.5893692030047936e-008</v>
       </c>
       <c r="F18">
-        <v>2.7722303480930439e-006</v>
+        <v>2.7170379921644694e-006</v>
       </c>
       <c r="G18">
-        <v>1.8392438289674105e-005</v>
+        <v>1.8950085924134927e-005</v>
       </c>
       <c r="H18">
-        <v>-9.2607492832469925e-006</v>
+        <v>-1.0102568834723701e-005</v>
       </c>
       <c r="I18">
-        <v>4.1093010093961943e-005</v>
+        <v>4.1418122986522647e-005</v>
       </c>
       <c r="J18">
-        <v>4.1912547883222272e-005</v>
+        <v>4.2767062229907729e-005</v>
       </c>
       <c r="K18">
-        <v>6.7184468557612536e-005</v>
+        <v>6.8387450532203417e-005</v>
       </c>
       <c r="L18">
-        <v>7.6051471368019643e-005</v>
+        <v>7.6302908815065401e-005</v>
       </c>
       <c r="M18">
-        <v>9.5815670829886191e-005</v>
+        <v>0.00010307176721410661</v>
       </c>
       <c r="N18">
-        <v>0.0001360891813695357</v>
+        <v>0.00013790270270277091</v>
       </c>
       <c r="O18">
-        <v>2.851013865709762e-007</v>
+        <v>1.3690693698542991e-006</v>
       </c>
       <c r="P18">
-        <v>8.133510951057365e-006</v>
+        <v>9.2128983869631893e-006</v>
       </c>
       <c r="Q18">
-        <v>-5.2042431647729156e-007</v>
+        <v>-5.2598949307882174e-007</v>
       </c>
       <c r="R18">
-        <v>-2.7335567322553209e-007</v>
+        <v>-2.1895867477506432e-007</v>
       </c>
       <c r="S18">
-        <v>0.00040096510085534099</v>
+        <v>0.00040185666832858537</v>
       </c>
       <c r="T18">
-        <v>0.00030589993264633597</v>
+        <v>0.00030771443369179228</v>
       </c>
       <c r="U18">
-        <v>0.00032264459062033364</v>
+        <v>0.00032556629053213666</v>
       </c>
       <c r="V18">
-        <v>0.00032882828808612974</v>
+        <v>0.00033122907454765467</v>
       </c>
       <c r="W18">
-        <v>-2.4792231901464631e-005</v>
+        <v>-2.5095272502010746e-005</v>
       </c>
       <c r="X18">
-        <v>-1.1605128746738092e-005</v>
+        <v>-1.2032481918827404e-005</v>
       </c>
       <c r="Y18">
-        <v>-4.6315749790859804e-006</v>
+        <v>-3.2561068352511804e-006</v>
       </c>
       <c r="Z18">
-        <v>2.0766340865740816e-006</v>
+        <v>2.899225290356009e-006</v>
       </c>
       <c r="AA18">
-        <v>1.0340977553892552e-005</v>
+        <v>1.0840861546772208e-005</v>
       </c>
       <c r="AB18">
-        <v>2.3307189381639045e-006</v>
+        <v>1.7386163363412193e-006</v>
       </c>
       <c r="AC18">
-        <v>-1.3961820098732119e-006</v>
+        <v>-1.9949260242942716e-006</v>
       </c>
       <c r="AD18">
-        <v>-8.9154048316052487e-006</v>
+        <v>-9.1976914471293708e-006</v>
       </c>
       <c r="AE18">
-        <v>5.5937955216764057e-006</v>
+        <v>5.4551772439592195e-006</v>
       </c>
       <c r="AF18">
-        <v>-1.0361466602570815e-005</v>
+        <v>-1.3251212198937637e-005</v>
       </c>
       <c r="AG18">
-        <v>-1.5715861166098793e-006</v>
+        <v>-1.5048776979311167e-006</v>
       </c>
       <c r="AH18">
-        <v>8.0771035405797939e-006</v>
+        <v>7.0571094583996572e-006</v>
       </c>
       <c r="AI18">
-        <v>1.9868658902414787e-005</v>
+        <v>2.7417248489577668e-005</v>
       </c>
       <c r="AJ18">
-        <v>1.0781382630756852e-006</v>
+        <v>1.1528453879263243e-006</v>
       </c>
       <c r="AK18">
-        <v>-4.1539001194528258e-006</v>
+        <v>-6.2585370296515054e-006</v>
       </c>
       <c r="AL18">
-        <v>-6.1262494044641986e-006</v>
+        <v>-5.9751198377596357e-006</v>
       </c>
       <c r="AM18">
-        <v>-8.5635818259003986e-006</v>
+        <v>-3.6858901044361917e-006</v>
       </c>
       <c r="AN18">
-        <v>1.2566739689128892e-005</v>
+        <v>1.2118155934761883e-005</v>
       </c>
       <c r="AO18">
-        <v>1.9129736764673521e-005</v>
+        <v>-3.5281111989815929e-006</v>
       </c>
       <c r="AP18">
-        <v>-0.00040000989191455924</v>
+        <v>-0.00040633742823793686</v>
       </c>
     </row>
     <row r="19">
@@ -4100,127 +4100,127 @@
         <v>70</v>
       </c>
       <c r="B19" s="42">
-        <v>0.24122009746309167</v>
+        <v>0.23812370280937262</v>
       </c>
       <c r="C19">
-        <v>2.2175154144066791e-005</v>
+        <v>2.1433944777983996e-005</v>
       </c>
       <c r="D19">
-        <v>1.3716741803894554e-006</v>
+        <v>1.4551711867713814e-006</v>
       </c>
       <c r="E19">
-        <v>-4.4446021929114063e-009</v>
+        <v>-5.2720622825016038e-009</v>
       </c>
       <c r="F19">
-        <v>2.9511611410567001e-005</v>
+        <v>2.9826609188360979e-005</v>
       </c>
       <c r="G19">
-        <v>5.8358305603613121e-005</v>
+        <v>5.8530869337245091e-005</v>
       </c>
       <c r="H19">
-        <v>8.8457661546461488e-006</v>
+        <v>8.2453657084472694e-006</v>
       </c>
       <c r="I19">
-        <v>0.00014787054683602363</v>
+        <v>0.00014758614517680792</v>
       </c>
       <c r="J19">
-        <v>0.0001120718134668072</v>
+        <v>0.0001129196600014647</v>
       </c>
       <c r="K19">
-        <v>0.00011947447483409316</v>
+        <v>0.00012041243653630528</v>
       </c>
       <c r="L19">
-        <v>0.00017452638012326624</v>
+        <v>0.00017469733004463685</v>
       </c>
       <c r="M19">
-        <v>0.00018540704599922673</v>
+        <v>0.0001932237816865148</v>
       </c>
       <c r="N19">
-        <v>0.00020571394287485412</v>
+        <v>0.00020774809159567731</v>
       </c>
       <c r="O19">
-        <v>7.3570984253988305e-007</v>
+        <v>1.4269608064544641e-006</v>
       </c>
       <c r="P19">
-        <v>2.4846686593792778e-005</v>
+        <v>2.5559094647406842e-005</v>
       </c>
       <c r="Q19">
-        <v>-1.0958307681945516e-006</v>
+        <v>-1.0825931602771735e-006</v>
       </c>
       <c r="R19">
-        <v>-7.767729796683029e-007</v>
+        <v>-7.4671701989833667e-007</v>
       </c>
       <c r="S19">
-        <v>0.00030589993264633597</v>
+        <v>0.00030771443369179228</v>
       </c>
       <c r="T19">
-        <v>0.0005264211270744856</v>
+        <v>0.00052799135671550035</v>
       </c>
       <c r="U19">
-        <v>0.00043709327318512263</v>
+        <v>0.0004400119656656448</v>
       </c>
       <c r="V19">
-        <v>0.00045368471936803952</v>
+        <v>0.00045636442224928584</v>
       </c>
       <c r="W19">
-        <v>-2.9216253747930084e-005</v>
+        <v>-2.9410909104666077e-005</v>
       </c>
       <c r="X19">
-        <v>-1.0543669690186834e-005</v>
+        <v>-1.0538528787935923e-005</v>
       </c>
       <c r="Y19">
-        <v>-4.0939235602434015e-006</v>
+        <v>-1.8795332704783129e-006</v>
       </c>
       <c r="Z19">
-        <v>1.1544314586702855e-005</v>
+        <v>1.4244530379494138e-005</v>
       </c>
       <c r="AA19">
-        <v>9.3678731038892737e-006</v>
+        <v>1.0872737543094611e-005</v>
       </c>
       <c r="AB19">
-        <v>1.9914427500938796e-006</v>
+        <v>2.7286354398773304e-006</v>
       </c>
       <c r="AC19">
-        <v>-1.9383576020664117e-006</v>
+        <v>-1.2418314718855755e-006</v>
       </c>
       <c r="AD19">
-        <v>3.0988616345041325e-006</v>
+        <v>4.0950163762586058e-006</v>
       </c>
       <c r="AE19">
-        <v>1.2015757528881497e-005</v>
+        <v>1.3099714561265875e-005</v>
       </c>
       <c r="AF19">
-        <v>1.0021102760084163e-005</v>
+        <v>8.9946878505244559e-006</v>
       </c>
       <c r="AG19">
-        <v>-3.2158280506280814e-006</v>
+        <v>-1.95771093791197e-006</v>
       </c>
       <c r="AH19">
-        <v>8.3259954449161453e-006</v>
+        <v>8.8776686013738402e-006</v>
       </c>
       <c r="AI19">
-        <v>2.9352020112786802e-005</v>
+        <v>3.6235179673801195e-005</v>
       </c>
       <c r="AJ19">
-        <v>3.8870533986602547e-006</v>
+        <v>3.898773416640877e-006</v>
       </c>
       <c r="AK19">
-        <v>-2.453689849552391e-005</v>
+        <v>-2.5827058157672748e-005</v>
       </c>
       <c r="AL19">
-        <v>-3.5539846582901681e-005</v>
+        <v>-3.3329339649620785e-005</v>
       </c>
       <c r="AM19">
-        <v>7.5647183695575762e-006</v>
+        <v>1.1509599744098149e-005</v>
       </c>
       <c r="AN19">
-        <v>-5.0209511119663148e-007</v>
+        <v>-3.2634341447452045e-007</v>
       </c>
       <c r="AO19">
-        <v>2.3044683965337172e-005</v>
+        <v>-4.7042788227017037e-007</v>
       </c>
       <c r="AP19">
-        <v>-0.0005143387036634008</v>
+        <v>-0.00052252182929615006</v>
       </c>
     </row>
     <row r="20">
@@ -4228,127 +4228,127 @@
         <v>71</v>
       </c>
       <c r="B20" s="44">
-        <v>0.32143717720466647</v>
+        <v>0.31821438760022502</v>
       </c>
       <c r="C20">
-        <v>1.6592854556798046e-005</v>
+        <v>1.6068467230108948e-005</v>
       </c>
       <c r="D20">
-        <v>-1.31478285521038e-006</v>
+        <v>-1.2574434854135148e-006</v>
       </c>
       <c r="E20">
-        <v>1.9109911531895145e-008</v>
+        <v>1.8621702660303102e-008</v>
       </c>
       <c r="F20">
-        <v>7.6728706811351202e-005</v>
+        <v>7.70678711128843e-005</v>
       </c>
       <c r="G20">
-        <v>0.00011518045302010784</v>
+        <v>0.00011563980312241502</v>
       </c>
       <c r="H20">
-        <v>2.7564184041252638e-005</v>
+        <v>2.7065321088778022e-005</v>
       </c>
       <c r="I20">
-        <v>0.0002507147532820527</v>
+        <v>0.00025053085647868317</v>
       </c>
       <c r="J20">
-        <v>0.0002043361906818934</v>
+        <v>0.00020556065281434439</v>
       </c>
       <c r="K20">
-        <v>0.00016636497827888017</v>
+        <v>0.00016761802192012169</v>
       </c>
       <c r="L20">
-        <v>0.00024675337150902889</v>
+        <v>0.00024746977414980567</v>
       </c>
       <c r="M20">
-        <v>0.00021046038352228084</v>
+        <v>0.00021688371710355036</v>
       </c>
       <c r="N20">
-        <v>0.00025995364733303467</v>
+        <v>0.00026263938306234996</v>
       </c>
       <c r="O20">
-        <v>2.4732574423195445e-005</v>
+        <v>2.5153322922716651e-005</v>
       </c>
       <c r="P20">
-        <v>5.1802765716279469e-005</v>
+        <v>5.2233553827668492e-005</v>
       </c>
       <c r="Q20">
-        <v>-1.1760138840438414e-006</v>
+        <v>-1.1712422641789377e-006</v>
       </c>
       <c r="R20">
-        <v>-8.1622216340676549e-007</v>
+        <v>-7.7886127363475663e-007</v>
       </c>
       <c r="S20">
-        <v>0.00032264459062033364</v>
+        <v>0.00032556629053213666</v>
       </c>
       <c r="T20">
-        <v>0.00043709327318512263</v>
+        <v>0.0004400119656656448</v>
       </c>
       <c r="U20">
-        <v>0.0006732497667942905</v>
+        <v>0.00067759445890464324</v>
       </c>
       <c r="V20">
-        <v>0.00054605477470339022</v>
+        <v>0.00054987335656083553</v>
       </c>
       <c r="W20">
-        <v>-2.9001407529376628e-005</v>
+        <v>-2.9371138479431058e-005</v>
       </c>
       <c r="X20">
-        <v>-1.4279888038792936e-005</v>
+        <v>-1.464784732334545e-005</v>
       </c>
       <c r="Y20">
-        <v>1.3030607852441974e-005</v>
+        <v>1.4870557603471986e-005</v>
       </c>
       <c r="Z20">
-        <v>1.623968613156718e-005</v>
+        <v>1.766160395356906e-005</v>
       </c>
       <c r="AA20">
-        <v>2.8254825304506923e-005</v>
+        <v>2.937978597661065e-005</v>
       </c>
       <c r="AB20">
-        <v>2.9526301226812782e-005</v>
+        <v>2.997059363949753e-005</v>
       </c>
       <c r="AC20">
-        <v>1.2161752464588516e-005</v>
+        <v>1.2407403429402096e-005</v>
       </c>
       <c r="AD20">
-        <v>8.3433551084079546e-006</v>
+        <v>8.809168058777225e-006</v>
       </c>
       <c r="AE20">
-        <v>2.7084674129769883e-005</v>
+        <v>2.7888939973105619e-005</v>
       </c>
       <c r="AF20">
-        <v>2.2476478035253115e-005</v>
+        <v>2.1141536129607207e-005</v>
       </c>
       <c r="AG20">
-        <v>1.0994834736257611e-005</v>
+        <v>1.189095595902564e-005</v>
       </c>
       <c r="AH20">
-        <v>1.4427003791448034e-005</v>
+        <v>1.4447385807352122e-005</v>
       </c>
       <c r="AI20">
-        <v>4.640772163793782e-005</v>
+        <v>5.3166163607128929e-005</v>
       </c>
       <c r="AJ20">
-        <v>3.4340576258321317e-006</v>
+        <v>3.4403792303629252e-006</v>
       </c>
       <c r="AK20">
-        <v>-1.5781975891541595e-005</v>
+        <v>-1.7087252851770545e-005</v>
       </c>
       <c r="AL20">
-        <v>-2.5652903721933833e-005</v>
+        <v>-2.5377564072426325e-005</v>
       </c>
       <c r="AM20">
-        <v>2.6541540425249272e-005</v>
+        <v>3.051718150137985e-005</v>
       </c>
       <c r="AN20">
-        <v>1.4539504964501682e-005</v>
+        <v>1.4538127790085346e-005</v>
       </c>
       <c r="AO20">
-        <v>3.6210550104679617e-005</v>
+        <v>5.734976349723803e-006</v>
       </c>
       <c r="AP20">
-        <v>-0.00057572721070874185</v>
+        <v>-0.00058379962659959412</v>
       </c>
     </row>
     <row r="21">
@@ -4356,127 +4356,127 @@
         <v>72</v>
       </c>
       <c r="B21" s="46">
-        <v>0.53791370254260007</v>
+        <v>0.53555154239486202</v>
       </c>
       <c r="C21">
-        <v>1.0049288962354983e-005</v>
+        <v>9.4897033567696436e-006</v>
       </c>
       <c r="D21">
-        <v>-2.5347661302334453e-006</v>
+        <v>-2.4769981294328631e-006</v>
       </c>
       <c r="E21">
-        <v>2.6916196714440763e-008</v>
+        <v>2.6504998988733146e-008</v>
       </c>
       <c r="F21">
-        <v>0.00013283391238320177</v>
+        <v>0.00013332323715633406</v>
       </c>
       <c r="G21">
-        <v>0.0001657512579764472</v>
+        <v>0.0001662234845230217</v>
       </c>
       <c r="H21">
-        <v>7.6385826322791518e-005</v>
+        <v>7.5877653170086667e-005</v>
       </c>
       <c r="I21">
-        <v>0.00021893612132088442</v>
+        <v>0.00021858548226335223</v>
       </c>
       <c r="J21">
-        <v>0.00024547576578353944</v>
+        <v>0.00024647651390258501</v>
       </c>
       <c r="K21">
-        <v>0.0002123554084251221</v>
+        <v>0.00021345802077399919</v>
       </c>
       <c r="L21">
-        <v>0.00030066781119384903</v>
+        <v>0.00030137075645459224</v>
       </c>
       <c r="M21">
-        <v>0.00020322052112371473</v>
+        <v>0.00020884502243644868</v>
       </c>
       <c r="N21">
-        <v>0.00027467588170429838</v>
+        <v>0.00027693469497704537</v>
       </c>
       <c r="O21">
-        <v>8.4833688734686246e-005</v>
+        <v>8.5420730546135554e-005</v>
       </c>
       <c r="P21">
-        <v>0.00011691206360954677</v>
+        <v>0.00011762702812629271</v>
       </c>
       <c r="Q21">
-        <v>-1.1727355541984473e-006</v>
+        <v>-1.1733982462881689e-006</v>
       </c>
       <c r="R21">
-        <v>-1.2041490917355223e-006</v>
+        <v>-1.1614251368051405e-006</v>
       </c>
       <c r="S21">
-        <v>0.00032882828808612974</v>
+        <v>0.00033122907454765467</v>
       </c>
       <c r="T21">
-        <v>0.00045368471936803952</v>
+        <v>0.00045636442224928584</v>
       </c>
       <c r="U21">
-        <v>0.00054605477470339022</v>
+        <v>0.00054987335656083553</v>
       </c>
       <c r="V21">
-        <v>0.00084712690947445627</v>
+        <v>0.00085112955281346737</v>
       </c>
       <c r="W21">
-        <v>-2.9305704547853874e-005</v>
+        <v>-2.9639085650494169e-005</v>
       </c>
       <c r="X21">
-        <v>8.2728722139370665e-007</v>
+        <v>7.8410571608951256e-007</v>
       </c>
       <c r="Y21">
-        <v>2.886184993310894e-005</v>
+        <v>3.1023231326233997e-005</v>
       </c>
       <c r="Z21">
-        <v>4.6399431227649896e-005</v>
+        <v>4.8074468398031977e-005</v>
       </c>
       <c r="AA21">
-        <v>5.7954047435246291e-005</v>
+        <v>5.9364707723022143e-005</v>
       </c>
       <c r="AB21">
-        <v>4.8229253760445737e-005</v>
+        <v>4.8723632054761381e-005</v>
       </c>
       <c r="AC21">
-        <v>3.4338737828916849e-005</v>
+        <v>3.4821358251136409e-005</v>
       </c>
       <c r="AD21">
-        <v>3.604547052909147e-005</v>
+        <v>3.6732859571079015e-005</v>
       </c>
       <c r="AE21">
-        <v>3.5358719955556112e-005</v>
+        <v>3.6004040631678194e-005</v>
       </c>
       <c r="AF21">
-        <v>4.3446583363528149e-005</v>
+        <v>4.2379327541817049e-005</v>
       </c>
       <c r="AG21">
-        <v>3.6299659146507882e-005</v>
+        <v>3.7447481340722538e-005</v>
       </c>
       <c r="AH21">
-        <v>3.4519637656894625e-005</v>
+        <v>3.4782637836399515e-005</v>
       </c>
       <c r="AI21">
-        <v>6.9940231673709132e-005</v>
+        <v>7.7002239468184925e-005</v>
       </c>
       <c r="AJ21">
-        <v>2.4140240848483541e-006</v>
+        <v>2.4276581866449845e-006</v>
       </c>
       <c r="AK21">
-        <v>-1.892728249796603e-005</v>
+        <v>-2.0360900594176093e-005</v>
       </c>
       <c r="AL21">
-        <v>-7.4461145913201461e-006</v>
+        <v>-7.2224181939856625e-006</v>
       </c>
       <c r="AM21">
-        <v>3.3008446136949601e-005</v>
+        <v>3.7475255665174771e-005</v>
       </c>
       <c r="AN21">
-        <v>4.4114818463522588e-005</v>
+        <v>4.4510376989898438e-005</v>
       </c>
       <c r="AO21">
-        <v>3.6743182181446521e-005</v>
+        <v>1.7346720579089567e-005</v>
       </c>
       <c r="AP21">
-        <v>-0.00064791243872289531</v>
+        <v>-0.0006565445349873873</v>
       </c>
     </row>
     <row r="22">
@@ -4484,127 +4484,127 @@
         <v>73</v>
       </c>
       <c r="B22" s="48">
-        <v>0.021492339368418024</v>
+        <v>0.021669143260047045</v>
       </c>
       <c r="C22">
-        <v>-2.9421948849392486e-006</v>
+        <v>-2.9612353110644452e-006</v>
       </c>
       <c r="D22">
-        <v>-1.6247231660567237e-007</v>
+        <v>-1.8035534091487149e-007</v>
       </c>
       <c r="E22">
-        <v>-2.6311411916055669e-009</v>
+        <v>-2.4839963851293024e-009</v>
       </c>
       <c r="F22">
-        <v>-4.203353510195394e-006</v>
+        <v>-4.263824246065079e-006</v>
       </c>
       <c r="G22">
-        <v>-5.2105654287807544e-006</v>
+        <v>-5.2182925460248235e-006</v>
       </c>
       <c r="H22">
-        <v>3.0680730509382997e-007</v>
+        <v>3.1052046240621893e-007</v>
       </c>
       <c r="I22">
-        <v>-8.3098323201029026e-006</v>
+        <v>-8.4119925083352442e-006</v>
       </c>
       <c r="J22">
-        <v>-5.3972373367138426e-006</v>
+        <v>-5.4823981271316339e-006</v>
       </c>
       <c r="K22">
-        <v>-9.4732077564624537e-006</v>
+        <v>-9.5739518070309484e-006</v>
       </c>
       <c r="L22">
-        <v>-1.6829613603013239e-005</v>
+        <v>-1.6963120946405926e-005</v>
       </c>
       <c r="M22">
-        <v>-1.3373376294594187e-005</v>
+        <v>-1.4026290268421811e-005</v>
       </c>
       <c r="N22">
-        <v>-1.7753650728944329e-005</v>
+        <v>-1.7968863313020506e-005</v>
       </c>
       <c r="O22">
-        <v>3.7262527219901041e-007</v>
+        <v>4.0568246932824329e-007</v>
       </c>
       <c r="P22">
-        <v>4.411048027073517e-006</v>
+        <v>4.4440610284290586e-006</v>
       </c>
       <c r="Q22">
-        <v>-2.9863504660210231e-008</v>
+        <v>-3.205923162381904e-008</v>
       </c>
       <c r="R22">
-        <v>-5.4969417477052686e-009</v>
+        <v>-6.9983156497303587e-009</v>
       </c>
       <c r="S22">
-        <v>-2.4792231901464631e-005</v>
+        <v>-2.5095272502010746e-005</v>
       </c>
       <c r="T22">
-        <v>-2.9216253747930084e-005</v>
+        <v>-2.9410909104666077e-005</v>
       </c>
       <c r="U22">
-        <v>-2.9001407529376628e-005</v>
+        <v>-2.9371138479431058e-005</v>
       </c>
       <c r="V22">
-        <v>-2.9305704547853874e-005</v>
+        <v>-2.9639085650494169e-005</v>
       </c>
       <c r="W22">
-        <v>7.7261376590459057e-006</v>
+        <v>7.7653498517311687e-006</v>
       </c>
       <c r="X22">
-        <v>-2.668998056089716e-006</v>
+        <v>-2.6894210815556517e-006</v>
       </c>
       <c r="Y22">
-        <v>1.4888535220118559e-006</v>
+        <v>1.1355242538379267e-006</v>
       </c>
       <c r="Z22">
-        <v>-1.5489603637526777e-006</v>
+        <v>-1.8826600193779879e-006</v>
       </c>
       <c r="AA22">
-        <v>-4.4612740530288802e-007</v>
+        <v>-7.5788881006784378e-007</v>
       </c>
       <c r="AB22">
-        <v>-3.485075958210293e-007</v>
+        <v>-6.137546330418299e-007</v>
       </c>
       <c r="AC22">
-        <v>9.1642006762451959e-007</v>
+        <v>6.5014907536189881e-007</v>
       </c>
       <c r="AD22">
-        <v>7.2946889298919958e-007</v>
+        <v>4.5291626340997131e-007</v>
       </c>
       <c r="AE22">
-        <v>-1.2159317591094743e-006</v>
+        <v>-1.4928615463157652e-006</v>
       </c>
       <c r="AF22">
-        <v>-1.1151932679304955e-007</v>
+        <v>-2.3646893069891942e-007</v>
       </c>
       <c r="AG22">
-        <v>2.4110246817791097e-007</v>
+        <v>-5.0030198543926451e-008</v>
       </c>
       <c r="AH22">
-        <v>3.8795294290065279e-007</v>
+        <v>1.7649093124842476e-007</v>
       </c>
       <c r="AI22">
-        <v>1.4606317956095557e-006</v>
+        <v>7.7853611095448686e-007</v>
       </c>
       <c r="AJ22">
-        <v>-1.9805172918899198e-007</v>
+        <v>-1.9256891780659461e-007</v>
       </c>
       <c r="AK22">
-        <v>1.1820313664072877e-006</v>
+        <v>1.2163977789425356e-006</v>
       </c>
       <c r="AL22">
-        <v>9.4560513080594134e-007</v>
+        <v>8.626441418769431e-007</v>
       </c>
       <c r="AM22">
-        <v>2.7048530090106043e-006</v>
+        <v>2.3578612931584824e-006</v>
       </c>
       <c r="AN22">
-        <v>3.0858681107736029e-006</v>
+        <v>2.9739608570318895e-006</v>
       </c>
       <c r="AO22">
-        <v>1.0200549164567093e-006</v>
+        <v>1.6469883503758496e-006</v>
       </c>
       <c r="AP22">
-        <v>4.684048526878996e-005</v>
+        <v>4.8008945201309005e-005</v>
       </c>
     </row>
     <row r="23">
@@ -4612,127 +4612,127 @@
         <v>74</v>
       </c>
       <c r="B23" s="50">
-        <v>3.705958150579427</v>
+        <v>3.7061275144406536</v>
       </c>
       <c r="C23">
-        <v>-2.2842023136516973e-006</v>
+        <v>-2.3093899068929268e-006</v>
       </c>
       <c r="D23">
-        <v>-1.180284803827605e-006</v>
+        <v>-1.1888137516625635e-006</v>
       </c>
       <c r="E23">
-        <v>5.7090765797892343e-009</v>
+        <v>5.9060951476975856e-009</v>
       </c>
       <c r="F23">
-        <v>4.0473386521211674e-005</v>
+        <v>4.1029776062692343e-005</v>
       </c>
       <c r="G23">
-        <v>-2.0211833156885605e-005</v>
+        <v>-2.0247012625917806e-005</v>
       </c>
       <c r="H23">
-        <v>-1.2421676964028212e-005</v>
+        <v>-1.2473712730409556e-005</v>
       </c>
       <c r="I23">
-        <v>7.2808668529554874e-005</v>
+        <v>7.2405098850131526e-005</v>
       </c>
       <c r="J23">
-        <v>-2.4202544910332347e-006</v>
+        <v>-2.5315281471237523e-006</v>
       </c>
       <c r="K23">
-        <v>-1.6421125710056077e-005</v>
+        <v>-1.6651496044337564e-005</v>
       </c>
       <c r="L23">
-        <v>1.4372310015921589e-005</v>
+        <v>1.4397572078518541e-005</v>
       </c>
       <c r="M23">
-        <v>-5.0252868797408614e-005</v>
+        <v>-5.1518649262629734e-005</v>
       </c>
       <c r="N23">
-        <v>6.0877632959140213e-006</v>
+        <v>6.0459290916063712e-006</v>
       </c>
       <c r="O23">
-        <v>-3.2869979142680197e-006</v>
+        <v>-3.2259668890518322e-006</v>
       </c>
       <c r="P23">
-        <v>9.7121132376103535e-006</v>
+        <v>9.8124145438962127e-006</v>
       </c>
       <c r="Q23">
-        <v>4.0267716829349919e-008</v>
+        <v>3.8186779376973193e-008</v>
       </c>
       <c r="R23">
-        <v>-3.3647742418540231e-007</v>
+        <v>-3.2857460266172808e-007</v>
       </c>
       <c r="S23">
-        <v>-1.1605128746738092e-005</v>
+        <v>-1.2032481918827404e-005</v>
       </c>
       <c r="T23">
-        <v>-1.0543669690186834e-005</v>
+        <v>-1.0538528787935923e-005</v>
       </c>
       <c r="U23">
-        <v>-1.4279888038792936e-005</v>
+        <v>-1.464784732334545e-005</v>
       </c>
       <c r="V23">
-        <v>8.2728722139370665e-007</v>
+        <v>7.8410571608951256e-007</v>
       </c>
       <c r="W23">
-        <v>-2.668998056089716e-006</v>
+        <v>-2.6894210815556517e-006</v>
       </c>
       <c r="X23">
-        <v>0.00020561739664233983</v>
+        <v>0.00020570457684010218</v>
       </c>
       <c r="Y23">
-        <v>-2.2867987785191955e-006</v>
+        <v>-1.7872018947315484e-006</v>
       </c>
       <c r="Z23">
-        <v>1.789870725228189e-006</v>
+        <v>1.7334429676801036e-006</v>
       </c>
       <c r="AA23">
-        <v>-8.7577623939628949e-008</v>
+        <v>1.7362752875604237e-007</v>
       </c>
       <c r="AB23">
-        <v>-4.7645105196437709e-006</v>
+        <v>-4.5683719134744386e-006</v>
       </c>
       <c r="AC23">
-        <v>-5.6357700920241547e-006</v>
+        <v>-5.4678833453257653e-006</v>
       </c>
       <c r="AD23">
-        <v>-2.4586011288120601e-006</v>
+        <v>-2.3477769551760043e-006</v>
       </c>
       <c r="AE23">
-        <v>-4.2380767751072567e-006</v>
+        <v>-3.9220038693309191e-006</v>
       </c>
       <c r="AF23">
-        <v>-2.003884588100043e-006</v>
+        <v>-1.5254192525200594e-006</v>
       </c>
       <c r="AG23">
-        <v>-4.4109991980257757e-006</v>
+        <v>-3.9537666154028055e-006</v>
       </c>
       <c r="AH23">
-        <v>-1.3249791183103383e-006</v>
+        <v>-9.425154959165183e-007</v>
       </c>
       <c r="AI23">
-        <v>-5.6476806196630551e-007</v>
+        <v>-4.6636457997242499e-008</v>
       </c>
       <c r="AJ23">
-        <v>5.867587182230277e-007</v>
+        <v>5.5388452563067605e-007</v>
       </c>
       <c r="AK23">
-        <v>-2.5243743447481076e-006</v>
+        <v>-2.3213266837219249e-006</v>
       </c>
       <c r="AL23">
-        <v>9.4258886698602917e-006</v>
+        <v>8.8322516702161742e-006</v>
       </c>
       <c r="AM23">
-        <v>6.4065876926698307e-006</v>
+        <v>6.9741712220176412e-006</v>
       </c>
       <c r="AN23">
-        <v>1.8766039443364292e-005</v>
+        <v>1.9422655464468162e-005</v>
       </c>
       <c r="AO23">
-        <v>2.1591863735965641e-005</v>
+        <v>2.1788446848683624e-005</v>
       </c>
       <c r="AP23">
-        <v>-4.6217836040980188e-005</v>
+        <v>-4.6351308374785374e-005</v>
       </c>
     </row>
     <row r="24">
@@ -4740,127 +4740,127 @@
         <v>75</v>
       </c>
       <c r="B24" s="52">
-        <v>0.088427427065400785</v>
+        <v>0.087092155368049082</v>
       </c>
       <c r="C24">
-        <v>-2.6122384814050417e-006</v>
+        <v>-2.5636235374156192e-006</v>
       </c>
       <c r="D24">
-        <v>-1.4122943374937161e-006</v>
+        <v>-1.4768776949171715e-006</v>
       </c>
       <c r="E24">
-        <v>1.5813547066086433e-008</v>
+        <v>1.6840048501916334e-008</v>
       </c>
       <c r="F24">
-        <v>2.3235038603243649e-005</v>
+        <v>2.5410318695237994e-005</v>
       </c>
       <c r="G24">
-        <v>1.725544364771434e-005</v>
+        <v>1.6821231397551189e-005</v>
       </c>
       <c r="H24">
-        <v>1.2959913391713698e-005</v>
+        <v>1.2223847002923946e-005</v>
       </c>
       <c r="I24">
-        <v>-1.2985696311704929e-005</v>
+        <v>-1.8518886521473684e-005</v>
       </c>
       <c r="J24">
-        <v>9.1969494140900446e-006</v>
+        <v>9.0658135587639245e-006</v>
       </c>
       <c r="K24">
-        <v>1.8178706591986267e-005</v>
+        <v>1.7339343582152344e-005</v>
       </c>
       <c r="L24">
-        <v>2.7579096414877379e-005</v>
+        <v>2.8056679495844849e-005</v>
       </c>
       <c r="M24">
-        <v>1.5205075871124502e-006</v>
+        <v>-4.6377892871179803e-006</v>
       </c>
       <c r="N24">
-        <v>-2.1869329764075655e-007</v>
+        <v>1.881929502629106e-006</v>
       </c>
       <c r="O24">
-        <v>-1.1150416219495254e-005</v>
+        <v>-1.0961921392815153e-005</v>
       </c>
       <c r="P24">
-        <v>-1.4851877609190432e-005</v>
+        <v>-1.4252319274319722e-005</v>
       </c>
       <c r="Q24">
-        <v>3.428103489969262e-008</v>
+        <v>2.7301354714099359e-008</v>
       </c>
       <c r="R24">
-        <v>4.1436961178894384e-007</v>
+        <v>4.4569342735604967e-007</v>
       </c>
       <c r="S24">
-        <v>-4.6315749790859804e-006</v>
+        <v>-3.2561068352511804e-006</v>
       </c>
       <c r="T24">
-        <v>-4.0939235602434015e-006</v>
+        <v>-1.8795332704783129e-006</v>
       </c>
       <c r="U24">
-        <v>1.3030607852441974e-005</v>
+        <v>1.4870557603471986e-005</v>
       </c>
       <c r="V24">
-        <v>2.886184993310894e-005</v>
+        <v>3.1023231326233997e-005</v>
       </c>
       <c r="W24">
-        <v>1.4888535220118559e-006</v>
+        <v>1.1355242538379267e-006</v>
       </c>
       <c r="X24">
-        <v>-2.2867987785191955e-006</v>
+        <v>-1.7872018947315484e-006</v>
       </c>
       <c r="Y24">
-        <v>0.0010423991372237511</v>
+        <v>0.0010465824973344689</v>
       </c>
       <c r="Z24">
-        <v>0.00040408184651562006</v>
+        <v>0.00040544062598465064</v>
       </c>
       <c r="AA24">
-        <v>0.00040148424618977768</v>
+        <v>0.00040436692858937908</v>
       </c>
       <c r="AB24">
-        <v>0.00040231259971754531</v>
+        <v>0.00040492880164712963</v>
       </c>
       <c r="AC24">
-        <v>0.00039151329210265816</v>
+        <v>0.00039319445603011149</v>
       </c>
       <c r="AD24">
-        <v>0.00040777688401417013</v>
+        <v>0.00040942594779439173</v>
       </c>
       <c r="AE24">
-        <v>0.00040616395217258461</v>
+        <v>0.00040923986966111882</v>
       </c>
       <c r="AF24">
-        <v>0.00040924300159192218</v>
+        <v>0.00041276175157133901</v>
       </c>
       <c r="AG24">
-        <v>0.00040698962787540777</v>
+        <v>0.00041084568652660869</v>
       </c>
       <c r="AH24">
-        <v>0.00040987645764059989</v>
+        <v>0.00041428668137754205</v>
       </c>
       <c r="AI24">
-        <v>0.00041247706124220739</v>
+        <v>0.00041709427058319958</v>
       </c>
       <c r="AJ24">
-        <v>7.8097697922861869e-007</v>
+        <v>6.5548127510310155e-007</v>
       </c>
       <c r="AK24">
-        <v>2.5720461149897583e-007</v>
+        <v>6.9898523339699471e-007</v>
       </c>
       <c r="AL24">
-        <v>1.1937203098798893e-005</v>
+        <v>8.2967756253637574e-006</v>
       </c>
       <c r="AM24">
-        <v>0.00017700709783017191</v>
+        <v>0.00018070475351414958</v>
       </c>
       <c r="AN24">
-        <v>0.00024681512259456151</v>
+        <v>0.00025115565359353653</v>
       </c>
       <c r="AO24">
-        <v>0.00014944660506991845</v>
+        <v>0.00012840022015475836</v>
       </c>
       <c r="AP24">
-        <v>-0.00042758302851905267</v>
+        <v>-0.00043234322940732817</v>
       </c>
     </row>
     <row r="25">
@@ -4868,127 +4868,127 @@
         <v>76</v>
       </c>
       <c r="B25" s="54">
-        <v>0.16966804225858068</v>
+        <v>0.16867147533635074</v>
       </c>
       <c r="C25">
-        <v>2.5651659560887277e-006</v>
+        <v>2.3035257734025374e-006</v>
       </c>
       <c r="D25">
-        <v>-9.8903734569424898e-008</v>
+        <v>-2.861537635533734e-007</v>
       </c>
       <c r="E25">
-        <v>3.3467275454540686e-009</v>
+        <v>5.4267287881987589e-009</v>
       </c>
       <c r="F25">
-        <v>4.2585669000465363e-005</v>
+        <v>4.4244666748914372e-005</v>
       </c>
       <c r="G25">
-        <v>1.9072347298937794e-005</v>
+        <v>1.9152511835205643e-005</v>
       </c>
       <c r="H25">
-        <v>2.9772217288906949e-005</v>
+        <v>2.9008592422752189e-005</v>
       </c>
       <c r="I25">
-        <v>1.6051098532026145e-005</v>
+        <v>1.1532560900428521e-005</v>
       </c>
       <c r="J25">
-        <v>3.1890012397859101e-005</v>
+        <v>3.1724283222555471e-005</v>
       </c>
       <c r="K25">
-        <v>3.9679033804963261e-005</v>
+        <v>3.9175454888008693e-005</v>
       </c>
       <c r="L25">
-        <v>3.4916282436393164e-005</v>
+        <v>3.5056367401661568e-005</v>
       </c>
       <c r="M25">
-        <v>2.7884088199277538e-005</v>
+        <v>2.0444658617424741e-005</v>
       </c>
       <c r="N25">
-        <v>3.7158101353686737e-006</v>
+        <v>5.1225277545594578e-006</v>
       </c>
       <c r="O25">
-        <v>-4.4744179123924961e-006</v>
+        <v>-3.7556254142177867e-006</v>
       </c>
       <c r="P25">
-        <v>-7.5309284809667942e-007</v>
+        <v>2.5978551697557275e-007</v>
       </c>
       <c r="Q25">
-        <v>2.7142791137503425e-007</v>
+        <v>2.3884675399935194e-007</v>
       </c>
       <c r="R25">
-        <v>1.0301390441543879e-007</v>
+        <v>1.4511416240333815e-007</v>
       </c>
       <c r="S25">
-        <v>2.0766340865740816e-006</v>
+        <v>2.899225290356009e-006</v>
       </c>
       <c r="T25">
-        <v>1.1544314586702855e-005</v>
+        <v>1.4244530379494138e-005</v>
       </c>
       <c r="U25">
-        <v>1.623968613156718e-005</v>
+        <v>1.766160395356906e-005</v>
       </c>
       <c r="V25">
-        <v>4.6399431227649896e-005</v>
+        <v>4.8074468398031977e-005</v>
       </c>
       <c r="W25">
-        <v>-1.5489603637526777e-006</v>
+        <v>-1.8826600193779879e-006</v>
       </c>
       <c r="X25">
-        <v>1.789870725228189e-006</v>
+        <v>1.7334429676801036e-006</v>
       </c>
       <c r="Y25">
-        <v>0.00040408184651562006</v>
+        <v>0.00040544062598465064</v>
       </c>
       <c r="Z25">
-        <v>0.00070138650161764924</v>
+        <v>0.00069985233088170717</v>
       </c>
       <c r="AA25">
-        <v>0.00039501328640832213</v>
+        <v>0.00039523327225700041</v>
       </c>
       <c r="AB25">
-        <v>0.00040108153221787705</v>
+        <v>0.00040103889894710365</v>
       </c>
       <c r="AC25">
-        <v>0.00038187516611261617</v>
+        <v>0.00038111933980099135</v>
       </c>
       <c r="AD25">
-        <v>0.00040615586878694836</v>
+        <v>0.00040534602446976801</v>
       </c>
       <c r="AE25">
-        <v>0.00040256506602848386</v>
+        <v>0.00040300515737162979</v>
       </c>
       <c r="AF25">
-        <v>0.000406249809338061</v>
+        <v>0.00040698780472538934</v>
       </c>
       <c r="AG25">
-        <v>0.00039728042079936439</v>
+        <v>0.00039827932766506194</v>
       </c>
       <c r="AH25">
-        <v>0.00040479041143994356</v>
+        <v>0.00040641750518664161</v>
       </c>
       <c r="AI25">
-        <v>0.00040246657831222475</v>
+        <v>0.00040411990113430312</v>
       </c>
       <c r="AJ25">
-        <v>9.7556327315862015e-007</v>
+        <v>9.4432640690916946e-007</v>
       </c>
       <c r="AK25">
-        <v>1.5895729135248509e-005</v>
+        <v>1.5746708165548291e-005</v>
       </c>
       <c r="AL25">
-        <v>5.383221627001473e-005</v>
+        <v>4.9342469135271547e-005</v>
       </c>
       <c r="AM25">
-        <v>0.00014950126733785364</v>
+        <v>0.00015186334166978537</v>
       </c>
       <c r="AN25">
-        <v>0.00022154933314881027</v>
+        <v>0.00022408046260449435</v>
       </c>
       <c r="AO25">
-        <v>0.00013292669372406125</v>
+        <v>0.0001138777539698932</v>
       </c>
       <c r="AP25">
-        <v>-0.00048767552068101878</v>
+        <v>-0.00048679327927524124</v>
       </c>
     </row>
     <row r="26">
@@ -4996,127 +4996,127 @@
         <v>77</v>
       </c>
       <c r="B26" s="56">
-        <v>0.14796566933687616</v>
+        <v>0.14721070348243023</v>
       </c>
       <c r="C26">
-        <v>-6.1480928525265669e-006</v>
+        <v>-5.9854706066210048e-006</v>
       </c>
       <c r="D26">
-        <v>-8.5519710667186671e-008</v>
+        <v>-1.5003954140125943e-007</v>
       </c>
       <c r="E26">
-        <v>3.6488823689211939e-009</v>
+        <v>4.5939750203273051e-009</v>
       </c>
       <c r="F26">
-        <v>6.0798857632218413e-005</v>
+        <v>6.3082394451988085e-005</v>
       </c>
       <c r="G26">
-        <v>3.3890928328997999e-005</v>
+        <v>3.3563824903551828e-005</v>
       </c>
       <c r="H26">
-        <v>3.7871518396302173e-005</v>
+        <v>3.7331295725158105e-005</v>
       </c>
       <c r="I26">
-        <v>0.00017140285409053394</v>
+        <v>0.00016697856894276706</v>
       </c>
       <c r="J26">
-        <v>4.7373184465018844e-005</v>
+        <v>4.7283214122017732e-005</v>
       </c>
       <c r="K26">
-        <v>5.4360154694098176e-005</v>
+        <v>5.3658533812372466e-005</v>
       </c>
       <c r="L26">
-        <v>3.8596885642352249e-005</v>
+        <v>3.9190129771313245e-005</v>
       </c>
       <c r="M26">
-        <v>1.6547942943106568e-005</v>
+        <v>1.0562117758169682e-005</v>
       </c>
       <c r="N26">
-        <v>3.9868371525026122e-006</v>
+        <v>5.7547306732661944e-006</v>
       </c>
       <c r="O26">
-        <v>-1.6264723733069384e-005</v>
+        <v>-1.6278950981465222e-005</v>
       </c>
       <c r="P26">
-        <v>-1.3110318379588601e-005</v>
+        <v>-1.2671064972245006e-005</v>
       </c>
       <c r="Q26">
-        <v>1.0056600360797459e-007</v>
+        <v>9.1312201297307484e-008</v>
       </c>
       <c r="R26">
-        <v>2.6023525017693039e-007</v>
+        <v>2.8860415989162376e-007</v>
       </c>
       <c r="S26">
-        <v>1.0340977553892552e-005</v>
+        <v>1.0840861546772208e-005</v>
       </c>
       <c r="T26">
-        <v>9.3678731038892737e-006</v>
+        <v>1.0872737543094611e-005</v>
       </c>
       <c r="U26">
-        <v>2.8254825304506923e-005</v>
+        <v>2.937978597661065e-005</v>
       </c>
       <c r="V26">
-        <v>5.7954047435246291e-005</v>
+        <v>5.9364707723022143e-005</v>
       </c>
       <c r="W26">
-        <v>-4.4612740530288802e-007</v>
+        <v>-7.5788881006784378e-007</v>
       </c>
       <c r="X26">
-        <v>-8.7577623939628949e-008</v>
+        <v>1.7362752875604237e-007</v>
       </c>
       <c r="Y26">
-        <v>0.00040148424618977768</v>
+        <v>0.00040436692858937908</v>
       </c>
       <c r="Z26">
-        <v>0.00039501328640832213</v>
+        <v>0.00039523327225700041</v>
       </c>
       <c r="AA26">
-        <v>0.00072479267400433242</v>
+        <v>0.00072701021406823931</v>
       </c>
       <c r="AB26">
-        <v>0.00039819281552462137</v>
+        <v>0.00039987326997609375</v>
       </c>
       <c r="AC26">
-        <v>0.00038562946673371897</v>
+        <v>0.00038661088245688248</v>
       </c>
       <c r="AD26">
-        <v>0.00040219192651074528</v>
+        <v>0.00040312902647649885</v>
       </c>
       <c r="AE26">
-        <v>0.00039903454284090747</v>
+        <v>0.00040117483331531851</v>
       </c>
       <c r="AF26">
-        <v>0.0004049723042121833</v>
+        <v>0.00040744229658496762</v>
       </c>
       <c r="AG26">
-        <v>0.00040139518717607534</v>
+        <v>0.0004041504570453241</v>
       </c>
       <c r="AH26">
-        <v>0.00039900697455591333</v>
+        <v>0.00040221702041429538</v>
       </c>
       <c r="AI26">
-        <v>0.00040284981305409914</v>
+        <v>0.0004061023004008492</v>
       </c>
       <c r="AJ26">
-        <v>3.5738702634457672e-007</v>
+        <v>2.4569732034004609e-007</v>
       </c>
       <c r="AK26">
-        <v>1.8454110273557358e-005</v>
+        <v>1.8898305474517817e-005</v>
       </c>
       <c r="AL26">
-        <v>3.8222550525919666e-005</v>
+        <v>3.4390660047410846e-005</v>
       </c>
       <c r="AM26">
-        <v>0.00014463971842960173</v>
+        <v>0.0001473083131949232</v>
       </c>
       <c r="AN26">
-        <v>0.00021964192834750409</v>
+        <v>0.0002228190962851678</v>
       </c>
       <c r="AO26">
-        <v>0.00014720638389864566</v>
+        <v>0.0001109546980809342</v>
       </c>
       <c r="AP26">
-        <v>-0.00047875571207210146</v>
+        <v>-0.00048107354296419785</v>
       </c>
     </row>
     <row r="27">
@@ -5124,127 +5124,127 @@
         <v>78</v>
       </c>
       <c r="B27" s="58">
-        <v>0.20263543279980348</v>
+        <v>0.20194206047497273</v>
       </c>
       <c r="C27">
-        <v>-8.3291446018805466e-006</v>
+        <v>-8.2273743438368948e-006</v>
       </c>
       <c r="D27">
-        <v>1.8308282989344809e-007</v>
+        <v>9.6750197830381275e-008</v>
       </c>
       <c r="E27">
-        <v>2.2560010419486656e-009</v>
+        <v>3.4325231597389311e-009</v>
       </c>
       <c r="F27">
-        <v>6.3782716654939758e-005</v>
+        <v>6.586282011977713e-005</v>
       </c>
       <c r="G27">
-        <v>2.9451251591198656e-005</v>
+        <v>2.9113658753665766e-005</v>
       </c>
       <c r="H27">
-        <v>3.9594852907438307e-005</v>
+        <v>3.9202701076031289e-005</v>
       </c>
       <c r="I27">
-        <v>8.5378323731873036e-005</v>
+        <v>8.1372758819724659e-005</v>
       </c>
       <c r="J27">
-        <v>4.8136812272764873e-005</v>
+        <v>4.8353502230760692e-005</v>
       </c>
       <c r="K27">
-        <v>4.6099012975285248e-005</v>
+        <v>4.5168777664249862e-005</v>
       </c>
       <c r="L27">
-        <v>4.2955249127794177e-005</v>
+        <v>4.3389703833699941e-005</v>
       </c>
       <c r="M27">
-        <v>2.3331581142452144e-005</v>
+        <v>1.731328733090099e-005</v>
       </c>
       <c r="N27">
-        <v>8.1641983662402888e-006</v>
+        <v>9.5454956921986025e-006</v>
       </c>
       <c r="O27">
-        <v>-2.0538440933876805e-005</v>
+        <v>-2.0724285015696188e-005</v>
       </c>
       <c r="P27">
-        <v>-2.4281067587399416e-005</v>
+        <v>-2.4162488725263066e-005</v>
       </c>
       <c r="Q27">
-        <v>1.4783080081378226e-007</v>
+        <v>1.3739573166310781e-007</v>
       </c>
       <c r="R27">
-        <v>5.9871213269350256e-008</v>
+        <v>8.3898352104654422e-008</v>
       </c>
       <c r="S27">
-        <v>2.3307189381639045e-006</v>
+        <v>1.7386163363412193e-006</v>
       </c>
       <c r="T27">
-        <v>1.9914427500938796e-006</v>
+        <v>2.7286354398773304e-006</v>
       </c>
       <c r="U27">
-        <v>2.9526301226812782e-005</v>
+        <v>2.997059363949753e-005</v>
       </c>
       <c r="V27">
-        <v>4.8229253760445737e-005</v>
+        <v>4.8723632054761381e-005</v>
       </c>
       <c r="W27">
-        <v>-3.485075958210293e-007</v>
+        <v>-6.137546330418299e-007</v>
       </c>
       <c r="X27">
-        <v>-4.7645105196437709e-006</v>
+        <v>-4.5683719134744386e-006</v>
       </c>
       <c r="Y27">
-        <v>0.00040231259971754531</v>
+        <v>0.00040492880164712963</v>
       </c>
       <c r="Z27">
-        <v>0.00040108153221787705</v>
+        <v>0.00040103889894710365</v>
       </c>
       <c r="AA27">
-        <v>0.00039819281552462137</v>
+        <v>0.00039987326997609375</v>
       </c>
       <c r="AB27">
-        <v>0.00079254554871991648</v>
+        <v>0.00079475261483227973</v>
       </c>
       <c r="AC27">
-        <v>0.00038737243355216311</v>
+        <v>0.000388182284600272</v>
       </c>
       <c r="AD27">
-        <v>0.00040076777532832098</v>
+        <v>0.000401536048597071</v>
       </c>
       <c r="AE27">
-        <v>0.00040359351418778366</v>
+        <v>0.00040553745959276665</v>
       </c>
       <c r="AF27">
-        <v>0.00040935426325029863</v>
+        <v>0.00041159413318293933</v>
       </c>
       <c r="AG27">
-        <v>0.00040531708294522099</v>
+        <v>0.00040784828807215005</v>
       </c>
       <c r="AH27">
-        <v>0.00039951455867291469</v>
+        <v>0.00040246512623406808</v>
       </c>
       <c r="AI27">
-        <v>0.00040693389807052328</v>
+        <v>0.00040991897225836865</v>
       </c>
       <c r="AJ27">
-        <v>8.915585662378764e-007</v>
+        <v>7.77925716806385e-007</v>
       </c>
       <c r="AK27">
-        <v>1.9508960761846786e-005</v>
+        <v>1.9907112257510224e-005</v>
       </c>
       <c r="AL27">
-        <v>1.725991040074047e-005</v>
+        <v>1.3392342018076178e-005</v>
       </c>
       <c r="AM27">
-        <v>0.00015655778710017007</v>
+        <v>0.00015893673537363645</v>
       </c>
       <c r="AN27">
-        <v>0.00021886736241679287</v>
+        <v>0.00022180168910254964</v>
       </c>
       <c r="AO27">
-        <v>0.00015085968648812846</v>
+        <v>0.00011002647308434358</v>
       </c>
       <c r="AP27">
-        <v>-0.00047668382589024849</v>
+        <v>-0.00047687124664680088</v>
       </c>
     </row>
     <row r="28">
@@ -5252,127 +5252,127 @@
         <v>79</v>
       </c>
       <c r="B28" s="60">
-        <v>0.18116308144916565</v>
+        <v>0.18069755201873702</v>
       </c>
       <c r="C28">
-        <v>-3.2206796953546379e-006</v>
+        <v>-3.0512157408658435e-006</v>
       </c>
       <c r="D28">
-        <v>-3.6922932629806123e-007</v>
+        <v>-4.5639613423209734e-007</v>
       </c>
       <c r="E28">
-        <v>4.683812022522709e-009</v>
+        <v>5.8186728297166114e-009</v>
       </c>
       <c r="F28">
-        <v>3.6694469644645993e-005</v>
+        <v>3.8763792665232444e-005</v>
       </c>
       <c r="G28">
-        <v>2.4575656793736539e-005</v>
+        <v>2.4459194341473521e-005</v>
       </c>
       <c r="H28">
-        <v>4.1472015736853361e-005</v>
+        <v>4.1140396085820408e-005</v>
       </c>
       <c r="I28">
-        <v>-6.6492616617335845e-006</v>
+        <v>-9.9608127622214634e-006</v>
       </c>
       <c r="J28">
-        <v>3.6026458008795377e-005</v>
+        <v>3.5960673289889608e-005</v>
       </c>
       <c r="K28">
-        <v>4.4760088199863379e-005</v>
+        <v>4.4140105487325209e-005</v>
       </c>
       <c r="L28">
-        <v>2.359717219091617e-005</v>
+        <v>2.441745926934888e-005</v>
       </c>
       <c r="M28">
-        <v>2.0949157345983768e-006</v>
+        <v>-3.6712926107483138e-006</v>
       </c>
       <c r="N28">
-        <v>4.9457814599474461e-006</v>
+        <v>6.0950655028141561e-006</v>
       </c>
       <c r="O28">
-        <v>-1.2933124185042329e-005</v>
+        <v>-1.3082745607955688e-005</v>
       </c>
       <c r="P28">
-        <v>-2.8567886472008493e-005</v>
+        <v>-2.8486464029892024e-005</v>
       </c>
       <c r="Q28">
-        <v>3.4125469372067987e-007</v>
+        <v>3.271082156917113e-007</v>
       </c>
       <c r="R28">
-        <v>3.0548915709725381e-007</v>
+        <v>3.2981006691703227e-007</v>
       </c>
       <c r="S28">
-        <v>-1.3961820098732119e-006</v>
+        <v>-1.9949260242942716e-006</v>
       </c>
       <c r="T28">
-        <v>-1.9383576020664117e-006</v>
+        <v>-1.2418314718855755e-006</v>
       </c>
       <c r="U28">
-        <v>1.2161752464588516e-005</v>
+        <v>1.2407403429402096e-005</v>
       </c>
       <c r="V28">
-        <v>3.4338737828916849e-005</v>
+        <v>3.4821358251136409e-005</v>
       </c>
       <c r="W28">
-        <v>9.1642006762451959e-007</v>
+        <v>6.5014907536189881e-007</v>
       </c>
       <c r="X28">
-        <v>-5.6357700920241547e-006</v>
+        <v>-5.4678833453257653e-006</v>
       </c>
       <c r="Y28">
-        <v>0.00039151329210265816</v>
+        <v>0.00039319445603011149</v>
       </c>
       <c r="Z28">
-        <v>0.00038187516611261617</v>
+        <v>0.00038111933980099135</v>
       </c>
       <c r="AA28">
-        <v>0.00038562946673371897</v>
+        <v>0.00038661088245688248</v>
       </c>
       <c r="AB28">
-        <v>0.00038737243355216311</v>
+        <v>0.000388182284600272</v>
       </c>
       <c r="AC28">
-        <v>0.00076634999539452087</v>
+        <v>0.00076733838377661932</v>
       </c>
       <c r="AD28">
-        <v>0.00039094636953889171</v>
+        <v>0.00039128594530491611</v>
       </c>
       <c r="AE28">
-        <v>0.00038770962843929119</v>
+        <v>0.00038892531824976842</v>
       </c>
       <c r="AF28">
-        <v>0.00039197668317257395</v>
+        <v>0.00039342489704449567</v>
       </c>
       <c r="AG28">
-        <v>0.00039137152062845653</v>
+        <v>0.00039306646203778842</v>
       </c>
       <c r="AH28">
-        <v>0.00038978169103223313</v>
+        <v>0.00039179943560905937</v>
       </c>
       <c r="AI28">
-        <v>0.00039214834421521659</v>
+        <v>0.00039404597248016057</v>
       </c>
       <c r="AJ28">
-        <v>-1.1427480599997903e-007</v>
+        <v>-1.9800387870839688e-007</v>
       </c>
       <c r="AK28">
-        <v>2.1079442842292824e-005</v>
+        <v>2.1456337586683742e-005</v>
       </c>
       <c r="AL28">
-        <v>3.4074844026435337e-005</v>
+        <v>3.0367833758607052e-005</v>
       </c>
       <c r="AM28">
-        <v>0.00012197508485422148</v>
+        <v>0.00012369951560224293</v>
       </c>
       <c r="AN28">
-        <v>0.00018941544679752483</v>
+        <v>0.00019148442444948935</v>
       </c>
       <c r="AO28">
-        <v>0.00011494100030006665</v>
+        <v>8.0419854247972331e-005</v>
       </c>
       <c r="AP28">
-        <v>-0.00044221349977124745</v>
+        <v>-0.00044166285513180223</v>
       </c>
     </row>
     <row r="29">
@@ -5380,127 +5380,127 @@
         <v>80</v>
       </c>
       <c r="B29" s="62">
-        <v>0.15670710582499539</v>
+        <v>0.15624471444591531</v>
       </c>
       <c r="C29">
-        <v>-2.1606636180992929e-006</v>
+        <v>-1.878729065665198e-006</v>
       </c>
       <c r="D29">
-        <v>-3.2691149021661699e-008</v>
+        <v>-1.1823394706229884e-007</v>
       </c>
       <c r="E29">
-        <v>3.3861924066573644e-009</v>
+        <v>4.5198669120779643e-009</v>
       </c>
       <c r="F29">
-        <v>3.2152898195590197e-005</v>
+        <v>3.3906581350821768e-005</v>
       </c>
       <c r="G29">
-        <v>1.7894740527204988e-005</v>
+        <v>1.7673161332525544e-005</v>
       </c>
       <c r="H29">
-        <v>2.6586268515129632e-005</v>
+        <v>2.6122838509771811e-005</v>
       </c>
       <c r="I29">
-        <v>2.7186207177933301e-005</v>
+        <v>2.3916726630220741e-005</v>
       </c>
       <c r="J29">
-        <v>2.1984808266582192e-005</v>
+        <v>2.1759754083253502e-005</v>
       </c>
       <c r="K29">
-        <v>3.7900906781360821e-005</v>
+        <v>3.7205736557521105e-005</v>
       </c>
       <c r="L29">
-        <v>2.3830579479435526e-005</v>
+        <v>2.4516056335315922e-005</v>
       </c>
       <c r="M29">
-        <v>1.2215716568892443e-005</v>
+        <v>6.5337293116076199e-006</v>
       </c>
       <c r="N29">
-        <v>1.060913295726772e-007</v>
+        <v>1.2743049188284423e-006</v>
       </c>
       <c r="O29">
-        <v>-1.3956940263591715e-005</v>
+        <v>-1.4245120790307552e-005</v>
       </c>
       <c r="P29">
-        <v>-1.2509042616985297e-005</v>
+        <v>-1.250484049025119e-005</v>
       </c>
       <c r="Q29">
-        <v>9.9910454301623885e-008</v>
+        <v>8.4030241226266078e-008</v>
       </c>
       <c r="R29">
-        <v>7.3845466651597466e-008</v>
+        <v>9.9305010931922812e-008</v>
       </c>
       <c r="S29">
-        <v>-8.9154048316052487e-006</v>
+        <v>-9.1976914471293708e-006</v>
       </c>
       <c r="T29">
-        <v>3.0988616345041325e-006</v>
+        <v>4.0950163762586058e-006</v>
       </c>
       <c r="U29">
-        <v>8.3433551084079546e-006</v>
+        <v>8.809168058777225e-006</v>
       </c>
       <c r="V29">
-        <v>3.604547052909147e-005</v>
+        <v>3.6732859571079015e-005</v>
       </c>
       <c r="W29">
-        <v>7.2946889298919958e-007</v>
+        <v>4.5291626340997131e-007</v>
       </c>
       <c r="X29">
-        <v>-2.4586011288120601e-006</v>
+        <v>-2.3477769551760043e-006</v>
       </c>
       <c r="Y29">
-        <v>0.00040777688401417013</v>
+        <v>0.00040942594779439173</v>
       </c>
       <c r="Z29">
-        <v>0.00040615586878694836</v>
+        <v>0.00040534602446976801</v>
       </c>
       <c r="AA29">
-        <v>0.00040219192651074528</v>
+        <v>0.00040312902647649885</v>
       </c>
       <c r="AB29">
-        <v>0.00040076777532832098</v>
+        <v>0.000401536048597071</v>
       </c>
       <c r="AC29">
-        <v>0.00039094636953889171</v>
+        <v>0.00039128594530491611</v>
       </c>
       <c r="AD29">
-        <v>0.00072437917886889109</v>
+        <v>0.00072515903164523349</v>
       </c>
       <c r="AE29">
-        <v>0.00040415385021169161</v>
+        <v>0.00040532316683409013</v>
       </c>
       <c r="AF29">
-        <v>0.00041303851457010686</v>
+        <v>0.00041446897007393072</v>
       </c>
       <c r="AG29">
-        <v>0.00040930736023103004</v>
+        <v>0.00041097242651447766</v>
       </c>
       <c r="AH29">
-        <v>0.00040861820809942443</v>
+        <v>0.00041057887019088624</v>
       </c>
       <c r="AI29">
-        <v>0.00041009797504808855</v>
+        <v>0.00041194588448983011</v>
       </c>
       <c r="AJ29">
-        <v>-8.0348953933334672e-007</v>
+        <v>-8.9319740562460886e-007</v>
       </c>
       <c r="AK29">
-        <v>2.102238822590338e-005</v>
+        <v>2.1399712591545073e-005</v>
       </c>
       <c r="AL29">
-        <v>2.6845263593681731e-005</v>
+        <v>2.2972002120995392e-005</v>
       </c>
       <c r="AM29">
-        <v>0.00016229963487172141</v>
+        <v>0.00016395862951943711</v>
       </c>
       <c r="AN29">
-        <v>0.00022654221276478481</v>
+        <v>0.00022854862851508703</v>
       </c>
       <c r="AO29">
-        <v>0.00012421927604358422</v>
+        <v>8.5360618158683728e-005</v>
       </c>
       <c r="AP29">
-        <v>-0.00043585348605913173</v>
+        <v>-0.00043526500217888137</v>
       </c>
     </row>
     <row r="30">
@@ -5508,127 +5508,127 @@
         <v>81</v>
       </c>
       <c r="B30" s="64">
-        <v>0.1564606471172906</v>
+        <v>0.15583435742309787</v>
       </c>
       <c r="C30">
-        <v>1.6822808489548638e-006</v>
+        <v>1.8601942434671242e-006</v>
       </c>
       <c r="D30">
-        <v>5.8235760554578036e-008</v>
+        <v>-1.2959412249870765e-008</v>
       </c>
       <c r="E30">
-        <v>2.0050796164451299e-009</v>
+        <v>3.0747427021770088e-009</v>
       </c>
       <c r="F30">
-        <v>4.5619095959262961e-005</v>
+        <v>4.798065596966304e-005</v>
       </c>
       <c r="G30">
-        <v>2.1047671777806868e-005</v>
+        <v>2.0718899209248231e-005</v>
       </c>
       <c r="H30">
-        <v>2.8727728194853901e-005</v>
+        <v>2.819062918018544e-005</v>
       </c>
       <c r="I30">
-        <v>0.00020692008425780031</v>
+        <v>0.00020303885685219727</v>
       </c>
       <c r="J30">
-        <v>3.2526448353541393e-005</v>
+        <v>3.2307830672687991e-005</v>
       </c>
       <c r="K30">
-        <v>3.4727777814940279e-005</v>
+        <v>3.3859352017881603e-005</v>
       </c>
       <c r="L30">
-        <v>3.3780084606018336e-005</v>
+        <v>3.4209284274083593e-005</v>
       </c>
       <c r="M30">
-        <v>4.4081676531365272e-005</v>
+        <v>3.8088800263124328e-005</v>
       </c>
       <c r="N30">
-        <v>1.0079935660142819e-005</v>
+        <v>1.1487507894058186e-005</v>
       </c>
       <c r="O30">
-        <v>-6.1799784853872922e-006</v>
+        <v>-6.2333134071262182e-006</v>
       </c>
       <c r="P30">
-        <v>-4.0845350809355443e-006</v>
+        <v>-3.8001402494420716e-006</v>
       </c>
       <c r="Q30">
-        <v>2.9729811760800527e-007</v>
+        <v>2.8607903899948467e-007</v>
       </c>
       <c r="R30">
-        <v>-1.6407157547322961e-007</v>
+        <v>-1.3568759272952403e-007</v>
       </c>
       <c r="S30">
-        <v>5.5937955216764057e-006</v>
+        <v>5.4551772439592195e-006</v>
       </c>
       <c r="T30">
-        <v>1.2015757528881497e-005</v>
+        <v>1.3099714561265875e-005</v>
       </c>
       <c r="U30">
-        <v>2.7084674129769883e-005</v>
+        <v>2.7888939973105619e-005</v>
       </c>
       <c r="V30">
-        <v>3.5358719955556112e-005</v>
+        <v>3.6004040631678194e-005</v>
       </c>
       <c r="W30">
-        <v>-1.2159317591094743e-006</v>
+        <v>-1.4928615463157652e-006</v>
       </c>
       <c r="X30">
-        <v>-4.2380767751072567e-006</v>
+        <v>-3.9220038693309191e-006</v>
       </c>
       <c r="Y30">
-        <v>0.00040616395217258461</v>
+        <v>0.00040923986966111882</v>
       </c>
       <c r="Z30">
-        <v>0.00040256506602848386</v>
+        <v>0.00040300515737162979</v>
       </c>
       <c r="AA30">
-        <v>0.00039903454284090747</v>
+        <v>0.00040117483331531851</v>
       </c>
       <c r="AB30">
-        <v>0.00040359351418778366</v>
+        <v>0.00040553745959276665</v>
       </c>
       <c r="AC30">
-        <v>0.00038770962843929119</v>
+        <v>0.00038892531824976842</v>
       </c>
       <c r="AD30">
-        <v>0.00040415385021169161</v>
+        <v>0.00040532316683409013</v>
       </c>
       <c r="AE30">
-        <v>0.00066944545022104692</v>
+        <v>0.00067200772452458775</v>
       </c>
       <c r="AF30">
-        <v>0.00040843951952392271</v>
+        <v>0.00041110853826920854</v>
       </c>
       <c r="AG30">
-        <v>0.00040570911528192179</v>
+        <v>0.00040863009163989001</v>
       </c>
       <c r="AH30">
-        <v>0.00040571760000579103</v>
+        <v>0.0004090892446772405</v>
       </c>
       <c r="AI30">
-        <v>0.00040704715099180121</v>
+        <v>0.00041035036161160413</v>
       </c>
       <c r="AJ30">
-        <v>1.5620503633094324e-006</v>
+        <v>1.4537093930402508e-006</v>
       </c>
       <c r="AK30">
-        <v>2.5913115128783599e-006</v>
+        <v>2.9675894168048218e-006</v>
       </c>
       <c r="AL30">
-        <v>1.821206590629009e-005</v>
+        <v>1.4465085653334961e-005</v>
       </c>
       <c r="AM30">
-        <v>0.00016410635115775776</v>
+        <v>0.00016687029897799788</v>
       </c>
       <c r="AN30">
-        <v>0.00022412688243907109</v>
+        <v>0.00022748870404012785</v>
       </c>
       <c r="AO30">
-        <v>0.00012971396197030571</v>
+        <v>0.00010526941521295897</v>
       </c>
       <c r="AP30">
-        <v>-0.00048879068276028138</v>
+        <v>-0.00049071959395017651</v>
       </c>
     </row>
     <row r="31">
@@ -5636,127 +5636,127 @@
         <v>82</v>
       </c>
       <c r="B31" s="66">
-        <v>0.1408707046874173</v>
+        <v>0.1399988359310278</v>
       </c>
       <c r="C31">
-        <v>-2.6942722493586907e-006</v>
+        <v>-2.7523960014807661e-006</v>
       </c>
       <c r="D31">
-        <v>3.7249517133082162e-007</v>
+        <v>2.6971435125143941e-007</v>
       </c>
       <c r="E31">
-        <v>-5.5020054806323124e-010</v>
+        <v>8.2796512018523817e-010</v>
       </c>
       <c r="F31">
-        <v>3.2917015881726954e-005</v>
+        <v>3.5126085159460242e-005</v>
       </c>
       <c r="G31">
-        <v>3.0844326444915985e-005</v>
+        <v>3.0580734691649473e-005</v>
       </c>
       <c r="H31">
-        <v>4.1935567786795002e-005</v>
+        <v>4.147873628335976e-005</v>
       </c>
       <c r="I31">
-        <v>6.2749221625431161e-005</v>
+        <v>5.791744069693084e-005</v>
       </c>
       <c r="J31">
-        <v>7.3022167543804737e-005</v>
+        <v>7.2683787983176317e-005</v>
       </c>
       <c r="K31">
-        <v>5.2894905662205521e-005</v>
+        <v>5.1683689392831381e-005</v>
       </c>
       <c r="L31">
-        <v>8.0656064050054575e-005</v>
+        <v>8.0781937201692729e-005</v>
       </c>
       <c r="M31">
-        <v>3.3406215012167039e-005</v>
+        <v>2.6308989402662822e-005</v>
       </c>
       <c r="N31">
-        <v>1.1631357995376263e-005</v>
+        <v>1.2267559442093118e-005</v>
       </c>
       <c r="O31">
-        <v>-1.6709959874444176e-005</v>
+        <v>-1.6482766406604815e-005</v>
       </c>
       <c r="P31">
-        <v>-9.3581187959096117e-006</v>
+        <v>-8.7971455030878301e-006</v>
       </c>
       <c r="Q31">
-        <v>-6.5899152548758205e-007</v>
+        <v>-6.6611041472222661e-007</v>
       </c>
       <c r="R31">
-        <v>2.0004168872908066e-007</v>
+        <v>2.2924426976157816e-007</v>
       </c>
       <c r="S31">
-        <v>-1.0361466602570815e-005</v>
+        <v>-1.3251212198937637e-005</v>
       </c>
       <c r="T31">
-        <v>1.0021102760084163e-005</v>
+        <v>8.9946878505244559e-006</v>
       </c>
       <c r="U31">
-        <v>2.2476478035253115e-005</v>
+        <v>2.1141536129607207e-005</v>
       </c>
       <c r="V31">
-        <v>4.3446583363528149e-005</v>
+        <v>4.2379327541817049e-005</v>
       </c>
       <c r="W31">
-        <v>-1.1151932679304955e-007</v>
+        <v>-2.3646893069891942e-007</v>
       </c>
       <c r="X31">
-        <v>-2.003884588100043e-006</v>
+        <v>-1.5254192525200594e-006</v>
       </c>
       <c r="Y31">
-        <v>0.00040924300159192218</v>
+        <v>0.00041276175157133901</v>
       </c>
       <c r="Z31">
-        <v>0.000406249809338061</v>
+        <v>0.00040698780472538934</v>
       </c>
       <c r="AA31">
-        <v>0.0004049723042121833</v>
+        <v>0.00040744229658496762</v>
       </c>
       <c r="AB31">
-        <v>0.00040935426325029863</v>
+        <v>0.00041159413318293933</v>
       </c>
       <c r="AC31">
-        <v>0.00039197668317257395</v>
+        <v>0.00039342489704449567</v>
       </c>
       <c r="AD31">
-        <v>0.00041303851457010686</v>
+        <v>0.00041446897007393072</v>
       </c>
       <c r="AE31">
-        <v>0.00040843951952392271</v>
+        <v>0.00041110853826920854</v>
       </c>
       <c r="AF31">
-        <v>0.0007726801136631816</v>
+        <v>0.00077584463860027447</v>
       </c>
       <c r="AG31">
-        <v>0.00040879517814705277</v>
+        <v>0.00041214253229554651</v>
       </c>
       <c r="AH31">
-        <v>0.00041000969746578459</v>
+        <v>0.00041387307627423637</v>
       </c>
       <c r="AI31">
-        <v>0.00041319782664332391</v>
+        <v>0.0004168902398503644</v>
       </c>
       <c r="AJ31">
-        <v>2.0107146316127575e-006</v>
+        <v>1.8850615576936007e-006</v>
       </c>
       <c r="AK31">
-        <v>7.4435194917914672e-006</v>
+        <v>7.9744394407139981e-006</v>
       </c>
       <c r="AL31">
-        <v>1.5680701171155075e-005</v>
+        <v>1.2085275635836967e-005</v>
       </c>
       <c r="AM31">
-        <v>0.00017226022878756063</v>
+        <v>0.00017542379017838528</v>
       </c>
       <c r="AN31">
-        <v>0.00023501927660626938</v>
+        <v>0.00023889097934287059</v>
       </c>
       <c r="AO31">
-        <v>0.0001379532351314649</v>
+        <v>0.00011467566128293916</v>
       </c>
       <c r="AP31">
-        <v>-0.00048602704067803666</v>
+        <v>-0.00048580918582485618</v>
       </c>
     </row>
     <row r="32">
@@ -5764,127 +5764,127 @@
         <v>83</v>
       </c>
       <c r="B32" s="68">
-        <v>0.17417808196983048</v>
+        <v>0.17354662544821223</v>
       </c>
       <c r="C32">
-        <v>-7.0608282023337232e-006</v>
+        <v>-6.9703098249783688e-006</v>
       </c>
       <c r="D32">
-        <v>1.5071944669104611e-006</v>
+        <v>1.4366065722381345e-006</v>
       </c>
       <c r="E32">
-        <v>-1.1446278559799904e-008</v>
+        <v>-1.0355970486476632e-008</v>
       </c>
       <c r="F32">
-        <v>5.8581790707732729e-005</v>
+        <v>6.0647341145564614e-005</v>
       </c>
       <c r="G32">
-        <v>2.0254408291324496e-005</v>
+        <v>1.9971919892630333e-005</v>
       </c>
       <c r="H32">
-        <v>2.8058613379705238e-005</v>
+        <v>2.7453471000079443e-005</v>
       </c>
       <c r="I32">
-        <v>-3.1291993330550161e-006</v>
+        <v>-7.276197335241507e-006</v>
       </c>
       <c r="J32">
-        <v>3.0231703177434861e-005</v>
+        <v>3.0007355966603794e-005</v>
       </c>
       <c r="K32">
-        <v>3.9705644136841779e-005</v>
+        <v>3.8849454777251672e-005</v>
       </c>
       <c r="L32">
-        <v>2.5545709157311596e-005</v>
+        <v>2.5939269107034342e-005</v>
       </c>
       <c r="M32">
-        <v>2.2601141576842991e-005</v>
+        <v>1.6539691753148834e-005</v>
       </c>
       <c r="N32">
-        <v>2.4216683648363587e-006</v>
+        <v>3.9627402472842738e-006</v>
       </c>
       <c r="O32">
-        <v>-1.3607000476400813e-005</v>
+        <v>-1.3431625409114417e-005</v>
       </c>
       <c r="P32">
-        <v>-1.3834551077644458e-005</v>
+        <v>-1.331075370210338e-005</v>
       </c>
       <c r="Q32">
-        <v>4.0715617083411922e-007</v>
+        <v>3.9718023545358336e-007</v>
       </c>
       <c r="R32">
-        <v>3.880281082973266e-007</v>
+        <v>4.1791486239983743e-007</v>
       </c>
       <c r="S32">
-        <v>-1.5715861166098793e-006</v>
+        <v>-1.5048776979311167e-006</v>
       </c>
       <c r="T32">
-        <v>-3.2158280506280814e-006</v>
+        <v>-1.95771093791197e-006</v>
       </c>
       <c r="U32">
-        <v>1.0994834736257611e-005</v>
+        <v>1.189095595902564e-005</v>
       </c>
       <c r="V32">
-        <v>3.6299659146507882e-005</v>
+        <v>3.7447481340722538e-005</v>
       </c>
       <c r="W32">
-        <v>2.4110246817791097e-007</v>
+        <v>-5.0030198543926451e-008</v>
       </c>
       <c r="X32">
-        <v>-4.4109991980257757e-006</v>
+        <v>-3.9537666154028055e-006</v>
       </c>
       <c r="Y32">
-        <v>0.00040698962787540777</v>
+        <v>0.00041084568652660869</v>
       </c>
       <c r="Z32">
-        <v>0.00039728042079936439</v>
+        <v>0.00039827932766506194</v>
       </c>
       <c r="AA32">
-        <v>0.00040139518717607534</v>
+        <v>0.0004041504570453241</v>
       </c>
       <c r="AB32">
-        <v>0.00040531708294522099</v>
+        <v>0.00040784828807215005</v>
       </c>
       <c r="AC32">
-        <v>0.00039137152062845653</v>
+        <v>0.00039306646203778842</v>
       </c>
       <c r="AD32">
-        <v>0.00040930736023103004</v>
+        <v>0.00041097242651447766</v>
       </c>
       <c r="AE32">
-        <v>0.00040570911528192179</v>
+        <v>0.00040863009163989001</v>
       </c>
       <c r="AF32">
-        <v>0.00040879517814705277</v>
+        <v>0.00041214253229554651</v>
       </c>
       <c r="AG32">
-        <v>0.00079816359358305116</v>
+        <v>0.00080209385969115283</v>
       </c>
       <c r="AH32">
-        <v>0.0004084212065476715</v>
+        <v>0.00041253434547314986</v>
       </c>
       <c r="AI32">
-        <v>0.00041077851285336317</v>
+        <v>0.00041487556343903912</v>
       </c>
       <c r="AJ32">
-        <v>8.7383672120598286e-007</v>
+        <v>7.6937399234767938e-007</v>
       </c>
       <c r="AK32">
-        <v>1.4370636222700281e-005</v>
+        <v>1.4735717183226086e-005</v>
       </c>
       <c r="AL32">
-        <v>1.5243296623434048e-005</v>
+        <v>1.1350789722147744e-005</v>
       </c>
       <c r="AM32">
-        <v>0.00017518403869338112</v>
+        <v>0.00017853000600238651</v>
       </c>
       <c r="AN32">
-        <v>0.00023665634150445462</v>
+        <v>0.00024066480240021588</v>
       </c>
       <c r="AO32">
-        <v>0.00012940215879981757</v>
+        <v>0.00011440468100020527</v>
       </c>
       <c r="AP32">
-        <v>-0.00052368624413414713</v>
+        <v>-0.00052711606136422783</v>
       </c>
     </row>
     <row r="33">
@@ -5892,127 +5892,127 @@
         <v>84</v>
       </c>
       <c r="B33" s="70">
-        <v>0.12304466723555595</v>
+        <v>0.12099078759146743</v>
       </c>
       <c r="C33">
-        <v>1.7201627876411077e-006</v>
+        <v>1.4936291953983648e-006</v>
       </c>
       <c r="D33">
-        <v>-1.7155527950960071e-006</v>
+        <v>-1.7348382566227951e-006</v>
       </c>
       <c r="E33">
-        <v>1.4842365777489208e-008</v>
+        <v>1.5604901128459016e-008</v>
       </c>
       <c r="F33">
-        <v>-2.6695235389355022e-005</v>
+        <v>-2.4064314215068087e-005</v>
       </c>
       <c r="G33">
-        <v>9.3655179721029627e-006</v>
+        <v>9.1603245672613665e-006</v>
       </c>
       <c r="H33">
-        <v>2.6351405141876389e-005</v>
+        <v>2.5912754569108509e-005</v>
       </c>
       <c r="I33">
-        <v>-1.2996915044699635e-005</v>
+        <v>-1.80146802374603e-005</v>
       </c>
       <c r="J33">
-        <v>2.7200665221475215e-005</v>
+        <v>2.7148690665105618e-005</v>
       </c>
       <c r="K33">
-        <v>2.3826574394951692e-005</v>
+        <v>2.2869448814908768e-005</v>
       </c>
       <c r="L33">
-        <v>2.4647661078261268e-005</v>
+        <v>2.4994079830905678e-005</v>
       </c>
       <c r="M33">
-        <v>-7.5971544920461383e-006</v>
+        <v>-1.3733469032988947e-005</v>
       </c>
       <c r="N33">
-        <v>7.0742229134413884e-006</v>
+        <v>7.9574877523093585e-006</v>
       </c>
       <c r="O33">
-        <v>-1.4976570531056447e-005</v>
+        <v>-1.4799555215242842e-005</v>
       </c>
       <c r="P33">
-        <v>-2.0694718329690681e-006</v>
+        <v>-1.3586776894978852e-006</v>
       </c>
       <c r="Q33">
-        <v>1.8863472025965174e-007</v>
+        <v>1.851345182332464e-007</v>
       </c>
       <c r="R33">
-        <v>3.0285608289124195e-007</v>
+        <v>3.5091433062408159e-007</v>
       </c>
       <c r="S33">
-        <v>8.0771035405797939e-006</v>
+        <v>7.0571094583996572e-006</v>
       </c>
       <c r="T33">
-        <v>8.3259954449161453e-006</v>
+        <v>8.8776686013738402e-006</v>
       </c>
       <c r="U33">
-        <v>1.4427003791448034e-005</v>
+        <v>1.4447385807352122e-005</v>
       </c>
       <c r="V33">
-        <v>3.4519637656894625e-005</v>
+        <v>3.4782637836399515e-005</v>
       </c>
       <c r="W33">
-        <v>3.8795294290065279e-007</v>
+        <v>1.7649093124842476e-007</v>
       </c>
       <c r="X33">
-        <v>-1.3249791183103383e-006</v>
+        <v>-9.425154959165183e-007</v>
       </c>
       <c r="Y33">
-        <v>0.00040987645764059989</v>
+        <v>0.00041428668137754205</v>
       </c>
       <c r="Z33">
-        <v>0.00040479041143994356</v>
+        <v>0.00040641750518664161</v>
       </c>
       <c r="AA33">
-        <v>0.00039900697455591333</v>
+        <v>0.00040221702041429538</v>
       </c>
       <c r="AB33">
-        <v>0.00039951455867291469</v>
+        <v>0.00040246512623406808</v>
       </c>
       <c r="AC33">
-        <v>0.00038978169103223313</v>
+        <v>0.00039179943560905937</v>
       </c>
       <c r="AD33">
-        <v>0.00040861820809942443</v>
+        <v>0.00041057887019088624</v>
       </c>
       <c r="AE33">
-        <v>0.00040571760000579103</v>
+        <v>0.0004090892446772405</v>
       </c>
       <c r="AF33">
-        <v>0.00041000969746578459</v>
+        <v>0.00041387307627423637</v>
       </c>
       <c r="AG33">
-        <v>0.0004084212065476715</v>
+        <v>0.00041253434547314986</v>
       </c>
       <c r="AH33">
-        <v>0.00076926884289510705</v>
+        <v>0.0007729677278278498</v>
       </c>
       <c r="AI33">
-        <v>0.0004103778226494192</v>
+        <v>0.00041499824345238876</v>
       </c>
       <c r="AJ33">
-        <v>2.96970150637902e-006</v>
+        <v>2.7865028299215273e-006</v>
       </c>
       <c r="AK33">
-        <v>-5.332695237151038e-006</v>
+        <v>-4.538648596813159e-006</v>
       </c>
       <c r="AL33">
-        <v>3.146092875455436e-006</v>
+        <v>-8.462715825752136e-008</v>
       </c>
       <c r="AM33">
-        <v>0.00016869511340951706</v>
+        <v>0.00017249589128194687</v>
       </c>
       <c r="AN33">
-        <v>0.00023400203970030614</v>
+        <v>0.00023851307056089224</v>
       </c>
       <c r="AO33">
-        <v>0.00014290736933831238</v>
+        <v>0.00012803572352893146</v>
       </c>
       <c r="AP33">
-        <v>-0.00046209418351103999</v>
+        <v>-0.00046673389497683981</v>
       </c>
     </row>
     <row r="34">
@@ -6020,127 +6020,127 @@
         <v>85</v>
       </c>
       <c r="B34" s="72">
-        <v>0.28175572728477655</v>
+        <v>0.28060543635414892</v>
       </c>
       <c r="C34">
-        <v>-1.0174540049415314e-005</v>
+        <v>-9.7779038769873102e-006</v>
       </c>
       <c r="D34">
-        <v>3.5088428050066597e-007</v>
+        <v>3.4736910851744101e-007</v>
       </c>
       <c r="E34">
-        <v>3.4501885691116846e-009</v>
+        <v>3.9104818461065424e-009</v>
       </c>
       <c r="F34">
-        <v>6.8854776226102087e-005</v>
+        <v>7.1280408559634646e-005</v>
       </c>
       <c r="G34">
-        <v>1.8023153806085828e-005</v>
+        <v>1.7602170952127087e-005</v>
       </c>
       <c r="H34">
-        <v>2.3312730076651867e-005</v>
+        <v>2.2409646081385571e-005</v>
       </c>
       <c r="I34">
-        <v>4.4014451753860031e-005</v>
+        <v>3.8792847057426592e-005</v>
       </c>
       <c r="J34">
-        <v>3.5460858449790355e-005</v>
+        <v>3.5860336554234106e-005</v>
       </c>
       <c r="K34">
-        <v>2.3489999480817464e-005</v>
+        <v>2.3418212669260713e-005</v>
       </c>
       <c r="L34">
-        <v>1.7788388526727555e-005</v>
+        <v>1.9037282360267316e-005</v>
       </c>
       <c r="M34">
-        <v>3.8221169844648232e-005</v>
+        <v>3.2704554498045669e-005</v>
       </c>
       <c r="N34">
-        <v>5.3788399565639399e-006</v>
+        <v>9.4080893280886835e-006</v>
       </c>
       <c r="O34">
-        <v>-1.9173835418372759e-006</v>
+        <v>-1.7795937795747689e-006</v>
       </c>
       <c r="P34">
-        <v>-1.5272398554458695e-005</v>
+        <v>-1.4621600892997667e-005</v>
       </c>
       <c r="Q34">
-        <v>-1.0377709720595437e-007</v>
+        <v>-1.2156571249125704e-007</v>
       </c>
       <c r="R34">
-        <v>5.0108727619009046e-007</v>
+        <v>5.2817943229680735e-007</v>
       </c>
       <c r="S34">
-        <v>1.9868658902414787e-005</v>
+        <v>2.7417248489577668e-005</v>
       </c>
       <c r="T34">
-        <v>2.9352020112786802e-005</v>
+        <v>3.6235179673801195e-005</v>
       </c>
       <c r="U34">
-        <v>4.640772163793782e-005</v>
+        <v>5.3166163607128929e-005</v>
       </c>
       <c r="V34">
-        <v>6.9940231673709132e-005</v>
+        <v>7.7002239468184925e-005</v>
       </c>
       <c r="W34">
-        <v>1.4606317956095557e-006</v>
+        <v>7.7853611095448686e-007</v>
       </c>
       <c r="X34">
-        <v>-5.6476806196630551e-007</v>
+        <v>-4.6636457997242499e-008</v>
       </c>
       <c r="Y34">
-        <v>0.00041247706124220739</v>
+        <v>0.00041709427058319958</v>
       </c>
       <c r="Z34">
-        <v>0.00040246657831222475</v>
+        <v>0.00040411990113430312</v>
       </c>
       <c r="AA34">
-        <v>0.00040284981305409914</v>
+        <v>0.0004061023004008492</v>
       </c>
       <c r="AB34">
-        <v>0.00040693389807052328</v>
+        <v>0.00040991897225836865</v>
       </c>
       <c r="AC34">
-        <v>0.00039214834421521659</v>
+        <v>0.00039404597248016057</v>
       </c>
       <c r="AD34">
-        <v>0.00041009797504808855</v>
+        <v>0.00041194588448983011</v>
       </c>
       <c r="AE34">
-        <v>0.00040704715099180121</v>
+        <v>0.00041035036161160413</v>
       </c>
       <c r="AF34">
-        <v>0.00041319782664332391</v>
+        <v>0.0004168902398503644</v>
       </c>
       <c r="AG34">
-        <v>0.00041077851285336317</v>
+        <v>0.00041487556343903912</v>
       </c>
       <c r="AH34">
-        <v>0.0004103778226494192</v>
+        <v>0.00041499824345238876</v>
       </c>
       <c r="AI34">
-        <v>0.00092616738198778221</v>
+        <v>0.00092962298546953839</v>
       </c>
       <c r="AJ34">
-        <v>2.9309246852941515e-006</v>
+        <v>2.7708520050134351e-006</v>
       </c>
       <c r="AK34">
-        <v>4.6612520583102488e-006</v>
+        <v>5.2156738524701036e-006</v>
       </c>
       <c r="AL34">
-        <v>4.6324993259750333e-006</v>
+        <v>1.214209449226135e-006</v>
       </c>
       <c r="AM34">
-        <v>0.00023107001498303396</v>
+        <v>0.00023420856069502499</v>
       </c>
       <c r="AN34">
-        <v>0.0002413676927090637</v>
+        <v>0.00024590886463394791</v>
       </c>
       <c r="AO34">
-        <v>0.00014427450403095847</v>
+        <v>0.00013010065579448129</v>
       </c>
       <c r="AP34">
-        <v>-0.00055256917704798623</v>
+        <v>-0.00056294214886482518</v>
       </c>
     </row>
     <row r="35">
@@ -6148,127 +6148,127 @@
         <v>86</v>
       </c>
       <c r="B35" s="74">
-        <v>0.013228459354692032</v>
+        <v>0.013083133075041005</v>
       </c>
       <c r="C35">
-        <v>-2.985291974450226e-007</v>
+        <v>-3.1743798909241021e-007</v>
       </c>
       <c r="D35">
-        <v>1.5091311052930837e-007</v>
+        <v>1.5688245878275313e-007</v>
       </c>
       <c r="E35">
-        <v>-1.900508073921277e-009</v>
+        <v>-1.9644458001874094e-009</v>
       </c>
       <c r="F35">
-        <v>1.5645417313077337e-006</v>
+        <v>1.5738251730468475e-006</v>
       </c>
       <c r="G35">
-        <v>1.4157003435898898e-006</v>
+        <v>1.4106773893571412e-006</v>
       </c>
       <c r="H35">
-        <v>1.6173194357219559e-006</v>
+        <v>1.6368308290256186e-006</v>
       </c>
       <c r="I35">
-        <v>2.255681235630283e-005</v>
+        <v>2.2679259329575945e-005</v>
       </c>
       <c r="J35">
-        <v>2.3340341326779234e-006</v>
+        <v>2.3520768482450057e-006</v>
       </c>
       <c r="K35">
-        <v>9.2265018167683617e-007</v>
+        <v>9.3933704155851876e-007</v>
       </c>
       <c r="L35">
-        <v>5.2689114875636364e-006</v>
+        <v>5.2562045490779694e-006</v>
       </c>
       <c r="M35">
-        <v>3.0302444350286345e-006</v>
+        <v>3.2718364608088947e-006</v>
       </c>
       <c r="N35">
-        <v>2.6266879176414622e-006</v>
+        <v>2.6034599843525184e-006</v>
       </c>
       <c r="O35">
-        <v>7.0245978427905105e-007</v>
+        <v>6.788492163280821e-007</v>
       </c>
       <c r="P35">
-        <v>3.3400301616756043e-006</v>
+        <v>3.3276879194391733e-006</v>
       </c>
       <c r="Q35">
-        <v>8.8780327392359743e-008</v>
+        <v>8.8811649832477704e-008</v>
       </c>
       <c r="R35">
-        <v>2.6339732187769672e-008</v>
+        <v>2.7045074420720516e-008</v>
       </c>
       <c r="S35">
-        <v>1.0781382630756852e-006</v>
+        <v>1.1528453879263243e-006</v>
       </c>
       <c r="T35">
-        <v>3.8870533986602547e-006</v>
+        <v>3.898773416640877e-006</v>
       </c>
       <c r="U35">
-        <v>3.4340576258321317e-006</v>
+        <v>3.4403792303629252e-006</v>
       </c>
       <c r="V35">
-        <v>2.4140240848483541e-006</v>
+        <v>2.4276581866449845e-006</v>
       </c>
       <c r="W35">
-        <v>-1.9805172918899198e-007</v>
+        <v>-1.9256891780659461e-007</v>
       </c>
       <c r="X35">
-        <v>5.867587182230277e-007</v>
+        <v>5.5388452563067605e-007</v>
       </c>
       <c r="Y35">
-        <v>7.8097697922861869e-007</v>
+        <v>6.5548127510310155e-007</v>
       </c>
       <c r="Z35">
-        <v>9.7556327315862015e-007</v>
+        <v>9.4432640690916946e-007</v>
       </c>
       <c r="AA35">
-        <v>3.5738702634457672e-007</v>
+        <v>2.4569732034004609e-007</v>
       </c>
       <c r="AB35">
-        <v>8.915585662378764e-007</v>
+        <v>7.77925716806385e-007</v>
       </c>
       <c r="AC35">
-        <v>-1.1427480599997903e-007</v>
+        <v>-1.9800387870839688e-007</v>
       </c>
       <c r="AD35">
-        <v>-8.0348953933334672e-007</v>
+        <v>-8.9319740562460886e-007</v>
       </c>
       <c r="AE35">
-        <v>1.5620503633094324e-006</v>
+        <v>1.4537093930402508e-006</v>
       </c>
       <c r="AF35">
-        <v>2.0107146316127575e-006</v>
+        <v>1.8850615576936007e-006</v>
       </c>
       <c r="AG35">
-        <v>8.7383672120598286e-007</v>
+        <v>7.6937399234767938e-007</v>
       </c>
       <c r="AH35">
-        <v>2.96970150637902e-006</v>
+        <v>2.7865028299215273e-006</v>
       </c>
       <c r="AI35">
-        <v>2.9309246852941515e-006</v>
+        <v>2.7708520050134351e-006</v>
       </c>
       <c r="AJ35">
-        <v>3.5433722395997472e-006</v>
+        <v>3.5414561795850307e-006</v>
       </c>
       <c r="AK35">
-        <v>-1.8398965982657348e-005</v>
+        <v>-1.8380290140130309e-005</v>
       </c>
       <c r="AL35">
-        <v>-2.2548900787992684e-005</v>
+        <v>-2.2369101632241308e-005</v>
       </c>
       <c r="AM35">
-        <v>8.4806879413628725e-007</v>
+        <v>7.137559721317617e-007</v>
       </c>
       <c r="AN35">
-        <v>-1.3393559542826087e-006</v>
+        <v>-1.4695251591768151e-006</v>
       </c>
       <c r="AO35">
-        <v>3.3801270793580753e-007</v>
+        <v>-1.5047619369697972e-006</v>
       </c>
       <c r="AP35">
-        <v>-6.8008573192134521e-005</v>
+        <v>-6.7996656731512858e-005</v>
       </c>
     </row>
     <row r="36">
@@ -6276,127 +6276,127 @@
         <v>87</v>
       </c>
       <c r="B36" s="76">
-        <v>-0.018587116158083353</v>
+        <v>-0.017638527149721358</v>
       </c>
       <c r="C36">
-        <v>7.9851626278660644e-009</v>
+        <v>1.0252474378725544e-007</v>
       </c>
       <c r="D36">
-        <v>-5.4994028780463106e-007</v>
+        <v>-6.0799483160285996e-007</v>
       </c>
       <c r="E36">
-        <v>3.560173271636186e-009</v>
+        <v>4.151541350872783e-009</v>
       </c>
       <c r="F36">
-        <v>1.2335767069761425e-005</v>
+        <v>1.2447682856694151e-005</v>
       </c>
       <c r="G36">
-        <v>-1.1323579989716822e-005</v>
+        <v>-1.1154389961679917e-005</v>
       </c>
       <c r="H36">
-        <v>-2.3316837823088069e-006</v>
+        <v>-2.3988147301926446e-006</v>
       </c>
       <c r="I36">
-        <v>-0.00014228772999531669</v>
+        <v>-0.00014277536773756291</v>
       </c>
       <c r="J36">
-        <v>1.1360805555929623e-005</v>
+        <v>1.1131223218453481e-005</v>
       </c>
       <c r="K36">
-        <v>-9.9750936820527652e-006</v>
+        <v>-1.0164209893933878e-005</v>
       </c>
       <c r="L36">
-        <v>-2.7178493755894633e-005</v>
+        <v>-2.7212311970640865e-005</v>
       </c>
       <c r="M36">
-        <v>-3.5781360624717149e-005</v>
+        <v>-3.799216711831233e-005</v>
       </c>
       <c r="N36">
-        <v>-1.0806355827676414e-005</v>
+        <v>-1.1248726136713914e-005</v>
       </c>
       <c r="O36">
-        <v>-4.5863169187086576e-006</v>
+        <v>-4.5291560255274032e-006</v>
       </c>
       <c r="P36">
-        <v>-9.7050752742837386e-006</v>
+        <v>-9.7216222889167215e-006</v>
       </c>
       <c r="Q36">
-        <v>3.614481897566153e-007</v>
+        <v>3.6270036049158591e-007</v>
       </c>
       <c r="R36">
-        <v>-2.0258889907359599e-007</v>
+        <v>-2.0534660222153853e-007</v>
       </c>
       <c r="S36">
-        <v>-4.1539001194528258e-006</v>
+        <v>-6.2585370296515054e-006</v>
       </c>
       <c r="T36">
-        <v>-2.453689849552391e-005</v>
+        <v>-2.5827058157672748e-005</v>
       </c>
       <c r="U36">
-        <v>-1.5781975891541595e-005</v>
+        <v>-1.7087252851770545e-005</v>
       </c>
       <c r="V36">
-        <v>-1.892728249796603e-005</v>
+        <v>-2.0360900594176093e-005</v>
       </c>
       <c r="W36">
-        <v>1.1820313664072877e-006</v>
+        <v>1.2163977789425356e-006</v>
       </c>
       <c r="X36">
-        <v>-2.5243743447481076e-006</v>
+        <v>-2.3213266837219249e-006</v>
       </c>
       <c r="Y36">
-        <v>2.5720461149897583e-007</v>
+        <v>6.9898523339699471e-007</v>
       </c>
       <c r="Z36">
-        <v>1.5895729135248509e-005</v>
+        <v>1.5746708165548291e-005</v>
       </c>
       <c r="AA36">
-        <v>1.8454110273557358e-005</v>
+        <v>1.8898305474517817e-005</v>
       </c>
       <c r="AB36">
-        <v>1.9508960761846786e-005</v>
+        <v>1.9907112257510224e-005</v>
       </c>
       <c r="AC36">
-        <v>2.1079442842292824e-005</v>
+        <v>2.1456337586683742e-005</v>
       </c>
       <c r="AD36">
-        <v>2.102238822590338e-005</v>
+        <v>2.1399712591545073e-005</v>
       </c>
       <c r="AE36">
-        <v>2.5913115128783599e-006</v>
+        <v>2.9675894168048218e-006</v>
       </c>
       <c r="AF36">
-        <v>7.4435194917914672e-006</v>
+        <v>7.9744394407139981e-006</v>
       </c>
       <c r="AG36">
-        <v>1.4370636222700281e-005</v>
+        <v>1.4735717183226086e-005</v>
       </c>
       <c r="AH36">
-        <v>-5.332695237151038e-006</v>
+        <v>-4.538648596813159e-006</v>
       </c>
       <c r="AI36">
-        <v>4.6612520583102488e-006</v>
+        <v>5.2156738524701036e-006</v>
       </c>
       <c r="AJ36">
-        <v>-1.8398965982657348e-005</v>
+        <v>-1.8380290140130309e-005</v>
       </c>
       <c r="AK36">
-        <v>0.00064527527292623603</v>
+        <v>0.00064580673838764071</v>
       </c>
       <c r="AL36">
-        <v>9.4497147800144831e-005</v>
+        <v>9.3163147235691022e-005</v>
       </c>
       <c r="AM36">
-        <v>-6.587466366764688e-006</v>
+        <v>-6.0094006295828155e-006</v>
       </c>
       <c r="AN36">
-        <v>3.192857456710331e-005</v>
+        <v>3.2502003147555006e-005</v>
       </c>
       <c r="AO36">
-        <v>-9.4099733682754505e-006</v>
+        <v>3.26590340601905e-006</v>
       </c>
       <c r="AP36">
-        <v>0.00027552769280060266</v>
+        <v>0.00027739917830970186</v>
       </c>
     </row>
     <row r="37">
@@ -6404,127 +6404,127 @@
         <v>88</v>
       </c>
       <c r="B37" s="78">
-        <v>-0.063388716886461874</v>
+        <v>-0.062389793911917943</v>
       </c>
       <c r="C37">
-        <v>1.2059758058550897e-006</v>
+        <v>6.2102916537237028e-007</v>
       </c>
       <c r="D37">
-        <v>-1.1482281470692416e-006</v>
+        <v>-1.4170193888767322e-006</v>
       </c>
       <c r="E37">
-        <v>1.0019121238380966e-008</v>
+        <v>1.246790200974852e-008</v>
       </c>
       <c r="F37">
-        <v>3.5035060547663934e-007</v>
+        <v>-5.3541140620620177e-007</v>
       </c>
       <c r="G37">
-        <v>-2.5799005592011302e-006</v>
+        <v>-1.926882591517733e-006</v>
       </c>
       <c r="H37">
-        <v>-8.7386652357140472e-006</v>
+        <v>-9.3873073656590952e-006</v>
       </c>
       <c r="I37">
-        <v>-0.00014501536010140046</v>
+        <v>-0.0001454493643495981</v>
       </c>
       <c r="J37">
-        <v>-7.9025944442600579e-006</v>
+        <v>-8.2706886212612271e-006</v>
       </c>
       <c r="K37">
-        <v>-6.2837281387818613e-006</v>
+        <v>-6.0154365222669341e-006</v>
       </c>
       <c r="L37">
-        <v>-2.8141660298203816e-005</v>
+        <v>-2.8850179693937051e-005</v>
       </c>
       <c r="M37">
-        <v>-1.6341761701717682e-005</v>
+        <v>-2.0918834664780453e-005</v>
       </c>
       <c r="N37">
-        <v>-1.6468293489840983e-005</v>
+        <v>-1.7028896508459307e-005</v>
       </c>
       <c r="O37">
-        <v>1.1379092070620814e-005</v>
+        <v>1.2447718701449592e-005</v>
       </c>
       <c r="P37">
-        <v>4.4163868431970525e-006</v>
+        <v>5.3402235887112253e-006</v>
       </c>
       <c r="Q37">
-        <v>1.0169556615659325e-006</v>
+        <v>9.7319857190046152e-007</v>
       </c>
       <c r="R37">
-        <v>-4.0625088754614468e-007</v>
+        <v>-3.8593377822984748e-007</v>
       </c>
       <c r="S37">
-        <v>-6.1262494044641986e-006</v>
+        <v>-5.9751198377596357e-006</v>
       </c>
       <c r="T37">
-        <v>-3.5539846582901681e-005</v>
+        <v>-3.3329339649620785e-005</v>
       </c>
       <c r="U37">
-        <v>-2.5652903721933833e-005</v>
+        <v>-2.5377564072426325e-005</v>
       </c>
       <c r="V37">
-        <v>-7.4461145913201461e-006</v>
+        <v>-7.2224181939856625e-006</v>
       </c>
       <c r="W37">
-        <v>9.4560513080594134e-007</v>
+        <v>8.626441418769431e-007</v>
       </c>
       <c r="X37">
-        <v>9.4258886698602917e-006</v>
+        <v>8.8322516702161742e-006</v>
       </c>
       <c r="Y37">
-        <v>1.1937203098798893e-005</v>
+        <v>8.2967756253637574e-006</v>
       </c>
       <c r="Z37">
-        <v>5.383221627001473e-005</v>
+        <v>4.9342469135271547e-005</v>
       </c>
       <c r="AA37">
-        <v>3.8222550525919666e-005</v>
+        <v>3.4390660047410846e-005</v>
       </c>
       <c r="AB37">
-        <v>1.725991040074047e-005</v>
+        <v>1.3392342018076178e-005</v>
       </c>
       <c r="AC37">
-        <v>3.4074844026435337e-005</v>
+        <v>3.0367833758607052e-005</v>
       </c>
       <c r="AD37">
-        <v>2.6845263593681731e-005</v>
+        <v>2.2972002120995392e-005</v>
       </c>
       <c r="AE37">
-        <v>1.821206590629009e-005</v>
+        <v>1.4465085653334961e-005</v>
       </c>
       <c r="AF37">
-        <v>1.5680701171155075e-005</v>
+        <v>1.2085275635836967e-005</v>
       </c>
       <c r="AG37">
-        <v>1.5243296623434048e-005</v>
+        <v>1.1350789722147744e-005</v>
       </c>
       <c r="AH37">
-        <v>3.146092875455436e-006</v>
+        <v>-8.462715825752136e-008</v>
       </c>
       <c r="AI37">
-        <v>4.6324993259750333e-006</v>
+        <v>1.214209449226135e-006</v>
       </c>
       <c r="AJ37">
-        <v>-2.2548900787992684e-005</v>
+        <v>-2.2369101632241308e-005</v>
       </c>
       <c r="AK37">
-        <v>9.4497147800144831e-005</v>
+        <v>9.3163147235691022e-005</v>
       </c>
       <c r="AL37">
-        <v>0.00073478844000421644</v>
+        <v>0.00073160147061535345</v>
       </c>
       <c r="AM37">
-        <v>-2.7724591935134339e-006</v>
+        <v>-3.4154666028344074e-006</v>
       </c>
       <c r="AN37">
-        <v>1.3520214865822094e-005</v>
+        <v>1.1880160152172829e-005</v>
       </c>
       <c r="AO37">
-        <v>-1.3526267059664021e-006</v>
+        <v>1.164370285528417e-005</v>
       </c>
       <c r="AP37">
-        <v>0.00030299564549445896</v>
+        <v>0.00031112168285836933</v>
       </c>
     </row>
     <row r="38">
@@ -6532,127 +6532,127 @@
         <v>89</v>
       </c>
       <c r="B38" s="80">
-        <v>0.17303184417859624</v>
+        <v>0.17200382683083287</v>
       </c>
       <c r="C38">
-        <v>-6.2081679921257938e-006</v>
+        <v>-6.0272879253144178e-006</v>
       </c>
       <c r="D38">
-        <v>-1.0175938390587989e-007</v>
+        <v>-6.4609638909353189e-008</v>
       </c>
       <c r="E38">
-        <v>1.0678417267543154e-008</v>
+        <v>1.0551217249691462e-008</v>
       </c>
       <c r="F38">
-        <v>6.3632962067957435e-005</v>
+        <v>6.5448510151690979e-005</v>
       </c>
       <c r="G38">
-        <v>7.4097477972990687e-006</v>
+        <v>6.9502378940695622e-006</v>
       </c>
       <c r="H38">
-        <v>-7.771647279718557e-006</v>
+        <v>-8.433631575797539e-006</v>
       </c>
       <c r="I38">
-        <v>-4.2738136413975883e-005</v>
+        <v>-4.7001705974134234e-005</v>
       </c>
       <c r="J38">
-        <v>-4.231082383534469e-005</v>
+        <v>-4.2277869584417781e-005</v>
       </c>
       <c r="K38">
-        <v>1.1205716974278964e-005</v>
+        <v>1.0961963830670093e-005</v>
       </c>
       <c r="L38">
-        <v>1.7175999031811105e-005</v>
+        <v>1.7773987431751986e-005</v>
       </c>
       <c r="M38">
-        <v>-1.7439444218795815e-005</v>
+        <v>-1.9804278269498104e-005</v>
       </c>
       <c r="N38">
-        <v>-1.0046907095243447e-005</v>
+        <v>-7.397947347535539e-006</v>
       </c>
       <c r="O38">
-        <v>4.5725391578932935e-005</v>
+        <v>4.6125946278338737e-005</v>
       </c>
       <c r="P38">
-        <v>3.6774711517777067e-005</v>
+        <v>3.7515092635861082e-005</v>
       </c>
       <c r="Q38">
-        <v>-3.390646337551449e-007</v>
+        <v>-3.4128546557224585e-007</v>
       </c>
       <c r="R38">
-        <v>3.3960255120056272e-007</v>
+        <v>3.5098759074297303e-007</v>
       </c>
       <c r="S38">
-        <v>-8.5635818259003986e-006</v>
+        <v>-3.6858901044361917e-006</v>
       </c>
       <c r="T38">
-        <v>7.5647183695575762e-006</v>
+        <v>1.1509599744098149e-005</v>
       </c>
       <c r="U38">
-        <v>2.6541540425249272e-005</v>
+        <v>3.051718150137985e-005</v>
       </c>
       <c r="V38">
-        <v>3.3008446136949601e-005</v>
+        <v>3.7475255665174771e-005</v>
       </c>
       <c r="W38">
-        <v>2.7048530090106043e-006</v>
+        <v>2.3578612931584824e-006</v>
       </c>
       <c r="X38">
-        <v>6.4065876926698307e-006</v>
+        <v>6.9741712220176412e-006</v>
       </c>
       <c r="Y38">
-        <v>0.00017700709783017191</v>
+        <v>0.00018070475351414958</v>
       </c>
       <c r="Z38">
-        <v>0.00014950126733785364</v>
+        <v>0.00015186334166978537</v>
       </c>
       <c r="AA38">
-        <v>0.00014463971842960173</v>
+        <v>0.0001473083131949232</v>
       </c>
       <c r="AB38">
-        <v>0.00015655778710017007</v>
+        <v>0.00015893673537363645</v>
       </c>
       <c r="AC38">
-        <v>0.00012197508485422148</v>
+        <v>0.00012369951560224293</v>
       </c>
       <c r="AD38">
-        <v>0.00016229963487172141</v>
+        <v>0.00016395862951943711</v>
       </c>
       <c r="AE38">
-        <v>0.00016410635115775776</v>
+        <v>0.00016687029897799788</v>
       </c>
       <c r="AF38">
-        <v>0.00017226022878756063</v>
+        <v>0.00017542379017838528</v>
       </c>
       <c r="AG38">
-        <v>0.00017518403869338112</v>
+        <v>0.00017853000600238651</v>
       </c>
       <c r="AH38">
-        <v>0.00016869511340951706</v>
+        <v>0.00017249589128194687</v>
       </c>
       <c r="AI38">
-        <v>0.00023107001498303396</v>
+        <v>0.00023420856069502499</v>
       </c>
       <c r="AJ38">
-        <v>8.4806879413628725e-007</v>
+        <v>7.137559721317617e-007</v>
       </c>
       <c r="AK38">
-        <v>-6.587466366764688e-006</v>
+        <v>-6.0094006295828155e-006</v>
       </c>
       <c r="AL38">
-        <v>-2.7724591935134339e-006</v>
+        <v>-3.4154666028344074e-006</v>
       </c>
       <c r="AM38">
-        <v>0.00054588730332305797</v>
+        <v>0.00054832501936626999</v>
       </c>
       <c r="AN38">
-        <v>0.00013312404752774187</v>
+        <v>0.00013673656820282365</v>
       </c>
       <c r="AO38">
-        <v>0.00010116980191323943</v>
+        <v>9.5811828314399595e-005</v>
       </c>
       <c r="AP38">
-        <v>-0.00027115502607457395</v>
+        <v>-0.00027942616692718452</v>
       </c>
     </row>
     <row r="39">
@@ -6660,127 +6660,127 @@
         <v>90</v>
       </c>
       <c r="B39" s="82">
-        <v>-0.1915780816538962</v>
+        <v>-0.19286980791754091</v>
       </c>
       <c r="C39">
-        <v>-3.4747089969595519e-006</v>
+        <v>-3.6147826383296928e-006</v>
       </c>
       <c r="D39">
-        <v>-1.4500395939382504e-006</v>
+        <v>-1.469260996366889e-006</v>
       </c>
       <c r="E39">
-        <v>1.6089816134282093e-008</v>
+        <v>1.6596955131367341e-008</v>
       </c>
       <c r="F39">
-        <v>6.7404470227266461e-005</v>
+        <v>6.9564036973654214e-005</v>
       </c>
       <c r="G39">
-        <v>-9.1115693164547392e-006</v>
+        <v>-9.5557461050334541e-006</v>
       </c>
       <c r="H39">
-        <v>1.2113688920050114e-005</v>
+        <v>1.1526790580507809e-005</v>
       </c>
       <c r="I39">
-        <v>-0.00014641317021501401</v>
+        <v>-0.00015171131348329776</v>
       </c>
       <c r="J39">
-        <v>1.0386642045536777e-005</v>
+        <v>1.0098846413304107e-005</v>
       </c>
       <c r="K39">
-        <v>-1.1552803012544277e-005</v>
+        <v>-1.2556643183163081e-005</v>
       </c>
       <c r="L39">
-        <v>2.8885428344414387e-005</v>
+        <v>2.8824302606118271e-005</v>
       </c>
       <c r="M39">
-        <v>-3.0778599111392355e-005</v>
+        <v>-3.5403584024942597e-005</v>
       </c>
       <c r="N39">
-        <v>1.4101516176364055e-005</v>
+        <v>1.5185185284556901e-005</v>
       </c>
       <c r="O39">
-        <v>1.9998802726076549e-005</v>
+        <v>2.0529676296099356e-005</v>
       </c>
       <c r="P39">
-        <v>4.5076519039024244e-005</v>
+        <v>4.5984874304310914e-005</v>
       </c>
       <c r="Q39">
-        <v>-4.0750625793255453e-007</v>
+        <v>-4.0217974034124324e-007</v>
       </c>
       <c r="R39">
-        <v>-1.5489468733880459e-007</v>
+        <v>-1.33727861083134e-007</v>
       </c>
       <c r="S39">
-        <v>1.2566739689128892e-005</v>
+        <v>1.2118155934761883e-005</v>
       </c>
       <c r="T39">
-        <v>-5.0209511119663148e-007</v>
+        <v>-3.2634341447452045e-007</v>
       </c>
       <c r="U39">
-        <v>1.4539504964501682e-005</v>
+        <v>1.4538127790085346e-005</v>
       </c>
       <c r="V39">
-        <v>4.4114818463522588e-005</v>
+        <v>4.4510376989898438e-005</v>
       </c>
       <c r="W39">
-        <v>3.0858681107736029e-006</v>
+        <v>2.9739608570318895e-006</v>
       </c>
       <c r="X39">
-        <v>1.8766039443364292e-005</v>
+        <v>1.9422655464468162e-005</v>
       </c>
       <c r="Y39">
-        <v>0.00024681512259456151</v>
+        <v>0.00025115565359353653</v>
       </c>
       <c r="Z39">
-        <v>0.00022154933314881027</v>
+        <v>0.00022408046260449435</v>
       </c>
       <c r="AA39">
-        <v>0.00021964192834750409</v>
+        <v>0.0002228190962851678</v>
       </c>
       <c r="AB39">
-        <v>0.00021886736241679287</v>
+        <v>0.00022180168910254964</v>
       </c>
       <c r="AC39">
-        <v>0.00018941544679752483</v>
+        <v>0.00019148442444948935</v>
       </c>
       <c r="AD39">
-        <v>0.00022654221276478481</v>
+        <v>0.00022854862851508703</v>
       </c>
       <c r="AE39">
-        <v>0.00022412688243907109</v>
+        <v>0.00022748870404012785</v>
       </c>
       <c r="AF39">
-        <v>0.00023501927660626938</v>
+        <v>0.00023889097934287059</v>
       </c>
       <c r="AG39">
-        <v>0.00023665634150445462</v>
+        <v>0.00024066480240021588</v>
       </c>
       <c r="AH39">
-        <v>0.00023400203970030614</v>
+        <v>0.00023851307056089224</v>
       </c>
       <c r="AI39">
-        <v>0.0002413676927090637</v>
+        <v>0.00024590886463394791</v>
       </c>
       <c r="AJ39">
-        <v>-1.3393559542826087e-006</v>
+        <v>-1.4695251591768151e-006</v>
       </c>
       <c r="AK39">
-        <v>3.192857456710331e-005</v>
+        <v>3.2502003147555006e-005</v>
       </c>
       <c r="AL39">
-        <v>1.3520214865822094e-005</v>
+        <v>1.1880160152172829e-005</v>
       </c>
       <c r="AM39">
-        <v>0.00013312404752774187</v>
+        <v>0.00013673656820282365</v>
       </c>
       <c r="AN39">
-        <v>0.0012555221080445939</v>
+        <v>0.0012604376619608933</v>
       </c>
       <c r="AO39">
-        <v>0.00011860000608704958</v>
+        <v>0.00011351467614629119</v>
       </c>
       <c r="AP39">
-        <v>-0.00022183921240605237</v>
+        <v>-0.00022644971008292669</v>
       </c>
     </row>
     <row r="40">
@@ -6788,127 +6788,127 @@
         <v>91</v>
       </c>
       <c r="B40" s="84">
-        <v>0.038269845798942409</v>
+        <v>-0.017290424892321816</v>
       </c>
       <c r="C40">
-        <v>-4.4152009417706005e-006</v>
+        <v>-1.1315224187012664e-005</v>
       </c>
       <c r="D40">
-        <v>9.3602296376210984e-007</v>
+        <v>3.3872998367661739e-007</v>
       </c>
       <c r="E40">
-        <v>-4.803412033318179e-009</v>
+        <v>3.3415540503812032e-010</v>
       </c>
       <c r="F40">
-        <v>-3.5786210842447179e-005</v>
+        <v>8.468209459420187e-006</v>
       </c>
       <c r="G40">
-        <v>3.1934394070982398e-007</v>
+        <v>-8.0727329784815397e-006</v>
       </c>
       <c r="H40">
-        <v>-9.8657449106362817e-007</v>
+        <v>-7.6326370123682531e-006</v>
       </c>
       <c r="I40">
-        <v>-6.1528399281008617e-005</v>
+        <v>-0.00010447583529184955</v>
       </c>
       <c r="J40">
-        <v>-6.97413526769939e-007</v>
+        <v>-3.8224490277561176e-006</v>
       </c>
       <c r="K40">
-        <v>1.3321334298249351e-006</v>
+        <v>-1.5090125322283956e-005</v>
       </c>
       <c r="L40">
-        <v>-1.947745705359769e-005</v>
+        <v>-1.9043569434301118e-005</v>
       </c>
       <c r="M40">
-        <v>-2.1646718503318124e-005</v>
+        <v>-4.6047411686258612e-005</v>
       </c>
       <c r="N40">
-        <v>1.160966847812869e-005</v>
+        <v>1.9187239347263381e-005</v>
       </c>
       <c r="O40">
-        <v>3.0683959162420473e-005</v>
+        <v>2.7190897407220904e-005</v>
       </c>
       <c r="P40">
-        <v>2.8601821417423093e-005</v>
+        <v>2.9574302848604144e-005</v>
       </c>
       <c r="Q40">
-        <v>3.3972148556573861e-007</v>
+        <v>4.0115930129169372e-007</v>
       </c>
       <c r="R40">
-        <v>-6.1532563276367186e-008</v>
+        <v>2.1600337069519834e-007</v>
       </c>
       <c r="S40">
-        <v>1.9129736764673521e-005</v>
+        <v>-3.5281111989815929e-006</v>
       </c>
       <c r="T40">
-        <v>2.3044683965337172e-005</v>
+        <v>-4.7042788227017037e-007</v>
       </c>
       <c r="U40">
-        <v>3.6210550104679617e-005</v>
+        <v>5.734976349723803e-006</v>
       </c>
       <c r="V40">
-        <v>3.6743182181446521e-005</v>
+        <v>1.7346720579089567e-005</v>
       </c>
       <c r="W40">
-        <v>1.0200549164567093e-006</v>
+        <v>1.6469883503758496e-006</v>
       </c>
       <c r="X40">
-        <v>2.1591863735965641e-005</v>
+        <v>2.1788446848683624e-005</v>
       </c>
       <c r="Y40">
-        <v>0.00014944660506991845</v>
+        <v>0.00012840022015475836</v>
       </c>
       <c r="Z40">
-        <v>0.00013292669372406125</v>
+        <v>0.0001138777539698932</v>
       </c>
       <c r="AA40">
-        <v>0.00014720638389864566</v>
+        <v>0.0001109546980809342</v>
       </c>
       <c r="AB40">
-        <v>0.00015085968648812846</v>
+        <v>0.00011002647308434358</v>
       </c>
       <c r="AC40">
-        <v>0.00011494100030006665</v>
+        <v>8.0419854247972331e-005</v>
       </c>
       <c r="AD40">
-        <v>0.00012421927604358422</v>
+        <v>8.5360618158683728e-005</v>
       </c>
       <c r="AE40">
-        <v>0.00012971396197030571</v>
+        <v>0.00010526941521295897</v>
       </c>
       <c r="AF40">
-        <v>0.0001379532351314649</v>
+        <v>0.00011467566128293916</v>
       </c>
       <c r="AG40">
-        <v>0.00012940215879981757</v>
+        <v>0.00011440468100020527</v>
       </c>
       <c r="AH40">
-        <v>0.00014290736933831238</v>
+        <v>0.00012803572352893146</v>
       </c>
       <c r="AI40">
-        <v>0.00014427450403095847</v>
+        <v>0.00013010065579448129</v>
       </c>
       <c r="AJ40">
-        <v>3.3801270793580753e-007</v>
+        <v>-1.5047619369697972e-006</v>
       </c>
       <c r="AK40">
-        <v>-9.4099733682754505e-006</v>
+        <v>3.26590340601905e-006</v>
       </c>
       <c r="AL40">
-        <v>-1.3526267059664021e-006</v>
+        <v>1.164370285528417e-005</v>
       </c>
       <c r="AM40">
-        <v>0.00010116980191323943</v>
+        <v>9.5811828314399595e-005</v>
       </c>
       <c r="AN40">
-        <v>0.00011860000608704958</v>
+        <v>0.00011351467614629119</v>
       </c>
       <c r="AO40">
-        <v>0.0025941025081516744</v>
+        <v>0.0013144800168360031</v>
       </c>
       <c r="AP40">
-        <v>-0.00027443189328874858</v>
+        <v>-0.00019425499922096214</v>
       </c>
     </row>
     <row r="41">
@@ -6916,127 +6916,127 @@
         <v>92</v>
       </c>
       <c r="B41" s="86">
-        <v>-2.667042238656598</v>
+        <v>-2.6634817717930104</v>
       </c>
       <c r="C41">
-        <v>-2.8220416855022191e-005</v>
+        <v>-2.7821092744956907e-005</v>
       </c>
       <c r="D41">
-        <v>-9.8671875001025863e-005</v>
+        <v>-9.8458947539668295e-005</v>
       </c>
       <c r="E41">
-        <v>8.9165088657926699e-007</v>
+        <v>8.8918417274773365e-007</v>
       </c>
       <c r="F41">
-        <v>-0.00075616140594718384</v>
+        <v>-0.00076007757052674028</v>
       </c>
       <c r="G41">
-        <v>-0.00039344498934904584</v>
+        <v>-0.00039332339225611399</v>
       </c>
       <c r="H41">
-        <v>-0.00035824355492082734</v>
+        <v>-0.00035631449841888856</v>
       </c>
       <c r="I41">
-        <v>-0.0010938037451240403</v>
+        <v>-0.0010855624412434099</v>
       </c>
       <c r="J41">
-        <v>-0.00048214491719598599</v>
+        <v>-0.00048244303525332884</v>
       </c>
       <c r="K41">
-        <v>-0.00065926475285955596</v>
+        <v>-0.00065965859942462618</v>
       </c>
       <c r="L41">
-        <v>-0.00064653796293402232</v>
+        <v>-0.00064838574052548665</v>
       </c>
       <c r="M41">
-        <v>-0.00095122069122997963</v>
+        <v>-0.00094498820547280805</v>
       </c>
       <c r="N41">
-        <v>-0.00050292423659015553</v>
+        <v>-0.00051030646215106609</v>
       </c>
       <c r="O41">
-        <v>-0.00022441621158738868</v>
+        <v>-0.00022585421420360242</v>
       </c>
       <c r="P41">
-        <v>-0.00030096416528898717</v>
+        <v>-0.00030275701991135681</v>
       </c>
       <c r="Q41">
-        <v>-1.6336716856193764e-005</v>
+        <v>-1.6299109273449739e-005</v>
       </c>
       <c r="R41">
-        <v>-1.6496895911156737e-005</v>
+        <v>-1.6582194447138253e-005</v>
       </c>
       <c r="S41">
-        <v>-0.00040000989191455924</v>
+        <v>-0.00040633742823793686</v>
       </c>
       <c r="T41">
-        <v>-0.0005143387036634008</v>
+        <v>-0.00052252182929615006</v>
       </c>
       <c r="U41">
-        <v>-0.00057572721070874185</v>
+        <v>-0.00058379962659959412</v>
       </c>
       <c r="V41">
-        <v>-0.00064791243872289531</v>
+        <v>-0.0006565445349873873</v>
       </c>
       <c r="W41">
-        <v>4.684048526878996e-005</v>
+        <v>4.8008945201309005e-005</v>
       </c>
       <c r="X41">
-        <v>-4.6217836040980188e-005</v>
+        <v>-4.6351308374785374e-005</v>
       </c>
       <c r="Y41">
-        <v>-0.00042758302851905267</v>
+        <v>-0.00043234322940732817</v>
       </c>
       <c r="Z41">
-        <v>-0.00048767552068101878</v>
+        <v>-0.00048679327927524124</v>
       </c>
       <c r="AA41">
-        <v>-0.00047875571207210146</v>
+        <v>-0.00048107354296419785</v>
       </c>
       <c r="AB41">
-        <v>-0.00047668382589024849</v>
+        <v>-0.00047687124664680088</v>
       </c>
       <c r="AC41">
-        <v>-0.00044221349977124745</v>
+        <v>-0.00044166285513180223</v>
       </c>
       <c r="AD41">
-        <v>-0.00043585348605913173</v>
+        <v>-0.00043526500217888137</v>
       </c>
       <c r="AE41">
-        <v>-0.00048879068276028138</v>
+        <v>-0.00049071959395017651</v>
       </c>
       <c r="AF41">
-        <v>-0.00048602704067803666</v>
+        <v>-0.00048580918582485618</v>
       </c>
       <c r="AG41">
-        <v>-0.00052368624413414713</v>
+        <v>-0.00052711606136422783</v>
       </c>
       <c r="AH41">
-        <v>-0.00046209418351103999</v>
+        <v>-0.00046673389497683981</v>
       </c>
       <c r="AI41">
-        <v>-0.00055256917704798623</v>
+        <v>-0.00056294214886482518</v>
       </c>
       <c r="AJ41">
-        <v>-6.8008573192134521e-005</v>
+        <v>-6.7996656731512858e-005</v>
       </c>
       <c r="AK41">
-        <v>0.00027552769280060266</v>
+        <v>0.00027739917830970186</v>
       </c>
       <c r="AL41">
-        <v>0.00030299564549445896</v>
+        <v>0.00031112168285836933</v>
       </c>
       <c r="AM41">
-        <v>-0.00027115502607457395</v>
+        <v>-0.00027942616692718452</v>
       </c>
       <c r="AN41">
-        <v>-0.00022183921240605237</v>
+        <v>-0.00022644971008292669</v>
       </c>
       <c r="AO41">
-        <v>-0.00027443189328874858</v>
+        <v>-0.00019425499922096214</v>
       </c>
       <c r="AP41">
-        <v>0.0068267094943630039</v>
+        <v>0.0068363696172971406</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="100">
   <si>
     <t>Description:</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
   </si>
   <si>
-    <t>Last edit: 1 July 2025 DP</t>
+    <t>Last edit: 4 Nov 2025 DP</t>
   </si>
   <si>
     <t>Process:</t>
@@ -35,7 +35,7 @@
     <t>HO1a</t>
   </si>
   <si>
-    <t>Probit regression estimates of the probability of being a home owner, aged 18+</t>
+    <t>Probit regression estimates of the probability of being a home owner, benefit unit heads aged 18+</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -44,7 +44,10 @@
     <t>Have combined dhhtp_c4 and lessp_c3 into a single variable with 8 categories, dhhtp_c8</t>
   </si>
   <si>
-    <t>Added lagged home ownership, replaced dhe with dhe_pcs and dhe_mcs, added ethnicity (dot) and covid dummies (y2020 2021)</t>
+    <t>Added lagged home ownership, replaced dhe with dhe_pcs and dhe_mcs, added ethnicity (dot) and covid dummies (y2020, y2021)</t>
+  </si>
+  <si>
+    <t>Re-estimated process at benefit unit level using heads defined by highest personal non-benefit income, or age, or lowest idperson</t>
   </si>
   <si>
     <t>Goodness of fit</t>
@@ -176,6 +179,9 @@
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>COEFFICIENT</t>
+  </si>
+  <si>
     <t>Dgn</t>
   </si>
   <si>
@@ -218,10 +224,10 @@
     <t>Deh_c3_Low</t>
   </si>
   <si>
-    <t>Dhe_mcs</t>
-  </si>
-  <si>
-    <t>Dhe_pcs</t>
+    <t>Dhe_mcs_L1</t>
+  </si>
+  <si>
+    <t>Dhe_pcs_L1</t>
   </si>
   <si>
     <t>Ydses_c5_Q2_L1</t>
@@ -294,9 +300,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>HO1a - Home ownership</t>
@@ -1685,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1733,6 +1736,11 @@
     <row r="11">
       <c r="B11" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1746,40 +1754,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5">
-        <v>0.82789506350296693</v>
+        <v>0.82319609978173192</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>77729.811355272454</v>
+        <v>59493.034392457273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6">
-        <v>327875</v>
+        <v>227554</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6">
-        <v>-36026.976393268567</v>
+        <v>-27641.282255200716</v>
       </c>
     </row>
   </sheetData>
@@ -1793,5250 +1801,5250 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" t="s">
+        <v>71</v>
+      </c>
+      <c r="T1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V1" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" t="s">
+        <v>75</v>
+      </c>
+      <c r="X1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO1" t="s">
         <v>93</v>
       </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>67</v>
-      </c>
-      <c r="R1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" t="s">
-        <v>69</v>
-      </c>
-      <c r="T1" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1" t="s">
-        <v>71</v>
-      </c>
-      <c r="V1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>91</v>
-      </c>
       <c r="AP1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" s="8">
-        <v>-0.012547321579729693</v>
+        <v>0.019062443292943793</v>
       </c>
       <c r="C2">
-        <v>0.00012788072474818126</v>
+        <v>0.00018894763772858057</v>
       </c>
       <c r="D2">
-        <v>2.6107153443066734e-007</v>
+        <v>9.1790444399800689e-007</v>
       </c>
       <c r="E2">
-        <v>7.3082024556769315e-010</v>
+        <v>-6.4268006858846819e-010</v>
       </c>
       <c r="F2">
-        <v>-3.9358928149478273e-005</v>
+        <v>-2.0219000221252986e-005</v>
       </c>
       <c r="G2">
-        <v>-1.8823649229436483e-005</v>
+        <v>-4.6991462250256516e-005</v>
       </c>
       <c r="H2">
-        <v>3.1351207803885004e-006</v>
+        <v>-1.9234008507542367e-005</v>
       </c>
       <c r="I2">
-        <v>-8.3920860752459092e-005</v>
+        <v>-2.7636625565984726e-005</v>
       </c>
       <c r="J2">
-        <v>-3.469201653710432e-005</v>
+        <v>-4.9288056428607168e-005</v>
       </c>
       <c r="K2">
-        <v>-3.6690393304232743e-006</v>
+        <v>1.9745392131774749e-005</v>
       </c>
       <c r="L2">
-        <v>4.2740461689852515e-005</v>
+        <v>8.1041608767894614e-005</v>
       </c>
       <c r="M2">
-        <v>1.8168822437531845e-005</v>
+        <v>1.6889427551514538e-005</v>
       </c>
       <c r="N2">
-        <v>2.3190569799912995e-005</v>
+        <v>-1.2670939774698475e-006</v>
       </c>
       <c r="O2">
-        <v>-7.235372547289514e-006</v>
+        <v>-1.9930475746421838e-005</v>
       </c>
       <c r="P2">
-        <v>-7.4829875894158389e-006</v>
+        <v>-2.1074059112878633e-005</v>
       </c>
       <c r="Q2">
-        <v>-7.9122885279238555e-007</v>
+        <v>-1.1990824991993348e-006</v>
       </c>
       <c r="R2">
-        <v>-1.4508581854701431e-007</v>
+        <v>-2.1156417749525872e-007</v>
       </c>
       <c r="S2">
-        <v>1.8517040194903059e-005</v>
+        <v>1.4884072788953506e-005</v>
       </c>
       <c r="T2">
-        <v>2.1433944777983911e-005</v>
+        <v>1.452594121585812e-005</v>
       </c>
       <c r="U2">
-        <v>1.6068467230109077e-005</v>
+        <v>-5.4617283016080246e-006</v>
       </c>
       <c r="V2">
-        <v>9.4897033567697504e-006</v>
+        <v>-2.5404145693849345e-005</v>
       </c>
       <c r="W2">
-        <v>-2.9612353110644097e-006</v>
+        <v>-1.3492463693255288e-006</v>
       </c>
       <c r="X2">
-        <v>-2.3093899068929166e-006</v>
+        <v>-3.0566291045204588e-006</v>
       </c>
       <c r="Y2">
-        <v>-2.5636235374154108e-006</v>
+        <v>-5.4565205610653314e-006</v>
       </c>
       <c r="Z2">
-        <v>2.3035257734025827e-006</v>
+        <v>6.9045849256134104e-006</v>
       </c>
       <c r="AA2">
-        <v>-5.9854706066209294e-006</v>
+        <v>-9.2140248080619702e-006</v>
       </c>
       <c r="AB2">
-        <v>-8.2273743438366187e-006</v>
+        <v>-1.0313171308644734e-005</v>
       </c>
       <c r="AC2">
-        <v>-3.0512157408656893e-006</v>
+        <v>-1.1986385540214616e-006</v>
       </c>
       <c r="AD2">
-        <v>-1.878729065664977e-006</v>
+        <v>-8.4211831382252095e-006</v>
       </c>
       <c r="AE2">
-        <v>1.8601942434672763e-006</v>
+        <v>4.4683182648765972e-006</v>
       </c>
       <c r="AF2">
-        <v>-2.7523960014804505e-006</v>
+        <v>-5.0566565110452668e-006</v>
       </c>
       <c r="AG2">
-        <v>-6.9703098249782638e-006</v>
+        <v>-3.0027732850288947e-006</v>
       </c>
       <c r="AH2">
-        <v>1.4936291953985461e-006</v>
+        <v>7.0895687592728951e-006</v>
       </c>
       <c r="AI2">
-        <v>-9.7779038769871475e-006</v>
+        <v>-5.4643131419696338e-006</v>
       </c>
       <c r="AJ2">
-        <v>-3.1743798909241021e-007</v>
+        <v>5.111695547536668e-007</v>
       </c>
       <c r="AK2">
-        <v>1.0252474378722262e-007</v>
+        <v>-7.0023940935038615e-006</v>
       </c>
       <c r="AL2">
-        <v>6.2102916537222364e-007</v>
+        <v>3.2505700207749275e-006</v>
       </c>
       <c r="AM2">
-        <v>-6.0272879253143162e-006</v>
+        <v>-1.0859017052834651e-005</v>
       </c>
       <c r="AN2">
-        <v>-3.6147826383295437e-006</v>
+        <v>1.2811924345343312e-006</v>
       </c>
       <c r="AO2">
-        <v>-1.1315224187012598e-005</v>
+        <v>-1.4312852322922504e-005</v>
       </c>
       <c r="AP2">
-        <v>-2.7821092744957388e-005</v>
+        <v>-6.7254370666582053e-005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="10">
-        <v>0.0020472859817201039</v>
+        <v>0.0023780021352547099</v>
       </c>
       <c r="C3">
-        <v>2.6107153443066734e-007</v>
+        <v>9.1790444399800689e-007</v>
       </c>
       <c r="D3">
-        <v>3.5259811505297173e-006</v>
+        <v>4.210034360943834e-006</v>
       </c>
       <c r="E3">
-        <v>-3.319127947998936e-008</v>
+        <v>-3.926570512997089e-008</v>
       </c>
       <c r="F3">
-        <v>1.0405099437096015e-005</v>
+        <v>1.3563219432995692e-005</v>
       </c>
       <c r="G3">
-        <v>2.9745120178600814e-006</v>
+        <v>3.6616872850389131e-006</v>
       </c>
       <c r="H3">
-        <v>1.0402017000809438e-006</v>
+        <v>1.7777124139936971e-006</v>
       </c>
       <c r="I3">
-        <v>3.4230884546268265e-006</v>
+        <v>1.0222671685770986e-006</v>
       </c>
       <c r="J3">
-        <v>-6.0679716057771514e-007</v>
+        <v>-1.4468782533861939e-006</v>
       </c>
       <c r="K3">
-        <v>8.4195875642643294e-006</v>
+        <v>9.4863781555307288e-006</v>
       </c>
       <c r="L3">
-        <v>2.0490009476688531e-006</v>
+        <v>2.2006122222646099e-006</v>
       </c>
       <c r="M3">
-        <v>2.3673626878573877e-005</v>
+        <v>3.092132592191709e-005</v>
       </c>
       <c r="N3">
-        <v>3.2293225804663906e-006</v>
+        <v>6.3229540793006673e-006</v>
       </c>
       <c r="O3">
-        <v>-3.3651800074189429e-007</v>
+        <v>-8.6821190192918273e-008</v>
       </c>
       <c r="P3">
-        <v>3.0276666477094575e-007</v>
+        <v>1.1004814492502311e-006</v>
       </c>
       <c r="Q3">
-        <v>5.4590076078451582e-008</v>
+        <v>6.2591536913412424e-008</v>
       </c>
       <c r="R3">
-        <v>1.0922533180102369e-007</v>
+        <v>1.5341863011779749e-007</v>
       </c>
       <c r="S3">
-        <v>3.6103131531145211e-006</v>
+        <v>7.0112325618311525e-006</v>
       </c>
       <c r="T3">
-        <v>1.4551711867712239e-006</v>
+        <v>5.0923712108035726e-006</v>
       </c>
       <c r="U3">
-        <v>-1.2574434854147617e-006</v>
+        <v>6.2971182140917587e-007</v>
       </c>
       <c r="V3">
-        <v>-2.4769981294328631e-006</v>
+        <v>-1.3765013731005937e-006</v>
       </c>
       <c r="W3">
-        <v>-1.8035534091480585e-007</v>
+        <v>-6.5326357302293199e-007</v>
       </c>
       <c r="X3">
-        <v>-1.188813751662672e-006</v>
+        <v>1.6720268935133294e-007</v>
       </c>
       <c r="Y3">
-        <v>-1.4768776949176357e-006</v>
+        <v>-2.1227211759058631e-006</v>
       </c>
       <c r="Z3">
-        <v>-2.8615376355335222e-007</v>
+        <v>-1.4204724915873719e-006</v>
       </c>
       <c r="AA3">
-        <v>-1.5003954140171852e-007</v>
+        <v>-6.2302281700384794e-007</v>
       </c>
       <c r="AB3">
-        <v>9.675019783045412e-008</v>
+        <v>-3.8245723508207593e-007</v>
       </c>
       <c r="AC3">
-        <v>-4.5639613423287407e-007</v>
+        <v>-1.5039401779212911e-006</v>
       </c>
       <c r="AD3">
-        <v>-1.1823394706252754e-007</v>
+        <v>-5.2469527554032416e-007</v>
       </c>
       <c r="AE3">
-        <v>-1.2959412249917352e-008</v>
+        <v>6.2881907521521071e-008</v>
       </c>
       <c r="AF3">
-        <v>2.6971435125103707e-007</v>
+        <v>-2.7717215614446515e-007</v>
       </c>
       <c r="AG3">
-        <v>1.4366065722378973e-006</v>
+        <v>1.3296879948857597e-006</v>
       </c>
       <c r="AH3">
-        <v>-1.7348382566233592e-006</v>
+        <v>-2.7839570281417344e-006</v>
       </c>
       <c r="AI3">
-        <v>3.4736910851707509e-007</v>
+        <v>-1.6743132602498642e-007</v>
       </c>
       <c r="AJ3">
-        <v>1.5688245878254011e-007</v>
+        <v>2.4815399929093137e-007</v>
       </c>
       <c r="AK3">
-        <v>-6.0799483160199175e-007</v>
+        <v>-1.7037926334854316e-006</v>
       </c>
       <c r="AL3">
-        <v>-1.4170193888759013e-006</v>
+        <v>-2.1614958900012101e-006</v>
       </c>
       <c r="AM3">
-        <v>-6.4609638909448057e-008</v>
+        <v>7.0444166724729554e-007</v>
       </c>
       <c r="AN3">
-        <v>-1.4692609963669432e-006</v>
+        <v>-9.6951760303371382e-007</v>
       </c>
       <c r="AO3">
-        <v>3.3872998367635312e-007</v>
+        <v>9.7558378021902033e-007</v>
       </c>
       <c r="AP3">
-        <v>-9.8458947539657398e-005</v>
+        <v>-0.00012376283364610102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="12">
-        <v>3.1284428489710037e-005</v>
+        <v>2.4311369708430321e-005</v>
       </c>
       <c r="C4">
-        <v>7.3082024556769315e-010</v>
+        <v>-6.4268006858846819e-010</v>
       </c>
       <c r="D4">
-        <v>-3.319127947998936e-008</v>
+        <v>-3.926570512997089e-008</v>
       </c>
       <c r="E4">
-        <v>3.3266416448293453e-010</v>
+        <v>3.9171282221316664e-010</v>
       </c>
       <c r="F4">
-        <v>-7.5887267038591521e-008</v>
+        <v>-9.8924914800829391e-008</v>
       </c>
       <c r="G4">
-        <v>-3.8134195524482578e-008</v>
+        <v>-4.2368055248962267e-008</v>
       </c>
       <c r="H4">
-        <v>1.2500513794479444e-009</v>
+        <v>-7.3681864782384581e-009</v>
       </c>
       <c r="I4">
-        <v>-3.1782662285909042e-008</v>
+        <v>-1.2961160922818789e-008</v>
       </c>
       <c r="J4">
-        <v>2.0071365463966766e-008</v>
+        <v>2.7749671842506712e-008</v>
       </c>
       <c r="K4">
-        <v>-7.7294683543152274e-008</v>
+        <v>-8.1540273387928264e-008</v>
       </c>
       <c r="L4">
-        <v>6.5198397298578303e-010</v>
+        <v>8.38595363692589e-009</v>
       </c>
       <c r="M4">
-        <v>-1.8449959883007081e-007</v>
+        <v>-2.4581495209989136e-007</v>
       </c>
       <c r="N4">
-        <v>-4.5685262813786592e-008</v>
+        <v>-8.4418280486789125e-008</v>
       </c>
       <c r="O4">
-        <v>1.8389447355979837e-009</v>
+        <v>-1.2940026932474375e-009</v>
       </c>
       <c r="P4">
-        <v>-2.1974859052379486e-008</v>
+        <v>-3.6682717107661002e-008</v>
       </c>
       <c r="Q4">
-        <v>-1.0764623120362862e-009</v>
+        <v>-1.3344564458733015e-009</v>
       </c>
       <c r="R4">
-        <v>-5.6057026211111896e-010</v>
+        <v>-7.138658799892091e-010</v>
       </c>
       <c r="S4">
-        <v>-3.5893692030041808e-008</v>
+        <v>-6.6781547832464609e-008</v>
       </c>
       <c r="T4">
-        <v>-5.2720622824999362e-009</v>
+        <v>-3.8981138735169933e-008</v>
       </c>
       <c r="U4">
-        <v>1.8621702660315119e-008</v>
+        <v>-7.4653988349580514e-010</v>
       </c>
       <c r="V4">
-        <v>2.6504998988733093e-008</v>
+        <v>1.2515057612066826e-008</v>
       </c>
       <c r="W4">
-        <v>-2.4839963851299245e-009</v>
+        <v>6.0928547468144311e-010</v>
       </c>
       <c r="X4">
-        <v>5.9060951476986973e-009</v>
+        <v>-5.8607539928650276e-009</v>
       </c>
       <c r="Y4">
-        <v>1.6840048501920847e-008</v>
+        <v>2.1978717852510756e-008</v>
       </c>
       <c r="Z4">
-        <v>5.4267287881985273e-009</v>
+        <v>1.6306733397015664e-008</v>
       </c>
       <c r="AA4">
-        <v>4.5939750203317785e-009</v>
+        <v>9.5683249076728374e-009</v>
       </c>
       <c r="AB4">
-        <v>3.4325231597384547e-009</v>
+        <v>8.8833016353610491e-009</v>
       </c>
       <c r="AC4">
-        <v>5.8186728297240692e-009</v>
+        <v>1.5600795521473537e-008</v>
       </c>
       <c r="AD4">
-        <v>4.5198669120803201e-009</v>
+        <v>8.2051577455061754e-009</v>
       </c>
       <c r="AE4">
-        <v>3.0747427021775349e-009</v>
+        <v>3.0500671676812088e-009</v>
       </c>
       <c r="AF4">
-        <v>8.2796512018935422e-010</v>
+        <v>6.4412683012873535e-009</v>
       </c>
       <c r="AG4">
-        <v>-1.0355970486474249e-008</v>
+        <v>-9.0443303483782628e-009</v>
       </c>
       <c r="AH4">
-        <v>1.5604901128464562e-008</v>
+        <v>2.5522950832854794e-008</v>
       </c>
       <c r="AI4">
-        <v>3.9104818461098776e-009</v>
+        <v>9.2518322747465004e-009</v>
       </c>
       <c r="AJ4">
-        <v>-1.9644458001853613e-009</v>
+        <v>-2.7171497249077253e-009</v>
       </c>
       <c r="AK4">
-        <v>4.1515413508645443e-009</v>
+        <v>1.3540654772268073e-008</v>
       </c>
       <c r="AL4">
-        <v>1.2467902009740387e-008</v>
+        <v>1.628273406235385e-008</v>
       </c>
       <c r="AM4">
-        <v>1.0551217249692203e-008</v>
+        <v>3.8229807900505006e-009</v>
       </c>
       <c r="AN4">
-        <v>1.6596955131367764e-008</v>
+        <v>1.0734047954189822e-008</v>
       </c>
       <c r="AO4">
-        <v>3.3415540504087318e-010</v>
+        <v>-6.3829656433431133e-009</v>
       </c>
       <c r="AP4">
-        <v>8.8918417274762756e-007</v>
+        <v>1.0986516244585932e-006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="14">
-        <v>-0.061733650559734683</v>
+        <v>0.012895419891557488</v>
       </c>
       <c r="C5">
-        <v>-3.9358928149478273e-005</v>
+        <v>-2.0219000221252986e-005</v>
       </c>
       <c r="D5">
-        <v>1.0405099437096015e-005</v>
+        <v>1.3563219432995692e-005</v>
       </c>
       <c r="E5">
-        <v>-7.5887267038591521e-008</v>
+        <v>-9.8924914800829391e-008</v>
       </c>
       <c r="F5">
-        <v>0.014042774896952064</v>
+        <v>0.01909551194349678</v>
       </c>
       <c r="G5">
-        <v>0.00029078762583973738</v>
+        <v>0.00065908908431060501</v>
       </c>
       <c r="H5">
-        <v>0.0003010758271195825</v>
+        <v>0.00064109738043132813</v>
       </c>
       <c r="I5">
-        <v>0.00038456358166450084</v>
+        <v>0.00075370002560914214</v>
       </c>
       <c r="J5">
-        <v>0.00031918650137636393</v>
+        <v>0.00068548053526255978</v>
       </c>
       <c r="K5">
-        <v>0.00032746072881628116</v>
+        <v>0.00068149461829622318</v>
       </c>
       <c r="L5">
-        <v>0.00035046407028355007</v>
+        <v>0.00069941954455417633</v>
       </c>
       <c r="M5">
-        <v>7.4009428114626715e-006</v>
+        <v>4.4888735535366238e-005</v>
       </c>
       <c r="N5">
-        <v>4.4214792340000625e-006</v>
+        <v>-5.5826373990298701e-005</v>
       </c>
       <c r="O5">
-        <v>0.00010530240034764936</v>
+        <v>0.00015280457125900154</v>
       </c>
       <c r="P5">
-        <v>0.00010986367446221836</v>
+        <v>0.00015217875230864902</v>
       </c>
       <c r="Q5">
-        <v>-5.5058632227625303e-007</v>
+        <v>1.0589642950723105e-007</v>
       </c>
       <c r="R5">
-        <v>-6.0560811041093439e-007</v>
+        <v>-2.4449872586452882e-007</v>
       </c>
       <c r="S5">
-        <v>2.7170379921619961e-006</v>
+        <v>-2.9452461624698152e-005</v>
       </c>
       <c r="T5">
-        <v>2.9826609188361928e-005</v>
+        <v>-5.7827767708908611e-005</v>
       </c>
       <c r="U5">
-        <v>7.7067871112882592e-005</v>
+        <v>2.0406508971919075e-005</v>
       </c>
       <c r="V5">
-        <v>0.00013332323715633561</v>
+        <v>0.00012718878827616318</v>
       </c>
       <c r="W5">
-        <v>-4.2638242460648021e-006</v>
+        <v>-2.1981978641412828e-006</v>
       </c>
       <c r="X5">
-        <v>4.1029776062692153e-005</v>
+        <v>6.4011269037128371e-005</v>
       </c>
       <c r="Y5">
-        <v>2.5410318695238008e-005</v>
+        <v>3.3106865039906383e-006</v>
       </c>
       <c r="Z5">
-        <v>4.4244666748915375e-005</v>
+        <v>5.0083044514629634e-005</v>
       </c>
       <c r="AA5">
-        <v>6.3082394451987732e-005</v>
+        <v>7.0479338259572425e-005</v>
       </c>
       <c r="AB5">
-        <v>6.5862820119779028e-005</v>
+        <v>6.1358063412193483e-005</v>
       </c>
       <c r="AC5">
-        <v>3.876379266523138e-005</v>
+        <v>5.8485873698033226e-005</v>
       </c>
       <c r="AD5">
-        <v>3.3906581350823055e-005</v>
+        <v>5.0678852997012804e-005</v>
       </c>
       <c r="AE5">
-        <v>4.7980655969664375e-005</v>
+        <v>8.8202930660462398e-005</v>
       </c>
       <c r="AF5">
-        <v>3.5126085159461462e-005</v>
+        <v>2.1809542836067845e-005</v>
       </c>
       <c r="AG5">
-        <v>6.0647341145565753e-005</v>
+        <v>6.7888307755388012e-005</v>
       </c>
       <c r="AH5">
-        <v>-2.4064314215068873e-005</v>
+        <v>-3.6430295702103566e-005</v>
       </c>
       <c r="AI5">
-        <v>7.1280408559634917e-005</v>
+        <v>7.4816169942917279e-005</v>
       </c>
       <c r="AJ5">
-        <v>1.5738251730462275e-006</v>
+        <v>2.0646900710835877e-006</v>
       </c>
       <c r="AK5">
-        <v>1.2447682856696831e-005</v>
+        <v>3.8763103751403615e-005</v>
       </c>
       <c r="AL5">
-        <v>-5.3541140620432475e-007</v>
+        <v>1.6976494343452032e-007</v>
       </c>
       <c r="AM5">
-        <v>6.5448510151691196e-005</v>
+        <v>6.6249810993077485e-005</v>
       </c>
       <c r="AN5">
-        <v>6.9564036973655027e-005</v>
+        <v>8.8829777847241383e-005</v>
       </c>
       <c r="AO5">
-        <v>8.4682094594198617e-006</v>
+        <v>-3.461276275298046e-005</v>
       </c>
       <c r="AP5">
-        <v>-0.00076007757052670992</v>
+        <v>-0.0012680599551409745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="16">
-        <v>0.058280669444391739</v>
+        <v>0.017334225162208478</v>
       </c>
       <c r="C6">
-        <v>-1.8823649229436483e-005</v>
+        <v>-4.6991462250256516e-005</v>
       </c>
       <c r="D6">
-        <v>2.9745120178600814e-006</v>
+        <v>3.6616872850389131e-006</v>
       </c>
       <c r="E6">
-        <v>-3.8134195524482578e-008</v>
+        <v>-4.2368055248962267e-008</v>
       </c>
       <c r="F6">
-        <v>0.00029078762583973738</v>
+        <v>0.00065908908431060501</v>
       </c>
       <c r="G6">
-        <v>0.00047165021033879006</v>
+        <v>0.00093038581274555157</v>
       </c>
       <c r="H6">
-        <v>0.00021512625599857889</v>
+        <v>0.00052191315056045586</v>
       </c>
       <c r="I6">
-        <v>0.00024395488585539398</v>
+        <v>0.00059091446370586787</v>
       </c>
       <c r="J6">
-        <v>0.00027847687402064996</v>
+        <v>0.00060377712164276878</v>
       </c>
       <c r="K6">
-        <v>0.00030637594648905744</v>
+        <v>0.00064153165801635764</v>
       </c>
       <c r="L6">
-        <v>0.00027767216828231329</v>
+        <v>0.00060336779928799403</v>
       </c>
       <c r="M6">
-        <v>-8.899326996849578e-006</v>
+        <v>-2.9929081927307069e-005</v>
       </c>
       <c r="N6">
-        <v>-1.0397388851971634e-005</v>
+        <v>-4.2117884275961256e-005</v>
       </c>
       <c r="O6">
-        <v>2.1938167007051179e-005</v>
+        <v>3.8952507117503429e-005</v>
       </c>
       <c r="P6">
-        <v>2.9345700319629949e-005</v>
+        <v>5.5634176118713434e-005</v>
       </c>
       <c r="Q6">
-        <v>-2.9499764257745249e-007</v>
+        <v>3.3445131353844681e-007</v>
       </c>
       <c r="R6">
-        <v>5.2347753403858497e-008</v>
+        <v>6.0598256661434905e-007</v>
       </c>
       <c r="S6">
-        <v>1.8950085924134944e-005</v>
+        <v>1.7201246141644041e-005</v>
       </c>
       <c r="T6">
-        <v>5.8530869337246176e-005</v>
+        <v>2.6687010482826545e-005</v>
       </c>
       <c r="U6">
-        <v>0.00011563980312241556</v>
+        <v>0.00011881705780286176</v>
       </c>
       <c r="V6">
-        <v>0.00016622348452302328</v>
+        <v>0.00022185467234822799</v>
       </c>
       <c r="W6">
-        <v>-5.2182925460247837e-006</v>
+        <v>-1.0593954103372224e-005</v>
       </c>
       <c r="X6">
-        <v>-2.0247012625917792e-005</v>
+        <v>-2.4052375578865337e-005</v>
       </c>
       <c r="Y6">
-        <v>1.6821231397551979e-005</v>
+        <v>3.1626405469781338e-005</v>
       </c>
       <c r="Z6">
-        <v>1.9152511835206626e-005</v>
+        <v>4.0073760916241387e-005</v>
       </c>
       <c r="AA6">
-        <v>3.3563824903552418e-005</v>
+        <v>5.9501500556113362e-005</v>
       </c>
       <c r="AB6">
-        <v>2.9113658753666929e-005</v>
+        <v>5.3914486731929852e-005</v>
       </c>
       <c r="AC6">
-        <v>2.4459194341473887e-005</v>
+        <v>3.6055336745835541e-005</v>
       </c>
       <c r="AD6">
-        <v>1.7673161332526791e-005</v>
+        <v>4.2529158245214823e-005</v>
       </c>
       <c r="AE6">
-        <v>2.0718899209249278e-005</v>
+        <v>3.8483740793973267e-005</v>
       </c>
       <c r="AF6">
-        <v>3.0580734691650719e-005</v>
+        <v>4.451893637960284e-005</v>
       </c>
       <c r="AG6">
-        <v>1.9971919892631458e-005</v>
+        <v>3.9424676636034861e-005</v>
       </c>
       <c r="AH6">
-        <v>9.1603245672615088e-006</v>
+        <v>2.1949782324671749e-005</v>
       </c>
       <c r="AI6">
-        <v>1.7602170952127778e-005</v>
+        <v>2.9532828423308875e-005</v>
       </c>
       <c r="AJ6">
-        <v>1.4106773893570794e-006</v>
+        <v>1.7244796404762409e-006</v>
       </c>
       <c r="AK6">
-        <v>-1.1154389961679522e-005</v>
+        <v>2.3739537860719109e-006</v>
       </c>
       <c r="AL6">
-        <v>-1.9268825915178262e-006</v>
+        <v>2.9729109743699926e-006</v>
       </c>
       <c r="AM6">
-        <v>6.9502378940697248e-006</v>
+        <v>-3.4396390706460038e-006</v>
       </c>
       <c r="AN6">
-        <v>-9.5557461050329662e-006</v>
+        <v>-7.5170850529177958e-006</v>
       </c>
       <c r="AO6">
-        <v>-8.0727329784813635e-006</v>
+        <v>-1.7901567271006092e-005</v>
       </c>
       <c r="AP6">
-        <v>-0.00039332339225611832</v>
+        <v>-0.00080082845960302855</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="18">
-        <v>-0.0073299585645495045</v>
+        <v>-0.011491879290672294</v>
       </c>
       <c r="C7">
-        <v>3.1351207803885004e-006</v>
+        <v>-1.9234008507542367e-005</v>
       </c>
       <c r="D7">
-        <v>1.0402017000809438e-006</v>
+        <v>1.7777124139936971e-006</v>
       </c>
       <c r="E7">
-        <v>1.2500513794479444e-009</v>
+        <v>-7.3681864782384581e-009</v>
       </c>
       <c r="F7">
-        <v>0.0003010758271195825</v>
+        <v>0.00064109738043132813</v>
       </c>
       <c r="G7">
-        <v>0.00021512625599857889</v>
+        <v>0.00052191315056045586</v>
       </c>
       <c r="H7">
-        <v>0.00040645339702684178</v>
+        <v>0.0009421695396883954</v>
       </c>
       <c r="I7">
-        <v>0.00024606985468679255</v>
+        <v>0.00055955895724362295</v>
       </c>
       <c r="J7">
-        <v>0.00023901117014001855</v>
+        <v>0.00053680604369090595</v>
       </c>
       <c r="K7">
-        <v>0.00023135950253664407</v>
+        <v>0.00052988739361980444</v>
       </c>
       <c r="L7">
-        <v>0.00023697744312051121</v>
+        <v>0.00052675361233548931</v>
       </c>
       <c r="M7">
-        <v>6.194182337558582e-005</v>
+        <v>7.0504168216535619e-005</v>
       </c>
       <c r="N7">
-        <v>5.5949172224482901e-006</v>
+        <v>-2.8551276349292418e-006</v>
       </c>
       <c r="O7">
-        <v>2.1516016831757046e-005</v>
+        <v>3.7990981259980626e-005</v>
       </c>
       <c r="P7">
-        <v>3.0755995748241111e-005</v>
+        <v>4.7561627325495276e-005</v>
       </c>
       <c r="Q7">
-        <v>2.0023432095994349e-009</v>
+        <v>2.8045621202800893e-007</v>
       </c>
       <c r="R7">
-        <v>-2.8846225345227695e-007</v>
+        <v>2.3697115515700178e-007</v>
       </c>
       <c r="S7">
-        <v>-1.0102568834723561e-005</v>
+        <v>-2.1863965375210907e-005</v>
       </c>
       <c r="T7">
-        <v>8.2453657084484315e-006</v>
+        <v>-1.7436150984919568e-005</v>
       </c>
       <c r="U7">
-        <v>2.7065321088779635e-005</v>
+        <v>1.5379962932345748e-005</v>
       </c>
       <c r="V7">
-        <v>7.5877653170087968e-005</v>
+        <v>9.8753209057929532e-005</v>
       </c>
       <c r="W7">
-        <v>3.1052046240622741e-007</v>
+        <v>3.2519165590751367e-006</v>
       </c>
       <c r="X7">
-        <v>-1.2473712730409489e-005</v>
+        <v>-2.3121875250242425e-005</v>
       </c>
       <c r="Y7">
-        <v>1.2223847002925052e-005</v>
+        <v>1.6911770380696296e-005</v>
       </c>
       <c r="Z7">
-        <v>2.900859242275307e-005</v>
+        <v>4.6706176682048179e-005</v>
       </c>
       <c r="AA7">
-        <v>3.7331295725159054e-005</v>
+        <v>5.6118241391775228e-005</v>
       </c>
       <c r="AB7">
-        <v>3.9202701076032536e-005</v>
+        <v>4.961621045324187e-005</v>
       </c>
       <c r="AC7">
-        <v>4.1140396085821411e-005</v>
+        <v>6.3360687740348669e-005</v>
       </c>
       <c r="AD7">
-        <v>2.6122838509773255e-005</v>
+        <v>4.6833934160612407e-005</v>
       </c>
       <c r="AE7">
-        <v>2.8190629180186639e-005</v>
+        <v>5.5739607388940673e-005</v>
       </c>
       <c r="AF7">
-        <v>4.14787362833614e-005</v>
+        <v>5.9006384643461109e-005</v>
       </c>
       <c r="AG7">
-        <v>2.7453471000080798e-005</v>
+        <v>4.5514612820429668e-005</v>
       </c>
       <c r="AH7">
-        <v>2.5912754569109292e-005</v>
+        <v>3.0157068886052474e-005</v>
       </c>
       <c r="AI7">
-        <v>2.2409646081386628e-005</v>
+        <v>4.4036892350708147e-005</v>
       </c>
       <c r="AJ7">
-        <v>1.6368308290256982e-006</v>
+        <v>2.4585921436822465e-006</v>
       </c>
       <c r="AK7">
-        <v>-2.3988147301928767e-006</v>
+        <v>1.1968911409842887e-005</v>
       </c>
       <c r="AL7">
-        <v>-9.3873073656597762e-006</v>
+        <v>-1.1932204850815798e-005</v>
       </c>
       <c r="AM7">
-        <v>-8.4336315757972409e-006</v>
+        <v>3.2779946164936472e-006</v>
       </c>
       <c r="AN7">
-        <v>1.1526790580508473e-005</v>
+        <v>5.6720079613716023e-007</v>
       </c>
       <c r="AO7">
-        <v>-7.6326370123678465e-006</v>
+        <v>-2.1030588931399613e-005</v>
       </c>
       <c r="AP7">
-        <v>-0.00035631449841889615</v>
+        <v>-0.00072356508734771263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="20">
-        <v>-0.24616059164101423</v>
+        <v>-0.10599854676388853</v>
       </c>
       <c r="C8">
-        <v>-8.3920860752459092e-005</v>
+        <v>-2.7636625565984726e-005</v>
       </c>
       <c r="D8">
-        <v>3.4230884546268265e-006</v>
+        <v>1.0222671685770986e-006</v>
       </c>
       <c r="E8">
-        <v>-3.1782662285909042e-008</v>
+        <v>-1.2961160922818789e-008</v>
       </c>
       <c r="F8">
-        <v>0.00038456358166450084</v>
+        <v>0.00075370002560914214</v>
       </c>
       <c r="G8">
-        <v>0.00024395488585539398</v>
+        <v>0.00059091446370586787</v>
       </c>
       <c r="H8">
-        <v>0.00024606985468679255</v>
+        <v>0.00055955895724362295</v>
       </c>
       <c r="I8">
-        <v>0.032537510279123216</v>
+        <v>0.02813188622231836</v>
       </c>
       <c r="J8">
-        <v>0.0003512376319002832</v>
+        <v>0.00072592390332729888</v>
       </c>
       <c r="K8">
-        <v>0.00028872406982202671</v>
+        <v>0.00062139683887623396</v>
       </c>
       <c r="L8">
-        <v>0.00032229293728453271</v>
+        <v>0.00068605022565675327</v>
       </c>
       <c r="M8">
-        <v>-4.6194695604231637e-005</v>
+        <v>3.5711586850166685e-005</v>
       </c>
       <c r="N8">
-        <v>0.00011382480355427512</v>
+        <v>0.00014571868219131641</v>
       </c>
       <c r="O8">
-        <v>-3.5922949152058544e-005</v>
+        <v>8.6809914791799171e-005</v>
       </c>
       <c r="P8">
-        <v>6.2082276270439258e-005</v>
+        <v>0.00020147066161922401</v>
       </c>
       <c r="Q8">
-        <v>2.689194403567782e-006</v>
+        <v>1.1783697000286257e-006</v>
       </c>
       <c r="R8">
-        <v>1.4166592043480422e-006</v>
+        <v>1.5662952765942899e-007</v>
       </c>
       <c r="S8">
-        <v>4.1418122986522017e-005</v>
+        <v>6.9117886888648644e-005</v>
       </c>
       <c r="T8">
-        <v>0.0001475861451768093</v>
+        <v>7.7217416611187988e-005</v>
       </c>
       <c r="U8">
-        <v>0.00025053085647868425</v>
+        <v>0.00027774812238656667</v>
       </c>
       <c r="V8">
-        <v>0.00021858548226335356</v>
+        <v>0.00047700497649964314</v>
       </c>
       <c r="W8">
-        <v>-8.4119925083351799e-006</v>
+        <v>-5.9090369373980734e-006</v>
       </c>
       <c r="X8">
-        <v>7.2405098850131553e-005</v>
+        <v>2.5260337948133032e-005</v>
       </c>
       <c r="Y8">
-        <v>-1.8518886521472586e-005</v>
+        <v>1.5825987529069794e-005</v>
       </c>
       <c r="Z8">
-        <v>1.1532560900429436e-005</v>
+        <v>4.8667966901542637e-005</v>
       </c>
       <c r="AA8">
-        <v>0.00016697856894276779</v>
+        <v>0.00027885264661320607</v>
       </c>
       <c r="AB8">
-        <v>8.1372758819726245e-005</v>
+        <v>0.00016931878525802354</v>
       </c>
       <c r="AC8">
-        <v>-9.9608127622207824e-006</v>
+        <v>3.3088229457751132e-006</v>
       </c>
       <c r="AD8">
-        <v>2.3916726630222456e-005</v>
+        <v>6.9014922507617605e-005</v>
       </c>
       <c r="AE8">
-        <v>0.00020303885685219863</v>
+        <v>8.3771645997239447e-005</v>
       </c>
       <c r="AF8">
-        <v>5.7917440696932846e-005</v>
+        <v>9.9943120434731634e-005</v>
       </c>
       <c r="AG8">
-        <v>-7.2761973352398264e-006</v>
+        <v>2.0371308897565443e-005</v>
       </c>
       <c r="AH8">
-        <v>-1.8014680237459833e-005</v>
+        <v>1.7164065772947419e-005</v>
       </c>
       <c r="AI8">
-        <v>3.8792847057427676e-005</v>
+        <v>7.2950579330191849e-005</v>
       </c>
       <c r="AJ8">
-        <v>2.2679259329575864e-005</v>
+        <v>9.7203314910085643e-006</v>
       </c>
       <c r="AK8">
-        <v>-0.00014277536773756234</v>
+        <v>-4.2864696516441096e-005</v>
       </c>
       <c r="AL8">
-        <v>-0.00014544936434959853</v>
+        <v>-3.8220434256641676e-005</v>
       </c>
       <c r="AM8">
-        <v>-4.7001705974133908e-005</v>
+        <v>-1.8548106257671132e-005</v>
       </c>
       <c r="AN8">
-        <v>-0.00015171131348329692</v>
+        <v>-0.00015936785496778385</v>
       </c>
       <c r="AO8">
-        <v>-0.0001044758352918492</v>
+        <v>-8.9680225190618508e-005</v>
       </c>
       <c r="AP8">
-        <v>-0.0010855624412434096</v>
+        <v>-0.0011990589407363064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="22">
-        <v>-0.19456295381846483</v>
+        <v>-0.17976023826672047</v>
       </c>
       <c r="C9">
-        <v>-3.469201653710432e-005</v>
+        <v>-4.9288056428607168e-005</v>
       </c>
       <c r="D9">
-        <v>-6.0679716057771514e-007</v>
+        <v>-1.4468782533861939e-006</v>
       </c>
       <c r="E9">
-        <v>2.0071365463966766e-008</v>
+        <v>2.7749671842506712e-008</v>
       </c>
       <c r="F9">
-        <v>0.00031918650137636393</v>
+        <v>0.00068548053526255978</v>
       </c>
       <c r="G9">
-        <v>0.00027847687402064996</v>
+        <v>0.00060377712164276878</v>
       </c>
       <c r="H9">
-        <v>0.00023901117014001855</v>
+        <v>0.00053680604369090595</v>
       </c>
       <c r="I9">
-        <v>0.0003512376319002832</v>
+        <v>0.00072592390332729888</v>
       </c>
       <c r="J9">
-        <v>0.00086271286253422369</v>
+        <v>0.0013307798765844797</v>
       </c>
       <c r="K9">
-        <v>0.00029126334389177383</v>
+        <v>0.00059449733300892082</v>
       </c>
       <c r="L9">
-        <v>0.00031721482912266204</v>
+        <v>0.00062184260098745766</v>
       </c>
       <c r="M9">
-        <v>9.816237949293641e-005</v>
+        <v>8.6100359266914049e-005</v>
       </c>
       <c r="N9">
-        <v>5.1334421332999557e-005</v>
+        <v>3.0576129792420498e-005</v>
       </c>
       <c r="O9">
-        <v>2.5106817227960352e-005</v>
+        <v>4.4373414103020622e-005</v>
       </c>
       <c r="P9">
-        <v>2.8797854478725666e-005</v>
+        <v>4.8595680291052838e-005</v>
       </c>
       <c r="Q9">
-        <v>-3.4470170825954287e-007</v>
+        <v>2.5677042969583334e-008</v>
       </c>
       <c r="R9">
-        <v>-6.2508342962321771e-008</v>
+        <v>2.1561218144052509e-007</v>
       </c>
       <c r="S9">
-        <v>4.2767062229907322e-005</v>
+        <v>-2.8916157700149033e-006</v>
       </c>
       <c r="T9">
-        <v>0.00011291966000146619</v>
+        <v>5.1528360001284302e-005</v>
       </c>
       <c r="U9">
-        <v>0.00020556065281434631</v>
+        <v>0.00019886943104741403</v>
       </c>
       <c r="V9">
-        <v>0.00024647651390258631</v>
+        <v>0.00027838484579186733</v>
       </c>
       <c r="W9">
-        <v>-5.4823981271315746e-006</v>
+        <v>-1.3605763122693461e-006</v>
       </c>
       <c r="X9">
-        <v>-2.5315281471236168e-006</v>
+        <v>-8.1713240965126618e-007</v>
       </c>
       <c r="Y9">
-        <v>9.0658135587654085e-006</v>
+        <v>1.6910292269908415e-005</v>
       </c>
       <c r="Z9">
-        <v>3.172428322255638e-005</v>
+        <v>4.9008782758040496e-005</v>
       </c>
       <c r="AA9">
-        <v>4.7283214122018877e-005</v>
+        <v>6.2269613969801171e-005</v>
       </c>
       <c r="AB9">
-        <v>4.8353502230762386e-005</v>
+        <v>7.4991438986809402e-005</v>
       </c>
       <c r="AC9">
-        <v>3.5960673289890923e-005</v>
+        <v>4.6798934243861067e-005</v>
       </c>
       <c r="AD9">
-        <v>2.1759754083255555e-005</v>
+        <v>3.4367207296911602e-005</v>
       </c>
       <c r="AE9">
-        <v>3.2307830672689441e-005</v>
+        <v>4.1590795210360796e-005</v>
       </c>
       <c r="AF9">
-        <v>7.2683787983178757e-005</v>
+        <v>9.5828590752391183e-005</v>
       </c>
       <c r="AG9">
-        <v>3.0007355966605746e-005</v>
+        <v>4.3789173135840026e-005</v>
       </c>
       <c r="AH9">
-        <v>2.7148690665106539e-005</v>
+        <v>3.5355658991120932e-005</v>
       </c>
       <c r="AI9">
-        <v>3.5860336554235624e-005</v>
+        <v>4.2864181639667488e-005</v>
       </c>
       <c r="AJ9">
-        <v>2.3520768482450854e-006</v>
+        <v>3.6790981533805952e-006</v>
       </c>
       <c r="AK9">
-        <v>1.113122321845336e-005</v>
+        <v>2.878212601836622e-005</v>
       </c>
       <c r="AL9">
-        <v>-8.2706886212621859e-006</v>
+        <v>-3.5794869069607555e-006</v>
       </c>
       <c r="AM9">
-        <v>-4.227786958441751e-005</v>
+        <v>-6.9490811371710718e-005</v>
       </c>
       <c r="AN9">
-        <v>1.0098846413304975e-005</v>
+        <v>8.9275167355450775e-006</v>
       </c>
       <c r="AO9">
-        <v>-3.8224490277556026e-006</v>
+        <v>-9.1589706597766728e-006</v>
       </c>
       <c r="AP9">
-        <v>-0.00048244303525333475</v>
+        <v>-0.00081536554112171587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.19361632610613511</v>
+        <v>-0.16310985360076471</v>
       </c>
       <c r="C10">
-        <v>-3.6690393304232743e-006</v>
+        <v>1.9745392131774749e-005</v>
       </c>
       <c r="D10">
-        <v>8.4195875642643294e-006</v>
+        <v>9.4863781555307288e-006</v>
       </c>
       <c r="E10">
-        <v>-7.7294683543152274e-008</v>
+        <v>-8.1540273387928264e-008</v>
       </c>
       <c r="F10">
-        <v>0.00032746072881628116</v>
+        <v>0.00068149461829622318</v>
       </c>
       <c r="G10">
-        <v>0.00030637594648905744</v>
+        <v>0.00064153165801635764</v>
       </c>
       <c r="H10">
-        <v>0.00023135950253664407</v>
+        <v>0.00052988739361980444</v>
       </c>
       <c r="I10">
-        <v>0.00028872406982202671</v>
+        <v>0.00062139683887623396</v>
       </c>
       <c r="J10">
-        <v>0.00029126334389177383</v>
+        <v>0.00059449733300892082</v>
       </c>
       <c r="K10">
-        <v>0.00040038160410295847</v>
+        <v>0.00072943125040578747</v>
       </c>
       <c r="L10">
-        <v>0.0003192229851988494</v>
+        <v>0.00065055736232540076</v>
       </c>
       <c r="M10">
-        <v>2.7065594761859066e-005</v>
+        <v>3.8116724884761041e-006</v>
       </c>
       <c r="N10">
-        <v>4.0355160162868722e-005</v>
+        <v>-2.1966936022073333e-005</v>
       </c>
       <c r="O10">
-        <v>2.3002017928518717e-005</v>
+        <v>3.0799638593192297e-005</v>
       </c>
       <c r="P10">
-        <v>3.222749341970943e-005</v>
+        <v>4.4197157298011961e-005</v>
       </c>
       <c r="Q10">
-        <v>1.1676695370223369e-008</v>
+        <v>5.3870219150891564e-007</v>
       </c>
       <c r="R10">
-        <v>3.3303270018820507e-008</v>
+        <v>6.2338771711301892e-007</v>
       </c>
       <c r="S10">
-        <v>6.8387450532201547e-005</v>
+        <v>4.2981932512952125e-005</v>
       </c>
       <c r="T10">
-        <v>0.00012041243653630638</v>
+        <v>7.1981745014269394e-005</v>
       </c>
       <c r="U10">
-        <v>0.00016761802192011998</v>
+        <v>0.00014098316680873652</v>
       </c>
       <c r="V10">
-        <v>0.00021345802077400066</v>
+        <v>0.00022324792406510369</v>
       </c>
       <c r="W10">
-        <v>-9.5739518070307417e-006</v>
+        <v>-7.1261517501733006e-006</v>
       </c>
       <c r="X10">
-        <v>-1.6651496044337727e-005</v>
+        <v>-1.7272249849171144e-005</v>
       </c>
       <c r="Y10">
-        <v>1.7339343582152473e-005</v>
+        <v>2.62982399278995e-005</v>
       </c>
       <c r="Z10">
-        <v>3.9175454888009825e-005</v>
+        <v>5.6178033401799938e-005</v>
       </c>
       <c r="AA10">
-        <v>5.3658533812372405e-005</v>
+        <v>7.6323852799504009e-005</v>
       </c>
       <c r="AB10">
-        <v>4.5168777664251691e-005</v>
+        <v>6.2921334202830303e-005</v>
       </c>
       <c r="AC10">
-        <v>4.4140105487324294e-005</v>
+        <v>5.7140633105299419e-005</v>
       </c>
       <c r="AD10">
-        <v>3.7205736557522412e-005</v>
+        <v>6.0501803556184004e-005</v>
       </c>
       <c r="AE10">
-        <v>3.3859352017882931e-005</v>
+        <v>4.712016533266904e-005</v>
       </c>
       <c r="AF10">
-        <v>5.1683689392832547e-005</v>
+        <v>6.4754156107434322e-005</v>
       </c>
       <c r="AG10">
-        <v>3.8849454777252864e-005</v>
+        <v>5.8547398550991032e-005</v>
       </c>
       <c r="AH10">
-        <v>2.2869448814908118e-005</v>
+        <v>3.2464286945684979e-005</v>
       </c>
       <c r="AI10">
-        <v>2.3418212669260984e-005</v>
+        <v>3.3099942168052427e-005</v>
       </c>
       <c r="AJ10">
-        <v>9.3933704155801562e-007</v>
+        <v>1.4134699010033908e-006</v>
       </c>
       <c r="AK10">
-        <v>-1.0164209893931614e-005</v>
+        <v>-8.648739595707461e-007</v>
       </c>
       <c r="AL10">
-        <v>-6.0154365222654942e-006</v>
+        <v>-3.7122289715280251e-007</v>
       </c>
       <c r="AM10">
-        <v>1.0961963830670148e-005</v>
+        <v>1.051980362756468e-005</v>
       </c>
       <c r="AN10">
-        <v>-1.2556643183162484e-005</v>
+        <v>-1.5982971249723548e-005</v>
       </c>
       <c r="AO10">
-        <v>-1.5090125322284091e-005</v>
+        <v>-2.6968576389061036e-005</v>
       </c>
       <c r="AP10">
-        <v>-0.00065965859942460818</v>
+        <v>-0.001074992448172149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="26">
-        <v>-0.30313527886328301</v>
+        <v>-0.30688245059348612</v>
       </c>
       <c r="C11">
-        <v>4.2740461689852515e-005</v>
+        <v>8.1041608767894614e-005</v>
       </c>
       <c r="D11">
-        <v>2.0490009476688531e-006</v>
+        <v>2.2006122222646099e-006</v>
       </c>
       <c r="E11">
-        <v>6.5198397298578303e-010</v>
+        <v>8.38595363692589e-009</v>
       </c>
       <c r="F11">
-        <v>0.00035046407028355007</v>
+        <v>0.00069941954455417633</v>
       </c>
       <c r="G11">
-        <v>0.00027767216828231329</v>
+        <v>0.00060336779928799403</v>
       </c>
       <c r="H11">
-        <v>0.00023697744312051121</v>
+        <v>0.00052675361233548931</v>
       </c>
       <c r="I11">
-        <v>0.00032229293728453271</v>
+        <v>0.00068605022565675327</v>
       </c>
       <c r="J11">
-        <v>0.00031721482912266204</v>
+        <v>0.00062184260098745766</v>
       </c>
       <c r="K11">
-        <v>0.0003192229851988494</v>
+        <v>0.00065055736232540076</v>
       </c>
       <c r="L11">
-        <v>0.00098503678111363179</v>
+        <v>0.001316176071048023</v>
       </c>
       <c r="M11">
-        <v>5.0543186417760691e-005</v>
+        <v>5.1128033282845354e-005</v>
       </c>
       <c r="N11">
-        <v>8.6701953597710516e-005</v>
+        <v>5.9747179657920765e-005</v>
       </c>
       <c r="O11">
-        <v>9.602881082997625e-006</v>
+        <v>1.0786728535042394e-005</v>
       </c>
       <c r="P11">
-        <v>2.8853425304335982e-005</v>
+        <v>3.765986360414951e-005</v>
       </c>
       <c r="Q11">
-        <v>-5.6321510997911591e-007</v>
+        <v>-4.8276326197862321e-007</v>
       </c>
       <c r="R11">
-        <v>-7.0757348551744233e-007</v>
+        <v>-4.3270734964571776e-007</v>
       </c>
       <c r="S11">
-        <v>7.6302908815064155e-005</v>
+        <v>7.1355909149969999e-005</v>
       </c>
       <c r="T11">
-        <v>0.00017469733004463797</v>
+        <v>0.00017145138545501218</v>
       </c>
       <c r="U11">
-        <v>0.00024746977414980665</v>
+        <v>0.0002664085811517233</v>
       </c>
       <c r="V11">
-        <v>0.00030137075645459322</v>
+        <v>0.00036098338415828553</v>
       </c>
       <c r="W11">
-        <v>-1.6963120946405787e-005</v>
+        <v>-1.9510440726569187e-005</v>
       </c>
       <c r="X11">
-        <v>1.4397572078518554e-005</v>
+        <v>1.6923460502841575e-005</v>
       </c>
       <c r="Y11">
-        <v>2.8056679495846024e-005</v>
+        <v>3.8822206662332336e-005</v>
       </c>
       <c r="Z11">
-        <v>3.5056367401662253e-005</v>
+        <v>5.8487502512385833e-005</v>
       </c>
       <c r="AA11">
-        <v>3.9190129771313957e-005</v>
+        <v>5.6620429204231235e-005</v>
       </c>
       <c r="AB11">
-        <v>4.3389703833701777e-005</v>
+        <v>6.0711769440053944e-005</v>
       </c>
       <c r="AC11">
-        <v>2.4417459269349466e-005</v>
+        <v>3.1883391601819595e-005</v>
       </c>
       <c r="AD11">
-        <v>2.4516056335317969e-005</v>
+        <v>4.8532108911144482e-005</v>
       </c>
       <c r="AE11">
-        <v>3.4209284274085016e-005</v>
+        <v>4.5377217982958259e-005</v>
       </c>
       <c r="AF11">
-        <v>8.0781937201695222e-005</v>
+        <v>0.00010995579831171762</v>
       </c>
       <c r="AG11">
-        <v>2.5939269107036212e-005</v>
+        <v>4.6578357377776651e-005</v>
       </c>
       <c r="AH11">
-        <v>2.4994079830906186e-005</v>
+        <v>4.6263790147862593e-005</v>
       </c>
       <c r="AI11">
-        <v>1.9037282360268834e-005</v>
+        <v>3.2366297458186156e-005</v>
       </c>
       <c r="AJ11">
-        <v>5.2562045490778187e-006</v>
+        <v>7.4956068780418676e-006</v>
       </c>
       <c r="AK11">
-        <v>-2.7212311970640195e-005</v>
+        <v>-2.8838397806338459e-005</v>
       </c>
       <c r="AL11">
-        <v>-2.8850179693937152e-005</v>
+        <v>-3.232819977011126e-005</v>
       </c>
       <c r="AM11">
-        <v>1.7773987431752149e-005</v>
+        <v>1.5507633409854893e-005</v>
       </c>
       <c r="AN11">
-        <v>2.8824302606119165e-005</v>
+        <v>4.434539662439695e-005</v>
       </c>
       <c r="AO11">
-        <v>-1.9043569434300711e-005</v>
+        <v>-3.3723609365557839e-005</v>
       </c>
       <c r="AP11">
-        <v>-0.00064838574052548514</v>
+        <v>-0.0010882463341904702</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="28">
-        <v>0.092825627804387356</v>
+        <v>0.079547001079882218</v>
       </c>
       <c r="C12">
-        <v>1.8168822437531845e-005</v>
+        <v>1.6889427551514538e-005</v>
       </c>
       <c r="D12">
-        <v>2.3673626878573877e-005</v>
+        <v>3.092132592191709e-005</v>
       </c>
       <c r="E12">
-        <v>-1.8449959883007081e-007</v>
+        <v>-2.4581495209989136e-007</v>
       </c>
       <c r="F12">
-        <v>7.4009428114626715e-006</v>
+        <v>4.4888735535366238e-005</v>
       </c>
       <c r="G12">
-        <v>-8.899326996849578e-006</v>
+        <v>-2.9929081927307069e-005</v>
       </c>
       <c r="H12">
-        <v>6.194182337558582e-005</v>
+        <v>7.0504168216535619e-005</v>
       </c>
       <c r="I12">
-        <v>-4.6194695604231637e-005</v>
+        <v>3.5711586850166685e-005</v>
       </c>
       <c r="J12">
-        <v>9.816237949293641e-005</v>
+        <v>8.6100359266914049e-005</v>
       </c>
       <c r="K12">
-        <v>2.7065594761859066e-005</v>
+        <v>3.8116724884761041e-006</v>
       </c>
       <c r="L12">
-        <v>5.0543186417760691e-005</v>
+        <v>5.1128033282845354e-005</v>
       </c>
       <c r="M12">
-        <v>0.001238825558640152</v>
+        <v>0.0014622447452973255</v>
       </c>
       <c r="N12">
-        <v>0.0001630611353894897</v>
+        <v>0.00034229794492351403</v>
       </c>
       <c r="O12">
-        <v>-1.5553720629054224e-005</v>
+        <v>-2.9268093393659117e-005</v>
       </c>
       <c r="P12">
-        <v>-4.6474647591307418e-006</v>
+        <v>-8.5043824339662752e-006</v>
       </c>
       <c r="Q12">
-        <v>-7.7921602106963636e-007</v>
+        <v>-1.5928779039035085e-006</v>
       </c>
       <c r="R12">
-        <v>3.9532297634890702e-007</v>
+        <v>3.9394704892968519e-007</v>
       </c>
       <c r="S12">
-        <v>0.00010307176721410211</v>
+        <v>0.00022628912202526751</v>
       </c>
       <c r="T12">
-        <v>0.00019322378168651393</v>
+        <v>0.00038450754058676358</v>
       </c>
       <c r="U12">
-        <v>0.00021688371710354415</v>
+        <v>0.00039877029553871709</v>
       </c>
       <c r="V12">
-        <v>0.00020884502243644841</v>
+        <v>0.00037654072547360526</v>
       </c>
       <c r="W12">
-        <v>-1.4026290268421372e-005</v>
+        <v>-3.2941815395869099e-005</v>
       </c>
       <c r="X12">
-        <v>-5.151864926263033e-005</v>
+        <v>-5.1092436065715036e-005</v>
       </c>
       <c r="Y12">
-        <v>-4.6377892871198506e-006</v>
+        <v>-1.171444925546317e-005</v>
       </c>
       <c r="Z12">
-        <v>2.0444658617424558e-005</v>
+        <v>1.377442932259899e-005</v>
       </c>
       <c r="AA12">
-        <v>1.056211775816746e-005</v>
+        <v>-1.7815526670196947e-006</v>
       </c>
       <c r="AB12">
-        <v>1.7313287330902169e-005</v>
+        <v>1.4079622249694464e-005</v>
       </c>
       <c r="AC12">
-        <v>-3.6712926107519594e-006</v>
+        <v>-2.1079255577771287e-005</v>
       </c>
       <c r="AD12">
-        <v>6.5337293116074437e-006</v>
+        <v>2.7513307153190908e-006</v>
       </c>
       <c r="AE12">
-        <v>3.8088800263124524e-005</v>
+        <v>5.4076813806703119e-005</v>
       </c>
       <c r="AF12">
-        <v>2.6308989402661996e-005</v>
+        <v>3.5111368773794877e-005</v>
       </c>
       <c r="AG12">
-        <v>1.6539691753148671e-005</v>
+        <v>1.4149529459904172e-005</v>
       </c>
       <c r="AH12">
-        <v>-1.3733469032991576e-005</v>
+        <v>-2.6402140234405274e-005</v>
       </c>
       <c r="AI12">
-        <v>3.2704554498044585e-005</v>
+        <v>3.3061235991897926e-005</v>
       </c>
       <c r="AJ12">
-        <v>3.271836460807736e-006</v>
+        <v>5.804676334270497e-006</v>
       </c>
       <c r="AK12">
-        <v>-3.7992167118307682e-005</v>
+        <v>-6.325808516207212e-005</v>
       </c>
       <c r="AL12">
-        <v>-2.0918834664776583e-005</v>
+        <v>-4.6446641240313678e-005</v>
       </c>
       <c r="AM12">
-        <v>-1.9804278269498537e-005</v>
+        <v>-2.2908420247029753e-005</v>
       </c>
       <c r="AN12">
-        <v>-3.5403584024942651e-005</v>
+        <v>-3.5975750636681658e-005</v>
       </c>
       <c r="AO12">
-        <v>-4.604741168625975e-005</v>
+        <v>-5.4967395147993649e-005</v>
       </c>
       <c r="AP12">
-        <v>-0.00094498820547275016</v>
+        <v>-0.0012762639937461938</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" s="30">
-        <v>-0.016217397218885665</v>
+        <v>-0.060378086871245427</v>
       </c>
       <c r="C13">
-        <v>2.3190569799912995e-005</v>
+        <v>-1.2670939774698475e-006</v>
       </c>
       <c r="D13">
-        <v>3.2293225804663906e-006</v>
+        <v>6.3229540793006673e-006</v>
       </c>
       <c r="E13">
-        <v>-4.5685262813786592e-008</v>
+        <v>-8.4418280486789125e-008</v>
       </c>
       <c r="F13">
-        <v>4.4214792340000625e-006</v>
+        <v>-5.5826373990298701e-005</v>
       </c>
       <c r="G13">
-        <v>-1.0397388851971634e-005</v>
+        <v>-4.2117884275961256e-005</v>
       </c>
       <c r="H13">
-        <v>5.5949172224482901e-006</v>
+        <v>-2.8551276349292418e-006</v>
       </c>
       <c r="I13">
-        <v>0.00011382480355427512</v>
+        <v>0.00014571868219131641</v>
       </c>
       <c r="J13">
-        <v>5.1334421332999557e-005</v>
+        <v>3.0576129792420498e-005</v>
       </c>
       <c r="K13">
-        <v>4.0355160162868722e-005</v>
+        <v>-2.1966936022073333e-005</v>
       </c>
       <c r="L13">
-        <v>8.6701953597710516e-005</v>
+        <v>5.9747179657920765e-005</v>
       </c>
       <c r="M13">
-        <v>0.0001630611353894897</v>
+        <v>0.00034229794492351403</v>
       </c>
       <c r="N13">
-        <v>0.00033497153210734201</v>
+        <v>0.00066183440428242354</v>
       </c>
       <c r="O13">
-        <v>-1.6156746983188384e-006</v>
+        <v>-1.446725269633087e-007</v>
       </c>
       <c r="P13">
-        <v>-5.9279040666617019e-006</v>
+        <v>-1.3652258818549123e-006</v>
       </c>
       <c r="Q13">
-        <v>8.2337651011315021e-007</v>
+        <v>7.2524281625305845e-007</v>
       </c>
       <c r="R13">
-        <v>1.255829100044072e-006</v>
+        <v>1.3291153349139657e-006</v>
       </c>
       <c r="S13">
-        <v>0.00013790270270276842</v>
+        <v>0.0003322244199550654</v>
       </c>
       <c r="T13">
-        <v>0.00020774809159567785</v>
+        <v>0.00048899698819935796</v>
       </c>
       <c r="U13">
-        <v>0.00026263938306234834</v>
+        <v>0.00054234300562312852</v>
       </c>
       <c r="V13">
-        <v>0.00027693469497704526</v>
+        <v>0.00055638070028019688</v>
       </c>
       <c r="W13">
-        <v>-1.7968863313020266e-005</v>
+        <v>-4.6611020427512924e-005</v>
       </c>
       <c r="X13">
-        <v>6.0459290916061814e-006</v>
+        <v>1.1808724530298936e-005</v>
       </c>
       <c r="Y13">
-        <v>1.8819295026292754e-006</v>
+        <v>-3.8651836017596954e-007</v>
       </c>
       <c r="Z13">
-        <v>5.1225277545595425e-006</v>
+        <v>1.0300944309266066e-006</v>
       </c>
       <c r="AA13">
-        <v>5.7547306732656998e-006</v>
+        <v>1.4226440318394358e-006</v>
       </c>
       <c r="AB13">
-        <v>9.5454956921998968e-006</v>
+        <v>5.9353718532672434e-006</v>
       </c>
       <c r="AC13">
-        <v>6.09506550281316e-006</v>
+        <v>-1.1469328372500471e-006</v>
       </c>
       <c r="AD13">
-        <v>1.2743049188292555e-006</v>
+        <v>9.5209343616987744e-006</v>
       </c>
       <c r="AE13">
-        <v>1.148750789405873e-005</v>
+        <v>2.2112269379800968e-005</v>
       </c>
       <c r="AF13">
-        <v>1.2267559442094239e-005</v>
+        <v>2.8780282965246597e-005</v>
       </c>
       <c r="AG13">
-        <v>3.9627402472852495e-006</v>
+        <v>5.1300524338422616e-006</v>
       </c>
       <c r="AH13">
-        <v>7.957487752308708e-006</v>
+        <v>4.6997410614375737e-006</v>
       </c>
       <c r="AI13">
-        <v>9.4080893280891172e-006</v>
+        <v>1.1251888311289968e-005</v>
       </c>
       <c r="AJ13">
-        <v>2.6034599843520966e-006</v>
+        <v>4.1248553936926794e-006</v>
       </c>
       <c r="AK13">
-        <v>-1.1248726136711986e-005</v>
+        <v>-2.5684886083855723e-005</v>
       </c>
       <c r="AL13">
-        <v>-1.7028896508458121e-005</v>
+        <v>-3.4514447261543315e-005</v>
       </c>
       <c r="AM13">
-        <v>-7.3979473475357287e-006</v>
+        <v>1.3212190402499182e-005</v>
       </c>
       <c r="AN13">
-        <v>1.5185185284557307e-005</v>
+        <v>3.9397493975321031e-005</v>
       </c>
       <c r="AO13">
-        <v>1.9187239347263246e-005</v>
+        <v>3.3577921031039922e-005</v>
       </c>
       <c r="AP13">
-        <v>-0.00051030646215104777</v>
+        <v>-0.00080839978582509966</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" s="32">
-        <v>-0.14746585553287281</v>
+        <v>-0.144951548051068</v>
       </c>
       <c r="C14">
-        <v>-7.235372547289514e-006</v>
+        <v>-1.9930475746421838e-005</v>
       </c>
       <c r="D14">
-        <v>-3.3651800074189429e-007</v>
+        <v>-8.6821190192918273e-008</v>
       </c>
       <c r="E14">
-        <v>1.8389447355979837e-009</v>
+        <v>-1.2940026932474375e-009</v>
       </c>
       <c r="F14">
-        <v>0.00010530240034764936</v>
+        <v>0.00015280457125900154</v>
       </c>
       <c r="G14">
-        <v>2.1938167007051179e-005</v>
+        <v>3.8952507117503429e-005</v>
       </c>
       <c r="H14">
-        <v>2.1516016831757046e-005</v>
+        <v>3.7990981259980626e-005</v>
       </c>
       <c r="I14">
-        <v>-3.5922949152058544e-005</v>
+        <v>8.6809914791799171e-005</v>
       </c>
       <c r="J14">
-        <v>2.5106817227960352e-005</v>
+        <v>4.4373414103020622e-005</v>
       </c>
       <c r="K14">
-        <v>2.3002017928518717e-005</v>
+        <v>3.0799638593192297e-005</v>
       </c>
       <c r="L14">
-        <v>9.602881082997625e-006</v>
+        <v>1.0786728535042394e-005</v>
       </c>
       <c r="M14">
-        <v>-1.5553720629054224e-005</v>
+        <v>-2.9268093393659117e-005</v>
       </c>
       <c r="N14">
-        <v>-1.6156746983188384e-006</v>
+        <v>-1.446725269633087e-007</v>
       </c>
       <c r="O14">
-        <v>0.00026002357461654501</v>
+        <v>0.0003501233329607791</v>
       </c>
       <c r="P14">
-        <v>0.00021873238050523568</v>
+        <v>0.00029201457873657613</v>
       </c>
       <c r="Q14">
-        <v>-9.8295315034314918e-008</v>
+        <v>2.3005738238155903e-009</v>
       </c>
       <c r="R14">
-        <v>6.1346329277269804e-008</v>
+        <v>1.6494916383435248e-007</v>
       </c>
       <c r="S14">
-        <v>1.3690693698538349e-006</v>
+        <v>-2.5762186851251101e-006</v>
       </c>
       <c r="T14">
-        <v>1.4269608064549994e-006</v>
+        <v>-6.8896915372780856e-006</v>
       </c>
       <c r="U14">
-        <v>2.515332292271699e-005</v>
+        <v>3.3672125007707757e-005</v>
       </c>
       <c r="V14">
-        <v>8.5420730546135798e-005</v>
+        <v>0.00011883493935629087</v>
       </c>
       <c r="W14">
-        <v>4.0568246932831677e-007</v>
+        <v>7.9571214332780425e-007</v>
       </c>
       <c r="X14">
-        <v>-3.225966889051839e-006</v>
+        <v>4.3036010826267765e-006</v>
       </c>
       <c r="Y14">
-        <v>-1.0961921392814662e-005</v>
+        <v>-1.0064043398450995e-005</v>
       </c>
       <c r="Z14">
-        <v>-3.7556254142176783e-006</v>
+        <v>-4.3885105089461426e-006</v>
       </c>
       <c r="AA14">
-        <v>-1.6278950981465053e-005</v>
+        <v>-1.9140988367270893e-005</v>
       </c>
       <c r="AB14">
-        <v>-2.0724285015695785e-005</v>
+        <v>-3.0688957124645384e-005</v>
       </c>
       <c r="AC14">
-        <v>-1.3082745607955334e-005</v>
+        <v>-2.0628762376289773e-005</v>
       </c>
       <c r="AD14">
-        <v>-1.4245120790306973e-005</v>
+        <v>-1.6390371485274349e-005</v>
       </c>
       <c r="AE14">
-        <v>-6.2333134071258565e-006</v>
+        <v>-8.472289427204899e-006</v>
       </c>
       <c r="AF14">
-        <v>-1.6482766406603941e-005</v>
+        <v>-2.5168559666112527e-005</v>
       </c>
       <c r="AG14">
-        <v>-1.3431625409113793e-005</v>
+        <v>-1.9805151516668045e-005</v>
       </c>
       <c r="AH14">
-        <v>-1.4799555215242849e-005</v>
+        <v>-3.0815801605366099e-005</v>
       </c>
       <c r="AI14">
-        <v>-1.7795937795747282e-006</v>
+        <v>-8.8121754855129987e-006</v>
       </c>
       <c r="AJ14">
-        <v>6.7884921632802111e-007</v>
+        <v>2.0069095052518842e-008</v>
       </c>
       <c r="AK14">
-        <v>-4.5291560255271287e-006</v>
+        <v>-1.8087319245912158e-006</v>
       </c>
       <c r="AL14">
-        <v>1.2447718701449595e-005</v>
+        <v>1.4726779578960167e-005</v>
       </c>
       <c r="AM14">
-        <v>4.6125946278338791e-005</v>
+        <v>6.3204879976501524e-005</v>
       </c>
       <c r="AN14">
-        <v>2.0529676296099654e-005</v>
+        <v>3.6211852898845444e-005</v>
       </c>
       <c r="AO14">
-        <v>2.7190897407221107e-005</v>
+        <v>4.3254506552806844e-005</v>
       </c>
       <c r="AP14">
-        <v>-0.00022585421420360098</v>
+        <v>-0.00030407644068005079</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B15" s="34">
-        <v>-0.26272429801462749</v>
+        <v>-0.25465518191969305</v>
       </c>
       <c r="C15">
-        <v>-7.4829875894158389e-006</v>
+        <v>-2.1074059112878633e-005</v>
       </c>
       <c r="D15">
-        <v>3.0276666477094575e-007</v>
+        <v>1.1004814492502311e-006</v>
       </c>
       <c r="E15">
-        <v>-2.1974859052379486e-008</v>
+        <v>-3.6682717107661002e-008</v>
       </c>
       <c r="F15">
-        <v>0.00010986367446221836</v>
+        <v>0.00015217875230864902</v>
       </c>
       <c r="G15">
-        <v>2.9345700319629949e-005</v>
+        <v>5.5634176118713434e-005</v>
       </c>
       <c r="H15">
-        <v>3.0755995748241111e-005</v>
+        <v>4.7561627325495276e-005</v>
       </c>
       <c r="I15">
-        <v>6.2082276270439258e-005</v>
+        <v>0.00020147066161922401</v>
       </c>
       <c r="J15">
-        <v>2.8797854478725666e-005</v>
+        <v>4.8595680291052838e-005</v>
       </c>
       <c r="K15">
-        <v>3.222749341970943e-005</v>
+        <v>4.4197157298011961e-005</v>
       </c>
       <c r="L15">
-        <v>2.8853425304335982e-005</v>
+        <v>3.765986360414951e-005</v>
       </c>
       <c r="M15">
-        <v>-4.6474647591307418e-006</v>
+        <v>-8.5043824339662752e-006</v>
       </c>
       <c r="N15">
-        <v>-5.9279040666617019e-006</v>
+        <v>-1.3652258818549123e-006</v>
       </c>
       <c r="O15">
-        <v>0.00021873238050523568</v>
+        <v>0.00029201457873657613</v>
       </c>
       <c r="P15">
-        <v>0.00035932503480700447</v>
+        <v>0.00048708324458381427</v>
       </c>
       <c r="Q15">
-        <v>-6.6476113471094928e-008</v>
+        <v>1.4822987477131018e-010</v>
       </c>
       <c r="R15">
-        <v>4.0036411696342752e-007</v>
+        <v>6.0498870313312555e-007</v>
       </c>
       <c r="S15">
-        <v>9.2128983869626371e-006</v>
+        <v>9.1571433522245278e-006</v>
       </c>
       <c r="T15">
-        <v>2.5559094647407591e-005</v>
+        <v>3.3653730719065569e-005</v>
       </c>
       <c r="U15">
-        <v>5.2233553827668987e-005</v>
+        <v>7.805283398497108e-005</v>
       </c>
       <c r="V15">
-        <v>0.00011762702812629294</v>
+        <v>0.00017132514491252648</v>
       </c>
       <c r="W15">
-        <v>4.4440610284291721e-006</v>
+        <v>6.1815425713756375e-006</v>
       </c>
       <c r="X15">
-        <v>9.8124145438962195e-006</v>
+        <v>2.2984246170428858e-005</v>
       </c>
       <c r="Y15">
-        <v>-1.4252319274319133e-005</v>
+        <v>-2.983056031935224e-006</v>
       </c>
       <c r="Z15">
-        <v>2.5978551697570828e-007</v>
+        <v>4.7229054744867639e-006</v>
       </c>
       <c r="AA15">
-        <v>-1.2671064972244857e-005</v>
+        <v>-1.5497115704036563e-005</v>
       </c>
       <c r="AB15">
-        <v>-2.4162488725262649e-005</v>
+        <v>-3.3242409807728142e-005</v>
       </c>
       <c r="AC15">
-        <v>-2.8486464029891759e-005</v>
+        <v>-3.693855171522541e-005</v>
       </c>
       <c r="AD15">
-        <v>-1.2504840490250627e-005</v>
+        <v>-1.0232488628933071e-005</v>
       </c>
       <c r="AE15">
-        <v>-3.8001402494417116e-006</v>
+        <v>-2.8085104644424592e-006</v>
       </c>
       <c r="AF15">
-        <v>-8.797145503086812e-006</v>
+        <v>-5.6300281281924788e-006</v>
       </c>
       <c r="AG15">
-        <v>-1.3310753702102757e-005</v>
+        <v>-1.3843613410107115e-005</v>
       </c>
       <c r="AH15">
-        <v>-1.3586776894979394e-006</v>
+        <v>-1.5557813089719672e-005</v>
       </c>
       <c r="AI15">
-        <v>-1.4621600892997558e-005</v>
+        <v>-9.4705342957230644e-006</v>
       </c>
       <c r="AJ15">
-        <v>3.3276879194390937e-006</v>
+        <v>3.3523078147858838e-006</v>
       </c>
       <c r="AK15">
-        <v>-9.7216222889163098e-006</v>
+        <v>-1.1811555604739871e-005</v>
       </c>
       <c r="AL15">
-        <v>5.3402235887113227e-006</v>
+        <v>8.76130078635941e-006</v>
       </c>
       <c r="AM15">
-        <v>3.7515092635861122e-005</v>
+        <v>6.416426935821308e-005</v>
       </c>
       <c r="AN15">
-        <v>4.5984874304311335e-005</v>
+        <v>8.6004830109555054e-005</v>
       </c>
       <c r="AO15">
-        <v>2.9574302848604279e-005</v>
+        <v>5.2401526149359407e-005</v>
       </c>
       <c r="AP15">
-        <v>-0.00030275701991134971</v>
+        <v>-0.00042018138682623526</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="36">
-        <v>0.0037342951915878679</v>
+        <v>0.0036585396371072937</v>
       </c>
       <c r="C16">
-        <v>-7.9122885279238555e-007</v>
+        <v>-1.1990824991993348e-006</v>
       </c>
       <c r="D16">
-        <v>5.4590076078451582e-008</v>
+        <v>6.2591536913412424e-008</v>
       </c>
       <c r="E16">
-        <v>-1.0764623120362862e-009</v>
+        <v>-1.3344564458733015e-009</v>
       </c>
       <c r="F16">
-        <v>-5.5058632227625303e-007</v>
+        <v>1.0589642950723105e-007</v>
       </c>
       <c r="G16">
-        <v>-2.9499764257745249e-007</v>
+        <v>3.3445131353844681e-007</v>
       </c>
       <c r="H16">
-        <v>2.0023432095994349e-009</v>
+        <v>2.8045621202800893e-007</v>
       </c>
       <c r="I16">
-        <v>2.689194403567782e-006</v>
+        <v>1.1783697000286257e-006</v>
       </c>
       <c r="J16">
-        <v>-3.4470170825954287e-007</v>
+        <v>2.5677042969583334e-008</v>
       </c>
       <c r="K16">
-        <v>1.1676695370223369e-008</v>
+        <v>5.3870219150891564e-007</v>
       </c>
       <c r="L16">
-        <v>-5.6321510997911591e-007</v>
+        <v>-4.8276326197862321e-007</v>
       </c>
       <c r="M16">
-        <v>-7.7921602106963636e-007</v>
+        <v>-1.5928779039035085e-006</v>
       </c>
       <c r="N16">
-        <v>8.2337651011315021e-007</v>
+        <v>7.2524281625305845e-007</v>
       </c>
       <c r="O16">
-        <v>-9.8295315034314918e-008</v>
+        <v>2.3005738238155903e-009</v>
       </c>
       <c r="P16">
-        <v>-6.6476113471094928e-008</v>
+        <v>1.4822987477131018e-010</v>
       </c>
       <c r="Q16">
-        <v>3.5927253610158445e-007</v>
+        <v>4.9127433615081086e-007</v>
       </c>
       <c r="R16">
-        <v>-2.8670051351141457e-008</v>
+        <v>-3.0477013525568561e-008</v>
       </c>
       <c r="S16">
-        <v>-5.2598949307893397e-007</v>
+        <v>-9.9865241406542973e-007</v>
       </c>
       <c r="T16">
-        <v>-1.082593160277186e-006</v>
+        <v>-2.0936753277018303e-006</v>
       </c>
       <c r="U16">
-        <v>-1.1712422641789682e-006</v>
+        <v>-1.8796289633447245e-006</v>
       </c>
       <c r="V16">
-        <v>-1.1733982462882396e-006</v>
+        <v>-1.6573994570743242e-006</v>
       </c>
       <c r="W16">
-        <v>-3.205923162380832e-008</v>
+        <v>-1.8175792073448295e-009</v>
       </c>
       <c r="X16">
-        <v>3.8186779376962182e-008</v>
+        <v>1.2643921735474548e-008</v>
       </c>
       <c r="Y16">
-        <v>2.7301354714079031e-008</v>
+        <v>-2.9081980020724066e-008</v>
       </c>
       <c r="Z16">
-        <v>2.3884675399934908e-007</v>
+        <v>-4.0318292284600454e-008</v>
       </c>
       <c r="AA16">
-        <v>9.1312201297291603e-008</v>
+        <v>4.3315426533133679e-008</v>
       </c>
       <c r="AB16">
-        <v>1.3739573166314297e-007</v>
+        <v>1.5752936271232524e-007</v>
       </c>
       <c r="AC16">
-        <v>3.2710821569166387e-007</v>
+        <v>1.2854958619771973e-007</v>
       </c>
       <c r="AD16">
-        <v>8.4030241226292336e-008</v>
+        <v>1.8626188516508072e-007</v>
       </c>
       <c r="AE16">
-        <v>2.8607903899949791e-007</v>
+        <v>9.1757563282953775e-008</v>
       </c>
       <c r="AF16">
-        <v>-6.6611041472218002e-007</v>
+        <v>-1.341169874279427e-006</v>
       </c>
       <c r="AG16">
-        <v>3.9718023545360877e-007</v>
+        <v>4.228812390649141e-007</v>
       </c>
       <c r="AH16">
-        <v>1.8513451823322819e-007</v>
+        <v>1.7214734342241863e-008</v>
       </c>
       <c r="AI16">
-        <v>-1.2156571249124857e-007</v>
+        <v>-1.832902010723789e-007</v>
       </c>
       <c r="AJ16">
-        <v>8.8811649832457534e-008</v>
+        <v>6.1998983468083446e-008</v>
       </c>
       <c r="AK16">
-        <v>3.6270036049166956e-007</v>
+        <v>5.812110532758491e-007</v>
       </c>
       <c r="AL16">
-        <v>9.7319857190056803e-007</v>
+        <v>1.5080866010079759e-006</v>
       </c>
       <c r="AM16">
-        <v>-3.4128546557224754e-007</v>
+        <v>1.7496194412443849e-008</v>
       </c>
       <c r="AN16">
-        <v>-4.0217974034122969e-007</v>
+        <v>-8.5742149494599676e-007</v>
       </c>
       <c r="AO16">
-        <v>4.0115930129168271e-007</v>
+        <v>4.9130597591549865e-007</v>
       </c>
       <c r="AP16">
-        <v>-1.6299109273448618e-005</v>
+        <v>-2.1508327258095072e-005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B17" s="38">
-        <v>0.006103055307191115</v>
+        <v>0.0058281227512731737</v>
       </c>
       <c r="C17">
-        <v>-1.4508581854701431e-007</v>
+        <v>-2.1156417749525872e-007</v>
       </c>
       <c r="D17">
-        <v>1.0922533180102369e-007</v>
+        <v>1.5341863011779749e-007</v>
       </c>
       <c r="E17">
-        <v>-5.6057026211111896e-010</v>
+        <v>-7.138658799892091e-010</v>
       </c>
       <c r="F17">
-        <v>-6.0560811041093439e-007</v>
+        <v>-2.4449872586452882e-007</v>
       </c>
       <c r="G17">
-        <v>5.2347753403858497e-008</v>
+        <v>6.0598256661434905e-007</v>
       </c>
       <c r="H17">
-        <v>-2.8846225345227695e-007</v>
+        <v>2.3697115515700178e-007</v>
       </c>
       <c r="I17">
-        <v>1.4166592043480422e-006</v>
+        <v>1.5662952765942899e-007</v>
       </c>
       <c r="J17">
-        <v>-6.2508342962321771e-008</v>
+        <v>2.1561218144052509e-007</v>
       </c>
       <c r="K17">
-        <v>3.3303270018820507e-008</v>
+        <v>6.2338771711301892e-007</v>
       </c>
       <c r="L17">
-        <v>-7.0757348551744233e-007</v>
+        <v>-4.3270734964571776e-007</v>
       </c>
       <c r="M17">
-        <v>3.9532297634890702e-007</v>
+        <v>3.9394704892968519e-007</v>
       </c>
       <c r="N17">
-        <v>1.255829100044072e-006</v>
+        <v>1.3291153349139657e-006</v>
       </c>
       <c r="O17">
-        <v>6.1346329277269804e-008</v>
+        <v>1.6494916383435248e-007</v>
       </c>
       <c r="P17">
-        <v>4.0036411696342752e-007</v>
+        <v>6.0498870313312555e-007</v>
       </c>
       <c r="Q17">
-        <v>-2.8670051351141457e-008</v>
+        <v>-3.0477013525568561e-008</v>
       </c>
       <c r="R17">
-        <v>2.8226657720447701e-007</v>
+        <v>3.9988027917134218e-007</v>
       </c>
       <c r="S17">
-        <v>-2.189586747751018e-007</v>
+        <v>-4.0192139970285961e-007</v>
       </c>
       <c r="T17">
-        <v>-7.4671701989823227e-007</v>
+        <v>-1.2433801457650174e-006</v>
       </c>
       <c r="U17">
-        <v>-7.7886127363473037e-007</v>
+        <v>-1.3245107931655647e-006</v>
       </c>
       <c r="V17">
-        <v>-1.1614251368051566e-006</v>
+        <v>-1.5276026607032562e-006</v>
       </c>
       <c r="W17">
-        <v>-6.9983156497226295e-009</v>
+        <v>-1.1950023209417145e-008</v>
       </c>
       <c r="X17">
-        <v>-3.2857460266173232e-007</v>
+        <v>-5.1361535112100706e-007</v>
       </c>
       <c r="Y17">
-        <v>4.4569342735605814e-007</v>
+        <v>7.8376623555860937e-007</v>
       </c>
       <c r="Z17">
-        <v>1.4511416240336071e-007</v>
+        <v>4.982369696192317e-007</v>
       </c>
       <c r="AA17">
-        <v>2.8860415989163921e-007</v>
+        <v>6.0566207473539998e-007</v>
       </c>
       <c r="AB17">
-        <v>8.3898352104731079e-008</v>
+        <v>2.4327593757564965e-007</v>
       </c>
       <c r="AC17">
-        <v>3.2981006691701331e-007</v>
+        <v>5.7231458365000172e-007</v>
       </c>
       <c r="AD17">
-        <v>9.9305010931962623e-008</v>
+        <v>3.6387305672495656e-007</v>
       </c>
       <c r="AE17">
-        <v>-1.3568759272950307e-007</v>
+        <v>1.7298314821990692e-007</v>
       </c>
       <c r="AF17">
-        <v>2.2924426976167048e-007</v>
+        <v>6.0059830972189296e-007</v>
       </c>
       <c r="AG17">
-        <v>4.1791486239990688e-007</v>
+        <v>8.4608689702091202e-007</v>
       </c>
       <c r="AH17">
-        <v>3.5091433062409641e-007</v>
+        <v>6.0651870150983846e-007</v>
       </c>
       <c r="AI17">
-        <v>5.2817943229684631e-007</v>
+        <v>9.8348127539321973e-007</v>
       </c>
       <c r="AJ17">
-        <v>2.7045074420717075e-008</v>
+        <v>1.9090271616559965e-008</v>
       </c>
       <c r="AK17">
-        <v>-2.0534660222149491e-007</v>
+        <v>-2.2717045843404118e-007</v>
       </c>
       <c r="AL17">
-        <v>-3.8593377822986103e-007</v>
+        <v>-2.5367117759044332e-007</v>
       </c>
       <c r="AM17">
-        <v>3.5098759074296964e-007</v>
+        <v>6.9564686889849267e-007</v>
       </c>
       <c r="AN17">
-        <v>-1.3372786108309842e-007</v>
+        <v>1.0031866967654594e-007</v>
       </c>
       <c r="AO17">
-        <v>2.1600337069520682e-007</v>
+        <v>3.799758399756497e-007</v>
       </c>
       <c r="AP17">
-        <v>-1.6582194447138083e-005</v>
+        <v>-2.4388921088267708e-005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="39" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B18" s="40">
-        <v>0.09548203051726574</v>
+        <v>0.056028923187156528</v>
       </c>
       <c r="C18">
-        <v>1.8517040194903059e-005</v>
+        <v>1.4884072788953506e-005</v>
       </c>
       <c r="D18">
-        <v>3.6103131531145211e-006</v>
+        <v>7.0112325618311525e-006</v>
       </c>
       <c r="E18">
-        <v>-3.5893692030041808e-008</v>
+        <v>-6.6781547832464609e-008</v>
       </c>
       <c r="F18">
-        <v>2.7170379921619961e-006</v>
+        <v>-2.9452461624698152e-005</v>
       </c>
       <c r="G18">
-        <v>1.8950085924134944e-005</v>
+        <v>1.7201246141644041e-005</v>
       </c>
       <c r="H18">
-        <v>-1.0102568834723561e-005</v>
+        <v>-2.1863965375210907e-005</v>
       </c>
       <c r="I18">
-        <v>4.1418122986522017e-005</v>
+        <v>6.9117886888648644e-005</v>
       </c>
       <c r="J18">
-        <v>4.2767062229907322e-005</v>
+        <v>-2.8916157700149033e-006</v>
       </c>
       <c r="K18">
-        <v>6.8387450532201547e-005</v>
+        <v>4.2981932512952125e-005</v>
       </c>
       <c r="L18">
-        <v>7.6302908815064155e-005</v>
+        <v>7.1355909149969999e-005</v>
       </c>
       <c r="M18">
-        <v>0.00010307176721410211</v>
+        <v>0.00022628912202526751</v>
       </c>
       <c r="N18">
-        <v>0.00013790270270276842</v>
+        <v>0.0003322244199550654</v>
       </c>
       <c r="O18">
-        <v>1.3690693698538349e-006</v>
+        <v>-2.5762186851251101e-006</v>
       </c>
       <c r="P18">
-        <v>9.2128983869626371e-006</v>
+        <v>9.1571433522245278e-006</v>
       </c>
       <c r="Q18">
-        <v>-5.2598949307893397e-007</v>
+        <v>-9.9865241406542973e-007</v>
       </c>
       <c r="R18">
-        <v>-2.189586747751018e-007</v>
+        <v>-4.0192139970285961e-007</v>
       </c>
       <c r="S18">
-        <v>0.00040185666832858309</v>
+        <v>0.0006181954883799028</v>
       </c>
       <c r="T18">
-        <v>0.00030771443369179228</v>
+        <v>0.00052559917204737978</v>
       </c>
       <c r="U18">
-        <v>0.00032556629053213444</v>
+        <v>0.00053702855942069493</v>
       </c>
       <c r="V18">
-        <v>0.0003312290745476545</v>
+        <v>0.00053567397011358264</v>
       </c>
       <c r="W18">
-        <v>-2.5095272502010553e-005</v>
+        <v>-5.2821863752288208e-005</v>
       </c>
       <c r="X18">
-        <v>-1.203248191882754e-005</v>
+        <v>-6.3882520270649556e-006</v>
       </c>
       <c r="Y18">
-        <v>-3.2561068352510787e-006</v>
+        <v>-2.0648352133008092e-006</v>
       </c>
       <c r="Z18">
-        <v>2.8992252903558938e-006</v>
+        <v>-2.5281665727460142e-008</v>
       </c>
       <c r="AA18">
-        <v>1.0840861546771853e-005</v>
+        <v>1.1924496994903507e-005</v>
       </c>
       <c r="AB18">
-        <v>1.738616336342561e-006</v>
+        <v>7.6860631952979739e-007</v>
       </c>
       <c r="AC18">
-        <v>-1.9949260242950272e-006</v>
+        <v>-3.5974050545001064e-006</v>
       </c>
       <c r="AD18">
-        <v>-9.1976914471285034e-006</v>
+        <v>-8.4707807627059983e-006</v>
       </c>
       <c r="AE18">
-        <v>5.4551772439596363e-006</v>
+        <v>1.2436215472632833e-005</v>
       </c>
       <c r="AF18">
-        <v>-1.3251212198936776e-005</v>
+        <v>-7.5382480447067985e-006</v>
       </c>
       <c r="AG18">
-        <v>-1.5048776979301138e-006</v>
+        <v>9.7311790138335068e-007</v>
       </c>
       <c r="AH18">
-        <v>7.0571094583989321e-006</v>
+        <v>-1.6505423023474369e-006</v>
       </c>
       <c r="AI18">
-        <v>2.7417248489578047e-005</v>
+        <v>3.491319224955999e-005</v>
       </c>
       <c r="AJ18">
-        <v>1.1528453879259364e-006</v>
+        <v>2.1082369280683485e-006</v>
       </c>
       <c r="AK18">
-        <v>-6.2585370296498384e-006</v>
+        <v>-9.7051415601163675e-006</v>
       </c>
       <c r="AL18">
-        <v>-5.9751198377587954e-006</v>
+        <v>-2.1826107707637484e-005</v>
       </c>
       <c r="AM18">
-        <v>-3.6858901044363273e-006</v>
+        <v>1.0274605883777777e-005</v>
       </c>
       <c r="AN18">
-        <v>1.2118155934762154e-005</v>
+        <v>3.5375413406100618e-005</v>
       </c>
       <c r="AO18">
-        <v>-3.52811119898162e-006</v>
+        <v>2.6951643665568104e-007</v>
       </c>
       <c r="AP18">
-        <v>-0.00040633742823792483</v>
+        <v>-0.00065287149090789373</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" s="42">
-        <v>0.23812370280937262</v>
+        <v>0.19812606479476158</v>
       </c>
       <c r="C19">
-        <v>2.1433944777983911e-005</v>
+        <v>1.452594121585812e-005</v>
       </c>
       <c r="D19">
-        <v>1.4551711867712239e-006</v>
+        <v>5.0923712108035726e-006</v>
       </c>
       <c r="E19">
-        <v>-5.2720622824999362e-009</v>
+        <v>-3.8981138735169933e-008</v>
       </c>
       <c r="F19">
-        <v>2.9826609188361928e-005</v>
+        <v>-5.7827767708908611e-005</v>
       </c>
       <c r="G19">
-        <v>5.8530869337246176e-005</v>
+        <v>2.6687010482826545e-005</v>
       </c>
       <c r="H19">
-        <v>8.2453657084484315e-006</v>
+        <v>-1.7436150984919568e-005</v>
       </c>
       <c r="I19">
-        <v>0.0001475861451768093</v>
+        <v>7.7217416611187988e-005</v>
       </c>
       <c r="J19">
-        <v>0.00011291966000146619</v>
+        <v>5.1528360001284302e-005</v>
       </c>
       <c r="K19">
-        <v>0.00012041243653630638</v>
+        <v>7.1981745014269394e-005</v>
       </c>
       <c r="L19">
-        <v>0.00017469733004463797</v>
+        <v>0.00017145138545501218</v>
       </c>
       <c r="M19">
-        <v>0.00019322378168651393</v>
+        <v>0.00038450754058676358</v>
       </c>
       <c r="N19">
-        <v>0.00020774809159567785</v>
+        <v>0.00048899698819935796</v>
       </c>
       <c r="O19">
-        <v>1.4269608064549994e-006</v>
+        <v>-6.8896915372780856e-006</v>
       </c>
       <c r="P19">
-        <v>2.5559094647407591e-005</v>
+        <v>3.3653730719065569e-005</v>
       </c>
       <c r="Q19">
-        <v>-1.082593160277186e-006</v>
+        <v>-2.0936753277018303e-006</v>
       </c>
       <c r="R19">
-        <v>-7.4671701989823227e-007</v>
+        <v>-1.2433801457650174e-006</v>
       </c>
       <c r="S19">
-        <v>0.00030771443369179228</v>
+        <v>0.00052559917204737978</v>
       </c>
       <c r="T19">
-        <v>0.00052799135671550068</v>
+        <v>0.0008778546858203833</v>
       </c>
       <c r="U19">
-        <v>0.00044001196566564329</v>
+        <v>0.0007252136106781021</v>
       </c>
       <c r="V19">
-        <v>0.00045636442224928568</v>
+        <v>0.00073911770354669819</v>
       </c>
       <c r="W19">
-        <v>-2.9410909104665857e-005</v>
+        <v>-6.1184059747835561e-005</v>
       </c>
       <c r="X19">
-        <v>-1.0538528787935978e-005</v>
+        <v>-3.7947678682015299e-006</v>
       </c>
       <c r="Y19">
-        <v>-1.879533270477764e-006</v>
+        <v>1.2817069161161698e-006</v>
       </c>
       <c r="Z19">
-        <v>1.4244530379494007e-005</v>
+        <v>1.3240452776389524e-005</v>
       </c>
       <c r="AA19">
-        <v>1.0872737543094408e-005</v>
+        <v>1.2476331565497992e-005</v>
       </c>
       <c r="AB19">
-        <v>2.7286354398788212e-006</v>
+        <v>2.0236482215974834e-006</v>
       </c>
       <c r="AC19">
-        <v>-1.2418314718859313e-006</v>
+        <v>-6.8425417764040975e-006</v>
       </c>
       <c r="AD19">
-        <v>4.0950163762599611e-006</v>
+        <v>1.8609689284261745e-005</v>
       </c>
       <c r="AE19">
-        <v>1.3099714561266492e-005</v>
+        <v>2.6256493518372172e-005</v>
       </c>
       <c r="AF19">
-        <v>8.9946878505259772e-006</v>
+        <v>3.1407502484235399e-005</v>
       </c>
       <c r="AG19">
-        <v>-1.9577109379104521e-006</v>
+        <v>1.7490729274399655e-006</v>
       </c>
       <c r="AH19">
-        <v>8.8776686013733523e-006</v>
+        <v>1.1941363959170487e-005</v>
       </c>
       <c r="AI19">
-        <v>3.6235179673801954e-005</v>
+        <v>4.1766734008430472e-005</v>
       </c>
       <c r="AJ19">
-        <v>3.8987734166405195e-006</v>
+        <v>6.0262347839048993e-006</v>
       </c>
       <c r="AK19">
-        <v>-2.5827058157671142e-005</v>
+        <v>-4.6872100138054961e-005</v>
       </c>
       <c r="AL19">
-        <v>-3.3329339649620324e-005</v>
+        <v>-6.7115840162723433e-005</v>
       </c>
       <c r="AM19">
-        <v>1.1509599744097986e-005</v>
+        <v>3.21774671993565e-005</v>
       </c>
       <c r="AN19">
-        <v>-3.2634341447403256e-007</v>
+        <v>2.4848831685137375e-005</v>
       </c>
       <c r="AO19">
-        <v>-4.7042788226998064e-007</v>
+        <v>5.4919818375307578e-006</v>
       </c>
       <c r="AP19">
-        <v>-0.00052252182929613791</v>
+        <v>-0.00081528509648339724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B20" s="44">
-        <v>0.31821438760022502</v>
+        <v>0.24558049591874415</v>
       </c>
       <c r="C20">
-        <v>1.6068467230109077e-005</v>
+        <v>-5.4617283016080246e-006</v>
       </c>
       <c r="D20">
-        <v>-1.2574434854147617e-006</v>
+        <v>6.2971182140917587e-007</v>
       </c>
       <c r="E20">
-        <v>1.8621702660315119e-008</v>
+        <v>-7.4653988349580514e-010</v>
       </c>
       <c r="F20">
-        <v>7.7067871112882592e-005</v>
+        <v>2.0406508971919075e-005</v>
       </c>
       <c r="G20">
-        <v>0.00011563980312241556</v>
+        <v>0.00011881705780286176</v>
       </c>
       <c r="H20">
-        <v>2.7065321088779635e-005</v>
+        <v>1.5379962932345748e-005</v>
       </c>
       <c r="I20">
-        <v>0.00025053085647868425</v>
+        <v>0.00027774812238656667</v>
       </c>
       <c r="J20">
-        <v>0.00020556065281434631</v>
+        <v>0.00019886943104741403</v>
       </c>
       <c r="K20">
-        <v>0.00016761802192011998</v>
+        <v>0.00014098316680873652</v>
       </c>
       <c r="L20">
-        <v>0.00024746977414980665</v>
+        <v>0.0002664085811517233</v>
       </c>
       <c r="M20">
-        <v>0.00021688371710354415</v>
+        <v>0.00039877029553871709</v>
       </c>
       <c r="N20">
-        <v>0.00026263938306234834</v>
+        <v>0.00054234300562312852</v>
       </c>
       <c r="O20">
-        <v>2.515332292271699e-005</v>
+        <v>3.3672125007707757e-005</v>
       </c>
       <c r="P20">
-        <v>5.2233553827668987e-005</v>
+        <v>7.805283398497108e-005</v>
       </c>
       <c r="Q20">
-        <v>-1.1712422641789682e-006</v>
+        <v>-1.8796289633447245e-006</v>
       </c>
       <c r="R20">
-        <v>-7.7886127363473037e-007</v>
+        <v>-1.3245107931655647e-006</v>
       </c>
       <c r="S20">
-        <v>0.00032556629053213444</v>
+        <v>0.00053702855942069493</v>
       </c>
       <c r="T20">
-        <v>0.00044001196566564329</v>
+        <v>0.0007252136106781021</v>
       </c>
       <c r="U20">
-        <v>0.00067759445890464237</v>
+        <v>0.0010414559171678475</v>
       </c>
       <c r="V20">
-        <v>0.00054987335656083575</v>
+        <v>0.00084660439966625705</v>
       </c>
       <c r="W20">
-        <v>-2.9371138479430848e-005</v>
+        <v>-5.9130766111084258e-005</v>
       </c>
       <c r="X20">
-        <v>-1.4647847323345396e-005</v>
+        <v>-9.6668533485705702e-006</v>
       </c>
       <c r="Y20">
-        <v>1.4870557603473111e-005</v>
+        <v>2.0903920768753777e-005</v>
       </c>
       <c r="Z20">
-        <v>1.7661603953569064e-005</v>
+        <v>1.6691177973604407e-005</v>
       </c>
       <c r="AA20">
-        <v>2.937978597661088e-005</v>
+        <v>3.020181919171421e-005</v>
       </c>
       <c r="AB20">
-        <v>2.9970593639499313e-005</v>
+        <v>3.4055185979845265e-005</v>
       </c>
       <c r="AC20">
-        <v>1.2407403429402279e-005</v>
+        <v>1.1719108700266008e-005</v>
       </c>
       <c r="AD20">
-        <v>8.8091680587791223e-006</v>
+        <v>1.9798333368560285e-005</v>
       </c>
       <c r="AE20">
-        <v>2.7888939973106595e-005</v>
+        <v>4.1908679342650702e-005</v>
       </c>
       <c r="AF20">
-        <v>2.1141536129609427e-005</v>
+        <v>4.0206067787797281e-005</v>
       </c>
       <c r="AG20">
-        <v>1.1890955959027727e-005</v>
+        <v>1.4275253276953943e-005</v>
       </c>
       <c r="AH20">
-        <v>1.4447385807352095e-005</v>
+        <v>1.3068158798258727e-005</v>
       </c>
       <c r="AI20">
-        <v>5.316616360713023e-005</v>
+        <v>7.3799905878736433e-005</v>
       </c>
       <c r="AJ20">
-        <v>3.4403792303626931e-006</v>
+        <v>5.5680105136555876e-006</v>
       </c>
       <c r="AK20">
-        <v>-1.7087252851769322e-005</v>
+        <v>-3.3287647285331971e-005</v>
       </c>
       <c r="AL20">
-        <v>-2.53775640724264e-005</v>
+        <v>-4.856055424662907e-005</v>
       </c>
       <c r="AM20">
-        <v>3.051718150137985e-005</v>
+        <v>5.6440226258127084e-005</v>
       </c>
       <c r="AN20">
-        <v>1.4538127790085997e-005</v>
+        <v>3.9036968393280059e-005</v>
       </c>
       <c r="AO20">
-        <v>5.7349763497242096e-006</v>
+        <v>1.0936207128327204e-005</v>
       </c>
       <c r="AP20">
-        <v>-0.00058379962659958675</v>
+        <v>-0.00087657203411124372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="45" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" s="46">
-        <v>0.53555154239486202</v>
+        <v>0.45260127554706414</v>
       </c>
       <c r="C21">
-        <v>9.4897033567697504e-006</v>
+        <v>-2.5404145693849345e-005</v>
       </c>
       <c r="D21">
-        <v>-2.4769981294328631e-006</v>
+        <v>-1.3765013731005937e-006</v>
       </c>
       <c r="E21">
-        <v>2.6504998988733093e-008</v>
+        <v>1.2515057612066826e-008</v>
       </c>
       <c r="F21">
-        <v>0.00013332323715633561</v>
+        <v>0.00012718878827616318</v>
       </c>
       <c r="G21">
-        <v>0.00016622348452302328</v>
+        <v>0.00022185467234822799</v>
       </c>
       <c r="H21">
-        <v>7.5877653170087968e-005</v>
+        <v>9.8753209057929532e-005</v>
       </c>
       <c r="I21">
-        <v>0.00021858548226335356</v>
+        <v>0.00047700497649964314</v>
       </c>
       <c r="J21">
-        <v>0.00024647651390258631</v>
+        <v>0.00027838484579186733</v>
       </c>
       <c r="K21">
-        <v>0.00021345802077400066</v>
+        <v>0.00022324792406510369</v>
       </c>
       <c r="L21">
-        <v>0.00030137075645459322</v>
+        <v>0.00036098338415828553</v>
       </c>
       <c r="M21">
-        <v>0.00020884502243644841</v>
+        <v>0.00037654072547360526</v>
       </c>
       <c r="N21">
-        <v>0.00027693469497704526</v>
+        <v>0.00055638070028019688</v>
       </c>
       <c r="O21">
-        <v>8.5420730546135798e-005</v>
+        <v>0.00011883493935629087</v>
       </c>
       <c r="P21">
-        <v>0.00011762702812629294</v>
+        <v>0.00017132514491252648</v>
       </c>
       <c r="Q21">
-        <v>-1.1733982462882396e-006</v>
+        <v>-1.6573994570743242e-006</v>
       </c>
       <c r="R21">
-        <v>-1.1614251368051566e-006</v>
+        <v>-1.5276026607032562e-006</v>
       </c>
       <c r="S21">
-        <v>0.0003312290745476545</v>
+        <v>0.00053567397011358264</v>
       </c>
       <c r="T21">
-        <v>0.00045636442224928568</v>
+        <v>0.00073911770354669819</v>
       </c>
       <c r="U21">
-        <v>0.00054987335656083575</v>
+        <v>0.00084660439966625705</v>
       </c>
       <c r="V21">
-        <v>0.00085112955281346802</v>
+        <v>0.0012768607516629085</v>
       </c>
       <c r="W21">
-        <v>-2.9639085650493949e-005</v>
+        <v>-5.8567081998071795e-005</v>
       </c>
       <c r="X21">
-        <v>7.8410571608962098e-007</v>
+        <v>8.8919236159488253e-006</v>
       </c>
       <c r="Y21">
-        <v>3.1023231326235678e-005</v>
+        <v>4.7230141781310535e-005</v>
       </c>
       <c r="Z21">
-        <v>4.8074468398032086e-005</v>
+        <v>6.1210231389333182e-005</v>
       </c>
       <c r="AA21">
-        <v>5.9364707723022821e-005</v>
+        <v>7.394664528094047e-005</v>
       </c>
       <c r="AB21">
-        <v>4.8723632054763549e-005</v>
+        <v>6.0916031049356524e-005</v>
       </c>
       <c r="AC21">
-        <v>3.4821358251137283e-005</v>
+        <v>3.0854723208393392e-005</v>
       </c>
       <c r="AD21">
-        <v>3.6732859571081631e-005</v>
+        <v>5.4233051447352625e-005</v>
       </c>
       <c r="AE21">
-        <v>3.6004040631679556e-005</v>
+        <v>6.1534689512365685e-005</v>
       </c>
       <c r="AF21">
-        <v>4.2379327541820213e-005</v>
+        <v>6.941023716429527e-005</v>
       </c>
       <c r="AG21">
-        <v>3.7447481340725222e-005</v>
+        <v>5.5550520462775981e-005</v>
       </c>
       <c r="AH21">
-        <v>3.4782637836399874e-005</v>
+        <v>4.480004288900839e-005</v>
       </c>
       <c r="AI21">
-        <v>7.7002239468186497e-005</v>
+        <v>0.00010460774289662919</v>
       </c>
       <c r="AJ21">
-        <v>2.4276581866448354e-006</v>
+        <v>3.8109024638165528e-006</v>
       </c>
       <c r="AK21">
-        <v>-2.0360900594175327e-005</v>
+        <v>-2.6905867298020424e-005</v>
       </c>
       <c r="AL21">
-        <v>-7.2224181939863537e-006</v>
+        <v>-2.6701492802552706e-005</v>
       </c>
       <c r="AM21">
-        <v>3.7475255665174825e-005</v>
+        <v>6.5075653341252352e-005</v>
       </c>
       <c r="AN21">
-        <v>4.4510376989899414e-005</v>
+        <v>6.8631927242742482e-005</v>
       </c>
       <c r="AO21">
-        <v>1.7346720579090299e-005</v>
+        <v>3.8001087087854524e-005</v>
       </c>
       <c r="AP21">
-        <v>-0.00065654453498738611</v>
+        <v>-0.00099654314500691719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" s="48">
-        <v>0.021669143260047045</v>
+        <v>0.029418171557324534</v>
       </c>
       <c r="C22">
-        <v>-2.9612353110644097e-006</v>
+        <v>-1.3492463693255288e-006</v>
       </c>
       <c r="D22">
-        <v>-1.8035534091480585e-007</v>
+        <v>-6.5326357302293199e-007</v>
       </c>
       <c r="E22">
-        <v>-2.4839963851299245e-009</v>
+        <v>6.0928547468144311e-010</v>
       </c>
       <c r="F22">
-        <v>-4.2638242460648021e-006</v>
+        <v>-2.1981978641412828e-006</v>
       </c>
       <c r="G22">
-        <v>-5.2182925460247837e-006</v>
+        <v>-1.0593954103372224e-005</v>
       </c>
       <c r="H22">
-        <v>3.1052046240622741e-007</v>
+        <v>3.2519165590751367e-006</v>
       </c>
       <c r="I22">
-        <v>-8.4119925083351799e-006</v>
+        <v>-5.9090369373980734e-006</v>
       </c>
       <c r="J22">
-        <v>-5.4823981271315746e-006</v>
+        <v>-1.3605763122693461e-006</v>
       </c>
       <c r="K22">
-        <v>-9.5739518070307417e-006</v>
+        <v>-7.1261517501733006e-006</v>
       </c>
       <c r="L22">
-        <v>-1.6963120946405787e-005</v>
+        <v>-1.9510440726569187e-005</v>
       </c>
       <c r="M22">
-        <v>-1.4026290268421372e-005</v>
+        <v>-3.2941815395869099e-005</v>
       </c>
       <c r="N22">
-        <v>-1.7968863313020266e-005</v>
+        <v>-4.6611020427512924e-005</v>
       </c>
       <c r="O22">
-        <v>4.0568246932831677e-007</v>
+        <v>7.9571214332780425e-007</v>
       </c>
       <c r="P22">
-        <v>4.4440610284291721e-006</v>
+        <v>6.1815425713756375e-006</v>
       </c>
       <c r="Q22">
-        <v>-3.205923162380832e-008</v>
+        <v>-1.8175792073448295e-009</v>
       </c>
       <c r="R22">
-        <v>-6.9983156497226295e-009</v>
+        <v>-1.1950023209417145e-008</v>
       </c>
       <c r="S22">
-        <v>-2.5095272502010553e-005</v>
+        <v>-5.2821863752288208e-005</v>
       </c>
       <c r="T22">
-        <v>-2.9410909104665857e-005</v>
+        <v>-6.1184059747835561e-005</v>
       </c>
       <c r="U22">
-        <v>-2.9371138479430848e-005</v>
+        <v>-5.9130766111084258e-005</v>
       </c>
       <c r="V22">
-        <v>-2.9639085650493949e-005</v>
+        <v>-5.8567081998071795e-005</v>
       </c>
       <c r="W22">
-        <v>7.7653498517311517e-006</v>
+        <v>1.2966458387776563e-005</v>
       </c>
       <c r="X22">
-        <v>-2.6894210815556432e-006</v>
+        <v>-4.7486449253106205e-006</v>
       </c>
       <c r="Y22">
-        <v>1.1355242538379258e-006</v>
+        <v>1.3026009295876447e-006</v>
       </c>
       <c r="Z22">
-        <v>-1.8826600193779392e-006</v>
+        <v>-1.8191083714965117e-006</v>
       </c>
       <c r="AA22">
-        <v>-7.578888100678044e-007</v>
+        <v>-1.3241783798138233e-006</v>
       </c>
       <c r="AB22">
-        <v>-6.1375463304196458e-007</v>
+        <v>-6.1886305871439664e-007</v>
       </c>
       <c r="AC22">
-        <v>6.501490753619437e-007</v>
+        <v>1.7457256735408715e-006</v>
       </c>
       <c r="AD22">
-        <v>4.529162634098739e-007</v>
+        <v>-5.7280385187644144e-007</v>
       </c>
       <c r="AE22">
-        <v>-1.4928615463157779e-006</v>
+        <v>-2.5464447642512554e-006</v>
       </c>
       <c r="AF22">
-        <v>-2.3646893069901768e-007</v>
+        <v>-1.9053698782991744e-006</v>
       </c>
       <c r="AG22">
-        <v>-5.0030198544017931e-008</v>
+        <v>-2.5407575797308063e-007</v>
       </c>
       <c r="AH22">
-        <v>1.7649093124845441e-007</v>
+        <v>1.3026583188232237e-006</v>
       </c>
       <c r="AI22">
-        <v>7.7853611095443265e-007</v>
+        <v>2.1104999447177234e-006</v>
       </c>
       <c r="AJ22">
-        <v>-1.9256891780656306e-007</v>
+        <v>-3.7879379789052547e-007</v>
       </c>
       <c r="AK22">
-        <v>1.2163977789424145e-006</v>
+        <v>2.2628069051866646e-006</v>
       </c>
       <c r="AL22">
-        <v>8.6264414187688931e-007</v>
+        <v>3.8617154332693008e-006</v>
       </c>
       <c r="AM22">
-        <v>2.3578612931584926e-006</v>
+        <v>2.6710494213892514e-006</v>
       </c>
       <c r="AN22">
-        <v>2.973960857031859e-006</v>
+        <v>2.2724021093152135e-006</v>
       </c>
       <c r="AO22">
-        <v>1.6469883503758293e-006</v>
+        <v>2.7631122555568436e-006</v>
       </c>
       <c r="AP22">
-        <v>4.8008945201308781e-005</v>
+        <v>8.8828958102027142e-005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B23" s="50">
-        <v>3.7061275144406536</v>
+        <v>3.6810046715236786</v>
       </c>
       <c r="C23">
-        <v>-2.3093899068929166e-006</v>
+        <v>-3.0566291045204588e-006</v>
       </c>
       <c r="D23">
-        <v>-1.188813751662672e-006</v>
+        <v>1.6720268935133294e-007</v>
       </c>
       <c r="E23">
-        <v>5.9060951476986973e-009</v>
+        <v>-5.8607539928650276e-009</v>
       </c>
       <c r="F23">
-        <v>4.1029776062692153e-005</v>
+        <v>6.4011269037128371e-005</v>
       </c>
       <c r="G23">
-        <v>-2.0247012625917792e-005</v>
+        <v>-2.4052375578865337e-005</v>
       </c>
       <c r="H23">
-        <v>-1.2473712730409489e-005</v>
+        <v>-2.3121875250242425e-005</v>
       </c>
       <c r="I23">
-        <v>7.2405098850131553e-005</v>
+        <v>2.5260337948133032e-005</v>
       </c>
       <c r="J23">
-        <v>-2.5315281471236168e-006</v>
+        <v>-8.1713240965126618e-007</v>
       </c>
       <c r="K23">
-        <v>-1.6651496044337727e-005</v>
+        <v>-1.7272249849171144e-005</v>
       </c>
       <c r="L23">
-        <v>1.4397572078518554e-005</v>
+        <v>1.6923460502841575e-005</v>
       </c>
       <c r="M23">
-        <v>-5.151864926263033e-005</v>
+        <v>-5.1092436065715036e-005</v>
       </c>
       <c r="N23">
-        <v>6.0459290916061814e-006</v>
+        <v>1.1808724530298936e-005</v>
       </c>
       <c r="O23">
-        <v>-3.225966889051839e-006</v>
+        <v>4.3036010826267765e-006</v>
       </c>
       <c r="P23">
-        <v>9.8124145438962195e-006</v>
+        <v>2.2984246170428858e-005</v>
       </c>
       <c r="Q23">
-        <v>3.8186779376962182e-008</v>
+        <v>1.2643921735474548e-008</v>
       </c>
       <c r="R23">
-        <v>-3.2857460266173232e-007</v>
+        <v>-5.1361535112100706e-007</v>
       </c>
       <c r="S23">
-        <v>-1.203248191882754e-005</v>
+        <v>-6.3882520270649556e-006</v>
       </c>
       <c r="T23">
-        <v>-1.0538528787935978e-005</v>
+        <v>-3.7947678682015299e-006</v>
       </c>
       <c r="U23">
-        <v>-1.4647847323345396e-005</v>
+        <v>-9.6668533485705702e-006</v>
       </c>
       <c r="V23">
-        <v>7.8410571608962098e-007</v>
+        <v>8.8919236159488253e-006</v>
       </c>
       <c r="W23">
-        <v>-2.6894210815556432e-006</v>
+        <v>-4.7486449253106205e-006</v>
       </c>
       <c r="X23">
-        <v>0.00020570457684010224</v>
+        <v>0.00026618574213022972</v>
       </c>
       <c r="Y23">
-        <v>-1.7872018947313993e-006</v>
+        <v>1.4826369253339504e-006</v>
       </c>
       <c r="Z23">
-        <v>1.7334429676801693e-006</v>
+        <v>2.3964949404020164e-007</v>
       </c>
       <c r="AA23">
-        <v>1.7362752875598054e-007</v>
+        <v>-1.4784363475479879e-006</v>
       </c>
       <c r="AB23">
-        <v>-4.5683719134742133e-006</v>
+        <v>-6.4972865769638083e-006</v>
       </c>
       <c r="AC23">
-        <v>-5.4678833453256653e-006</v>
+        <v>-8.7540485316786906e-006</v>
       </c>
       <c r="AD23">
-        <v>-2.3477769551759128e-006</v>
+        <v>-7.4585799833967909e-007</v>
       </c>
       <c r="AE23">
-        <v>-3.9220038693308276e-006</v>
+        <v>-6.2547532110338081e-006</v>
       </c>
       <c r="AF23">
-        <v>-1.5254192525198752e-006</v>
+        <v>2.4636066722224614e-006</v>
       </c>
       <c r="AG23">
-        <v>-3.9537666154027344e-006</v>
+        <v>-1.9966671669001821e-006</v>
       </c>
       <c r="AH23">
-        <v>-9.4251549591647934e-007</v>
+        <v>5.3214870260497741e-007</v>
       </c>
       <c r="AI23">
-        <v>-4.6636457997062928e-008</v>
+        <v>-1.9561255611679146e-006</v>
       </c>
       <c r="AJ23">
-        <v>5.5388452563065381e-007</v>
+        <v>6.676103653544172e-007</v>
       </c>
       <c r="AK23">
-        <v>-2.3213266837218369e-006</v>
+        <v>-5.0528363681051455e-006</v>
       </c>
       <c r="AL23">
-        <v>8.8322516702161606e-006</v>
+        <v>2.291161423511528e-005</v>
       </c>
       <c r="AM23">
-        <v>6.9741712220176887e-006</v>
+        <v>9.5760742955595027e-006</v>
       </c>
       <c r="AN23">
-        <v>1.9422655464468328e-005</v>
+        <v>3.3223723877602205e-005</v>
       </c>
       <c r="AO23">
-        <v>2.1788446848683607e-005</v>
+        <v>2.8847637244940806e-005</v>
       </c>
       <c r="AP23">
-        <v>-4.635130837478164e-005</v>
+        <v>-0.00011630195622004899</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="51" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B24" s="52">
-        <v>0.087092155368049082</v>
+        <v>0.10858792566199335</v>
       </c>
       <c r="C24">
-        <v>-2.5636235374154108e-006</v>
+        <v>-5.4565205610653314e-006</v>
       </c>
       <c r="D24">
-        <v>-1.4768776949176357e-006</v>
+        <v>-2.1227211759058631e-006</v>
       </c>
       <c r="E24">
-        <v>1.6840048501920847e-008</v>
+        <v>2.1978717852510756e-008</v>
       </c>
       <c r="F24">
-        <v>2.5410318695238008e-005</v>
+        <v>3.3106865039906383e-006</v>
       </c>
       <c r="G24">
-        <v>1.6821231397551979e-005</v>
+        <v>3.1626405469781338e-005</v>
       </c>
       <c r="H24">
-        <v>1.2223847002925052e-005</v>
+        <v>1.6911770380696296e-005</v>
       </c>
       <c r="I24">
-        <v>-1.8518886521472586e-005</v>
+        <v>1.5825987529069794e-005</v>
       </c>
       <c r="J24">
-        <v>9.0658135587654085e-006</v>
+        <v>1.6910292269908415e-005</v>
       </c>
       <c r="K24">
-        <v>1.7339343582152473e-005</v>
+        <v>2.62982399278995e-005</v>
       </c>
       <c r="L24">
-        <v>2.8056679495846024e-005</v>
+        <v>3.8822206662332336e-005</v>
       </c>
       <c r="M24">
-        <v>-4.6377892871198506e-006</v>
+        <v>-1.171444925546317e-005</v>
       </c>
       <c r="N24">
-        <v>1.8819295026292754e-006</v>
+        <v>-3.8651836017596954e-007</v>
       </c>
       <c r="O24">
-        <v>-1.0961921392814662e-005</v>
+        <v>-1.0064043398450995e-005</v>
       </c>
       <c r="P24">
-        <v>-1.4252319274319133e-005</v>
+        <v>-2.983056031935224e-006</v>
       </c>
       <c r="Q24">
-        <v>2.7301354714079031e-008</v>
+        <v>-2.9081980020724066e-008</v>
       </c>
       <c r="R24">
-        <v>4.4569342735605814e-007</v>
+        <v>7.8376623555860937e-007</v>
       </c>
       <c r="S24">
-        <v>-3.2561068352510787e-006</v>
+        <v>-2.0648352133008092e-006</v>
       </c>
       <c r="T24">
-        <v>-1.879533270477764e-006</v>
+        <v>1.2817069161161698e-006</v>
       </c>
       <c r="U24">
-        <v>1.4870557603473111e-005</v>
+        <v>2.0903920768753777e-005</v>
       </c>
       <c r="V24">
-        <v>3.1023231326235678e-005</v>
+        <v>4.7230141781310535e-005</v>
       </c>
       <c r="W24">
-        <v>1.1355242538379258e-006</v>
+        <v>1.3026009295876447e-006</v>
       </c>
       <c r="X24">
-        <v>-1.7872018947313993e-006</v>
+        <v>1.4826369253339504e-006</v>
       </c>
       <c r="Y24">
-        <v>0.0010465824973344704</v>
+        <v>0.0013344736427729799</v>
       </c>
       <c r="Z24">
-        <v>0.00040544062598465123</v>
+        <v>0.00052034972697558317</v>
       </c>
       <c r="AA24">
-        <v>0.00040436692858937973</v>
+        <v>0.00051153562916468186</v>
       </c>
       <c r="AB24">
-        <v>0.0004049288016471312</v>
+        <v>0.0005202063212616508</v>
       </c>
       <c r="AC24">
-        <v>0.00039319445603011225</v>
+        <v>0.00050058027671729581</v>
       </c>
       <c r="AD24">
-        <v>0.00040942594779439352</v>
+        <v>0.00051997911135611406</v>
       </c>
       <c r="AE24">
-        <v>0.0004092398696611198</v>
+        <v>0.00052251720408019579</v>
       </c>
       <c r="AF24">
-        <v>0.00041276175157134134</v>
+        <v>0.00052963345500201377</v>
       </c>
       <c r="AG24">
-        <v>0.00041084568652661037</v>
+        <v>0.000525044964266943</v>
       </c>
       <c r="AH24">
-        <v>0.00041428668137754281</v>
+        <v>0.00053392649986694221</v>
       </c>
       <c r="AI24">
-        <v>0.00041709427058320083</v>
+        <v>0.00054227900662922224</v>
       </c>
       <c r="AJ24">
-        <v>6.5548127510304564e-007</v>
+        <v>7.4685978340721438e-007</v>
       </c>
       <c r="AK24">
-        <v>6.9898523339728609e-007</v>
+        <v>-5.9577869557207769e-006</v>
       </c>
       <c r="AL24">
-        <v>8.2967756253633423e-006</v>
+        <v>1.9073735838888796e-005</v>
       </c>
       <c r="AM24">
-        <v>0.00018070475351414993</v>
+        <v>0.00023421167778613547</v>
       </c>
       <c r="AN24">
-        <v>0.00025115565359353729</v>
+        <v>0.00032199417819482243</v>
       </c>
       <c r="AO24">
-        <v>0.00012840022015475887</v>
+        <v>0.00016054235651108368</v>
       </c>
       <c r="AP24">
-        <v>-0.00043234322940733288</v>
+        <v>-0.00056242643761634289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" s="54">
-        <v>0.16867147533635074</v>
+        <v>0.14897954092470864</v>
       </c>
       <c r="C25">
-        <v>2.3035257734025827e-006</v>
+        <v>6.9045849256134104e-006</v>
       </c>
       <c r="D25">
-        <v>-2.8615376355335222e-007</v>
+        <v>-1.4204724915873719e-006</v>
       </c>
       <c r="E25">
-        <v>5.4267287881985273e-009</v>
+        <v>1.6306733397015664e-008</v>
       </c>
       <c r="F25">
-        <v>4.4244666748915375e-005</v>
+        <v>5.0083044514629634e-005</v>
       </c>
       <c r="G25">
-        <v>1.9152511835206626e-005</v>
+        <v>4.0073760916241387e-005</v>
       </c>
       <c r="H25">
-        <v>2.900859242275307e-005</v>
+        <v>4.6706176682048179e-005</v>
       </c>
       <c r="I25">
-        <v>1.1532560900429436e-005</v>
+        <v>4.8667966901542637e-005</v>
       </c>
       <c r="J25">
-        <v>3.172428322255638e-005</v>
+        <v>4.9008782758040496e-005</v>
       </c>
       <c r="K25">
-        <v>3.9175454888009825e-005</v>
+        <v>5.6178033401799938e-005</v>
       </c>
       <c r="L25">
-        <v>3.5056367401662253e-005</v>
+        <v>5.8487502512385833e-005</v>
       </c>
       <c r="M25">
-        <v>2.0444658617424558e-005</v>
+        <v>1.377442932259899e-005</v>
       </c>
       <c r="N25">
-        <v>5.1225277545595425e-006</v>
+        <v>1.0300944309266066e-006</v>
       </c>
       <c r="O25">
-        <v>-3.7556254142176783e-006</v>
+        <v>-4.3885105089461426e-006</v>
       </c>
       <c r="P25">
-        <v>2.5978551697570828e-007</v>
+        <v>4.7229054744867639e-006</v>
       </c>
       <c r="Q25">
-        <v>2.3884675399934908e-007</v>
+        <v>-4.0318292284600454e-008</v>
       </c>
       <c r="R25">
-        <v>1.4511416240336071e-007</v>
+        <v>4.982369696192317e-007</v>
       </c>
       <c r="S25">
-        <v>2.8992252903558938e-006</v>
+        <v>-2.5281665727460142e-008</v>
       </c>
       <c r="T25">
-        <v>1.4244530379494007e-005</v>
+        <v>1.3240452776389524e-005</v>
       </c>
       <c r="U25">
-        <v>1.7661603953569064e-005</v>
+        <v>1.6691177973604407e-005</v>
       </c>
       <c r="V25">
-        <v>4.8074468398032086e-005</v>
+        <v>6.1210231389333182e-005</v>
       </c>
       <c r="W25">
-        <v>-1.8826600193779392e-006</v>
+        <v>-1.8191083714965117e-006</v>
       </c>
       <c r="X25">
-        <v>1.7334429676801693e-006</v>
+        <v>2.3964949404020164e-007</v>
       </c>
       <c r="Y25">
-        <v>0.00040544062598465123</v>
+        <v>0.00052034972697558317</v>
       </c>
       <c r="Z25">
-        <v>0.00069985233088170771</v>
+        <v>0.00092323100732360868</v>
       </c>
       <c r="AA25">
-        <v>0.000395233272257001</v>
+        <v>0.00050415919903426564</v>
       </c>
       <c r="AB25">
-        <v>0.00040103889894710522</v>
+        <v>0.00051383556149295253</v>
       </c>
       <c r="AC25">
-        <v>0.00038111933980099189</v>
+        <v>0.00048591169037263997</v>
       </c>
       <c r="AD25">
-        <v>0.00040534602446976964</v>
+        <v>0.00051629905420938981</v>
       </c>
       <c r="AE25">
-        <v>0.0004030051573716306</v>
+        <v>0.00051419313073667564</v>
       </c>
       <c r="AF25">
-        <v>0.00040698780472539151</v>
+        <v>0.000523312394897458</v>
       </c>
       <c r="AG25">
-        <v>0.00039827932766506357</v>
+        <v>0.00050856889698043094</v>
       </c>
       <c r="AH25">
-        <v>0.00040641750518664226</v>
+        <v>0.00052443684758426935</v>
       </c>
       <c r="AI25">
-        <v>0.00040411990113430426</v>
+        <v>0.00052576778216103712</v>
       </c>
       <c r="AJ25">
-        <v>9.4432640690907628e-007</v>
+        <v>1.1396440287283138e-006</v>
       </c>
       <c r="AK25">
-        <v>1.5746708165548742e-005</v>
+        <v>1.7289091847633489e-005</v>
       </c>
       <c r="AL25">
-        <v>4.9342469135271296e-005</v>
+        <v>7.196136020451606e-005</v>
       </c>
       <c r="AM25">
-        <v>0.00015186334166978569</v>
+        <v>0.0001919967666176049</v>
       </c>
       <c r="AN25">
-        <v>0.00022408046260449503</v>
+        <v>0.00029441787277817005</v>
       </c>
       <c r="AO25">
-        <v>0.00011387775396989366</v>
+        <v>0.00013964516152186851</v>
       </c>
       <c r="AP25">
-        <v>-0.00048679327927524552</v>
+        <v>-0.00060454647545752607</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="55" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B26" s="56">
-        <v>0.14721070348243023</v>
+        <v>0.14566796561743484</v>
       </c>
       <c r="C26">
-        <v>-5.9854706066209294e-006</v>
+        <v>-9.2140248080619702e-006</v>
       </c>
       <c r="D26">
-        <v>-1.5003954140171852e-007</v>
+        <v>-6.2302281700384794e-007</v>
       </c>
       <c r="E26">
-        <v>4.5939750203317785e-009</v>
+        <v>9.5683249076728374e-009</v>
       </c>
       <c r="F26">
-        <v>6.3082394451987732e-005</v>
+        <v>7.0479338259572425e-005</v>
       </c>
       <c r="G26">
-        <v>3.3563824903552418e-005</v>
+        <v>5.9501500556113362e-005</v>
       </c>
       <c r="H26">
-        <v>3.7331295725159054e-005</v>
+        <v>5.6118241391775228e-005</v>
       </c>
       <c r="I26">
-        <v>0.00016697856894276779</v>
+        <v>0.00027885264661320607</v>
       </c>
       <c r="J26">
-        <v>4.7283214122018877e-005</v>
+        <v>6.2269613969801171e-005</v>
       </c>
       <c r="K26">
-        <v>5.3658533812372405e-005</v>
+        <v>7.6323852799504009e-005</v>
       </c>
       <c r="L26">
-        <v>3.9190129771313957e-005</v>
+        <v>5.6620429204231235e-005</v>
       </c>
       <c r="M26">
-        <v>1.056211775816746e-005</v>
+        <v>-1.7815526670196947e-006</v>
       </c>
       <c r="N26">
-        <v>5.7547306732656998e-006</v>
+        <v>1.4226440318394358e-006</v>
       </c>
       <c r="O26">
-        <v>-1.6278950981465053e-005</v>
+        <v>-1.9140988367270893e-005</v>
       </c>
       <c r="P26">
-        <v>-1.2671064972244857e-005</v>
+        <v>-1.5497115704036563e-005</v>
       </c>
       <c r="Q26">
-        <v>9.1312201297291603e-008</v>
+        <v>4.3315426533133679e-008</v>
       </c>
       <c r="R26">
-        <v>2.8860415989163921e-007</v>
+        <v>6.0566207473539998e-007</v>
       </c>
       <c r="S26">
-        <v>1.0840861546771853e-005</v>
+        <v>1.1924496994903507e-005</v>
       </c>
       <c r="T26">
-        <v>1.0872737543094408e-005</v>
+        <v>1.2476331565497992e-005</v>
       </c>
       <c r="U26">
-        <v>2.937978597661088e-005</v>
+        <v>3.020181919171421e-005</v>
       </c>
       <c r="V26">
-        <v>5.9364707723022821e-005</v>
+        <v>7.394664528094047e-005</v>
       </c>
       <c r="W26">
-        <v>-7.578888100678044e-007</v>
+        <v>-1.3241783798138233e-006</v>
       </c>
       <c r="X26">
-        <v>1.7362752875598054e-007</v>
+        <v>-1.4784363475479879e-006</v>
       </c>
       <c r="Y26">
-        <v>0.00040436692858937973</v>
+        <v>0.00051153562916468186</v>
       </c>
       <c r="Z26">
-        <v>0.000395233272257001</v>
+        <v>0.00050415919903426564</v>
       </c>
       <c r="AA26">
-        <v>0.00072701021406823985</v>
+        <v>0.00097086286747575113</v>
       </c>
       <c r="AB26">
-        <v>0.00039987326997609522</v>
+        <v>0.00050912476892693863</v>
       </c>
       <c r="AC26">
-        <v>0.00038661088245688303</v>
+        <v>0.00049185211071092673</v>
       </c>
       <c r="AD26">
-        <v>0.00040312902647650047</v>
+        <v>0.00051158469672698409</v>
       </c>
       <c r="AE26">
-        <v>0.00040117483331531944</v>
+        <v>0.00051011167138284195</v>
       </c>
       <c r="AF26">
-        <v>0.00040744229658496974</v>
+        <v>0.00052312032635263173</v>
       </c>
       <c r="AG26">
-        <v>0.00040415045704532567</v>
+        <v>0.00051572872470170025</v>
       </c>
       <c r="AH26">
-        <v>0.00040221702041429592</v>
+        <v>0.0005177522843573002</v>
       </c>
       <c r="AI26">
-        <v>0.00040610230040085034</v>
+        <v>0.00052607671614143684</v>
       </c>
       <c r="AJ26">
-        <v>2.4569732033994614e-007</v>
+        <v>-3.0259415907579416e-007</v>
       </c>
       <c r="AK26">
-        <v>1.8898305474518288e-005</v>
+        <v>2.1198313042686329e-005</v>
       </c>
       <c r="AL26">
-        <v>3.4390660047410623e-005</v>
+        <v>5.3465892274768818e-005</v>
       </c>
       <c r="AM26">
-        <v>0.00014730831319492352</v>
+        <v>0.0001870636910257013</v>
       </c>
       <c r="AN26">
-        <v>0.00022281909628516845</v>
+        <v>0.000285233309074899</v>
       </c>
       <c r="AO26">
-        <v>0.00011095469808093466</v>
+        <v>0.00013171953013120264</v>
       </c>
       <c r="AP26">
-        <v>-0.00048107354296420067</v>
+        <v>-0.00060671180888266572</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" s="58">
-        <v>0.20194206047497273</v>
+        <v>0.20663723541909171</v>
       </c>
       <c r="C27">
-        <v>-8.2273743438366187e-006</v>
+        <v>-1.0313171308644734e-005</v>
       </c>
       <c r="D27">
-        <v>9.675019783045412e-008</v>
+        <v>-3.8245723508207593e-007</v>
       </c>
       <c r="E27">
-        <v>3.4325231597384547e-009</v>
+        <v>8.8833016353610491e-009</v>
       </c>
       <c r="F27">
-        <v>6.5862820119779028e-005</v>
+        <v>6.1358063412193483e-005</v>
       </c>
       <c r="G27">
-        <v>2.9113658753666929e-005</v>
+        <v>5.3914486731929852e-005</v>
       </c>
       <c r="H27">
-        <v>3.9202701076032536e-005</v>
+        <v>4.961621045324187e-005</v>
       </c>
       <c r="I27">
-        <v>8.1372758819726245e-005</v>
+        <v>0.00016931878525802354</v>
       </c>
       <c r="J27">
-        <v>4.8353502230762386e-005</v>
+        <v>7.4991438986809402e-005</v>
       </c>
       <c r="K27">
-        <v>4.5168777664251691e-005</v>
+        <v>6.2921334202830303e-005</v>
       </c>
       <c r="L27">
-        <v>4.3389703833701777e-005</v>
+        <v>6.0711769440053944e-005</v>
       </c>
       <c r="M27">
-        <v>1.7313287330902169e-005</v>
+        <v>1.4079622249694464e-005</v>
       </c>
       <c r="N27">
-        <v>9.5454956921998968e-006</v>
+        <v>5.9353718532672434e-006</v>
       </c>
       <c r="O27">
-        <v>-2.0724285015695785e-005</v>
+        <v>-3.0688957124645384e-005</v>
       </c>
       <c r="P27">
-        <v>-2.4162488725262649e-005</v>
+        <v>-3.3242409807728142e-005</v>
       </c>
       <c r="Q27">
-        <v>1.3739573166314297e-007</v>
+        <v>1.5752936271232524e-007</v>
       </c>
       <c r="R27">
-        <v>8.3898352104731079e-008</v>
+        <v>2.4327593757564965e-007</v>
       </c>
       <c r="S27">
-        <v>1.738616336342561e-006</v>
+        <v>7.6860631952979739e-007</v>
       </c>
       <c r="T27">
-        <v>2.7286354398788212e-006</v>
+        <v>2.0236482215974834e-006</v>
       </c>
       <c r="U27">
-        <v>2.9970593639499313e-005</v>
+        <v>3.4055185979845265e-005</v>
       </c>
       <c r="V27">
-        <v>4.8723632054763549e-005</v>
+        <v>6.0916031049356524e-005</v>
       </c>
       <c r="W27">
-        <v>-6.1375463304196458e-007</v>
+        <v>-6.1886305871439664e-007</v>
       </c>
       <c r="X27">
-        <v>-4.5683719134742133e-006</v>
+        <v>-6.4972865769638083e-006</v>
       </c>
       <c r="Y27">
-        <v>0.0004049288016471312</v>
+        <v>0.0005202063212616508</v>
       </c>
       <c r="Z27">
-        <v>0.00040103889894710522</v>
+        <v>0.00051383556149295253</v>
       </c>
       <c r="AA27">
-        <v>0.00039987326997609522</v>
+        <v>0.00050912476892693863</v>
       </c>
       <c r="AB27">
-        <v>0.00079475261483228114</v>
+        <v>0.0010410332107662955</v>
       </c>
       <c r="AC27">
-        <v>0.00038818228460027259</v>
+        <v>0.00049786627218526155</v>
       </c>
       <c r="AD27">
-        <v>0.00040153604859707263</v>
+        <v>0.00050937296467844023</v>
       </c>
       <c r="AE27">
-        <v>0.00040553745959276763</v>
+        <v>0.00051533481889534953</v>
       </c>
       <c r="AF27">
-        <v>0.00041159413318294144</v>
+        <v>0.00052932014414411473</v>
       </c>
       <c r="AG27">
-        <v>0.00040784828807215173</v>
+        <v>0.00052272715331533586</v>
       </c>
       <c r="AH27">
-        <v>0.00040246512623406873</v>
+        <v>0.00052072103211164063</v>
       </c>
       <c r="AI27">
-        <v>0.00040991897225836984</v>
+        <v>0.00053419577656390411</v>
       </c>
       <c r="AJ27">
-        <v>7.7792571680627997e-007</v>
+        <v>7.8121096403120024e-007</v>
       </c>
       <c r="AK27">
-        <v>1.9907112257510732e-005</v>
+        <v>3.2632265726924685e-005</v>
       </c>
       <c r="AL27">
-        <v>1.3392342018075987e-005</v>
+        <v>2.3791568521155883e-005</v>
       </c>
       <c r="AM27">
-        <v>0.00015893673537363678</v>
+        <v>0.0002016981735404138</v>
       </c>
       <c r="AN27">
-        <v>0.00022180168910255032</v>
+        <v>0.00028435230084728413</v>
       </c>
       <c r="AO27">
-        <v>0.00011002647308434409</v>
+        <v>0.00014507143757859741</v>
       </c>
       <c r="AP27">
-        <v>-0.00047687124664680484</v>
+        <v>-0.00060296090955374887</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="59" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B28" s="60">
-        <v>0.18069755201873702</v>
+        <v>0.19965295135163547</v>
       </c>
       <c r="C28">
-        <v>-3.0512157408656893e-006</v>
+        <v>-1.1986385540214616e-006</v>
       </c>
       <c r="D28">
-        <v>-4.5639613423287407e-007</v>
+        <v>-1.5039401779212911e-006</v>
       </c>
       <c r="E28">
-        <v>5.8186728297240692e-009</v>
+        <v>1.5600795521473537e-008</v>
       </c>
       <c r="F28">
-        <v>3.876379266523138e-005</v>
+        <v>5.8485873698033226e-005</v>
       </c>
       <c r="G28">
-        <v>2.4459194341473887e-005</v>
+        <v>3.6055336745835541e-005</v>
       </c>
       <c r="H28">
-        <v>4.1140396085821411e-005</v>
+        <v>6.3360687740348669e-005</v>
       </c>
       <c r="I28">
-        <v>-9.9608127622207824e-006</v>
+        <v>3.3088229457751132e-006</v>
       </c>
       <c r="J28">
-        <v>3.5960673289890923e-005</v>
+        <v>4.6798934243861067e-005</v>
       </c>
       <c r="K28">
-        <v>4.4140105487324294e-005</v>
+        <v>5.7140633105299419e-005</v>
       </c>
       <c r="L28">
-        <v>2.4417459269349466e-005</v>
+        <v>3.1883391601819595e-005</v>
       </c>
       <c r="M28">
-        <v>-3.6712926107519594e-006</v>
+        <v>-2.1079255577771287e-005</v>
       </c>
       <c r="N28">
-        <v>6.09506550281316e-006</v>
+        <v>-1.1469328372500471e-006</v>
       </c>
       <c r="O28">
-        <v>-1.3082745607955334e-005</v>
+        <v>-2.0628762376289773e-005</v>
       </c>
       <c r="P28">
-        <v>-2.8486464029891759e-005</v>
+        <v>-3.693855171522541e-005</v>
       </c>
       <c r="Q28">
-        <v>3.2710821569166387e-007</v>
+        <v>1.2854958619771973e-007</v>
       </c>
       <c r="R28">
-        <v>3.2981006691701331e-007</v>
+        <v>5.7231458365000172e-007</v>
       </c>
       <c r="S28">
-        <v>-1.9949260242950272e-006</v>
+        <v>-3.5974050545001064e-006</v>
       </c>
       <c r="T28">
-        <v>-1.2418314718859313e-006</v>
+        <v>-6.8425417764040975e-006</v>
       </c>
       <c r="U28">
-        <v>1.2407403429402279e-005</v>
+        <v>1.1719108700266008e-005</v>
       </c>
       <c r="V28">
-        <v>3.4821358251137283e-005</v>
+        <v>3.0854723208393392e-005</v>
       </c>
       <c r="W28">
-        <v>6.501490753619437e-007</v>
+        <v>1.7457256735408715e-006</v>
       </c>
       <c r="X28">
-        <v>-5.4678833453256653e-006</v>
+        <v>-8.7540485316786906e-006</v>
       </c>
       <c r="Y28">
-        <v>0.00039319445603011225</v>
+        <v>0.00050058027671729581</v>
       </c>
       <c r="Z28">
-        <v>0.00038111933980099189</v>
+        <v>0.00048591169037263997</v>
       </c>
       <c r="AA28">
-        <v>0.00038661088245688303</v>
+        <v>0.00049185211071092673</v>
       </c>
       <c r="AB28">
-        <v>0.00038818228460027259</v>
+        <v>0.00049786627218526155</v>
       </c>
       <c r="AC28">
-        <v>0.00076733838377662008</v>
+        <v>0.0010258044753750249</v>
       </c>
       <c r="AD28">
-        <v>0.00039128594530491784</v>
+        <v>0.00049671095707840148</v>
       </c>
       <c r="AE28">
-        <v>0.00038892531824976945</v>
+        <v>0.00049533758608076171</v>
       </c>
       <c r="AF28">
-        <v>0.00039342489704449784</v>
+        <v>0.00050343103582341068</v>
       </c>
       <c r="AG28">
-        <v>0.00039306646203779005</v>
+        <v>0.00050014831161000349</v>
       </c>
       <c r="AH28">
-        <v>0.00039179943560906013</v>
+        <v>0.0005054783719640627</v>
       </c>
       <c r="AI28">
-        <v>0.00039404597248016176</v>
+        <v>0.0005100993575582524</v>
       </c>
       <c r="AJ28">
-        <v>-1.9800387870848751e-007</v>
+        <v>-7.4479776836812179e-007</v>
       </c>
       <c r="AK28">
-        <v>2.1456337586684172e-005</v>
+        <v>3.3510277764512816e-005</v>
       </c>
       <c r="AL28">
-        <v>3.0367833758606832e-005</v>
+        <v>5.4402427370255421e-005</v>
       </c>
       <c r="AM28">
-        <v>0.00012369951560224323</v>
+        <v>0.00015615954036215577</v>
       </c>
       <c r="AN28">
-        <v>0.00019148442444949005</v>
+        <v>0.00025355206957475512</v>
       </c>
       <c r="AO28">
-        <v>8.0419854247972819e-005</v>
+        <v>9.0689602332166185e-005</v>
       </c>
       <c r="AP28">
-        <v>-0.00044166285513180581</v>
+        <v>-0.00052604386838211732</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="61" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B29" s="62">
-        <v>0.15624471444591531</v>
+        <v>0.15990004743035754</v>
       </c>
       <c r="C29">
-        <v>-1.878729065664977e-006</v>
+        <v>-8.4211831382252095e-006</v>
       </c>
       <c r="D29">
-        <v>-1.1823394706252754e-007</v>
+        <v>-5.2469527554032416e-007</v>
       </c>
       <c r="E29">
-        <v>4.5198669120803201e-009</v>
+        <v>8.2051577455061754e-009</v>
       </c>
       <c r="F29">
-        <v>3.3906581350823055e-005</v>
+        <v>5.0678852997012804e-005</v>
       </c>
       <c r="G29">
-        <v>1.7673161332526791e-005</v>
+        <v>4.2529158245214823e-005</v>
       </c>
       <c r="H29">
-        <v>2.6122838509773255e-005</v>
+        <v>4.6833934160612407e-005</v>
       </c>
       <c r="I29">
-        <v>2.3916726630222456e-005</v>
+        <v>6.9014922507617605e-005</v>
       </c>
       <c r="J29">
-        <v>2.1759754083255555e-005</v>
+        <v>3.4367207296911602e-005</v>
       </c>
       <c r="K29">
-        <v>3.7205736557522412e-005</v>
+        <v>6.0501803556184004e-005</v>
       </c>
       <c r="L29">
-        <v>2.4516056335317969e-005</v>
+        <v>4.8532108911144482e-005</v>
       </c>
       <c r="M29">
-        <v>6.5337293116074437e-006</v>
+        <v>2.7513307153190908e-006</v>
       </c>
       <c r="N29">
-        <v>1.2743049188292555e-006</v>
+        <v>9.5209343616987744e-006</v>
       </c>
       <c r="O29">
-        <v>-1.4245120790306973e-005</v>
+        <v>-1.6390371485274349e-005</v>
       </c>
       <c r="P29">
-        <v>-1.2504840490250627e-005</v>
+        <v>-1.0232488628933071e-005</v>
       </c>
       <c r="Q29">
-        <v>8.4030241226292336e-008</v>
+        <v>1.8626188516508072e-007</v>
       </c>
       <c r="R29">
-        <v>9.9305010931962623e-008</v>
+        <v>3.6387305672495656e-007</v>
       </c>
       <c r="S29">
-        <v>-9.1976914471285034e-006</v>
+        <v>-8.4707807627059983e-006</v>
       </c>
       <c r="T29">
-        <v>4.0950163762599611e-006</v>
+        <v>1.8609689284261745e-005</v>
       </c>
       <c r="U29">
-        <v>8.8091680587791223e-006</v>
+        <v>1.9798333368560285e-005</v>
       </c>
       <c r="V29">
-        <v>3.6732859571081631e-005</v>
+        <v>5.4233051447352625e-005</v>
       </c>
       <c r="W29">
-        <v>4.529162634098739e-007</v>
+        <v>-5.7280385187644144e-007</v>
       </c>
       <c r="X29">
-        <v>-2.3477769551759128e-006</v>
+        <v>-7.4585799833967909e-007</v>
       </c>
       <c r="Y29">
-        <v>0.00040942594779439352</v>
+        <v>0.00051997911135611406</v>
       </c>
       <c r="Z29">
-        <v>0.00040534602446976964</v>
+        <v>0.00051629905420938981</v>
       </c>
       <c r="AA29">
-        <v>0.00040312902647650047</v>
+        <v>0.00051158469672698409</v>
       </c>
       <c r="AB29">
-        <v>0.00040153604859707263</v>
+        <v>0.00050937296467844023</v>
       </c>
       <c r="AC29">
-        <v>0.00039128594530491784</v>
+        <v>0.00049671095707840148</v>
       </c>
       <c r="AD29">
-        <v>0.000725159031645235</v>
+        <v>0.00094922645497473666</v>
       </c>
       <c r="AE29">
-        <v>0.00040532316683409094</v>
+        <v>0.0005153046357864793</v>
       </c>
       <c r="AF29">
-        <v>0.00041446897007393262</v>
+        <v>0.00053082327942721242</v>
       </c>
       <c r="AG29">
-        <v>0.00041097242651447902</v>
+        <v>0.00052310382665577359</v>
       </c>
       <c r="AH29">
-        <v>0.00041057887019088678</v>
+        <v>0.00052560675009238065</v>
       </c>
       <c r="AI29">
-        <v>0.00041194588448983114</v>
+        <v>0.00053138186603843307</v>
       </c>
       <c r="AJ29">
-        <v>-8.9319740562471474e-007</v>
+        <v>-1.7785162949822643e-006</v>
       </c>
       <c r="AK29">
-        <v>2.1399712591545541e-005</v>
+        <v>2.5614915838043812e-005</v>
       </c>
       <c r="AL29">
-        <v>2.2972002120995236e-005</v>
+        <v>4.3210533993365694e-005</v>
       </c>
       <c r="AM29">
-        <v>0.00016395862951943741</v>
+        <v>0.0002102823705365061</v>
       </c>
       <c r="AN29">
-        <v>0.00022854862851508765</v>
+        <v>0.00027804782011876041</v>
       </c>
       <c r="AO29">
-        <v>8.5360618158684135e-005</v>
+        <v>0.00010085454407000955</v>
       </c>
       <c r="AP29">
-        <v>-0.00043526500217888506</v>
+        <v>-0.00057253860122573113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="63" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="64">
-        <v>0.15583435742309787</v>
+        <v>0.16326549907506352</v>
       </c>
       <c r="C30">
-        <v>1.8601942434672763e-006</v>
+        <v>4.4683182648765972e-006</v>
       </c>
       <c r="D30">
-        <v>-1.2959412249917352e-008</v>
+        <v>6.2881907521521071e-008</v>
       </c>
       <c r="E30">
-        <v>3.0747427021775349e-009</v>
+        <v>3.0500671676812088e-009</v>
       </c>
       <c r="F30">
-        <v>4.7980655969664375e-005</v>
+        <v>8.8202930660462398e-005</v>
       </c>
       <c r="G30">
-        <v>2.0718899209249278e-005</v>
+        <v>3.8483740793973267e-005</v>
       </c>
       <c r="H30">
-        <v>2.8190629180186639e-005</v>
+        <v>5.5739607388940673e-005</v>
       </c>
       <c r="I30">
-        <v>0.00020303885685219863</v>
+        <v>8.3771645997239447e-005</v>
       </c>
       <c r="J30">
-        <v>3.2307830672689441e-005</v>
+        <v>4.1590795210360796e-005</v>
       </c>
       <c r="K30">
-        <v>3.3859352017882931e-005</v>
+        <v>4.712016533266904e-005</v>
       </c>
       <c r="L30">
-        <v>3.4209284274085016e-005</v>
+        <v>4.5377217982958259e-005</v>
       </c>
       <c r="M30">
-        <v>3.8088800263124524e-005</v>
+        <v>5.4076813806703119e-005</v>
       </c>
       <c r="N30">
-        <v>1.148750789405873e-005</v>
+        <v>2.2112269379800968e-005</v>
       </c>
       <c r="O30">
-        <v>-6.2333134071258565e-006</v>
+        <v>-8.472289427204899e-006</v>
       </c>
       <c r="P30">
-        <v>-3.8001402494417116e-006</v>
+        <v>-2.8085104644424592e-006</v>
       </c>
       <c r="Q30">
-        <v>2.8607903899949791e-007</v>
+        <v>9.1757563282953775e-008</v>
       </c>
       <c r="R30">
-        <v>-1.3568759272950307e-007</v>
+        <v>1.7298314821990692e-007</v>
       </c>
       <c r="S30">
-        <v>5.4551772439596363e-006</v>
+        <v>1.2436215472632833e-005</v>
       </c>
       <c r="T30">
-        <v>1.3099714561266492e-005</v>
+        <v>2.6256493518372172e-005</v>
       </c>
       <c r="U30">
-        <v>2.7888939973106595e-005</v>
+        <v>4.1908679342650702e-005</v>
       </c>
       <c r="V30">
-        <v>3.6004040631679556e-005</v>
+        <v>6.1534689512365685e-005</v>
       </c>
       <c r="W30">
-        <v>-1.4928615463157779e-006</v>
+        <v>-2.5464447642512554e-006</v>
       </c>
       <c r="X30">
-        <v>-3.9220038693308276e-006</v>
+        <v>-6.2547532110338081e-006</v>
       </c>
       <c r="Y30">
-        <v>0.0004092398696611198</v>
+        <v>0.00052251720408019579</v>
       </c>
       <c r="Z30">
-        <v>0.0004030051573716306</v>
+        <v>0.00051419313073667564</v>
       </c>
       <c r="AA30">
-        <v>0.00040117483331531944</v>
+        <v>0.00051011167138284195</v>
       </c>
       <c r="AB30">
-        <v>0.00040553745959276763</v>
+        <v>0.00051533481889534953</v>
       </c>
       <c r="AC30">
-        <v>0.00038892531824976945</v>
+        <v>0.00049533758608076171</v>
       </c>
       <c r="AD30">
-        <v>0.00040532316683409094</v>
+        <v>0.0005153046357864793</v>
       </c>
       <c r="AE30">
-        <v>0.00067200772452458862</v>
+        <v>0.00087740966681362233</v>
       </c>
       <c r="AF30">
-        <v>0.00041110853826921065</v>
+        <v>0.00052754367410924857</v>
       </c>
       <c r="AG30">
-        <v>0.00040863009163989158</v>
+        <v>0.00052136165674489363</v>
       </c>
       <c r="AH30">
-        <v>0.0004090892446772411</v>
+        <v>0.00052362406615767026</v>
       </c>
       <c r="AI30">
-        <v>0.00041035036161160522</v>
+        <v>0.00053232795629203718</v>
       </c>
       <c r="AJ30">
-        <v>1.4537093930401382e-006</v>
+        <v>1.5101225969933761e-006</v>
       </c>
       <c r="AK30">
-        <v>2.9675894168052978e-006</v>
+        <v>2.5209122481618776e-006</v>
       </c>
       <c r="AL30">
-        <v>1.44650856533347e-005</v>
+        <v>2.5903160647082618e-005</v>
       </c>
       <c r="AM30">
-        <v>0.00016687029897799821</v>
+        <v>0.0002155139108673137</v>
       </c>
       <c r="AN30">
-        <v>0.0002274887040401285</v>
+        <v>0.00029841900131883498</v>
       </c>
       <c r="AO30">
-        <v>0.00010526941521295947</v>
+        <v>0.0001271602942039595</v>
       </c>
       <c r="AP30">
-        <v>-0.00049071959395018041</v>
+        <v>-0.00064375537185679566</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="65" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B31" s="66">
-        <v>0.1399988359310278</v>
+        <v>0.15517808042713058</v>
       </c>
       <c r="C31">
-        <v>-2.7523960014804505e-006</v>
+        <v>-5.0566565110452668e-006</v>
       </c>
       <c r="D31">
-        <v>2.6971435125103707e-007</v>
+        <v>-2.7717215614446515e-007</v>
       </c>
       <c r="E31">
-        <v>8.2796512018935422e-010</v>
+        <v>6.4412683012873535e-009</v>
       </c>
       <c r="F31">
-        <v>3.5126085159461462e-005</v>
+        <v>2.1809542836067845e-005</v>
       </c>
       <c r="G31">
-        <v>3.0580734691650719e-005</v>
+        <v>4.451893637960284e-005</v>
       </c>
       <c r="H31">
-        <v>4.14787362833614e-005</v>
+        <v>5.9006384643461109e-005</v>
       </c>
       <c r="I31">
-        <v>5.7917440696932846e-005</v>
+        <v>9.9943120434731634e-005</v>
       </c>
       <c r="J31">
-        <v>7.2683787983178757e-005</v>
+        <v>9.5828590752391183e-005</v>
       </c>
       <c r="K31">
-        <v>5.1683689392832547e-005</v>
+        <v>6.4754156107434322e-005</v>
       </c>
       <c r="L31">
-        <v>8.0781937201695222e-005</v>
+        <v>0.00010995579831171762</v>
       </c>
       <c r="M31">
-        <v>2.6308989402661996e-005</v>
+        <v>3.5111368773794877e-005</v>
       </c>
       <c r="N31">
-        <v>1.2267559442094239e-005</v>
+        <v>2.8780282965246597e-005</v>
       </c>
       <c r="O31">
-        <v>-1.6482766406603941e-005</v>
+        <v>-2.5168559666112527e-005</v>
       </c>
       <c r="P31">
-        <v>-8.797145503086812e-006</v>
+        <v>-5.6300281281924788e-006</v>
       </c>
       <c r="Q31">
-        <v>-6.6611041472218002e-007</v>
+        <v>-1.341169874279427e-006</v>
       </c>
       <c r="R31">
-        <v>2.2924426976167048e-007</v>
+        <v>6.0059830972189296e-007</v>
       </c>
       <c r="S31">
-        <v>-1.3251212198936776e-005</v>
+        <v>-7.5382480447067985e-006</v>
       </c>
       <c r="T31">
-        <v>8.9946878505259772e-006</v>
+        <v>3.1407502484235399e-005</v>
       </c>
       <c r="U31">
-        <v>2.1141536129609427e-005</v>
+        <v>4.0206067787797281e-005</v>
       </c>
       <c r="V31">
-        <v>4.2379327541820213e-005</v>
+        <v>6.941023716429527e-005</v>
       </c>
       <c r="W31">
-        <v>-2.3646893069901768e-007</v>
+        <v>-1.9053698782991744e-006</v>
       </c>
       <c r="X31">
-        <v>-1.5254192525198752e-006</v>
+        <v>2.4636066722224614e-006</v>
       </c>
       <c r="Y31">
-        <v>0.00041276175157134134</v>
+        <v>0.00052963345500201377</v>
       </c>
       <c r="Z31">
-        <v>0.00040698780472539151</v>
+        <v>0.000523312394897458</v>
       </c>
       <c r="AA31">
-        <v>0.00040744229658496974</v>
+        <v>0.00052312032635263173</v>
       </c>
       <c r="AB31">
-        <v>0.00041159413318294144</v>
+        <v>0.00052932014414411473</v>
       </c>
       <c r="AC31">
-        <v>0.00039342489704449784</v>
+        <v>0.00050343103582341068</v>
       </c>
       <c r="AD31">
-        <v>0.00041446897007393262</v>
+        <v>0.00053082327942721242</v>
       </c>
       <c r="AE31">
-        <v>0.00041110853826921065</v>
+        <v>0.00052754367410924857</v>
       </c>
       <c r="AF31">
-        <v>0.00077584463860027664</v>
+        <v>0.0010724630294577189</v>
       </c>
       <c r="AG31">
-        <v>0.00041214253229554813</v>
+        <v>0.00052992558049759237</v>
       </c>
       <c r="AH31">
-        <v>0.00041387307627423697</v>
+        <v>0.00053342400403307033</v>
       </c>
       <c r="AI31">
-        <v>0.00041689023985036554</v>
+        <v>0.00054663953773376878</v>
       </c>
       <c r="AJ31">
-        <v>1.8850615576934889e-006</v>
+        <v>2.439419028126157e-006</v>
       </c>
       <c r="AK31">
-        <v>7.9744394407144945e-006</v>
+        <v>3.8152069580556428e-006</v>
       </c>
       <c r="AL31">
-        <v>1.2085275635836802e-005</v>
+        <v>3.2941881058534014e-005</v>
       </c>
       <c r="AM31">
-        <v>0.00017542379017838558</v>
+        <v>0.00022741240615512833</v>
       </c>
       <c r="AN31">
-        <v>0.0002388909793428713</v>
+        <v>0.00032256084552232192</v>
       </c>
       <c r="AO31">
-        <v>0.0001146756612829396</v>
+        <v>0.00014347262527256209</v>
       </c>
       <c r="AP31">
-        <v>-0.00048580918582485889</v>
+        <v>-0.00062271333639108773</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" s="68">
-        <v>0.17354662544821223</v>
+        <v>0.19170086670117747</v>
       </c>
       <c r="C32">
-        <v>-6.9703098249782638e-006</v>
+        <v>-3.0027732850288947e-006</v>
       </c>
       <c r="D32">
-        <v>1.4366065722378973e-006</v>
+        <v>1.3296879948857597e-006</v>
       </c>
       <c r="E32">
-        <v>-1.0355970486474249e-008</v>
+        <v>-9.0443303483782628e-009</v>
       </c>
       <c r="F32">
-        <v>6.0647341145565753e-005</v>
+        <v>6.7888307755388012e-005</v>
       </c>
       <c r="G32">
-        <v>1.9971919892631458e-005</v>
+        <v>3.9424676636034861e-005</v>
       </c>
       <c r="H32">
-        <v>2.7453471000080798e-005</v>
+        <v>4.5514612820429668e-005</v>
       </c>
       <c r="I32">
-        <v>-7.2761973352398264e-006</v>
+        <v>2.0371308897565443e-005</v>
       </c>
       <c r="J32">
-        <v>3.0007355966605746e-005</v>
+        <v>4.3789173135840026e-005</v>
       </c>
       <c r="K32">
-        <v>3.8849454777252864e-005</v>
+        <v>5.8547398550991032e-005</v>
       </c>
       <c r="L32">
-        <v>2.5939269107036212e-005</v>
+        <v>4.6578357377776651e-005</v>
       </c>
       <c r="M32">
-        <v>1.6539691753148671e-005</v>
+        <v>1.4149529459904172e-005</v>
       </c>
       <c r="N32">
-        <v>3.9627402472852495e-006</v>
+        <v>5.1300524338422616e-006</v>
       </c>
       <c r="O32">
-        <v>-1.3431625409113793e-005</v>
+        <v>-1.9805151516668045e-005</v>
       </c>
       <c r="P32">
-        <v>-1.3310753702102757e-005</v>
+        <v>-1.3843613410107115e-005</v>
       </c>
       <c r="Q32">
-        <v>3.9718023545360877e-007</v>
+        <v>4.228812390649141e-007</v>
       </c>
       <c r="R32">
-        <v>4.1791486239990688e-007</v>
+        <v>8.4608689702091202e-007</v>
       </c>
       <c r="S32">
-        <v>-1.5048776979301138e-006</v>
+        <v>9.7311790138335068e-007</v>
       </c>
       <c r="T32">
-        <v>-1.9577109379104521e-006</v>
+        <v>1.7490729274399655e-006</v>
       </c>
       <c r="U32">
-        <v>1.1890955959027727e-005</v>
+        <v>1.4275253276953943e-005</v>
       </c>
       <c r="V32">
-        <v>3.7447481340725222e-005</v>
+        <v>5.5550520462775981e-005</v>
       </c>
       <c r="W32">
-        <v>-5.0030198544017931e-008</v>
+        <v>-2.5407575797308063e-007</v>
       </c>
       <c r="X32">
-        <v>-3.9537666154027344e-006</v>
+        <v>-1.9966671669001821e-006</v>
       </c>
       <c r="Y32">
-        <v>0.00041084568652661037</v>
+        <v>0.000525044964266943</v>
       </c>
       <c r="Z32">
-        <v>0.00039827932766506357</v>
+        <v>0.00050856889698043094</v>
       </c>
       <c r="AA32">
-        <v>0.00040415045704532567</v>
+        <v>0.00051572872470170025</v>
       </c>
       <c r="AB32">
-        <v>0.00040784828807215173</v>
+        <v>0.00052272715331533586</v>
       </c>
       <c r="AC32">
-        <v>0.00039306646203779005</v>
+        <v>0.00050014831161000349</v>
       </c>
       <c r="AD32">
-        <v>0.00041097242651447902</v>
+        <v>0.00052310382665577359</v>
       </c>
       <c r="AE32">
-        <v>0.00040863009163989158</v>
+        <v>0.00052136165674489363</v>
       </c>
       <c r="AF32">
-        <v>0.00041214253229554813</v>
+        <v>0.00052992558049759237</v>
       </c>
       <c r="AG32">
-        <v>0.00080209385969115456</v>
+        <v>0.0010738819203514709</v>
       </c>
       <c r="AH32">
-        <v>0.00041253434547315051</v>
+        <v>0.0005321665064464252</v>
       </c>
       <c r="AI32">
-        <v>0.00041487556343904031</v>
+        <v>0.00054231966304740483</v>
       </c>
       <c r="AJ32">
-        <v>7.6937399234758621e-007</v>
+        <v>5.987900736266934e-007</v>
       </c>
       <c r="AK32">
-        <v>1.4735717183226581e-005</v>
+        <v>1.9596658771933055e-005</v>
       </c>
       <c r="AL32">
-        <v>1.135078972214751e-005</v>
+        <v>2.506351755500703e-005</v>
       </c>
       <c r="AM32">
-        <v>0.00017853000600238689</v>
+        <v>0.0002316582847054638</v>
       </c>
       <c r="AN32">
-        <v>0.00024066480240021664</v>
+        <v>0.00031187179503043647</v>
       </c>
       <c r="AO32">
-        <v>0.00011440468100020576</v>
+        <v>0.00014467835714745245</v>
       </c>
       <c r="AP32">
-        <v>-0.00052711606136422945</v>
+        <v>-0.00068551348669360827</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="69" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" s="70">
-        <v>0.12099078759146743</v>
+        <v>0.12937060834752762</v>
       </c>
       <c r="C33">
-        <v>1.4936291953985461e-006</v>
+        <v>7.0895687592728951e-006</v>
       </c>
       <c r="D33">
-        <v>-1.7348382566233592e-006</v>
+        <v>-2.7839570281417344e-006</v>
       </c>
       <c r="E33">
-        <v>1.5604901128464562e-008</v>
+        <v>2.5522950832854794e-008</v>
       </c>
       <c r="F33">
-        <v>-2.4064314215068873e-005</v>
+        <v>-3.6430295702103566e-005</v>
       </c>
       <c r="G33">
-        <v>9.1603245672615088e-006</v>
+        <v>2.1949782324671749e-005</v>
       </c>
       <c r="H33">
-        <v>2.5912754569109292e-005</v>
+        <v>3.0157068886052474e-005</v>
       </c>
       <c r="I33">
-        <v>-1.8014680237459833e-005</v>
+        <v>1.7164065772947419e-005</v>
       </c>
       <c r="J33">
-        <v>2.7148690665106539e-005</v>
+        <v>3.5355658991120932e-005</v>
       </c>
       <c r="K33">
-        <v>2.2869448814908118e-005</v>
+        <v>3.2464286945684979e-005</v>
       </c>
       <c r="L33">
-        <v>2.4994079830906186e-005</v>
+        <v>4.6263790147862593e-005</v>
       </c>
       <c r="M33">
-        <v>-1.3733469032991576e-005</v>
+        <v>-2.6402140234405274e-005</v>
       </c>
       <c r="N33">
-        <v>7.957487752308708e-006</v>
+        <v>4.6997410614375737e-006</v>
       </c>
       <c r="O33">
-        <v>-1.4799555215242849e-005</v>
+        <v>-3.0815801605366099e-005</v>
       </c>
       <c r="P33">
-        <v>-1.3586776894979394e-006</v>
+        <v>-1.5557813089719672e-005</v>
       </c>
       <c r="Q33">
-        <v>1.8513451823322819e-007</v>
+        <v>1.7214734342241863e-008</v>
       </c>
       <c r="R33">
-        <v>3.5091433062409641e-007</v>
+        <v>6.0651870150983846e-007</v>
       </c>
       <c r="S33">
-        <v>7.0571094583989321e-006</v>
+        <v>-1.6505423023474369e-006</v>
       </c>
       <c r="T33">
-        <v>8.8776686013733523e-006</v>
+        <v>1.1941363959170487e-005</v>
       </c>
       <c r="U33">
-        <v>1.4447385807352095e-005</v>
+        <v>1.3068158798258727e-005</v>
       </c>
       <c r="V33">
-        <v>3.4782637836399874e-005</v>
+        <v>4.480004288900839e-005</v>
       </c>
       <c r="W33">
-        <v>1.7649093124845441e-007</v>
+        <v>1.3026583188232237e-006</v>
       </c>
       <c r="X33">
-        <v>-9.4251549591647934e-007</v>
+        <v>5.3214870260497741e-007</v>
       </c>
       <c r="Y33">
-        <v>0.00041428668137754281</v>
+        <v>0.00053392649986694221</v>
       </c>
       <c r="Z33">
-        <v>0.00040641750518664226</v>
+        <v>0.00052443684758426935</v>
       </c>
       <c r="AA33">
-        <v>0.00040221702041429592</v>
+        <v>0.0005177522843573002</v>
       </c>
       <c r="AB33">
-        <v>0.00040246512623406873</v>
+        <v>0.00052072103211164063</v>
       </c>
       <c r="AC33">
-        <v>0.00039179943560906013</v>
+        <v>0.0005054783719640627</v>
       </c>
       <c r="AD33">
-        <v>0.00041057887019088678</v>
+        <v>0.00052560675009238065</v>
       </c>
       <c r="AE33">
-        <v>0.0004090892446772411</v>
+        <v>0.00052362406615767026</v>
       </c>
       <c r="AF33">
-        <v>0.00041387307627423697</v>
+        <v>0.00053342400403307033</v>
       </c>
       <c r="AG33">
-        <v>0.00041253434547315051</v>
+        <v>0.0005321665064464252</v>
       </c>
       <c r="AH33">
-        <v>0.00077296772782785056</v>
+        <v>0.001021863835239732</v>
       </c>
       <c r="AI33">
-        <v>0.00041499824345239</v>
+        <v>0.00054633061232671508</v>
       </c>
       <c r="AJ33">
-        <v>2.7865028299215256e-006</v>
+        <v>3.1367247403372762e-006</v>
       </c>
       <c r="AK33">
-        <v>-4.5386485968130641e-006</v>
+        <v>-6.7571939381335272e-006</v>
       </c>
       <c r="AL33">
-        <v>-8.4627158258107507e-008</v>
+        <v>4.1404979969618215e-006</v>
       </c>
       <c r="AM33">
-        <v>0.00017249589128194722</v>
+        <v>0.00021789005609580922</v>
       </c>
       <c r="AN33">
-        <v>0.00023851307056089289</v>
+        <v>0.00031100233412608861</v>
       </c>
       <c r="AO33">
-        <v>0.00012803572352893203</v>
+        <v>0.00017239632380401326</v>
       </c>
       <c r="AP33">
-        <v>-0.00046673389497684599</v>
+        <v>-0.00057492929764712142</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="71" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B34" s="72">
-        <v>0.28060543635414892</v>
+        <v>0.2935069651780744</v>
       </c>
       <c r="C34">
-        <v>-9.7779038769871475e-006</v>
+        <v>-5.4643131419696338e-006</v>
       </c>
       <c r="D34">
-        <v>3.4736910851707509e-007</v>
+        <v>-1.6743132602498642e-007</v>
       </c>
       <c r="E34">
-        <v>3.9104818461098776e-009</v>
+        <v>9.2518322747465004e-009</v>
       </c>
       <c r="F34">
-        <v>7.1280408559634917e-005</v>
+        <v>7.4816169942917279e-005</v>
       </c>
       <c r="G34">
-        <v>1.7602170952127778e-005</v>
+        <v>2.9532828423308875e-005</v>
       </c>
       <c r="H34">
-        <v>2.2409646081386628e-005</v>
+        <v>4.4036892350708147e-005</v>
       </c>
       <c r="I34">
-        <v>3.8792847057427676e-005</v>
+        <v>7.2950579330191849e-005</v>
       </c>
       <c r="J34">
-        <v>3.5860336554235624e-005</v>
+        <v>4.2864181639667488e-005</v>
       </c>
       <c r="K34">
-        <v>2.3418212669260984e-005</v>
+        <v>3.3099942168052427e-005</v>
       </c>
       <c r="L34">
-        <v>1.9037282360268834e-005</v>
+        <v>3.2366297458186156e-005</v>
       </c>
       <c r="M34">
-        <v>3.2704554498044585e-005</v>
+        <v>3.3061235991897926e-005</v>
       </c>
       <c r="N34">
-        <v>9.4080893280891172e-006</v>
+        <v>1.1251888311289968e-005</v>
       </c>
       <c r="O34">
-        <v>-1.7795937795747282e-006</v>
+        <v>-8.8121754855129987e-006</v>
       </c>
       <c r="P34">
-        <v>-1.4621600892997558e-005</v>
+        <v>-9.4705342957230644e-006</v>
       </c>
       <c r="Q34">
-        <v>-1.2156571249124857e-007</v>
+        <v>-1.832902010723789e-007</v>
       </c>
       <c r="R34">
-        <v>5.2817943229684631e-007</v>
+        <v>9.8348127539321973e-007</v>
       </c>
       <c r="S34">
-        <v>2.7417248489578047e-005</v>
+        <v>3.491319224955999e-005</v>
       </c>
       <c r="T34">
-        <v>3.6235179673801954e-005</v>
+        <v>4.1766734008430472e-005</v>
       </c>
       <c r="U34">
-        <v>5.316616360713023e-005</v>
+        <v>7.3799905878736433e-005</v>
       </c>
       <c r="V34">
-        <v>7.7002239468186497e-005</v>
+        <v>0.00010460774289662919</v>
       </c>
       <c r="W34">
-        <v>7.7853611095443265e-007</v>
+        <v>2.1104999447177234e-006</v>
       </c>
       <c r="X34">
-        <v>-4.6636457997062928e-008</v>
+        <v>-1.9561255611679146e-006</v>
       </c>
       <c r="Y34">
-        <v>0.00041709427058320083</v>
+        <v>0.00054227900662922224</v>
       </c>
       <c r="Z34">
-        <v>0.00040411990113430426</v>
+        <v>0.00052576778216103712</v>
       </c>
       <c r="AA34">
-        <v>0.00040610230040085034</v>
+        <v>0.00052607671614143684</v>
       </c>
       <c r="AB34">
-        <v>0.00040991897225836984</v>
+        <v>0.00053419577656390411</v>
       </c>
       <c r="AC34">
-        <v>0.00039404597248016176</v>
+        <v>0.0005100993575582524</v>
       </c>
       <c r="AD34">
-        <v>0.00041194588448983114</v>
+        <v>0.00053138186603843307</v>
       </c>
       <c r="AE34">
-        <v>0.00041035036161160522</v>
+        <v>0.00053232795629203718</v>
       </c>
       <c r="AF34">
-        <v>0.00041689023985036554</v>
+        <v>0.00054663953773376878</v>
       </c>
       <c r="AG34">
-        <v>0.00041487556343904031</v>
+        <v>0.00054231966304740483</v>
       </c>
       <c r="AH34">
-        <v>0.00041499824345239</v>
+        <v>0.00054633061232671508</v>
       </c>
       <c r="AI34">
-        <v>0.0009296229854695397</v>
+        <v>0.0012245328715740661</v>
       </c>
       <c r="AJ34">
-        <v>2.770852005013386e-006</v>
+        <v>3.3924600101043872e-006</v>
       </c>
       <c r="AK34">
-        <v>5.2156738524703865e-006</v>
+        <v>4.0203031465552289e-006</v>
       </c>
       <c r="AL34">
-        <v>1.2142094492256335e-006</v>
+        <v>1.2555664563201377e-005</v>
       </c>
       <c r="AM34">
-        <v>0.00023420856069502529</v>
+        <v>0.00035582608443855918</v>
       </c>
       <c r="AN34">
-        <v>0.00024590886463394862</v>
+        <v>0.00032374735282852355</v>
       </c>
       <c r="AO34">
-        <v>0.00013010065579448181</v>
+        <v>0.00017472602418663245</v>
       </c>
       <c r="AP34">
-        <v>-0.00056294214886482962</v>
+        <v>-0.00073284384434719606</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="73" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" s="74">
-        <v>0.013083133075041005</v>
+        <v>0.011934231986872651</v>
       </c>
       <c r="C35">
-        <v>-3.1743798909241021e-007</v>
+        <v>5.111695547536668e-007</v>
       </c>
       <c r="D35">
-        <v>1.5688245878254011e-007</v>
+        <v>2.4815399929093137e-007</v>
       </c>
       <c r="E35">
-        <v>-1.9644458001853613e-009</v>
+        <v>-2.7171497249077253e-009</v>
       </c>
       <c r="F35">
-        <v>1.5738251730462275e-006</v>
+        <v>2.0646900710835877e-006</v>
       </c>
       <c r="G35">
-        <v>1.4106773893570794e-006</v>
+        <v>1.7244796404762409e-006</v>
       </c>
       <c r="H35">
-        <v>1.6368308290256982e-006</v>
+        <v>2.4585921436822465e-006</v>
       </c>
       <c r="I35">
-        <v>2.2679259329575864e-005</v>
+        <v>9.7203314910085643e-006</v>
       </c>
       <c r="J35">
-        <v>2.3520768482450854e-006</v>
+        <v>3.6790981533805952e-006</v>
       </c>
       <c r="K35">
-        <v>9.3933704155801562e-007</v>
+        <v>1.4134699010033908e-006</v>
       </c>
       <c r="L35">
-        <v>5.2562045490778187e-006</v>
+        <v>7.4956068780418676e-006</v>
       </c>
       <c r="M35">
-        <v>3.271836460807736e-006</v>
+        <v>5.804676334270497e-006</v>
       </c>
       <c r="N35">
-        <v>2.6034599843520966e-006</v>
+        <v>4.1248553936926794e-006</v>
       </c>
       <c r="O35">
-        <v>6.7884921632802111e-007</v>
+        <v>2.0069095052518842e-008</v>
       </c>
       <c r="P35">
-        <v>3.3276879194390937e-006</v>
+        <v>3.3523078147858838e-006</v>
       </c>
       <c r="Q35">
-        <v>8.8811649832457534e-008</v>
+        <v>6.1998983468083446e-008</v>
       </c>
       <c r="R35">
-        <v>2.7045074420717075e-008</v>
+        <v>1.9090271616559965e-008</v>
       </c>
       <c r="S35">
-        <v>1.1528453879259364e-006</v>
+        <v>2.1082369280683485e-006</v>
       </c>
       <c r="T35">
-        <v>3.8987734166405195e-006</v>
+        <v>6.0262347839048993e-006</v>
       </c>
       <c r="U35">
-        <v>3.4403792303626931e-006</v>
+        <v>5.5680105136555876e-006</v>
       </c>
       <c r="V35">
-        <v>2.4276581866448354e-006</v>
+        <v>3.8109024638165528e-006</v>
       </c>
       <c r="W35">
-        <v>-1.9256891780656306e-007</v>
+        <v>-3.7879379789052547e-007</v>
       </c>
       <c r="X35">
-        <v>5.5388452563065381e-007</v>
+        <v>6.676103653544172e-007</v>
       </c>
       <c r="Y35">
-        <v>6.5548127510304564e-007</v>
+        <v>7.4685978340721438e-007</v>
       </c>
       <c r="Z35">
-        <v>9.4432640690907628e-007</v>
+        <v>1.1396440287283138e-006</v>
       </c>
       <c r="AA35">
-        <v>2.4569732033994614e-007</v>
+        <v>-3.0259415907579416e-007</v>
       </c>
       <c r="AB35">
-        <v>7.7792571680627997e-007</v>
+        <v>7.8121096403120024e-007</v>
       </c>
       <c r="AC35">
-        <v>-1.9800387870848751e-007</v>
+        <v>-7.4479776836812179e-007</v>
       </c>
       <c r="AD35">
-        <v>-8.9319740562471474e-007</v>
+        <v>-1.7785162949822643e-006</v>
       </c>
       <c r="AE35">
-        <v>1.4537093930401382e-006</v>
+        <v>1.5101225969933761e-006</v>
       </c>
       <c r="AF35">
-        <v>1.8850615576934889e-006</v>
+        <v>2.439419028126157e-006</v>
       </c>
       <c r="AG35">
-        <v>7.6937399234758621e-007</v>
+        <v>5.987900736266934e-007</v>
       </c>
       <c r="AH35">
-        <v>2.7865028299215256e-006</v>
+        <v>3.1367247403372762e-006</v>
       </c>
       <c r="AI35">
-        <v>2.770852005013386e-006</v>
+        <v>3.3924600101043872e-006</v>
       </c>
       <c r="AJ35">
-        <v>3.5414561795849926e-006</v>
+        <v>4.7223179157636531e-006</v>
       </c>
       <c r="AK35">
-        <v>-1.8380290140130071e-005</v>
+        <v>-2.4493875547867576e-005</v>
       </c>
       <c r="AL35">
-        <v>-2.2369101632241145e-005</v>
+        <v>-2.9945382918090931e-005</v>
       </c>
       <c r="AM35">
-        <v>7.1375597213179897e-007</v>
+        <v>1.5598177132318398e-006</v>
       </c>
       <c r="AN35">
-        <v>-1.4695251591766525e-006</v>
+        <v>-2.4250475077160073e-006</v>
       </c>
       <c r="AO35">
-        <v>-1.5047619369698311e-006</v>
+        <v>-2.6241374964349604e-006</v>
       </c>
       <c r="AP35">
-        <v>-6.7996656731506271e-005</v>
+        <v>-8.9029936285981516e-005</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="75" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B36" s="76">
-        <v>-0.017638527149721358</v>
+        <v>-0.014555424047665593</v>
       </c>
       <c r="C36">
-        <v>1.0252474378722262e-007</v>
+        <v>-7.0023940935038615e-006</v>
       </c>
       <c r="D36">
-        <v>-6.0799483160199175e-007</v>
+        <v>-1.7037926334854316e-006</v>
       </c>
       <c r="E36">
-        <v>4.1515413508645443e-009</v>
+        <v>1.3540654772268073e-008</v>
       </c>
       <c r="F36">
-        <v>1.2447682856696831e-005</v>
+        <v>3.8763103751403615e-005</v>
       </c>
       <c r="G36">
-        <v>-1.1154389961679522e-005</v>
+        <v>2.3739537860719109e-006</v>
       </c>
       <c r="H36">
-        <v>-2.3988147301928767e-006</v>
+        <v>1.1968911409842887e-005</v>
       </c>
       <c r="I36">
-        <v>-0.00014277536773756234</v>
+        <v>-4.2864696516441096e-005</v>
       </c>
       <c r="J36">
-        <v>1.113122321845336e-005</v>
+        <v>2.878212601836622e-005</v>
       </c>
       <c r="K36">
-        <v>-1.0164209893931614e-005</v>
+        <v>-8.648739595707461e-007</v>
       </c>
       <c r="L36">
-        <v>-2.7212311970640195e-005</v>
+        <v>-2.8838397806338459e-005</v>
       </c>
       <c r="M36">
-        <v>-3.7992167118307682e-005</v>
+        <v>-6.325808516207212e-005</v>
       </c>
       <c r="N36">
-        <v>-1.1248726136711986e-005</v>
+        <v>-2.5684886083855723e-005</v>
       </c>
       <c r="O36">
-        <v>-4.5291560255271287e-006</v>
+        <v>-1.8087319245912158e-006</v>
       </c>
       <c r="P36">
-        <v>-9.7216222889163098e-006</v>
+        <v>-1.1811555604739871e-005</v>
       </c>
       <c r="Q36">
-        <v>3.6270036049166956e-007</v>
+        <v>5.812110532758491e-007</v>
       </c>
       <c r="R36">
-        <v>-2.0534660222149491e-007</v>
+        <v>-2.2717045843404118e-007</v>
       </c>
       <c r="S36">
-        <v>-6.2585370296498384e-006</v>
+        <v>-9.7051415601163675e-006</v>
       </c>
       <c r="T36">
-        <v>-2.5827058157671142e-005</v>
+        <v>-4.6872100138054961e-005</v>
       </c>
       <c r="U36">
-        <v>-1.7087252851769322e-005</v>
+        <v>-3.3287647285331971e-005</v>
       </c>
       <c r="V36">
-        <v>-2.0360900594175327e-005</v>
+        <v>-2.6905867298020424e-005</v>
       </c>
       <c r="W36">
-        <v>1.2163977789424145e-006</v>
+        <v>2.2628069051866646e-006</v>
       </c>
       <c r="X36">
-        <v>-2.3213266837218369e-006</v>
+        <v>-5.0528363681051455e-006</v>
       </c>
       <c r="Y36">
-        <v>6.9898523339728609e-007</v>
+        <v>-5.9577869557207769e-006</v>
       </c>
       <c r="Z36">
-        <v>1.5746708165548742e-005</v>
+        <v>1.7289091847633489e-005</v>
       </c>
       <c r="AA36">
-        <v>1.8898305474518288e-005</v>
+        <v>2.1198313042686329e-005</v>
       </c>
       <c r="AB36">
-        <v>1.9907112257510732e-005</v>
+        <v>3.2632265726924685e-005</v>
       </c>
       <c r="AC36">
-        <v>2.1456337586684172e-005</v>
+        <v>3.3510277764512816e-005</v>
       </c>
       <c r="AD36">
-        <v>2.1399712591545541e-005</v>
+        <v>2.5614915838043812e-005</v>
       </c>
       <c r="AE36">
-        <v>2.9675894168052978e-006</v>
+        <v>2.5209122481618776e-006</v>
       </c>
       <c r="AF36">
-        <v>7.9744394407144945e-006</v>
+        <v>3.8152069580556428e-006</v>
       </c>
       <c r="AG36">
-        <v>1.4735717183226581e-005</v>
+        <v>1.9596658771933055e-005</v>
       </c>
       <c r="AH36">
-        <v>-4.5386485968130641e-006</v>
+        <v>-6.7571939381335272e-006</v>
       </c>
       <c r="AI36">
-        <v>5.2156738524703865e-006</v>
+        <v>4.0203031465552289e-006</v>
       </c>
       <c r="AJ36">
-        <v>-1.8380290140130071e-005</v>
+        <v>-2.4493875547867576e-005</v>
       </c>
       <c r="AK36">
-        <v>0.00064580673838763973</v>
+        <v>0.00084428338373772718</v>
       </c>
       <c r="AL36">
-        <v>9.316314723569029e-005</v>
+        <v>0.00013882389507349167</v>
       </c>
       <c r="AM36">
-        <v>-6.0094006295829239e-006</v>
+        <v>-1.7556571020767298e-005</v>
       </c>
       <c r="AN36">
-        <v>3.250200314755441e-005</v>
+        <v>2.4976561260880043e-005</v>
       </c>
       <c r="AO36">
-        <v>3.2659034060193075e-006</v>
+        <v>-1.3924617866137252e-006</v>
       </c>
       <c r="AP36">
-        <v>0.00027739917830967237</v>
+        <v>0.00038545106711325428</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="77" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B37" s="78">
-        <v>-0.062389793911917943</v>
+        <v>-0.056947070214125595</v>
       </c>
       <c r="C37">
-        <v>6.2102916537222364e-007</v>
+        <v>3.2505700207749275e-006</v>
       </c>
       <c r="D37">
-        <v>-1.4170193888759013e-006</v>
+        <v>-2.1614958900012101e-006</v>
       </c>
       <c r="E37">
-        <v>1.2467902009740387e-008</v>
+        <v>1.628273406235385e-008</v>
       </c>
       <c r="F37">
-        <v>-5.3541140620432475e-007</v>
+        <v>1.6976494343452032e-007</v>
       </c>
       <c r="G37">
-        <v>-1.9268825915178262e-006</v>
+        <v>2.9729109743699926e-006</v>
       </c>
       <c r="H37">
-        <v>-9.3873073656597762e-006</v>
+        <v>-1.1932204850815798e-005</v>
       </c>
       <c r="I37">
-        <v>-0.00014544936434959853</v>
+        <v>-3.8220434256641676e-005</v>
       </c>
       <c r="J37">
-        <v>-8.2706886212621859e-006</v>
+        <v>-3.5794869069607555e-006</v>
       </c>
       <c r="K37">
-        <v>-6.0154365222654942e-006</v>
+        <v>-3.7122289715280251e-007</v>
       </c>
       <c r="L37">
-        <v>-2.8850179693937152e-005</v>
+        <v>-3.232819977011126e-005</v>
       </c>
       <c r="M37">
-        <v>-2.0918834664776583e-005</v>
+        <v>-4.6446641240313678e-005</v>
       </c>
       <c r="N37">
-        <v>-1.7028896508458121e-005</v>
+        <v>-3.4514447261543315e-005</v>
       </c>
       <c r="O37">
-        <v>1.2447718701449595e-005</v>
+        <v>1.4726779578960167e-005</v>
       </c>
       <c r="P37">
-        <v>5.3402235887113227e-006</v>
+        <v>8.76130078635941e-006</v>
       </c>
       <c r="Q37">
-        <v>9.7319857190056803e-007</v>
+        <v>1.5080866010079759e-006</v>
       </c>
       <c r="R37">
-        <v>-3.8593377822986103e-007</v>
+        <v>-2.5367117759044332e-007</v>
       </c>
       <c r="S37">
-        <v>-5.9751198377587954e-006</v>
+        <v>-2.1826107707637484e-005</v>
       </c>
       <c r="T37">
-        <v>-3.3329339649620324e-005</v>
+        <v>-6.7115840162723433e-005</v>
       </c>
       <c r="U37">
-        <v>-2.53775640724264e-005</v>
+        <v>-4.856055424662907e-005</v>
       </c>
       <c r="V37">
-        <v>-7.2224181939863537e-006</v>
+        <v>-2.6701492802552706e-005</v>
       </c>
       <c r="W37">
-        <v>8.6264414187688931e-007</v>
+        <v>3.8617154332693008e-006</v>
       </c>
       <c r="X37">
-        <v>8.8322516702161606e-006</v>
+        <v>2.291161423511528e-005</v>
       </c>
       <c r="Y37">
-        <v>8.2967756253633423e-006</v>
+        <v>1.9073735838888796e-005</v>
       </c>
       <c r="Z37">
-        <v>4.9342469135271296e-005</v>
+        <v>7.196136020451606e-005</v>
       </c>
       <c r="AA37">
-        <v>3.4390660047410623e-005</v>
+        <v>5.3465892274768818e-005</v>
       </c>
       <c r="AB37">
-        <v>1.3392342018075987e-005</v>
+        <v>2.3791568521155883e-005</v>
       </c>
       <c r="AC37">
-        <v>3.0367833758606832e-005</v>
+        <v>5.4402427370255421e-005</v>
       </c>
       <c r="AD37">
-        <v>2.2972002120995236e-005</v>
+        <v>4.3210533993365694e-005</v>
       </c>
       <c r="AE37">
-        <v>1.44650856533347e-005</v>
+        <v>2.5903160647082618e-005</v>
       </c>
       <c r="AF37">
-        <v>1.2085275635836802e-005</v>
+        <v>3.2941881058534014e-005</v>
       </c>
       <c r="AG37">
-        <v>1.135078972214751e-005</v>
+        <v>2.506351755500703e-005</v>
       </c>
       <c r="AH37">
-        <v>-8.4627158258107507e-008</v>
+        <v>4.1404979969618215e-006</v>
       </c>
       <c r="AI37">
-        <v>1.2142094492256335e-006</v>
+        <v>1.2555664563201377e-005</v>
       </c>
       <c r="AJ37">
-        <v>-2.2369101632241145e-005</v>
+        <v>-2.9945382918090931e-005</v>
       </c>
       <c r="AK37">
-        <v>9.316314723569029e-005</v>
+        <v>0.00013882389507349167</v>
       </c>
       <c r="AL37">
-        <v>0.0007316014706153528</v>
+        <v>0.00096776470973089143</v>
       </c>
       <c r="AM37">
-        <v>-3.4154666028345972e-006</v>
+        <v>-1.2553086462449342e-005</v>
       </c>
       <c r="AN37">
-        <v>1.1880160152172043e-005</v>
+        <v>2.4047772973866631e-005</v>
       </c>
       <c r="AO37">
-        <v>1.1643702855284428e-005</v>
+        <v>1.912554481871387e-005</v>
       </c>
       <c r="AP37">
-        <v>0.00031112168285833295</v>
+        <v>0.00040011091287588151</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="79" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B38" s="80">
-        <v>0.17200382683083287</v>
+        <v>0.17971265191929756</v>
       </c>
       <c r="C38">
-        <v>-6.0272879253143162e-006</v>
+        <v>-1.0859017052834651e-005</v>
       </c>
       <c r="D38">
-        <v>-6.4609638909448057e-008</v>
+        <v>7.0444166724729554e-007</v>
       </c>
       <c r="E38">
-        <v>1.0551217249692203e-008</v>
+        <v>3.8229807900505006e-009</v>
       </c>
       <c r="F38">
-        <v>6.5448510151691196e-005</v>
+        <v>6.6249810993077485e-005</v>
       </c>
       <c r="G38">
-        <v>6.9502378940697248e-006</v>
+        <v>-3.4396390706460038e-006</v>
       </c>
       <c r="H38">
-        <v>-8.4336315757972409e-006</v>
+        <v>3.2779946164936472e-006</v>
       </c>
       <c r="I38">
-        <v>-4.7001705974133908e-005</v>
+        <v>-1.8548106257671132e-005</v>
       </c>
       <c r="J38">
-        <v>-4.227786958441751e-005</v>
+        <v>-6.9490811371710718e-005</v>
       </c>
       <c r="K38">
-        <v>1.0961963830670148e-005</v>
+        <v>1.051980362756468e-005</v>
       </c>
       <c r="L38">
-        <v>1.7773987431752149e-005</v>
+        <v>1.5507633409854893e-005</v>
       </c>
       <c r="M38">
-        <v>-1.9804278269498537e-005</v>
+        <v>-2.2908420247029753e-005</v>
       </c>
       <c r="N38">
-        <v>-7.3979473475357287e-006</v>
+        <v>1.3212190402499182e-005</v>
       </c>
       <c r="O38">
-        <v>4.6125946278338791e-005</v>
+        <v>6.3204879976501524e-005</v>
       </c>
       <c r="P38">
-        <v>3.7515092635861122e-005</v>
+        <v>6.416426935821308e-005</v>
       </c>
       <c r="Q38">
-        <v>-3.4128546557224754e-007</v>
+        <v>1.7496194412443849e-008</v>
       </c>
       <c r="R38">
-        <v>3.5098759074296964e-007</v>
+        <v>6.9564686889849267e-007</v>
       </c>
       <c r="S38">
-        <v>-3.6858901044363273e-006</v>
+        <v>1.0274605883777777e-005</v>
       </c>
       <c r="T38">
-        <v>1.1509599744097986e-005</v>
+        <v>3.21774671993565e-005</v>
       </c>
       <c r="U38">
-        <v>3.051718150137985e-005</v>
+        <v>5.6440226258127084e-005</v>
       </c>
       <c r="V38">
-        <v>3.7475255665174825e-005</v>
+        <v>6.5075653341252352e-005</v>
       </c>
       <c r="W38">
-        <v>2.3578612931584926e-006</v>
+        <v>2.6710494213892514e-006</v>
       </c>
       <c r="X38">
-        <v>6.9741712220176887e-006</v>
+        <v>9.5760742955595027e-006</v>
       </c>
       <c r="Y38">
-        <v>0.00018070475351414993</v>
+        <v>0.00023421167778613547</v>
       </c>
       <c r="Z38">
-        <v>0.00015186334166978569</v>
+        <v>0.0001919967666176049</v>
       </c>
       <c r="AA38">
-        <v>0.00014730831319492352</v>
+        <v>0.0001870636910257013</v>
       </c>
       <c r="AB38">
-        <v>0.00015893673537363678</v>
+        <v>0.0002016981735404138</v>
       </c>
       <c r="AC38">
-        <v>0.00012369951560224323</v>
+        <v>0.00015615954036215577</v>
       </c>
       <c r="AD38">
-        <v>0.00016395862951943741</v>
+        <v>0.0002102823705365061</v>
       </c>
       <c r="AE38">
-        <v>0.00016687029897799821</v>
+        <v>0.0002155139108673137</v>
       </c>
       <c r="AF38">
-        <v>0.00017542379017838558</v>
+        <v>0.00022741240615512833</v>
       </c>
       <c r="AG38">
-        <v>0.00017853000600238689</v>
+        <v>0.0002316582847054638</v>
       </c>
       <c r="AH38">
-        <v>0.00017249589128194722</v>
+        <v>0.00021789005609580922</v>
       </c>
       <c r="AI38">
-        <v>0.00023420856069502529</v>
+        <v>0.00035582608443855918</v>
       </c>
       <c r="AJ38">
-        <v>7.1375597213179897e-007</v>
+        <v>1.5598177132318398e-006</v>
       </c>
       <c r="AK38">
-        <v>-6.0094006295829239e-006</v>
+        <v>-1.7556571020767298e-005</v>
       </c>
       <c r="AL38">
-        <v>-3.4154666028345972e-006</v>
+        <v>-1.2553086462449342e-005</v>
       </c>
       <c r="AM38">
-        <v>0.0005483250193662702</v>
+        <v>0.00077980900064036451</v>
       </c>
       <c r="AN38">
-        <v>0.00013673656820282397</v>
+        <v>0.00018949507868750714</v>
       </c>
       <c r="AO38">
-        <v>9.5811828314399826e-005</v>
+        <v>0.00013531069464640949</v>
       </c>
       <c r="AP38">
-        <v>-0.00027942616692718534</v>
+        <v>-0.00044213336103730752</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="81" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B39" s="82">
-        <v>-0.19286980791754091</v>
+        <v>-0.18786278476143792</v>
       </c>
       <c r="C39">
-        <v>-3.6147826383295437e-006</v>
+        <v>1.2811924345343312e-006</v>
       </c>
       <c r="D39">
-        <v>-1.4692609963669432e-006</v>
+        <v>-9.6951760303371382e-007</v>
       </c>
       <c r="E39">
-        <v>1.6596955131367764e-008</v>
+        <v>1.0734047954189822e-008</v>
       </c>
       <c r="F39">
-        <v>6.9564036973655027e-005</v>
+        <v>8.8829777847241383e-005</v>
       </c>
       <c r="G39">
-        <v>-9.5557461050329662e-006</v>
+        <v>-7.5170850529177958e-006</v>
       </c>
       <c r="H39">
-        <v>1.1526790580508473e-005</v>
+        <v>5.6720079613716023e-007</v>
       </c>
       <c r="I39">
-        <v>-0.00015171131348329692</v>
+        <v>-0.00015936785496778385</v>
       </c>
       <c r="J39">
-        <v>1.0098846413304975e-005</v>
+        <v>8.9275167355450775e-006</v>
       </c>
       <c r="K39">
-        <v>-1.2556643183162484e-005</v>
+        <v>-1.5982971249723548e-005</v>
       </c>
       <c r="L39">
-        <v>2.8824302606119165e-005</v>
+        <v>4.434539662439695e-005</v>
       </c>
       <c r="M39">
-        <v>-3.5403584024942651e-005</v>
+        <v>-3.5975750636681658e-005</v>
       </c>
       <c r="N39">
-        <v>1.5185185284557307e-005</v>
+        <v>3.9397493975321031e-005</v>
       </c>
       <c r="O39">
-        <v>2.0529676296099654e-005</v>
+        <v>3.6211852898845444e-005</v>
       </c>
       <c r="P39">
-        <v>4.5984874304311335e-005</v>
+        <v>8.6004830109555054e-005</v>
       </c>
       <c r="Q39">
-        <v>-4.0217974034122969e-007</v>
+        <v>-8.5742149494599676e-007</v>
       </c>
       <c r="R39">
-        <v>-1.3372786108309842e-007</v>
+        <v>1.0031866967654594e-007</v>
       </c>
       <c r="S39">
-        <v>1.2118155934762154e-005</v>
+        <v>3.5375413406100618e-005</v>
       </c>
       <c r="T39">
-        <v>-3.2634341447403256e-007</v>
+        <v>2.4848831685137375e-005</v>
       </c>
       <c r="U39">
-        <v>1.4538127790085997e-005</v>
+        <v>3.9036968393280059e-005</v>
       </c>
       <c r="V39">
-        <v>4.4510376989899414e-005</v>
+        <v>6.8631927242742482e-005</v>
       </c>
       <c r="W39">
-        <v>2.973960857031859e-006</v>
+        <v>2.2724021093152135e-006</v>
       </c>
       <c r="X39">
-        <v>1.9422655464468328e-005</v>
+        <v>3.3223723877602205e-005</v>
       </c>
       <c r="Y39">
-        <v>0.00025115565359353729</v>
+        <v>0.00032199417819482243</v>
       </c>
       <c r="Z39">
-        <v>0.00022408046260449503</v>
+        <v>0.00029441787277817005</v>
       </c>
       <c r="AA39">
-        <v>0.00022281909628516845</v>
+        <v>0.000285233309074899</v>
       </c>
       <c r="AB39">
-        <v>0.00022180168910255032</v>
+        <v>0.00028435230084728413</v>
       </c>
       <c r="AC39">
-        <v>0.00019148442444949005</v>
+        <v>0.00025355206957475512</v>
       </c>
       <c r="AD39">
-        <v>0.00022854862851508765</v>
+        <v>0.00027804782011876041</v>
       </c>
       <c r="AE39">
-        <v>0.0002274887040401285</v>
+        <v>0.00029841900131883498</v>
       </c>
       <c r="AF39">
-        <v>0.0002388909793428713</v>
+        <v>0.00032256084552232192</v>
       </c>
       <c r="AG39">
-        <v>0.00024066480240021664</v>
+        <v>0.00031187179503043647</v>
       </c>
       <c r="AH39">
-        <v>0.00023851307056089289</v>
+        <v>0.00031100233412608861</v>
       </c>
       <c r="AI39">
-        <v>0.00024590886463394862</v>
+        <v>0.00032374735282852355</v>
       </c>
       <c r="AJ39">
-        <v>-1.4695251591766525e-006</v>
+        <v>-2.4250475077160073e-006</v>
       </c>
       <c r="AK39">
-        <v>3.250200314755441e-005</v>
+        <v>2.4976561260880043e-005</v>
       </c>
       <c r="AL39">
-        <v>1.1880160152172043e-005</v>
+        <v>2.4047772973866631e-005</v>
       </c>
       <c r="AM39">
-        <v>0.00013673656820282397</v>
+        <v>0.00018949507868750714</v>
       </c>
       <c r="AN39">
-        <v>0.0012604376619608942</v>
+        <v>0.0015019678797580976</v>
       </c>
       <c r="AO39">
-        <v>0.0001135146761462916</v>
+        <v>0.00015472403273091066</v>
       </c>
       <c r="AP39">
-        <v>-0.0002264497100829345</v>
+        <v>-0.00033475287464714964</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="83" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B40" s="84">
-        <v>-0.017290424892321816</v>
+        <v>-0.028810033144918829</v>
       </c>
       <c r="C40">
-        <v>-1.1315224187012598e-005</v>
+        <v>-1.4312852322922504e-005</v>
       </c>
       <c r="D40">
-        <v>3.3872998367635312e-007</v>
+        <v>9.7558378021902033e-007</v>
       </c>
       <c r="E40">
-        <v>3.3415540504087318e-010</v>
+        <v>-6.3829656433431133e-009</v>
       </c>
       <c r="F40">
-        <v>8.4682094594198617e-006</v>
+        <v>-3.461276275298046e-005</v>
       </c>
       <c r="G40">
-        <v>-8.0727329784813635e-006</v>
+        <v>-1.7901567271006092e-005</v>
       </c>
       <c r="H40">
-        <v>-7.6326370123678465e-006</v>
+        <v>-2.1030588931399613e-005</v>
       </c>
       <c r="I40">
-        <v>-0.0001044758352918492</v>
+        <v>-8.9680225190618508e-005</v>
       </c>
       <c r="J40">
-        <v>-3.8224490277556026e-006</v>
+        <v>-9.1589706597766728e-006</v>
       </c>
       <c r="K40">
-        <v>-1.5090125322284091e-005</v>
+        <v>-2.6968576389061036e-005</v>
       </c>
       <c r="L40">
-        <v>-1.9043569434300711e-005</v>
+        <v>-3.3723609365557839e-005</v>
       </c>
       <c r="M40">
-        <v>-4.604741168625975e-005</v>
+        <v>-5.4967395147993649e-005</v>
       </c>
       <c r="N40">
-        <v>1.9187239347263246e-005</v>
+        <v>3.3577921031039922e-005</v>
       </c>
       <c r="O40">
-        <v>2.7190897407221107e-005</v>
+        <v>4.3254506552806844e-005</v>
       </c>
       <c r="P40">
-        <v>2.9574302848604279e-005</v>
+        <v>5.2401526149359407e-005</v>
       </c>
       <c r="Q40">
-        <v>4.0115930129168271e-007</v>
+        <v>4.9130597591549865e-007</v>
       </c>
       <c r="R40">
-        <v>2.1600337069520682e-007</v>
+        <v>3.799758399756497e-007</v>
       </c>
       <c r="S40">
-        <v>-3.52811119898162e-006</v>
+        <v>2.6951643665568104e-007</v>
       </c>
       <c r="T40">
-        <v>-4.7042788226998064e-007</v>
+        <v>5.4919818375307578e-006</v>
       </c>
       <c r="U40">
-        <v>5.7349763497242096e-006</v>
+        <v>1.0936207128327204e-005</v>
       </c>
       <c r="V40">
-        <v>1.7346720579090299e-005</v>
+        <v>3.8001087087854524e-005</v>
       </c>
       <c r="W40">
-        <v>1.6469883503758293e-006</v>
+        <v>2.7631122555568436e-006</v>
       </c>
       <c r="X40">
-        <v>2.1788446848683607e-005</v>
+        <v>2.8847637244940806e-005</v>
       </c>
       <c r="Y40">
-        <v>0.00012840022015475887</v>
+        <v>0.00016054235651108368</v>
       </c>
       <c r="Z40">
-        <v>0.00011387775396989366</v>
+        <v>0.00013964516152186851</v>
       </c>
       <c r="AA40">
-        <v>0.00011095469808093466</v>
+        <v>0.00013171953013120264</v>
       </c>
       <c r="AB40">
-        <v>0.00011002647308434409</v>
+        <v>0.00014507143757859741</v>
       </c>
       <c r="AC40">
-        <v>8.0419854247972819e-005</v>
+        <v>9.0689602332166185e-005</v>
       </c>
       <c r="AD40">
-        <v>8.5360618158684135e-005</v>
+        <v>0.00010085454407000955</v>
       </c>
       <c r="AE40">
-        <v>0.00010526941521295947</v>
+        <v>0.0001271602942039595</v>
       </c>
       <c r="AF40">
-        <v>0.0001146756612829396</v>
+        <v>0.00014347262527256209</v>
       </c>
       <c r="AG40">
-        <v>0.00011440468100020576</v>
+        <v>0.00014467835714745245</v>
       </c>
       <c r="AH40">
-        <v>0.00012803572352893203</v>
+        <v>0.00017239632380401326</v>
       </c>
       <c r="AI40">
-        <v>0.00013010065579448181</v>
+        <v>0.00017472602418663245</v>
       </c>
       <c r="AJ40">
-        <v>-1.5047619369698311e-006</v>
+        <v>-2.6241374964349604e-006</v>
       </c>
       <c r="AK40">
-        <v>3.2659034060193075e-006</v>
+        <v>-1.3924617866137252e-006</v>
       </c>
       <c r="AL40">
-        <v>1.1643702855284428e-005</v>
+        <v>1.912554481871387e-005</v>
       </c>
       <c r="AM40">
-        <v>9.5811828314399826e-005</v>
+        <v>0.00013531069464640949</v>
       </c>
       <c r="AN40">
-        <v>0.0001135146761462916</v>
+        <v>0.00015472403273091066</v>
       </c>
       <c r="AO40">
-        <v>0.0013144800168360031</v>
+        <v>0.0016680611167976798</v>
       </c>
       <c r="AP40">
-        <v>-0.00019425499922096044</v>
+        <v>-0.00025571850085421481</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="85" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B41" s="86">
-        <v>-2.6634817717930104</v>
+        <v>-2.613301948203012</v>
       </c>
       <c r="C41">
-        <v>-2.7821092744957388e-005</v>
+        <v>-6.7254370666582053e-005</v>
       </c>
       <c r="D41">
-        <v>-9.8458947539657398e-005</v>
+        <v>-0.00012376283364610102</v>
       </c>
       <c r="E41">
-        <v>8.8918417274762756e-007</v>
+        <v>1.0986516244585932e-006</v>
       </c>
       <c r="F41">
-        <v>-0.00076007757052670992</v>
+        <v>-0.0012680599551409745</v>
       </c>
       <c r="G41">
-        <v>-0.00039332339225611832</v>
+        <v>-0.00080082845960302855</v>
       </c>
       <c r="H41">
-        <v>-0.00035631449841889615</v>
+        <v>-0.00072356508734771263</v>
       </c>
       <c r="I41">
-        <v>-0.0010855624412434096</v>
+        <v>-0.0011990589407363064</v>
       </c>
       <c r="J41">
-        <v>-0.00048244303525333475</v>
+        <v>-0.00081536554112171587</v>
       </c>
       <c r="K41">
-        <v>-0.00065965859942460818</v>
+        <v>-0.001074992448172149</v>
       </c>
       <c r="L41">
-        <v>-0.00064838574052548514</v>
+        <v>-0.0010882463341904702</v>
       </c>
       <c r="M41">
-        <v>-0.00094498820547275016</v>
+        <v>-0.0012762639937461938</v>
       </c>
       <c r="N41">
-        <v>-0.00051030646215104777</v>
+        <v>-0.00080839978582509966</v>
       </c>
       <c r="O41">
-        <v>-0.00022585421420360098</v>
+        <v>-0.00030407644068005079</v>
       </c>
       <c r="P41">
-        <v>-0.00030275701991134971</v>
+        <v>-0.00042018138682623526</v>
       </c>
       <c r="Q41">
-        <v>-1.6299109273448618e-005</v>
+        <v>-2.1508327258095072e-005</v>
       </c>
       <c r="R41">
-        <v>-1.6582194447138083e-005</v>
+        <v>-2.4388921088267708e-005</v>
       </c>
       <c r="S41">
-        <v>-0.00040633742823792483</v>
+        <v>-0.00065287149090789373</v>
       </c>
       <c r="T41">
-        <v>-0.00052252182929613791</v>
+        <v>-0.00081528509648339724</v>
       </c>
       <c r="U41">
-        <v>-0.00058379962659958675</v>
+        <v>-0.00087657203411124372</v>
       </c>
       <c r="V41">
-        <v>-0.00065654453498738611</v>
+        <v>-0.00099654314500691719</v>
       </c>
       <c r="W41">
-        <v>4.8008945201308781e-005</v>
+        <v>8.8828958102027142e-005</v>
       </c>
       <c r="X41">
-        <v>-4.635130837478164e-005</v>
+        <v>-0.00011630195622004899</v>
       </c>
       <c r="Y41">
-        <v>-0.00043234322940733288</v>
+        <v>-0.00056242643761634289</v>
       </c>
       <c r="Z41">
-        <v>-0.00048679327927524552</v>
+        <v>-0.00060454647545752607</v>
       </c>
       <c r="AA41">
-        <v>-0.00048107354296420067</v>
+        <v>-0.00060671180888266572</v>
       </c>
       <c r="AB41">
-        <v>-0.00047687124664680484</v>
+        <v>-0.00060296090955374887</v>
       </c>
       <c r="AC41">
-        <v>-0.00044166285513180581</v>
+        <v>-0.00052604386838211732</v>
       </c>
       <c r="AD41">
-        <v>-0.00043526500217888506</v>
+        <v>-0.00057253860122573113</v>
       </c>
       <c r="AE41">
-        <v>-0.00049071959395018041</v>
+        <v>-0.00064375537185679566</v>
       </c>
       <c r="AF41">
-        <v>-0.00048580918582485889</v>
+        <v>-0.00062271333639108773</v>
       </c>
       <c r="AG41">
-        <v>-0.00052711606136422945</v>
+        <v>-0.00068551348669360827</v>
       </c>
       <c r="AH41">
-        <v>-0.00046673389497684599</v>
+        <v>-0.00057492929764712142</v>
       </c>
       <c r="AI41">
-        <v>-0.00056294214886482962</v>
+        <v>-0.00073284384434719606</v>
       </c>
       <c r="AJ41">
-        <v>-6.7996656731506271e-005</v>
+        <v>-8.9029936285981516e-005</v>
       </c>
       <c r="AK41">
-        <v>0.00027739917830967237</v>
+        <v>0.00038545106711325428</v>
       </c>
       <c r="AL41">
-        <v>0.00031112168285833295</v>
+        <v>0.00040011091287588151</v>
       </c>
       <c r="AM41">
-        <v>-0.00027942616692718534</v>
+        <v>-0.00044213336103730752</v>
       </c>
       <c r="AN41">
-        <v>-0.0002264497100829345</v>
+        <v>-0.00033475287464714964</v>
       </c>
       <c r="AO41">
-        <v>-0.00019425499922096044</v>
+        <v>-0.00025571850085421481</v>
       </c>
       <c r="AP41">
-        <v>0.0068363696172967156</v>
+        <v>0.0094034129818738339</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/initial_populations/regression_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27509A2-5F91-D34E-97AA-9C0D6B72DB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F188D8E-6197-8F41-BBFD-D819C5B872CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_HO1" sheetId="3" r:id="rId3"/>
+    <sheet name="HO1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
   <si>
     <t>Description:</t>
   </si>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>HO1 - Home ownership</t>
@@ -715,32 +712,32 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>0.83956863095016954</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>47460.99545693447</v>
+        <v>47460.995456934616</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>212305</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>-16484536.500980252</v>
@@ -753,10 +750,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AR42"/>
+  <dimension ref="A1:AQ42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -886,11 +883,8 @@
       <c r="AQ1" t="s">
         <v>54</v>
       </c>
-      <c r="AR1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -898,130 +892,130 @@
         <v>6.4632822275978415E-3</v>
       </c>
       <c r="C2">
-        <v>2.8112890482808616E-4</v>
+        <v>2.8112890482808638E-4</v>
       </c>
       <c r="D2">
-        <v>1.3265941706505518E-6</v>
+        <v>1.326594170650528E-6</v>
       </c>
       <c r="E2">
-        <v>-4.1167369895799019E-9</v>
+        <v>-4.1167369895795048E-9</v>
       </c>
       <c r="F2">
-        <v>3.577529414745983E-5</v>
+        <v>3.5775294147460501E-5</v>
       </c>
       <c r="G2">
-        <v>-3.5478166954228811E-5</v>
+        <v>-3.547816695422892E-5</v>
       </c>
       <c r="H2">
-        <v>-1.9616090988398419E-5</v>
+        <v>-1.9616090988398405E-5</v>
       </c>
       <c r="I2">
-        <v>-5.4779245973899396E-5</v>
+        <v>-5.4779245973899369E-5</v>
       </c>
       <c r="J2">
-        <v>-4.4797962091598376E-5</v>
+        <v>-4.4797962091597977E-5</v>
       </c>
       <c r="K2">
-        <v>5.5210393956374733E-5</v>
+        <v>5.521039395637499E-5</v>
       </c>
       <c r="L2">
-        <v>1.4023728334026971E-4</v>
+        <v>1.4023728334026914E-4</v>
       </c>
       <c r="M2">
-        <v>5.1447425980216355E-6</v>
+        <v>5.1447425980230213E-6</v>
       </c>
       <c r="N2">
-        <v>-3.0141657115765127E-5</v>
+        <v>-3.0141657115764432E-5</v>
       </c>
       <c r="O2">
-        <v>-2.0112437652260877E-5</v>
+        <v>-2.0112437652261216E-5</v>
       </c>
       <c r="P2">
-        <v>-2.2499293713270261E-5</v>
+        <v>-2.2499293713269813E-5</v>
       </c>
       <c r="Q2">
-        <v>-2.2586808177342496E-5</v>
+        <v>-2.2586808177342252E-5</v>
       </c>
       <c r="R2">
-        <v>-2.1314131056072083E-6</v>
+        <v>-2.1314131056072062E-6</v>
       </c>
       <c r="S2">
-        <v>-4.794534777729969E-7</v>
+        <v>-4.7945347777298271E-7</v>
       </c>
       <c r="T2">
-        <v>-1.0673484702894912E-5</v>
+        <v>-1.0673484702895094E-5</v>
       </c>
       <c r="U2">
-        <v>-1.1917548239504982E-5</v>
+        <v>-1.1917548239504753E-5</v>
       </c>
       <c r="V2">
-        <v>-2.0040872286459621E-5</v>
+        <v>-2.0040872286459011E-5</v>
       </c>
       <c r="W2">
-        <v>-3.3429963124193714E-5</v>
+        <v>-3.3429963124193498E-5</v>
       </c>
       <c r="X2">
-        <v>-3.2380729423232183E-7</v>
+        <v>-3.2380729423231209E-7</v>
       </c>
       <c r="Y2">
-        <v>4.5785218710541319E-6</v>
+        <v>4.5785218710541725E-6</v>
       </c>
       <c r="Z2">
-        <v>1.7266423627667071E-5</v>
+        <v>1.7266423627667288E-5</v>
       </c>
       <c r="AA2">
-        <v>4.8888985168169384E-5</v>
+        <v>4.8888985168169479E-5</v>
       </c>
       <c r="AB2">
-        <v>7.8037873559623172E-6</v>
+        <v>7.8037873559625391E-6</v>
       </c>
       <c r="AC2">
-        <v>1.742594842869441E-5</v>
+        <v>1.7425948428694091E-5</v>
       </c>
       <c r="AD2">
-        <v>9.8638238250881819E-6</v>
+        <v>9.8638238250881853E-6</v>
       </c>
       <c r="AE2">
-        <v>1.1707726106089E-6</v>
+        <v>1.1707726106089339E-6</v>
       </c>
       <c r="AF2">
-        <v>1.3265544569139946E-5</v>
+        <v>1.3265544569140191E-5</v>
       </c>
       <c r="AG2">
-        <v>1.6010176626664494E-5</v>
+        <v>1.6010176626664653E-5</v>
       </c>
       <c r="AH2">
-        <v>5.8296923045337368E-5</v>
+        <v>5.8296923045337124E-5</v>
       </c>
       <c r="AI2">
-        <v>5.3311968753028329E-5</v>
+        <v>5.3311968753028356E-5</v>
       </c>
       <c r="AJ2">
-        <v>1.8319910200220186E-5</v>
+        <v>1.8319910200220579E-5</v>
       </c>
       <c r="AK2">
-        <v>7.8527576009740294E-7</v>
+        <v>7.8527576009741988E-7</v>
       </c>
       <c r="AL2">
-        <v>2.9722505776108946E-6</v>
+        <v>2.9722505776107422E-6</v>
       </c>
       <c r="AM2">
-        <v>-6.6561361730079099E-6</v>
+        <v>-6.6561361730082217E-6</v>
       </c>
       <c r="AN2">
-        <v>-1.8539723440685436E-5</v>
+        <v>-1.8539723440685585E-5</v>
       </c>
       <c r="AO2">
-        <v>9.7104217756908978E-5</v>
+        <v>9.710421775690887E-5</v>
       </c>
       <c r="AP2">
-        <v>-3.6166354192387089E-5</v>
+        <v>-3.6166354192387116E-5</v>
       </c>
       <c r="AQ2">
-        <v>-1.0463361448893699E-4</v>
+        <v>-1.0463361448894311E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1029,130 +1023,130 @@
         <v>5.6434204237526715E-4</v>
       </c>
       <c r="C3">
-        <v>1.3265941706505518E-6</v>
+        <v>1.326594170650528E-6</v>
       </c>
       <c r="D3">
-        <v>5.9683447131139818E-6</v>
+        <v>5.9683447131137794E-6</v>
       </c>
       <c r="E3">
-        <v>-5.6847250053372611E-8</v>
+        <v>-5.6847250053370963E-8</v>
       </c>
       <c r="F3">
-        <v>1.5858106540866003E-5</v>
+        <v>1.5858106540867264E-5</v>
       </c>
       <c r="G3">
-        <v>1.8346668871471976E-6</v>
+        <v>1.8346668871478103E-6</v>
       </c>
       <c r="H3">
-        <v>-1.2472407725576227E-7</v>
+        <v>-1.2472407725467807E-7</v>
       </c>
       <c r="I3">
-        <v>3.4033004266297721E-6</v>
+        <v>3.4033004266301516E-6</v>
       </c>
       <c r="J3">
-        <v>-4.9694033723346383E-6</v>
+        <v>-4.9694033723339031E-6</v>
       </c>
       <c r="K3">
-        <v>7.7389062860290616E-6</v>
+        <v>7.7389062860289531E-6</v>
       </c>
       <c r="L3">
-        <v>4.9873168394488625E-7</v>
+        <v>4.9873168394480547E-7</v>
       </c>
       <c r="M3">
-        <v>3.470209969312979E-5</v>
+        <v>3.4702099693127012E-5</v>
       </c>
       <c r="N3">
-        <v>-1.8902290535966368E-6</v>
+        <v>-1.8902290535952477E-6</v>
       </c>
       <c r="O3">
-        <v>1.0099838873522417E-5</v>
+        <v>1.0099838873521611E-5</v>
       </c>
       <c r="P3">
-        <v>8.0220833846362442E-7</v>
+        <v>8.0220833846373284E-7</v>
       </c>
       <c r="Q3">
         <v>2.1282685206250372E-6</v>
       </c>
       <c r="R3">
-        <v>8.0256914007371868E-8</v>
+        <v>8.0256914007411466E-8</v>
       </c>
       <c r="S3">
-        <v>1.5109744239548027E-7</v>
+        <v>1.5109744239549213E-7</v>
       </c>
       <c r="T3">
-        <v>5.1030028172545373E-7</v>
+        <v>5.1030028172586284E-7</v>
       </c>
       <c r="U3">
-        <v>-1.4168889714592145E-6</v>
+        <v>-1.4168889714583302E-6</v>
       </c>
       <c r="V3">
-        <v>-9.2865874744494012E-6</v>
+        <v>-9.2865874744480307E-6</v>
       </c>
       <c r="W3">
-        <v>-1.2390114950463161E-5</v>
+        <v>-1.2390114950462741E-5</v>
       </c>
       <c r="X3">
-        <v>-5.1957233843464934E-7</v>
+        <v>-5.1957233843454346E-7</v>
       </c>
       <c r="Y3">
-        <v>1.4965674266039544E-6</v>
+        <v>1.496567426603846E-6</v>
       </c>
       <c r="Z3">
-        <v>7.1880752591649884E-7</v>
+        <v>7.1880752591607194E-7</v>
       </c>
       <c r="AA3">
-        <v>1.0385655473421718E-6</v>
+        <v>1.0385655473419618E-6</v>
       </c>
       <c r="AB3">
-        <v>-1.5581584983847213E-6</v>
+        <v>-1.5581584983845231E-6</v>
       </c>
       <c r="AC3">
-        <v>1.5415407692319087E-6</v>
+        <v>1.5415407692324897E-6</v>
       </c>
       <c r="AD3">
-        <v>-1.7550097060608648E-6</v>
+        <v>-1.755009706060648E-6</v>
       </c>
       <c r="AE3">
-        <v>-5.380086323422273E-7</v>
+        <v>-5.3800863234197319E-7</v>
       </c>
       <c r="AF3">
-        <v>-1.1732734063388387E-6</v>
+        <v>-1.1732734063388366E-6</v>
       </c>
       <c r="AG3">
-        <v>2.2386440755936066E-6</v>
+        <v>2.238644075594053E-6</v>
       </c>
       <c r="AH3">
-        <v>-6.0326533419206095E-7</v>
+        <v>-6.032653341916476E-7</v>
       </c>
       <c r="AI3">
-        <v>-2.5941061600834274E-6</v>
+        <v>-2.5941061600832292E-6</v>
       </c>
       <c r="AJ3">
-        <v>1.0391713542184542E-6</v>
+        <v>1.039171354219037E-6</v>
       </c>
       <c r="AK3">
-        <v>-1.9472051545106283E-7</v>
+        <v>-1.9472051545090359E-7</v>
       </c>
       <c r="AL3">
-        <v>-8.8297879159707828E-7</v>
+        <v>-8.829787915970715E-7</v>
       </c>
       <c r="AM3">
-        <v>-3.2583311215830148E-6</v>
+        <v>-3.2583311215834349E-6</v>
       </c>
       <c r="AN3">
-        <v>2.8968676621128807E-6</v>
+        <v>2.89686766211284E-6</v>
       </c>
       <c r="AO3">
-        <v>-2.7473720154349768E-6</v>
+        <v>-2.7473720154348752E-6</v>
       </c>
       <c r="AP3">
-        <v>2.2824532579532E-6</v>
+        <v>2.2824532579531864E-6</v>
       </c>
       <c r="AQ3">
-        <v>-1.4969811846435749E-4</v>
+        <v>-1.496981184643576E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1160,130 +1154,130 @@
         <v>3.0972954241088396E-5</v>
       </c>
       <c r="C4">
-        <v>-4.1167369895799019E-9</v>
+        <v>-4.1167369895795048E-9</v>
       </c>
       <c r="D4">
-        <v>-5.6847250053372611E-8</v>
+        <v>-5.6847250053370963E-8</v>
       </c>
       <c r="E4">
-        <v>5.9231247559258677E-10</v>
+        <v>5.9231247559257074E-10</v>
       </c>
       <c r="F4">
-        <v>-1.1933800828556481E-7</v>
+        <v>-1.193380082855773E-7</v>
       </c>
       <c r="G4">
-        <v>-2.9545646628552649E-8</v>
+        <v>-2.9545646628558409E-8</v>
       </c>
       <c r="H4">
-        <v>2.7724951974399332E-8</v>
+        <v>2.7724951974389274E-8</v>
       </c>
       <c r="I4">
-        <v>6.6969234602274993E-9</v>
+        <v>6.6969234602236347E-9</v>
       </c>
       <c r="J4">
-        <v>6.7832198310583502E-8</v>
+        <v>6.7832198310577413E-8</v>
       </c>
       <c r="K4">
-        <v>-6.7412777043315261E-8</v>
+        <v>-6.7412777043313832E-8</v>
       </c>
       <c r="L4">
-        <v>2.6617813063754605E-8</v>
+        <v>2.6617813063754672E-8</v>
       </c>
       <c r="M4">
-        <v>-2.3131242938586972E-7</v>
+        <v>-2.3131242938584193E-7</v>
       </c>
       <c r="N4">
-        <v>5.4814708542981449E-8</v>
+        <v>5.4814708542968638E-8</v>
       </c>
       <c r="O4">
-        <v>-1.952651274976213E-7</v>
+        <v>-1.9526512749761413E-7</v>
       </c>
       <c r="P4">
-        <v>-1.3109522906017836E-8</v>
+        <v>-1.3109522906018683E-8</v>
       </c>
       <c r="Q4">
-        <v>-6.277204478045878E-8</v>
+        <v>-6.2772044780458462E-8</v>
       </c>
       <c r="R4">
-        <v>-1.4423251762424175E-9</v>
+        <v>-1.4423251762428079E-9</v>
       </c>
       <c r="S4">
-        <v>-2.7431527697144156E-10</v>
+        <v>-2.7431527697157474E-10</v>
       </c>
       <c r="T4">
-        <v>1.9731431167351537E-8</v>
+        <v>1.9731431167347116E-8</v>
       </c>
       <c r="U4">
-        <v>4.6841916230393653E-8</v>
+        <v>4.6841916230385024E-8</v>
       </c>
       <c r="V4">
-        <v>1.0953159158623194E-7</v>
+        <v>1.0953159158621928E-7</v>
       </c>
       <c r="W4">
-        <v>1.2569611486879355E-7</v>
+        <v>1.2569611486878902E-7</v>
       </c>
       <c r="X4">
-        <v>-7.6582206144059152E-10</v>
+        <v>-7.658220614415709E-10</v>
       </c>
       <c r="Y4">
-        <v>-2.9644124332866767E-8</v>
+        <v>-2.9644124332865602E-8</v>
       </c>
       <c r="Z4">
-        <v>-9.1943244777236244E-10</v>
+        <v>-9.1943244776833904E-10</v>
       </c>
       <c r="AA4">
-        <v>-1.3761691063373766E-8</v>
+        <v>-1.3761691063372072E-8</v>
       </c>
       <c r="AB4">
-        <v>1.9331386674732338E-8</v>
+        <v>1.9331386674730246E-8</v>
       </c>
       <c r="AC4">
-        <v>-1.1343051444583115E-8</v>
+        <v>-1.1343051444589269E-8</v>
       </c>
       <c r="AD4">
-        <v>3.1891023417151982E-8</v>
+        <v>3.1891023417150023E-8</v>
       </c>
       <c r="AE4">
-        <v>5.7308876488009801E-9</v>
+        <v>5.7308876487989684E-9</v>
       </c>
       <c r="AF4">
-        <v>6.8595281824058502E-9</v>
+        <v>6.8595281824057973E-9</v>
       </c>
       <c r="AG4">
-        <v>-2.7341669616014112E-8</v>
+        <v>-2.7341669616018331E-8</v>
       </c>
       <c r="AH4">
-        <v>6.414093021727785E-9</v>
+        <v>6.4140930217235499E-9</v>
       </c>
       <c r="AI4">
-        <v>2.1617943775583462E-8</v>
+        <v>2.1617943775581397E-8</v>
       </c>
       <c r="AJ4">
-        <v>-8.3040855573977436E-9</v>
+        <v>-8.3040855574029317E-9</v>
       </c>
       <c r="AK4">
-        <v>5.0881193645026895E-10</v>
+        <v>5.088119364487337E-10</v>
       </c>
       <c r="AL4">
-        <v>9.0022978437306922E-9</v>
+        <v>9.0022978437305863E-9</v>
       </c>
       <c r="AM4">
-        <v>2.9540166073960222E-8</v>
+        <v>2.954016607396414E-8</v>
       </c>
       <c r="AN4">
-        <v>-2.1345251528660468E-8</v>
+        <v>-2.1345251528660415E-8</v>
       </c>
       <c r="AO4">
-        <v>7.0629170521039134E-9</v>
+        <v>7.0629170521029075E-9</v>
       </c>
       <c r="AP4">
         <v>-1.4071416819641246E-8</v>
       </c>
       <c r="AQ4">
-        <v>1.2922709265102472E-6</v>
+        <v>1.2922709265102534E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1291,130 +1285,130 @@
         <v>-0.22816021923480417</v>
       </c>
       <c r="C5">
-        <v>3.577529414745983E-5</v>
+        <v>3.5775294147460501E-5</v>
       </c>
       <c r="D5">
-        <v>1.5858106540866003E-5</v>
+        <v>1.5858106540867264E-5</v>
       </c>
       <c r="E5">
-        <v>-1.1933800828556481E-7</v>
+        <v>-1.193380082855773E-7</v>
       </c>
       <c r="F5">
         <v>2.6201536227452096E-2</v>
       </c>
       <c r="G5">
-        <v>8.6223136404836023E-4</v>
+        <v>8.6223136404836316E-4</v>
       </c>
       <c r="H5">
-        <v>8.3001935566200927E-4</v>
+        <v>8.3001935566201371E-4</v>
       </c>
       <c r="I5">
-        <v>9.4410729998791083E-4</v>
+        <v>9.4410729998791203E-4</v>
       </c>
       <c r="J5">
-        <v>8.907965921434158E-4</v>
+        <v>8.9079659214342166E-4</v>
       </c>
       <c r="K5">
-        <v>8.9363118851582826E-4</v>
+        <v>8.9363118851583162E-4</v>
       </c>
       <c r="L5">
-        <v>9.2893922120956059E-4</v>
+        <v>9.2893922120955853E-4</v>
       </c>
       <c r="M5">
-        <v>-1.0359063805551346E-4</v>
+        <v>-1.035906380555159E-4</v>
       </c>
       <c r="N5">
-        <v>-3.7113780297914304E-5</v>
+        <v>-3.7113780297906389E-5</v>
       </c>
       <c r="O5">
-        <v>-6.8557040865207608E-5</v>
+        <v>-6.855704086521265E-5</v>
       </c>
       <c r="P5">
-        <v>1.9057456995744067E-4</v>
+        <v>1.9057456995744126E-4</v>
       </c>
       <c r="Q5">
-        <v>1.7051250024409912E-4</v>
+        <v>1.7051250024409999E-4</v>
       </c>
       <c r="R5">
-        <v>3.0734449677816423E-6</v>
+        <v>3.0734449677817973E-6</v>
       </c>
       <c r="S5">
-        <v>-1.70217233895437E-6</v>
+        <v>-1.7021723389542858E-6</v>
       </c>
       <c r="T5">
-        <v>-6.8545697744602142E-5</v>
+        <v>-6.8545697744600841E-5</v>
       </c>
       <c r="U5">
-        <v>-1.1285954672276581E-4</v>
+        <v>-1.1285954672276083E-4</v>
       </c>
       <c r="V5">
-        <v>-4.3536970090694296E-6</v>
+        <v>-4.3536970090630599E-6</v>
       </c>
       <c r="W5">
-        <v>2.6211592284412316E-4</v>
+        <v>2.6211592284412511E-4</v>
       </c>
       <c r="X5">
-        <v>-2.707574289062187E-7</v>
+        <v>-2.7075742890616449E-7</v>
       </c>
       <c r="Y5">
-        <v>7.8240198564441456E-5</v>
+        <v>7.8240198564441673E-5</v>
       </c>
       <c r="Z5">
-        <v>-3.5656270265161906E-5</v>
+        <v>-3.5656270265161988E-5</v>
       </c>
       <c r="AA5">
-        <v>4.1009830256702473E-5</v>
+        <v>4.1009830256702581E-5</v>
       </c>
       <c r="AB5">
-        <v>4.6647438236290399E-5</v>
+        <v>4.6647438236291347E-5</v>
       </c>
       <c r="AC5">
-        <v>9.4048309793545056E-5</v>
+        <v>9.4048309793546967E-5</v>
       </c>
       <c r="AD5">
-        <v>1.7463949362533308E-4</v>
+        <v>1.7463949362533454E-4</v>
       </c>
       <c r="AE5">
-        <v>1.3537401281889813E-5</v>
+        <v>1.353740128189228E-5</v>
       </c>
       <c r="AF5">
-        <v>5.6339334809153123E-5</v>
+        <v>5.6339334809153557E-5</v>
       </c>
       <c r="AG5">
-        <v>7.2549263802658252E-5</v>
+        <v>7.2549263802661776E-5</v>
       </c>
       <c r="AH5">
-        <v>8.1294174609361622E-5</v>
+        <v>8.129417460936295E-5</v>
       </c>
       <c r="AI5">
-        <v>-1.1935451546435144E-7</v>
+        <v>-1.193545154633079E-7</v>
       </c>
       <c r="AJ5">
-        <v>1.0343462939672773E-4</v>
+        <v>1.0343462939673212E-4</v>
       </c>
       <c r="AK5">
-        <v>2.8372371979947257E-6</v>
+        <v>2.8372371979952678E-6</v>
       </c>
       <c r="AL5">
-        <v>3.2535226324208655E-5</v>
+        <v>3.253522632420795E-5</v>
       </c>
       <c r="AM5">
-        <v>-1.1760968013645135E-5</v>
+        <v>-1.1760968013646762E-5</v>
       </c>
       <c r="AN5">
-        <v>9.0706039357784822E-5</v>
+        <v>9.0706039357783656E-5</v>
       </c>
       <c r="AO5">
-        <v>1.5386057604885057E-4</v>
+        <v>1.5386057604885089E-4</v>
       </c>
       <c r="AP5">
-        <v>5.2729231957938005E-4</v>
+        <v>5.2729231957937995E-4</v>
       </c>
       <c r="AQ5">
-        <v>-1.6940687462424404E-3</v>
+        <v>-1.6940687462424716E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1422,130 +1416,130 @@
         <v>-3.6410240215586274E-2</v>
       </c>
       <c r="C6">
-        <v>-3.5478166954228811E-5</v>
+        <v>-3.547816695422892E-5</v>
       </c>
       <c r="D6">
-        <v>1.8346668871471976E-6</v>
+        <v>1.8346668871478103E-6</v>
       </c>
       <c r="E6">
-        <v>-2.9545646628552649E-8</v>
+        <v>-2.9545646628558409E-8</v>
       </c>
       <c r="F6">
-        <v>8.6223136404836023E-4</v>
+        <v>8.6223136404836316E-4</v>
       </c>
       <c r="G6">
-        <v>1.3101217713311626E-3</v>
+        <v>1.3101217713311641E-3</v>
       </c>
       <c r="H6">
-        <v>7.4719263369302073E-4</v>
+        <v>7.4719263369302225E-4</v>
       </c>
       <c r="I6">
-        <v>8.286616411086904E-4</v>
+        <v>8.2866164110869105E-4</v>
       </c>
       <c r="J6">
-        <v>8.3648800598759554E-4</v>
+        <v>8.364880059875989E-4</v>
       </c>
       <c r="K6">
-        <v>9.0859493595949988E-4</v>
+        <v>9.0859493595950324E-4</v>
       </c>
       <c r="L6">
-        <v>8.6715963143938716E-4</v>
+        <v>8.6715963143938618E-4</v>
       </c>
       <c r="M6">
-        <v>-7.8109208978108507E-5</v>
+        <v>-7.8109208978104007E-5</v>
       </c>
       <c r="N6">
-        <v>-1.1106778717279641E-4</v>
+        <v>-1.1106778717279267E-4</v>
       </c>
       <c r="O6">
-        <v>-1.1370285343764226E-4</v>
+        <v>-1.1370285343764578E-4</v>
       </c>
       <c r="P6">
-        <v>2.0876707732625619E-5</v>
+        <v>2.0876707732626106E-5</v>
       </c>
       <c r="Q6">
-        <v>2.5985018000353286E-5</v>
+        <v>2.5985018000354424E-5</v>
       </c>
       <c r="R6">
-        <v>-6.2137180231451083E-7</v>
+        <v>-6.2137180231444307E-7</v>
       </c>
       <c r="S6">
-        <v>-8.2971140868829353E-7</v>
+        <v>-8.2971140868822672E-7</v>
       </c>
       <c r="T6">
-        <v>-7.2899349776585416E-5</v>
+        <v>-7.2899349776584698E-5</v>
       </c>
       <c r="U6">
-        <v>-5.4913677236374247E-5</v>
+        <v>-5.4913677236371022E-5</v>
       </c>
       <c r="V6">
-        <v>7.4896629417315057E-5</v>
+        <v>7.4896629417317442E-5</v>
       </c>
       <c r="W6">
-        <v>2.6613440371310332E-4</v>
+        <v>2.6613440371310489E-4</v>
       </c>
       <c r="X6">
-        <v>-3.5266315947477373E-6</v>
+        <v>-3.5266315947480727E-6</v>
       </c>
       <c r="Y6">
-        <v>-3.6131200329632938E-5</v>
+        <v>-3.6131200329632559E-5</v>
       </c>
       <c r="Z6">
-        <v>1.4100748858151844E-5</v>
+        <v>1.4100748858153267E-5</v>
       </c>
       <c r="AA6">
-        <v>6.739098545921685E-5</v>
+        <v>6.7390985459217826E-5</v>
       </c>
       <c r="AB6">
-        <v>5.7688548343415136E-5</v>
+        <v>5.7688548343415854E-5</v>
       </c>
       <c r="AC6">
-        <v>6.3869003200144124E-5</v>
+        <v>6.3869003200144828E-5</v>
       </c>
       <c r="AD6">
-        <v>-2.7076336599812296E-5</v>
+        <v>-2.7076336599811374E-5</v>
       </c>
       <c r="AE6">
-        <v>3.417940781260557E-5</v>
+        <v>3.4179407812607407E-5</v>
       </c>
       <c r="AF6">
-        <v>6.0167040611791025E-5</v>
+        <v>6.0167040611791797E-5</v>
       </c>
       <c r="AG6">
-        <v>4.5790779789221042E-5</v>
+        <v>4.5790779789223523E-5</v>
       </c>
       <c r="AH6">
-        <v>8.2417209680077236E-5</v>
+        <v>8.24172096800779E-5</v>
       </c>
       <c r="AI6">
-        <v>-1.0263090904517983E-5</v>
+        <v>-1.0263090904517292E-5</v>
       </c>
       <c r="AJ6">
-        <v>3.8272565510345097E-5</v>
+        <v>3.8272565510348187E-5</v>
       </c>
       <c r="AK6">
-        <v>-2.6064669447827888E-6</v>
+        <v>-2.6064669447825855E-6</v>
       </c>
       <c r="AL6">
-        <v>1.4713503793645222E-5</v>
+        <v>1.4713503793644707E-5</v>
       </c>
       <c r="AM6">
-        <v>2.2756918819256489E-5</v>
+        <v>2.2756918819256028E-5</v>
       </c>
       <c r="AN6">
-        <v>8.0026343163583374E-5</v>
+        <v>8.0026343163582615E-5</v>
       </c>
       <c r="AO6">
-        <v>7.7999632797990667E-5</v>
+        <v>7.7999632797991154E-5</v>
       </c>
       <c r="AP6">
-        <v>-1.8521547443979357E-5</v>
+        <v>-1.8521547443979276E-5</v>
       </c>
       <c r="AQ6">
-        <v>-7.4329922940479919E-4</v>
+        <v>-7.4329922940483042E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1553,130 +1547,130 @@
         <v>4.1499949375019095E-4</v>
       </c>
       <c r="C7">
-        <v>-1.9616090988398419E-5</v>
+        <v>-1.9616090988398405E-5</v>
       </c>
       <c r="D7">
-        <v>-1.2472407725576227E-7</v>
+        <v>-1.2472407725467807E-7</v>
       </c>
       <c r="E7">
-        <v>2.7724951974399332E-8</v>
+        <v>2.7724951974389274E-8</v>
       </c>
       <c r="F7">
-        <v>8.3001935566200927E-4</v>
+        <v>8.3001935566201371E-4</v>
       </c>
       <c r="G7">
-        <v>7.4719263369302073E-4</v>
+        <v>7.4719263369302225E-4</v>
       </c>
       <c r="H7">
-        <v>1.6722460724610854E-3</v>
+        <v>1.6722460724610865E-3</v>
       </c>
       <c r="I7">
-        <v>7.5186860241506731E-4</v>
+        <v>7.5186860241506753E-4</v>
       </c>
       <c r="J7">
-        <v>8.0966052712205046E-4</v>
+        <v>8.096605271220536E-4</v>
       </c>
       <c r="K7">
-        <v>7.5247791262529715E-4</v>
+        <v>7.5247791262530073E-4</v>
       </c>
       <c r="L7">
-        <v>7.6751238638530107E-4</v>
+        <v>7.6751238638529977E-4</v>
       </c>
       <c r="M7">
-        <v>1.2757067527436217E-4</v>
+        <v>1.2757067527436784E-4</v>
       </c>
       <c r="N7">
-        <v>6.6965069705780177E-5</v>
+        <v>6.6965069705783809E-5</v>
       </c>
       <c r="O7">
-        <v>-3.3086822578122873E-5</v>
+        <v>-3.3086822578124825E-5</v>
       </c>
       <c r="P7">
-        <v>-5.3737705446191091E-6</v>
+        <v>-5.3737705446185941E-6</v>
       </c>
       <c r="Q7">
-        <v>1.5761996969566731E-5</v>
+        <v>1.5761996969567869E-5</v>
       </c>
       <c r="R7">
-        <v>-1.161153565455648E-6</v>
+        <v>-1.1611535654556061E-6</v>
       </c>
       <c r="S7">
-        <v>5.2644771053443058E-7</v>
+        <v>5.264477105344958E-7</v>
       </c>
       <c r="T7">
-        <v>-1.9866113831989986E-6</v>
+        <v>-1.9866113831980736E-6</v>
       </c>
       <c r="U7">
-        <v>-1.0626962083514489E-5</v>
+        <v>-1.0626962083511521E-5</v>
       </c>
       <c r="V7">
-        <v>3.3439141718737903E-5</v>
+        <v>3.3439141718740973E-5</v>
       </c>
       <c r="W7">
-        <v>2.3690804101118506E-4</v>
+        <v>2.3690804101118675E-4</v>
       </c>
       <c r="X7">
-        <v>8.2080509184270777E-6</v>
+        <v>8.2080509184267727E-6</v>
       </c>
       <c r="Y7">
-        <v>-5.0501516284037653E-5</v>
+        <v>-5.0501516284037328E-5</v>
       </c>
       <c r="Z7">
-        <v>-2.0956617604762464E-5</v>
+        <v>-2.0956617604760865E-5</v>
       </c>
       <c r="AA7">
-        <v>3.4266425746719157E-8</v>
+        <v>3.4266425747613623E-8</v>
       </c>
       <c r="AB7">
-        <v>1.1145157449789273E-5</v>
+        <v>1.1145157449789937E-5</v>
       </c>
       <c r="AC7">
-        <v>2.1486487525607271E-5</v>
+        <v>2.1486487525607779E-5</v>
       </c>
       <c r="AD7">
-        <v>3.5309338747711492E-6</v>
+        <v>3.5309338747718268E-6</v>
       </c>
       <c r="AE7">
-        <v>-2.4259919458970088E-6</v>
+        <v>-2.4259919458952063E-6</v>
       </c>
       <c r="AF7">
-        <v>1.2135610741111388E-5</v>
+        <v>1.2135610741112153E-5</v>
       </c>
       <c r="AG7">
-        <v>1.0646501247680785E-5</v>
+        <v>1.0646501247682945E-5</v>
       </c>
       <c r="AH7">
-        <v>7.9261892200310823E-5</v>
+        <v>7.9261892200311338E-5</v>
       </c>
       <c r="AI7">
-        <v>-5.0683902400714418E-5</v>
+        <v>-5.0683902400713835E-5</v>
       </c>
       <c r="AJ7">
-        <v>6.7301913658924638E-6</v>
+        <v>6.730191365895337E-6</v>
       </c>
       <c r="AK7">
-        <v>5.362191621479054E-6</v>
+        <v>5.3621916214791488E-6</v>
       </c>
       <c r="AL7">
-        <v>4.5088265248921392E-6</v>
+        <v>4.5088265248917055E-6</v>
       </c>
       <c r="AM7">
-        <v>-1.8791040016733732E-5</v>
+        <v>-1.8791040016734084E-5</v>
       </c>
       <c r="AN7">
-        <v>-5.8515461676648359E-5</v>
+        <v>-5.8515461676648969E-5</v>
       </c>
       <c r="AO7">
-        <v>4.7719899226147234E-4</v>
+        <v>4.7719899226147261E-4</v>
       </c>
       <c r="AP7">
-        <v>-8.7355630996348765E-6</v>
+        <v>-8.7355630996347139E-6</v>
       </c>
       <c r="AQ7">
-        <v>-9.2364851458754337E-4</v>
+        <v>-9.2364851458757503E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1684,130 +1678,130 @@
         <v>-0.32282326022716623</v>
       </c>
       <c r="C8">
-        <v>-5.4779245973899396E-5</v>
+        <v>-5.4779245973899369E-5</v>
       </c>
       <c r="D8">
-        <v>3.4033004266297721E-6</v>
+        <v>3.4033004266301516E-6</v>
       </c>
       <c r="E8">
-        <v>6.6969234602274993E-9</v>
+        <v>6.6969234602236347E-9</v>
       </c>
       <c r="F8">
-        <v>9.4410729998791083E-4</v>
+        <v>9.4410729998791203E-4</v>
       </c>
       <c r="G8">
-        <v>8.286616411086904E-4</v>
+        <v>8.2866164110869105E-4</v>
       </c>
       <c r="H8">
-        <v>7.5186860241506731E-4</v>
+        <v>7.5186860241506753E-4</v>
       </c>
       <c r="I8">
         <v>2.3348972678353057E-2</v>
       </c>
       <c r="J8">
-        <v>9.1347697357601059E-4</v>
+        <v>9.134769735760146E-4</v>
       </c>
       <c r="K8">
-        <v>8.4939976849165164E-4</v>
+        <v>8.4939976849165608E-4</v>
       </c>
       <c r="L8">
-        <v>9.2260799600029481E-4</v>
+        <v>9.2260799600029318E-4</v>
       </c>
       <c r="M8">
-        <v>1.9947495953087608E-4</v>
+        <v>1.9947495953088402E-4</v>
       </c>
       <c r="N8">
-        <v>9.1114879777542506E-5</v>
+        <v>9.1114879777547141E-5</v>
       </c>
       <c r="O8">
-        <v>-2.325389302355917E-5</v>
+        <v>-2.3253893023560362E-5</v>
       </c>
       <c r="P8">
-        <v>1.0007799831811463E-4</v>
+        <v>1.000779983181152E-4</v>
       </c>
       <c r="Q8">
-        <v>1.0578522504095744E-4</v>
+        <v>1.0578522504095869E-4</v>
       </c>
       <c r="R8">
-        <v>1.5461417812719452E-6</v>
+        <v>1.5461417812720125E-6</v>
       </c>
       <c r="S8">
-        <v>3.6767718028928474E-7</v>
+        <v>3.6767718028934699E-7</v>
       </c>
       <c r="T8">
-        <v>-3.4503047078789107E-5</v>
+        <v>-3.4503047078787752E-5</v>
       </c>
       <c r="U8">
-        <v>-8.4988799460574652E-6</v>
+        <v>-8.498879946053291E-6</v>
       </c>
       <c r="V8">
-        <v>2.244178279617774E-4</v>
+        <v>2.2441782796178082E-4</v>
       </c>
       <c r="W8">
-        <v>4.666156026794133E-4</v>
+        <v>4.6661560267941471E-4</v>
       </c>
       <c r="X8">
-        <v>6.5324197449251624E-6</v>
+        <v>6.532419744924871E-6</v>
       </c>
       <c r="Y8">
-        <v>-3.3492001192811946E-5</v>
+        <v>-3.3492001192811458E-5</v>
       </c>
       <c r="Z8">
-        <v>-3.1424693107275596E-5</v>
+        <v>-3.1424693107274458E-5</v>
       </c>
       <c r="AA8">
-        <v>-2.8725543439385242E-5</v>
+        <v>-2.872554343938432E-5</v>
       </c>
       <c r="AB8">
-        <v>1.0317200800238663E-4</v>
+        <v>1.0317200800238744E-4</v>
       </c>
       <c r="AC8">
-        <v>1.7860382209606296E-4</v>
+        <v>1.7860382209606356E-4</v>
       </c>
       <c r="AD8">
-        <v>-5.6695689615589702E-5</v>
+        <v>-5.6695689615589065E-5</v>
       </c>
       <c r="AE8">
-        <v>1.2634464412900282E-5</v>
+        <v>1.2634464412902599E-5</v>
       </c>
       <c r="AF8">
-        <v>1.8205980953951656E-5</v>
+        <v>1.8205980953952517E-5</v>
       </c>
       <c r="AG8">
-        <v>4.2619576812610648E-5</v>
+        <v>4.2619576812613034E-5</v>
       </c>
       <c r="AH8">
-        <v>2.0120935756152304E-5</v>
+        <v>2.0120935756152914E-5</v>
       </c>
       <c r="AI8">
-        <v>-7.1353744195980115E-5</v>
+        <v>-7.13537441959796E-5</v>
       </c>
       <c r="AJ8">
-        <v>4.3285807418827656E-5</v>
+        <v>4.3285807418830908E-5</v>
       </c>
       <c r="AK8">
-        <v>-6.2117200108762773E-8</v>
+        <v>-6.2117200108545933E-8</v>
       </c>
       <c r="AL8">
-        <v>-8.3063578496498942E-6</v>
+        <v>-8.3063578496506531E-6</v>
       </c>
       <c r="AM8">
-        <v>1.8376836389002288E-5</v>
+        <v>1.8376836389001638E-5</v>
       </c>
       <c r="AN8">
-        <v>-3.6023502360053232E-5</v>
+        <v>-3.6023502360054018E-5</v>
       </c>
       <c r="AO8">
-        <v>-3.3454447711108999E-4</v>
+        <v>-3.3454447711108977E-4</v>
       </c>
       <c r="AP8">
-        <v>-1.023812248388258E-5</v>
+        <v>-1.0238122483882363E-5</v>
       </c>
       <c r="AQ8">
-        <v>-1.2711840087197717E-3</v>
+        <v>-1.2711840087198127E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1815,130 +1809,130 @@
         <v>-0.16951677677070059</v>
       </c>
       <c r="C9">
-        <v>-4.4797962091598376E-5</v>
+        <v>-4.4797962091597977E-5</v>
       </c>
       <c r="D9">
-        <v>-4.9694033723346383E-6</v>
+        <v>-4.9694033723339031E-6</v>
       </c>
       <c r="E9">
-        <v>6.7832198310583502E-8</v>
+        <v>6.7832198310577413E-8</v>
       </c>
       <c r="F9">
-        <v>8.907965921434158E-4</v>
+        <v>8.9079659214342166E-4</v>
       </c>
       <c r="G9">
-        <v>8.3648800598759554E-4</v>
+        <v>8.364880059875989E-4</v>
       </c>
       <c r="H9">
-        <v>8.0966052712205046E-4</v>
+        <v>8.096605271220536E-4</v>
       </c>
       <c r="I9">
-        <v>9.1347697357601059E-4</v>
+        <v>9.134769735760146E-4</v>
       </c>
       <c r="J9">
-        <v>1.8751008815373128E-3</v>
+        <v>1.8751008815373169E-3</v>
       </c>
       <c r="K9">
-        <v>8.4846320166785043E-4</v>
+        <v>8.4846320166785498E-4</v>
       </c>
       <c r="L9">
-        <v>9.3040363847546315E-4</v>
+        <v>9.3040363847546109E-4</v>
       </c>
       <c r="M9">
-        <v>1.9985273475418445E-4</v>
+        <v>1.9985273475419258E-4</v>
       </c>
       <c r="N9">
-        <v>1.1253045278680155E-4</v>
+        <v>1.1253045278680619E-4</v>
       </c>
       <c r="O9">
-        <v>8.1175441025864599E-5</v>
+        <v>8.1175441025863217E-5</v>
       </c>
       <c r="P9">
-        <v>3.4181586790791511E-5</v>
+        <v>3.4181586790791891E-5</v>
       </c>
       <c r="Q9">
-        <v>3.7616276483109275E-5</v>
+        <v>3.7616276483110522E-5</v>
       </c>
       <c r="R9">
-        <v>-8.2603992970009953E-7</v>
+        <v>-8.2603992970004066E-7</v>
       </c>
       <c r="S9">
-        <v>-4.9531431168658191E-7</v>
+        <v>-4.953143116865152E-7</v>
       </c>
       <c r="T9">
-        <v>4.4637275949544072E-5</v>
+        <v>4.4637275949545074E-5</v>
       </c>
       <c r="U9">
-        <v>1.1229399958418317E-4</v>
+        <v>1.1229399958418665E-4</v>
       </c>
       <c r="V9">
-        <v>3.2350042465627559E-4</v>
+        <v>3.2350042465627857E-4</v>
       </c>
       <c r="W9">
-        <v>5.2318050692513256E-4</v>
+        <v>5.2318050692513418E-4</v>
       </c>
       <c r="X9">
-        <v>-1.8026290309752102E-6</v>
+        <v>-1.8026290309755795E-6</v>
       </c>
       <c r="Y9">
-        <v>-1.8136603876306901E-5</v>
+        <v>-1.8136603876306413E-5</v>
       </c>
       <c r="Z9">
-        <v>4.7306697845002186E-6</v>
+        <v>4.7306697845017365E-6</v>
       </c>
       <c r="AA9">
-        <v>-3.7007076476470589E-5</v>
+        <v>-3.700707647646918E-5</v>
       </c>
       <c r="AB9">
-        <v>6.8738675636799551E-5</v>
+        <v>6.8738675636800432E-5</v>
       </c>
       <c r="AC9">
-        <v>5.8409954117462943E-5</v>
+        <v>5.8409954117463553E-5</v>
       </c>
       <c r="AD9">
-        <v>2.8703307502328491E-5</v>
+        <v>2.8703307502329087E-5</v>
       </c>
       <c r="AE9">
-        <v>2.4856407070118303E-5</v>
+        <v>2.4856407070120417E-5</v>
       </c>
       <c r="AF9">
-        <v>3.9582490462197041E-5</v>
+        <v>3.9582490462197916E-5</v>
       </c>
       <c r="AG9">
-        <v>6.4084318226283464E-5</v>
+        <v>6.4084318226285836E-5</v>
       </c>
       <c r="AH9">
-        <v>6.5673054719547137E-5</v>
+        <v>6.567305471954776E-5</v>
       </c>
       <c r="AI9">
-        <v>-1.3120477274821793E-5</v>
+        <v>-1.3120477274821305E-5</v>
       </c>
       <c r="AJ9">
-        <v>3.0340055453893279E-5</v>
+        <v>3.034005545389626E-5</v>
       </c>
       <c r="AK9">
-        <v>-3.290881842042101E-6</v>
+        <v>-3.2908818420419655E-6</v>
       </c>
       <c r="AL9">
-        <v>5.5951372627970818E-5</v>
+        <v>5.595137262796995E-5</v>
       </c>
       <c r="AM9">
-        <v>4.6422348104346438E-5</v>
+        <v>4.6422348104345842E-5</v>
       </c>
       <c r="AN9">
-        <v>-2.0722848788845924E-4</v>
+        <v>-2.0722848788846002E-4</v>
       </c>
       <c r="AO9">
-        <v>4.1730098122317124E-5</v>
+        <v>4.1730098122317314E-5</v>
       </c>
       <c r="AP9">
-        <v>-2.7236852486551465E-5</v>
+        <v>-2.7236852486551275E-5</v>
       </c>
       <c r="AQ9">
-        <v>-8.9636741664405792E-4</v>
+        <v>-8.9636741664410194E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1946,130 +1940,130 @@
         <v>-0.23127185169099237</v>
       </c>
       <c r="C10">
-        <v>5.5210393956374733E-5</v>
+        <v>5.521039395637499E-5</v>
       </c>
       <c r="D10">
-        <v>7.7389062860290616E-6</v>
+        <v>7.7389062860289531E-6</v>
       </c>
       <c r="E10">
-        <v>-6.7412777043315261E-8</v>
+        <v>-6.7412777043313832E-8</v>
       </c>
       <c r="F10">
-        <v>8.9363118851582826E-4</v>
+        <v>8.9363118851583162E-4</v>
       </c>
       <c r="G10">
-        <v>9.0859493595949988E-4</v>
+        <v>9.0859493595950324E-4</v>
       </c>
       <c r="H10">
-        <v>7.5247791262529715E-4</v>
+        <v>7.5247791262530073E-4</v>
       </c>
       <c r="I10">
-        <v>8.4939976849165164E-4</v>
+        <v>8.4939976849165608E-4</v>
       </c>
       <c r="J10">
-        <v>8.4846320166785043E-4</v>
+        <v>8.4846320166785498E-4</v>
       </c>
       <c r="K10">
-        <v>1.0328437041269771E-3</v>
+        <v>1.0328437041269814E-3</v>
       </c>
       <c r="L10">
-        <v>9.4768211965578055E-4</v>
+        <v>9.4768211965577903E-4</v>
       </c>
       <c r="M10">
-        <v>-3.2567021250591512E-5</v>
+        <v>-3.2567021250590373E-5</v>
       </c>
       <c r="N10">
-        <v>-4.0484063828348017E-5</v>
+        <v>-4.0484063828340482E-5</v>
       </c>
       <c r="O10">
-        <v>-6.7602302385641152E-5</v>
+        <v>-6.7602302385645272E-5</v>
       </c>
       <c r="P10">
-        <v>2.4711706474931251E-5</v>
+        <v>2.4711706474932064E-5</v>
       </c>
       <c r="Q10">
-        <v>4.3474608275561482E-5</v>
+        <v>4.3474608275563163E-5</v>
       </c>
       <c r="R10">
-        <v>7.4024502984189135E-7</v>
+        <v>7.4024502984203195E-7</v>
       </c>
       <c r="S10">
-        <v>2.1282269063230908E-7</v>
+        <v>2.1282269063242215E-7</v>
       </c>
       <c r="T10">
-        <v>2.031377868285297E-5</v>
+        <v>2.0313778682854789E-5</v>
       </c>
       <c r="U10">
-        <v>5.2655564435101471E-5</v>
+        <v>5.2655564435106838E-5</v>
       </c>
       <c r="V10">
-        <v>1.6462365153520618E-4</v>
+        <v>1.6462365153521245E-4</v>
       </c>
       <c r="W10">
-        <v>3.3354089345732501E-4</v>
+        <v>3.3354089345732782E-4</v>
       </c>
       <c r="X10">
-        <v>-1.7945862808882952E-6</v>
+        <v>-1.7945862808884104E-6</v>
       </c>
       <c r="Y10">
-        <v>-3.0418846568515639E-5</v>
+        <v>-3.0418846568515422E-5</v>
       </c>
       <c r="Z10">
-        <v>4.7370994212763307E-5</v>
+        <v>4.7370994212764107E-5</v>
       </c>
       <c r="AA10">
-        <v>7.3491147857295761E-5</v>
+        <v>7.3491147857296629E-5</v>
       </c>
       <c r="AB10">
-        <v>1.0310700463884659E-4</v>
+        <v>1.0310700463884772E-4</v>
       </c>
       <c r="AC10">
-        <v>9.0925851162753765E-5</v>
+        <v>9.0925851162755296E-5</v>
       </c>
       <c r="AD10">
-        <v>6.1089026213288278E-5</v>
+        <v>6.1089026213289688E-5</v>
       </c>
       <c r="AE10">
-        <v>6.6286521729026188E-5</v>
+        <v>6.6286521729028803E-5</v>
       </c>
       <c r="AF10">
-        <v>7.1528282831583414E-5</v>
+        <v>7.1528282831584281E-5</v>
       </c>
       <c r="AG10">
-        <v>7.8113270531383227E-5</v>
+        <v>7.8113270531386859E-5</v>
       </c>
       <c r="AH10">
-        <v>1.2575875012095644E-4</v>
+        <v>1.257587501209579E-4</v>
       </c>
       <c r="AI10">
-        <v>2.226288709827314E-5</v>
+        <v>2.2262887098274163E-5</v>
       </c>
       <c r="AJ10">
-        <v>4.9603539928871746E-5</v>
+        <v>4.9603539928876354E-5</v>
       </c>
       <c r="AK10">
-        <v>9.6575497509496168E-7</v>
+        <v>9.6575497509544957E-7</v>
       </c>
       <c r="AL10">
-        <v>-2.2976444901648039E-6</v>
+        <v>-2.297644490165617E-6</v>
       </c>
       <c r="AM10">
-        <v>8.0243595814510709E-6</v>
+        <v>8.0243595814496072E-6</v>
       </c>
       <c r="AN10">
-        <v>4.4279381699769408E-5</v>
+        <v>4.4279381699768459E-5</v>
       </c>
       <c r="AO10">
-        <v>2.888690178773221E-5</v>
+        <v>2.8886901787732752E-5</v>
       </c>
       <c r="AP10">
-        <v>-3.9268400613410898E-5</v>
+        <v>-3.9268400613410844E-5</v>
       </c>
       <c r="AQ10">
-        <v>-1.3079474208521477E-3</v>
+        <v>-1.3079474208521902E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -2077,130 +2071,130 @@
         <v>-0.31097216190126653</v>
       </c>
       <c r="C11">
-        <v>1.4023728334026971E-4</v>
+        <v>1.4023728334026914E-4</v>
       </c>
       <c r="D11">
-        <v>4.9873168394488625E-7</v>
+        <v>4.9873168394480547E-7</v>
       </c>
       <c r="E11">
-        <v>2.6617813063754605E-8</v>
+        <v>2.6617813063754672E-8</v>
       </c>
       <c r="F11">
-        <v>9.2893922120956059E-4</v>
+        <v>9.2893922120955853E-4</v>
       </c>
       <c r="G11">
-        <v>8.6715963143938716E-4</v>
+        <v>8.6715963143938618E-4</v>
       </c>
       <c r="H11">
-        <v>7.6751238638530107E-4</v>
+        <v>7.6751238638529977E-4</v>
       </c>
       <c r="I11">
-        <v>9.2260799600029481E-4</v>
+        <v>9.2260799600029318E-4</v>
       </c>
       <c r="J11">
-        <v>9.3040363847546315E-4</v>
+        <v>9.3040363847546109E-4</v>
       </c>
       <c r="K11">
-        <v>9.4768211965578055E-4</v>
+        <v>9.4768211965577903E-4</v>
       </c>
       <c r="L11">
-        <v>1.9877537839606816E-3</v>
+        <v>1.987753783960679E-3</v>
       </c>
       <c r="M11">
-        <v>1.8763115494407028E-4</v>
+        <v>1.8763115494407911E-4</v>
       </c>
       <c r="N11">
-        <v>6.3389990730463935E-5</v>
+        <v>6.3389990730470928E-5</v>
       </c>
       <c r="O11">
-        <v>1.1420923373704514E-4</v>
+        <v>1.1420923373704357E-4</v>
       </c>
       <c r="P11">
-        <v>-1.0134571477975532E-5</v>
+        <v>-1.0134571477974936E-5</v>
       </c>
       <c r="Q11">
-        <v>1.6478273802558209E-5</v>
+        <v>1.6478273802559618E-5</v>
       </c>
       <c r="R11">
-        <v>9.3230697697240341E-12</v>
+        <v>9.3230698612035924E-12</v>
       </c>
       <c r="S11">
-        <v>2.7920041098774568E-7</v>
+        <v>2.7920041098783123E-7</v>
       </c>
       <c r="T11">
-        <v>7.6756881094065108E-5</v>
+        <v>7.6756881094066178E-5</v>
       </c>
       <c r="U11">
-        <v>2.4206490012415949E-4</v>
+        <v>2.4206490012416434E-4</v>
       </c>
       <c r="V11">
-        <v>3.7949607995923314E-4</v>
+        <v>3.7949607995923796E-4</v>
       </c>
       <c r="W11">
-        <v>5.8351952611375587E-4</v>
+        <v>5.8351952611375793E-4</v>
       </c>
       <c r="X11">
-        <v>-2.1965468206758998E-5</v>
+        <v>-2.1965468206759297E-5</v>
       </c>
       <c r="Y11">
-        <v>1.4747985826144201E-5</v>
+        <v>1.474798582614458E-5</v>
       </c>
       <c r="Z11">
-        <v>2.0324370487780771E-5</v>
+        <v>2.0324370487782276E-5</v>
       </c>
       <c r="AA11">
-        <v>2.4743376151655427E-5</v>
+        <v>2.4743376151656728E-5</v>
       </c>
       <c r="AB11">
-        <v>4.1177353497015543E-5</v>
+        <v>4.1177353497016356E-5</v>
       </c>
       <c r="AC11">
-        <v>1.0117371643853877E-4</v>
+        <v>1.0117371643853889E-4</v>
       </c>
       <c r="AD11">
-        <v>-2.0070685526101992E-6</v>
+        <v>-2.0070685526090337E-6</v>
       </c>
       <c r="AE11">
-        <v>8.1815627285201594E-5</v>
+        <v>8.1815627285204007E-5</v>
       </c>
       <c r="AF11">
-        <v>3.9811978649014707E-5</v>
+        <v>3.9811978649015683E-5</v>
       </c>
       <c r="AG11">
-        <v>3.3611327592697259E-5</v>
+        <v>3.3611327592700268E-5</v>
       </c>
       <c r="AH11">
-        <v>8.1296279798946804E-5</v>
+        <v>8.1296279798947428E-5</v>
       </c>
       <c r="AI11">
-        <v>-2.4066676115797527E-5</v>
+        <v>-2.4066676115796985E-5</v>
       </c>
       <c r="AJ11">
-        <v>1.1916052073412801E-5</v>
+        <v>1.191605207341665E-5</v>
       </c>
       <c r="AK11">
-        <v>2.416064052237891E-6</v>
+        <v>2.4160640522381349E-6</v>
       </c>
       <c r="AL11">
-        <v>3.506460102106171E-5</v>
+        <v>3.5064601021060789E-5</v>
       </c>
       <c r="AM11">
-        <v>2.5405246892679036E-5</v>
+        <v>2.5405246892678114E-5</v>
       </c>
       <c r="AN11">
-        <v>-8.5454281862488426E-5</v>
+        <v>-8.5454281862489537E-5</v>
       </c>
       <c r="AO11">
-        <v>-1.2942189627549654E-4</v>
+        <v>-1.2942189627549643E-4</v>
       </c>
       <c r="AP11">
-        <v>-1.2099708312511207E-4</v>
+        <v>-1.2099708312511239E-4</v>
       </c>
       <c r="AQ11">
-        <v>-1.4141511358084448E-3</v>
+        <v>-1.414151135808499E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2208,130 +2202,130 @@
         <v>8.2285815045357424E-2</v>
       </c>
       <c r="C12">
-        <v>5.1447425980216355E-6</v>
+        <v>5.1447425980230213E-6</v>
       </c>
       <c r="D12">
-        <v>3.470209969312979E-5</v>
+        <v>3.4702099693127012E-5</v>
       </c>
       <c r="E12">
-        <v>-2.3131242938586972E-7</v>
+        <v>-2.3131242938584193E-7</v>
       </c>
       <c r="F12">
-        <v>-1.0359063805551346E-4</v>
+        <v>-1.035906380555159E-4</v>
       </c>
       <c r="G12">
-        <v>-7.8109208978108507E-5</v>
+        <v>-7.8109208978104007E-5</v>
       </c>
       <c r="H12">
-        <v>1.2757067527436217E-4</v>
+        <v>1.2757067527436784E-4</v>
       </c>
       <c r="I12">
-        <v>1.9947495953087608E-4</v>
+        <v>1.9947495953088402E-4</v>
       </c>
       <c r="J12">
-        <v>1.9985273475418445E-4</v>
+        <v>1.9985273475419258E-4</v>
       </c>
       <c r="K12">
-        <v>-3.2567021250591512E-5</v>
+        <v>-3.2567021250590373E-5</v>
       </c>
       <c r="L12">
-        <v>1.8763115494407028E-4</v>
+        <v>1.8763115494407911E-4</v>
       </c>
       <c r="M12">
-        <v>2.3822979943480863E-3</v>
+        <v>2.3822979943480785E-3</v>
       </c>
       <c r="N12">
-        <v>9.1770972196944566E-4</v>
+        <v>9.1770972196945791E-4</v>
       </c>
       <c r="O12">
-        <v>5.822109740119387E-4</v>
+        <v>5.8221097401193545E-4</v>
       </c>
       <c r="P12">
-        <v>-9.5758626674469736E-6</v>
+        <v>-9.5758626674468652E-6</v>
       </c>
       <c r="Q12">
-        <v>4.4960659175164353E-5</v>
+        <v>4.4960659175164244E-5</v>
       </c>
       <c r="R12">
-        <v>-1.3333294103259368E-6</v>
+        <v>-1.3333294103256606E-6</v>
       </c>
       <c r="S12">
-        <v>1.0176437447734127E-6</v>
+        <v>1.0176437447734441E-6</v>
       </c>
       <c r="T12">
-        <v>5.9888275028258705E-4</v>
+        <v>5.9888275028258879E-4</v>
       </c>
       <c r="U12">
-        <v>9.4422754944994101E-4</v>
+        <v>9.442275494499486E-4</v>
       </c>
       <c r="V12">
-        <v>9.8266822688254847E-4</v>
+        <v>9.8266822688255844E-4</v>
       </c>
       <c r="W12">
-        <v>9.6845664510417659E-4</v>
+        <v>9.6845664510417898E-4</v>
       </c>
       <c r="X12">
-        <v>-6.2278906244901268E-5</v>
+        <v>-6.2278906244900794E-5</v>
       </c>
       <c r="Y12">
-        <v>-1.0231541598829856E-4</v>
+        <v>-1.0231541598829889E-4</v>
       </c>
       <c r="Z12">
-        <v>-4.8978046632238521E-5</v>
+        <v>-4.8978046632240364E-5</v>
       </c>
       <c r="AA12">
-        <v>-1.1098295168370919E-4</v>
+        <v>-1.1098295168371038E-4</v>
       </c>
       <c r="AB12">
-        <v>-6.9205814836941355E-5</v>
+        <v>-6.9205814836940461E-5</v>
       </c>
       <c r="AC12">
-        <v>-4.8256077991982637E-5</v>
+        <v>-4.8256077991980374E-5</v>
       </c>
       <c r="AD12">
-        <v>-5.2392372042240828E-5</v>
+        <v>-5.2392372042239473E-5</v>
       </c>
       <c r="AE12">
-        <v>-7.5121324619838891E-5</v>
+        <v>-7.5121324619836506E-5</v>
       </c>
       <c r="AF12">
-        <v>-9.3145208914089102E-5</v>
+        <v>-9.3145208914088926E-5</v>
       </c>
       <c r="AG12">
-        <v>-7.7223843157840763E-5</v>
+        <v>-7.7223843157837673E-5</v>
       </c>
       <c r="AH12">
-        <v>-3.238662415237098E-5</v>
+        <v>-3.2386624152369137E-5</v>
       </c>
       <c r="AI12">
-        <v>-1.1727002339032079E-4</v>
+        <v>-1.1727002339032006E-4</v>
       </c>
       <c r="AJ12">
-        <v>-4.4754407273305073E-5</v>
+        <v>-4.4754407273300953E-5</v>
       </c>
       <c r="AK12">
-        <v>-4.9393925643333636E-6</v>
+        <v>-4.9393925643324691E-6</v>
       </c>
       <c r="AL12">
-        <v>4.5142387333384952E-6</v>
+        <v>4.5142387333377363E-6</v>
       </c>
       <c r="AM12">
-        <v>3.0585834488925626E-5</v>
+        <v>3.0585834488922698E-5</v>
       </c>
       <c r="AN12">
-        <v>-3.2006034234519082E-4</v>
+        <v>-3.200603423451919E-4</v>
       </c>
       <c r="AO12">
-        <v>-1.7228259834017846E-4</v>
+        <v>-1.722825983401787E-4</v>
       </c>
       <c r="AP12">
-        <v>8.6181194343179035E-5</v>
+        <v>8.6181194343178005E-5</v>
       </c>
       <c r="AQ12">
-        <v>-1.8426557074204064E-3</v>
+        <v>-1.8426557074204353E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -2339,130 +2333,130 @@
         <v>-9.768703336053669E-2</v>
       </c>
       <c r="C13">
-        <v>-3.0141657115765127E-5</v>
+        <v>-3.0141657115764432E-5</v>
       </c>
       <c r="D13">
-        <v>-1.8902290535966368E-6</v>
+        <v>-1.8902290535952477E-6</v>
       </c>
       <c r="E13">
-        <v>5.4814708542981449E-8</v>
+        <v>5.4814708542968638E-8</v>
       </c>
       <c r="F13">
-        <v>-3.7113780297914304E-5</v>
+        <v>-3.7113780297906389E-5</v>
       </c>
       <c r="G13">
-        <v>-1.1106778717279641E-4</v>
+        <v>-1.1106778717279267E-4</v>
       </c>
       <c r="H13">
-        <v>6.6965069705780177E-5</v>
+        <v>6.6965069705783809E-5</v>
       </c>
       <c r="I13">
-        <v>9.1114879777542506E-5</v>
+        <v>9.1114879777547141E-5</v>
       </c>
       <c r="J13">
-        <v>1.1253045278680155E-4</v>
+        <v>1.1253045278680619E-4</v>
       </c>
       <c r="K13">
-        <v>-4.0484063828348017E-5</v>
+        <v>-4.0484063828340482E-5</v>
       </c>
       <c r="L13">
-        <v>6.3389990730463935E-5</v>
+        <v>6.3389990730470928E-5</v>
       </c>
       <c r="M13">
-        <v>9.1770972196944566E-4</v>
+        <v>9.1770972196945791E-4</v>
       </c>
       <c r="N13">
-        <v>1.5646532966439967E-3</v>
+        <v>1.5646532966440056E-3</v>
       </c>
       <c r="O13">
-        <v>8.3603633536570023E-4</v>
+        <v>8.3603633536570251E-4</v>
       </c>
       <c r="P13">
-        <v>1.0314560732841327E-5</v>
+        <v>1.0314560732840948E-5</v>
       </c>
       <c r="Q13">
-        <v>4.0662954753325293E-5</v>
+        <v>4.0662954753325077E-5</v>
       </c>
       <c r="R13">
-        <v>2.7047131822862348E-6</v>
+        <v>2.7047131822863889E-6</v>
       </c>
       <c r="S13">
-        <v>4.0961622585628593E-6</v>
+        <v>4.0961622585628186E-6</v>
       </c>
       <c r="T13">
-        <v>8.3077080486111438E-4</v>
+        <v>8.3077080486111546E-4</v>
       </c>
       <c r="U13">
-        <v>1.1656223889178912E-3</v>
+        <v>1.1656223889178969E-3</v>
       </c>
       <c r="V13">
-        <v>1.2460425326496964E-3</v>
+        <v>1.2460425326497018E-3</v>
       </c>
       <c r="W13">
-        <v>1.247342522928933E-3</v>
+        <v>1.2473425229289343E-3</v>
       </c>
       <c r="X13">
-        <v>-7.8598479677458028E-5</v>
+        <v>-7.8598479677458082E-5</v>
       </c>
       <c r="Y13">
-        <v>-1.5617117774558114E-5</v>
+        <v>-1.5617117774557681E-5</v>
       </c>
       <c r="Z13">
-        <v>-3.2564882355588126E-5</v>
+        <v>-3.2564882355588044E-5</v>
       </c>
       <c r="AA13">
-        <v>-1.487695871176641E-4</v>
+        <v>-1.4876958711766323E-4</v>
       </c>
       <c r="AB13">
-        <v>-2.8052432512672319E-5</v>
+        <v>-2.805243251267219E-5</v>
       </c>
       <c r="AC13">
-        <v>-5.0129465975949538E-5</v>
+        <v>-5.0129465975949593E-5</v>
       </c>
       <c r="AD13">
-        <v>1.665977496860565E-5</v>
+        <v>1.6659774968606788E-5</v>
       </c>
       <c r="AE13">
-        <v>-6.4531435307838898E-5</v>
+        <v>-6.4531435307836756E-5</v>
       </c>
       <c r="AF13">
-        <v>-4.7992317119584821E-5</v>
+        <v>-4.799231711958478E-5</v>
       </c>
       <c r="AG13">
-        <v>-4.6559863675810631E-5</v>
+        <v>-4.655986367580893E-5</v>
       </c>
       <c r="AH13">
-        <v>-5.0729066942762838E-5</v>
+        <v>-5.0729066942761998E-5</v>
       </c>
       <c r="AI13">
-        <v>-7.1832354904920583E-5</v>
+        <v>-7.1832354904920827E-5</v>
       </c>
       <c r="AJ13">
-        <v>-6.818365065441661E-5</v>
+        <v>-6.8183650654414442E-5</v>
       </c>
       <c r="AK13">
-        <v>-6.6941176230893155E-6</v>
+        <v>-6.6941176230890715E-6</v>
       </c>
       <c r="AL13">
-        <v>3.9497308044425788E-5</v>
+        <v>3.9497308044424595E-5</v>
       </c>
       <c r="AM13">
-        <v>4.076369953180854E-5</v>
+        <v>4.076369953180751E-5</v>
       </c>
       <c r="AN13">
-        <v>-2.3554541100202246E-4</v>
+        <v>-2.3554541100202344E-4</v>
       </c>
       <c r="AO13">
-        <v>-1.1478379244263866E-4</v>
+        <v>-1.1478379244263959E-4</v>
       </c>
       <c r="AP13">
-        <v>7.5340316913247781E-5</v>
+        <v>7.5340316913246697E-5</v>
       </c>
       <c r="AQ13">
-        <v>-1.41573054798117E-3</v>
+        <v>-1.4157305479812121E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2470,130 +2464,130 @@
         <v>7.638794242542879E-2</v>
       </c>
       <c r="C14">
-        <v>-2.0112437652260877E-5</v>
+        <v>-2.0112437652261216E-5</v>
       </c>
       <c r="D14">
-        <v>1.0099838873522417E-5</v>
+        <v>1.0099838873521611E-5</v>
       </c>
       <c r="E14">
-        <v>-1.952651274976213E-7</v>
+        <v>-1.9526512749761413E-7</v>
       </c>
       <c r="F14">
-        <v>-6.8557040865207608E-5</v>
+        <v>-6.855704086521265E-5</v>
       </c>
       <c r="G14">
-        <v>-1.1370285343764226E-4</v>
+        <v>-1.1370285343764578E-4</v>
       </c>
       <c r="H14">
-        <v>-3.3086822578122873E-5</v>
+        <v>-3.3086822578124825E-5</v>
       </c>
       <c r="I14">
-        <v>-2.325389302355917E-5</v>
+        <v>-2.3253893023560362E-5</v>
       </c>
       <c r="J14">
-        <v>8.1175441025864599E-5</v>
+        <v>8.1175441025863217E-5</v>
       </c>
       <c r="K14">
-        <v>-6.7602302385641152E-5</v>
+        <v>-6.7602302385645272E-5</v>
       </c>
       <c r="L14">
-        <v>1.1420923373704514E-4</v>
+        <v>1.1420923373704357E-4</v>
       </c>
       <c r="M14">
-        <v>5.822109740119387E-4</v>
+        <v>5.8221097401193545E-4</v>
       </c>
       <c r="N14">
-        <v>8.3603633536570023E-4</v>
+        <v>8.3603633536570251E-4</v>
       </c>
       <c r="O14">
-        <v>1.3644894791165489E-3</v>
+        <v>1.3644894791165498E-3</v>
       </c>
       <c r="P14">
-        <v>4.1693150565471151E-5</v>
+        <v>4.1693150565471422E-5</v>
       </c>
       <c r="Q14">
-        <v>6.1624677791175377E-5</v>
+        <v>6.1624677791174401E-5</v>
       </c>
       <c r="R14">
-        <v>-5.8963946480637986E-7</v>
+        <v>-5.8963946480609949E-7</v>
       </c>
       <c r="S14">
-        <v>1.8661925277529087E-6</v>
+        <v>1.8661925277529188E-6</v>
       </c>
       <c r="T14">
-        <v>5.6222486849111242E-4</v>
+        <v>5.6222486849111534E-4</v>
       </c>
       <c r="U14">
-        <v>8.4768197367473728E-4</v>
+        <v>8.4768197367474335E-4</v>
       </c>
       <c r="V14">
-        <v>9.7195264892662976E-4</v>
+        <v>9.7195264892663551E-4</v>
       </c>
       <c r="W14">
-        <v>1.0097894482138943E-3</v>
+        <v>1.0097894482138973E-3</v>
       </c>
       <c r="X14">
-        <v>-8.6699607570422092E-5</v>
+        <v>-8.6699607570421983E-5</v>
       </c>
       <c r="Y14">
-        <v>1.0600849929859335E-5</v>
+        <v>1.0600849929859226E-5</v>
       </c>
       <c r="Z14">
-        <v>-7.9314437795450669E-5</v>
+        <v>-7.9314437795451807E-5</v>
       </c>
       <c r="AA14">
-        <v>-1.4020124075363747E-4</v>
+        <v>-1.4020124075363698E-4</v>
       </c>
       <c r="AB14">
-        <v>-6.3122869523632265E-5</v>
+        <v>-6.3122869523631005E-5</v>
       </c>
       <c r="AC14">
-        <v>-3.6227492135023581E-5</v>
+        <v>-3.6227492135020497E-5</v>
       </c>
       <c r="AD14">
-        <v>-3.9881871100633758E-5</v>
+        <v>-3.9881871100631914E-5</v>
       </c>
       <c r="AE14">
-        <v>-7.5098127813274834E-5</v>
+        <v>-7.5098127813273615E-5</v>
       </c>
       <c r="AF14">
-        <v>-4.5983987193006496E-5</v>
+        <v>-4.5983987193006388E-5</v>
       </c>
       <c r="AG14">
-        <v>-3.1009572311479485E-5</v>
+        <v>-3.1009572311476883E-5</v>
       </c>
       <c r="AH14">
-        <v>-4.7042669894432096E-5</v>
+        <v>-4.7042669894429304E-5</v>
       </c>
       <c r="AI14">
-        <v>-1.0074407885215658E-4</v>
+        <v>-1.0074407885215577E-4</v>
       </c>
       <c r="AJ14">
-        <v>-4.9305930858369203E-5</v>
+        <v>-4.9305930858366547E-5</v>
       </c>
       <c r="AK14">
-        <v>-6.7303345985180395E-7</v>
+        <v>-6.730334598509908E-7</v>
       </c>
       <c r="AL14">
-        <v>-4.5536945392407038E-6</v>
+        <v>-4.5536945392413001E-6</v>
       </c>
       <c r="AM14">
-        <v>3.7495458104732553E-7</v>
+        <v>3.7495458104542818E-7</v>
       </c>
       <c r="AN14">
-        <v>-2.0511023347054844E-4</v>
+        <v>-2.0511023347054877E-4</v>
       </c>
       <c r="AO14">
-        <v>3.154656412322418E-5</v>
+        <v>3.1546564123223963E-5</v>
       </c>
       <c r="AP14">
-        <v>-5.5606349597319988E-5</v>
+        <v>-5.5606349597320476E-5</v>
       </c>
       <c r="AQ14">
-        <v>-9.3187609190674295E-4</v>
+        <v>-9.3187609190677895E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2601,130 +2595,130 @@
         <v>-0.16018735542740917</v>
       </c>
       <c r="C15">
-        <v>-2.2499293713270261E-5</v>
+        <v>-2.2499293713269813E-5</v>
       </c>
       <c r="D15">
-        <v>8.0220833846362442E-7</v>
+        <v>8.0220833846373284E-7</v>
       </c>
       <c r="E15">
-        <v>-1.3109522906017836E-8</v>
+        <v>-1.3109522906018683E-8</v>
       </c>
       <c r="F15">
-        <v>1.9057456995744067E-4</v>
+        <v>1.9057456995744126E-4</v>
       </c>
       <c r="G15">
-        <v>2.0876707732625619E-5</v>
+        <v>2.0876707732626106E-5</v>
       </c>
       <c r="H15">
-        <v>-5.3737705446191091E-6</v>
+        <v>-5.3737705446185941E-6</v>
       </c>
       <c r="I15">
-        <v>1.0007799831811463E-4</v>
+        <v>1.000779983181152E-4</v>
       </c>
       <c r="J15">
-        <v>3.4181586790791511E-5</v>
+        <v>3.4181586790791891E-5</v>
       </c>
       <c r="K15">
-        <v>2.4711706474931251E-5</v>
+        <v>2.4711706474932064E-5</v>
       </c>
       <c r="L15">
-        <v>-1.0134571477975532E-5</v>
+        <v>-1.0134571477974936E-5</v>
       </c>
       <c r="M15">
-        <v>-9.5758626674469736E-6</v>
+        <v>-9.5758626674468652E-6</v>
       </c>
       <c r="N15">
-        <v>1.0314560732841327E-5</v>
+        <v>1.0314560732840948E-5</v>
       </c>
       <c r="O15">
-        <v>4.1693150565471151E-5</v>
+        <v>4.1693150565471422E-5</v>
       </c>
       <c r="P15">
-        <v>4.5474023274856101E-4</v>
+        <v>4.5474023274856117E-4</v>
       </c>
       <c r="Q15">
-        <v>3.560848839786289E-4</v>
+        <v>3.560848839786288E-4</v>
       </c>
       <c r="R15">
-        <v>1.9426397832773269E-8</v>
+        <v>1.9426397832806727E-8</v>
       </c>
       <c r="S15">
-        <v>5.340121189455809E-7</v>
+        <v>5.3401211894557328E-7</v>
       </c>
       <c r="T15">
-        <v>2.0795092029448959E-5</v>
+        <v>2.0795092029449142E-5</v>
       </c>
       <c r="U15">
-        <v>1.5486651373896187E-5</v>
+        <v>1.5486651373897054E-5</v>
       </c>
       <c r="V15">
-        <v>8.2849316112058424E-5</v>
+        <v>8.2849316112058465E-5</v>
       </c>
       <c r="W15">
-        <v>1.4894397473712295E-4</v>
+        <v>1.4894397473712279E-4</v>
       </c>
       <c r="X15">
-        <v>1.0949355150664113E-6</v>
+        <v>1.094935515066396E-6</v>
       </c>
       <c r="Y15">
-        <v>-5.8245829301121707E-6</v>
+        <v>-5.8245829301120894E-6</v>
       </c>
       <c r="Z15">
-        <v>-3.1175427167072878E-5</v>
+        <v>-3.1175427167073177E-5</v>
       </c>
       <c r="AA15">
-        <v>-3.7262553226173311E-5</v>
+        <v>-3.7262553226173067E-5</v>
       </c>
       <c r="AB15">
-        <v>-2.2876754188527269E-5</v>
+        <v>-2.2876754188527154E-5</v>
       </c>
       <c r="AC15">
-        <v>-5.0072296371223493E-5</v>
+        <v>-5.0072296371223039E-5</v>
       </c>
       <c r="AD15">
-        <v>-3.4080668034028742E-5</v>
+        <v>-3.4080668034028701E-5</v>
       </c>
       <c r="AE15">
-        <v>-4.6758089173920948E-5</v>
+        <v>-4.6758089173920278E-5</v>
       </c>
       <c r="AF15">
-        <v>-2.8765651174544882E-5</v>
+        <v>-2.8765651174544523E-5</v>
       </c>
       <c r="AG15">
-        <v>-3.3154601384905038E-5</v>
+        <v>-3.315460138490455E-5</v>
       </c>
       <c r="AH15">
-        <v>-7.2744924350735894E-5</v>
+        <v>-7.2744924350735704E-5</v>
       </c>
       <c r="AI15">
-        <v>-5.1069377647702127E-5</v>
+        <v>-5.1069377647701991E-5</v>
       </c>
       <c r="AJ15">
-        <v>-1.0949375670774226E-5</v>
+        <v>-1.0949375670773792E-5</v>
       </c>
       <c r="AK15">
-        <v>-3.3912605620624949E-7</v>
+        <v>-3.3912605620616139E-7</v>
       </c>
       <c r="AL15">
-        <v>-2.2546113393745793E-5</v>
+        <v>-2.2546113393746064E-5</v>
       </c>
       <c r="AM15">
-        <v>3.2506559709382198E-5</v>
+        <v>3.2506559709381887E-5</v>
       </c>
       <c r="AN15">
-        <v>1.1901767475533623E-4</v>
+        <v>1.1901767475533589E-4</v>
       </c>
       <c r="AO15">
-        <v>-5.8690351177264056E-5</v>
+        <v>-5.869035117726453E-5</v>
       </c>
       <c r="AP15">
-        <v>4.6271565935284101E-5</v>
+        <v>4.6271565935284006E-5</v>
       </c>
       <c r="AQ15">
-        <v>-3.9554637457495627E-4</v>
+        <v>-3.9554637457496435E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2732,127 +2726,127 @@
         <v>-0.29036718320850879</v>
       </c>
       <c r="C16">
-        <v>-2.2586808177342496E-5</v>
+        <v>-2.2586808177342252E-5</v>
       </c>
       <c r="D16">
         <v>2.1282685206250372E-6</v>
       </c>
       <c r="E16">
-        <v>-6.277204478045878E-8</v>
+        <v>-6.2772044780458462E-8</v>
       </c>
       <c r="F16">
-        <v>1.7051250024409912E-4</v>
+        <v>1.7051250024409999E-4</v>
       </c>
       <c r="G16">
-        <v>2.5985018000353286E-5</v>
+        <v>2.5985018000354424E-5</v>
       </c>
       <c r="H16">
-        <v>1.5761996969566731E-5</v>
+        <v>1.5761996969567869E-5</v>
       </c>
       <c r="I16">
-        <v>1.0578522504095744E-4</v>
+        <v>1.0578522504095869E-4</v>
       </c>
       <c r="J16">
-        <v>3.7616276483109275E-5</v>
+        <v>3.7616276483110522E-5</v>
       </c>
       <c r="K16">
-        <v>4.3474608275561482E-5</v>
+        <v>4.3474608275563163E-5</v>
       </c>
       <c r="L16">
-        <v>1.6478273802558209E-5</v>
+        <v>1.6478273802559618E-5</v>
       </c>
       <c r="M16">
-        <v>4.4960659175164353E-5</v>
+        <v>4.4960659175164244E-5</v>
       </c>
       <c r="N16">
-        <v>4.0662954753325293E-5</v>
+        <v>4.0662954753325077E-5</v>
       </c>
       <c r="O16">
-        <v>6.1624677791175377E-5</v>
+        <v>6.1624677791174401E-5</v>
       </c>
       <c r="P16">
-        <v>3.560848839786289E-4</v>
+        <v>3.560848839786288E-4</v>
       </c>
       <c r="Q16">
-        <v>6.3917201808539681E-4</v>
+        <v>6.3917201808539649E-4</v>
       </c>
       <c r="R16">
-        <v>2.4947026978050173E-7</v>
+        <v>2.49470269780557E-7</v>
       </c>
       <c r="S16">
-        <v>1.5835452301698131E-6</v>
+        <v>1.5835452301698169E-6</v>
       </c>
       <c r="T16">
-        <v>6.482276032215102E-5</v>
+        <v>6.4822760322151928E-5</v>
       </c>
       <c r="U16">
-        <v>1.0771820110734801E-4</v>
+        <v>1.0771820110734944E-4</v>
       </c>
       <c r="V16">
-        <v>1.6181146352520478E-4</v>
+        <v>1.6181146352520502E-4</v>
       </c>
       <c r="W16">
         <v>2.6017211800716147E-4</v>
       </c>
       <c r="X16">
-        <v>6.2610150065106485E-6</v>
+        <v>6.2610150065105977E-6</v>
       </c>
       <c r="Y16">
-        <v>1.9898933301434337E-5</v>
+        <v>1.9898933301434418E-5</v>
       </c>
       <c r="Z16">
-        <v>-7.5816050341255911E-6</v>
+        <v>-7.5816050341258079E-6</v>
       </c>
       <c r="AA16">
-        <v>-3.6685283273134935E-5</v>
+        <v>-3.6685283273134189E-5</v>
       </c>
       <c r="AB16">
-        <v>-3.8715299044301533E-5</v>
+        <v>-3.8715299044301133E-5</v>
       </c>
       <c r="AC16">
-        <v>-6.509150997918161E-5</v>
+        <v>-6.5091509979180756E-5</v>
       </c>
       <c r="AD16">
-        <v>-6.868166203677031E-6</v>
+        <v>-6.8681662036768412E-6</v>
       </c>
       <c r="AE16">
-        <v>-3.7631187956116328E-5</v>
+        <v>-3.7631187956115223E-5</v>
       </c>
       <c r="AF16">
-        <v>-2.2762734449607715E-5</v>
+        <v>-2.2762734449607295E-5</v>
       </c>
       <c r="AG16">
-        <v>-1.4122926656044935E-5</v>
+        <v>-1.4122926656044249E-5</v>
       </c>
       <c r="AH16">
-        <v>-5.8817254954288322E-5</v>
+        <v>-5.8817254954287726E-5</v>
       </c>
       <c r="AI16">
-        <v>-3.8382906244001269E-5</v>
+        <v>-3.838290624400074E-5</v>
       </c>
       <c r="AJ16">
-        <v>-3.0873430161111945E-5</v>
+        <v>-3.0873430161111322E-5</v>
       </c>
       <c r="AK16">
-        <v>3.7534158956150756E-6</v>
+        <v>3.7534158956152518E-6</v>
       </c>
       <c r="AL16">
-        <v>-2.8223201037218791E-5</v>
+        <v>-2.822320103721917E-5</v>
       </c>
       <c r="AM16">
-        <v>3.7413788626726831E-5</v>
+        <v>3.7413788626726276E-5</v>
       </c>
       <c r="AN16">
-        <v>5.7451431620964639E-5</v>
+        <v>5.7451431620964382E-5</v>
       </c>
       <c r="AO16">
-        <v>-1.2516515398242815E-6</v>
+        <v>-1.2516515398247423E-6</v>
       </c>
       <c r="AP16">
-        <v>7.2041057755371188E-5</v>
+        <v>7.2041057755371378E-5</v>
       </c>
       <c r="AQ16">
-        <v>-5.8441870859435492E-4</v>
+        <v>-5.844187085943701E-4</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.2">
@@ -2863,127 +2857,127 @@
         <v>3.3896248744885579E-3</v>
       </c>
       <c r="C17">
-        <v>-2.1314131056072083E-6</v>
+        <v>-2.1314131056072062E-6</v>
       </c>
       <c r="D17">
-        <v>8.0256914007371868E-8</v>
+        <v>8.0256914007411466E-8</v>
       </c>
       <c r="E17">
-        <v>-1.4423251762424175E-9</v>
+        <v>-1.4423251762428079E-9</v>
       </c>
       <c r="F17">
-        <v>3.0734449677816423E-6</v>
+        <v>3.0734449677817973E-6</v>
       </c>
       <c r="G17">
-        <v>-6.2137180231451083E-7</v>
+        <v>-6.2137180231444307E-7</v>
       </c>
       <c r="H17">
-        <v>-1.161153565455648E-6</v>
+        <v>-1.1611535654556061E-6</v>
       </c>
       <c r="I17">
-        <v>1.5461417812719452E-6</v>
+        <v>1.5461417812720125E-6</v>
       </c>
       <c r="J17">
-        <v>-8.2603992970009953E-7</v>
+        <v>-8.2603992970004066E-7</v>
       </c>
       <c r="K17">
-        <v>7.4024502984189135E-7</v>
+        <v>7.4024502984203195E-7</v>
       </c>
       <c r="L17">
-        <v>9.3230697697240341E-12</v>
+        <v>9.3230698612035924E-12</v>
       </c>
       <c r="M17">
-        <v>-1.3333294103259368E-6</v>
+        <v>-1.3333294103256606E-6</v>
       </c>
       <c r="N17">
-        <v>2.7047131822862348E-6</v>
+        <v>2.7047131822863889E-6</v>
       </c>
       <c r="O17">
-        <v>-5.8963946480637986E-7</v>
+        <v>-5.8963946480609949E-7</v>
       </c>
       <c r="P17">
-        <v>1.9426397832773269E-8</v>
+        <v>1.9426397832806727E-8</v>
       </c>
       <c r="Q17">
-        <v>2.4947026978050173E-7</v>
+        <v>2.49470269780557E-7</v>
       </c>
       <c r="R17">
-        <v>6.9141493532443408E-7</v>
+        <v>6.9141493532443768E-7</v>
       </c>
       <c r="S17">
-        <v>8.0230964082090225E-10</v>
+        <v>8.0230964082521683E-10</v>
       </c>
       <c r="T17">
-        <v>-5.5556404205093615E-7</v>
+        <v>-5.555640420507858E-7</v>
       </c>
       <c r="U17">
-        <v>-1.3447481638493957E-6</v>
+        <v>-1.3447481638492051E-6</v>
       </c>
       <c r="V17">
-        <v>-1.7722475576095535E-6</v>
+        <v>-1.7722475576093131E-6</v>
       </c>
       <c r="W17">
-        <v>-2.2866867654687182E-6</v>
+        <v>-2.2866867654685793E-6</v>
       </c>
       <c r="X17">
-        <v>8.8985406800937536E-8</v>
+        <v>8.8985406800946218E-8</v>
       </c>
       <c r="Y17">
-        <v>-4.3443997023015957E-7</v>
+        <v>-4.3443997023016634E-7</v>
       </c>
       <c r="Z17">
-        <v>1.6770348741398323E-6</v>
+        <v>1.6770348741398243E-6</v>
       </c>
       <c r="AA17">
-        <v>1.8694535527795944E-6</v>
+        <v>1.8694535527796605E-6</v>
       </c>
       <c r="AB17">
-        <v>1.8537091297097752E-6</v>
+        <v>1.8537091297097828E-6</v>
       </c>
       <c r="AC17">
-        <v>9.5667861141264576E-7</v>
+        <v>9.5667861141266355E-7</v>
       </c>
       <c r="AD17">
-        <v>2.3295339590020807E-6</v>
+        <v>2.3295339590021383E-6</v>
       </c>
       <c r="AE17">
-        <v>1.861160247108241E-6</v>
+        <v>1.8611602471083274E-6</v>
       </c>
       <c r="AF17">
-        <v>1.6305010205535002E-6</v>
+        <v>1.6305010205535036E-6</v>
       </c>
       <c r="AG17">
-        <v>4.5757298848168299E-7</v>
+        <v>4.5757298848173339E-7</v>
       </c>
       <c r="AH17">
-        <v>-4.6269263056545673E-8</v>
+        <v>-4.6269263056471134E-8</v>
       </c>
       <c r="AI17">
-        <v>6.5241491009719002E-7</v>
+        <v>6.5241491009719912E-7</v>
       </c>
       <c r="AJ17">
-        <v>9.8272188761751689E-7</v>
+        <v>9.827218876176016E-7</v>
       </c>
       <c r="AK17">
-        <v>1.833438770533413E-7</v>
+        <v>1.8334387705335062E-7</v>
       </c>
       <c r="AL17">
-        <v>4.305201160794975E-7</v>
+        <v>4.3052011607947887E-7</v>
       </c>
       <c r="AM17">
-        <v>1.6319100763837298E-6</v>
+        <v>1.6319100763837145E-6</v>
       </c>
       <c r="AN17">
-        <v>4.2662222833033745E-6</v>
+        <v>4.2662222833033678E-6</v>
       </c>
       <c r="AO17">
-        <v>-3.1499113454875489E-6</v>
+        <v>-3.1499113454875539E-6</v>
       </c>
       <c r="AP17">
-        <v>1.6854425713367265E-6</v>
+        <v>1.6854425713366985E-6</v>
       </c>
       <c r="AQ17">
-        <v>-3.5939342340611408E-5</v>
+        <v>-3.5939342340613359E-5</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.2">
@@ -2994,127 +2988,127 @@
         <v>6.4096400774035587E-3</v>
       </c>
       <c r="C18">
-        <v>-4.794534777729969E-7</v>
+        <v>-4.7945347777298271E-7</v>
       </c>
       <c r="D18">
-        <v>1.5109744239548027E-7</v>
+        <v>1.5109744239549213E-7</v>
       </c>
       <c r="E18">
-        <v>-2.7431527697144156E-10</v>
+        <v>-2.7431527697157474E-10</v>
       </c>
       <c r="F18">
-        <v>-1.70217233895437E-6</v>
+        <v>-1.7021723389542858E-6</v>
       </c>
       <c r="G18">
-        <v>-8.2971140868829353E-7</v>
+        <v>-8.2971140868822672E-7</v>
       </c>
       <c r="H18">
-        <v>5.2644771053443058E-7</v>
+        <v>5.264477105344958E-7</v>
       </c>
       <c r="I18">
-        <v>3.6767718028928474E-7</v>
+        <v>3.6767718028934699E-7</v>
       </c>
       <c r="J18">
-        <v>-4.9531431168658191E-7</v>
+        <v>-4.953143116865152E-7</v>
       </c>
       <c r="K18">
-        <v>2.1282269063230908E-7</v>
+        <v>2.1282269063242215E-7</v>
       </c>
       <c r="L18">
-        <v>2.7920041098774568E-7</v>
+        <v>2.7920041098783123E-7</v>
       </c>
       <c r="M18">
-        <v>1.0176437447734127E-6</v>
+        <v>1.0176437447734441E-6</v>
       </c>
       <c r="N18">
-        <v>4.0961622585628593E-6</v>
+        <v>4.0961622585628186E-6</v>
       </c>
       <c r="O18">
-        <v>1.8661925277529087E-6</v>
+        <v>1.8661925277529188E-6</v>
       </c>
       <c r="P18">
-        <v>5.340121189455809E-7</v>
+        <v>5.3401211894557328E-7</v>
       </c>
       <c r="Q18">
-        <v>1.5835452301698131E-6</v>
+        <v>1.5835452301698169E-6</v>
       </c>
       <c r="R18">
-        <v>8.0230964082090225E-10</v>
+        <v>8.0230964082521683E-10</v>
       </c>
       <c r="S18">
-        <v>5.4053218381146255E-7</v>
+        <v>5.4053218381145832E-7</v>
       </c>
       <c r="T18">
-        <v>1.4365341546275652E-6</v>
+        <v>1.4365341546275677E-6</v>
       </c>
       <c r="U18">
-        <v>8.8503257474661528E-8</v>
+        <v>8.8503257474791971E-8</v>
       </c>
       <c r="V18">
-        <v>-3.9474375791860514E-7</v>
+        <v>-3.9474375791844886E-7</v>
       </c>
       <c r="W18">
-        <v>-4.2656000868509725E-7</v>
+        <v>-4.2656000868510233E-7</v>
       </c>
       <c r="X18">
-        <v>-8.6811795515324119E-8</v>
+        <v>-8.6811795515320731E-8</v>
       </c>
       <c r="Y18">
-        <v>-7.4583835058462903E-7</v>
+        <v>-7.4583835058463581E-7</v>
       </c>
       <c r="Z18">
-        <v>2.202641148870387E-6</v>
+        <v>2.2026411488703709E-6</v>
       </c>
       <c r="AA18">
-        <v>5.740318315651428E-7</v>
+        <v>5.7403183156519701E-7</v>
       </c>
       <c r="AB18">
-        <v>1.4876646129928875E-6</v>
+        <v>1.4876646129928866E-6</v>
       </c>
       <c r="AC18">
-        <v>1.4441917380431773E-6</v>
+        <v>1.444191738043176E-6</v>
       </c>
       <c r="AD18">
-        <v>3.0555373342077059E-6</v>
+        <v>3.0555373342077703E-6</v>
       </c>
       <c r="AE18">
-        <v>1.2878337366921464E-6</v>
+        <v>1.2878337366922777E-6</v>
       </c>
       <c r="AF18">
-        <v>1.1058903538892655E-6</v>
+        <v>1.1058903538892659E-6</v>
       </c>
       <c r="AG18">
-        <v>2.1224009477937054E-6</v>
+        <v>2.1224009477937668E-6</v>
       </c>
       <c r="AH18">
-        <v>1.7949373561311511E-6</v>
+        <v>1.7949373561312164E-6</v>
       </c>
       <c r="AI18">
-        <v>1.2552053985589265E-6</v>
+        <v>1.255205398558928E-6</v>
       </c>
       <c r="AJ18">
-        <v>1.7837850240596663E-6</v>
+        <v>1.7837850240597375E-6</v>
       </c>
       <c r="AK18">
-        <v>1.0507136979885357E-7</v>
+        <v>1.0507136979886374E-7</v>
       </c>
       <c r="AL18">
-        <v>-2.7538131528377809E-7</v>
+        <v>-2.7538131528380519E-7</v>
       </c>
       <c r="AM18">
-        <v>-8.4439032274812593E-7</v>
+        <v>-8.443903227481615E-7</v>
       </c>
       <c r="AN18">
-        <v>1.0737580966028471E-6</v>
+        <v>1.073758096602815E-6</v>
       </c>
       <c r="AO18">
-        <v>1.136414186256636E-6</v>
+        <v>1.1364141862566055E-6</v>
       </c>
       <c r="AP18">
-        <v>4.4094739935865321E-7</v>
+        <v>4.4094739935862102E-7</v>
       </c>
       <c r="AQ18">
-        <v>-3.7450627238493609E-5</v>
+        <v>-3.7450627238493311E-5</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.2">
@@ -3125,127 +3119,127 @@
         <v>6.1420640408511917E-2</v>
       </c>
       <c r="C19">
-        <v>-1.0673484702894912E-5</v>
+        <v>-1.0673484702895094E-5</v>
       </c>
       <c r="D19">
-        <v>5.1030028172545373E-7</v>
+        <v>5.1030028172586284E-7</v>
       </c>
       <c r="E19">
-        <v>1.9731431167351537E-8</v>
+        <v>1.9731431167347116E-8</v>
       </c>
       <c r="F19">
-        <v>-6.8545697744602142E-5</v>
+        <v>-6.8545697744600841E-5</v>
       </c>
       <c r="G19">
-        <v>-7.2899349776585416E-5</v>
+        <v>-7.2899349776584698E-5</v>
       </c>
       <c r="H19">
-        <v>-1.9866113831989986E-6</v>
+        <v>-1.9866113831980736E-6</v>
       </c>
       <c r="I19">
-        <v>-3.4503047078789107E-5</v>
+        <v>-3.4503047078787752E-5</v>
       </c>
       <c r="J19">
-        <v>4.4637275949544072E-5</v>
+        <v>4.4637275949545074E-5</v>
       </c>
       <c r="K19">
-        <v>2.031377868285297E-5</v>
+        <v>2.0313778682854789E-5</v>
       </c>
       <c r="L19">
-        <v>7.6756881094065108E-5</v>
+        <v>7.6756881094066178E-5</v>
       </c>
       <c r="M19">
-        <v>5.9888275028258705E-4</v>
+        <v>5.9888275028258879E-4</v>
       </c>
       <c r="N19">
-        <v>8.3077080486111438E-4</v>
+        <v>8.3077080486111546E-4</v>
       </c>
       <c r="O19">
-        <v>5.6222486849111242E-4</v>
+        <v>5.6222486849111534E-4</v>
       </c>
       <c r="P19">
-        <v>2.0795092029448959E-5</v>
+        <v>2.0795092029449142E-5</v>
       </c>
       <c r="Q19">
-        <v>6.482276032215102E-5</v>
+        <v>6.4822760322151928E-5</v>
       </c>
       <c r="R19">
-        <v>-5.5556404205093615E-7</v>
+        <v>-5.555640420507858E-7</v>
       </c>
       <c r="S19">
-        <v>1.4365341546275652E-6</v>
+        <v>1.4365341546275677E-6</v>
       </c>
       <c r="T19">
-        <v>1.098904984289571E-3</v>
+        <v>1.098904984289573E-3</v>
       </c>
       <c r="U19">
-        <v>1.0568694061240834E-3</v>
+        <v>1.0568694061240886E-3</v>
       </c>
       <c r="V19">
-        <v>1.0844481908290572E-3</v>
+        <v>1.084448190829062E-3</v>
       </c>
       <c r="W19">
-        <v>1.0562671546371512E-3</v>
+        <v>1.0562671546371534E-3</v>
       </c>
       <c r="X19">
-        <v>-8.9907985798011504E-5</v>
+        <v>-8.9907985798011531E-5</v>
       </c>
       <c r="Y19">
-        <v>-3.9401235947596419E-5</v>
+        <v>-3.9401235947596311E-5</v>
       </c>
       <c r="Z19">
-        <v>-6.3204131786215689E-5</v>
+        <v>-6.3204131786215797E-5</v>
       </c>
       <c r="AA19">
-        <v>-1.4131031433913029E-4</v>
+        <v>-1.4131031433913004E-4</v>
       </c>
       <c r="AB19">
-        <v>-3.6422773862496143E-5</v>
+        <v>-3.6422773862495831E-5</v>
       </c>
       <c r="AC19">
-        <v>-6.4218361472962972E-5</v>
+        <v>-6.421836147296262E-5</v>
       </c>
       <c r="AD19">
-        <v>-1.3074955380070619E-5</v>
+        <v>-1.3074955380069887E-5</v>
       </c>
       <c r="AE19">
-        <v>-1.0236663306032264E-4</v>
+        <v>-1.0236663306032121E-4</v>
       </c>
       <c r="AF19">
-        <v>-6.371038590301462E-5</v>
+        <v>-6.3710385903014417E-5</v>
       </c>
       <c r="AG19">
-        <v>-1.0070549821154497E-4</v>
+        <v>-1.007054982115433E-4</v>
       </c>
       <c r="AH19">
-        <v>-5.6119967496870443E-5</v>
+        <v>-5.6119967496869711E-5</v>
       </c>
       <c r="AI19">
-        <v>-8.668045482080331E-5</v>
+        <v>-8.6680454820802877E-5</v>
       </c>
       <c r="AJ19">
-        <v>-6.1006798192371091E-5</v>
+        <v>-6.1006798192369193E-5</v>
       </c>
       <c r="AK19">
-        <v>-1.5362920924607128E-6</v>
+        <v>-1.5362920924603469E-6</v>
       </c>
       <c r="AL19">
-        <v>-1.378315844875695E-5</v>
+        <v>-1.3783158448757709E-5</v>
       </c>
       <c r="AM19">
-        <v>1.7382599122847339E-5</v>
+        <v>1.7382599122846092E-5</v>
       </c>
       <c r="AN19">
-        <v>-2.3319174777097036E-4</v>
+        <v>-2.3319174777097114E-4</v>
       </c>
       <c r="AO19">
-        <v>-9.416029377574324E-5</v>
+        <v>-9.4160293775743755E-5</v>
       </c>
       <c r="AP19">
-        <v>2.75556420633257E-6</v>
+        <v>2.7555642063318924E-6</v>
       </c>
       <c r="AQ19">
-        <v>-1.0251759642876048E-3</v>
+        <v>-1.0251759642876408E-3</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.2">
@@ -3256,127 +3250,127 @@
         <v>0.19574973953966798</v>
       </c>
       <c r="C20">
-        <v>-1.1917548239504982E-5</v>
+        <v>-1.1917548239504753E-5</v>
       </c>
       <c r="D20">
-        <v>-1.4168889714592145E-6</v>
+        <v>-1.4168889714583302E-6</v>
       </c>
       <c r="E20">
-        <v>4.6841916230393653E-8</v>
+        <v>4.6841916230385024E-8</v>
       </c>
       <c r="F20">
-        <v>-1.1285954672276581E-4</v>
+        <v>-1.1285954672276083E-4</v>
       </c>
       <c r="G20">
-        <v>-5.4913677236374247E-5</v>
+        <v>-5.4913677236371022E-5</v>
       </c>
       <c r="H20">
-        <v>-1.0626962083514489E-5</v>
+        <v>-1.0626962083511521E-5</v>
       </c>
       <c r="I20">
-        <v>-8.4988799460574652E-6</v>
+        <v>-8.498879946053291E-6</v>
       </c>
       <c r="J20">
-        <v>1.1229399958418317E-4</v>
+        <v>1.1229399958418665E-4</v>
       </c>
       <c r="K20">
-        <v>5.2655564435101471E-5</v>
+        <v>5.2655564435106838E-5</v>
       </c>
       <c r="L20">
-        <v>2.4206490012415949E-4</v>
+        <v>2.4206490012416434E-4</v>
       </c>
       <c r="M20">
-        <v>9.4422754944994101E-4</v>
+        <v>9.442275494499486E-4</v>
       </c>
       <c r="N20">
-        <v>1.1656223889178912E-3</v>
+        <v>1.1656223889178969E-3</v>
       </c>
       <c r="O20">
-        <v>8.4768197367473728E-4</v>
+        <v>8.4768197367474335E-4</v>
       </c>
       <c r="P20">
-        <v>1.5486651373896187E-5</v>
+        <v>1.5486651373897054E-5</v>
       </c>
       <c r="Q20">
-        <v>1.0771820110734801E-4</v>
+        <v>1.0771820110734944E-4</v>
       </c>
       <c r="R20">
-        <v>-1.3447481638493957E-6</v>
+        <v>-1.3447481638492051E-6</v>
       </c>
       <c r="S20">
-        <v>8.8503257474661528E-8</v>
+        <v>8.8503257474791971E-8</v>
       </c>
       <c r="T20">
-        <v>1.0568694061240834E-3</v>
+        <v>1.0568694061240886E-3</v>
       </c>
       <c r="U20">
-        <v>1.6452200017001224E-3</v>
+        <v>1.6452200017001285E-3</v>
       </c>
       <c r="V20">
-        <v>1.4656753578747924E-3</v>
+        <v>1.4656753578747973E-3</v>
       </c>
       <c r="W20">
-        <v>1.4687187730693747E-3</v>
+        <v>1.4687187730693765E-3</v>
       </c>
       <c r="X20">
-        <v>-1.0742096630132796E-4</v>
+        <v>-1.0742096630132804E-4</v>
       </c>
       <c r="Y20">
-        <v>-3.5724480291825353E-5</v>
+        <v>-3.5724480291825244E-5</v>
       </c>
       <c r="Z20">
-        <v>-7.5921319888607662E-5</v>
+        <v>-7.5921319888607553E-5</v>
       </c>
       <c r="AA20">
-        <v>-1.9346700180987436E-4</v>
+        <v>-1.9346700180987409E-4</v>
       </c>
       <c r="AB20">
-        <v>-7.7173607768917402E-5</v>
+        <v>-7.7173607768917104E-5</v>
       </c>
       <c r="AC20">
-        <v>-7.4888902913436081E-5</v>
+        <v>-7.4888902913436027E-5</v>
       </c>
       <c r="AD20">
-        <v>-4.958481719039202E-5</v>
+        <v>-4.9584817190391343E-5</v>
       </c>
       <c r="AE20">
-        <v>-1.2705014471360609E-4</v>
+        <v>-1.2705014471360454E-4</v>
       </c>
       <c r="AF20">
-        <v>-1.0936706202805714E-4</v>
+        <v>-1.0936706202805687E-4</v>
       </c>
       <c r="AG20">
-        <v>-1.2189741840338278E-4</v>
+        <v>-1.2189741840338078E-4</v>
       </c>
       <c r="AH20">
-        <v>-7.8849646958014522E-5</v>
+        <v>-7.8849646958013925E-5</v>
       </c>
       <c r="AI20">
-        <v>-1.2514452539871273E-4</v>
+        <v>-1.2514452539871249E-4</v>
       </c>
       <c r="AJ20">
-        <v>-8.8118282280409427E-5</v>
+        <v>-8.811828228040753E-5</v>
       </c>
       <c r="AK20">
-        <v>-6.9776142869160368E-6</v>
+        <v>-6.9776142869156437E-6</v>
       </c>
       <c r="AL20">
-        <v>3.0288265024222734E-5</v>
+        <v>3.0288265024221649E-5</v>
       </c>
       <c r="AM20">
-        <v>5.3573246627999012E-5</v>
+        <v>5.3573246627997603E-5</v>
       </c>
       <c r="AN20">
-        <v>-2.7756033228826927E-4</v>
+        <v>-2.775603322882704E-4</v>
       </c>
       <c r="AO20">
-        <v>-1.7065811430583329E-4</v>
+        <v>-1.7065811430583416E-4</v>
       </c>
       <c r="AP20">
-        <v>2.9604358400705188E-5</v>
+        <v>2.9604358400704266E-5</v>
       </c>
       <c r="AQ20">
-        <v>-1.1878898687438101E-3</v>
+        <v>-1.1878898687438565E-3</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.2">
@@ -3387,127 +3381,127 @@
         <v>0.27581238654293538</v>
       </c>
       <c r="C21">
-        <v>-2.0040872286459621E-5</v>
+        <v>-2.0040872286459011E-5</v>
       </c>
       <c r="D21">
-        <v>-9.2865874744494012E-6</v>
+        <v>-9.2865874744480307E-6</v>
       </c>
       <c r="E21">
-        <v>1.0953159158623194E-7</v>
+        <v>1.0953159158621928E-7</v>
       </c>
       <c r="F21">
-        <v>-4.3536970090694296E-6</v>
+        <v>-4.3536970090630599E-6</v>
       </c>
       <c r="G21">
-        <v>7.4896629417315057E-5</v>
+        <v>7.4896629417317442E-5</v>
       </c>
       <c r="H21">
-        <v>3.3439141718737903E-5</v>
+        <v>3.3439141718740973E-5</v>
       </c>
       <c r="I21">
-        <v>2.244178279617774E-4</v>
+        <v>2.2441782796178082E-4</v>
       </c>
       <c r="J21">
-        <v>3.2350042465627559E-4</v>
+        <v>3.2350042465627857E-4</v>
       </c>
       <c r="K21">
-        <v>1.6462365153520618E-4</v>
+        <v>1.6462365153521245E-4</v>
       </c>
       <c r="L21">
-        <v>3.7949607995923314E-4</v>
+        <v>3.7949607995923796E-4</v>
       </c>
       <c r="M21">
-        <v>9.8266822688254847E-4</v>
+        <v>9.8266822688255844E-4</v>
       </c>
       <c r="N21">
-        <v>1.2460425326496964E-3</v>
+        <v>1.2460425326497018E-3</v>
       </c>
       <c r="O21">
-        <v>9.7195264892662976E-4</v>
+        <v>9.7195264892663551E-4</v>
       </c>
       <c r="P21">
-        <v>8.2849316112058424E-5</v>
+        <v>8.2849316112058465E-5</v>
       </c>
       <c r="Q21">
-        <v>1.6181146352520478E-4</v>
+        <v>1.6181146352520502E-4</v>
       </c>
       <c r="R21">
-        <v>-1.7722475576095535E-6</v>
+        <v>-1.7722475576093131E-6</v>
       </c>
       <c r="S21">
-        <v>-3.9474375791860514E-7</v>
+        <v>-3.9474375791844886E-7</v>
       </c>
       <c r="T21">
-        <v>1.0844481908290572E-3</v>
+        <v>1.084448190829062E-3</v>
       </c>
       <c r="U21">
-        <v>1.4656753578747924E-3</v>
+        <v>1.4656753578747973E-3</v>
       </c>
       <c r="V21">
-        <v>1.9601509316439871E-3</v>
+        <v>1.9601509316439923E-3</v>
       </c>
       <c r="W21">
-        <v>1.6562633574830946E-3</v>
+        <v>1.6562633574830963E-3</v>
       </c>
       <c r="X21">
-        <v>-1.0620582284438267E-4</v>
+        <v>-1.0620582284438286E-4</v>
       </c>
       <c r="Y21">
-        <v>-4.636980705190663E-5</v>
+        <v>-4.6369807051906088E-5</v>
       </c>
       <c r="Z21">
-        <v>-3.72131688071773E-5</v>
+        <v>-3.7213168807176676E-5</v>
       </c>
       <c r="AA21">
-        <v>-1.2317815371916358E-4</v>
+        <v>-1.2317815371916299E-4</v>
       </c>
       <c r="AB21">
-        <v>-1.800057262929754E-5</v>
+        <v>-1.8000572629296964E-5</v>
       </c>
       <c r="AC21">
-        <v>-6.1102469237547038E-5</v>
+        <v>-6.1102469237546875E-5</v>
       </c>
       <c r="AD21">
-        <v>-1.6962377483280234E-5</v>
+        <v>-1.696237748327915E-5</v>
       </c>
       <c r="AE21">
-        <v>-9.7436342027805878E-5</v>
+        <v>-9.7436342027804089E-5</v>
       </c>
       <c r="AF21">
-        <v>-6.0840869958251562E-5</v>
+        <v>-6.0840869958251115E-5</v>
       </c>
       <c r="AG21">
-        <v>-8.9326957455047447E-5</v>
+        <v>-8.9326957455045198E-5</v>
       </c>
       <c r="AH21">
-        <v>-3.2931007509360891E-5</v>
+        <v>-3.2931007509360294E-5</v>
       </c>
       <c r="AI21">
-        <v>-1.1961983438036681E-4</v>
+        <v>-1.1961983438036667E-4</v>
       </c>
       <c r="AJ21">
-        <v>-3.7001550324963599E-5</v>
+        <v>-3.7001550324961322E-5</v>
       </c>
       <c r="AK21">
-        <v>-3.8931243886192624E-6</v>
+        <v>-3.8931243886189371E-6</v>
       </c>
       <c r="AL21">
-        <v>9.3426894991116343E-6</v>
+        <v>9.3426894991103875E-6</v>
       </c>
       <c r="AM21">
-        <v>4.4047385844616098E-5</v>
+        <v>4.4047385844614743E-5</v>
       </c>
       <c r="AN21">
-        <v>-2.4737388454350041E-4</v>
+        <v>-2.4737388454350165E-4</v>
       </c>
       <c r="AO21">
-        <v>-2.286249725011406E-4</v>
+        <v>-2.2862497250114165E-4</v>
       </c>
       <c r="AP21">
-        <v>1.7113101496332088E-5</v>
+        <v>1.7113101496331112E-5</v>
       </c>
       <c r="AQ21">
-        <v>-1.3002500503033593E-3</v>
+        <v>-1.3002500503034127E-3</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.2">
@@ -3518,127 +3512,127 @@
         <v>0.52182117001425188</v>
       </c>
       <c r="C22">
-        <v>-3.3429963124193714E-5</v>
+        <v>-3.3429963124193498E-5</v>
       </c>
       <c r="D22">
-        <v>-1.2390114950463161E-5</v>
+        <v>-1.2390114950462741E-5</v>
       </c>
       <c r="E22">
-        <v>1.2569611486879355E-7</v>
+        <v>1.2569611486878902E-7</v>
       </c>
       <c r="F22">
-        <v>2.6211592284412316E-4</v>
+        <v>2.6211592284412511E-4</v>
       </c>
       <c r="G22">
-        <v>2.6613440371310332E-4</v>
+        <v>2.6613440371310489E-4</v>
       </c>
       <c r="H22">
-        <v>2.3690804101118506E-4</v>
+        <v>2.3690804101118675E-4</v>
       </c>
       <c r="I22">
-        <v>4.666156026794133E-4</v>
+        <v>4.6661560267941471E-4</v>
       </c>
       <c r="J22">
-        <v>5.2318050692513256E-4</v>
+        <v>5.2318050692513418E-4</v>
       </c>
       <c r="K22">
-        <v>3.3354089345732501E-4</v>
+        <v>3.3354089345732782E-4</v>
       </c>
       <c r="L22">
-        <v>5.8351952611375587E-4</v>
+        <v>5.8351952611375793E-4</v>
       </c>
       <c r="M22">
-        <v>9.6845664510417659E-4</v>
+        <v>9.6845664510417898E-4</v>
       </c>
       <c r="N22">
-        <v>1.247342522928933E-3</v>
+        <v>1.2473425229289343E-3</v>
       </c>
       <c r="O22">
-        <v>1.0097894482138943E-3</v>
+        <v>1.0097894482138973E-3</v>
       </c>
       <c r="P22">
-        <v>1.4894397473712295E-4</v>
+        <v>1.4894397473712279E-4</v>
       </c>
       <c r="Q22">
         <v>2.6017211800716147E-4</v>
       </c>
       <c r="R22">
-        <v>-2.2866867654687182E-6</v>
+        <v>-2.2866867654685793E-6</v>
       </c>
       <c r="S22">
-        <v>-4.2656000868509725E-7</v>
+        <v>-4.2656000868510233E-7</v>
       </c>
       <c r="T22">
-        <v>1.0562671546371512E-3</v>
+        <v>1.0562671546371534E-3</v>
       </c>
       <c r="U22">
-        <v>1.4687187730693747E-3</v>
+        <v>1.4687187730693765E-3</v>
       </c>
       <c r="V22">
-        <v>1.6562633574830946E-3</v>
+        <v>1.6562633574830963E-3</v>
       </c>
       <c r="W22">
-        <v>2.2704724877776377E-3</v>
+        <v>2.2704724877776398E-3</v>
       </c>
       <c r="X22">
-        <v>-9.9376378694009275E-5</v>
+        <v>-9.9376378694009614E-5</v>
       </c>
       <c r="Y22">
-        <v>-2.014169751871455E-5</v>
+        <v>-2.0141697518714008E-5</v>
       </c>
       <c r="Z22">
-        <v>-1.1335900487810985E-5</v>
+        <v>-1.1335900487810036E-5</v>
       </c>
       <c r="AA22">
-        <v>-1.3502267583929078E-4</v>
+        <v>-1.3502267583929013E-4</v>
       </c>
       <c r="AB22">
-        <v>9.627716102455743E-6</v>
+        <v>9.6277161024561903E-6</v>
       </c>
       <c r="AC22">
-        <v>2.6603497878505821E-6</v>
+        <v>2.6603497878507125E-6</v>
       </c>
       <c r="AD22">
-        <v>1.3311531076106819E-5</v>
+        <v>1.3311531076107416E-5</v>
       </c>
       <c r="AE22">
-        <v>-4.9966637432240349E-5</v>
+        <v>-4.996663743223837E-5</v>
       </c>
       <c r="AF22">
-        <v>-2.0407541310214171E-5</v>
+        <v>-2.0407541310213589E-5</v>
       </c>
       <c r="AG22">
-        <v>-2.4757502982398743E-5</v>
+        <v>-2.4757502982396263E-5</v>
       </c>
       <c r="AH22">
-        <v>5.4323512462519023E-5</v>
+        <v>5.4323512462519348E-5</v>
       </c>
       <c r="AI22">
         <v>-8.782909803770575E-5</v>
       </c>
       <c r="AJ22">
-        <v>2.3376172638838962E-5</v>
+        <v>2.3376172638841456E-5</v>
       </c>
       <c r="AK22">
-        <v>-1.9996834611987475E-6</v>
+        <v>-1.9996834611985036E-6</v>
       </c>
       <c r="AL22">
-        <v>1.4045143057342304E-5</v>
+        <v>1.4045143057340732E-5</v>
       </c>
       <c r="AM22">
-        <v>5.5298533649530068E-5</v>
+        <v>5.5298533649528712E-5</v>
       </c>
       <c r="AN22">
-        <v>-2.565978510918802E-4</v>
+        <v>-2.5659785109188166E-4</v>
       </c>
       <c r="AO22">
-        <v>7.4148520867829888E-5</v>
+        <v>7.4148520867828641E-5</v>
       </c>
       <c r="AP22">
-        <v>-1.7284344698871394E-5</v>
+        <v>-1.728434469887237E-5</v>
       </c>
       <c r="AQ22">
-        <v>-1.5115842393550105E-3</v>
+        <v>-1.5115842393550773E-3</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.2">
@@ -3649,127 +3643,127 @@
         <v>2.7611671543221375E-2</v>
       </c>
       <c r="C23">
-        <v>-3.2380729423232183E-7</v>
+        <v>-3.2380729423231209E-7</v>
       </c>
       <c r="D23">
-        <v>-5.1957233843464934E-7</v>
+        <v>-5.1957233843454346E-7</v>
       </c>
       <c r="E23">
-        <v>-7.6582206144059152E-10</v>
+        <v>-7.658220614415709E-10</v>
       </c>
       <c r="F23">
-        <v>-2.707574289062187E-7</v>
+        <v>-2.7075742890616449E-7</v>
       </c>
       <c r="G23">
-        <v>-3.5266315947477373E-6</v>
+        <v>-3.5266315947480727E-6</v>
       </c>
       <c r="H23">
-        <v>8.2080509184270777E-6</v>
+        <v>8.2080509184267727E-6</v>
       </c>
       <c r="I23">
-        <v>6.5324197449251624E-6</v>
+        <v>6.532419744924871E-6</v>
       </c>
       <c r="J23">
-        <v>-1.8026290309752102E-6</v>
+        <v>-1.8026290309755795E-6</v>
       </c>
       <c r="K23">
-        <v>-1.7945862808882952E-6</v>
+        <v>-1.7945862808884104E-6</v>
       </c>
       <c r="L23">
-        <v>-2.1965468206758998E-5</v>
+        <v>-2.1965468206759297E-5</v>
       </c>
       <c r="M23">
-        <v>-6.2278906244901268E-5</v>
+        <v>-6.2278906244900794E-5</v>
       </c>
       <c r="N23">
-        <v>-7.8598479677458028E-5</v>
+        <v>-7.8598479677458082E-5</v>
       </c>
       <c r="O23">
-        <v>-8.6699607570422092E-5</v>
+        <v>-8.6699607570421983E-5</v>
       </c>
       <c r="P23">
-        <v>1.0949355150664113E-6</v>
+        <v>1.094935515066396E-6</v>
       </c>
       <c r="Q23">
-        <v>6.2610150065106485E-6</v>
+        <v>6.2610150065105977E-6</v>
       </c>
       <c r="R23">
-        <v>8.8985406800937536E-8</v>
+        <v>8.8985406800946218E-8</v>
       </c>
       <c r="S23">
-        <v>-8.6811795515324119E-8</v>
+        <v>-8.6811795515320731E-8</v>
       </c>
       <c r="T23">
-        <v>-8.9907985798011504E-5</v>
+        <v>-8.9907985798011531E-5</v>
       </c>
       <c r="U23">
-        <v>-1.0742096630132796E-4</v>
+        <v>-1.0742096630132804E-4</v>
       </c>
       <c r="V23">
-        <v>-1.0620582284438267E-4</v>
+        <v>-1.0620582284438286E-4</v>
       </c>
       <c r="W23">
-        <v>-9.9376378694009275E-5</v>
+        <v>-9.9376378694009614E-5</v>
       </c>
       <c r="X23">
-        <v>1.8927257709107903E-5</v>
+        <v>1.8927257709107899E-5</v>
       </c>
       <c r="Y23">
-        <v>-3.2889122638969173E-6</v>
+        <v>-3.2889122638969241E-6</v>
       </c>
       <c r="Z23">
-        <v>7.5135905332548009E-6</v>
+        <v>7.513590533254828E-6</v>
       </c>
       <c r="AA23">
         <v>1.4778029294038274E-5</v>
       </c>
       <c r="AB23">
-        <v>5.7787937086666591E-6</v>
+        <v>5.7787937086666802E-6</v>
       </c>
       <c r="AC23">
-        <v>4.709381224881867E-6</v>
+        <v>4.7093812248819204E-6</v>
       </c>
       <c r="AD23">
-        <v>7.9506036482359879E-6</v>
+        <v>7.9506036482358744E-6</v>
       </c>
       <c r="AE23">
-        <v>1.0765277846094642E-5</v>
+        <v>1.0765277846094515E-5</v>
       </c>
       <c r="AF23">
-        <v>6.1319733205818757E-6</v>
+        <v>6.1319733205818613E-6</v>
       </c>
       <c r="AG23">
-        <v>7.4327991648870512E-6</v>
+        <v>7.4327991648868877E-6</v>
       </c>
       <c r="AH23">
-        <v>6.205263403363483E-6</v>
+        <v>6.2052634033634271E-6</v>
       </c>
       <c r="AI23">
-        <v>1.0328813921610181E-5</v>
+        <v>1.032881392161015E-5</v>
       </c>
       <c r="AJ23">
-        <v>1.1796023550697918E-5</v>
+        <v>1.1796023550697735E-5</v>
       </c>
       <c r="AK23">
-        <v>5.2102672916749615E-7</v>
+        <v>5.2102672916746735E-7</v>
       </c>
       <c r="AL23">
-        <v>2.5066950764933505E-6</v>
+        <v>2.5066950764934386E-6</v>
       </c>
       <c r="AM23">
-        <v>-1.8117120046136337E-9</v>
+        <v>-1.811712004518766E-9</v>
       </c>
       <c r="AN23">
-        <v>2.2420804717912002E-5</v>
+        <v>2.242080471791211E-5</v>
       </c>
       <c r="AO23">
-        <v>1.1999638764810597E-5</v>
+        <v>1.1999638764810673E-5</v>
       </c>
       <c r="AP23">
-        <v>1.857148608807111E-5</v>
+        <v>1.8571486088071208E-5</v>
       </c>
       <c r="AQ23">
-        <v>9.6714393400046313E-5</v>
+        <v>9.6714393400049241E-5</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.2">
@@ -3780,127 +3774,127 @@
         <v>3.7598541335309421</v>
       </c>
       <c r="C24">
-        <v>4.5785218710541319E-6</v>
+        <v>4.5785218710541725E-6</v>
       </c>
       <c r="D24">
-        <v>1.4965674266039544E-6</v>
+        <v>1.496567426603846E-6</v>
       </c>
       <c r="E24">
-        <v>-2.9644124332866767E-8</v>
+        <v>-2.9644124332865602E-8</v>
       </c>
       <c r="F24">
-        <v>7.8240198564441456E-5</v>
+        <v>7.8240198564441673E-5</v>
       </c>
       <c r="G24">
-        <v>-3.6131200329632938E-5</v>
+        <v>-3.6131200329632559E-5</v>
       </c>
       <c r="H24">
-        <v>-5.0501516284037653E-5</v>
+        <v>-5.0501516284037328E-5</v>
       </c>
       <c r="I24">
-        <v>-3.3492001192811946E-5</v>
+        <v>-3.3492001192811458E-5</v>
       </c>
       <c r="J24">
-        <v>-1.8136603876306901E-5</v>
+        <v>-1.8136603876306413E-5</v>
       </c>
       <c r="K24">
-        <v>-3.0418846568515639E-5</v>
+        <v>-3.0418846568515422E-5</v>
       </c>
       <c r="L24">
-        <v>1.4747985826144201E-5</v>
+        <v>1.474798582614458E-5</v>
       </c>
       <c r="M24">
-        <v>-1.0231541598829856E-4</v>
+        <v>-1.0231541598829889E-4</v>
       </c>
       <c r="N24">
-        <v>-1.5617117774558114E-5</v>
+        <v>-1.5617117774557681E-5</v>
       </c>
       <c r="O24">
-        <v>1.0600849929859335E-5</v>
+        <v>1.0600849929859226E-5</v>
       </c>
       <c r="P24">
-        <v>-5.8245829301121707E-6</v>
+        <v>-5.8245829301120894E-6</v>
       </c>
       <c r="Q24">
-        <v>1.9898933301434337E-5</v>
+        <v>1.9898933301434418E-5</v>
       </c>
       <c r="R24">
-        <v>-4.3443997023015957E-7</v>
+        <v>-4.3443997023016634E-7</v>
       </c>
       <c r="S24">
-        <v>-7.4583835058462903E-7</v>
+        <v>-7.4583835058463581E-7</v>
       </c>
       <c r="T24">
-        <v>-3.9401235947596419E-5</v>
+        <v>-3.9401235947596311E-5</v>
       </c>
       <c r="U24">
-        <v>-3.5724480291825353E-5</v>
+        <v>-3.5724480291825244E-5</v>
       </c>
       <c r="V24">
-        <v>-4.636980705190663E-5</v>
+        <v>-4.6369807051906088E-5</v>
       </c>
       <c r="W24">
-        <v>-2.014169751871455E-5</v>
+        <v>-2.0141697518714008E-5</v>
       </c>
       <c r="X24">
-        <v>-3.2889122638969173E-6</v>
+        <v>-3.2889122638969241E-6</v>
       </c>
       <c r="Y24">
-        <v>3.6255988393740302E-4</v>
+        <v>3.6255988393740297E-4</v>
       </c>
       <c r="Z24">
-        <v>1.968704679545874E-5</v>
+        <v>1.9687046795458191E-5</v>
       </c>
       <c r="AA24">
-        <v>3.1276971046190651E-5</v>
+        <v>3.1276971046190705E-5</v>
       </c>
       <c r="AB24">
-        <v>1.2715874956721917E-5</v>
+        <v>1.2715874956722029E-5</v>
       </c>
       <c r="AC24">
-        <v>-1.7461209962555666E-6</v>
+        <v>-1.7461209962554059E-6</v>
       </c>
       <c r="AD24">
-        <v>-1.5210288610090506E-5</v>
+        <v>-1.5210288610090774E-5</v>
       </c>
       <c r="AE24">
-        <v>2.0607156288907608E-5</v>
+        <v>2.0607156288907795E-5</v>
       </c>
       <c r="AF24">
-        <v>9.8331796399977138E-6</v>
+        <v>9.8331796399977968E-6</v>
       </c>
       <c r="AG24">
-        <v>3.6750717129365831E-5</v>
+        <v>3.675071712936577E-5</v>
       </c>
       <c r="AH24">
-        <v>1.5277720187865527E-5</v>
+        <v>1.5277720187865425E-5</v>
       </c>
       <c r="AI24">
-        <v>2.6555133209520629E-5</v>
+        <v>2.6555133209520663E-5</v>
       </c>
       <c r="AJ24">
-        <v>3.5620091428164465E-5</v>
+        <v>3.5620091428164384E-5</v>
       </c>
       <c r="AK24">
-        <v>-2.1800818275312209E-6</v>
+        <v>-2.1800818275311565E-6</v>
       </c>
       <c r="AL24">
-        <v>2.0137847917285159E-5</v>
+        <v>2.013784791728501E-5</v>
       </c>
       <c r="AM24">
-        <v>8.6527431378260133E-6</v>
+        <v>8.652743137825871E-6</v>
       </c>
       <c r="AN24">
-        <v>1.6463398465124558E-5</v>
+        <v>1.646339846512447E-5</v>
       </c>
       <c r="AO24">
-        <v>5.5543807386748482E-5</v>
+        <v>5.5543807386748333E-5</v>
       </c>
       <c r="AP24">
-        <v>4.3445861702618699E-6</v>
+        <v>4.3445861702619309E-6</v>
       </c>
       <c r="AQ24">
-        <v>-5.6131652601594748E-5</v>
+        <v>-5.6131652601602737E-5</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.2">
@@ -3911,79 +3905,79 @@
         <v>0.11973795003126128</v>
       </c>
       <c r="C25">
-        <v>1.7266423627667071E-5</v>
+        <v>1.7266423627667288E-5</v>
       </c>
       <c r="D25">
-        <v>7.1880752591649884E-7</v>
+        <v>7.1880752591607194E-7</v>
       </c>
       <c r="E25">
-        <v>-9.1943244777236244E-10</v>
+        <v>-9.1943244776833904E-10</v>
       </c>
       <c r="F25">
-        <v>-3.5656270265161906E-5</v>
+        <v>-3.5656270265161988E-5</v>
       </c>
       <c r="G25">
-        <v>1.4100748858151844E-5</v>
+        <v>1.4100748858153267E-5</v>
       </c>
       <c r="H25">
-        <v>-2.0956617604762464E-5</v>
+        <v>-2.0956617604760865E-5</v>
       </c>
       <c r="I25">
-        <v>-3.1424693107275596E-5</v>
+        <v>-3.1424693107274458E-5</v>
       </c>
       <c r="J25">
-        <v>4.7306697845002186E-6</v>
+        <v>4.7306697845017365E-6</v>
       </c>
       <c r="K25">
-        <v>4.7370994212763307E-5</v>
+        <v>4.7370994212764107E-5</v>
       </c>
       <c r="L25">
-        <v>2.0324370487780771E-5</v>
+        <v>2.0324370487782276E-5</v>
       </c>
       <c r="M25">
-        <v>-4.8978046632238521E-5</v>
+        <v>-4.8978046632240364E-5</v>
       </c>
       <c r="N25">
-        <v>-3.2564882355588126E-5</v>
+        <v>-3.2564882355588044E-5</v>
       </c>
       <c r="O25">
-        <v>-7.9314437795450669E-5</v>
+        <v>-7.9314437795451807E-5</v>
       </c>
       <c r="P25">
-        <v>-3.1175427167072878E-5</v>
+        <v>-3.1175427167073177E-5</v>
       </c>
       <c r="Q25">
-        <v>-7.5816050341255911E-6</v>
+        <v>-7.5816050341258079E-6</v>
       </c>
       <c r="R25">
-        <v>1.6770348741398323E-6</v>
+        <v>1.6770348741398243E-6</v>
       </c>
       <c r="S25">
-        <v>2.202641148870387E-6</v>
+        <v>2.2026411488703709E-6</v>
       </c>
       <c r="T25">
-        <v>-6.3204131786215689E-5</v>
+        <v>-6.3204131786215797E-5</v>
       </c>
       <c r="U25">
-        <v>-7.5921319888607662E-5</v>
+        <v>-7.5921319888607553E-5</v>
       </c>
       <c r="V25">
-        <v>-3.72131688071773E-5</v>
+        <v>-3.7213168807176676E-5</v>
       </c>
       <c r="W25">
-        <v>-1.1335900487810985E-5</v>
+        <v>-1.1335900487810036E-5</v>
       </c>
       <c r="X25">
-        <v>7.5135905332548009E-6</v>
+        <v>7.513590533254828E-6</v>
       </c>
       <c r="Y25">
-        <v>1.968704679545874E-5</v>
+        <v>1.9687046795458191E-5</v>
       </c>
       <c r="Z25">
         <v>1.7829102112164779E-3</v>
       </c>
       <c r="AA25">
-        <v>7.7344479256869761E-4</v>
+        <v>7.7344479256869804E-4</v>
       </c>
       <c r="AB25">
         <v>7.4569366744624288E-4</v>
@@ -3995,43 +3989,43 @@
         <v>7.1632360716470734E-4</v>
       </c>
       <c r="AE25">
-        <v>7.550145523109096E-4</v>
+        <v>7.5501455231091101E-4</v>
       </c>
       <c r="AF25">
-        <v>7.7699909288053996E-4</v>
+        <v>7.7699909288054018E-4</v>
       </c>
       <c r="AG25">
-        <v>7.693773324055456E-4</v>
+        <v>7.693773324055469E-4</v>
       </c>
       <c r="AH25">
-        <v>7.6273160318997366E-4</v>
+        <v>7.6273160318997399E-4</v>
       </c>
       <c r="AI25">
-        <v>7.5720573404033454E-4</v>
+        <v>7.5720573404033475E-4</v>
       </c>
       <c r="AJ25">
-        <v>7.6416647815987589E-4</v>
+        <v>7.6416647815987719E-4</v>
       </c>
       <c r="AK25">
-        <v>-5.3300982779042657E-7</v>
+        <v>-5.3300982779029104E-7</v>
       </c>
       <c r="AL25">
-        <v>1.3613920744783578E-5</v>
+        <v>1.3613920744783036E-5</v>
       </c>
       <c r="AM25">
-        <v>-2.936048102112536E-5</v>
+        <v>-2.9360481021125929E-5</v>
       </c>
       <c r="AN25">
-        <v>4.0365629356841894E-4</v>
+        <v>4.0365629356841823E-4</v>
       </c>
       <c r="AO25">
-        <v>4.3801699276803494E-4</v>
+        <v>4.3801699276803418E-4</v>
       </c>
       <c r="AP25">
-        <v>1.8372719529889995E-4</v>
+        <v>1.8372719529889965E-4</v>
       </c>
       <c r="AQ25">
-        <v>-9.4485755885231589E-4</v>
+        <v>-9.4485755885233996E-4</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.2">
@@ -4042,127 +4036,127 @@
         <v>0.20776134759559226</v>
       </c>
       <c r="C26">
-        <v>4.8888985168169384E-5</v>
+        <v>4.8888985168169479E-5</v>
       </c>
       <c r="D26">
-        <v>1.0385655473421718E-6</v>
+        <v>1.0385655473419618E-6</v>
       </c>
       <c r="E26">
-        <v>-1.3761691063373766E-8</v>
+        <v>-1.3761691063372072E-8</v>
       </c>
       <c r="F26">
-        <v>4.1009830256702473E-5</v>
+        <v>4.1009830256702581E-5</v>
       </c>
       <c r="G26">
-        <v>6.739098545921685E-5</v>
+        <v>6.7390985459217826E-5</v>
       </c>
       <c r="H26">
-        <v>3.4266425746719157E-8</v>
+        <v>3.4266425747613623E-8</v>
       </c>
       <c r="I26">
-        <v>-2.8725543439385242E-5</v>
+        <v>-2.872554343938432E-5</v>
       </c>
       <c r="J26">
-        <v>-3.7007076476470589E-5</v>
+        <v>-3.700707647646918E-5</v>
       </c>
       <c r="K26">
-        <v>7.3491147857295761E-5</v>
+        <v>7.3491147857296629E-5</v>
       </c>
       <c r="L26">
-        <v>2.4743376151655427E-5</v>
+        <v>2.4743376151656728E-5</v>
       </c>
       <c r="M26">
-        <v>-1.1098295168370919E-4</v>
+        <v>-1.1098295168371038E-4</v>
       </c>
       <c r="N26">
-        <v>-1.487695871176641E-4</v>
+        <v>-1.4876958711766323E-4</v>
       </c>
       <c r="O26">
-        <v>-1.4020124075363747E-4</v>
+        <v>-1.4020124075363698E-4</v>
       </c>
       <c r="P26">
-        <v>-3.7262553226173311E-5</v>
+        <v>-3.7262553226173067E-5</v>
       </c>
       <c r="Q26">
-        <v>-3.6685283273134935E-5</v>
+        <v>-3.6685283273134189E-5</v>
       </c>
       <c r="R26">
-        <v>1.8694535527795944E-6</v>
+        <v>1.8694535527796605E-6</v>
       </c>
       <c r="S26">
-        <v>5.740318315651428E-7</v>
+        <v>5.7403183156519701E-7</v>
       </c>
       <c r="T26">
-        <v>-1.4131031433913029E-4</v>
+        <v>-1.4131031433913004E-4</v>
       </c>
       <c r="U26">
-        <v>-1.9346700180987436E-4</v>
+        <v>-1.9346700180987409E-4</v>
       </c>
       <c r="V26">
-        <v>-1.2317815371916358E-4</v>
+        <v>-1.2317815371916299E-4</v>
       </c>
       <c r="W26">
-        <v>-1.3502267583929078E-4</v>
+        <v>-1.3502267583929013E-4</v>
       </c>
       <c r="X26">
         <v>1.4778029294038274E-5</v>
       </c>
       <c r="Y26">
-        <v>3.1276971046190651E-5</v>
+        <v>3.1276971046190705E-5</v>
       </c>
       <c r="Z26">
-        <v>7.7344479256869761E-4</v>
+        <v>7.7344479256869804E-4</v>
       </c>
       <c r="AA26">
-        <v>1.4978939884172156E-3</v>
+        <v>1.4978939884172161E-3</v>
       </c>
       <c r="AB26">
-        <v>7.511956368061952E-4</v>
+        <v>7.5119563680619509E-4</v>
       </c>
       <c r="AC26">
-        <v>7.6110629188786978E-4</v>
+        <v>7.6110629188786989E-4</v>
       </c>
       <c r="AD26">
-        <v>7.1582806530391902E-4</v>
+        <v>7.1582806530391934E-4</v>
       </c>
       <c r="AE26">
-        <v>7.6784052700741719E-4</v>
+        <v>7.6784052700741849E-4</v>
       </c>
       <c r="AF26">
-        <v>7.7867231578512884E-4</v>
+        <v>7.7867231578512895E-4</v>
       </c>
       <c r="AG26">
-        <v>7.8430937845117054E-4</v>
+        <v>7.8430937845117173E-4</v>
       </c>
       <c r="AH26">
-        <v>7.7433551300843144E-4</v>
+        <v>7.7433551300843187E-4</v>
       </c>
       <c r="AI26">
-        <v>7.6157320364625728E-4</v>
+        <v>7.6157320364625739E-4</v>
       </c>
       <c r="AJ26">
-        <v>7.7308254998453233E-4</v>
+        <v>7.7308254998453385E-4</v>
       </c>
       <c r="AK26">
-        <v>8.5266355710638699E-6</v>
+        <v>8.5266355710639512E-6</v>
       </c>
       <c r="AL26">
-        <v>3.8832066032371665E-7</v>
+        <v>3.8832066032320166E-7</v>
       </c>
       <c r="AM26">
-        <v>-3.802203384952897E-5</v>
+        <v>-3.8022033849529431E-5</v>
       </c>
       <c r="AN26">
-        <v>5.8979347552161234E-4</v>
+        <v>5.8979347552161137E-4</v>
       </c>
       <c r="AO26">
-        <v>3.5927650880636104E-4</v>
+        <v>3.592765088063606E-4</v>
       </c>
       <c r="AP26">
-        <v>1.9307276699712317E-4</v>
+        <v>1.9307276699712285E-4</v>
       </c>
       <c r="AQ26">
-        <v>-9.6631756788385752E-4</v>
+        <v>-9.6631756788387508E-4</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.2">
@@ -4173,127 +4167,127 @@
         <v>0.18252792719255037</v>
       </c>
       <c r="C27">
-        <v>7.8037873559623172E-6</v>
+        <v>7.8037873559625391E-6</v>
       </c>
       <c r="D27">
-        <v>-1.5581584983847213E-6</v>
+        <v>-1.5581584983845231E-6</v>
       </c>
       <c r="E27">
-        <v>1.9331386674732338E-8</v>
+        <v>1.9331386674730246E-8</v>
       </c>
       <c r="F27">
-        <v>4.6647438236290399E-5</v>
+        <v>4.6647438236291347E-5</v>
       </c>
       <c r="G27">
-        <v>5.7688548343415136E-5</v>
+        <v>5.7688548343415854E-5</v>
       </c>
       <c r="H27">
-        <v>1.1145157449789273E-5</v>
+        <v>1.1145157449789937E-5</v>
       </c>
       <c r="I27">
-        <v>1.0317200800238663E-4</v>
+        <v>1.0317200800238744E-4</v>
       </c>
       <c r="J27">
-        <v>6.8738675636799551E-5</v>
+        <v>6.8738675636800432E-5</v>
       </c>
       <c r="K27">
-        <v>1.0310700463884659E-4</v>
+        <v>1.0310700463884772E-4</v>
       </c>
       <c r="L27">
-        <v>4.1177353497015543E-5</v>
+        <v>4.1177353497016356E-5</v>
       </c>
       <c r="M27">
-        <v>-6.9205814836941355E-5</v>
+        <v>-6.9205814836940461E-5</v>
       </c>
       <c r="N27">
-        <v>-2.8052432512672319E-5</v>
+        <v>-2.805243251267219E-5</v>
       </c>
       <c r="O27">
-        <v>-6.3122869523632265E-5</v>
+        <v>-6.3122869523631005E-5</v>
       </c>
       <c r="P27">
-        <v>-2.2876754188527269E-5</v>
+        <v>-2.2876754188527154E-5</v>
       </c>
       <c r="Q27">
-        <v>-3.8715299044301533E-5</v>
+        <v>-3.8715299044301133E-5</v>
       </c>
       <c r="R27">
-        <v>1.8537091297097752E-6</v>
+        <v>1.8537091297097828E-6</v>
       </c>
       <c r="S27">
-        <v>1.4876646129928875E-6</v>
+        <v>1.4876646129928866E-6</v>
       </c>
       <c r="T27">
-        <v>-3.6422773862496143E-5</v>
+        <v>-3.6422773862495831E-5</v>
       </c>
       <c r="U27">
-        <v>-7.7173607768917402E-5</v>
+        <v>-7.7173607768917104E-5</v>
       </c>
       <c r="V27">
-        <v>-1.800057262929754E-5</v>
+        <v>-1.8000572629296964E-5</v>
       </c>
       <c r="W27">
-        <v>9.627716102455743E-6</v>
+        <v>9.6277161024561903E-6</v>
       </c>
       <c r="X27">
-        <v>5.7787937086666591E-6</v>
+        <v>5.7787937086666802E-6</v>
       </c>
       <c r="Y27">
-        <v>1.2715874956721917E-5</v>
+        <v>1.2715874956722029E-5</v>
       </c>
       <c r="Z27">
         <v>7.4569366744624288E-4</v>
       </c>
       <c r="AA27">
-        <v>7.511956368061952E-4</v>
+        <v>7.5119563680619509E-4</v>
       </c>
       <c r="AB27">
-        <v>1.4344447698320494E-3</v>
+        <v>1.4344447698320492E-3</v>
       </c>
       <c r="AC27">
-        <v>7.3991240095867957E-4</v>
+        <v>7.3991240095867968E-4</v>
       </c>
       <c r="AD27">
-        <v>7.0372975942405212E-4</v>
+        <v>7.0372975942405223E-4</v>
       </c>
       <c r="AE27">
-        <v>7.4286054183321396E-4</v>
+        <v>7.4286054183321504E-4</v>
       </c>
       <c r="AF27">
-        <v>7.6006349065540048E-4</v>
+        <v>7.600634906554007E-4</v>
       </c>
       <c r="AG27">
-        <v>7.5936487329163551E-4</v>
+        <v>7.5936487329163638E-4</v>
       </c>
       <c r="AH27">
-        <v>7.610793717362091E-4</v>
+        <v>7.6107937173620953E-4</v>
       </c>
       <c r="AI27">
-        <v>7.3781523166903016E-4</v>
+        <v>7.3781523166903038E-4</v>
       </c>
       <c r="AJ27">
-        <v>7.5115809429039779E-4</v>
+        <v>7.5115809429039909E-4</v>
       </c>
       <c r="AK27">
-        <v>-1.234021170565784E-6</v>
+        <v>-1.234021170565662E-6</v>
       </c>
       <c r="AL27">
-        <v>6.4100084106337034E-5</v>
+        <v>6.41000841063366E-5</v>
       </c>
       <c r="AM27">
-        <v>3.8413146181994379E-5</v>
+        <v>3.8413146181993756E-5</v>
       </c>
       <c r="AN27">
-        <v>3.7078127527999502E-4</v>
+        <v>3.7078127527999437E-4</v>
       </c>
       <c r="AO27">
-        <v>3.5922475752295989E-4</v>
+        <v>3.5922475752295929E-4</v>
       </c>
       <c r="AP27">
-        <v>1.5082046462053236E-4</v>
+        <v>1.5082046462053201E-4</v>
       </c>
       <c r="AQ27">
-        <v>-8.975689655072918E-4</v>
+        <v>-8.9756896550730958E-4</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.2">
@@ -4304,127 +4298,127 @@
         <v>0.23195318704118995</v>
       </c>
       <c r="C28">
-        <v>1.742594842869441E-5</v>
+        <v>1.7425948428694091E-5</v>
       </c>
       <c r="D28">
-        <v>1.5415407692319087E-6</v>
+        <v>1.5415407692324897E-6</v>
       </c>
       <c r="E28">
-        <v>-1.1343051444583115E-8</v>
+        <v>-1.1343051444589269E-8</v>
       </c>
       <c r="F28">
-        <v>9.4048309793545056E-5</v>
+        <v>9.4048309793546967E-5</v>
       </c>
       <c r="G28">
-        <v>6.3869003200144124E-5</v>
+        <v>6.3869003200144828E-5</v>
       </c>
       <c r="H28">
-        <v>2.1486487525607271E-5</v>
+        <v>2.1486487525607779E-5</v>
       </c>
       <c r="I28">
-        <v>1.7860382209606296E-4</v>
+        <v>1.7860382209606356E-4</v>
       </c>
       <c r="J28">
-        <v>5.8409954117462943E-5</v>
+        <v>5.8409954117463553E-5</v>
       </c>
       <c r="K28">
-        <v>9.0925851162753765E-5</v>
+        <v>9.0925851162755296E-5</v>
       </c>
       <c r="L28">
-        <v>1.0117371643853877E-4</v>
+        <v>1.0117371643853889E-4</v>
       </c>
       <c r="M28">
-        <v>-4.8256077991982637E-5</v>
+        <v>-4.8256077991980374E-5</v>
       </c>
       <c r="N28">
-        <v>-5.0129465975949538E-5</v>
+        <v>-5.0129465975949593E-5</v>
       </c>
       <c r="O28">
-        <v>-3.6227492135023581E-5</v>
+        <v>-3.6227492135020497E-5</v>
       </c>
       <c r="P28">
-        <v>-5.0072296371223493E-5</v>
+        <v>-5.0072296371223039E-5</v>
       </c>
       <c r="Q28">
-        <v>-6.509150997918161E-5</v>
+        <v>-6.5091509979180756E-5</v>
       </c>
       <c r="R28">
-        <v>9.5667861141264576E-7</v>
+        <v>9.5667861141266355E-7</v>
       </c>
       <c r="S28">
-        <v>1.4441917380431773E-6</v>
+        <v>1.444191738043176E-6</v>
       </c>
       <c r="T28">
-        <v>-6.4218361472962972E-5</v>
+        <v>-6.421836147296262E-5</v>
       </c>
       <c r="U28">
-        <v>-7.4888902913436081E-5</v>
+        <v>-7.4888902913436027E-5</v>
       </c>
       <c r="V28">
-        <v>-6.1102469237547038E-5</v>
+        <v>-6.1102469237546875E-5</v>
       </c>
       <c r="W28">
-        <v>2.6603497878505821E-6</v>
+        <v>2.6603497878507125E-6</v>
       </c>
       <c r="X28">
-        <v>4.709381224881867E-6</v>
+        <v>4.7093812248819204E-6</v>
       </c>
       <c r="Y28">
-        <v>-1.7461209962555666E-6</v>
+        <v>-1.7461209962554059E-6</v>
       </c>
       <c r="Z28">
         <v>7.4787480026574358E-4</v>
       </c>
       <c r="AA28">
-        <v>7.6110629188786978E-4</v>
+        <v>7.6110629188786989E-4</v>
       </c>
       <c r="AB28">
-        <v>7.3991240095867957E-4</v>
+        <v>7.3991240095867968E-4</v>
       </c>
       <c r="AC28">
-        <v>1.5011445640914103E-3</v>
+        <v>1.5011445640914101E-3</v>
       </c>
       <c r="AD28">
         <v>7.0810320904198562E-4</v>
       </c>
       <c r="AE28">
-        <v>7.361068216457916E-4</v>
+        <v>7.3610682164579279E-4</v>
       </c>
       <c r="AF28">
         <v>7.6094771021342029E-4</v>
       </c>
       <c r="AG28">
-        <v>7.5572350659418492E-4</v>
+        <v>7.5572350659418601E-4</v>
       </c>
       <c r="AH28">
-        <v>7.6356677636898551E-4</v>
+        <v>7.6356677636898584E-4</v>
       </c>
       <c r="AI28">
-        <v>7.3124499252540348E-4</v>
+        <v>7.312449925254037E-4</v>
       </c>
       <c r="AJ28">
-        <v>7.512500511690915E-4</v>
+        <v>7.5125005116909291E-4</v>
       </c>
       <c r="AK28">
-        <v>-1.6351559695978535E-7</v>
+        <v>-1.6351559695964983E-7</v>
       </c>
       <c r="AL28">
-        <v>3.9399127541021737E-5</v>
+        <v>3.9399127541021222E-5</v>
       </c>
       <c r="AM28">
-        <v>-6.6095193044127623E-7</v>
+        <v>-6.6095193044184543E-7</v>
       </c>
       <c r="AN28">
-        <v>3.5577701878915561E-4</v>
+        <v>3.5577701878915496E-4</v>
       </c>
       <c r="AO28">
-        <v>3.6237658942931599E-4</v>
+        <v>3.623765894293155E-4</v>
       </c>
       <c r="AP28">
-        <v>1.5633072236814291E-4</v>
+        <v>1.5633072236814256E-4</v>
       </c>
       <c r="AQ28">
-        <v>-8.9412996349830405E-4</v>
+        <v>-8.9412996349832042E-4</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.2">
@@ -4435,127 +4429,127 @@
         <v>0.24119524108849472</v>
       </c>
       <c r="C29">
-        <v>9.8638238250881819E-6</v>
+        <v>9.8638238250881853E-6</v>
       </c>
       <c r="D29">
-        <v>-1.7550097060608648E-6</v>
+        <v>-1.755009706060648E-6</v>
       </c>
       <c r="E29">
-        <v>3.1891023417151982E-8</v>
+        <v>3.1891023417150023E-8</v>
       </c>
       <c r="F29">
-        <v>1.7463949362533308E-4</v>
+        <v>1.7463949362533454E-4</v>
       </c>
       <c r="G29">
-        <v>-2.7076336599812296E-5</v>
+        <v>-2.7076336599811374E-5</v>
       </c>
       <c r="H29">
-        <v>3.5309338747711492E-6</v>
+        <v>3.5309338747718268E-6</v>
       </c>
       <c r="I29">
-        <v>-5.6695689615589702E-5</v>
+        <v>-5.6695689615589065E-5</v>
       </c>
       <c r="J29">
-        <v>2.8703307502328491E-5</v>
+        <v>2.8703307502329087E-5</v>
       </c>
       <c r="K29">
-        <v>6.1089026213288278E-5</v>
+        <v>6.1089026213289688E-5</v>
       </c>
       <c r="L29">
-        <v>-2.0070685526101992E-6</v>
+        <v>-2.0070685526090337E-6</v>
       </c>
       <c r="M29">
-        <v>-5.2392372042240828E-5</v>
+        <v>-5.2392372042239473E-5</v>
       </c>
       <c r="N29">
-        <v>1.665977496860565E-5</v>
+        <v>1.6659774968606788E-5</v>
       </c>
       <c r="O29">
-        <v>-3.9881871100633758E-5</v>
+        <v>-3.9881871100631914E-5</v>
       </c>
       <c r="P29">
-        <v>-3.4080668034028742E-5</v>
+        <v>-3.4080668034028701E-5</v>
       </c>
       <c r="Q29">
-        <v>-6.868166203677031E-6</v>
+        <v>-6.8681662036768412E-6</v>
       </c>
       <c r="R29">
-        <v>2.3295339590020807E-6</v>
+        <v>2.3295339590021383E-6</v>
       </c>
       <c r="S29">
-        <v>3.0555373342077059E-6</v>
+        <v>3.0555373342077703E-6</v>
       </c>
       <c r="T29">
-        <v>-1.3074955380070619E-5</v>
+        <v>-1.3074955380069887E-5</v>
       </c>
       <c r="U29">
-        <v>-4.958481719039202E-5</v>
+        <v>-4.9584817190391343E-5</v>
       </c>
       <c r="V29">
-        <v>-1.6962377483280234E-5</v>
+        <v>-1.696237748327915E-5</v>
       </c>
       <c r="W29">
-        <v>1.3311531076106819E-5</v>
+        <v>1.3311531076107416E-5</v>
       </c>
       <c r="X29">
-        <v>7.9506036482359879E-6</v>
+        <v>7.9506036482358744E-6</v>
       </c>
       <c r="Y29">
-        <v>-1.5210288610090506E-5</v>
+        <v>-1.5210288610090774E-5</v>
       </c>
       <c r="Z29">
         <v>7.1632360716470734E-4</v>
       </c>
       <c r="AA29">
-        <v>7.1582806530391902E-4</v>
+        <v>7.1582806530391934E-4</v>
       </c>
       <c r="AB29">
-        <v>7.0372975942405212E-4</v>
+        <v>7.0372975942405223E-4</v>
       </c>
       <c r="AC29">
         <v>7.0810320904198562E-4</v>
       </c>
       <c r="AD29">
-        <v>1.5775495779269632E-3</v>
+        <v>1.5775495779269629E-3</v>
       </c>
       <c r="AE29">
-        <v>7.1170950198479145E-4</v>
+        <v>7.1170950198479264E-4</v>
       </c>
       <c r="AF29">
-        <v>7.2540991627650713E-4</v>
+        <v>7.2540991627650703E-4</v>
       </c>
       <c r="AG29">
-        <v>7.2014888669303398E-4</v>
+        <v>7.2014888669303485E-4</v>
       </c>
       <c r="AH29">
-        <v>7.2996092153206754E-4</v>
+        <v>7.2996092153206809E-4</v>
       </c>
       <c r="AI29">
         <v>7.0524345154143958E-4</v>
       </c>
       <c r="AJ29">
-        <v>7.1722419945449093E-4</v>
+        <v>7.1722419945449212E-4</v>
       </c>
       <c r="AK29">
-        <v>5.0225066063041825E-6</v>
+        <v>5.0225066063042909E-6</v>
       </c>
       <c r="AL29">
-        <v>2.453419465443628E-5</v>
+        <v>2.4534194654435819E-5</v>
       </c>
       <c r="AM29">
-        <v>-1.6385837844701495E-5</v>
+        <v>-1.6385837844701929E-5</v>
       </c>
       <c r="AN29">
-        <v>2.519451660062277E-4</v>
+        <v>2.5194516600622716E-4</v>
       </c>
       <c r="AO29">
-        <v>2.5536412099808796E-4</v>
+        <v>2.5536412099808742E-4</v>
       </c>
       <c r="AP29">
-        <v>1.0386015992686103E-4</v>
+        <v>1.0386015992686073E-4</v>
       </c>
       <c r="AQ29">
-        <v>-1.0671680372188875E-3</v>
+        <v>-1.0671680372189051E-3</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.2">
@@ -4566,127 +4560,127 @@
         <v>0.17254371301921609</v>
       </c>
       <c r="C30">
-        <v>1.1707726106089E-6</v>
+        <v>1.1707726106089339E-6</v>
       </c>
       <c r="D30">
-        <v>-5.380086323422273E-7</v>
+        <v>-5.3800863234197319E-7</v>
       </c>
       <c r="E30">
-        <v>5.7308876488009801E-9</v>
+        <v>5.7308876487989684E-9</v>
       </c>
       <c r="F30">
-        <v>1.3537401281889813E-5</v>
+        <v>1.353740128189228E-5</v>
       </c>
       <c r="G30">
-        <v>3.417940781260557E-5</v>
+        <v>3.4179407812607407E-5</v>
       </c>
       <c r="H30">
-        <v>-2.4259919458970088E-6</v>
+        <v>-2.4259919458952063E-6</v>
       </c>
       <c r="I30">
-        <v>1.2634464412900282E-5</v>
+        <v>1.2634464412902599E-5</v>
       </c>
       <c r="J30">
-        <v>2.4856407070118303E-5</v>
+        <v>2.4856407070120417E-5</v>
       </c>
       <c r="K30">
-        <v>6.6286521729026188E-5</v>
+        <v>6.6286521729028803E-5</v>
       </c>
       <c r="L30">
-        <v>8.1815627285201594E-5</v>
+        <v>8.1815627285204007E-5</v>
       </c>
       <c r="M30">
-        <v>-7.5121324619838891E-5</v>
+        <v>-7.5121324619836506E-5</v>
       </c>
       <c r="N30">
-        <v>-6.4531435307838898E-5</v>
+        <v>-6.4531435307836756E-5</v>
       </c>
       <c r="O30">
-        <v>-7.5098127813274834E-5</v>
+        <v>-7.5098127813273615E-5</v>
       </c>
       <c r="P30">
-        <v>-4.6758089173920948E-5</v>
+        <v>-4.6758089173920278E-5</v>
       </c>
       <c r="Q30">
-        <v>-3.7631187956116328E-5</v>
+        <v>-3.7631187956115223E-5</v>
       </c>
       <c r="R30">
-        <v>1.861160247108241E-6</v>
+        <v>1.8611602471083274E-6</v>
       </c>
       <c r="S30">
-        <v>1.2878337366921464E-6</v>
+        <v>1.2878337366922777E-6</v>
       </c>
       <c r="T30">
-        <v>-1.0236663306032264E-4</v>
+        <v>-1.0236663306032121E-4</v>
       </c>
       <c r="U30">
-        <v>-1.2705014471360609E-4</v>
+        <v>-1.2705014471360454E-4</v>
       </c>
       <c r="V30">
-        <v>-9.7436342027805878E-5</v>
+        <v>-9.7436342027804089E-5</v>
       </c>
       <c r="W30">
-        <v>-4.9966637432240349E-5</v>
+        <v>-4.996663743223837E-5</v>
       </c>
       <c r="X30">
-        <v>1.0765277846094642E-5</v>
+        <v>1.0765277846094515E-5</v>
       </c>
       <c r="Y30">
-        <v>2.0607156288907608E-5</v>
+        <v>2.0607156288907795E-5</v>
       </c>
       <c r="Z30">
-        <v>7.550145523109096E-4</v>
+        <v>7.5501455231091101E-4</v>
       </c>
       <c r="AA30">
-        <v>7.6784052700741719E-4</v>
+        <v>7.6784052700741849E-4</v>
       </c>
       <c r="AB30">
-        <v>7.4286054183321396E-4</v>
+        <v>7.4286054183321504E-4</v>
       </c>
       <c r="AC30">
-        <v>7.361068216457916E-4</v>
+        <v>7.3610682164579279E-4</v>
       </c>
       <c r="AD30">
-        <v>7.1170950198479145E-4</v>
+        <v>7.1170950198479264E-4</v>
       </c>
       <c r="AE30">
-        <v>1.3293294989884833E-3</v>
+        <v>1.3293294989884844E-3</v>
       </c>
       <c r="AF30">
-        <v>7.6697621586470669E-4</v>
+        <v>7.6697621586470702E-4</v>
       </c>
       <c r="AG30">
-        <v>7.6544278559137881E-4</v>
+        <v>7.6544278559138E-4</v>
       </c>
       <c r="AH30">
-        <v>7.6283076917153781E-4</v>
+        <v>7.6283076917153846E-4</v>
       </c>
       <c r="AI30">
-        <v>7.4789339007903083E-4</v>
+        <v>7.4789339007903138E-4</v>
       </c>
       <c r="AJ30">
-        <v>7.5594023651026133E-4</v>
+        <v>7.5594023651026263E-4</v>
       </c>
       <c r="AK30">
-        <v>-1.8291446418303723E-6</v>
+        <v>-1.8291446418301961E-6</v>
       </c>
       <c r="AL30">
-        <v>3.8910220723056035E-5</v>
+        <v>3.8910220723055493E-5</v>
       </c>
       <c r="AM30">
-        <v>7.7361081896957769E-6</v>
+        <v>7.7361081896950722E-6</v>
       </c>
       <c r="AN30">
-        <v>3.6283458477464426E-4</v>
+        <v>3.6283458477464394E-4</v>
       </c>
       <c r="AO30">
-        <v>3.7037320868375784E-4</v>
+        <v>3.7037320868375741E-4</v>
       </c>
       <c r="AP30">
-        <v>8.1505091668721672E-5</v>
+        <v>8.1505091668721536E-5</v>
       </c>
       <c r="AQ30">
-        <v>-8.0569875164453598E-4</v>
+        <v>-8.0569875164455593E-4</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.2">
@@ -4697,127 +4691,127 @@
         <v>0.1723510910659582</v>
       </c>
       <c r="C31">
-        <v>1.3265544569139946E-5</v>
+        <v>1.3265544569140191E-5</v>
       </c>
       <c r="D31">
-        <v>-1.1732734063388387E-6</v>
+        <v>-1.1732734063388366E-6</v>
       </c>
       <c r="E31">
-        <v>6.8595281824058502E-9</v>
+        <v>6.8595281824057973E-9</v>
       </c>
       <c r="F31">
-        <v>5.6339334809153123E-5</v>
+        <v>5.6339334809153557E-5</v>
       </c>
       <c r="G31">
-        <v>6.0167040611791025E-5</v>
+        <v>6.0167040611791797E-5</v>
       </c>
       <c r="H31">
-        <v>1.2135610741111388E-5</v>
+        <v>1.2135610741112153E-5</v>
       </c>
       <c r="I31">
-        <v>1.8205980953951656E-5</v>
+        <v>1.8205980953952517E-5</v>
       </c>
       <c r="J31">
-        <v>3.9582490462197041E-5</v>
+        <v>3.9582490462197916E-5</v>
       </c>
       <c r="K31">
-        <v>7.1528282831583414E-5</v>
+        <v>7.1528282831584281E-5</v>
       </c>
       <c r="L31">
-        <v>3.9811978649014707E-5</v>
+        <v>3.9811978649015683E-5</v>
       </c>
       <c r="M31">
-        <v>-9.3145208914089102E-5</v>
+        <v>-9.3145208914088926E-5</v>
       </c>
       <c r="N31">
-        <v>-4.7992317119584821E-5</v>
+        <v>-4.799231711958478E-5</v>
       </c>
       <c r="O31">
-        <v>-4.5983987193006496E-5</v>
+        <v>-4.5983987193006388E-5</v>
       </c>
       <c r="P31">
-        <v>-2.8765651174544882E-5</v>
+        <v>-2.8765651174544523E-5</v>
       </c>
       <c r="Q31">
-        <v>-2.2762734449607715E-5</v>
+        <v>-2.2762734449607295E-5</v>
       </c>
       <c r="R31">
-        <v>1.6305010205535002E-6</v>
+        <v>1.6305010205535036E-6</v>
       </c>
       <c r="S31">
-        <v>1.1058903538892655E-6</v>
+        <v>1.1058903538892659E-6</v>
       </c>
       <c r="T31">
-        <v>-6.371038590301462E-5</v>
+        <v>-6.3710385903014417E-5</v>
       </c>
       <c r="U31">
-        <v>-1.0936706202805714E-4</v>
+        <v>-1.0936706202805687E-4</v>
       </c>
       <c r="V31">
-        <v>-6.0840869958251562E-5</v>
+        <v>-6.0840869958251115E-5</v>
       </c>
       <c r="W31">
-        <v>-2.0407541310214171E-5</v>
+        <v>-2.0407541310213589E-5</v>
       </c>
       <c r="X31">
-        <v>6.1319733205818757E-6</v>
+        <v>6.1319733205818613E-6</v>
       </c>
       <c r="Y31">
-        <v>9.8331796399977138E-6</v>
+        <v>9.8331796399977968E-6</v>
       </c>
       <c r="Z31">
-        <v>7.7699909288053996E-4</v>
+        <v>7.7699909288054018E-4</v>
       </c>
       <c r="AA31">
-        <v>7.7867231578512884E-4</v>
+        <v>7.7867231578512895E-4</v>
       </c>
       <c r="AB31">
-        <v>7.6006349065540048E-4</v>
+        <v>7.600634906554007E-4</v>
       </c>
       <c r="AC31">
         <v>7.6094771021342029E-4</v>
       </c>
       <c r="AD31">
-        <v>7.2540991627650713E-4</v>
+        <v>7.2540991627650703E-4</v>
       </c>
       <c r="AE31">
-        <v>7.6697621586470669E-4</v>
+        <v>7.6697621586470702E-4</v>
       </c>
       <c r="AF31">
         <v>1.2539018697873318E-3</v>
       </c>
       <c r="AG31">
-        <v>7.8266815795799438E-4</v>
+        <v>7.8266815795799535E-4</v>
       </c>
       <c r="AH31">
-        <v>7.8052871448417371E-4</v>
+        <v>7.8052871448417436E-4</v>
       </c>
       <c r="AI31">
-        <v>7.6371479598301114E-4</v>
+        <v>7.6371479598301136E-4</v>
       </c>
       <c r="AJ31">
-        <v>7.7476239923824979E-4</v>
+        <v>7.7476239923825099E-4</v>
       </c>
       <c r="AK31">
-        <v>-3.0148453066603301E-7</v>
+        <v>-3.0148453066589748E-7</v>
       </c>
       <c r="AL31">
-        <v>1.4159230250620407E-5</v>
+        <v>1.4159230250619946E-5</v>
       </c>
       <c r="AM31">
-        <v>-3.9086952848728384E-6</v>
+        <v>-3.9086952848735432E-6</v>
       </c>
       <c r="AN31">
-        <v>4.0313852647264769E-4</v>
+        <v>4.031385264726472E-4</v>
       </c>
       <c r="AO31">
-        <v>4.538236365014742E-4</v>
+        <v>4.5382363650147382E-4</v>
       </c>
       <c r="AP31">
-        <v>1.3906624210919795E-4</v>
+        <v>1.3906624210919763E-4</v>
       </c>
       <c r="AQ31">
-        <v>-8.4645066631172682E-4</v>
+        <v>-8.4645066631174439E-4</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.2">
@@ -4828,127 +4822,127 @@
         <v>0.17189564764273826</v>
       </c>
       <c r="C32">
-        <v>1.6010176626664494E-5</v>
+        <v>1.6010176626664653E-5</v>
       </c>
       <c r="D32">
-        <v>2.2386440755936066E-6</v>
+        <v>2.238644075594053E-6</v>
       </c>
       <c r="E32">
-        <v>-2.7341669616014112E-8</v>
+        <v>-2.7341669616018331E-8</v>
       </c>
       <c r="F32">
-        <v>7.2549263802658252E-5</v>
+        <v>7.2549263802661776E-5</v>
       </c>
       <c r="G32">
-        <v>4.5790779789221042E-5</v>
+        <v>4.5790779789223523E-5</v>
       </c>
       <c r="H32">
-        <v>1.0646501247680785E-5</v>
+        <v>1.0646501247682945E-5</v>
       </c>
       <c r="I32">
-        <v>4.2619576812610648E-5</v>
+        <v>4.2619576812613034E-5</v>
       </c>
       <c r="J32">
-        <v>6.4084318226283464E-5</v>
+        <v>6.4084318226285836E-5</v>
       </c>
       <c r="K32">
-        <v>7.8113270531383227E-5</v>
+        <v>7.8113270531386859E-5</v>
       </c>
       <c r="L32">
-        <v>3.3611327592697259E-5</v>
+        <v>3.3611327592700268E-5</v>
       </c>
       <c r="M32">
-        <v>-7.7223843157840763E-5</v>
+        <v>-7.7223843157837673E-5</v>
       </c>
       <c r="N32">
-        <v>-4.6559863675810631E-5</v>
+        <v>-4.655986367580893E-5</v>
       </c>
       <c r="O32">
-        <v>-3.1009572311479485E-5</v>
+        <v>-3.1009572311476883E-5</v>
       </c>
       <c r="P32">
-        <v>-3.3154601384905038E-5</v>
+        <v>-3.315460138490455E-5</v>
       </c>
       <c r="Q32">
-        <v>-1.4122926656044935E-5</v>
+        <v>-1.4122926656044249E-5</v>
       </c>
       <c r="R32">
-        <v>4.5757298848168299E-7</v>
+        <v>4.5757298848173339E-7</v>
       </c>
       <c r="S32">
-        <v>2.1224009477937054E-6</v>
+        <v>2.1224009477937668E-6</v>
       </c>
       <c r="T32">
-        <v>-1.0070549821154497E-4</v>
+        <v>-1.007054982115433E-4</v>
       </c>
       <c r="U32">
-        <v>-1.2189741840338278E-4</v>
+        <v>-1.2189741840338078E-4</v>
       </c>
       <c r="V32">
-        <v>-8.9326957455047447E-5</v>
+        <v>-8.9326957455045198E-5</v>
       </c>
       <c r="W32">
-        <v>-2.4757502982398743E-5</v>
+        <v>-2.4757502982396263E-5</v>
       </c>
       <c r="X32">
-        <v>7.4327991648870512E-6</v>
+        <v>7.4327991648868877E-6</v>
       </c>
       <c r="Y32">
-        <v>3.6750717129365831E-5</v>
+        <v>3.675071712936577E-5</v>
       </c>
       <c r="Z32">
-        <v>7.693773324055456E-4</v>
+        <v>7.693773324055469E-4</v>
       </c>
       <c r="AA32">
-        <v>7.8430937845117054E-4</v>
+        <v>7.8430937845117173E-4</v>
       </c>
       <c r="AB32">
-        <v>7.5936487329163551E-4</v>
+        <v>7.5936487329163638E-4</v>
       </c>
       <c r="AC32">
-        <v>7.5572350659418492E-4</v>
+        <v>7.5572350659418601E-4</v>
       </c>
       <c r="AD32">
-        <v>7.2014888669303398E-4</v>
+        <v>7.2014888669303485E-4</v>
       </c>
       <c r="AE32">
-        <v>7.6544278559137881E-4</v>
+        <v>7.6544278559138E-4</v>
       </c>
       <c r="AF32">
-        <v>7.8266815795799438E-4</v>
+        <v>7.8266815795799535E-4</v>
       </c>
       <c r="AG32">
-        <v>1.4677620688006178E-3</v>
+        <v>1.4677620688006189E-3</v>
       </c>
       <c r="AH32">
-        <v>7.750593445862657E-4</v>
+        <v>7.7505934458626624E-4</v>
       </c>
       <c r="AI32">
-        <v>7.619877931902974E-4</v>
+        <v>7.6198779319029762E-4</v>
       </c>
       <c r="AJ32">
-        <v>7.7450408603590027E-4</v>
+        <v>7.7450408603590157E-4</v>
       </c>
       <c r="AK32">
-        <v>1.5609863016137644E-6</v>
+        <v>1.5609863016138864E-6</v>
       </c>
       <c r="AL32">
-        <v>3.565577403068194E-5</v>
+        <v>3.5655774030681425E-5</v>
       </c>
       <c r="AM32">
-        <v>4.8440844445908561E-6</v>
+        <v>4.8440844445902598E-6</v>
       </c>
       <c r="AN32">
-        <v>4.1317050690739868E-4</v>
+        <v>4.1317050690739792E-4</v>
       </c>
       <c r="AO32">
-        <v>4.2125340029787841E-4</v>
+        <v>4.2125340029787792E-4</v>
       </c>
       <c r="AP32">
-        <v>1.679526220000061E-4</v>
+        <v>1.679526220000058E-4</v>
       </c>
       <c r="AQ32">
-        <v>-9.4795639767386542E-4</v>
+        <v>-9.4795639767388602E-4</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.2">
@@ -4959,127 +4953,127 @@
         <v>0.23367794163863631</v>
       </c>
       <c r="C33">
-        <v>5.8296923045337368E-5</v>
+        <v>5.8296923045337124E-5</v>
       </c>
       <c r="D33">
-        <v>-6.0326533419206095E-7</v>
+        <v>-6.032653341916476E-7</v>
       </c>
       <c r="E33">
-        <v>6.414093021727785E-9</v>
+        <v>6.4140930217235499E-9</v>
       </c>
       <c r="F33">
-        <v>8.1294174609361622E-5</v>
+        <v>8.129417460936295E-5</v>
       </c>
       <c r="G33">
-        <v>8.2417209680077236E-5</v>
+        <v>8.24172096800779E-5</v>
       </c>
       <c r="H33">
-        <v>7.9261892200310823E-5</v>
+        <v>7.9261892200311338E-5</v>
       </c>
       <c r="I33">
-        <v>2.0120935756152304E-5</v>
+        <v>2.0120935756152914E-5</v>
       </c>
       <c r="J33">
-        <v>6.5673054719547137E-5</v>
+        <v>6.567305471954776E-5</v>
       </c>
       <c r="K33">
-        <v>1.2575875012095644E-4</v>
+        <v>1.257587501209579E-4</v>
       </c>
       <c r="L33">
-        <v>8.1296279798946804E-5</v>
+        <v>8.1296279798947428E-5</v>
       </c>
       <c r="M33">
-        <v>-3.238662415237098E-5</v>
+        <v>-3.2386624152369137E-5</v>
       </c>
       <c r="N33">
-        <v>-5.0729066942762838E-5</v>
+        <v>-5.0729066942761998E-5</v>
       </c>
       <c r="O33">
-        <v>-4.7042669894432096E-5</v>
+        <v>-4.7042669894429304E-5</v>
       </c>
       <c r="P33">
-        <v>-7.2744924350735894E-5</v>
+        <v>-7.2744924350735704E-5</v>
       </c>
       <c r="Q33">
-        <v>-5.8817254954288322E-5</v>
+        <v>-5.8817254954287726E-5</v>
       </c>
       <c r="R33">
-        <v>-4.6269263056545673E-8</v>
+        <v>-4.6269263056471134E-8</v>
       </c>
       <c r="S33">
-        <v>1.7949373561311511E-6</v>
+        <v>1.7949373561312164E-6</v>
       </c>
       <c r="T33">
-        <v>-5.6119967496870443E-5</v>
+        <v>-5.6119967496869711E-5</v>
       </c>
       <c r="U33">
-        <v>-7.8849646958014522E-5</v>
+        <v>-7.8849646958013925E-5</v>
       </c>
       <c r="V33">
-        <v>-3.2931007509360891E-5</v>
+        <v>-3.2931007509360294E-5</v>
       </c>
       <c r="W33">
-        <v>5.4323512462519023E-5</v>
+        <v>5.4323512462519348E-5</v>
       </c>
       <c r="X33">
-        <v>6.205263403363483E-6</v>
+        <v>6.2052634033634271E-6</v>
       </c>
       <c r="Y33">
-        <v>1.5277720187865527E-5</v>
+        <v>1.5277720187865425E-5</v>
       </c>
       <c r="Z33">
-        <v>7.6273160318997366E-4</v>
+        <v>7.6273160318997399E-4</v>
       </c>
       <c r="AA33">
-        <v>7.7433551300843144E-4</v>
+        <v>7.7433551300843187E-4</v>
       </c>
       <c r="AB33">
-        <v>7.610793717362091E-4</v>
+        <v>7.6107937173620953E-4</v>
       </c>
       <c r="AC33">
-        <v>7.6356677636898551E-4</v>
+        <v>7.6356677636898584E-4</v>
       </c>
       <c r="AD33">
-        <v>7.2996092153206754E-4</v>
+        <v>7.2996092153206809E-4</v>
       </c>
       <c r="AE33">
-        <v>7.6283076917153781E-4</v>
+        <v>7.6283076917153846E-4</v>
       </c>
       <c r="AF33">
-        <v>7.8052871448417371E-4</v>
+        <v>7.8052871448417436E-4</v>
       </c>
       <c r="AG33">
-        <v>7.750593445862657E-4</v>
+        <v>7.7505934458626624E-4</v>
       </c>
       <c r="AH33">
-        <v>1.8063757651037822E-3</v>
+        <v>1.8063757651037827E-3</v>
       </c>
       <c r="AI33">
-        <v>7.6229310677184965E-4</v>
+        <v>7.6229310677184976E-4</v>
       </c>
       <c r="AJ33">
-        <v>7.8562042983484665E-4</v>
+        <v>7.8562042983484795E-4</v>
       </c>
       <c r="AK33">
-        <v>3.4652889032662815E-6</v>
+        <v>3.4652889032663628E-6</v>
       </c>
       <c r="AL33">
-        <v>4.9996074257607022E-6</v>
+        <v>4.9996074257602956E-6</v>
       </c>
       <c r="AM33">
-        <v>-3.90904381029371E-5</v>
+        <v>-3.9090438102937561E-5</v>
       </c>
       <c r="AN33">
-        <v>3.7974521770316888E-4</v>
+        <v>3.7974521770316828E-4</v>
       </c>
       <c r="AO33">
-        <v>4.1354276603727726E-4</v>
+        <v>4.1354276603727661E-4</v>
       </c>
       <c r="AP33">
-        <v>1.3766436870969563E-4</v>
+        <v>1.3766436870969522E-4</v>
       </c>
       <c r="AQ33">
-        <v>-9.5311335697661765E-4</v>
+        <v>-9.5311335697663034E-4</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.2">
@@ -5090,127 +5084,127 @@
         <v>0.14091350168386374</v>
       </c>
       <c r="C34">
-        <v>5.3311968753028329E-5</v>
+        <v>5.3311968753028356E-5</v>
       </c>
       <c r="D34">
-        <v>-2.5941061600834274E-6</v>
+        <v>-2.5941061600832292E-6</v>
       </c>
       <c r="E34">
-        <v>2.1617943775583462E-8</v>
+        <v>2.1617943775581397E-8</v>
       </c>
       <c r="F34">
-        <v>-1.1935451546435144E-7</v>
+        <v>-1.193545154633079E-7</v>
       </c>
       <c r="G34">
-        <v>-1.0263090904517983E-5</v>
+        <v>-1.0263090904517292E-5</v>
       </c>
       <c r="H34">
-        <v>-5.0683902400714418E-5</v>
+        <v>-5.0683902400713835E-5</v>
       </c>
       <c r="I34">
-        <v>-7.1353744195980115E-5</v>
+        <v>-7.13537441959796E-5</v>
       </c>
       <c r="J34">
-        <v>-1.3120477274821793E-5</v>
+        <v>-1.3120477274821305E-5</v>
       </c>
       <c r="K34">
-        <v>2.226288709827314E-5</v>
+        <v>2.2262887098274163E-5</v>
       </c>
       <c r="L34">
-        <v>-2.4066676115797527E-5</v>
+        <v>-2.4066676115796985E-5</v>
       </c>
       <c r="M34">
-        <v>-1.1727002339032079E-4</v>
+        <v>-1.1727002339032006E-4</v>
       </c>
       <c r="N34">
-        <v>-7.1832354904920583E-5</v>
+        <v>-7.1832354904920827E-5</v>
       </c>
       <c r="O34">
-        <v>-1.0074407885215658E-4</v>
+        <v>-1.0074407885215577E-4</v>
       </c>
       <c r="P34">
-        <v>-5.1069377647702127E-5</v>
+        <v>-5.1069377647701991E-5</v>
       </c>
       <c r="Q34">
-        <v>-3.8382906244001269E-5</v>
+        <v>-3.838290624400074E-5</v>
       </c>
       <c r="R34">
-        <v>6.5241491009719002E-7</v>
+        <v>6.5241491009719912E-7</v>
       </c>
       <c r="S34">
-        <v>1.2552053985589265E-6</v>
+        <v>1.255205398558928E-6</v>
       </c>
       <c r="T34">
-        <v>-8.668045482080331E-5</v>
+        <v>-8.6680454820802877E-5</v>
       </c>
       <c r="U34">
-        <v>-1.2514452539871273E-4</v>
+        <v>-1.2514452539871249E-4</v>
       </c>
       <c r="V34">
-        <v>-1.1961983438036681E-4</v>
+        <v>-1.1961983438036667E-4</v>
       </c>
       <c r="W34">
         <v>-8.782909803770575E-5</v>
       </c>
       <c r="X34">
-        <v>1.0328813921610181E-5</v>
+        <v>1.032881392161015E-5</v>
       </c>
       <c r="Y34">
-        <v>2.6555133209520629E-5</v>
+        <v>2.6555133209520663E-5</v>
       </c>
       <c r="Z34">
-        <v>7.5720573404033454E-4</v>
+        <v>7.5720573404033475E-4</v>
       </c>
       <c r="AA34">
-        <v>7.6157320364625728E-4</v>
+        <v>7.6157320364625739E-4</v>
       </c>
       <c r="AB34">
-        <v>7.3781523166903016E-4</v>
+        <v>7.3781523166903038E-4</v>
       </c>
       <c r="AC34">
-        <v>7.3124499252540348E-4</v>
+        <v>7.312449925254037E-4</v>
       </c>
       <c r="AD34">
         <v>7.0524345154143958E-4</v>
       </c>
       <c r="AE34">
-        <v>7.4789339007903083E-4</v>
+        <v>7.4789339007903138E-4</v>
       </c>
       <c r="AF34">
-        <v>7.6371479598301114E-4</v>
+        <v>7.6371479598301136E-4</v>
       </c>
       <c r="AG34">
-        <v>7.619877931902974E-4</v>
+        <v>7.6198779319029762E-4</v>
       </c>
       <c r="AH34">
-        <v>7.6229310677184965E-4</v>
+        <v>7.6229310677184976E-4</v>
       </c>
       <c r="AI34">
         <v>1.3621672254674972E-3</v>
       </c>
       <c r="AJ34">
-        <v>7.5635114519675734E-4</v>
+        <v>7.5635114519675853E-4</v>
       </c>
       <c r="AK34">
-        <v>2.4859443049534736E-7</v>
+        <v>2.4859443049538802E-7</v>
       </c>
       <c r="AL34">
-        <v>2.5396689358757644E-5</v>
+        <v>2.5396689358757237E-5</v>
       </c>
       <c r="AM34">
-        <v>-2.4094375958101839E-5</v>
+        <v>-2.4094375958102191E-5</v>
       </c>
       <c r="AN34">
-        <v>3.7869190555775504E-4</v>
+        <v>3.786919055577545E-4</v>
       </c>
       <c r="AO34">
-        <v>3.8213493631657029E-4</v>
+        <v>3.8213493631656992E-4</v>
       </c>
       <c r="AP34">
-        <v>1.5770781126099801E-4</v>
+        <v>1.5770781126099766E-4</v>
       </c>
       <c r="AQ34">
-        <v>-6.8489990643275924E-4</v>
+        <v>-6.8489990643277507E-4</v>
       </c>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.2">
@@ -5221,127 +5215,127 @@
         <v>0.30290679674202742</v>
       </c>
       <c r="C35">
-        <v>1.8319910200220186E-5</v>
+        <v>1.8319910200220579E-5</v>
       </c>
       <c r="D35">
-        <v>1.0391713542184542E-6</v>
+        <v>1.039171354219037E-6</v>
       </c>
       <c r="E35">
-        <v>-8.3040855573977436E-9</v>
+        <v>-8.3040855574029317E-9</v>
       </c>
       <c r="F35">
-        <v>1.0343462939672773E-4</v>
+        <v>1.0343462939673212E-4</v>
       </c>
       <c r="G35">
-        <v>3.8272565510345097E-5</v>
+        <v>3.8272565510348187E-5</v>
       </c>
       <c r="H35">
-        <v>6.7301913658924638E-6</v>
+        <v>6.730191365895337E-6</v>
       </c>
       <c r="I35">
-        <v>4.3285807418827656E-5</v>
+        <v>4.3285807418830908E-5</v>
       </c>
       <c r="J35">
-        <v>3.0340055453893279E-5</v>
+        <v>3.034005545389626E-5</v>
       </c>
       <c r="K35">
-        <v>4.9603539928871746E-5</v>
+        <v>4.9603539928876354E-5</v>
       </c>
       <c r="L35">
-        <v>1.1916052073412801E-5</v>
+        <v>1.191605207341665E-5</v>
       </c>
       <c r="M35">
-        <v>-4.4754407273305073E-5</v>
+        <v>-4.4754407273300953E-5</v>
       </c>
       <c r="N35">
-        <v>-6.818365065441661E-5</v>
+        <v>-6.8183650654414442E-5</v>
       </c>
       <c r="O35">
-        <v>-4.9305930858369203E-5</v>
+        <v>-4.9305930858366547E-5</v>
       </c>
       <c r="P35">
-        <v>-1.0949375670774226E-5</v>
+        <v>-1.0949375670773792E-5</v>
       </c>
       <c r="Q35">
-        <v>-3.0873430161111945E-5</v>
+        <v>-3.0873430161111322E-5</v>
       </c>
       <c r="R35">
-        <v>9.8272188761751689E-7</v>
+        <v>9.827218876176016E-7</v>
       </c>
       <c r="S35">
-        <v>1.7837850240596663E-6</v>
+        <v>1.7837850240597375E-6</v>
       </c>
       <c r="T35">
-        <v>-6.1006798192371091E-5</v>
+        <v>-6.1006798192369193E-5</v>
       </c>
       <c r="U35">
-        <v>-8.8118282280409427E-5</v>
+        <v>-8.811828228040753E-5</v>
       </c>
       <c r="V35">
-        <v>-3.7001550324963599E-5</v>
+        <v>-3.7001550324961322E-5</v>
       </c>
       <c r="W35">
-        <v>2.3376172638838962E-5</v>
+        <v>2.3376172638841456E-5</v>
       </c>
       <c r="X35">
-        <v>1.1796023550697918E-5</v>
+        <v>1.1796023550697735E-5</v>
       </c>
       <c r="Y35">
-        <v>3.5620091428164465E-5</v>
+        <v>3.5620091428164384E-5</v>
       </c>
       <c r="Z35">
-        <v>7.6416647815987589E-4</v>
+        <v>7.6416647815987719E-4</v>
       </c>
       <c r="AA35">
-        <v>7.7308254998453233E-4</v>
+        <v>7.7308254998453385E-4</v>
       </c>
       <c r="AB35">
-        <v>7.5115809429039779E-4</v>
+        <v>7.5115809429039909E-4</v>
       </c>
       <c r="AC35">
-        <v>7.512500511690915E-4</v>
+        <v>7.5125005116909291E-4</v>
       </c>
       <c r="AD35">
-        <v>7.1722419945449093E-4</v>
+        <v>7.1722419945449212E-4</v>
       </c>
       <c r="AE35">
-        <v>7.5594023651026133E-4</v>
+        <v>7.5594023651026263E-4</v>
       </c>
       <c r="AF35">
-        <v>7.7476239923824979E-4</v>
+        <v>7.7476239923825099E-4</v>
       </c>
       <c r="AG35">
-        <v>7.7450408603590027E-4</v>
+        <v>7.7450408603590157E-4</v>
       </c>
       <c r="AH35">
-        <v>7.8562042983484665E-4</v>
+        <v>7.8562042983484795E-4</v>
       </c>
       <c r="AI35">
-        <v>7.5635114519675734E-4</v>
+        <v>7.5635114519675853E-4</v>
       </c>
       <c r="AJ35">
-        <v>1.6537907546181024E-3</v>
+        <v>1.6537907546181033E-3</v>
       </c>
       <c r="AK35">
-        <v>-7.2282610919735004E-7</v>
+        <v>-7.2282610919724162E-7</v>
       </c>
       <c r="AL35">
-        <v>2.6564275031928816E-5</v>
+        <v>2.6564275031928328E-5</v>
       </c>
       <c r="AM35">
-        <v>-3.1611184333234948E-5</v>
+        <v>-3.1611184333235463E-5</v>
       </c>
       <c r="AN35">
-        <v>4.8275100182641116E-4</v>
+        <v>4.8275100182641046E-4</v>
       </c>
       <c r="AO35">
-        <v>4.3972520854778632E-4</v>
+        <v>4.3972520854778573E-4</v>
       </c>
       <c r="AP35">
-        <v>1.8591249768122573E-4</v>
+        <v>1.8591249768122543E-4</v>
       </c>
       <c r="AQ35">
-        <v>-9.259532816699187E-4</v>
+        <v>-9.2595328166993453E-4</v>
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.2">
@@ -5352,127 +5346,127 @@
         <v>1.0357699272879675E-2</v>
       </c>
       <c r="C36">
-        <v>7.8527576009740294E-7</v>
+        <v>7.8527576009741988E-7</v>
       </c>
       <c r="D36">
-        <v>-1.9472051545106283E-7</v>
+        <v>-1.9472051545090359E-7</v>
       </c>
       <c r="E36">
-        <v>5.0881193645026895E-10</v>
+        <v>5.088119364487337E-10</v>
       </c>
       <c r="F36">
-        <v>2.8372371979947257E-6</v>
+        <v>2.8372371979952678E-6</v>
       </c>
       <c r="G36">
-        <v>-2.6064669447827888E-6</v>
+        <v>-2.6064669447825855E-6</v>
       </c>
       <c r="H36">
-        <v>5.362191621479054E-6</v>
+        <v>5.3621916214791488E-6</v>
       </c>
       <c r="I36">
-        <v>-6.2117200108762773E-8</v>
+        <v>-6.2117200108545933E-8</v>
       </c>
       <c r="J36">
-        <v>-3.290881842042101E-6</v>
+        <v>-3.2908818420419655E-6</v>
       </c>
       <c r="K36">
-        <v>9.6575497509496168E-7</v>
+        <v>9.6575497509544957E-7</v>
       </c>
       <c r="L36">
-        <v>2.416064052237891E-6</v>
+        <v>2.4160640522381349E-6</v>
       </c>
       <c r="M36">
-        <v>-4.9393925643333636E-6</v>
+        <v>-4.9393925643324691E-6</v>
       </c>
       <c r="N36">
-        <v>-6.6941176230893155E-6</v>
+        <v>-6.6941176230890715E-6</v>
       </c>
       <c r="O36">
-        <v>-6.7303345985180395E-7</v>
+        <v>-6.730334598509908E-7</v>
       </c>
       <c r="P36">
-        <v>-3.3912605620624949E-7</v>
+        <v>-3.3912605620616139E-7</v>
       </c>
       <c r="Q36">
-        <v>3.7534158956150756E-6</v>
+        <v>3.7534158956152518E-6</v>
       </c>
       <c r="R36">
-        <v>1.833438770533413E-7</v>
+        <v>1.8334387705335062E-7</v>
       </c>
       <c r="S36">
-        <v>1.0507136979885357E-7</v>
+        <v>1.0507136979886374E-7</v>
       </c>
       <c r="T36">
-        <v>-1.5362920924607128E-6</v>
+        <v>-1.5362920924603469E-6</v>
       </c>
       <c r="U36">
-        <v>-6.9776142869160368E-6</v>
+        <v>-6.9776142869156437E-6</v>
       </c>
       <c r="V36">
-        <v>-3.8931243886192624E-6</v>
+        <v>-3.8931243886189371E-6</v>
       </c>
       <c r="W36">
-        <v>-1.9996834611987475E-6</v>
+        <v>-1.9996834611985036E-6</v>
       </c>
       <c r="X36">
-        <v>5.2102672916749615E-7</v>
+        <v>5.2102672916746735E-7</v>
       </c>
       <c r="Y36">
-        <v>-2.1800818275312209E-6</v>
+        <v>-2.1800818275311565E-6</v>
       </c>
       <c r="Z36">
-        <v>-5.3300982779042657E-7</v>
+        <v>-5.3300982779029104E-7</v>
       </c>
       <c r="AA36">
-        <v>8.5266355710638699E-6</v>
+        <v>8.5266355710639512E-6</v>
       </c>
       <c r="AB36">
-        <v>-1.234021170565784E-6</v>
+        <v>-1.234021170565662E-6</v>
       </c>
       <c r="AC36">
-        <v>-1.6351559695978535E-7</v>
+        <v>-1.6351559695964983E-7</v>
       </c>
       <c r="AD36">
-        <v>5.0225066063041825E-6</v>
+        <v>5.0225066063042909E-6</v>
       </c>
       <c r="AE36">
-        <v>-1.8291446418303723E-6</v>
+        <v>-1.8291446418301961E-6</v>
       </c>
       <c r="AF36">
-        <v>-3.0148453066603301E-7</v>
+        <v>-3.0148453066589748E-7</v>
       </c>
       <c r="AG36">
-        <v>1.5609863016137644E-6</v>
+        <v>1.5609863016138864E-6</v>
       </c>
       <c r="AH36">
-        <v>3.4652889032662815E-6</v>
+        <v>3.4652889032663628E-6</v>
       </c>
       <c r="AI36">
-        <v>2.4859443049534736E-7</v>
+        <v>2.4859443049538802E-7</v>
       </c>
       <c r="AJ36">
-        <v>-7.2282610919735004E-7</v>
+        <v>-7.2282610919724162E-7</v>
       </c>
       <c r="AK36">
-        <v>5.3361304336867322E-6</v>
+        <v>5.3361304336867779E-6</v>
       </c>
       <c r="AL36">
-        <v>-2.6043434160854269E-5</v>
+        <v>-2.6043434160854371E-5</v>
       </c>
       <c r="AM36">
-        <v>-2.7909292836626275E-5</v>
+        <v>-2.7909292836626391E-5</v>
       </c>
       <c r="AN36">
         <v>1.0790087923448649E-5</v>
       </c>
       <c r="AO36">
-        <v>1.2783271833306149E-5</v>
+        <v>1.2783271833306101E-5</v>
       </c>
       <c r="AP36">
-        <v>-4.6529424496662906E-6</v>
+        <v>-4.6529424496661348E-6</v>
       </c>
       <c r="AQ36">
-        <v>-8.8602220955333961E-5</v>
+        <v>-8.8602220955340196E-5</v>
       </c>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.2">
@@ -5483,127 +5477,127 @@
         <v>1.8176840109713221E-2</v>
       </c>
       <c r="C37">
-        <v>2.9722505776108946E-6</v>
+        <v>2.9722505776107422E-6</v>
       </c>
       <c r="D37">
-        <v>-8.8297879159707828E-7</v>
+        <v>-8.829787915970715E-7</v>
       </c>
       <c r="E37">
-        <v>9.0022978437306922E-9</v>
+        <v>9.0022978437305863E-9</v>
       </c>
       <c r="F37">
-        <v>3.2535226324208655E-5</v>
+        <v>3.253522632420795E-5</v>
       </c>
       <c r="G37">
-        <v>1.4713503793645222E-5</v>
+        <v>1.4713503793644707E-5</v>
       </c>
       <c r="H37">
-        <v>4.5088265248921392E-6</v>
+        <v>4.5088265248917055E-6</v>
       </c>
       <c r="I37">
-        <v>-8.3063578496498942E-6</v>
+        <v>-8.3063578496506531E-6</v>
       </c>
       <c r="J37">
-        <v>5.5951372627970818E-5</v>
+        <v>5.595137262796995E-5</v>
       </c>
       <c r="K37">
-        <v>-2.2976444901648039E-6</v>
+        <v>-2.297644490165617E-6</v>
       </c>
       <c r="L37">
-        <v>3.506460102106171E-5</v>
+        <v>3.5064601021060789E-5</v>
       </c>
       <c r="M37">
-        <v>4.5142387333384952E-6</v>
+        <v>4.5142387333377363E-6</v>
       </c>
       <c r="N37">
-        <v>3.9497308044425788E-5</v>
+        <v>3.9497308044424595E-5</v>
       </c>
       <c r="O37">
-        <v>-4.5536945392407038E-6</v>
+        <v>-4.5536945392413001E-6</v>
       </c>
       <c r="P37">
-        <v>-2.2546113393745793E-5</v>
+        <v>-2.2546113393746064E-5</v>
       </c>
       <c r="Q37">
-        <v>-2.8223201037218791E-5</v>
+        <v>-2.822320103721917E-5</v>
       </c>
       <c r="R37">
-        <v>4.305201160794975E-7</v>
+        <v>4.3052011607947887E-7</v>
       </c>
       <c r="S37">
-        <v>-2.7538131528377809E-7</v>
+        <v>-2.7538131528380519E-7</v>
       </c>
       <c r="T37">
-        <v>-1.378315844875695E-5</v>
+        <v>-1.3783158448757709E-5</v>
       </c>
       <c r="U37">
-        <v>3.0288265024222734E-5</v>
+        <v>3.0288265024221649E-5</v>
       </c>
       <c r="V37">
-        <v>9.3426894991116343E-6</v>
+        <v>9.3426894991103875E-6</v>
       </c>
       <c r="W37">
-        <v>1.4045143057342304E-5</v>
+        <v>1.4045143057340732E-5</v>
       </c>
       <c r="X37">
-        <v>2.5066950764933505E-6</v>
+        <v>2.5066950764934386E-6</v>
       </c>
       <c r="Y37">
-        <v>2.0137847917285159E-5</v>
+        <v>2.013784791728501E-5</v>
       </c>
       <c r="Z37">
-        <v>1.3613920744783578E-5</v>
+        <v>1.3613920744783036E-5</v>
       </c>
       <c r="AA37">
-        <v>3.8832066032371665E-7</v>
+        <v>3.8832066032320166E-7</v>
       </c>
       <c r="AB37">
-        <v>6.4100084106337034E-5</v>
+        <v>6.41000841063366E-5</v>
       </c>
       <c r="AC37">
-        <v>3.9399127541021737E-5</v>
+        <v>3.9399127541021222E-5</v>
       </c>
       <c r="AD37">
-        <v>2.453419465443628E-5</v>
+        <v>2.4534194654435819E-5</v>
       </c>
       <c r="AE37">
-        <v>3.8910220723056035E-5</v>
+        <v>3.8910220723055493E-5</v>
       </c>
       <c r="AF37">
-        <v>1.4159230250620407E-5</v>
+        <v>1.4159230250619946E-5</v>
       </c>
       <c r="AG37">
-        <v>3.565577403068194E-5</v>
+        <v>3.5655774030681425E-5</v>
       </c>
       <c r="AH37">
-        <v>4.9996074257607022E-6</v>
+        <v>4.9996074257602956E-6</v>
       </c>
       <c r="AI37">
-        <v>2.5396689358757644E-5</v>
+        <v>2.5396689358757237E-5</v>
       </c>
       <c r="AJ37">
-        <v>2.6564275031928816E-5</v>
+        <v>2.6564275031928328E-5</v>
       </c>
       <c r="AK37">
-        <v>-2.6043434160854269E-5</v>
+        <v>-2.6043434160854371E-5</v>
       </c>
       <c r="AL37">
-        <v>1.0300909134313358E-3</v>
+        <v>1.030090913431336E-3</v>
       </c>
       <c r="AM37">
-        <v>1.3125959820653427E-4</v>
+        <v>1.3125959820653454E-4</v>
       </c>
       <c r="AN37">
-        <v>-6.923938146948002E-5</v>
+        <v>-6.9239381469480047E-5</v>
       </c>
       <c r="AO37">
-        <v>-4.4285602571714937E-5</v>
+        <v>-4.4285602571714924E-5</v>
       </c>
       <c r="AP37">
-        <v>3.3859687520107213E-6</v>
+        <v>3.3859687520102402E-6</v>
       </c>
       <c r="AQ37">
-        <v>3.2797219291620384E-4</v>
+        <v>3.2797219291621349E-4</v>
       </c>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.2">
@@ -5614,127 +5608,127 @@
         <v>-3.0870329180964724E-2</v>
       </c>
       <c r="C38">
-        <v>-6.6561361730079099E-6</v>
+        <v>-6.6561361730082217E-6</v>
       </c>
       <c r="D38">
-        <v>-3.2583311215830148E-6</v>
+        <v>-3.2583311215834349E-6</v>
       </c>
       <c r="E38">
-        <v>2.9540166073960222E-8</v>
+        <v>2.954016607396414E-8</v>
       </c>
       <c r="F38">
-        <v>-1.1760968013645135E-5</v>
+        <v>-1.1760968013646762E-5</v>
       </c>
       <c r="G38">
-        <v>2.2756918819256489E-5</v>
+        <v>2.2756918819256028E-5</v>
       </c>
       <c r="H38">
-        <v>-1.8791040016733732E-5</v>
+        <v>-1.8791040016734084E-5</v>
       </c>
       <c r="I38">
-        <v>1.8376836389002288E-5</v>
+        <v>1.8376836389001638E-5</v>
       </c>
       <c r="J38">
-        <v>4.6422348104346438E-5</v>
+        <v>4.6422348104345842E-5</v>
       </c>
       <c r="K38">
-        <v>8.0243595814510709E-6</v>
+        <v>8.0243595814496072E-6</v>
       </c>
       <c r="L38">
-        <v>2.5405246892679036E-5</v>
+        <v>2.5405246892678114E-5</v>
       </c>
       <c r="M38">
-        <v>3.0585834488925626E-5</v>
+        <v>3.0585834488922698E-5</v>
       </c>
       <c r="N38">
-        <v>4.076369953180854E-5</v>
+        <v>4.076369953180751E-5</v>
       </c>
       <c r="O38">
-        <v>3.7495458104732553E-7</v>
+        <v>3.7495458104542818E-7</v>
       </c>
       <c r="P38">
-        <v>3.2506559709382198E-5</v>
+        <v>3.2506559709381887E-5</v>
       </c>
       <c r="Q38">
-        <v>3.7413788626726831E-5</v>
+        <v>3.7413788626726276E-5</v>
       </c>
       <c r="R38">
-        <v>1.6319100763837298E-6</v>
+        <v>1.6319100763837145E-6</v>
       </c>
       <c r="S38">
-        <v>-8.4439032274812593E-7</v>
+        <v>-8.443903227481615E-7</v>
       </c>
       <c r="T38">
-        <v>1.7382599122847339E-5</v>
+        <v>1.7382599122846092E-5</v>
       </c>
       <c r="U38">
-        <v>5.3573246627999012E-5</v>
+        <v>5.3573246627997603E-5</v>
       </c>
       <c r="V38">
-        <v>4.4047385844616098E-5</v>
+        <v>4.4047385844614743E-5</v>
       </c>
       <c r="W38">
-        <v>5.5298533649530068E-5</v>
+        <v>5.5298533649528712E-5</v>
       </c>
       <c r="X38">
-        <v>-1.8117120046136337E-9</v>
+        <v>-1.811712004518766E-9</v>
       </c>
       <c r="Y38">
-        <v>8.6527431378260133E-6</v>
+        <v>8.652743137825871E-6</v>
       </c>
       <c r="Z38">
-        <v>-2.936048102112536E-5</v>
+        <v>-2.9360481021125929E-5</v>
       </c>
       <c r="AA38">
-        <v>-3.802203384952897E-5</v>
+        <v>-3.8022033849529431E-5</v>
       </c>
       <c r="AB38">
-        <v>3.8413146181994379E-5</v>
+        <v>3.8413146181993756E-5</v>
       </c>
       <c r="AC38">
-        <v>-6.6095193044127623E-7</v>
+        <v>-6.6095193044184543E-7</v>
       </c>
       <c r="AD38">
-        <v>-1.6385837844701495E-5</v>
+        <v>-1.6385837844701929E-5</v>
       </c>
       <c r="AE38">
-        <v>7.7361081896957769E-6</v>
+        <v>7.7361081896950722E-6</v>
       </c>
       <c r="AF38">
-        <v>-3.9086952848728384E-6</v>
+        <v>-3.9086952848735432E-6</v>
       </c>
       <c r="AG38">
-        <v>4.8440844445908561E-6</v>
+        <v>4.8440844445902598E-6</v>
       </c>
       <c r="AH38">
-        <v>-3.90904381029371E-5</v>
+        <v>-3.9090438102937561E-5</v>
       </c>
       <c r="AI38">
-        <v>-2.4094375958101839E-5</v>
+        <v>-2.4094375958102191E-5</v>
       </c>
       <c r="AJ38">
-        <v>-3.1611184333234948E-5</v>
+        <v>-3.1611184333235463E-5</v>
       </c>
       <c r="AK38">
-        <v>-2.7909292836626275E-5</v>
+        <v>-2.7909292836626391E-5</v>
       </c>
       <c r="AL38">
-        <v>1.3125959820653427E-4</v>
+        <v>1.3125959820653454E-4</v>
       </c>
       <c r="AM38">
-        <v>1.1036402493871658E-3</v>
+        <v>1.1036402493871664E-3</v>
       </c>
       <c r="AN38">
-        <v>-1.0051472388101426E-4</v>
+        <v>-1.0051472388101434E-4</v>
       </c>
       <c r="AO38">
-        <v>-8.6293625798551429E-5</v>
+        <v>-8.6293625798551348E-5</v>
       </c>
       <c r="AP38">
-        <v>-2.3954656456203234E-5</v>
+        <v>-2.3954656456203938E-5</v>
       </c>
       <c r="AQ38">
-        <v>3.6478947468375717E-4</v>
+        <v>3.6478947468377836E-4</v>
       </c>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.2">
@@ -5745,127 +5739,127 @@
         <v>0.15168590552598571</v>
       </c>
       <c r="C39">
-        <v>-1.8539723440685436E-5</v>
+        <v>-1.8539723440685585E-5</v>
       </c>
       <c r="D39">
-        <v>2.8968676621128807E-6</v>
+        <v>2.89686766211284E-6</v>
       </c>
       <c r="E39">
-        <v>-2.1345251528660468E-8</v>
+        <v>-2.1345251528660415E-8</v>
       </c>
       <c r="F39">
-        <v>9.0706039357784822E-5</v>
+        <v>9.0706039357783656E-5</v>
       </c>
       <c r="G39">
-        <v>8.0026343163583374E-5</v>
+        <v>8.0026343163582615E-5</v>
       </c>
       <c r="H39">
-        <v>-5.8515461676648359E-5</v>
+        <v>-5.8515461676648969E-5</v>
       </c>
       <c r="I39">
-        <v>-3.6023502360053232E-5</v>
+        <v>-3.6023502360054018E-5</v>
       </c>
       <c r="J39">
-        <v>-2.0722848788845924E-4</v>
+        <v>-2.0722848788846002E-4</v>
       </c>
       <c r="K39">
-        <v>4.4279381699769408E-5</v>
+        <v>4.4279381699768459E-5</v>
       </c>
       <c r="L39">
-        <v>-8.5454281862488426E-5</v>
+        <v>-8.5454281862489537E-5</v>
       </c>
       <c r="M39">
-        <v>-3.2006034234519082E-4</v>
+        <v>-3.200603423451919E-4</v>
       </c>
       <c r="N39">
-        <v>-2.3554541100202246E-4</v>
+        <v>-2.3554541100202344E-4</v>
       </c>
       <c r="O39">
-        <v>-2.0511023347054844E-4</v>
+        <v>-2.0511023347054877E-4</v>
       </c>
       <c r="P39">
-        <v>1.1901767475533623E-4</v>
+        <v>1.1901767475533589E-4</v>
       </c>
       <c r="Q39">
-        <v>5.7451431620964639E-5</v>
+        <v>5.7451431620964382E-5</v>
       </c>
       <c r="R39">
-        <v>4.2662222833033745E-6</v>
+        <v>4.2662222833033678E-6</v>
       </c>
       <c r="S39">
-        <v>1.0737580966028471E-6</v>
+        <v>1.073758096602815E-6</v>
       </c>
       <c r="T39">
-        <v>-2.3319174777097036E-4</v>
+        <v>-2.3319174777097114E-4</v>
       </c>
       <c r="U39">
-        <v>-2.7756033228826927E-4</v>
+        <v>-2.775603322882704E-4</v>
       </c>
       <c r="V39">
-        <v>-2.4737388454350041E-4</v>
+        <v>-2.4737388454350165E-4</v>
       </c>
       <c r="W39">
-        <v>-2.565978510918802E-4</v>
+        <v>-2.5659785109188166E-4</v>
       </c>
       <c r="X39">
-        <v>2.2420804717912002E-5</v>
+        <v>2.242080471791211E-5</v>
       </c>
       <c r="Y39">
-        <v>1.6463398465124558E-5</v>
+        <v>1.646339846512447E-5</v>
       </c>
       <c r="Z39">
-        <v>4.0365629356841894E-4</v>
+        <v>4.0365629356841823E-4</v>
       </c>
       <c r="AA39">
-        <v>5.8979347552161234E-4</v>
+        <v>5.8979347552161137E-4</v>
       </c>
       <c r="AB39">
-        <v>3.7078127527999502E-4</v>
+        <v>3.7078127527999437E-4</v>
       </c>
       <c r="AC39">
-        <v>3.5577701878915561E-4</v>
+        <v>3.5577701878915496E-4</v>
       </c>
       <c r="AD39">
-        <v>2.519451660062277E-4</v>
+        <v>2.5194516600622716E-4</v>
       </c>
       <c r="AE39">
-        <v>3.6283458477464426E-4</v>
+        <v>3.6283458477464394E-4</v>
       </c>
       <c r="AF39">
-        <v>4.0313852647264769E-4</v>
+        <v>4.031385264726472E-4</v>
       </c>
       <c r="AG39">
-        <v>4.1317050690739868E-4</v>
+        <v>4.1317050690739792E-4</v>
       </c>
       <c r="AH39">
-        <v>3.7974521770316888E-4</v>
+        <v>3.7974521770316828E-4</v>
       </c>
       <c r="AI39">
-        <v>3.7869190555775504E-4</v>
+        <v>3.786919055577545E-4</v>
       </c>
       <c r="AJ39">
-        <v>4.8275100182641116E-4</v>
+        <v>4.8275100182641046E-4</v>
       </c>
       <c r="AK39">
         <v>1.0790087923448649E-5</v>
       </c>
       <c r="AL39">
-        <v>-6.923938146948002E-5</v>
+        <v>-6.9239381469480047E-5</v>
       </c>
       <c r="AM39">
-        <v>-1.0051472388101426E-4</v>
+        <v>-1.0051472388101434E-4</v>
       </c>
       <c r="AN39">
-        <v>2.0236849481693464E-3</v>
+        <v>2.0236849481693455E-3</v>
       </c>
       <c r="AO39">
-        <v>1.8471926713625863E-4</v>
+        <v>1.8471926713625828E-4</v>
       </c>
       <c r="AP39">
-        <v>1.910423534690394E-4</v>
+        <v>1.9104235346903897E-4</v>
       </c>
       <c r="AQ39">
-        <v>-7.9150724467696033E-4</v>
+        <v>-7.9150724467695437E-4</v>
       </c>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.2">
@@ -5876,127 +5870,127 @@
         <v>-8.7209085759077334E-2</v>
       </c>
       <c r="C40">
-        <v>9.7104217756908978E-5</v>
+        <v>9.710421775690887E-5</v>
       </c>
       <c r="D40">
-        <v>-2.7473720154349768E-6</v>
+        <v>-2.7473720154348752E-6</v>
       </c>
       <c r="E40">
-        <v>7.0629170521039134E-9</v>
+        <v>7.0629170521029075E-9</v>
       </c>
       <c r="F40">
-        <v>1.5386057604885057E-4</v>
+        <v>1.5386057604885089E-4</v>
       </c>
       <c r="G40">
-        <v>7.7999632797990667E-5</v>
+        <v>7.7999632797991154E-5</v>
       </c>
       <c r="H40">
-        <v>4.7719899226147234E-4</v>
+        <v>4.7719899226147261E-4</v>
       </c>
       <c r="I40">
-        <v>-3.3454447711108999E-4</v>
+        <v>-3.3454447711108977E-4</v>
       </c>
       <c r="J40">
-        <v>4.1730098122317124E-5</v>
+        <v>4.1730098122317314E-5</v>
       </c>
       <c r="K40">
-        <v>2.888690178773221E-5</v>
+        <v>2.8886901787732752E-5</v>
       </c>
       <c r="L40">
-        <v>-1.2942189627549654E-4</v>
+        <v>-1.2942189627549643E-4</v>
       </c>
       <c r="M40">
-        <v>-1.7228259834017846E-4</v>
+        <v>-1.722825983401787E-4</v>
       </c>
       <c r="N40">
-        <v>-1.1478379244263866E-4</v>
+        <v>-1.1478379244263959E-4</v>
       </c>
       <c r="O40">
-        <v>3.154656412322418E-5</v>
+        <v>3.1546564123223963E-5</v>
       </c>
       <c r="P40">
-        <v>-5.8690351177264056E-5</v>
+        <v>-5.869035117726453E-5</v>
       </c>
       <c r="Q40">
-        <v>-1.2516515398242815E-6</v>
+        <v>-1.2516515398247423E-6</v>
       </c>
       <c r="R40">
-        <v>-3.1499113454875489E-6</v>
+        <v>-3.1499113454875539E-6</v>
       </c>
       <c r="S40">
-        <v>1.136414186256636E-6</v>
+        <v>1.1364141862566055E-6</v>
       </c>
       <c r="T40">
-        <v>-9.416029377574324E-5</v>
+        <v>-9.4160293775743755E-5</v>
       </c>
       <c r="U40">
-        <v>-1.7065811430583329E-4</v>
+        <v>-1.7065811430583416E-4</v>
       </c>
       <c r="V40">
-        <v>-2.286249725011406E-4</v>
+        <v>-2.2862497250114165E-4</v>
       </c>
       <c r="W40">
-        <v>7.4148520867829888E-5</v>
+        <v>7.4148520867828641E-5</v>
       </c>
       <c r="X40">
-        <v>1.1999638764810597E-5</v>
+        <v>1.1999638764810673E-5</v>
       </c>
       <c r="Y40">
-        <v>5.5543807386748482E-5</v>
+        <v>5.5543807386748333E-5</v>
       </c>
       <c r="Z40">
-        <v>4.3801699276803494E-4</v>
+        <v>4.3801699276803418E-4</v>
       </c>
       <c r="AA40">
-        <v>3.5927650880636104E-4</v>
+        <v>3.592765088063606E-4</v>
       </c>
       <c r="AB40">
-        <v>3.5922475752295989E-4</v>
+        <v>3.5922475752295929E-4</v>
       </c>
       <c r="AC40">
-        <v>3.6237658942931599E-4</v>
+        <v>3.623765894293155E-4</v>
       </c>
       <c r="AD40">
-        <v>2.5536412099808796E-4</v>
+        <v>2.5536412099808742E-4</v>
       </c>
       <c r="AE40">
-        <v>3.7037320868375784E-4</v>
+        <v>3.7037320868375741E-4</v>
       </c>
       <c r="AF40">
-        <v>4.538236365014742E-4</v>
+        <v>4.5382363650147382E-4</v>
       </c>
       <c r="AG40">
-        <v>4.2125340029787841E-4</v>
+        <v>4.2125340029787792E-4</v>
       </c>
       <c r="AH40">
-        <v>4.1354276603727726E-4</v>
+        <v>4.1354276603727661E-4</v>
       </c>
       <c r="AI40">
-        <v>3.8213493631657029E-4</v>
+        <v>3.8213493631656992E-4</v>
       </c>
       <c r="AJ40">
-        <v>4.3972520854778632E-4</v>
+        <v>4.3972520854778573E-4</v>
       </c>
       <c r="AK40">
-        <v>1.2783271833306149E-5</v>
+        <v>1.2783271833306101E-5</v>
       </c>
       <c r="AL40">
-        <v>-4.4285602571714937E-5</v>
+        <v>-4.4285602571714924E-5</v>
       </c>
       <c r="AM40">
-        <v>-8.6293625798551429E-5</v>
+        <v>-8.6293625798551348E-5</v>
       </c>
       <c r="AN40">
-        <v>1.8471926713625863E-4</v>
+        <v>1.8471926713625828E-4</v>
       </c>
       <c r="AO40">
-        <v>4.2055786013327013E-3</v>
+        <v>4.2055786013327004E-3</v>
       </c>
       <c r="AP40">
-        <v>1.3715932821484168E-4</v>
+        <v>1.371593282148413E-4</v>
       </c>
       <c r="AQ40">
-        <v>-4.6461468779139417E-4</v>
+        <v>-4.6461468779139564E-4</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.2">
@@ -6007,127 +6001,127 @@
         <v>-3.173783483970876E-2</v>
       </c>
       <c r="C41">
-        <v>-3.6166354192387089E-5</v>
+        <v>-3.6166354192387116E-5</v>
       </c>
       <c r="D41">
-        <v>2.2824532579532E-6</v>
+        <v>2.2824532579531864E-6</v>
       </c>
       <c r="E41">
         <v>-1.4071416819641246E-8</v>
       </c>
       <c r="F41">
-        <v>5.2729231957938005E-4</v>
+        <v>5.2729231957937995E-4</v>
       </c>
       <c r="G41">
-        <v>-1.8521547443979357E-5</v>
+        <v>-1.8521547443979276E-5</v>
       </c>
       <c r="H41">
-        <v>-8.7355630996348765E-6</v>
+        <v>-8.7355630996347139E-6</v>
       </c>
       <c r="I41">
-        <v>-1.023812248388258E-5</v>
+        <v>-1.0238122483882363E-5</v>
       </c>
       <c r="J41">
-        <v>-2.7236852486551465E-5</v>
+        <v>-2.7236852486551275E-5</v>
       </c>
       <c r="K41">
-        <v>-3.9268400613410898E-5</v>
+        <v>-3.9268400613410844E-5</v>
       </c>
       <c r="L41">
-        <v>-1.2099708312511207E-4</v>
+        <v>-1.2099708312511239E-4</v>
       </c>
       <c r="M41">
-        <v>8.6181194343179035E-5</v>
+        <v>8.6181194343178005E-5</v>
       </c>
       <c r="N41">
-        <v>7.5340316913247781E-5</v>
+        <v>7.5340316913246697E-5</v>
       </c>
       <c r="O41">
-        <v>-5.5606349597319988E-5</v>
+        <v>-5.5606349597320476E-5</v>
       </c>
       <c r="P41">
-        <v>4.6271565935284101E-5</v>
+        <v>4.6271565935284006E-5</v>
       </c>
       <c r="Q41">
-        <v>7.2041057755371188E-5</v>
+        <v>7.2041057755371378E-5</v>
       </c>
       <c r="R41">
-        <v>1.6854425713367265E-6</v>
+        <v>1.6854425713366985E-6</v>
       </c>
       <c r="S41">
-        <v>4.4094739935865321E-7</v>
+        <v>4.4094739935862102E-7</v>
       </c>
       <c r="T41">
-        <v>2.75556420633257E-6</v>
+        <v>2.7555642063318924E-6</v>
       </c>
       <c r="U41">
-        <v>2.9604358400705188E-5</v>
+        <v>2.9604358400704266E-5</v>
       </c>
       <c r="V41">
-        <v>1.7113101496332088E-5</v>
+        <v>1.7113101496331112E-5</v>
       </c>
       <c r="W41">
-        <v>-1.7284344698871394E-5</v>
+        <v>-1.728434469887237E-5</v>
       </c>
       <c r="X41">
-        <v>1.857148608807111E-5</v>
+        <v>1.8571486088071208E-5</v>
       </c>
       <c r="Y41">
-        <v>4.3445861702618699E-6</v>
+        <v>4.3445861702619309E-6</v>
       </c>
       <c r="Z41">
-        <v>1.8372719529889995E-4</v>
+        <v>1.8372719529889965E-4</v>
       </c>
       <c r="AA41">
-        <v>1.9307276699712317E-4</v>
+        <v>1.9307276699712285E-4</v>
       </c>
       <c r="AB41">
-        <v>1.5082046462053236E-4</v>
+        <v>1.5082046462053201E-4</v>
       </c>
       <c r="AC41">
-        <v>1.5633072236814291E-4</v>
+        <v>1.5633072236814256E-4</v>
       </c>
       <c r="AD41">
-        <v>1.0386015992686103E-4</v>
+        <v>1.0386015992686073E-4</v>
       </c>
       <c r="AE41">
-        <v>8.1505091668721672E-5</v>
+        <v>8.1505091668721536E-5</v>
       </c>
       <c r="AF41">
-        <v>1.3906624210919795E-4</v>
+        <v>1.3906624210919763E-4</v>
       </c>
       <c r="AG41">
-        <v>1.679526220000061E-4</v>
+        <v>1.679526220000058E-4</v>
       </c>
       <c r="AH41">
-        <v>1.3766436870969563E-4</v>
+        <v>1.3766436870969522E-4</v>
       </c>
       <c r="AI41">
-        <v>1.5770781126099801E-4</v>
+        <v>1.5770781126099766E-4</v>
       </c>
       <c r="AJ41">
-        <v>1.8591249768122573E-4</v>
+        <v>1.8591249768122543E-4</v>
       </c>
       <c r="AK41">
-        <v>-4.6529424496662906E-6</v>
+        <v>-4.6529424496661348E-6</v>
       </c>
       <c r="AL41">
-        <v>3.3859687520107213E-6</v>
+        <v>3.3859687520102402E-6</v>
       </c>
       <c r="AM41">
-        <v>-2.3954656456203234E-5</v>
+        <v>-2.3954656456203938E-5</v>
       </c>
       <c r="AN41">
-        <v>1.910423534690394E-4</v>
+        <v>1.9104235346903897E-4</v>
       </c>
       <c r="AO41">
-        <v>1.3715932821484168E-4</v>
+        <v>1.371593282148413E-4</v>
       </c>
       <c r="AP41">
-        <v>2.4382516578593484E-3</v>
+        <v>2.4382516578593475E-3</v>
       </c>
       <c r="AQ41">
-        <v>-3.4105097352048246E-4</v>
+        <v>-3.4105097352048002E-4</v>
       </c>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.2">
@@ -6138,127 +6132,127 @@
         <v>-2.5865446472421207</v>
       </c>
       <c r="C42">
-        <v>-1.0463361448893699E-4</v>
+        <v>-1.0463361448894311E-4</v>
       </c>
       <c r="D42">
-        <v>-1.4969811846435749E-4</v>
+        <v>-1.496981184643576E-4</v>
       </c>
       <c r="E42">
-        <v>1.2922709265102472E-6</v>
+        <v>1.2922709265102534E-6</v>
       </c>
       <c r="F42">
-        <v>-1.6940687462424404E-3</v>
+        <v>-1.6940687462424716E-3</v>
       </c>
       <c r="G42">
-        <v>-7.4329922940479919E-4</v>
+        <v>-7.4329922940483042E-4</v>
       </c>
       <c r="H42">
-        <v>-9.2364851458754337E-4</v>
+        <v>-9.2364851458757503E-4</v>
       </c>
       <c r="I42">
-        <v>-1.2711840087197717E-3</v>
+        <v>-1.2711840087198127E-3</v>
       </c>
       <c r="J42">
-        <v>-8.9636741664405792E-4</v>
+        <v>-8.9636741664410194E-4</v>
       </c>
       <c r="K42">
-        <v>-1.3079474208521477E-3</v>
+        <v>-1.3079474208521902E-3</v>
       </c>
       <c r="L42">
-        <v>-1.4141511358084448E-3</v>
+        <v>-1.414151135808499E-3</v>
       </c>
       <c r="M42">
-        <v>-1.8426557074204064E-3</v>
+        <v>-1.8426557074204353E-3</v>
       </c>
       <c r="N42">
-        <v>-1.41573054798117E-3</v>
+        <v>-1.4157305479812121E-3</v>
       </c>
       <c r="O42">
-        <v>-9.3187609190674295E-4</v>
+        <v>-9.3187609190677895E-4</v>
       </c>
       <c r="P42">
-        <v>-3.9554637457495627E-4</v>
+        <v>-3.9554637457496435E-4</v>
       </c>
       <c r="Q42">
-        <v>-5.8441870859435492E-4</v>
+        <v>-5.844187085943701E-4</v>
       </c>
       <c r="R42">
-        <v>-3.5939342340611408E-5</v>
+        <v>-3.5939342340613359E-5</v>
       </c>
       <c r="S42">
-        <v>-3.7450627238493609E-5</v>
+        <v>-3.7450627238493311E-5</v>
       </c>
       <c r="T42">
-        <v>-1.0251759642876048E-3</v>
+        <v>-1.0251759642876408E-3</v>
       </c>
       <c r="U42">
-        <v>-1.1878898687438101E-3</v>
+        <v>-1.1878898687438565E-3</v>
       </c>
       <c r="V42">
-        <v>-1.3002500503033593E-3</v>
+        <v>-1.3002500503034127E-3</v>
       </c>
       <c r="W42">
-        <v>-1.5115842393550105E-3</v>
+        <v>-1.5115842393550773E-3</v>
       </c>
       <c r="X42">
-        <v>9.6714393400046313E-5</v>
+        <v>9.6714393400049241E-5</v>
       </c>
       <c r="Y42">
-        <v>-5.6131652601594748E-5</v>
+        <v>-5.6131652601602737E-5</v>
       </c>
       <c r="Z42">
-        <v>-9.4485755885231589E-4</v>
+        <v>-9.4485755885233996E-4</v>
       </c>
       <c r="AA42">
-        <v>-9.6631756788385752E-4</v>
+        <v>-9.6631756788387508E-4</v>
       </c>
       <c r="AB42">
-        <v>-8.975689655072918E-4</v>
+        <v>-8.9756896550730958E-4</v>
       </c>
       <c r="AC42">
-        <v>-8.9412996349830405E-4</v>
+        <v>-8.9412996349832042E-4</v>
       </c>
       <c r="AD42">
-        <v>-1.0671680372188875E-3</v>
+        <v>-1.0671680372189051E-3</v>
       </c>
       <c r="AE42">
-        <v>-8.0569875164453598E-4</v>
+        <v>-8.0569875164455593E-4</v>
       </c>
       <c r="AF42">
-        <v>-8.4645066631172682E-4</v>
+        <v>-8.4645066631174439E-4</v>
       </c>
       <c r="AG42">
-        <v>-9.4795639767386542E-4</v>
+        <v>-9.4795639767388602E-4</v>
       </c>
       <c r="AH42">
-        <v>-9.5311335697661765E-4</v>
+        <v>-9.5311335697663034E-4</v>
       </c>
       <c r="AI42">
-        <v>-6.8489990643275924E-4</v>
+        <v>-6.8489990643277507E-4</v>
       </c>
       <c r="AJ42">
-        <v>-9.259532816699187E-4</v>
+        <v>-9.2595328166993453E-4</v>
       </c>
       <c r="AK42">
-        <v>-8.8602220955333961E-5</v>
+        <v>-8.8602220955340196E-5</v>
       </c>
       <c r="AL42">
-        <v>3.2797219291620384E-4</v>
+        <v>3.2797219291621349E-4</v>
       </c>
       <c r="AM42">
-        <v>3.6478947468375717E-4</v>
+        <v>3.6478947468377836E-4</v>
       </c>
       <c r="AN42">
-        <v>-7.9150724467696033E-4</v>
+        <v>-7.9150724467695437E-4</v>
       </c>
       <c r="AO42">
-        <v>-4.6461468779139417E-4</v>
+        <v>-4.6461468779139564E-4</v>
       </c>
       <c r="AP42">
-        <v>-3.4105097352048246E-4</v>
+        <v>-3.4105097352048002E-4</v>
       </c>
       <c r="AQ42">
-        <v>1.2509939995914373E-2</v>
+        <v>1.2509939995914668E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F188D8E-6197-8F41-BBFD-D819C5B872CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439A085E-269C-7544-A5C5-548B49D2AFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>Description:</t>
   </si>
@@ -30,10 +30,10 @@
     <t>Model parameters governing projection of home ownership</t>
   </si>
   <si>
-    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
+    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>Last edit: 20 Jan 2026 DP</t>
+    <t>Last edit: 18 Feb 2026 AK</t>
   </si>
   <si>
     <t>Process:</t>
@@ -105,16 +105,19 @@
     <t>Les_c4_Retired_L1</t>
   </si>
   <si>
-    <t>Deh_c3_Medium</t>
+    <t>Deh_c4_Medium</t>
   </si>
   <si>
-    <t>Deh_c3_Low</t>
+    <t>Deh_c4_Low</t>
   </si>
   <si>
-    <t>L_Dhe_mcs</t>
+    <t>Deh_c4_Na</t>
   </si>
   <si>
-    <t>L_Dhe_pcs</t>
+    <t>Dhe_mcs_L1</t>
+  </si>
+  <si>
+    <t>Dhe_pcs_L1</t>
   </si>
   <si>
     <t>Ydses_c5_Q2_L1</t>
@@ -712,35 +715,35 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5">
-        <v>0.83956863095016954</v>
+        <v>0.83958937703208414</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5">
-        <v>47460.995456934616</v>
+        <v>47365.165719435339</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>212305</v>
+        <v>212317</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6">
-        <v>-16484536.500980252</v>
+        <v>-16482530.501589302</v>
       </c>
     </row>
   </sheetData>
@@ -750,10 +753,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AQ42"/>
+  <dimension ref="A1:AR43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -883,5376 +886,5636 @@
       <c r="AQ1" t="s">
         <v>54</v>
       </c>
+      <c r="AR1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>6.4632822275978415E-3</v>
+        <v>6.2194984110876799E-3</v>
       </c>
       <c r="C2">
-        <v>2.8112890482808638E-4</v>
+        <v>2.8146619058651593E-4</v>
       </c>
       <c r="D2">
-        <v>1.326594170650528E-6</v>
+        <v>1.4291240659697303E-6</v>
       </c>
       <c r="E2">
-        <v>-4.1167369895795048E-9</v>
+        <v>-5.025600437948128E-9</v>
       </c>
       <c r="F2">
-        <v>3.5775294147460501E-5</v>
+        <v>3.5693012886716798E-5</v>
       </c>
       <c r="G2">
-        <v>-3.547816695422892E-5</v>
+        <v>-3.5546821742172072E-5</v>
       </c>
       <c r="H2">
-        <v>-1.9616090988398405E-5</v>
+        <v>-2.0122773749544225E-5</v>
       </c>
       <c r="I2">
-        <v>-5.4779245973899369E-5</v>
+        <v>-5.5413465060733047E-5</v>
       </c>
       <c r="J2">
-        <v>-4.4797962091597977E-5</v>
+        <v>-4.5185603035329654E-5</v>
       </c>
       <c r="K2">
-        <v>5.521039395637499E-5</v>
+        <v>5.5363422683366666E-5</v>
       </c>
       <c r="L2">
-        <v>1.4023728334026914E-4</v>
+        <v>1.4065523718975839E-4</v>
       </c>
       <c r="M2">
-        <v>5.1447425980230213E-6</v>
+        <v>8.6112091692997289E-6</v>
       </c>
       <c r="N2">
-        <v>-3.0141657115764432E-5</v>
+        <v>-2.6637022552932892E-5</v>
       </c>
       <c r="O2">
-        <v>-2.0112437652261216E-5</v>
+        <v>-1.7655651429965078E-5</v>
       </c>
       <c r="P2">
-        <v>-2.2499293713269813E-5</v>
+        <v>-2.3789194441618113E-5</v>
       </c>
       <c r="Q2">
-        <v>-2.2586808177342252E-5</v>
+        <v>-2.301808862443896E-5</v>
       </c>
       <c r="R2">
-        <v>-2.1314131056072062E-6</v>
+        <v>-1.9991232116846684E-5</v>
       </c>
       <c r="S2">
-        <v>-4.7945347777298271E-7</v>
+        <v>-2.1368279016704371E-6</v>
       </c>
       <c r="T2">
-        <v>-1.0673484702895094E-5</v>
+        <v>-4.7837096942411658E-7</v>
       </c>
       <c r="U2">
-        <v>-1.1917548239504753E-5</v>
+        <v>-1.5244814183300351E-6</v>
       </c>
       <c r="V2">
-        <v>-2.0040872286459011E-5</v>
+        <v>-5.9587664478239729E-6</v>
       </c>
       <c r="W2">
-        <v>-3.3429963124193498E-5</v>
+        <v>-1.3316277170117171E-5</v>
       </c>
       <c r="X2">
-        <v>-3.2380729423231209E-7</v>
+        <v>-2.721632264849499E-5</v>
       </c>
       <c r="Y2">
-        <v>4.5785218710541725E-6</v>
+        <v>-8.8012917236686415E-7</v>
       </c>
       <c r="Z2">
-        <v>1.7266423627667288E-5</v>
+        <v>4.9755911632620251E-6</v>
       </c>
       <c r="AA2">
-        <v>4.8888985168169479E-5</v>
+        <v>1.7287330830570322E-5</v>
       </c>
       <c r="AB2">
-        <v>7.8037873559625391E-6</v>
+        <v>4.8948865204144819E-5</v>
       </c>
       <c r="AC2">
-        <v>1.7425948428694091E-5</v>
+        <v>6.8915729934002374E-6</v>
       </c>
       <c r="AD2">
-        <v>9.8638238250881853E-6</v>
+        <v>1.7277102604806705E-5</v>
       </c>
       <c r="AE2">
-        <v>1.1707726106089339E-6</v>
+        <v>9.7020337901788286E-6</v>
       </c>
       <c r="AF2">
-        <v>1.3265544569140191E-5</v>
+        <v>1.0342575481194911E-6</v>
       </c>
       <c r="AG2">
-        <v>1.6010176626664653E-5</v>
+        <v>1.3082509943611559E-5</v>
       </c>
       <c r="AH2">
-        <v>5.8296923045337124E-5</v>
+        <v>1.5665031090431597E-5</v>
       </c>
       <c r="AI2">
-        <v>5.3311968753028356E-5</v>
+        <v>5.8200929759627217E-5</v>
       </c>
       <c r="AJ2">
-        <v>1.8319910200220579E-5</v>
+        <v>5.3312940069351668E-5</v>
       </c>
       <c r="AK2">
-        <v>7.8527576009741988E-7</v>
+        <v>1.8427642154406498E-5</v>
       </c>
       <c r="AL2">
-        <v>2.9722505776107422E-6</v>
+        <v>7.5362715777955239E-7</v>
       </c>
       <c r="AM2">
-        <v>-6.6561361730082217E-6</v>
+        <v>2.7899555367540847E-6</v>
       </c>
       <c r="AN2">
-        <v>-1.8539723440685585E-5</v>
+        <v>-6.0572978614861404E-6</v>
       </c>
       <c r="AO2">
-        <v>9.710421775690887E-5</v>
+        <v>-1.9208425160340764E-5</v>
       </c>
       <c r="AP2">
-        <v>-3.6166354192387116E-5</v>
+        <v>9.629450597452188E-5</v>
       </c>
       <c r="AQ2">
-        <v>-1.0463361448894311E-4</v>
+        <v>-3.6166396130143145E-5</v>
+      </c>
+      <c r="AR2">
+        <v>-1.1197837044877331E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>5.6434204237526715E-4</v>
+        <v>5.8413621188082633E-4</v>
       </c>
       <c r="C3">
-        <v>1.326594170650528E-6</v>
+        <v>1.4291240659697303E-6</v>
       </c>
       <c r="D3">
-        <v>5.9683447131137794E-6</v>
+        <v>5.9720743835448233E-6</v>
       </c>
       <c r="E3">
-        <v>-5.6847250053370963E-8</v>
+        <v>-5.6852363231677108E-8</v>
       </c>
       <c r="F3">
-        <v>1.5858106540867264E-5</v>
+        <v>1.6109954998658602E-5</v>
       </c>
       <c r="G3">
-        <v>1.8346668871478103E-6</v>
+        <v>2.0336585594565887E-6</v>
       </c>
       <c r="H3">
-        <v>-1.2472407725467807E-7</v>
+        <v>-1.1185525635914795E-7</v>
       </c>
       <c r="I3">
-        <v>3.4033004266301516E-6</v>
+        <v>3.2672839238176988E-6</v>
       </c>
       <c r="J3">
-        <v>-4.9694033723339031E-6</v>
+        <v>-4.9146859051916807E-6</v>
       </c>
       <c r="K3">
-        <v>7.7389062860289531E-6</v>
+        <v>7.8739917807044415E-6</v>
       </c>
       <c r="L3">
-        <v>4.9873168394480547E-7</v>
+        <v>8.7421588639760633E-7</v>
       </c>
       <c r="M3">
-        <v>3.4702099693127012E-5</v>
+        <v>3.4441900912970938E-5</v>
       </c>
       <c r="N3">
-        <v>-1.8902290535952477E-6</v>
+        <v>-1.2067623884613775E-6</v>
       </c>
       <c r="O3">
-        <v>1.0099838873521611E-5</v>
+        <v>1.0690973080088486E-5</v>
       </c>
       <c r="P3">
-        <v>8.0220833846373284E-7</v>
+        <v>7.6504321303376806E-7</v>
       </c>
       <c r="Q3">
-        <v>2.1282685206250372E-6</v>
+        <v>2.1390247898502815E-6</v>
       </c>
       <c r="R3">
-        <v>8.0256914007411466E-8</v>
+        <v>4.4112042401839107E-7</v>
       </c>
       <c r="S3">
-        <v>1.5109744239549213E-7</v>
+        <v>7.4634706505448963E-8</v>
       </c>
       <c r="T3">
-        <v>5.1030028172586284E-7</v>
+        <v>1.5011781054636549E-7</v>
       </c>
       <c r="U3">
-        <v>-1.4168889714583302E-6</v>
+        <v>2.6290738479293803E-6</v>
       </c>
       <c r="V3">
-        <v>-9.2865874744480307E-6</v>
+        <v>4.0896437724174625E-8</v>
       </c>
       <c r="W3">
-        <v>-1.2390114950462741E-5</v>
+        <v>-7.5672200670731695E-6</v>
       </c>
       <c r="X3">
-        <v>-5.1957233843454346E-7</v>
+        <v>-1.0675380067589863E-5</v>
       </c>
       <c r="Y3">
-        <v>1.496567426603846E-6</v>
+        <v>-6.6748254030559736E-7</v>
       </c>
       <c r="Z3">
-        <v>7.1880752591607194E-7</v>
+        <v>1.54440204316277E-6</v>
       </c>
       <c r="AA3">
-        <v>1.0385655473419618E-6</v>
+        <v>8.0337811264282518E-7</v>
       </c>
       <c r="AB3">
-        <v>-1.5581584983845231E-6</v>
+        <v>1.0530364558413889E-6</v>
       </c>
       <c r="AC3">
-        <v>1.5415407692324897E-6</v>
+        <v>-1.8382999182388732E-6</v>
       </c>
       <c r="AD3">
-        <v>-1.755009706060648E-6</v>
+        <v>1.5383183500143276E-6</v>
       </c>
       <c r="AE3">
-        <v>-5.3800863234197319E-7</v>
+        <v>-1.8308010113871236E-6</v>
       </c>
       <c r="AF3">
-        <v>-1.1732734063388366E-6</v>
+        <v>-5.2526180591917402E-7</v>
       </c>
       <c r="AG3">
-        <v>2.238644075594053E-6</v>
+        <v>-1.1730599063885798E-6</v>
       </c>
       <c r="AH3">
-        <v>-6.032653341916476E-7</v>
+        <v>2.2506246174812692E-6</v>
       </c>
       <c r="AI3">
-        <v>-2.5941061600832292E-6</v>
+        <v>-3.8795646039082308E-7</v>
       </c>
       <c r="AJ3">
-        <v>1.039171354219037E-6</v>
+        <v>-2.5299981379242695E-6</v>
       </c>
       <c r="AK3">
-        <v>-1.9472051545090359E-7</v>
+        <v>1.0314506632024591E-6</v>
       </c>
       <c r="AL3">
-        <v>-8.829787915970715E-7</v>
+        <v>-1.9882876856226541E-7</v>
       </c>
       <c r="AM3">
-        <v>-3.2583311215834349E-6</v>
+        <v>-1.0334561001571762E-6</v>
       </c>
       <c r="AN3">
-        <v>2.89686766211284E-6</v>
+        <v>-3.3704414111874513E-6</v>
       </c>
       <c r="AO3">
-        <v>-2.7473720154348752E-6</v>
+        <v>2.5632093426097846E-6</v>
       </c>
       <c r="AP3">
-        <v>2.2824532579531864E-6</v>
+        <v>-2.4660800694133118E-6</v>
       </c>
       <c r="AQ3">
-        <v>-1.496981184643576E-4</v>
+        <v>2.8769194255477449E-6</v>
+      </c>
+      <c r="AR3">
+        <v>-1.5108751749055521E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>3.0972954241088396E-5</v>
+        <v>3.0802937460202532E-5</v>
       </c>
       <c r="C4">
-        <v>-4.1167369895795048E-9</v>
+        <v>-5.025600437948128E-9</v>
       </c>
       <c r="D4">
-        <v>-5.6847250053370963E-8</v>
+        <v>-5.6852363231677108E-8</v>
       </c>
       <c r="E4">
-        <v>5.9231247559257074E-10</v>
+        <v>5.922179953843621E-10</v>
       </c>
       <c r="F4">
-        <v>-1.193380082855773E-7</v>
+        <v>-1.2125823873163458E-7</v>
       </c>
       <c r="G4">
-        <v>-2.9545646628558409E-8</v>
+        <v>-3.1341342569801729E-8</v>
       </c>
       <c r="H4">
-        <v>2.7724951974389274E-8</v>
+        <v>2.7550293355761364E-8</v>
       </c>
       <c r="I4">
-        <v>6.6969234602236347E-9</v>
+        <v>7.2020790086821234E-9</v>
       </c>
       <c r="J4">
-        <v>6.7832198310577413E-8</v>
+        <v>6.7428679235413632E-8</v>
       </c>
       <c r="K4">
-        <v>-6.7412777043313832E-8</v>
+        <v>-6.8473376932484961E-8</v>
       </c>
       <c r="L4">
-        <v>2.6617813063754672E-8</v>
+        <v>2.3690955699467459E-8</v>
       </c>
       <c r="M4">
-        <v>-2.3131242938584193E-7</v>
+        <v>-2.3015219449498051E-7</v>
       </c>
       <c r="N4">
-        <v>5.4814708542968638E-8</v>
+        <v>5.0528850632616748E-8</v>
       </c>
       <c r="O4">
-        <v>-1.9526512749761413E-7</v>
+        <v>-1.9910775263609158E-7</v>
       </c>
       <c r="P4">
-        <v>-1.3109522906018683E-8</v>
+        <v>-1.2937412481575491E-8</v>
       </c>
       <c r="Q4">
-        <v>-6.2772044780458462E-8</v>
+        <v>-6.3156979178276286E-8</v>
       </c>
       <c r="R4">
-        <v>-1.4423251762428079E-9</v>
+        <v>-4.5650897893752227E-9</v>
       </c>
       <c r="S4">
-        <v>-2.7431527697157474E-10</v>
+        <v>-1.399242314237439E-9</v>
       </c>
       <c r="T4">
-        <v>1.9731431167347116E-8</v>
+        <v>-2.699530366139988E-10</v>
       </c>
       <c r="U4">
-        <v>4.6841916230385024E-8</v>
+        <v>3.3963749674784312E-9</v>
       </c>
       <c r="V4">
-        <v>1.0953159158621928E-7</v>
+        <v>3.7406145124965055E-8</v>
       </c>
       <c r="W4">
-        <v>1.2569611486878902E-7</v>
+        <v>9.7184433493242625E-8</v>
       </c>
       <c r="X4">
-        <v>-7.658220614415709E-10</v>
+        <v>1.1339059128340685E-7</v>
       </c>
       <c r="Y4">
-        <v>-2.9644124332865602E-8</v>
+        <v>3.3265898855702914E-10</v>
       </c>
       <c r="Z4">
-        <v>-9.1943244776833904E-10</v>
+        <v>-3.0133491008762956E-8</v>
       </c>
       <c r="AA4">
-        <v>-1.3761691063372072E-8</v>
+        <v>-1.4981685368495665E-9</v>
       </c>
       <c r="AB4">
-        <v>1.9331386674730246E-8</v>
+        <v>-1.394582194611735E-8</v>
       </c>
       <c r="AC4">
-        <v>-1.1343051444589269E-8</v>
+        <v>2.2078457435882491E-8</v>
       </c>
       <c r="AD4">
-        <v>3.1891023417150023E-8</v>
+        <v>-1.1194550169759669E-8</v>
       </c>
       <c r="AE4">
-        <v>5.7308876487989684E-9</v>
+        <v>3.2723610468812312E-8</v>
       </c>
       <c r="AF4">
-        <v>6.8595281824057973E-9</v>
+        <v>5.7938431956644173E-9</v>
       </c>
       <c r="AG4">
-        <v>-2.7341669616018331E-8</v>
+        <v>6.8814316970050909E-9</v>
       </c>
       <c r="AH4">
-        <v>6.4140930217235499E-9</v>
+        <v>-2.7434163249738048E-8</v>
       </c>
       <c r="AI4">
-        <v>2.1617943775581397E-8</v>
+        <v>4.5365599978252974E-9</v>
       </c>
       <c r="AJ4">
-        <v>-8.3040855574029317E-9</v>
+        <v>2.1232591831367259E-8</v>
       </c>
       <c r="AK4">
-        <v>5.088119364487337E-10</v>
+        <v>-8.1013346839824349E-9</v>
       </c>
       <c r="AL4">
-        <v>9.0022978437305863E-9</v>
+        <v>5.3733541348344549E-10</v>
       </c>
       <c r="AM4">
-        <v>2.954016607396414E-8</v>
+        <v>1.0532553549405659E-8</v>
       </c>
       <c r="AN4">
-        <v>-2.1345251528660415E-8</v>
+        <v>3.0504208080624811E-8</v>
       </c>
       <c r="AO4">
-        <v>7.0629170521029075E-9</v>
+        <v>-1.8978066609551009E-8</v>
       </c>
       <c r="AP4">
-        <v>-1.4071416819641246E-8</v>
+        <v>4.8751495865864164E-9</v>
       </c>
       <c r="AQ4">
-        <v>1.2922709265102534E-6</v>
+        <v>-1.9033125358466659E-8</v>
+      </c>
+      <c r="AR4">
+        <v>1.3016074712162899E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>-0.22816021923480417</v>
+        <v>-0.22997603870695507</v>
       </c>
       <c r="C5">
-        <v>3.5775294147460501E-5</v>
+        <v>3.5693012886716798E-5</v>
       </c>
       <c r="D5">
-        <v>1.5858106540867264E-5</v>
+        <v>1.6109954998658602E-5</v>
       </c>
       <c r="E5">
-        <v>-1.193380082855773E-7</v>
+        <v>-1.2125823873163458E-7</v>
       </c>
       <c r="F5">
-        <v>2.6201536227452096E-2</v>
+        <v>2.6340860167573747E-2</v>
       </c>
       <c r="G5">
-        <v>8.6223136404836316E-4</v>
+        <v>8.6171088453805046E-4</v>
       </c>
       <c r="H5">
-        <v>8.3001935566201371E-4</v>
+        <v>8.286378239600391E-4</v>
       </c>
       <c r="I5">
-        <v>9.4410729998791203E-4</v>
+        <v>9.4427308489316566E-4</v>
       </c>
       <c r="J5">
-        <v>8.9079659214342166E-4</v>
+        <v>8.9145613046020286E-4</v>
       </c>
       <c r="K5">
-        <v>8.9363118851583162E-4</v>
+        <v>8.9314743300410399E-4</v>
       </c>
       <c r="L5">
-        <v>9.2893922120955853E-4</v>
+        <v>9.3225011656550424E-4</v>
       </c>
       <c r="M5">
-        <v>-1.035906380555159E-4</v>
+        <v>-1.6602519071407239E-4</v>
       </c>
       <c r="N5">
-        <v>-3.7113780297906389E-5</v>
+        <v>-2.9731825869334905E-5</v>
       </c>
       <c r="O5">
-        <v>-6.855704086521265E-5</v>
+        <v>-6.172430999311113E-5</v>
       </c>
       <c r="P5">
-        <v>1.9057456995744126E-4</v>
+        <v>1.8746798063866074E-4</v>
       </c>
       <c r="Q5">
-        <v>1.7051250024409999E-4</v>
+        <v>1.6771431991547862E-4</v>
       </c>
       <c r="R5">
-        <v>3.0734449677817973E-6</v>
+        <v>3.2619929965713407E-4</v>
       </c>
       <c r="S5">
-        <v>-1.7021723389542858E-6</v>
+        <v>3.0203234492251625E-6</v>
       </c>
       <c r="T5">
-        <v>-6.8545697744600841E-5</v>
+        <v>-1.7356364933733404E-6</v>
       </c>
       <c r="U5">
-        <v>-1.1285954672276083E-4</v>
+        <v>-5.8484053727484516E-5</v>
       </c>
       <c r="V5">
-        <v>-4.3536970090630599E-6</v>
+        <v>-1.0102292364712291E-4</v>
       </c>
       <c r="W5">
-        <v>2.6211592284412511E-4</v>
+        <v>7.4958948626412445E-6</v>
       </c>
       <c r="X5">
-        <v>-2.7075742890616449E-7</v>
+        <v>2.7173445688109853E-4</v>
       </c>
       <c r="Y5">
-        <v>7.8240198564441673E-5</v>
+        <v>-1.4161054501806052E-6</v>
       </c>
       <c r="Z5">
-        <v>-3.5656270265161988E-5</v>
+        <v>7.8507686799529804E-5</v>
       </c>
       <c r="AA5">
-        <v>4.1009830256702581E-5</v>
+        <v>-3.8431760991383771E-5</v>
       </c>
       <c r="AB5">
-        <v>4.6647438236291347E-5</v>
+        <v>4.0390838116251054E-5</v>
       </c>
       <c r="AC5">
-        <v>9.4048309793546967E-5</v>
+        <v>4.4771017040781664E-5</v>
       </c>
       <c r="AD5">
-        <v>1.7463949362533454E-4</v>
+        <v>9.3477649221147816E-5</v>
       </c>
       <c r="AE5">
-        <v>1.353740128189228E-5</v>
+        <v>1.7575059429689936E-4</v>
       </c>
       <c r="AF5">
-        <v>5.6339334809153557E-5</v>
+        <v>1.1928274997384481E-5</v>
       </c>
       <c r="AG5">
-        <v>7.2549263802661776E-5</v>
+        <v>5.4599933350207035E-5</v>
       </c>
       <c r="AH5">
-        <v>8.129417460936295E-5</v>
+        <v>7.2043061656770335E-5</v>
       </c>
       <c r="AI5">
-        <v>-1.193545154633079E-7</v>
+        <v>8.2957739914124584E-5</v>
       </c>
       <c r="AJ5">
-        <v>1.0343462939673212E-4</v>
+        <v>-7.77058651276689E-7</v>
       </c>
       <c r="AK5">
-        <v>2.8372371979952678E-6</v>
+        <v>1.0245960372130385E-4</v>
       </c>
       <c r="AL5">
-        <v>3.253522632420795E-5</v>
+        <v>2.8400966665832598E-6</v>
       </c>
       <c r="AM5">
-        <v>-1.1760968013646762E-5</v>
+        <v>3.2492339922331724E-5</v>
       </c>
       <c r="AN5">
-        <v>9.0706039357783656E-5</v>
+        <v>-1.150887113923727E-5</v>
       </c>
       <c r="AO5">
-        <v>1.5386057604885089E-4</v>
+        <v>8.8099333403130311E-5</v>
       </c>
       <c r="AP5">
-        <v>5.2729231957937995E-4</v>
+        <v>1.5417843260810292E-4</v>
       </c>
       <c r="AQ5">
-        <v>-1.6940687462424716E-3</v>
+        <v>5.3598449500832359E-4</v>
+      </c>
+      <c r="AR5">
+        <v>-1.7041180280966313E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
-        <v>-3.6410240215586274E-2</v>
+        <v>-3.708306771340996E-2</v>
       </c>
       <c r="C6">
-        <v>-3.547816695422892E-5</v>
+        <v>-3.5546821742172072E-5</v>
       </c>
       <c r="D6">
-        <v>1.8346668871478103E-6</v>
+        <v>2.0336585594565887E-6</v>
       </c>
       <c r="E6">
-        <v>-2.9545646628558409E-8</v>
+        <v>-3.1341342569801729E-8</v>
       </c>
       <c r="F6">
-        <v>8.6223136404836316E-4</v>
+        <v>8.6171088453805046E-4</v>
       </c>
       <c r="G6">
-        <v>1.3101217713311641E-3</v>
+        <v>1.3085420186110159E-3</v>
       </c>
       <c r="H6">
-        <v>7.4719263369302225E-4</v>
+        <v>7.4668330253938758E-4</v>
       </c>
       <c r="I6">
-        <v>8.2866164110869105E-4</v>
+        <v>8.2926088305942502E-4</v>
       </c>
       <c r="J6">
-        <v>8.364880059875989E-4</v>
+        <v>8.367411794159193E-4</v>
       </c>
       <c r="K6">
-        <v>9.0859493595950324E-4</v>
+        <v>9.0802551549253659E-4</v>
       </c>
       <c r="L6">
-        <v>8.6715963143938618E-4</v>
+        <v>8.6716788748521646E-4</v>
       </c>
       <c r="M6">
-        <v>-7.8109208978104007E-5</v>
+        <v>-9.9202937585403037E-5</v>
       </c>
       <c r="N6">
-        <v>-1.1106778717279267E-4</v>
+        <v>-1.0843729647281764E-4</v>
       </c>
       <c r="O6">
-        <v>-1.1370285343764578E-4</v>
+        <v>-1.1090688854946735E-4</v>
       </c>
       <c r="P6">
-        <v>2.0876707732626106E-5</v>
+        <v>1.9277092682075853E-5</v>
       </c>
       <c r="Q6">
-        <v>2.5985018000354424E-5</v>
+        <v>2.4805816520034234E-5</v>
       </c>
       <c r="R6">
-        <v>-6.2137180231444307E-7</v>
+        <v>8.1138257130614728E-5</v>
       </c>
       <c r="S6">
-        <v>-8.2971140868822672E-7</v>
+        <v>-6.3359574133267163E-7</v>
       </c>
       <c r="T6">
-        <v>-7.2899349776584698E-5</v>
+        <v>-8.3343042330275326E-7</v>
       </c>
       <c r="U6">
-        <v>-5.4913677236371022E-5</v>
+        <v>-6.7179132887617822E-5</v>
       </c>
       <c r="V6">
-        <v>7.4896629417317442E-5</v>
+        <v>-5.1404552429366125E-5</v>
       </c>
       <c r="W6">
-        <v>2.6613440371310489E-4</v>
+        <v>7.9489869601636262E-5</v>
       </c>
       <c r="X6">
-        <v>-3.5266315947480727E-6</v>
+        <v>2.6970997282692809E-4</v>
       </c>
       <c r="Y6">
-        <v>-3.6131200329632559E-5</v>
+        <v>-3.8807858093355706E-6</v>
       </c>
       <c r="Z6">
-        <v>1.4100748858153267E-5</v>
+        <v>-3.6037797824131786E-5</v>
       </c>
       <c r="AA6">
-        <v>6.7390985459217826E-5</v>
+        <v>1.3037144040851909E-5</v>
       </c>
       <c r="AB6">
-        <v>5.7688548343415854E-5</v>
+        <v>6.6020458688432636E-5</v>
       </c>
       <c r="AC6">
-        <v>6.3869003200144828E-5</v>
+        <v>5.6715143533783832E-5</v>
       </c>
       <c r="AD6">
-        <v>-2.7076336599811374E-5</v>
+        <v>6.3064642699161744E-5</v>
       </c>
       <c r="AE6">
-        <v>3.4179407812607407E-5</v>
+        <v>-2.7232023735876125E-5</v>
       </c>
       <c r="AF6">
-        <v>6.0167040611791797E-5</v>
+        <v>3.3310808397440674E-5</v>
       </c>
       <c r="AG6">
-        <v>4.5790779789223523E-5</v>
+        <v>5.9318219588254349E-5</v>
       </c>
       <c r="AH6">
-        <v>8.24172096800779E-5</v>
+        <v>4.4602307736509063E-5</v>
       </c>
       <c r="AI6">
-        <v>-1.0263090904517292E-5</v>
+        <v>8.1415614475761363E-5</v>
       </c>
       <c r="AJ6">
-        <v>3.8272565510348187E-5</v>
+        <v>-1.1683834204389244E-5</v>
       </c>
       <c r="AK6">
-        <v>-2.6064669447825855E-6</v>
+        <v>3.7773138243759274E-5</v>
       </c>
       <c r="AL6">
-        <v>1.4713503793644707E-5</v>
+        <v>-2.6637215720125339E-6</v>
       </c>
       <c r="AM6">
-        <v>2.2756918819256028E-5</v>
+        <v>1.5173013117684455E-5</v>
       </c>
       <c r="AN6">
-        <v>8.0026343163582615E-5</v>
+        <v>2.3607783540637679E-5</v>
       </c>
       <c r="AO6">
-        <v>7.7999632797991154E-5</v>
+        <v>7.6671685962596917E-5</v>
       </c>
       <c r="AP6">
-        <v>-1.8521547443979276E-5</v>
+        <v>7.6617248480896627E-5</v>
       </c>
       <c r="AQ6">
-        <v>-7.4329922940483042E-4</v>
+        <v>-1.9991321342714908E-5</v>
+      </c>
+      <c r="AR6">
+        <v>-7.4809789003865603E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
-        <v>4.1499949375019095E-4</v>
+        <v>6.6175007719442274E-4</v>
       </c>
       <c r="C7">
-        <v>-1.9616090988398405E-5</v>
+        <v>-2.0122773749544225E-5</v>
       </c>
       <c r="D7">
-        <v>-1.2472407725467807E-7</v>
+        <v>-1.1185525635914795E-7</v>
       </c>
       <c r="E7">
-        <v>2.7724951974389274E-8</v>
+        <v>2.7550293355761364E-8</v>
       </c>
       <c r="F7">
-        <v>8.3001935566201371E-4</v>
+        <v>8.286378239600391E-4</v>
       </c>
       <c r="G7">
-        <v>7.4719263369302225E-4</v>
+        <v>7.4668330253938758E-4</v>
       </c>
       <c r="H7">
-        <v>1.6722460724610865E-3</v>
+        <v>1.6727900031725475E-3</v>
       </c>
       <c r="I7">
-        <v>7.5186860241506753E-4</v>
+        <v>7.5249295526677888E-4</v>
       </c>
       <c r="J7">
-        <v>8.096605271220536E-4</v>
+        <v>8.0966042236997409E-4</v>
       </c>
       <c r="K7">
-        <v>7.5247791262530073E-4</v>
+        <v>7.5211995569826942E-4</v>
       </c>
       <c r="L7">
-        <v>7.6751238638529977E-4</v>
+        <v>7.6748269586649398E-4</v>
       </c>
       <c r="M7">
-        <v>1.2757067527436784E-4</v>
+        <v>1.1363816361346469E-4</v>
       </c>
       <c r="N7">
-        <v>6.6965069705783809E-5</v>
+        <v>6.9488224617278535E-5</v>
       </c>
       <c r="O7">
-        <v>-3.3086822578124825E-5</v>
+        <v>-3.1581848641296865E-5</v>
       </c>
       <c r="P7">
-        <v>-5.3737705446185941E-6</v>
+        <v>-7.9018872038996658E-6</v>
       </c>
       <c r="Q7">
-        <v>1.5761996969567869E-5</v>
+        <v>1.410971794572072E-5</v>
       </c>
       <c r="R7">
-        <v>-1.1611535654556061E-6</v>
+        <v>2.9122343371156781E-5</v>
       </c>
       <c r="S7">
-        <v>5.264477105344958E-7</v>
+        <v>-1.1664683959863817E-6</v>
       </c>
       <c r="T7">
-        <v>-1.9866113831980736E-6</v>
+        <v>5.301842216694119E-7</v>
       </c>
       <c r="U7">
-        <v>-1.0626962083511521E-5</v>
+        <v>-1.3106869394842989E-6</v>
       </c>
       <c r="V7">
-        <v>3.3439141718740973E-5</v>
+        <v>-9.2527450996528877E-6</v>
       </c>
       <c r="W7">
-        <v>2.3690804101118675E-4</v>
+        <v>3.5791766193276912E-5</v>
       </c>
       <c r="X7">
-        <v>8.2080509184267727E-6</v>
+        <v>2.3756347917922645E-4</v>
       </c>
       <c r="Y7">
-        <v>-5.0501516284037328E-5</v>
+        <v>8.0886147054234218E-6</v>
       </c>
       <c r="Z7">
-        <v>-2.0956617604760865E-5</v>
+        <v>-5.0672069799272514E-5</v>
       </c>
       <c r="AA7">
-        <v>3.4266425747613623E-8</v>
+        <v>-2.0841472353823047E-5</v>
       </c>
       <c r="AB7">
-        <v>1.1145157449789937E-5</v>
+        <v>7.9453655340772154E-7</v>
       </c>
       <c r="AC7">
-        <v>2.1486487525607779E-5</v>
+        <v>1.2034189424276463E-5</v>
       </c>
       <c r="AD7">
-        <v>3.5309338747718268E-6</v>
+        <v>2.2053049757190105E-5</v>
       </c>
       <c r="AE7">
-        <v>-2.4259919458952063E-6</v>
+        <v>3.7862723068680612E-6</v>
       </c>
       <c r="AF7">
-        <v>1.2135610741112153E-5</v>
+        <v>-2.4642478965994428E-6</v>
       </c>
       <c r="AG7">
-        <v>1.0646501247682945E-5</v>
+        <v>1.2648055640997823E-5</v>
       </c>
       <c r="AH7">
-        <v>7.9261892200311338E-5</v>
+        <v>1.0768090976808656E-5</v>
       </c>
       <c r="AI7">
-        <v>-5.0683902400713835E-5</v>
+        <v>7.9511109446624823E-5</v>
       </c>
       <c r="AJ7">
-        <v>6.730191365895337E-6</v>
+        <v>-5.1010582005930416E-5</v>
       </c>
       <c r="AK7">
-        <v>5.3621916214791488E-6</v>
+        <v>6.5978064815258261E-6</v>
       </c>
       <c r="AL7">
-        <v>4.5088265248917055E-6</v>
+        <v>5.3837581896933056E-6</v>
       </c>
       <c r="AM7">
-        <v>-1.8791040016734084E-5</v>
+        <v>4.2793639545473446E-6</v>
       </c>
       <c r="AN7">
-        <v>-5.8515461676648969E-5</v>
+        <v>-1.8879900017464195E-5</v>
       </c>
       <c r="AO7">
-        <v>4.7719899226147261E-4</v>
+        <v>-5.909903294188602E-5</v>
       </c>
       <c r="AP7">
-        <v>-8.7355630996347139E-6</v>
+        <v>4.7530690062067563E-4</v>
       </c>
       <c r="AQ7">
-        <v>-9.2364851458757503E-4</v>
+        <v>-9.2991318796916496E-6</v>
+      </c>
+      <c r="AR7">
+        <v>-9.2332408612558398E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-0.32282326022716623</v>
+        <v>-0.32482281259723883</v>
       </c>
       <c r="C8">
-        <v>-5.4779245973899369E-5</v>
+        <v>-5.5413465060733047E-5</v>
       </c>
       <c r="D8">
-        <v>3.4033004266301516E-6</v>
+        <v>3.2672839238176988E-6</v>
       </c>
       <c r="E8">
-        <v>6.6969234602236347E-9</v>
+        <v>7.2020790086821234E-9</v>
       </c>
       <c r="F8">
-        <v>9.4410729998791203E-4</v>
+        <v>9.4427308489316566E-4</v>
       </c>
       <c r="G8">
-        <v>8.2866164110869105E-4</v>
+        <v>8.2926088305942502E-4</v>
       </c>
       <c r="H8">
-        <v>7.5186860241506753E-4</v>
+        <v>7.5249295526677888E-4</v>
       </c>
       <c r="I8">
-        <v>2.3348972678353057E-2</v>
+        <v>2.3523483339712138E-2</v>
       </c>
       <c r="J8">
-        <v>9.134769735760146E-4</v>
+        <v>9.138977159688363E-4</v>
       </c>
       <c r="K8">
-        <v>8.4939976849165608E-4</v>
+        <v>8.490173288640936E-4</v>
       </c>
       <c r="L8">
-        <v>9.2260799600029318E-4</v>
+        <v>9.2443821230499008E-4</v>
       </c>
       <c r="M8">
-        <v>1.9947495953088402E-4</v>
+        <v>1.6299466364116461E-4</v>
       </c>
       <c r="N8">
-        <v>9.1114879777547141E-5</v>
+        <v>9.3547503302302291E-5</v>
       </c>
       <c r="O8">
-        <v>-2.3253893023560362E-5</v>
+        <v>-2.1114345880494765E-5</v>
       </c>
       <c r="P8">
-        <v>1.000779983181152E-4</v>
+        <v>1.0028816046733386E-4</v>
       </c>
       <c r="Q8">
-        <v>1.0578522504095869E-4</v>
+        <v>1.1277986531697083E-4</v>
       </c>
       <c r="R8">
-        <v>1.5461417812720125E-6</v>
+        <v>1.6310890532891071E-4</v>
       </c>
       <c r="S8">
-        <v>3.6767718028934699E-7</v>
+        <v>1.5162897221240028E-6</v>
       </c>
       <c r="T8">
-        <v>-3.4503047078787752E-5</v>
+        <v>3.7028689239618184E-7</v>
       </c>
       <c r="U8">
-        <v>-8.498879946053291E-6</v>
+        <v>-3.2656810632920402E-5</v>
       </c>
       <c r="V8">
-        <v>2.2441782796178082E-4</v>
+        <v>-5.3750834703501337E-6</v>
       </c>
       <c r="W8">
-        <v>4.6661560267941471E-4</v>
+        <v>2.2872994690582076E-4</v>
       </c>
       <c r="X8">
-        <v>6.532419744924871E-6</v>
+        <v>4.7145896495025198E-4</v>
       </c>
       <c r="Y8">
-        <v>-3.3492001192811458E-5</v>
+        <v>6.3746065360249272E-6</v>
       </c>
       <c r="Z8">
-        <v>-3.1424693107274458E-5</v>
+        <v>-3.3270208919033886E-5</v>
       </c>
       <c r="AA8">
-        <v>-2.872554343938432E-5</v>
+        <v>-3.2437771826810446E-5</v>
       </c>
       <c r="AB8">
-        <v>1.0317200800238744E-4</v>
+        <v>-2.9229802679619197E-5</v>
       </c>
       <c r="AC8">
-        <v>1.7860382209606356E-4</v>
+        <v>1.031122696550558E-4</v>
       </c>
       <c r="AD8">
-        <v>-5.6695689615589065E-5</v>
+        <v>1.7855613269220609E-4</v>
       </c>
       <c r="AE8">
-        <v>1.2634464412902599E-5</v>
+        <v>-5.8949311858412691E-5</v>
       </c>
       <c r="AF8">
-        <v>1.8205980953952517E-5</v>
+        <v>1.0881485996786603E-5</v>
       </c>
       <c r="AG8">
-        <v>4.2619576812613034E-5</v>
+        <v>1.7315350382810361E-5</v>
       </c>
       <c r="AH8">
-        <v>2.0120935756152914E-5</v>
+        <v>4.1981192211854523E-5</v>
       </c>
       <c r="AI8">
-        <v>-7.13537441959796E-5</v>
+        <v>2.0619688018626948E-5</v>
       </c>
       <c r="AJ8">
-        <v>4.3285807418830908E-5</v>
+        <v>-7.3542239003363062E-5</v>
       </c>
       <c r="AK8">
-        <v>-6.2117200108545933E-8</v>
+        <v>4.0725605605695177E-5</v>
       </c>
       <c r="AL8">
-        <v>-8.3063578496506531E-6</v>
+        <v>8.9778289742622466E-8</v>
       </c>
       <c r="AM8">
-        <v>1.8376836389001638E-5</v>
+        <v>-9.8928125259052885E-6</v>
       </c>
       <c r="AN8">
-        <v>-3.6023502360054018E-5</v>
+        <v>1.7382693735625671E-5</v>
       </c>
       <c r="AO8">
-        <v>-3.3454447711108977E-4</v>
+        <v>-3.7244021950440405E-5</v>
       </c>
       <c r="AP8">
-        <v>-1.0238122483882363E-5</v>
+        <v>-3.3184969413944162E-4</v>
       </c>
       <c r="AQ8">
-        <v>-1.2711840087198127E-3</v>
+        <v>-6.1691330145958805E-6</v>
+      </c>
+      <c r="AR8">
+        <v>-1.2707421004932093E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-0.16951677677070059</v>
+        <v>-0.169520608838408</v>
       </c>
       <c r="C9">
-        <v>-4.4797962091597977E-5</v>
+        <v>-4.5185603035329654E-5</v>
       </c>
       <c r="D9">
-        <v>-4.9694033723339031E-6</v>
+        <v>-4.9146859051916807E-6</v>
       </c>
       <c r="E9">
-        <v>6.7832198310577413E-8</v>
+        <v>6.7428679235413632E-8</v>
       </c>
       <c r="F9">
-        <v>8.9079659214342166E-4</v>
+        <v>8.9145613046020286E-4</v>
       </c>
       <c r="G9">
-        <v>8.364880059875989E-4</v>
+        <v>8.367411794159193E-4</v>
       </c>
       <c r="H9">
-        <v>8.096605271220536E-4</v>
+        <v>8.0966042236997409E-4</v>
       </c>
       <c r="I9">
-        <v>9.134769735760146E-4</v>
+        <v>9.138977159688363E-4</v>
       </c>
       <c r="J9">
-        <v>1.8751008815373169E-3</v>
+        <v>1.8754956466473613E-3</v>
       </c>
       <c r="K9">
-        <v>8.4846320166785498E-4</v>
+        <v>8.4831632185878084E-4</v>
       </c>
       <c r="L9">
-        <v>9.3040363847546109E-4</v>
+        <v>9.3142501353699861E-4</v>
       </c>
       <c r="M9">
-        <v>1.9985273475419258E-4</v>
+        <v>1.6083784252666765E-4</v>
       </c>
       <c r="N9">
-        <v>1.1253045278680619E-4</v>
+        <v>1.1750934636720032E-4</v>
       </c>
       <c r="O9">
-        <v>8.1175441025863217E-5</v>
+        <v>8.4767938279897432E-5</v>
       </c>
       <c r="P9">
-        <v>3.4181586790791891E-5</v>
+        <v>3.2690853070458552E-5</v>
       </c>
       <c r="Q9">
-        <v>3.7616276483110522E-5</v>
+        <v>3.5731808964720136E-5</v>
       </c>
       <c r="R9">
-        <v>-8.2603992970004066E-7</v>
+        <v>1.1666353154177341E-4</v>
       </c>
       <c r="S9">
-        <v>-4.953143116865152E-7</v>
+        <v>-8.5658903423030848E-7</v>
       </c>
       <c r="T9">
-        <v>4.4637275949545074E-5</v>
+        <v>-4.902424090789011E-7</v>
       </c>
       <c r="U9">
-        <v>1.1229399958418665E-4</v>
+        <v>5.3482635041096952E-5</v>
       </c>
       <c r="V9">
-        <v>3.2350042465627857E-4</v>
+        <v>1.2003288923608897E-4</v>
       </c>
       <c r="W9">
-        <v>5.2318050692513418E-4</v>
+        <v>3.3061619883240241E-4</v>
       </c>
       <c r="X9">
-        <v>-1.8026290309755795E-6</v>
+        <v>5.2952814935974455E-4</v>
       </c>
       <c r="Y9">
-        <v>-1.8136603876306413E-5</v>
+        <v>-2.488351361771574E-6</v>
       </c>
       <c r="Z9">
-        <v>4.7306697845017365E-6</v>
+        <v>-1.8566270140317476E-5</v>
       </c>
       <c r="AA9">
-        <v>-3.700707647646918E-5</v>
+        <v>5.0633885885188409E-6</v>
       </c>
       <c r="AB9">
-        <v>6.8738675636800432E-5</v>
+        <v>-3.596298080626992E-5</v>
       </c>
       <c r="AC9">
-        <v>5.8409954117463553E-5</v>
+        <v>7.0132150518283749E-5</v>
       </c>
       <c r="AD9">
-        <v>2.8703307502329087E-5</v>
+        <v>5.882684501621814E-5</v>
       </c>
       <c r="AE9">
-        <v>2.4856407070120417E-5</v>
+        <v>2.8730926641592781E-5</v>
       </c>
       <c r="AF9">
-        <v>3.9582490462197916E-5</v>
+        <v>2.5489001720621651E-5</v>
       </c>
       <c r="AG9">
-        <v>6.4084318226285836E-5</v>
+        <v>4.0771703577004566E-5</v>
       </c>
       <c r="AH9">
-        <v>6.567305471954776E-5</v>
+        <v>6.4558461819304181E-5</v>
       </c>
       <c r="AI9">
-        <v>-1.3120477274821305E-5</v>
+        <v>6.6263594359214229E-5</v>
       </c>
       <c r="AJ9">
-        <v>3.034005545389626E-5</v>
+        <v>-1.3041040500511906E-5</v>
       </c>
       <c r="AK9">
-        <v>-3.2908818420419655E-6</v>
+        <v>3.0555407066694786E-5</v>
       </c>
       <c r="AL9">
-        <v>5.595137262796995E-5</v>
+        <v>-3.250440209772427E-6</v>
       </c>
       <c r="AM9">
-        <v>4.6422348104345842E-5</v>
+        <v>5.6339776325737585E-5</v>
       </c>
       <c r="AN9">
-        <v>-2.0722848788846002E-4</v>
+        <v>4.5915404099321059E-5</v>
       </c>
       <c r="AO9">
-        <v>4.1730098122317314E-5</v>
+        <v>-2.0628212791292926E-4</v>
       </c>
       <c r="AP9">
-        <v>-2.7236852486551275E-5</v>
+        <v>4.2277852227119104E-5</v>
       </c>
       <c r="AQ9">
-        <v>-8.9636741664410194E-4</v>
+        <v>-2.6325064785907192E-5</v>
+      </c>
+      <c r="AR9">
+        <v>-9.0258539961335794E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-0.23127185169099237</v>
+        <v>-0.2316966676510972</v>
       </c>
       <c r="C10">
-        <v>5.521039395637499E-5</v>
+        <v>5.5363422683366666E-5</v>
       </c>
       <c r="D10">
-        <v>7.7389062860289531E-6</v>
+        <v>7.8739917807044415E-6</v>
       </c>
       <c r="E10">
-        <v>-6.7412777043313832E-8</v>
+        <v>-6.8473376932484961E-8</v>
       </c>
       <c r="F10">
-        <v>8.9363118851583162E-4</v>
+        <v>8.9314743300410399E-4</v>
       </c>
       <c r="G10">
-        <v>9.0859493595950324E-4</v>
+        <v>9.0802551549253659E-4</v>
       </c>
       <c r="H10">
-        <v>7.5247791262530073E-4</v>
+        <v>7.5211995569826942E-4</v>
       </c>
       <c r="I10">
-        <v>8.4939976849165608E-4</v>
+        <v>8.490173288640936E-4</v>
       </c>
       <c r="J10">
-        <v>8.4846320166785498E-4</v>
+        <v>8.4831632185878084E-4</v>
       </c>
       <c r="K10">
-        <v>1.0328437041269814E-3</v>
+        <v>1.0323588070113672E-3</v>
       </c>
       <c r="L10">
-        <v>9.4768211965577903E-4</v>
+        <v>9.4775546468833392E-4</v>
       </c>
       <c r="M10">
-        <v>-3.2567021250590373E-5</v>
+        <v>-4.9365867377557527E-5</v>
       </c>
       <c r="N10">
-        <v>-4.0484063828340482E-5</v>
+        <v>-3.9861216164640417E-5</v>
       </c>
       <c r="O10">
-        <v>-6.7602302385645272E-5</v>
+        <v>-6.6396689378284688E-5</v>
       </c>
       <c r="P10">
-        <v>2.4711706474932064E-5</v>
+        <v>2.3194485782185618E-5</v>
       </c>
       <c r="Q10">
-        <v>4.3474608275563163E-5</v>
+        <v>4.2399092598277934E-5</v>
       </c>
       <c r="R10">
-        <v>7.4024502984203195E-7</v>
+        <v>6.7223786297888498E-5</v>
       </c>
       <c r="S10">
-        <v>2.1282269063242215E-7</v>
+        <v>7.1670827353147135E-7</v>
       </c>
       <c r="T10">
-        <v>2.0313778682854789E-5</v>
+        <v>1.976317978857674E-7</v>
       </c>
       <c r="U10">
-        <v>5.2655564435106838E-5</v>
+        <v>2.2628048095354618E-5</v>
       </c>
       <c r="V10">
-        <v>1.6462365153521245E-4</v>
+        <v>5.5374353351013666E-5</v>
       </c>
       <c r="W10">
-        <v>3.3354089345732782E-4</v>
+        <v>1.6706505435160179E-4</v>
       </c>
       <c r="X10">
-        <v>-1.7945862808884104E-6</v>
+        <v>3.3531335028708618E-4</v>
       </c>
       <c r="Y10">
-        <v>-3.0418846568515422E-5</v>
+        <v>-2.0023713410200389E-6</v>
       </c>
       <c r="Z10">
-        <v>4.7370994212764107E-5</v>
+        <v>-3.0756508480692883E-5</v>
       </c>
       <c r="AA10">
-        <v>7.3491147857296629E-5</v>
+        <v>4.707152879763579E-5</v>
       </c>
       <c r="AB10">
-        <v>1.0310700463884772E-4</v>
+        <v>7.3234509212636613E-5</v>
       </c>
       <c r="AC10">
-        <v>9.0925851162755296E-5</v>
+        <v>1.0273754131728892E-4</v>
       </c>
       <c r="AD10">
-        <v>6.1089026213289688E-5</v>
+        <v>9.0519312338268454E-5</v>
       </c>
       <c r="AE10">
-        <v>6.6286521729028803E-5</v>
+        <v>6.0986854978757973E-5</v>
       </c>
       <c r="AF10">
-        <v>7.1528282831584281E-5</v>
+        <v>6.5741174949061334E-5</v>
       </c>
       <c r="AG10">
-        <v>7.8113270531386859E-5</v>
+        <v>7.0983982934595975E-5</v>
       </c>
       <c r="AH10">
-        <v>1.257587501209579E-4</v>
+        <v>7.7428785497347604E-5</v>
       </c>
       <c r="AI10">
-        <v>2.2262887098274163E-5</v>
+        <v>1.2519499794140315E-4</v>
       </c>
       <c r="AJ10">
-        <v>4.9603539928876354E-5</v>
+        <v>2.1697662720368714E-5</v>
       </c>
       <c r="AK10">
-        <v>9.6575497509544957E-7</v>
+        <v>4.9178265466384534E-5</v>
       </c>
       <c r="AL10">
-        <v>-2.297644490165617E-6</v>
+        <v>9.3443817916476104E-7</v>
       </c>
       <c r="AM10">
-        <v>8.0243595814496072E-6</v>
+        <v>-1.716200764187686E-6</v>
       </c>
       <c r="AN10">
-        <v>4.4279381699768459E-5</v>
+        <v>8.1523951257680819E-6</v>
       </c>
       <c r="AO10">
-        <v>2.8886901787732752E-5</v>
+        <v>4.2645198186014728E-5</v>
       </c>
       <c r="AP10">
-        <v>-3.9268400613410844E-5</v>
+        <v>2.8369072048134479E-5</v>
       </c>
       <c r="AQ10">
-        <v>-1.3079474208521902E-3</v>
+        <v>-3.9325834437783079E-5</v>
+      </c>
+      <c r="AR10">
+        <v>-1.3093890347538821E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-0.31097216190126653</v>
+        <v>-0.31205740280407029</v>
       </c>
       <c r="C11">
-        <v>1.4023728334026914E-4</v>
+        <v>1.4065523718975839E-4</v>
       </c>
       <c r="D11">
-        <v>4.9873168394480547E-7</v>
+        <v>8.7421588639760633E-7</v>
       </c>
       <c r="E11">
-        <v>2.6617813063754672E-8</v>
+        <v>2.3690955699467459E-8</v>
       </c>
       <c r="F11">
-        <v>9.2893922120955853E-4</v>
+        <v>9.3225011656550424E-4</v>
       </c>
       <c r="G11">
-        <v>8.6715963143938618E-4</v>
+        <v>8.6716788748521646E-4</v>
       </c>
       <c r="H11">
-        <v>7.6751238638529977E-4</v>
+        <v>7.6748269586649398E-4</v>
       </c>
       <c r="I11">
-        <v>9.2260799600029318E-4</v>
+        <v>9.2443821230499008E-4</v>
       </c>
       <c r="J11">
-        <v>9.3040363847546109E-4</v>
+        <v>9.3142501353699861E-4</v>
       </c>
       <c r="K11">
-        <v>9.4768211965577903E-4</v>
+        <v>9.4775546468833392E-4</v>
       </c>
       <c r="L11">
-        <v>1.987753783960679E-3</v>
+        <v>1.9914153837422631E-3</v>
       </c>
       <c r="M11">
-        <v>1.8763115494407911E-4</v>
+        <v>1.1664176233322463E-4</v>
       </c>
       <c r="N11">
-        <v>6.3389990730470928E-5</v>
+        <v>6.6684729493180449E-5</v>
       </c>
       <c r="O11">
-        <v>1.1420923373704357E-4</v>
+        <v>1.1916743051129176E-4</v>
       </c>
       <c r="P11">
-        <v>-1.0134571477974936E-5</v>
+        <v>-1.4128987074915372E-5</v>
       </c>
       <c r="Q11">
-        <v>1.6478273802559618E-5</v>
+        <v>1.3274980795444937E-5</v>
       </c>
       <c r="R11">
-        <v>9.3230698612035924E-12</v>
+        <v>1.6522151159633746E-4</v>
       </c>
       <c r="S11">
-        <v>2.7920041098783123E-7</v>
+        <v>-9.743656771696923E-8</v>
       </c>
       <c r="T11">
-        <v>7.6756881094066178E-5</v>
+        <v>2.4294686119932198E-7</v>
       </c>
       <c r="U11">
-        <v>2.4206490012416434E-4</v>
+        <v>8.6219933250658687E-5</v>
       </c>
       <c r="V11">
-        <v>3.7949607995923796E-4</v>
+        <v>2.5156608373770898E-4</v>
       </c>
       <c r="W11">
-        <v>5.8351952611375793E-4</v>
+        <v>3.8896045206823337E-4</v>
       </c>
       <c r="X11">
-        <v>-2.1965468206759297E-5</v>
+        <v>5.9134178277222855E-4</v>
       </c>
       <c r="Y11">
-        <v>1.474798582614458E-5</v>
+        <v>-2.2834476254886736E-5</v>
       </c>
       <c r="Z11">
-        <v>2.0324370487782276E-5</v>
+        <v>1.4200954736614277E-5</v>
       </c>
       <c r="AA11">
-        <v>2.4743376151656728E-5</v>
+        <v>1.9352416302367633E-5</v>
       </c>
       <c r="AB11">
-        <v>4.1177353497016356E-5</v>
+        <v>2.4725760862196182E-5</v>
       </c>
       <c r="AC11">
-        <v>1.0117371643853889E-4</v>
+        <v>4.0605089598333495E-5</v>
       </c>
       <c r="AD11">
-        <v>-2.0070685526090337E-6</v>
+        <v>1.0069247328556263E-4</v>
       </c>
       <c r="AE11">
-        <v>8.1815627285204007E-5</v>
+        <v>-2.6191783581515273E-6</v>
       </c>
       <c r="AF11">
-        <v>3.9811978649015683E-5</v>
+        <v>8.09291225211429E-5</v>
       </c>
       <c r="AG11">
-        <v>3.3611327592700268E-5</v>
+        <v>3.8859201443677496E-5</v>
       </c>
       <c r="AH11">
-        <v>8.1296279798947428E-5</v>
+        <v>3.2527472860314783E-5</v>
       </c>
       <c r="AI11">
-        <v>-2.4066676115796985E-5</v>
+        <v>8.1530340148463717E-5</v>
       </c>
       <c r="AJ11">
-        <v>1.191605207341665E-5</v>
+        <v>-2.4792242733467145E-5</v>
       </c>
       <c r="AK11">
-        <v>2.4160640522381349E-6</v>
+        <v>1.0968483219124091E-5</v>
       </c>
       <c r="AL11">
-        <v>3.5064601021060789E-5</v>
+        <v>2.397146460787926E-6</v>
       </c>
       <c r="AM11">
-        <v>2.5405246892678114E-5</v>
+        <v>3.5582490890898716E-5</v>
       </c>
       <c r="AN11">
-        <v>-8.5454281862489537E-5</v>
+        <v>2.5580868588570733E-5</v>
       </c>
       <c r="AO11">
-        <v>-1.2942189627549643E-4</v>
+        <v>-9.167141801651303E-5</v>
       </c>
       <c r="AP11">
-        <v>-1.2099708312511239E-4</v>
+        <v>-1.2936524605460301E-4</v>
       </c>
       <c r="AQ11">
-        <v>-1.414151135808499E-3</v>
+        <v>-1.184377992616742E-4</v>
+      </c>
+      <c r="AR11">
+        <v>-1.4224093550517488E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>8.2285815045357424E-2</v>
+        <v>6.2731313151585297E-2</v>
       </c>
       <c r="C12">
-        <v>5.1447425980230213E-6</v>
+        <v>8.6112091692997289E-6</v>
       </c>
       <c r="D12">
-        <v>3.4702099693127012E-5</v>
+        <v>3.4441900912970938E-5</v>
       </c>
       <c r="E12">
-        <v>-2.3131242938584193E-7</v>
+        <v>-2.3015219449498051E-7</v>
       </c>
       <c r="F12">
-        <v>-1.035906380555159E-4</v>
+        <v>-1.6602519071407239E-4</v>
       </c>
       <c r="G12">
-        <v>-7.8109208978104007E-5</v>
+        <v>-9.9202937585403037E-5</v>
       </c>
       <c r="H12">
-        <v>1.2757067527436784E-4</v>
+        <v>1.1363816361346469E-4</v>
       </c>
       <c r="I12">
-        <v>1.9947495953088402E-4</v>
+        <v>1.6299466364116461E-4</v>
       </c>
       <c r="J12">
-        <v>1.9985273475419258E-4</v>
+        <v>1.6083784252666765E-4</v>
       </c>
       <c r="K12">
-        <v>-3.2567021250590373E-5</v>
+        <v>-4.9365867377557527E-5</v>
       </c>
       <c r="L12">
-        <v>1.8763115494407911E-4</v>
+        <v>1.1664176233322463E-4</v>
       </c>
       <c r="M12">
-        <v>2.3822979943480785E-3</v>
+        <v>3.7303328407294147E-3</v>
       </c>
       <c r="N12">
-        <v>9.1770972196945791E-4</v>
+        <v>8.765195680925143E-4</v>
       </c>
       <c r="O12">
-        <v>5.8221097401193545E-4</v>
+        <v>5.3752699949331274E-4</v>
       </c>
       <c r="P12">
-        <v>-9.5758626674468652E-6</v>
+        <v>3.1807703983632797E-5</v>
       </c>
       <c r="Q12">
-        <v>4.4960659175164244E-5</v>
+        <v>7.5220033880616386E-5</v>
       </c>
       <c r="R12">
-        <v>-1.3333294103256606E-6</v>
+        <v>-2.653521883931787E-3</v>
       </c>
       <c r="S12">
-        <v>1.0176437447734441E-6</v>
+        <v>-1.6648626171438086E-7</v>
       </c>
       <c r="T12">
-        <v>5.9888275028258879E-4</v>
+        <v>1.1316195801015184E-6</v>
       </c>
       <c r="U12">
-        <v>9.442275494499486E-4</v>
+        <v>5.5357697921798281E-4</v>
       </c>
       <c r="V12">
-        <v>9.8266822688255844E-4</v>
+        <v>8.8075303916661035E-4</v>
       </c>
       <c r="W12">
-        <v>9.6845664510417898E-4</v>
+        <v>9.0792193412165862E-4</v>
       </c>
       <c r="X12">
-        <v>-6.2278906244900794E-5</v>
+        <v>9.0329353484267232E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.0231541598829889E-4</v>
+        <v>-5.4859984940604226E-5</v>
       </c>
       <c r="Z12">
-        <v>-4.8978046632240364E-5</v>
+        <v>-1.0375770842447805E-4</v>
       </c>
       <c r="AA12">
-        <v>-1.1098295168371038E-4</v>
+        <v>-6.0943647984895087E-5</v>
       </c>
       <c r="AB12">
-        <v>-6.9205814836940461E-5</v>
+        <v>-1.3932787522174736E-4</v>
       </c>
       <c r="AC12">
-        <v>-4.8256077991980374E-5</v>
+        <v>-7.2199292666469555E-5</v>
       </c>
       <c r="AD12">
-        <v>-5.2392372042239473E-5</v>
+        <v>-6.3965420224032805E-5</v>
       </c>
       <c r="AE12">
-        <v>-7.5121324619836506E-5</v>
+        <v>-4.7135871440098483E-5</v>
       </c>
       <c r="AF12">
-        <v>-9.3145208914088926E-5</v>
+        <v>-8.3986161123077315E-5</v>
       </c>
       <c r="AG12">
-        <v>-7.7223843157837673E-5</v>
+        <v>-1.1020423382030851E-4</v>
       </c>
       <c r="AH12">
-        <v>-3.2386624152369137E-5</v>
+        <v>-9.984613231822355E-5</v>
       </c>
       <c r="AI12">
-        <v>-1.1727002339032006E-4</v>
+        <v>-7.3308183296849958E-5</v>
       </c>
       <c r="AJ12">
-        <v>-4.4754407273300953E-5</v>
+        <v>-1.4333964618953388E-4</v>
       </c>
       <c r="AK12">
-        <v>-4.9393925643324691E-6</v>
+        <v>-3.0951248728201971E-5</v>
       </c>
       <c r="AL12">
-        <v>4.5142387333377363E-6</v>
+        <v>-6.7743743791598887E-6</v>
       </c>
       <c r="AM12">
-        <v>3.0585834488922698E-5</v>
+        <v>3.8748218790004901E-5</v>
       </c>
       <c r="AN12">
-        <v>-3.200603423451919E-4</v>
+        <v>5.2920032512073249E-5</v>
       </c>
       <c r="AO12">
-        <v>-1.722825983401787E-4</v>
+        <v>-2.5805846217603852E-4</v>
       </c>
       <c r="AP12">
-        <v>8.6181194343178005E-5</v>
+        <v>-1.8484590998285141E-4</v>
       </c>
       <c r="AQ12">
-        <v>-1.8426557074204353E-3</v>
+        <v>-4.578124551861591E-5</v>
+      </c>
+      <c r="AR12">
+        <v>-1.8153576128611196E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
-        <v>-9.768703336053669E-2</v>
+        <v>-0.10513365215994817</v>
       </c>
       <c r="C13">
-        <v>-3.0141657115764432E-5</v>
+        <v>-2.6637022552932892E-5</v>
       </c>
       <c r="D13">
-        <v>-1.8902290535952477E-6</v>
+        <v>-1.2067623884613775E-6</v>
       </c>
       <c r="E13">
-        <v>5.4814708542968638E-8</v>
+        <v>5.0528850632616748E-8</v>
       </c>
       <c r="F13">
-        <v>-3.7113780297906389E-5</v>
+        <v>-2.9731825869334905E-5</v>
       </c>
       <c r="G13">
-        <v>-1.1106778717279267E-4</v>
+        <v>-1.0843729647281764E-4</v>
       </c>
       <c r="H13">
-        <v>6.6965069705783809E-5</v>
+        <v>6.9488224617278535E-5</v>
       </c>
       <c r="I13">
-        <v>9.1114879777547141E-5</v>
+        <v>9.3547503302302291E-5</v>
       </c>
       <c r="J13">
-        <v>1.1253045278680619E-4</v>
+        <v>1.1750934636720032E-4</v>
       </c>
       <c r="K13">
-        <v>-4.0484063828340482E-5</v>
+        <v>-3.9861216164640417E-5</v>
       </c>
       <c r="L13">
-        <v>6.3389990730470928E-5</v>
+        <v>6.6684729493180449E-5</v>
       </c>
       <c r="M13">
-        <v>9.1770972196945791E-4</v>
+        <v>8.765195680925143E-4</v>
       </c>
       <c r="N13">
-        <v>1.5646532966440056E-3</v>
+        <v>1.5356696727484396E-3</v>
       </c>
       <c r="O13">
-        <v>8.3603633536570251E-4</v>
+        <v>8.2570265604477806E-4</v>
       </c>
       <c r="P13">
-        <v>1.0314560732840948E-5</v>
+        <v>6.0732215726747528E-6</v>
       </c>
       <c r="Q13">
-        <v>4.0662954753325077E-5</v>
+        <v>3.6232030624993293E-5</v>
       </c>
       <c r="R13">
-        <v>2.7047131822863889E-6</v>
+        <v>1.1170199370034821E-4</v>
       </c>
       <c r="S13">
-        <v>4.0961622585628186E-6</v>
+        <v>2.4554980889757653E-6</v>
       </c>
       <c r="T13">
-        <v>8.3077080486111546E-4</v>
+        <v>3.9530674567403695E-6</v>
       </c>
       <c r="U13">
-        <v>1.1656223889178969E-3</v>
+        <v>7.9670240802041763E-4</v>
       </c>
       <c r="V13">
-        <v>1.2460425326497018E-3</v>
+        <v>1.1429280249627028E-3</v>
       </c>
       <c r="W13">
-        <v>1.2473425229289343E-3</v>
+        <v>1.2236361101059514E-3</v>
       </c>
       <c r="X13">
-        <v>-7.8598479677458082E-5</v>
+        <v>1.2247635022513022E-3</v>
       </c>
       <c r="Y13">
-        <v>-1.5617117774557681E-5</v>
+        <v>-7.6843310552708165E-5</v>
       </c>
       <c r="Z13">
-        <v>-3.2564882355588044E-5</v>
+        <v>-1.8514906931706133E-5</v>
       </c>
       <c r="AA13">
-        <v>-1.4876958711766323E-4</v>
+        <v>-3.5983829455096307E-5</v>
       </c>
       <c r="AB13">
-        <v>-2.805243251267219E-5</v>
+        <v>-1.5510901670881549E-4</v>
       </c>
       <c r="AC13">
-        <v>-5.0129465975949593E-5</v>
+        <v>-3.2165990775245349E-5</v>
       </c>
       <c r="AD13">
-        <v>1.6659774968606788E-5</v>
+        <v>-5.4345393378910537E-5</v>
       </c>
       <c r="AE13">
-        <v>-6.4531435307836756E-5</v>
+        <v>1.5549704539968531E-5</v>
       </c>
       <c r="AF13">
-        <v>-4.799231711958478E-5</v>
+        <v>-6.6743008312570109E-5</v>
       </c>
       <c r="AG13">
-        <v>-4.655986367580893E-5</v>
+        <v>-5.4469038562333377E-5</v>
       </c>
       <c r="AH13">
-        <v>-5.0729066942761998E-5</v>
+        <v>-5.2169654490839788E-5</v>
       </c>
       <c r="AI13">
-        <v>-7.1832354904920827E-5</v>
+        <v>-5.146457097473053E-5</v>
       </c>
       <c r="AJ13">
-        <v>-6.8183650654414442E-5</v>
+        <v>-7.2163491999272628E-5</v>
       </c>
       <c r="AK13">
-        <v>-6.6941176230890715E-6</v>
+        <v>-7.1856500653891633E-5</v>
       </c>
       <c r="AL13">
-        <v>3.9497308044424595E-5</v>
+        <v>-7.027197181490915E-6</v>
       </c>
       <c r="AM13">
-        <v>4.076369953180751E-5</v>
+        <v>4.6269223299862366E-5</v>
       </c>
       <c r="AN13">
-        <v>-2.3554541100202344E-4</v>
+        <v>4.294686063254817E-5</v>
       </c>
       <c r="AO13">
-        <v>-1.1478379244263959E-4</v>
+        <v>-2.5821785337472514E-4</v>
       </c>
       <c r="AP13">
-        <v>7.5340316913246697E-5</v>
+        <v>-1.0874516977415523E-4</v>
       </c>
       <c r="AQ13">
-        <v>-1.4157305479812121E-3</v>
+        <v>7.2319667593658845E-5</v>
+      </c>
+      <c r="AR13">
+        <v>-1.385178765190847E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14">
-        <v>7.638794242542879E-2</v>
+        <v>7.0527964656417738E-2</v>
       </c>
       <c r="C14">
-        <v>-2.0112437652261216E-5</v>
+        <v>-1.7655651429965078E-5</v>
       </c>
       <c r="D14">
-        <v>1.0099838873521611E-5</v>
+        <v>1.0690973080088486E-5</v>
       </c>
       <c r="E14">
-        <v>-1.9526512749761413E-7</v>
+        <v>-1.9910775263609158E-7</v>
       </c>
       <c r="F14">
-        <v>-6.855704086521265E-5</v>
+        <v>-6.172430999311113E-5</v>
       </c>
       <c r="G14">
-        <v>-1.1370285343764578E-4</v>
+        <v>-1.1090688854946735E-4</v>
       </c>
       <c r="H14">
-        <v>-3.3086822578124825E-5</v>
+        <v>-3.1581848641296865E-5</v>
       </c>
       <c r="I14">
-        <v>-2.3253893023560362E-5</v>
+        <v>-2.1114345880494765E-5</v>
       </c>
       <c r="J14">
-        <v>8.1175441025863217E-5</v>
+        <v>8.4767938279897432E-5</v>
       </c>
       <c r="K14">
-        <v>-6.7602302385645272E-5</v>
+        <v>-6.6396689378284688E-5</v>
       </c>
       <c r="L14">
-        <v>1.1420923373704357E-4</v>
+        <v>1.1916743051129176E-4</v>
       </c>
       <c r="M14">
-        <v>5.8221097401193545E-4</v>
+        <v>5.3752699949331274E-4</v>
       </c>
       <c r="N14">
-        <v>8.3603633536570251E-4</v>
+        <v>8.2570265604477806E-4</v>
       </c>
       <c r="O14">
-        <v>1.3644894791165498E-3</v>
+        <v>1.364499912452266E-3</v>
       </c>
       <c r="P14">
-        <v>4.1693150565471422E-5</v>
+        <v>3.951299182959313E-5</v>
       </c>
       <c r="Q14">
-        <v>6.1624677791174401E-5</v>
+        <v>5.8257039779410161E-5</v>
       </c>
       <c r="R14">
-        <v>-5.8963946480609949E-7</v>
+        <v>1.6058796315741961E-4</v>
       </c>
       <c r="S14">
-        <v>1.8661925277529188E-6</v>
+        <v>-7.7775153372748297E-7</v>
       </c>
       <c r="T14">
-        <v>5.6222486849111534E-4</v>
+        <v>1.7566354327066453E-6</v>
       </c>
       <c r="U14">
-        <v>8.4768197367474335E-4</v>
+        <v>5.5895863279379471E-4</v>
       </c>
       <c r="V14">
-        <v>9.7195264892663551E-4</v>
+        <v>8.4692662598610585E-4</v>
       </c>
       <c r="W14">
-        <v>1.0097894482138973E-3</v>
+        <v>9.7253536384981981E-4</v>
       </c>
       <c r="X14">
-        <v>-8.6699607570421983E-5</v>
+        <v>1.0100131686617321E-3</v>
       </c>
       <c r="Y14">
-        <v>1.0600849929859226E-5</v>
+        <v>-8.6895890569275633E-5</v>
       </c>
       <c r="Z14">
-        <v>-7.9314437795451807E-5</v>
+        <v>8.907195302550392E-6</v>
       </c>
       <c r="AA14">
-        <v>-1.4020124075363698E-4</v>
+        <v>-8.1956330862310368E-5</v>
       </c>
       <c r="AB14">
-        <v>-6.3122869523631005E-5</v>
+        <v>-1.4349713365319574E-4</v>
       </c>
       <c r="AC14">
-        <v>-3.6227492135020497E-5</v>
+        <v>-6.5628037563820899E-5</v>
       </c>
       <c r="AD14">
-        <v>-3.9881871100631914E-5</v>
+        <v>-3.8989306731457524E-5</v>
       </c>
       <c r="AE14">
-        <v>-7.5098127813273615E-5</v>
+        <v>-4.0861793304796962E-5</v>
       </c>
       <c r="AF14">
-        <v>-4.5983987193006388E-5</v>
+        <v>-7.6460541431988094E-5</v>
       </c>
       <c r="AG14">
-        <v>-3.1009572311476883E-5</v>
+        <v>-5.0418850249967062E-5</v>
       </c>
       <c r="AH14">
-        <v>-4.7042669894429304E-5</v>
+        <v>-3.4635262816992341E-5</v>
       </c>
       <c r="AI14">
-        <v>-1.0074407885215577E-4</v>
+        <v>-4.7503911382340387E-5</v>
       </c>
       <c r="AJ14">
-        <v>-4.9305930858366547E-5</v>
+        <v>-1.0169657660128924E-4</v>
       </c>
       <c r="AK14">
-        <v>-6.730334598509908E-7</v>
+        <v>-5.0857917144412029E-5</v>
       </c>
       <c r="AL14">
-        <v>-4.5536945392413001E-6</v>
+        <v>-8.9471612672911954E-7</v>
       </c>
       <c r="AM14">
-        <v>3.7495458104542818E-7</v>
+        <v>5.2819471929674983E-7</v>
       </c>
       <c r="AN14">
-        <v>-2.0511023347054877E-4</v>
+        <v>2.3039662703446028E-6</v>
       </c>
       <c r="AO14">
-        <v>3.1546564123223963E-5</v>
+        <v>-2.1930707834242724E-4</v>
       </c>
       <c r="AP14">
-        <v>-5.5606349597320476E-5</v>
+        <v>3.5521313264978954E-5</v>
       </c>
       <c r="AQ14">
-        <v>-9.3187609190677895E-4</v>
+        <v>-5.7559875845351915E-5</v>
+      </c>
+      <c r="AR14">
+        <v>-9.2926641202923429E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15">
-        <v>-0.16018735542740917</v>
+        <v>-0.16793196598048554</v>
       </c>
       <c r="C15">
-        <v>-2.2499293713269813E-5</v>
+        <v>-2.3789194441618113E-5</v>
       </c>
       <c r="D15">
-        <v>8.0220833846373284E-7</v>
+        <v>7.6504321303376806E-7</v>
       </c>
       <c r="E15">
-        <v>-1.3109522906018683E-8</v>
+        <v>-1.2937412481575491E-8</v>
       </c>
       <c r="F15">
-        <v>1.9057456995744126E-4</v>
+        <v>1.8746798063866074E-4</v>
       </c>
       <c r="G15">
-        <v>2.0876707732626106E-5</v>
+        <v>1.9277092682075853E-5</v>
       </c>
       <c r="H15">
-        <v>-5.3737705446185941E-6</v>
+        <v>-7.9018872038996658E-6</v>
       </c>
       <c r="I15">
-        <v>1.000779983181152E-4</v>
+        <v>1.0028816046733386E-4</v>
       </c>
       <c r="J15">
-        <v>3.4181586790791891E-5</v>
+        <v>3.2690853070458552E-5</v>
       </c>
       <c r="K15">
-        <v>2.4711706474932064E-5</v>
+        <v>2.3194485782185618E-5</v>
       </c>
       <c r="L15">
-        <v>-1.0134571477974936E-5</v>
+        <v>-1.4128987074915372E-5</v>
       </c>
       <c r="M15">
-        <v>-9.5758626674468652E-6</v>
+        <v>3.1807703983632797E-5</v>
       </c>
       <c r="N15">
-        <v>1.0314560732840948E-5</v>
+        <v>6.0732215726747528E-6</v>
       </c>
       <c r="O15">
-        <v>4.1693150565471422E-5</v>
+        <v>3.951299182959313E-5</v>
       </c>
       <c r="P15">
-        <v>4.5474023274856117E-4</v>
+        <v>4.6382237683640032E-4</v>
       </c>
       <c r="Q15">
-        <v>3.560848839786288E-4</v>
+        <v>3.6279423285081052E-4</v>
       </c>
       <c r="R15">
-        <v>1.9426397832806727E-8</v>
+        <v>3.4439069539979322E-4</v>
       </c>
       <c r="S15">
-        <v>5.3401211894557328E-7</v>
+        <v>4.750771886343586E-8</v>
       </c>
       <c r="T15">
-        <v>2.0795092029449142E-5</v>
+        <v>5.3558013824367894E-7</v>
       </c>
       <c r="U15">
-        <v>1.5486651373897054E-5</v>
+        <v>9.6183441664443317E-6</v>
       </c>
       <c r="V15">
-        <v>8.2849316112058465E-5</v>
+        <v>5.8372017021213597E-6</v>
       </c>
       <c r="W15">
-        <v>1.4894397473712279E-4</v>
+        <v>7.410608342376983E-5</v>
       </c>
       <c r="X15">
-        <v>1.094935515066396E-6</v>
+        <v>1.4071304877211435E-4</v>
       </c>
       <c r="Y15">
-        <v>-5.8245829301120894E-6</v>
+        <v>1.4576348239074019E-6</v>
       </c>
       <c r="Z15">
-        <v>-3.1175427167073177E-5</v>
+        <v>-3.8848887147029901E-6</v>
       </c>
       <c r="AA15">
-        <v>-3.7262553226173067E-5</v>
+        <v>-3.3265732602447057E-5</v>
       </c>
       <c r="AB15">
-        <v>-2.2876754188527154E-5</v>
+        <v>-3.925575468109598E-5</v>
       </c>
       <c r="AC15">
-        <v>-5.0072296371223039E-5</v>
+        <v>-2.2859691779367987E-5</v>
       </c>
       <c r="AD15">
-        <v>-3.4080668034028701E-5</v>
+        <v>-5.2559127628541995E-5</v>
       </c>
       <c r="AE15">
-        <v>-4.6758089173920278E-5</v>
+        <v>-3.5423501372070247E-5</v>
       </c>
       <c r="AF15">
-        <v>-2.8765651174544523E-5</v>
+        <v>-4.8448032625530947E-5</v>
       </c>
       <c r="AG15">
-        <v>-3.315460138490455E-5</v>
+        <v>-3.204011785812453E-5</v>
       </c>
       <c r="AH15">
-        <v>-7.2744924350735704E-5</v>
+        <v>-3.4690317962329692E-5</v>
       </c>
       <c r="AI15">
-        <v>-5.1069377647701991E-5</v>
+        <v>-7.2580954092408892E-5</v>
       </c>
       <c r="AJ15">
-        <v>-1.0949375670773792E-5</v>
+        <v>-5.5562749301627453E-5</v>
       </c>
       <c r="AK15">
-        <v>-3.3912605620616139E-7</v>
+        <v>-1.0432928073413338E-5</v>
       </c>
       <c r="AL15">
-        <v>-2.2546113393746064E-5</v>
+        <v>-4.9773575722059652E-7</v>
       </c>
       <c r="AM15">
-        <v>3.2506559709381887E-5</v>
+        <v>-2.1151042344867726E-5</v>
       </c>
       <c r="AN15">
-        <v>1.1901767475533589E-4</v>
+        <v>3.6959498596427942E-5</v>
       </c>
       <c r="AO15">
-        <v>-5.869035117726453E-5</v>
+        <v>1.2773144809495276E-4</v>
       </c>
       <c r="AP15">
-        <v>4.6271565935284006E-5</v>
+        <v>-5.7656337052169139E-5</v>
       </c>
       <c r="AQ15">
-        <v>-3.9554637457496435E-4</v>
+        <v>3.125910408156593E-5</v>
+      </c>
+      <c r="AR15">
+        <v>-3.8917987329987043E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
       <c r="B16">
-        <v>-0.29036718320850879</v>
+        <v>-0.29784389523649452</v>
       </c>
       <c r="C16">
-        <v>-2.2586808177342252E-5</v>
+        <v>-2.301808862443896E-5</v>
       </c>
       <c r="D16">
-        <v>2.1282685206250372E-6</v>
+        <v>2.1390247898502815E-6</v>
       </c>
       <c r="E16">
-        <v>-6.2772044780458462E-8</v>
+        <v>-6.3156979178276286E-8</v>
       </c>
       <c r="F16">
-        <v>1.7051250024409999E-4</v>
+        <v>1.6771431991547862E-4</v>
       </c>
       <c r="G16">
-        <v>2.5985018000354424E-5</v>
+        <v>2.4805816520034234E-5</v>
       </c>
       <c r="H16">
-        <v>1.5761996969567869E-5</v>
+        <v>1.410971794572072E-5</v>
       </c>
       <c r="I16">
-        <v>1.0578522504095869E-4</v>
+        <v>1.1277986531697083E-4</v>
       </c>
       <c r="J16">
-        <v>3.7616276483110522E-5</v>
+        <v>3.5731808964720136E-5</v>
       </c>
       <c r="K16">
-        <v>4.3474608275563163E-5</v>
+        <v>4.2399092598277934E-5</v>
       </c>
       <c r="L16">
-        <v>1.6478273802559618E-5</v>
+        <v>1.3274980795444937E-5</v>
       </c>
       <c r="M16">
-        <v>4.4960659175164244E-5</v>
+        <v>7.5220033880616386E-5</v>
       </c>
       <c r="N16">
-        <v>4.0662954753325077E-5</v>
+        <v>3.6232030624993293E-5</v>
       </c>
       <c r="O16">
-        <v>6.1624677791174401E-5</v>
+        <v>5.8257039779410161E-5</v>
       </c>
       <c r="P16">
-        <v>3.560848839786288E-4</v>
+        <v>3.6279423285081052E-4</v>
       </c>
       <c r="Q16">
-        <v>6.3917201808539649E-4</v>
+        <v>6.461212123203946E-4</v>
       </c>
       <c r="R16">
-        <v>2.49470269780557E-7</v>
+        <v>2.8663360153962232E-4</v>
       </c>
       <c r="S16">
-        <v>1.5835452301698169E-6</v>
+        <v>2.7475565491847644E-7</v>
       </c>
       <c r="T16">
-        <v>6.4822760322151928E-5</v>
+        <v>1.5918997090952188E-6</v>
       </c>
       <c r="U16">
-        <v>1.0771820110734944E-4</v>
+        <v>5.8598990681616715E-5</v>
       </c>
       <c r="V16">
-        <v>1.6181146352520502E-4</v>
+        <v>9.8359890728288909E-5</v>
       </c>
       <c r="W16">
-        <v>2.6017211800716147E-4</v>
+        <v>1.5415680960899469E-4</v>
       </c>
       <c r="X16">
-        <v>6.2610150065105977E-6</v>
+        <v>2.5289764993684856E-4</v>
       </c>
       <c r="Y16">
-        <v>1.9898933301434418E-5</v>
+        <v>6.5559361166015352E-6</v>
       </c>
       <c r="Z16">
-        <v>-7.5816050341258079E-6</v>
+        <v>2.0796883493094963E-5</v>
       </c>
       <c r="AA16">
-        <v>-3.6685283273134189E-5</v>
+        <v>-1.0496459159796341E-5</v>
       </c>
       <c r="AB16">
-        <v>-3.8715299044301133E-5</v>
+        <v>-3.9485387687332194E-5</v>
       </c>
       <c r="AC16">
-        <v>-6.5091509979180756E-5</v>
+        <v>-3.9501476374592625E-5</v>
       </c>
       <c r="AD16">
-        <v>-6.8681662036768412E-6</v>
+        <v>-6.862772778935388E-5</v>
       </c>
       <c r="AE16">
-        <v>-3.7631187956115223E-5</v>
+        <v>-9.7347595746020131E-6</v>
       </c>
       <c r="AF16">
-        <v>-2.2762734449607295E-5</v>
+        <v>-4.0634291395630137E-5</v>
       </c>
       <c r="AG16">
-        <v>-1.4122926656044249E-5</v>
+        <v>-2.6836233821094467E-5</v>
       </c>
       <c r="AH16">
-        <v>-5.8817254954287726E-5</v>
+        <v>-1.672743705330049E-5</v>
       </c>
       <c r="AI16">
-        <v>-3.838290624400074E-5</v>
+        <v>-5.9407795257567903E-5</v>
       </c>
       <c r="AJ16">
-        <v>-3.0873430161111322E-5</v>
+        <v>-4.3466662405800127E-5</v>
       </c>
       <c r="AK16">
-        <v>3.7534158956152518E-6</v>
+        <v>-3.2141218011267882E-5</v>
       </c>
       <c r="AL16">
-        <v>-2.822320103721917E-5</v>
+        <v>3.6578289833164902E-6</v>
       </c>
       <c r="AM16">
-        <v>3.7413788626726276E-5</v>
+        <v>-2.6881329929756098E-5</v>
       </c>
       <c r="AN16">
-        <v>5.7451431620964382E-5</v>
+        <v>4.0798407042487686E-5</v>
       </c>
       <c r="AO16">
-        <v>-1.2516515398247423E-6</v>
+        <v>6.3268827136260056E-5</v>
       </c>
       <c r="AP16">
-        <v>7.2041057755371378E-5</v>
+        <v>-1.4219726237313363E-6</v>
       </c>
       <c r="AQ16">
-        <v>-5.844187085943701E-4</v>
+        <v>5.9821689659732502E-5</v>
+      </c>
+      <c r="AR16">
+        <v>-5.7924486955479148E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="B17">
-        <v>3.3896248744885579E-3</v>
+        <v>-0.11841368524533599</v>
       </c>
       <c r="C17">
-        <v>-2.1314131056072062E-6</v>
+        <v>-1.9991232116846684E-5</v>
       </c>
       <c r="D17">
-        <v>8.0256914007411466E-8</v>
+        <v>4.4112042401839107E-7</v>
       </c>
       <c r="E17">
-        <v>-1.4423251762428079E-9</v>
+        <v>-4.5650897893752227E-9</v>
       </c>
       <c r="F17">
-        <v>3.0734449677817973E-6</v>
+        <v>3.2619929965713407E-4</v>
       </c>
       <c r="G17">
-        <v>-6.2137180231444307E-7</v>
+        <v>8.1138257130614728E-5</v>
       </c>
       <c r="H17">
-        <v>-1.1611535654556061E-6</v>
+        <v>2.9122343371156781E-5</v>
       </c>
       <c r="I17">
-        <v>1.5461417812720125E-6</v>
+        <v>1.6310890532891071E-4</v>
       </c>
       <c r="J17">
-        <v>-8.2603992970004066E-7</v>
+        <v>1.1666353154177341E-4</v>
       </c>
       <c r="K17">
-        <v>7.4024502984203195E-7</v>
+        <v>6.7223786297888498E-5</v>
       </c>
       <c r="L17">
-        <v>9.3230698612035924E-12</v>
+        <v>1.6522151159633746E-4</v>
       </c>
       <c r="M17">
-        <v>-1.3333294103256606E-6</v>
+        <v>-2.653521883931787E-3</v>
       </c>
       <c r="N17">
-        <v>2.7047131822863889E-6</v>
+        <v>1.1170199370034821E-4</v>
       </c>
       <c r="O17">
-        <v>-5.8963946480609949E-7</v>
+        <v>1.6058796315741961E-4</v>
       </c>
       <c r="P17">
-        <v>1.9426397832806727E-8</v>
+        <v>3.4439069539979322E-4</v>
       </c>
       <c r="Q17">
-        <v>2.49470269780557E-7</v>
+        <v>2.8663360153962232E-4</v>
       </c>
       <c r="R17">
-        <v>6.9141493532443768E-7</v>
+        <v>5.4442690416987545E-3</v>
       </c>
       <c r="S17">
-        <v>8.0230964082521683E-10</v>
+        <v>-2.8117772270801111E-6</v>
       </c>
       <c r="T17">
-        <v>-5.555640420507858E-7</v>
+        <v>7.384207190735776E-8</v>
       </c>
       <c r="U17">
-        <v>-1.3447481638492051E-6</v>
+        <v>1.8588413253971007E-4</v>
       </c>
       <c r="V17">
-        <v>-1.7722475576093131E-6</v>
+        <v>2.1754077378542989E-4</v>
       </c>
       <c r="W17">
-        <v>-2.2866867654685793E-6</v>
+        <v>3.0985613200675135E-4</v>
       </c>
       <c r="X17">
-        <v>8.8985406800946218E-8</v>
+        <v>3.5940480533686492E-4</v>
       </c>
       <c r="Y17">
-        <v>-4.3443997023016634E-7</v>
+        <v>-2.1410202881636695E-5</v>
       </c>
       <c r="Z17">
-        <v>1.6770348741398243E-6</v>
+        <v>-2.1043541846403353E-7</v>
       </c>
       <c r="AA17">
-        <v>1.8694535527796605E-6</v>
+        <v>4.2380774740375976E-7</v>
       </c>
       <c r="AB17">
-        <v>1.8537091297097828E-6</v>
+        <v>1.8610082646741542E-5</v>
       </c>
       <c r="AC17">
-        <v>9.5667861141266355E-7</v>
+        <v>-2.2288464713802491E-5</v>
       </c>
       <c r="AD17">
-        <v>2.3295339590021383E-6</v>
+        <v>-1.7727784211023727E-5</v>
       </c>
       <c r="AE17">
-        <v>1.8611602471083274E-6</v>
+        <v>-4.8783790680020389E-5</v>
       </c>
       <c r="AF17">
-        <v>1.6305010205535036E-6</v>
+        <v>-2.5065042625230715E-5</v>
       </c>
       <c r="AG17">
-        <v>4.5757298848173339E-7</v>
+        <v>1.8090633652816132E-6</v>
       </c>
       <c r="AH17">
-        <v>-4.6269263056471134E-8</v>
+        <v>1.2618829344055396E-5</v>
       </c>
       <c r="AI17">
-        <v>6.5241491009719912E-7</v>
+        <v>3.5922120109516746E-5</v>
       </c>
       <c r="AJ17">
-        <v>9.827218876176016E-7</v>
+        <v>1.1023125334045581E-5</v>
       </c>
       <c r="AK17">
-        <v>1.8334387705335062E-7</v>
+        <v>-4.254930286671401E-5</v>
       </c>
       <c r="AL17">
-        <v>4.3052011607947887E-7</v>
+        <v>2.802164331873797E-6</v>
       </c>
       <c r="AM17">
-        <v>1.6319100763837145E-6</v>
+        <v>-8.6828716712565845E-5</v>
       </c>
       <c r="AN17">
-        <v>4.2662222833033678E-6</v>
+        <v>-2.3798799603195429E-5</v>
       </c>
       <c r="AO17">
-        <v>-3.1499113454875539E-6</v>
+        <v>-4.7291676796752815E-5</v>
       </c>
       <c r="AP17">
-        <v>1.6854425713366985E-6</v>
+        <v>4.6749325977003619E-6</v>
       </c>
       <c r="AQ17">
-        <v>-3.5939342340613359E-5</v>
+        <v>3.4084743905640205E-4</v>
+      </c>
+      <c r="AR17">
+        <v>-4.5208437257259295E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18">
-        <v>6.4096400774035587E-3</v>
+        <v>3.3955748773050205E-3</v>
       </c>
       <c r="C18">
-        <v>-4.7945347777298271E-7</v>
+        <v>-2.1368279016704371E-6</v>
       </c>
       <c r="D18">
-        <v>1.5109744239549213E-7</v>
+        <v>7.4634706505448963E-8</v>
       </c>
       <c r="E18">
-        <v>-2.7431527697157474E-10</v>
+        <v>-1.399242314237439E-9</v>
       </c>
       <c r="F18">
-        <v>-1.7021723389542858E-6</v>
+        <v>3.0203234492251625E-6</v>
       </c>
       <c r="G18">
-        <v>-8.2971140868822672E-7</v>
+        <v>-6.3359574133267163E-7</v>
       </c>
       <c r="H18">
-        <v>5.264477105344958E-7</v>
+        <v>-1.1664683959863817E-6</v>
       </c>
       <c r="I18">
-        <v>3.6767718028934699E-7</v>
+        <v>1.5162897221240028E-6</v>
       </c>
       <c r="J18">
-        <v>-4.953143116865152E-7</v>
+        <v>-8.5658903423030848E-7</v>
       </c>
       <c r="K18">
-        <v>2.1282269063242215E-7</v>
+        <v>7.1670827353147135E-7</v>
       </c>
       <c r="L18">
-        <v>2.7920041098783123E-7</v>
+        <v>-9.743656771696923E-8</v>
       </c>
       <c r="M18">
-        <v>1.0176437447734441E-6</v>
+        <v>-1.6648626171438086E-7</v>
       </c>
       <c r="N18">
-        <v>4.0961622585628186E-6</v>
+        <v>2.4554980889757653E-6</v>
       </c>
       <c r="O18">
-        <v>1.8661925277529188E-6</v>
+        <v>-7.7775153372748297E-7</v>
       </c>
       <c r="P18">
-        <v>5.3401211894557328E-7</v>
+        <v>4.750771886343586E-8</v>
       </c>
       <c r="Q18">
-        <v>1.5835452301698169E-6</v>
+        <v>2.7475565491847644E-7</v>
       </c>
       <c r="R18">
-        <v>8.0230964082521683E-10</v>
+        <v>-2.8117772270801111E-6</v>
       </c>
       <c r="S18">
-        <v>5.4053218381145832E-7</v>
+        <v>6.9236643712740672E-7</v>
       </c>
       <c r="T18">
-        <v>1.4365341546275677E-6</v>
+        <v>1.147494613922276E-9</v>
       </c>
       <c r="U18">
-        <v>8.8503257474791971E-8</v>
+        <v>-1.0209376897522538E-6</v>
       </c>
       <c r="V18">
-        <v>-3.9474375791844886E-7</v>
+        <v>-1.7221658705942185E-6</v>
       </c>
       <c r="W18">
-        <v>-4.2656000868510233E-7</v>
+        <v>-2.1884907717636586E-6</v>
       </c>
       <c r="X18">
-        <v>-8.6811795515320731E-8</v>
+        <v>-2.6786213730512468E-6</v>
       </c>
       <c r="Y18">
-        <v>-7.4583835058463581E-7</v>
+        <v>1.2425686991873106E-7</v>
       </c>
       <c r="Z18">
-        <v>2.2026411488703709E-6</v>
+        <v>-4.3427141609273728E-7</v>
       </c>
       <c r="AA18">
-        <v>5.7403183156519701E-7</v>
+        <v>1.6927981267511762E-6</v>
       </c>
       <c r="AB18">
-        <v>1.4876646129928866E-6</v>
+        <v>1.8758643822322131E-6</v>
       </c>
       <c r="AC18">
-        <v>1.444191738043176E-6</v>
+        <v>1.874872039419083E-6</v>
       </c>
       <c r="AD18">
-        <v>3.0555373342077703E-6</v>
+        <v>9.6666673244492122E-7</v>
       </c>
       <c r="AE18">
-        <v>1.2878337366922777E-6</v>
+        <v>2.3630718049775176E-6</v>
       </c>
       <c r="AF18">
-        <v>1.1058903538892659E-6</v>
+        <v>1.8759605362559923E-6</v>
       </c>
       <c r="AG18">
-        <v>2.1224009477937668E-6</v>
+        <v>1.650979196924224E-6</v>
       </c>
       <c r="AH18">
-        <v>1.7949373561312164E-6</v>
+        <v>4.6490583965244025E-7</v>
       </c>
       <c r="AI18">
-        <v>1.255205398558928E-6</v>
+        <v>-1.8151045883140975E-8</v>
       </c>
       <c r="AJ18">
-        <v>1.7837850240597375E-6</v>
+        <v>6.8205612843783312E-7</v>
       </c>
       <c r="AK18">
-        <v>1.0507136979886374E-7</v>
+        <v>1.0021656004577799E-6</v>
       </c>
       <c r="AL18">
-        <v>-2.7538131528380519E-7</v>
+        <v>1.8400954347317023E-7</v>
       </c>
       <c r="AM18">
-        <v>-8.443903227481615E-7</v>
+        <v>4.4041929045943611E-7</v>
       </c>
       <c r="AN18">
-        <v>1.073758096602815E-6</v>
+        <v>1.6260607114634014E-6</v>
       </c>
       <c r="AO18">
-        <v>1.1364141862566055E-6</v>
+        <v>4.378581733912487E-6</v>
       </c>
       <c r="AP18">
-        <v>4.4094739935862102E-7</v>
+        <v>-3.1479742465413821E-6</v>
       </c>
       <c r="AQ18">
-        <v>-3.7450627238493311E-5</v>
+        <v>1.6356103589936964E-6</v>
+      </c>
+      <c r="AR18">
+        <v>-3.5507447590695699E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>31</v>
       </c>
       <c r="B19">
-        <v>6.1420640408511917E-2</v>
+        <v>6.4033639247687811E-3</v>
       </c>
       <c r="C19">
-        <v>-1.0673484702895094E-5</v>
+        <v>-4.7837096942411658E-7</v>
       </c>
       <c r="D19">
-        <v>5.1030028172586284E-7</v>
+        <v>1.5011781054636549E-7</v>
       </c>
       <c r="E19">
-        <v>1.9731431167347116E-8</v>
+        <v>-2.699530366139988E-10</v>
       </c>
       <c r="F19">
-        <v>-6.8545697744600841E-5</v>
+        <v>-1.7356364933733404E-6</v>
       </c>
       <c r="G19">
-        <v>-7.2899349776584698E-5</v>
+        <v>-8.3343042330275326E-7</v>
       </c>
       <c r="H19">
-        <v>-1.9866113831980736E-6</v>
+        <v>5.301842216694119E-7</v>
       </c>
       <c r="I19">
-        <v>-3.4503047078787752E-5</v>
+        <v>3.7028689239618184E-7</v>
       </c>
       <c r="J19">
-        <v>4.4637275949545074E-5</v>
+        <v>-4.902424090789011E-7</v>
       </c>
       <c r="K19">
-        <v>2.0313778682854789E-5</v>
+        <v>1.976317978857674E-7</v>
       </c>
       <c r="L19">
-        <v>7.6756881094066178E-5</v>
+        <v>2.4294686119932198E-7</v>
       </c>
       <c r="M19">
-        <v>5.9888275028258879E-4</v>
+        <v>1.1316195801015184E-6</v>
       </c>
       <c r="N19">
-        <v>8.3077080486111546E-4</v>
+        <v>3.9530674567403695E-6</v>
       </c>
       <c r="O19">
-        <v>5.6222486849111534E-4</v>
+        <v>1.7566354327066453E-6</v>
       </c>
       <c r="P19">
-        <v>2.0795092029449142E-5</v>
+        <v>5.3558013824367894E-7</v>
       </c>
       <c r="Q19">
-        <v>6.4822760322151928E-5</v>
+        <v>1.5918997090952188E-6</v>
       </c>
       <c r="R19">
-        <v>-5.555640420507858E-7</v>
+        <v>7.384207190735776E-8</v>
       </c>
       <c r="S19">
-        <v>1.4365341546275677E-6</v>
+        <v>1.147494613922276E-9</v>
       </c>
       <c r="T19">
-        <v>1.098904984289573E-3</v>
+        <v>5.4119625220506971E-7</v>
       </c>
       <c r="U19">
-        <v>1.0568694061240886E-3</v>
+        <v>1.1987044576431225E-6</v>
       </c>
       <c r="V19">
-        <v>1.084448190829062E-3</v>
+        <v>-1.9782728430600284E-7</v>
       </c>
       <c r="W19">
-        <v>1.0562671546371534E-3</v>
+        <v>-6.3665781424131857E-7</v>
       </c>
       <c r="X19">
-        <v>-8.9907985798011531E-5</v>
+        <v>-6.7667992689169111E-7</v>
       </c>
       <c r="Y19">
-        <v>-3.9401235947596311E-5</v>
+        <v>-6.976396320248406E-8</v>
       </c>
       <c r="Z19">
-        <v>-6.3204131786215797E-5</v>
+        <v>-7.5305136532698109E-7</v>
       </c>
       <c r="AA19">
-        <v>-1.4131031433913004E-4</v>
+        <v>2.2165723038159063E-6</v>
       </c>
       <c r="AB19">
-        <v>-3.6422773862495831E-5</v>
+        <v>5.7337131840473079E-7</v>
       </c>
       <c r="AC19">
-        <v>-6.421836147296262E-5</v>
+        <v>1.4914308783271138E-6</v>
       </c>
       <c r="AD19">
-        <v>-1.3074955380069887E-5</v>
+        <v>1.4496723034041265E-6</v>
       </c>
       <c r="AE19">
-        <v>-1.0236663306032121E-4</v>
+        <v>3.0738925342622801E-6</v>
       </c>
       <c r="AF19">
-        <v>-6.3710385903014417E-5</v>
+        <v>1.2951561038672122E-6</v>
       </c>
       <c r="AG19">
-        <v>-1.007054982115433E-4</v>
+        <v>1.106825105242448E-6</v>
       </c>
       <c r="AH19">
-        <v>-5.6119967496869711E-5</v>
+        <v>2.1319103233906534E-6</v>
       </c>
       <c r="AI19">
-        <v>-8.6680454820802877E-5</v>
+        <v>1.8017606455416307E-6</v>
       </c>
       <c r="AJ19">
-        <v>-6.1006798192369193E-5</v>
+        <v>1.2605742181323541E-6</v>
       </c>
       <c r="AK19">
-        <v>-1.5362920924603469E-6</v>
+        <v>1.7906963979163347E-6</v>
       </c>
       <c r="AL19">
-        <v>-1.3783158448757709E-5</v>
+        <v>1.0436730982603765E-7</v>
       </c>
       <c r="AM19">
-        <v>1.7382599122846092E-5</v>
+        <v>-2.8659827315869238E-7</v>
       </c>
       <c r="AN19">
-        <v>-2.3319174777097114E-4</v>
+        <v>-8.246495457671037E-7</v>
       </c>
       <c r="AO19">
-        <v>-9.4160293775743755E-5</v>
+        <v>1.0863258192343018E-6</v>
       </c>
       <c r="AP19">
-        <v>2.7555642063318924E-6</v>
+        <v>1.1393478751827723E-6</v>
       </c>
       <c r="AQ19">
-        <v>-1.0251759642876408E-3</v>
+        <v>3.8065117494073738E-7</v>
+      </c>
+      <c r="AR19">
+        <v>-3.7219440850434456E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
       <c r="B20">
-        <v>0.19574973953966798</v>
+        <v>4.9219270189157359E-2</v>
       </c>
       <c r="C20">
-        <v>-1.1917548239504753E-5</v>
+        <v>-1.5244814183300351E-6</v>
       </c>
       <c r="D20">
-        <v>-1.4168889714583302E-6</v>
+        <v>2.6290738479293803E-6</v>
       </c>
       <c r="E20">
-        <v>4.6841916230385024E-8</v>
+        <v>3.3963749674784312E-9</v>
       </c>
       <c r="F20">
-        <v>-1.1285954672276083E-4</v>
+        <v>-5.8484053727484516E-5</v>
       </c>
       <c r="G20">
-        <v>-5.4913677236371022E-5</v>
+        <v>-6.7179132887617822E-5</v>
       </c>
       <c r="H20">
-        <v>-1.0626962083511521E-5</v>
+        <v>-1.3106869394842989E-6</v>
       </c>
       <c r="I20">
-        <v>-8.498879946053291E-6</v>
+        <v>-3.2656810632920402E-5</v>
       </c>
       <c r="J20">
-        <v>1.1229399958418665E-4</v>
+        <v>5.3482635041096952E-5</v>
       </c>
       <c r="K20">
-        <v>5.2655564435106838E-5</v>
+        <v>2.2628048095354618E-5</v>
       </c>
       <c r="L20">
-        <v>2.4206490012416434E-4</v>
+        <v>8.6219933250658687E-5</v>
       </c>
       <c r="M20">
-        <v>9.442275494499486E-4</v>
+        <v>5.5357697921798281E-4</v>
       </c>
       <c r="N20">
-        <v>1.1656223889178969E-3</v>
+        <v>7.9670240802041763E-4</v>
       </c>
       <c r="O20">
-        <v>8.4768197367474335E-4</v>
+        <v>5.5895863279379471E-4</v>
       </c>
       <c r="P20">
-        <v>1.5486651373897054E-5</v>
+        <v>9.6183441664443317E-6</v>
       </c>
       <c r="Q20">
-        <v>1.0771820110734944E-4</v>
+        <v>5.8598990681616715E-5</v>
       </c>
       <c r="R20">
-        <v>-1.3447481638492051E-6</v>
+        <v>1.8588413253971007E-4</v>
       </c>
       <c r="S20">
-        <v>8.8503257474791971E-8</v>
+        <v>-1.0209376897522538E-6</v>
       </c>
       <c r="T20">
-        <v>1.0568694061240886E-3</v>
+        <v>1.1987044576431225E-6</v>
       </c>
       <c r="U20">
-        <v>1.6452200017001285E-3</v>
+        <v>1.086977632958782E-3</v>
       </c>
       <c r="V20">
-        <v>1.4656753578747973E-3</v>
+        <v>1.0512204497081954E-3</v>
       </c>
       <c r="W20">
-        <v>1.4687187730693765E-3</v>
+        <v>1.0812167587195361E-3</v>
       </c>
       <c r="X20">
-        <v>-1.0742096630132804E-4</v>
+        <v>1.0511043088143215E-3</v>
       </c>
       <c r="Y20">
-        <v>-3.5724480291825244E-5</v>
+        <v>-9.0289236893063883E-5</v>
       </c>
       <c r="Z20">
-        <v>-7.5921319888607553E-5</v>
+        <v>-4.2096803658873104E-5</v>
       </c>
       <c r="AA20">
-        <v>-1.9346700180987409E-4</v>
+        <v>-7.0256201479889806E-5</v>
       </c>
       <c r="AB20">
-        <v>-7.7173607768917104E-5</v>
+        <v>-1.541062606541848E-4</v>
       </c>
       <c r="AC20">
-        <v>-7.4888902913436027E-5</v>
+        <v>-5.8932991712022518E-5</v>
       </c>
       <c r="AD20">
-        <v>-4.9584817190391343E-5</v>
+        <v>-7.2764261477538159E-5</v>
       </c>
       <c r="AE20">
-        <v>-1.2705014471360454E-4</v>
+        <v>-1.6024342923861488E-5</v>
       </c>
       <c r="AF20">
-        <v>-1.0936706202805687E-4</v>
+        <v>-1.0728365483053255E-4</v>
       </c>
       <c r="AG20">
-        <v>-1.2189741840338078E-4</v>
+        <v>-7.6683138230329036E-5</v>
       </c>
       <c r="AH20">
-        <v>-7.8849646958013925E-5</v>
+        <v>-1.1188255377009998E-4</v>
       </c>
       <c r="AI20">
-        <v>-1.2514452539871249E-4</v>
+        <v>-5.9957956943448984E-5</v>
       </c>
       <c r="AJ20">
-        <v>-8.811828228040753E-5</v>
+        <v>-8.8887993567265792E-5</v>
       </c>
       <c r="AK20">
-        <v>-6.9776142869156437E-6</v>
+        <v>-6.6545579199711678E-5</v>
       </c>
       <c r="AL20">
-        <v>3.0288265024221649E-5</v>
+        <v>-2.3725656799221991E-6</v>
       </c>
       <c r="AM20">
-        <v>5.3573246627997603E-5</v>
+        <v>-9.1963602796573968E-6</v>
       </c>
       <c r="AN20">
-        <v>-2.775603322882704E-4</v>
+        <v>2.3016057492726588E-5</v>
       </c>
       <c r="AO20">
-        <v>-1.7065811430583416E-4</v>
+        <v>-2.7490848896883897E-4</v>
       </c>
       <c r="AP20">
-        <v>2.9604358400704266E-5</v>
+        <v>-8.7248140318261109E-5</v>
       </c>
       <c r="AQ20">
-        <v>-1.1878898687438565E-3</v>
+        <v>-5.8642862670350707E-6</v>
+      </c>
+      <c r="AR20">
+        <v>-1.0196715691800115E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
       <c r="B21">
-        <v>0.27581238654293538</v>
+        <v>0.18263629806519482</v>
       </c>
       <c r="C21">
-        <v>-2.0040872286459011E-5</v>
+        <v>-5.9587664478239729E-6</v>
       </c>
       <c r="D21">
-        <v>-9.2865874744480307E-6</v>
+        <v>4.0896437724174625E-8</v>
       </c>
       <c r="E21">
-        <v>1.0953159158621928E-7</v>
+        <v>3.7406145124965055E-8</v>
       </c>
       <c r="F21">
-        <v>-4.3536970090630599E-6</v>
+        <v>-1.0102292364712291E-4</v>
       </c>
       <c r="G21">
-        <v>7.4896629417317442E-5</v>
+        <v>-5.1404552429366125E-5</v>
       </c>
       <c r="H21">
-        <v>3.3439141718740973E-5</v>
+        <v>-9.2527450996528877E-6</v>
       </c>
       <c r="I21">
-        <v>2.2441782796178082E-4</v>
+        <v>-5.3750834703501337E-6</v>
       </c>
       <c r="J21">
-        <v>3.2350042465627857E-4</v>
+        <v>1.2003288923608897E-4</v>
       </c>
       <c r="K21">
-        <v>1.6462365153521245E-4</v>
+        <v>5.5374353351013666E-5</v>
       </c>
       <c r="L21">
-        <v>3.7949607995923796E-4</v>
+        <v>2.5156608373770898E-4</v>
       </c>
       <c r="M21">
-        <v>9.8266822688255844E-4</v>
+        <v>8.8075303916661035E-4</v>
       </c>
       <c r="N21">
-        <v>1.2460425326497018E-3</v>
+        <v>1.1429280249627028E-3</v>
       </c>
       <c r="O21">
-        <v>9.7195264892663551E-4</v>
+        <v>8.4692662598610585E-4</v>
       </c>
       <c r="P21">
-        <v>8.2849316112058465E-5</v>
+        <v>5.8372017021213597E-6</v>
       </c>
       <c r="Q21">
-        <v>1.6181146352520502E-4</v>
+        <v>9.8359890728288909E-5</v>
       </c>
       <c r="R21">
-        <v>-1.7722475576093131E-6</v>
+        <v>2.1754077378542989E-4</v>
       </c>
       <c r="S21">
-        <v>-3.9474375791844886E-7</v>
+        <v>-1.7221658705942185E-6</v>
       </c>
       <c r="T21">
-        <v>1.084448190829062E-3</v>
+        <v>-1.9782728430600284E-7</v>
       </c>
       <c r="U21">
-        <v>1.4656753578747973E-3</v>
+        <v>1.0512204497081954E-3</v>
       </c>
       <c r="V21">
-        <v>1.9601509316439923E-3</v>
+        <v>1.6501980482671347E-3</v>
       </c>
       <c r="W21">
-        <v>1.6562633574830963E-3</v>
+        <v>1.4701703826561765E-3</v>
       </c>
       <c r="X21">
-        <v>-1.0620582284438286E-4</v>
+        <v>1.4721584046300401E-3</v>
       </c>
       <c r="Y21">
-        <v>-4.6369807051906088E-5</v>
+        <v>-1.0792607663255875E-4</v>
       </c>
       <c r="Z21">
-        <v>-3.7213168807176676E-5</v>
+        <v>-3.8929824901778279E-5</v>
       </c>
       <c r="AA21">
-        <v>-1.2317815371916299E-4</v>
+        <v>-8.1629638956081811E-5</v>
       </c>
       <c r="AB21">
-        <v>-1.8000572629296964E-5</v>
+        <v>-2.0316292167935158E-4</v>
       </c>
       <c r="AC21">
-        <v>-6.1102469237546875E-5</v>
+        <v>-8.4515238686783364E-5</v>
       </c>
       <c r="AD21">
-        <v>-1.696237748327915E-5</v>
+        <v>-8.1535986562578807E-5</v>
       </c>
       <c r="AE21">
-        <v>-9.7436342027804089E-5</v>
+        <v>-5.2154777233526321E-5</v>
       </c>
       <c r="AF21">
-        <v>-6.0840869958251115E-5</v>
+        <v>-1.3072670098595755E-4</v>
       </c>
       <c r="AG21">
-        <v>-8.9326957455045198E-5</v>
+        <v>-1.2019289300574914E-4</v>
       </c>
       <c r="AH21">
-        <v>-3.2931007509360294E-5</v>
+        <v>-1.3094214939028613E-4</v>
       </c>
       <c r="AI21">
-        <v>-1.1961983438036667E-4</v>
+        <v>-8.0671840727107561E-5</v>
       </c>
       <c r="AJ21">
-        <v>-3.7001550324961322E-5</v>
+        <v>-1.2687223334913883E-4</v>
       </c>
       <c r="AK21">
-        <v>-3.8931243886189371E-6</v>
+        <v>-9.2428188134873487E-5</v>
       </c>
       <c r="AL21">
-        <v>9.3426894991103875E-6</v>
+        <v>-7.5960404032256732E-6</v>
       </c>
       <c r="AM21">
-        <v>4.4047385844614743E-5</v>
+        <v>4.2481684031844217E-5</v>
       </c>
       <c r="AN21">
-        <v>-2.4737388454350165E-4</v>
+        <v>5.7762560452753319E-5</v>
       </c>
       <c r="AO21">
-        <v>-2.2862497250114165E-4</v>
+        <v>-3.1403034863770884E-4</v>
       </c>
       <c r="AP21">
-        <v>1.7113101496331112E-5</v>
+        <v>-1.6312895012986591E-4</v>
       </c>
       <c r="AQ21">
-        <v>-1.3002500503034127E-3</v>
+        <v>2.5422342668913144E-5</v>
+      </c>
+      <c r="AR21">
+        <v>-1.1834741592251807E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>34</v>
       </c>
       <c r="B22">
-        <v>0.52182117001425188</v>
+        <v>0.26380870392506922</v>
       </c>
       <c r="C22">
-        <v>-3.3429963124193498E-5</v>
+        <v>-1.3316277170117171E-5</v>
       </c>
       <c r="D22">
-        <v>-1.2390114950462741E-5</v>
+        <v>-7.5672200670731695E-6</v>
       </c>
       <c r="E22">
-        <v>1.2569611486878902E-7</v>
+        <v>9.7184433493242625E-8</v>
       </c>
       <c r="F22">
-        <v>2.6211592284412511E-4</v>
+        <v>7.4958948626412445E-6</v>
       </c>
       <c r="G22">
-        <v>2.6613440371310489E-4</v>
+        <v>7.9489869601636262E-5</v>
       </c>
       <c r="H22">
-        <v>2.3690804101118675E-4</v>
+        <v>3.5791766193276912E-5</v>
       </c>
       <c r="I22">
-        <v>4.6661560267941471E-4</v>
+        <v>2.2872994690582076E-4</v>
       </c>
       <c r="J22">
-        <v>5.2318050692513418E-4</v>
+        <v>3.3061619883240241E-4</v>
       </c>
       <c r="K22">
-        <v>3.3354089345732782E-4</v>
+        <v>1.6706505435160179E-4</v>
       </c>
       <c r="L22">
-        <v>5.8351952611375793E-4</v>
+        <v>3.8896045206823337E-4</v>
       </c>
       <c r="M22">
-        <v>9.6845664510417898E-4</v>
+        <v>9.0792193412165862E-4</v>
       </c>
       <c r="N22">
-        <v>1.2473425229289343E-3</v>
+        <v>1.2236361101059514E-3</v>
       </c>
       <c r="O22">
-        <v>1.0097894482138973E-3</v>
+        <v>9.7253536384981981E-4</v>
       </c>
       <c r="P22">
-        <v>1.4894397473712279E-4</v>
+        <v>7.410608342376983E-5</v>
       </c>
       <c r="Q22">
-        <v>2.6017211800716147E-4</v>
+        <v>1.5415680960899469E-4</v>
       </c>
       <c r="R22">
-        <v>-2.2866867654685793E-6</v>
+        <v>3.0985613200675135E-4</v>
       </c>
       <c r="S22">
-        <v>-4.2656000868510233E-7</v>
+        <v>-2.1884907717636586E-6</v>
       </c>
       <c r="T22">
-        <v>1.0562671546371534E-3</v>
+        <v>-6.3665781424131857E-7</v>
       </c>
       <c r="U22">
-        <v>1.4687187730693765E-3</v>
+        <v>1.0812167587195361E-3</v>
       </c>
       <c r="V22">
-        <v>1.6562633574830963E-3</v>
+        <v>1.4701703826561765E-3</v>
       </c>
       <c r="W22">
-        <v>2.2704724877776398E-3</v>
+        <v>1.9653331791295949E-3</v>
       </c>
       <c r="X22">
-        <v>-9.9376378694009614E-5</v>
+        <v>1.65936562626303E-3</v>
       </c>
       <c r="Y22">
-        <v>-2.0141697518714008E-5</v>
+        <v>-1.0690408945349152E-4</v>
       </c>
       <c r="Z22">
-        <v>-1.1335900487810036E-5</v>
+        <v>-4.948534999014249E-5</v>
       </c>
       <c r="AA22">
-        <v>-1.3502267583929013E-4</v>
+        <v>-4.3293725108609624E-5</v>
       </c>
       <c r="AB22">
-        <v>9.6277161024561903E-6</v>
+        <v>-1.3278256412763346E-4</v>
       </c>
       <c r="AC22">
-        <v>2.6603497878507125E-6</v>
+        <v>-2.9080008337777869E-5</v>
       </c>
       <c r="AD22">
-        <v>1.3311531076107416E-5</v>
+        <v>-6.8084515909800605E-5</v>
       </c>
       <c r="AE22">
-        <v>-4.996663743223837E-5</v>
+        <v>-1.9468761298580055E-5</v>
       </c>
       <c r="AF22">
-        <v>-2.0407541310213589E-5</v>
+        <v>-1.0123446117766711E-4</v>
       </c>
       <c r="AG22">
-        <v>-2.4757502982396263E-5</v>
+        <v>-7.1663658041114364E-5</v>
       </c>
       <c r="AH22">
-        <v>5.4323512462519348E-5</v>
+        <v>-9.8449462106184066E-5</v>
       </c>
       <c r="AI22">
-        <v>-8.782909803770575E-5</v>
+        <v>-3.4966447824666812E-5</v>
       </c>
       <c r="AJ22">
-        <v>2.3376172638841456E-5</v>
+        <v>-1.2199498047994907E-4</v>
       </c>
       <c r="AK22">
-        <v>-1.9996834611985036E-6</v>
+        <v>-4.114754127933928E-5</v>
       </c>
       <c r="AL22">
-        <v>1.4045143057340732E-5</v>
+        <v>-4.4964108615656818E-6</v>
       </c>
       <c r="AM22">
-        <v>5.5298533649528712E-5</v>
+        <v>1.8654150972247834E-5</v>
       </c>
       <c r="AN22">
-        <v>-2.5659785109188166E-4</v>
+        <v>4.8755160941154545E-5</v>
       </c>
       <c r="AO22">
-        <v>7.4148520867828641E-5</v>
+        <v>-2.8142333793042306E-4</v>
       </c>
       <c r="AP22">
-        <v>-1.728434469887237E-5</v>
+        <v>-2.2054997777696728E-4</v>
       </c>
       <c r="AQ22">
-        <v>-1.5115842393550773E-3</v>
+        <v>9.6960204878589239E-6</v>
+      </c>
+      <c r="AR22">
+        <v>-1.302540809616962E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23">
-        <v>2.7611671543221375E-2</v>
+        <v>0.50697831448279884</v>
       </c>
       <c r="C23">
-        <v>-3.2380729423231209E-7</v>
+        <v>-2.721632264849499E-5</v>
       </c>
       <c r="D23">
-        <v>-5.1957233843454346E-7</v>
+        <v>-1.0675380067589863E-5</v>
       </c>
       <c r="E23">
-        <v>-7.658220614415709E-10</v>
+        <v>1.1339059128340685E-7</v>
       </c>
       <c r="F23">
-        <v>-2.7075742890616449E-7</v>
+        <v>2.7173445688109853E-4</v>
       </c>
       <c r="G23">
-        <v>-3.5266315947480727E-6</v>
+        <v>2.6970997282692809E-4</v>
       </c>
       <c r="H23">
-        <v>8.2080509184267727E-6</v>
+        <v>2.3756347917922645E-4</v>
       </c>
       <c r="I23">
-        <v>6.532419744924871E-6</v>
+        <v>4.7145896495025198E-4</v>
       </c>
       <c r="J23">
-        <v>-1.8026290309755795E-6</v>
+        <v>5.2952814935974455E-4</v>
       </c>
       <c r="K23">
-        <v>-1.7945862808884104E-6</v>
+        <v>3.3531335028708618E-4</v>
       </c>
       <c r="L23">
-        <v>-2.1965468206759297E-5</v>
+        <v>5.9134178277222855E-4</v>
       </c>
       <c r="M23">
-        <v>-6.2278906244900794E-5</v>
+        <v>9.0329353484267232E-4</v>
       </c>
       <c r="N23">
-        <v>-7.8598479677458082E-5</v>
+        <v>1.2247635022513022E-3</v>
       </c>
       <c r="O23">
-        <v>-8.6699607570421983E-5</v>
+        <v>1.0100131686617321E-3</v>
       </c>
       <c r="P23">
-        <v>1.094935515066396E-6</v>
+        <v>1.4071304877211435E-4</v>
       </c>
       <c r="Q23">
-        <v>6.2610150065105977E-6</v>
+        <v>2.5289764993684856E-4</v>
       </c>
       <c r="R23">
-        <v>8.8985406800946218E-8</v>
+        <v>3.5940480533686492E-4</v>
       </c>
       <c r="S23">
-        <v>-8.6811795515320731E-8</v>
+        <v>-2.6786213730512468E-6</v>
       </c>
       <c r="T23">
-        <v>-8.9907985798011531E-5</v>
+        <v>-6.7667992689169111E-7</v>
       </c>
       <c r="U23">
-        <v>-1.0742096630132804E-4</v>
+        <v>1.0511043088143215E-3</v>
       </c>
       <c r="V23">
-        <v>-1.0620582284438286E-4</v>
+        <v>1.4721584046300401E-3</v>
       </c>
       <c r="W23">
-        <v>-9.9376378694009614E-5</v>
+        <v>1.65936562626303E-3</v>
       </c>
       <c r="X23">
-        <v>1.8927257709107899E-5</v>
+        <v>2.2715271439952677E-3</v>
       </c>
       <c r="Y23">
-        <v>-3.2889122638969241E-6</v>
+        <v>-1.0002731001024714E-4</v>
       </c>
       <c r="Z23">
-        <v>7.513590533254828E-6</v>
+        <v>-2.3127264812960796E-5</v>
       </c>
       <c r="AA23">
-        <v>1.4778029294038274E-5</v>
+        <v>-1.8732133679106938E-5</v>
       </c>
       <c r="AB23">
-        <v>5.7787937086666802E-6</v>
+        <v>-1.4576005859972288E-4</v>
       </c>
       <c r="AC23">
-        <v>4.7093812248819204E-6</v>
+        <v>-1.4810455108628276E-6</v>
       </c>
       <c r="AD23">
-        <v>7.9506036482358744E-6</v>
+        <v>-5.1807561877762185E-6</v>
       </c>
       <c r="AE23">
-        <v>1.0765277846094515E-5</v>
+        <v>9.7448611023220498E-6</v>
       </c>
       <c r="AF23">
-        <v>6.1319733205818613E-6</v>
+        <v>-5.508174090934967E-5</v>
       </c>
       <c r="AG23">
-        <v>7.4327991648868877E-6</v>
+        <v>-3.2529031125660439E-5</v>
       </c>
       <c r="AH23">
-        <v>6.2052634033634271E-6</v>
+        <v>-3.4844837047748369E-5</v>
       </c>
       <c r="AI23">
-        <v>1.032881392161015E-5</v>
+        <v>5.1345965151524948E-5</v>
       </c>
       <c r="AJ23">
-        <v>1.1796023550697735E-5</v>
+        <v>-9.2062969685412452E-5</v>
       </c>
       <c r="AK23">
-        <v>5.2102672916746735E-7</v>
+        <v>1.8790786895364923E-5</v>
       </c>
       <c r="AL23">
-        <v>2.5066950764934386E-6</v>
+        <v>-2.6795645298892043E-6</v>
       </c>
       <c r="AM23">
-        <v>-1.811712004518766E-9</v>
+        <v>2.4052799086360171E-5</v>
       </c>
       <c r="AN23">
-        <v>2.242080471791211E-5</v>
+        <v>6.1042891178117117E-5</v>
       </c>
       <c r="AO23">
-        <v>1.1999638764810673E-5</v>
+        <v>-2.8940828298528831E-4</v>
       </c>
       <c r="AP23">
-        <v>1.8571486088071208E-5</v>
+        <v>8.07080910046832E-5</v>
       </c>
       <c r="AQ23">
-        <v>9.6714393400049241E-5</v>
+        <v>-2.836699554171915E-5</v>
+      </c>
+      <c r="AR23">
+        <v>-1.510594346293435E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24">
-        <v>3.7598541335309421</v>
+        <v>2.8574275367590649E-2</v>
       </c>
       <c r="C24">
-        <v>4.5785218710541725E-6</v>
+        <v>-8.8012917236686415E-7</v>
       </c>
       <c r="D24">
-        <v>1.496567426603846E-6</v>
+        <v>-6.6748254030559736E-7</v>
       </c>
       <c r="E24">
-        <v>-2.9644124332865602E-8</v>
+        <v>3.3265898855702914E-10</v>
       </c>
       <c r="F24">
-        <v>7.8240198564441673E-5</v>
+        <v>-1.4161054501806052E-6</v>
       </c>
       <c r="G24">
-        <v>-3.6131200329632559E-5</v>
+        <v>-3.8807858093355706E-6</v>
       </c>
       <c r="H24">
-        <v>-5.0501516284037328E-5</v>
+        <v>8.0886147054234218E-6</v>
       </c>
       <c r="I24">
-        <v>-3.3492001192811458E-5</v>
+        <v>6.3746065360249272E-6</v>
       </c>
       <c r="J24">
-        <v>-1.8136603876306413E-5</v>
+        <v>-2.488351361771574E-6</v>
       </c>
       <c r="K24">
-        <v>-3.0418846568515422E-5</v>
+        <v>-2.0023713410200389E-6</v>
       </c>
       <c r="L24">
-        <v>1.474798582614458E-5</v>
+        <v>-2.2834476254886736E-5</v>
       </c>
       <c r="M24">
-        <v>-1.0231541598829889E-4</v>
+        <v>-5.4859984940604226E-5</v>
       </c>
       <c r="N24">
-        <v>-1.5617117774557681E-5</v>
+        <v>-7.6843310552708165E-5</v>
       </c>
       <c r="O24">
-        <v>1.0600849929859226E-5</v>
+        <v>-8.6895890569275633E-5</v>
       </c>
       <c r="P24">
-        <v>-5.8245829301120894E-6</v>
+        <v>1.4576348239074019E-6</v>
       </c>
       <c r="Q24">
-        <v>1.9898933301434418E-5</v>
+        <v>6.5559361166015352E-6</v>
       </c>
       <c r="R24">
-        <v>-4.3443997023016634E-7</v>
+        <v>-2.1410202881636695E-5</v>
       </c>
       <c r="S24">
-        <v>-7.4583835058463581E-7</v>
+        <v>1.2425686991873106E-7</v>
       </c>
       <c r="T24">
-        <v>-3.9401235947596311E-5</v>
+        <v>-6.976396320248406E-8</v>
       </c>
       <c r="U24">
-        <v>-3.5724480291825244E-5</v>
+        <v>-9.0289236893063883E-5</v>
       </c>
       <c r="V24">
-        <v>-4.6369807051906088E-5</v>
+        <v>-1.0792607663255875E-4</v>
       </c>
       <c r="W24">
-        <v>-2.0141697518714008E-5</v>
+        <v>-1.0690408945349152E-4</v>
       </c>
       <c r="X24">
-        <v>-3.2889122638969241E-6</v>
+        <v>-1.0002731001024714E-4</v>
       </c>
       <c r="Y24">
-        <v>3.6255988393740297E-4</v>
+        <v>1.902669891138407E-5</v>
       </c>
       <c r="Z24">
-        <v>1.9687046795458191E-5</v>
+        <v>-3.0590391032472099E-6</v>
       </c>
       <c r="AA24">
-        <v>3.1276971046190705E-5</v>
+        <v>8.0429527969372142E-6</v>
       </c>
       <c r="AB24">
-        <v>1.2715874956722029E-5</v>
+        <v>1.5637831015458551E-5</v>
       </c>
       <c r="AC24">
-        <v>-1.7461209962554059E-6</v>
+        <v>6.9676129688907098E-6</v>
       </c>
       <c r="AD24">
-        <v>-1.5210288610090774E-5</v>
+        <v>5.3519902051381508E-6</v>
       </c>
       <c r="AE24">
-        <v>2.0607156288907795E-5</v>
+        <v>8.1573404990516532E-6</v>
       </c>
       <c r="AF24">
-        <v>9.8331796399977968E-6</v>
+        <v>1.1076702198937472E-5</v>
       </c>
       <c r="AG24">
-        <v>3.675071712936577E-5</v>
+        <v>7.0776569668694412E-6</v>
       </c>
       <c r="AH24">
-        <v>1.5277720187865425E-5</v>
+        <v>8.2536169886756742E-6</v>
       </c>
       <c r="AI24">
-        <v>2.6555133209520663E-5</v>
+        <v>6.5214175339115954E-6</v>
       </c>
       <c r="AJ24">
-        <v>3.5620091428164384E-5</v>
+        <v>1.0516298471858637E-5</v>
       </c>
       <c r="AK24">
-        <v>-2.1800818275311565E-6</v>
+        <v>1.2162309662501373E-5</v>
       </c>
       <c r="AL24">
-        <v>2.013784791728501E-5</v>
+        <v>5.6828090318701979E-7</v>
       </c>
       <c r="AM24">
-        <v>8.652743137825871E-6</v>
+        <v>1.9961295204425745E-6</v>
       </c>
       <c r="AN24">
-        <v>1.646339846512447E-5</v>
+        <v>-3.8753112466631331E-7</v>
       </c>
       <c r="AO24">
-        <v>5.5543807386748333E-5</v>
+        <v>2.5498506571355222E-5</v>
       </c>
       <c r="AP24">
-        <v>4.3445861702619309E-6</v>
+        <v>1.1452309720167354E-5</v>
       </c>
       <c r="AQ24">
-        <v>-5.6131652601602737E-5</v>
+        <v>1.8842826737681332E-5</v>
+      </c>
+      <c r="AR24">
+        <v>9.7654341984000577E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
       <c r="B25">
-        <v>0.11973795003126128</v>
+        <v>3.7594555953906572</v>
       </c>
       <c r="C25">
-        <v>1.7266423627667288E-5</v>
+        <v>4.9755911632620251E-6</v>
       </c>
       <c r="D25">
-        <v>7.1880752591607194E-7</v>
+        <v>1.54440204316277E-6</v>
       </c>
       <c r="E25">
-        <v>-9.1943244776833904E-10</v>
+        <v>-3.0133491008762956E-8</v>
       </c>
       <c r="F25">
-        <v>-3.5656270265161988E-5</v>
+        <v>7.8507686799529804E-5</v>
       </c>
       <c r="G25">
-        <v>1.4100748858153267E-5</v>
+        <v>-3.6037797824131786E-5</v>
       </c>
       <c r="H25">
-        <v>-2.0956617604760865E-5</v>
+        <v>-5.0672069799272514E-5</v>
       </c>
       <c r="I25">
-        <v>-3.1424693107274458E-5</v>
+        <v>-3.3270208919033886E-5</v>
       </c>
       <c r="J25">
-        <v>4.7306697845017365E-6</v>
+        <v>-1.8566270140317476E-5</v>
       </c>
       <c r="K25">
-        <v>4.7370994212764107E-5</v>
+        <v>-3.0756508480692883E-5</v>
       </c>
       <c r="L25">
-        <v>2.0324370487782276E-5</v>
+        <v>1.4200954736614277E-5</v>
       </c>
       <c r="M25">
-        <v>-4.8978046632240364E-5</v>
+        <v>-1.0375770842447805E-4</v>
       </c>
       <c r="N25">
-        <v>-3.2564882355588044E-5</v>
+        <v>-1.8514906931706133E-5</v>
       </c>
       <c r="O25">
-        <v>-7.9314437795451807E-5</v>
+        <v>8.907195302550392E-6</v>
       </c>
       <c r="P25">
-        <v>-3.1175427167073177E-5</v>
+        <v>-3.8848887147029901E-6</v>
       </c>
       <c r="Q25">
-        <v>-7.5816050341258079E-6</v>
+        <v>2.0796883493094963E-5</v>
       </c>
       <c r="R25">
-        <v>1.6770348741398243E-6</v>
+        <v>-2.1043541846403353E-7</v>
       </c>
       <c r="S25">
-        <v>2.2026411488703709E-6</v>
+        <v>-4.3427141609273728E-7</v>
       </c>
       <c r="T25">
-        <v>-6.3204131786215797E-5</v>
+        <v>-7.5305136532698109E-7</v>
       </c>
       <c r="U25">
-        <v>-7.5921319888607553E-5</v>
+        <v>-4.2096803658873104E-5</v>
       </c>
       <c r="V25">
-        <v>-3.7213168807176676E-5</v>
+        <v>-3.8929824901778279E-5</v>
       </c>
       <c r="W25">
-        <v>-1.1335900487810036E-5</v>
+        <v>-4.948534999014249E-5</v>
       </c>
       <c r="X25">
-        <v>7.513590533254828E-6</v>
+        <v>-2.3127264812960796E-5</v>
       </c>
       <c r="Y25">
-        <v>1.9687046795458191E-5</v>
+        <v>-3.0590391032472099E-6</v>
       </c>
       <c r="Z25">
-        <v>1.7829102112164779E-3</v>
+        <v>3.6259774928762466E-4</v>
       </c>
       <c r="AA25">
-        <v>7.7344479256869804E-4</v>
+        <v>1.9210161674392008E-5</v>
       </c>
       <c r="AB25">
-        <v>7.4569366744624288E-4</v>
+        <v>3.1241255753313175E-5</v>
       </c>
       <c r="AC25">
-        <v>7.4787480026574358E-4</v>
+        <v>1.220510284907855E-5</v>
       </c>
       <c r="AD25">
-        <v>7.1632360716470734E-4</v>
+        <v>-2.2814398702927095E-6</v>
       </c>
       <c r="AE25">
-        <v>7.5501455231091101E-4</v>
+        <v>-1.5598803925787793E-5</v>
       </c>
       <c r="AF25">
-        <v>7.7699909288054018E-4</v>
+        <v>2.0449755266785209E-5</v>
       </c>
       <c r="AG25">
-        <v>7.693773324055469E-4</v>
+        <v>8.9336730557552018E-6</v>
       </c>
       <c r="AH25">
-        <v>7.6273160318997399E-4</v>
+        <v>3.6462585512417594E-5</v>
       </c>
       <c r="AI25">
-        <v>7.5720573404033475E-4</v>
+        <v>1.4141173772527925E-5</v>
       </c>
       <c r="AJ25">
-        <v>7.6416647815987719E-4</v>
+        <v>2.6462067046737145E-5</v>
       </c>
       <c r="AK25">
-        <v>-5.3300982779029104E-7</v>
+        <v>3.5530668842277339E-5</v>
       </c>
       <c r="AL25">
-        <v>1.3613920744783036E-5</v>
+        <v>-2.1875341033890164E-6</v>
       </c>
       <c r="AM25">
-        <v>-2.9360481021125929E-5</v>
+        <v>2.06451788935454E-5</v>
       </c>
       <c r="AN25">
-        <v>4.0365629356841823E-4</v>
+        <v>9.1523291371155621E-6</v>
       </c>
       <c r="AO25">
-        <v>4.3801699276803418E-4</v>
+        <v>1.7944867047482212E-5</v>
       </c>
       <c r="AP25">
-        <v>1.8372719529889965E-4</v>
+        <v>5.5692077909504099E-5</v>
       </c>
       <c r="AQ25">
-        <v>-9.4485755885233996E-4</v>
+        <v>3.2697424771510218E-6</v>
+      </c>
+      <c r="AR25">
+        <v>-5.4703025463282485E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
       <c r="B26">
-        <v>0.20776134759559226</v>
+        <v>0.12017344241232808</v>
       </c>
       <c r="C26">
-        <v>4.8888985168169479E-5</v>
+        <v>1.7287330830570322E-5</v>
       </c>
       <c r="D26">
-        <v>1.0385655473419618E-6</v>
+        <v>8.0337811264282518E-7</v>
       </c>
       <c r="E26">
-        <v>-1.3761691063372072E-8</v>
+        <v>-1.4981685368495665E-9</v>
       </c>
       <c r="F26">
-        <v>4.1009830256702581E-5</v>
+        <v>-3.8431760991383771E-5</v>
       </c>
       <c r="G26">
-        <v>6.7390985459217826E-5</v>
+        <v>1.3037144040851909E-5</v>
       </c>
       <c r="H26">
-        <v>3.4266425747613623E-8</v>
+        <v>-2.0841472353823047E-5</v>
       </c>
       <c r="I26">
-        <v>-2.872554343938432E-5</v>
+        <v>-3.2437771826810446E-5</v>
       </c>
       <c r="J26">
-        <v>-3.700707647646918E-5</v>
+        <v>5.0633885885188409E-6</v>
       </c>
       <c r="K26">
-        <v>7.3491147857296629E-5</v>
+        <v>4.707152879763579E-5</v>
       </c>
       <c r="L26">
-        <v>2.4743376151656728E-5</v>
+        <v>1.9352416302367633E-5</v>
       </c>
       <c r="M26">
-        <v>-1.1098295168371038E-4</v>
+        <v>-6.0943647984895087E-5</v>
       </c>
       <c r="N26">
-        <v>-1.4876958711766323E-4</v>
+        <v>-3.5983829455096307E-5</v>
       </c>
       <c r="O26">
-        <v>-1.4020124075363698E-4</v>
+        <v>-8.1956330862310368E-5</v>
       </c>
       <c r="P26">
-        <v>-3.7262553226173067E-5</v>
+        <v>-3.3265732602447057E-5</v>
       </c>
       <c r="Q26">
-        <v>-3.6685283273134189E-5</v>
+        <v>-1.0496459159796341E-5</v>
       </c>
       <c r="R26">
-        <v>1.8694535527796605E-6</v>
+        <v>4.2380774740375976E-7</v>
       </c>
       <c r="S26">
-        <v>5.7403183156519701E-7</v>
+        <v>1.6927981267511762E-6</v>
       </c>
       <c r="T26">
-        <v>-1.4131031433913004E-4</v>
+        <v>2.2165723038159063E-6</v>
       </c>
       <c r="U26">
-        <v>-1.9346700180987409E-4</v>
+        <v>-7.0256201479889806E-5</v>
       </c>
       <c r="V26">
-        <v>-1.2317815371916299E-4</v>
+        <v>-8.1629638956081811E-5</v>
       </c>
       <c r="W26">
-        <v>-1.3502267583929013E-4</v>
+        <v>-4.3293725108609624E-5</v>
       </c>
       <c r="X26">
-        <v>1.4778029294038274E-5</v>
+        <v>-1.8732133679106938E-5</v>
       </c>
       <c r="Y26">
-        <v>3.1276971046190705E-5</v>
+        <v>8.0429527969372142E-6</v>
       </c>
       <c r="Z26">
-        <v>7.7344479256869804E-4</v>
+        <v>1.9210161674392008E-5</v>
       </c>
       <c r="AA26">
-        <v>1.4978939884172161E-3</v>
+        <v>1.7839711579511468E-3</v>
       </c>
       <c r="AB26">
-        <v>7.5119563680619509E-4</v>
+        <v>7.7367586286283905E-4</v>
       </c>
       <c r="AC26">
-        <v>7.6110629188786989E-4</v>
+        <v>7.4648316463439546E-4</v>
       </c>
       <c r="AD26">
-        <v>7.1582806530391934E-4</v>
+        <v>7.4841854986365292E-4</v>
       </c>
       <c r="AE26">
-        <v>7.6784052700741849E-4</v>
+        <v>7.1739108919206839E-4</v>
       </c>
       <c r="AF26">
-        <v>7.7867231578512895E-4</v>
+        <v>7.5530378085450272E-4</v>
       </c>
       <c r="AG26">
-        <v>7.8430937845117173E-4</v>
+        <v>7.7723657791180679E-4</v>
       </c>
       <c r="AH26">
-        <v>7.7433551300843187E-4</v>
+        <v>7.6954634368792737E-4</v>
       </c>
       <c r="AI26">
-        <v>7.6157320364625739E-4</v>
+        <v>7.6184093132913096E-4</v>
       </c>
       <c r="AJ26">
-        <v>7.7308254998453385E-4</v>
+        <v>7.5740690747393266E-4</v>
       </c>
       <c r="AK26">
-        <v>8.5266355710639512E-6</v>
+        <v>7.6458640464500418E-4</v>
       </c>
       <c r="AL26">
-        <v>3.8832066032320166E-7</v>
+        <v>-5.4463936303678453E-7</v>
       </c>
       <c r="AM26">
-        <v>-3.8022033849529431E-5</v>
+        <v>1.4242220002960487E-5</v>
       </c>
       <c r="AN26">
-        <v>5.8979347552161137E-4</v>
+        <v>-2.8908515499029112E-5</v>
       </c>
       <c r="AO26">
-        <v>3.592765088063606E-4</v>
+        <v>4.026188614934633E-4</v>
       </c>
       <c r="AP26">
-        <v>1.9307276699712285E-4</v>
+        <v>4.3615326146382346E-4</v>
       </c>
       <c r="AQ26">
-        <v>-9.6631756788387508E-4</v>
+        <v>1.8289591655266461E-4</v>
+      </c>
+      <c r="AR26">
+        <v>-9.4117145899835124E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>39</v>
       </c>
       <c r="B27">
-        <v>0.18252792719255037</v>
+        <v>0.20887386151189496</v>
       </c>
       <c r="C27">
-        <v>7.8037873559625391E-6</v>
+        <v>4.8948865204144819E-5</v>
       </c>
       <c r="D27">
-        <v>-1.5581584983845231E-6</v>
+        <v>1.0530364558413889E-6</v>
       </c>
       <c r="E27">
-        <v>1.9331386674730246E-8</v>
+        <v>-1.394582194611735E-8</v>
       </c>
       <c r="F27">
-        <v>4.6647438236291347E-5</v>
+        <v>4.0390838116251054E-5</v>
       </c>
       <c r="G27">
-        <v>5.7688548343415854E-5</v>
+        <v>6.6020458688432636E-5</v>
       </c>
       <c r="H27">
-        <v>1.1145157449789937E-5</v>
+        <v>7.9453655340772154E-7</v>
       </c>
       <c r="I27">
-        <v>1.0317200800238744E-4</v>
+        <v>-2.9229802679619197E-5</v>
       </c>
       <c r="J27">
-        <v>6.8738675636800432E-5</v>
+        <v>-3.596298080626992E-5</v>
       </c>
       <c r="K27">
-        <v>1.0310700463884772E-4</v>
+        <v>7.3234509212636613E-5</v>
       </c>
       <c r="L27">
-        <v>4.1177353497016356E-5</v>
+        <v>2.4725760862196182E-5</v>
       </c>
       <c r="M27">
-        <v>-6.9205814836940461E-5</v>
+        <v>-1.3932787522174736E-4</v>
       </c>
       <c r="N27">
-        <v>-2.805243251267219E-5</v>
+        <v>-1.5510901670881549E-4</v>
       </c>
       <c r="O27">
-        <v>-6.3122869523631005E-5</v>
+        <v>-1.4349713365319574E-4</v>
       </c>
       <c r="P27">
-        <v>-2.2876754188527154E-5</v>
+        <v>-3.925575468109598E-5</v>
       </c>
       <c r="Q27">
-        <v>-3.8715299044301133E-5</v>
+        <v>-3.9485387687332194E-5</v>
       </c>
       <c r="R27">
-        <v>1.8537091297097828E-6</v>
+        <v>1.8610082646741542E-5</v>
       </c>
       <c r="S27">
-        <v>1.4876646129928866E-6</v>
+        <v>1.8758643822322131E-6</v>
       </c>
       <c r="T27">
-        <v>-3.6422773862495831E-5</v>
+        <v>5.7337131840473079E-7</v>
       </c>
       <c r="U27">
-        <v>-7.7173607768917104E-5</v>
+        <v>-1.541062606541848E-4</v>
       </c>
       <c r="V27">
-        <v>-1.8000572629296964E-5</v>
+        <v>-2.0316292167935158E-4</v>
       </c>
       <c r="W27">
-        <v>9.6277161024561903E-6</v>
+        <v>-1.3278256412763346E-4</v>
       </c>
       <c r="X27">
-        <v>5.7787937086666802E-6</v>
+        <v>-1.4576005859972288E-4</v>
       </c>
       <c r="Y27">
-        <v>1.2715874956722029E-5</v>
+        <v>1.5637831015458551E-5</v>
       </c>
       <c r="Z27">
-        <v>7.4569366744624288E-4</v>
+        <v>3.1241255753313175E-5</v>
       </c>
       <c r="AA27">
-        <v>7.5119563680619509E-4</v>
+        <v>7.7367586286283905E-4</v>
       </c>
       <c r="AB27">
-        <v>1.4344447698320492E-3</v>
+        <v>1.4981757436834066E-3</v>
       </c>
       <c r="AC27">
-        <v>7.3991240095867968E-4</v>
+        <v>7.5185604201974485E-4</v>
       </c>
       <c r="AD27">
-        <v>7.0372975942405223E-4</v>
+        <v>7.6177371932316048E-4</v>
       </c>
       <c r="AE27">
-        <v>7.4286054183321504E-4</v>
+        <v>7.1687459535563561E-4</v>
       </c>
       <c r="AF27">
-        <v>7.600634906554007E-4</v>
+        <v>7.6831157341145583E-4</v>
       </c>
       <c r="AG27">
-        <v>7.5936487329163638E-4</v>
+        <v>7.791782483080042E-4</v>
       </c>
       <c r="AH27">
-        <v>7.6107937173620953E-4</v>
+        <v>7.8484292423596966E-4</v>
       </c>
       <c r="AI27">
-        <v>7.3781523166903038E-4</v>
+        <v>7.7402815776810724E-4</v>
       </c>
       <c r="AJ27">
-        <v>7.5115809429039909E-4</v>
+        <v>7.6199865744506655E-4</v>
       </c>
       <c r="AK27">
-        <v>-1.234021170565662E-6</v>
+        <v>7.7307685019900618E-4</v>
       </c>
       <c r="AL27">
-        <v>6.41000841063366E-5</v>
+        <v>8.5446233084074294E-6</v>
       </c>
       <c r="AM27">
-        <v>3.8413146181993756E-5</v>
+        <v>9.3419940192719544E-7</v>
       </c>
       <c r="AN27">
-        <v>3.7078127527999437E-4</v>
+        <v>-3.8704430041460722E-5</v>
       </c>
       <c r="AO27">
-        <v>3.5922475752295929E-4</v>
+        <v>5.87445689839858E-4</v>
       </c>
       <c r="AP27">
-        <v>1.5082046462053201E-4</v>
+        <v>3.5801505068160425E-4</v>
       </c>
       <c r="AQ27">
-        <v>-8.9756896550730958E-4</v>
+        <v>1.9368630981975431E-4</v>
+      </c>
+      <c r="AR27">
+        <v>-9.5639080503178689E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28">
-        <v>0.23195318704118995</v>
+        <v>0.1835845304419145</v>
       </c>
       <c r="C28">
-        <v>1.7425948428694091E-5</v>
+        <v>6.8915729934002374E-6</v>
       </c>
       <c r="D28">
-        <v>1.5415407692324897E-6</v>
+        <v>-1.8382999182388732E-6</v>
       </c>
       <c r="E28">
-        <v>-1.1343051444589269E-8</v>
+        <v>2.2078457435882491E-8</v>
       </c>
       <c r="F28">
-        <v>9.4048309793546967E-5</v>
+        <v>4.4771017040781664E-5</v>
       </c>
       <c r="G28">
-        <v>6.3869003200144828E-5</v>
+        <v>5.6715143533783832E-5</v>
       </c>
       <c r="H28">
-        <v>2.1486487525607779E-5</v>
+        <v>1.2034189424276463E-5</v>
       </c>
       <c r="I28">
-        <v>1.7860382209606356E-4</v>
+        <v>1.031122696550558E-4</v>
       </c>
       <c r="J28">
-        <v>5.8409954117463553E-5</v>
+        <v>7.0132150518283749E-5</v>
       </c>
       <c r="K28">
-        <v>9.0925851162755296E-5</v>
+        <v>1.0273754131728892E-4</v>
       </c>
       <c r="L28">
-        <v>1.0117371643853889E-4</v>
+        <v>4.0605089598333495E-5</v>
       </c>
       <c r="M28">
-        <v>-4.8256077991980374E-5</v>
+        <v>-7.2199292666469555E-5</v>
       </c>
       <c r="N28">
-        <v>-5.0129465975949593E-5</v>
+        <v>-3.2165990775245349E-5</v>
       </c>
       <c r="O28">
-        <v>-3.6227492135020497E-5</v>
+        <v>-6.5628037563820899E-5</v>
       </c>
       <c r="P28">
-        <v>-5.0072296371223039E-5</v>
+        <v>-2.2859691779367987E-5</v>
       </c>
       <c r="Q28">
-        <v>-6.5091509979180756E-5</v>
+        <v>-3.9501476374592625E-5</v>
       </c>
       <c r="R28">
-        <v>9.5667861141266355E-7</v>
+        <v>-2.2288464713802491E-5</v>
       </c>
       <c r="S28">
-        <v>1.444191738043176E-6</v>
+        <v>1.874872039419083E-6</v>
       </c>
       <c r="T28">
-        <v>-6.421836147296262E-5</v>
+        <v>1.4914308783271138E-6</v>
       </c>
       <c r="U28">
-        <v>-7.4888902913436027E-5</v>
+        <v>-5.8932991712022518E-5</v>
       </c>
       <c r="V28">
-        <v>-6.1102469237546875E-5</v>
+        <v>-8.4515238686783364E-5</v>
       </c>
       <c r="W28">
-        <v>2.6603497878507125E-6</v>
+        <v>-2.9080008337777869E-5</v>
       </c>
       <c r="X28">
-        <v>4.7093812248819204E-6</v>
+        <v>-1.4810455108628276E-6</v>
       </c>
       <c r="Y28">
-        <v>-1.7461209962554059E-6</v>
+        <v>6.9676129688907098E-6</v>
       </c>
       <c r="Z28">
-        <v>7.4787480026574358E-4</v>
+        <v>1.220510284907855E-5</v>
       </c>
       <c r="AA28">
-        <v>7.6110629188786989E-4</v>
+        <v>7.4648316463439546E-4</v>
       </c>
       <c r="AB28">
-        <v>7.3991240095867968E-4</v>
+        <v>7.5185604201974485E-4</v>
       </c>
       <c r="AC28">
-        <v>1.5011445640914101E-3</v>
+        <v>1.4380291868138207E-3</v>
       </c>
       <c r="AD28">
-        <v>7.0810320904198562E-4</v>
+        <v>7.410318399598113E-4</v>
       </c>
       <c r="AE28">
-        <v>7.3610682164579279E-4</v>
+        <v>7.0524228611394115E-4</v>
       </c>
       <c r="AF28">
-        <v>7.6094771021342029E-4</v>
+        <v>7.4355214598202668E-4</v>
       </c>
       <c r="AG28">
-        <v>7.5572350659418601E-4</v>
+        <v>7.6093834629015504E-4</v>
       </c>
       <c r="AH28">
-        <v>7.6356677636898584E-4</v>
+        <v>7.602805057354017E-4</v>
       </c>
       <c r="AI28">
-        <v>7.312449925254037E-4</v>
+        <v>7.6121668735966419E-4</v>
       </c>
       <c r="AJ28">
-        <v>7.5125005116909291E-4</v>
+        <v>7.3862701731531439E-4</v>
       </c>
       <c r="AK28">
-        <v>-1.6351559695964983E-7</v>
+        <v>7.5124531691971551E-4</v>
       </c>
       <c r="AL28">
-        <v>3.9399127541021222E-5</v>
+        <v>-1.1778761042855737E-6</v>
       </c>
       <c r="AM28">
-        <v>-6.6095193044184543E-7</v>
+        <v>6.493873216813399E-5</v>
       </c>
       <c r="AN28">
-        <v>3.5577701878915496E-4</v>
+        <v>3.82326969437198E-5</v>
       </c>
       <c r="AO28">
-        <v>3.623765894293155E-4</v>
+        <v>3.7035832290054516E-4</v>
       </c>
       <c r="AP28">
-        <v>1.5633072236814256E-4</v>
+        <v>3.5860028366845032E-4</v>
       </c>
       <c r="AQ28">
-        <v>-8.9412996349832042E-4</v>
+        <v>1.5240502166054474E-4</v>
+      </c>
+      <c r="AR28">
+        <v>-8.8318060932463644E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>41</v>
       </c>
       <c r="B29">
-        <v>0.24119524108849472</v>
+        <v>0.23332530062435264</v>
       </c>
       <c r="C29">
-        <v>9.8638238250881853E-6</v>
+        <v>1.7277102604806705E-5</v>
       </c>
       <c r="D29">
-        <v>-1.755009706060648E-6</v>
+        <v>1.5383183500143276E-6</v>
       </c>
       <c r="E29">
-        <v>3.1891023417150023E-8</v>
+        <v>-1.1194550169759669E-8</v>
       </c>
       <c r="F29">
-        <v>1.7463949362533454E-4</v>
+        <v>9.3477649221147816E-5</v>
       </c>
       <c r="G29">
-        <v>-2.7076336599811374E-5</v>
+        <v>6.3064642699161744E-5</v>
       </c>
       <c r="H29">
-        <v>3.5309338747718268E-6</v>
+        <v>2.2053049757190105E-5</v>
       </c>
       <c r="I29">
-        <v>-5.6695689615589065E-5</v>
+        <v>1.7855613269220609E-4</v>
       </c>
       <c r="J29">
-        <v>2.8703307502329087E-5</v>
+        <v>5.882684501621814E-5</v>
       </c>
       <c r="K29">
-        <v>6.1089026213289688E-5</v>
+        <v>9.0519312338268454E-5</v>
       </c>
       <c r="L29">
-        <v>-2.0070685526090337E-6</v>
+        <v>1.0069247328556263E-4</v>
       </c>
       <c r="M29">
-        <v>-5.2392372042239473E-5</v>
+        <v>-6.3965420224032805E-5</v>
       </c>
       <c r="N29">
-        <v>1.6659774968606788E-5</v>
+        <v>-5.4345393378910537E-5</v>
       </c>
       <c r="O29">
-        <v>-3.9881871100631914E-5</v>
+        <v>-3.8989306731457524E-5</v>
       </c>
       <c r="P29">
-        <v>-3.4080668034028701E-5</v>
+        <v>-5.2559127628541995E-5</v>
       </c>
       <c r="Q29">
-        <v>-6.8681662036768412E-6</v>
+        <v>-6.862772778935388E-5</v>
       </c>
       <c r="R29">
-        <v>2.3295339590021383E-6</v>
+        <v>-1.7727784211023727E-5</v>
       </c>
       <c r="S29">
-        <v>3.0555373342077703E-6</v>
+        <v>9.6666673244492122E-7</v>
       </c>
       <c r="T29">
-        <v>-1.3074955380069887E-5</v>
+        <v>1.4496723034041265E-6</v>
       </c>
       <c r="U29">
-        <v>-4.9584817190391343E-5</v>
+        <v>-7.2764261477538159E-5</v>
       </c>
       <c r="V29">
-        <v>-1.696237748327915E-5</v>
+        <v>-8.1535986562578807E-5</v>
       </c>
       <c r="W29">
-        <v>1.3311531076107416E-5</v>
+        <v>-6.8084515909800605E-5</v>
       </c>
       <c r="X29">
-        <v>7.9506036482358744E-6</v>
+        <v>-5.1807561877762185E-6</v>
       </c>
       <c r="Y29">
-        <v>-1.5210288610090774E-5</v>
+        <v>5.3519902051381508E-6</v>
       </c>
       <c r="Z29">
-        <v>7.1632360716470734E-4</v>
+        <v>-2.2814398702927095E-6</v>
       </c>
       <c r="AA29">
-        <v>7.1582806530391934E-4</v>
+        <v>7.4841854986365292E-4</v>
       </c>
       <c r="AB29">
-        <v>7.0372975942405223E-4</v>
+        <v>7.6177371932316048E-4</v>
       </c>
       <c r="AC29">
-        <v>7.0810320904198562E-4</v>
+        <v>7.410318399598113E-4</v>
       </c>
       <c r="AD29">
-        <v>1.5775495779269629E-3</v>
+        <v>1.502886286720758E-3</v>
       </c>
       <c r="AE29">
-        <v>7.1170950198479264E-4</v>
+        <v>7.0922942862589738E-4</v>
       </c>
       <c r="AF29">
-        <v>7.2540991627650703E-4</v>
+        <v>7.3682799835802354E-4</v>
       </c>
       <c r="AG29">
-        <v>7.2014888669303485E-4</v>
+        <v>7.615944306781329E-4</v>
       </c>
       <c r="AH29">
-        <v>7.2996092153206809E-4</v>
+        <v>7.5636666939110815E-4</v>
       </c>
       <c r="AI29">
-        <v>7.0524345154143958E-4</v>
+        <v>7.6334350349218847E-4</v>
       </c>
       <c r="AJ29">
-        <v>7.1722419945449212E-4</v>
+        <v>7.3200164795952634E-4</v>
       </c>
       <c r="AK29">
-        <v>5.0225066063042909E-6</v>
+        <v>7.5174049771818707E-4</v>
       </c>
       <c r="AL29">
-        <v>2.4534194654435819E-5</v>
+        <v>-1.6518436540385309E-7</v>
       </c>
       <c r="AM29">
-        <v>-1.6385837844701929E-5</v>
+        <v>3.9951759158020936E-5</v>
       </c>
       <c r="AN29">
-        <v>2.5194516600622716E-4</v>
+        <v>-5.2588613544814027E-7</v>
       </c>
       <c r="AO29">
-        <v>2.5536412099808742E-4</v>
+        <v>3.5411842352448485E-4</v>
       </c>
       <c r="AP29">
-        <v>1.0386015992686073E-4</v>
+        <v>3.6104985962135577E-4</v>
       </c>
       <c r="AQ29">
-        <v>-1.0671680372189051E-3</v>
+        <v>1.5708521729649401E-4</v>
+      </c>
+      <c r="AR29">
+        <v>-8.8661189454627997E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
       <c r="B30">
-        <v>0.17254371301921609</v>
+        <v>0.24254280838046996</v>
       </c>
       <c r="C30">
-        <v>1.1707726106089339E-6</v>
+        <v>9.7020337901788286E-6</v>
       </c>
       <c r="D30">
-        <v>-5.3800863234197319E-7</v>
+        <v>-1.8308010113871236E-6</v>
       </c>
       <c r="E30">
-        <v>5.7308876487989684E-9</v>
+        <v>3.2723610468812312E-8</v>
       </c>
       <c r="F30">
-        <v>1.353740128189228E-5</v>
+        <v>1.7575059429689936E-4</v>
       </c>
       <c r="G30">
-        <v>3.4179407812607407E-5</v>
+        <v>-2.7232023735876125E-5</v>
       </c>
       <c r="H30">
-        <v>-2.4259919458952063E-6</v>
+        <v>3.7862723068680612E-6</v>
       </c>
       <c r="I30">
-        <v>1.2634464412902599E-5</v>
+        <v>-5.8949311858412691E-5</v>
       </c>
       <c r="J30">
-        <v>2.4856407070120417E-5</v>
+        <v>2.8730926641592781E-5</v>
       </c>
       <c r="K30">
-        <v>6.6286521729028803E-5</v>
+        <v>6.0986854978757973E-5</v>
       </c>
       <c r="L30">
-        <v>8.1815627285204007E-5</v>
+        <v>-2.6191783581515273E-6</v>
       </c>
       <c r="M30">
-        <v>-7.5121324619836506E-5</v>
+        <v>-4.7135871440098483E-5</v>
       </c>
       <c r="N30">
-        <v>-6.4531435307836756E-5</v>
+        <v>1.5549704539968531E-5</v>
       </c>
       <c r="O30">
-        <v>-7.5098127813273615E-5</v>
+        <v>-4.0861793304796962E-5</v>
       </c>
       <c r="P30">
-        <v>-4.6758089173920278E-5</v>
+        <v>-3.5423501372070247E-5</v>
       </c>
       <c r="Q30">
-        <v>-3.7631187956115223E-5</v>
+        <v>-9.7347595746020131E-6</v>
       </c>
       <c r="R30">
-        <v>1.8611602471083274E-6</v>
+        <v>-4.8783790680020389E-5</v>
       </c>
       <c r="S30">
-        <v>1.2878337366922777E-6</v>
+        <v>2.3630718049775176E-6</v>
       </c>
       <c r="T30">
-        <v>-1.0236663306032121E-4</v>
+        <v>3.0738925342622801E-6</v>
       </c>
       <c r="U30">
-        <v>-1.2705014471360454E-4</v>
+        <v>-1.6024342923861488E-5</v>
       </c>
       <c r="V30">
-        <v>-9.7436342027804089E-5</v>
+        <v>-5.2154777233526321E-5</v>
       </c>
       <c r="W30">
-        <v>-4.996663743223837E-5</v>
+        <v>-1.9468761298580055E-5</v>
       </c>
       <c r="X30">
-        <v>1.0765277846094515E-5</v>
+        <v>9.7448611023220498E-6</v>
       </c>
       <c r="Y30">
-        <v>2.0607156288907795E-5</v>
+        <v>8.1573404990516532E-6</v>
       </c>
       <c r="Z30">
-        <v>7.5501455231091101E-4</v>
+        <v>-1.5598803925787793E-5</v>
       </c>
       <c r="AA30">
-        <v>7.6784052700741849E-4</v>
+        <v>7.1739108919206839E-4</v>
       </c>
       <c r="AB30">
-        <v>7.4286054183321504E-4</v>
+        <v>7.1687459535563561E-4</v>
       </c>
       <c r="AC30">
-        <v>7.3610682164579279E-4</v>
+        <v>7.0524228611394115E-4</v>
       </c>
       <c r="AD30">
-        <v>7.1170950198479264E-4</v>
+        <v>7.0922942862589738E-4</v>
       </c>
       <c r="AE30">
-        <v>1.3293294989884844E-3</v>
+        <v>1.5795412096758126E-3</v>
       </c>
       <c r="AF30">
-        <v>7.6697621586470702E-4</v>
+        <v>7.1253374390743414E-4</v>
       </c>
       <c r="AG30">
-        <v>7.6544278559138E-4</v>
+        <v>7.2640625396238744E-4</v>
       </c>
       <c r="AH30">
-        <v>7.6283076917153846E-4</v>
+        <v>7.2105908662325417E-4</v>
       </c>
       <c r="AI30">
-        <v>7.4789339007903138E-4</v>
+        <v>7.304977004381235E-4</v>
       </c>
       <c r="AJ30">
-        <v>7.5594023651026263E-4</v>
+        <v>7.0628929833827284E-4</v>
       </c>
       <c r="AK30">
-        <v>-1.8291446418301961E-6</v>
+        <v>7.1805345060567773E-4</v>
       </c>
       <c r="AL30">
-        <v>3.8910220723055493E-5</v>
+        <v>5.031296807530376E-6</v>
       </c>
       <c r="AM30">
-        <v>7.7361081896950722E-6</v>
+        <v>2.4448304518809874E-5</v>
       </c>
       <c r="AN30">
-        <v>3.6283458477464394E-4</v>
+        <v>-1.6846050946496311E-5</v>
       </c>
       <c r="AO30">
-        <v>3.7037320868375741E-4</v>
+        <v>2.5177474873515359E-4</v>
       </c>
       <c r="AP30">
-        <v>8.1505091668721536E-5</v>
+        <v>2.5489463888757097E-4</v>
       </c>
       <c r="AQ30">
-        <v>-8.0569875164455593E-4</v>
+        <v>1.0507448715445149E-4</v>
+      </c>
+      <c r="AR30">
+        <v>-1.0650679633729598E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>43</v>
       </c>
       <c r="B31">
-        <v>0.1723510910659582</v>
+        <v>0.17364401602813226</v>
       </c>
       <c r="C31">
-        <v>1.3265544569140191E-5</v>
+        <v>1.0342575481194911E-6</v>
       </c>
       <c r="D31">
-        <v>-1.1732734063388366E-6</v>
+        <v>-5.2526180591917402E-7</v>
       </c>
       <c r="E31">
-        <v>6.8595281824057973E-9</v>
+        <v>5.7938431956644173E-9</v>
       </c>
       <c r="F31">
-        <v>5.6339334809153557E-5</v>
+        <v>1.1928274997384481E-5</v>
       </c>
       <c r="G31">
-        <v>6.0167040611791797E-5</v>
+        <v>3.3310808397440674E-5</v>
       </c>
       <c r="H31">
-        <v>1.2135610741112153E-5</v>
+        <v>-2.4642478965994428E-6</v>
       </c>
       <c r="I31">
-        <v>1.8205980953952517E-5</v>
+        <v>1.0881485996786603E-5</v>
       </c>
       <c r="J31">
-        <v>3.9582490462197916E-5</v>
+        <v>2.5489001720621651E-5</v>
       </c>
       <c r="K31">
-        <v>7.1528282831584281E-5</v>
+        <v>6.5741174949061334E-5</v>
       </c>
       <c r="L31">
-        <v>3.9811978649015683E-5</v>
+        <v>8.09291225211429E-5</v>
       </c>
       <c r="M31">
-        <v>-9.3145208914088926E-5</v>
+        <v>-8.3986161123077315E-5</v>
       </c>
       <c r="N31">
-        <v>-4.799231711958478E-5</v>
+        <v>-6.6743008312570109E-5</v>
       </c>
       <c r="O31">
-        <v>-4.5983987193006388E-5</v>
+        <v>-7.6460541431988094E-5</v>
       </c>
       <c r="P31">
-        <v>-2.8765651174544523E-5</v>
+        <v>-4.8448032625530947E-5</v>
       </c>
       <c r="Q31">
-        <v>-2.2762734449607295E-5</v>
+        <v>-4.0634291395630137E-5</v>
       </c>
       <c r="R31">
-        <v>1.6305010205535036E-6</v>
+        <v>-2.5065042625230715E-5</v>
       </c>
       <c r="S31">
-        <v>1.1058903538892659E-6</v>
+        <v>1.8759605362559923E-6</v>
       </c>
       <c r="T31">
-        <v>-6.3710385903014417E-5</v>
+        <v>1.2951561038672122E-6</v>
       </c>
       <c r="U31">
-        <v>-1.0936706202805687E-4</v>
+        <v>-1.0728365483053255E-4</v>
       </c>
       <c r="V31">
-        <v>-6.0840869958251115E-5</v>
+        <v>-1.3072670098595755E-4</v>
       </c>
       <c r="W31">
-        <v>-2.0407541310213589E-5</v>
+        <v>-1.0123446117766711E-4</v>
       </c>
       <c r="X31">
-        <v>6.1319733205818613E-6</v>
+        <v>-5.508174090934967E-5</v>
       </c>
       <c r="Y31">
-        <v>9.8331796399977968E-6</v>
+        <v>1.1076702198937472E-5</v>
       </c>
       <c r="Z31">
-        <v>7.7699909288054018E-4</v>
+        <v>2.0449755266785209E-5</v>
       </c>
       <c r="AA31">
-        <v>7.7867231578512895E-4</v>
+        <v>7.5530378085450272E-4</v>
       </c>
       <c r="AB31">
-        <v>7.600634906554007E-4</v>
+        <v>7.6831157341145583E-4</v>
       </c>
       <c r="AC31">
-        <v>7.6094771021342029E-4</v>
+        <v>7.4355214598202668E-4</v>
       </c>
       <c r="AD31">
-        <v>7.2540991627650703E-4</v>
+        <v>7.3682799835802354E-4</v>
       </c>
       <c r="AE31">
-        <v>7.6697621586470702E-4</v>
+        <v>7.1253374390743414E-4</v>
       </c>
       <c r="AF31">
-        <v>1.2539018697873318E-3</v>
+        <v>1.3290651235567123E-3</v>
       </c>
       <c r="AG31">
-        <v>7.8266815795799535E-4</v>
+        <v>7.6746642534817667E-4</v>
       </c>
       <c r="AH31">
-        <v>7.8052871448417436E-4</v>
+        <v>7.6583152107439069E-4</v>
       </c>
       <c r="AI31">
-        <v>7.6371479598301136E-4</v>
+        <v>7.6258973444780112E-4</v>
       </c>
       <c r="AJ31">
-        <v>7.7476239923825099E-4</v>
+        <v>7.4835602265390787E-4</v>
       </c>
       <c r="AK31">
-        <v>-3.0148453066589748E-7</v>
+        <v>7.5627131387999663E-4</v>
       </c>
       <c r="AL31">
-        <v>1.4159230250619946E-5</v>
+        <v>-1.8529476941658E-6</v>
       </c>
       <c r="AM31">
-        <v>-3.9086952848735432E-6</v>
+        <v>3.9382698627287582E-5</v>
       </c>
       <c r="AN31">
-        <v>4.031385264726472E-4</v>
+        <v>7.805007192486377E-6</v>
       </c>
       <c r="AO31">
-        <v>4.5382363650147382E-4</v>
+        <v>3.6214029100957267E-4</v>
       </c>
       <c r="AP31">
-        <v>1.3906624210919763E-4</v>
+        <v>3.6865975118195818E-4</v>
       </c>
       <c r="AQ31">
-        <v>-8.4645066631174439E-4</v>
+        <v>8.2628750884698016E-5</v>
+      </c>
+      <c r="AR31">
+        <v>-8.0170506302705124E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>44</v>
       </c>
       <c r="B32">
-        <v>0.17189564764273826</v>
+        <v>0.17344451232850441</v>
       </c>
       <c r="C32">
-        <v>1.6010176626664653E-5</v>
+        <v>1.3082509943611559E-5</v>
       </c>
       <c r="D32">
-        <v>2.238644075594053E-6</v>
+        <v>-1.1730599063885798E-6</v>
       </c>
       <c r="E32">
-        <v>-2.7341669616018331E-8</v>
+        <v>6.8814316970050909E-9</v>
       </c>
       <c r="F32">
-        <v>7.2549263802661776E-5</v>
+        <v>5.4599933350207035E-5</v>
       </c>
       <c r="G32">
-        <v>4.5790779789223523E-5</v>
+        <v>5.9318219588254349E-5</v>
       </c>
       <c r="H32">
-        <v>1.0646501247682945E-5</v>
+        <v>1.2648055640997823E-5</v>
       </c>
       <c r="I32">
-        <v>4.2619576812613034E-5</v>
+        <v>1.7315350382810361E-5</v>
       </c>
       <c r="J32">
-        <v>6.4084318226285836E-5</v>
+        <v>4.0771703577004566E-5</v>
       </c>
       <c r="K32">
-        <v>7.8113270531386859E-5</v>
+        <v>7.0983982934595975E-5</v>
       </c>
       <c r="L32">
-        <v>3.3611327592700268E-5</v>
+        <v>3.8859201443677496E-5</v>
       </c>
       <c r="M32">
-        <v>-7.7223843157837673E-5</v>
+        <v>-1.1020423382030851E-4</v>
       </c>
       <c r="N32">
-        <v>-4.655986367580893E-5</v>
+        <v>-5.4469038562333377E-5</v>
       </c>
       <c r="O32">
-        <v>-3.1009572311476883E-5</v>
+        <v>-5.0418850249967062E-5</v>
       </c>
       <c r="P32">
-        <v>-3.315460138490455E-5</v>
+        <v>-3.204011785812453E-5</v>
       </c>
       <c r="Q32">
-        <v>-1.4122926656044249E-5</v>
+        <v>-2.6836233821094467E-5</v>
       </c>
       <c r="R32">
-        <v>4.5757298848173339E-7</v>
+        <v>1.8090633652816132E-6</v>
       </c>
       <c r="S32">
-        <v>2.1224009477937668E-6</v>
+        <v>1.650979196924224E-6</v>
       </c>
       <c r="T32">
-        <v>-1.007054982115433E-4</v>
+        <v>1.106825105242448E-6</v>
       </c>
       <c r="U32">
-        <v>-1.2189741840338078E-4</v>
+        <v>-7.6683138230329036E-5</v>
       </c>
       <c r="V32">
-        <v>-8.9326957455045198E-5</v>
+        <v>-1.2019289300574914E-4</v>
       </c>
       <c r="W32">
-        <v>-2.4757502982396263E-5</v>
+        <v>-7.1663658041114364E-5</v>
       </c>
       <c r="X32">
-        <v>7.4327991648868877E-6</v>
+        <v>-3.2529031125660439E-5</v>
       </c>
       <c r="Y32">
-        <v>3.675071712936577E-5</v>
+        <v>7.0776569668694412E-6</v>
       </c>
       <c r="Z32">
-        <v>7.693773324055469E-4</v>
+        <v>8.9336730557552018E-6</v>
       </c>
       <c r="AA32">
-        <v>7.8430937845117173E-4</v>
+        <v>7.7723657791180679E-4</v>
       </c>
       <c r="AB32">
-        <v>7.5936487329163638E-4</v>
+        <v>7.791782483080042E-4</v>
       </c>
       <c r="AC32">
-        <v>7.5572350659418601E-4</v>
+        <v>7.6093834629015504E-4</v>
       </c>
       <c r="AD32">
-        <v>7.2014888669303485E-4</v>
+        <v>7.615944306781329E-4</v>
       </c>
       <c r="AE32">
-        <v>7.6544278559138E-4</v>
+        <v>7.2640625396238744E-4</v>
       </c>
       <c r="AF32">
-        <v>7.8266815795799535E-4</v>
+        <v>7.6746642534817667E-4</v>
       </c>
       <c r="AG32">
-        <v>1.4677620688006189E-3</v>
+        <v>1.2540553332792035E-3</v>
       </c>
       <c r="AH32">
-        <v>7.7505934458626624E-4</v>
+        <v>7.830959259011841E-4</v>
       </c>
       <c r="AI32">
-        <v>7.6198779319029762E-4</v>
+        <v>7.8032607517260688E-4</v>
       </c>
       <c r="AJ32">
-        <v>7.7450408603590157E-4</v>
+        <v>7.640153842604989E-4</v>
       </c>
       <c r="AK32">
-        <v>1.5609863016138864E-6</v>
+        <v>7.7484058353982708E-4</v>
       </c>
       <c r="AL32">
-        <v>3.5655774030681425E-5</v>
+        <v>-3.281817522999517E-7</v>
       </c>
       <c r="AM32">
-        <v>4.8440844445902598E-6</v>
+        <v>1.5480316663018216E-5</v>
       </c>
       <c r="AN32">
-        <v>4.1317050690739792E-4</v>
+        <v>-3.1962760641954713E-6</v>
       </c>
       <c r="AO32">
-        <v>4.2125340029787792E-4</v>
+        <v>4.0044559858913467E-4</v>
       </c>
       <c r="AP32">
-        <v>1.679526220000058E-4</v>
+        <v>4.5247991152615218E-4</v>
       </c>
       <c r="AQ32">
-        <v>-9.4795639767388602E-4</v>
+        <v>1.3885927297822763E-4</v>
+      </c>
+      <c r="AR32">
+        <v>-8.3386719969538216E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>45</v>
       </c>
       <c r="B33">
-        <v>0.23367794163863631</v>
+        <v>0.17265840927102863</v>
       </c>
       <c r="C33">
-        <v>5.8296923045337124E-5</v>
+        <v>1.5665031090431597E-5</v>
       </c>
       <c r="D33">
-        <v>-6.032653341916476E-7</v>
+        <v>2.2506246174812692E-6</v>
       </c>
       <c r="E33">
-        <v>6.4140930217235499E-9</v>
+        <v>-2.7434163249738048E-8</v>
       </c>
       <c r="F33">
-        <v>8.129417460936295E-5</v>
+        <v>7.2043061656770335E-5</v>
       </c>
       <c r="G33">
-        <v>8.24172096800779E-5</v>
+        <v>4.4602307736509063E-5</v>
       </c>
       <c r="H33">
-        <v>7.9261892200311338E-5</v>
+        <v>1.0768090976808656E-5</v>
       </c>
       <c r="I33">
-        <v>2.0120935756152914E-5</v>
+        <v>4.1981192211854523E-5</v>
       </c>
       <c r="J33">
-        <v>6.567305471954776E-5</v>
+        <v>6.4558461819304181E-5</v>
       </c>
       <c r="K33">
-        <v>1.257587501209579E-4</v>
+        <v>7.7428785497347604E-5</v>
       </c>
       <c r="L33">
-        <v>8.1296279798947428E-5</v>
+        <v>3.2527472860314783E-5</v>
       </c>
       <c r="M33">
-        <v>-3.2386624152369137E-5</v>
+        <v>-9.984613231822355E-5</v>
       </c>
       <c r="N33">
-        <v>-5.0729066942761998E-5</v>
+        <v>-5.2169654490839788E-5</v>
       </c>
       <c r="O33">
-        <v>-4.7042669894429304E-5</v>
+        <v>-3.4635262816992341E-5</v>
       </c>
       <c r="P33">
-        <v>-7.2744924350735704E-5</v>
+        <v>-3.4690317962329692E-5</v>
       </c>
       <c r="Q33">
-        <v>-5.8817254954287726E-5</v>
+        <v>-1.672743705330049E-5</v>
       </c>
       <c r="R33">
-        <v>-4.6269263056471134E-8</v>
+        <v>1.2618829344055396E-5</v>
       </c>
       <c r="S33">
-        <v>1.7949373561312164E-6</v>
+        <v>4.6490583965244025E-7</v>
       </c>
       <c r="T33">
-        <v>-5.6119967496869711E-5</v>
+        <v>2.1319103233906534E-6</v>
       </c>
       <c r="U33">
-        <v>-7.8849646958013925E-5</v>
+        <v>-1.1188255377009998E-4</v>
       </c>
       <c r="V33">
-        <v>-3.2931007509360294E-5</v>
+        <v>-1.3094214939028613E-4</v>
       </c>
       <c r="W33">
-        <v>5.4323512462519348E-5</v>
+        <v>-9.8449462106184066E-5</v>
       </c>
       <c r="X33">
-        <v>6.2052634033634271E-6</v>
+        <v>-3.4844837047748369E-5</v>
       </c>
       <c r="Y33">
-        <v>1.5277720187865425E-5</v>
+        <v>8.2536169886756742E-6</v>
       </c>
       <c r="Z33">
-        <v>7.6273160318997399E-4</v>
+        <v>3.6462585512417594E-5</v>
       </c>
       <c r="AA33">
-        <v>7.7433551300843187E-4</v>
+        <v>7.6954634368792737E-4</v>
       </c>
       <c r="AB33">
-        <v>7.6107937173620953E-4</v>
+        <v>7.8484292423596966E-4</v>
       </c>
       <c r="AC33">
-        <v>7.6356677636898584E-4</v>
+        <v>7.602805057354017E-4</v>
       </c>
       <c r="AD33">
-        <v>7.2996092153206809E-4</v>
+        <v>7.5636666939110815E-4</v>
       </c>
       <c r="AE33">
-        <v>7.6283076917153846E-4</v>
+        <v>7.2105908662325417E-4</v>
       </c>
       <c r="AF33">
-        <v>7.8052871448417436E-4</v>
+        <v>7.6583152107439069E-4</v>
       </c>
       <c r="AG33">
-        <v>7.7505934458626624E-4</v>
+        <v>7.830959259011841E-4</v>
       </c>
       <c r="AH33">
-        <v>1.8063757651037827E-3</v>
+        <v>1.4677061694923913E-3</v>
       </c>
       <c r="AI33">
-        <v>7.6229310677184976E-4</v>
+        <v>7.7468465870992036E-4</v>
       </c>
       <c r="AJ33">
-        <v>7.8562042983484795E-4</v>
+        <v>7.623418688766033E-4</v>
       </c>
       <c r="AK33">
-        <v>3.4652889032663628E-6</v>
+        <v>7.747081412409389E-4</v>
       </c>
       <c r="AL33">
-        <v>4.9996074257602956E-6</v>
+        <v>1.5603041923077144E-6</v>
       </c>
       <c r="AM33">
-        <v>-3.9090438102937561E-5</v>
+        <v>3.6112915972027104E-5</v>
       </c>
       <c r="AN33">
-        <v>3.7974521770316828E-4</v>
+        <v>4.8611499695481932E-6</v>
       </c>
       <c r="AO33">
-        <v>4.1354276603727661E-4</v>
+        <v>4.1191065967629377E-4</v>
       </c>
       <c r="AP33">
-        <v>1.3766436870969522E-4</v>
+        <v>4.1968965801691103E-4</v>
       </c>
       <c r="AQ33">
-        <v>-9.5311335697663034E-4</v>
+        <v>1.6842463336235261E-4</v>
+      </c>
+      <c r="AR33">
+        <v>-9.3874486166108844E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
       <c r="B34">
-        <v>0.14091350168386374</v>
+        <v>0.23499779729838441</v>
       </c>
       <c r="C34">
-        <v>5.3311968753028356E-5</v>
+        <v>5.8200929759627217E-5</v>
       </c>
       <c r="D34">
-        <v>-2.5941061600832292E-6</v>
+        <v>-3.8795646039082308E-7</v>
       </c>
       <c r="E34">
-        <v>2.1617943775581397E-8</v>
+        <v>4.5365599978252974E-9</v>
       </c>
       <c r="F34">
-        <v>-1.193545154633079E-7</v>
+        <v>8.2957739914124584E-5</v>
       </c>
       <c r="G34">
-        <v>-1.0263090904517292E-5</v>
+        <v>8.1415614475761363E-5</v>
       </c>
       <c r="H34">
-        <v>-5.0683902400713835E-5</v>
+        <v>7.9511109446624823E-5</v>
       </c>
       <c r="I34">
-        <v>-7.13537441959796E-5</v>
+        <v>2.0619688018626948E-5</v>
       </c>
       <c r="J34">
-        <v>-1.3120477274821305E-5</v>
+        <v>6.6263594359214229E-5</v>
       </c>
       <c r="K34">
-        <v>2.2262887098274163E-5</v>
+        <v>1.2519499794140315E-4</v>
       </c>
       <c r="L34">
-        <v>-2.4066676115796985E-5</v>
+        <v>8.1530340148463717E-5</v>
       </c>
       <c r="M34">
-        <v>-1.1727002339032006E-4</v>
+        <v>-7.3308183296849958E-5</v>
       </c>
       <c r="N34">
-        <v>-7.1832354904920827E-5</v>
+        <v>-5.146457097473053E-5</v>
       </c>
       <c r="O34">
-        <v>-1.0074407885215577E-4</v>
+        <v>-4.7503911382340387E-5</v>
       </c>
       <c r="P34">
-        <v>-5.1069377647701991E-5</v>
+        <v>-7.2580954092408892E-5</v>
       </c>
       <c r="Q34">
-        <v>-3.838290624400074E-5</v>
+        <v>-5.9407795257567903E-5</v>
       </c>
       <c r="R34">
-        <v>6.5241491009719912E-7</v>
+        <v>3.5922120109516746E-5</v>
       </c>
       <c r="S34">
-        <v>1.255205398558928E-6</v>
+        <v>-1.8151045883140975E-8</v>
       </c>
       <c r="T34">
-        <v>-8.6680454820802877E-5</v>
+        <v>1.8017606455416307E-6</v>
       </c>
       <c r="U34">
-        <v>-1.2514452539871249E-4</v>
+        <v>-5.9957956943448984E-5</v>
       </c>
       <c r="V34">
-        <v>-1.1961983438036667E-4</v>
+        <v>-8.0671840727107561E-5</v>
       </c>
       <c r="W34">
-        <v>-8.782909803770575E-5</v>
+        <v>-3.4966447824666812E-5</v>
       </c>
       <c r="X34">
-        <v>1.032881392161015E-5</v>
+        <v>5.1345965151524948E-5</v>
       </c>
       <c r="Y34">
-        <v>2.6555133209520663E-5</v>
+        <v>6.5214175339115954E-6</v>
       </c>
       <c r="Z34">
-        <v>7.5720573404033475E-4</v>
+        <v>1.4141173772527925E-5</v>
       </c>
       <c r="AA34">
-        <v>7.6157320364625739E-4</v>
+        <v>7.6184093132913096E-4</v>
       </c>
       <c r="AB34">
-        <v>7.3781523166903038E-4</v>
+        <v>7.7402815776810724E-4</v>
       </c>
       <c r="AC34">
-        <v>7.312449925254037E-4</v>
+        <v>7.6121668735966419E-4</v>
       </c>
       <c r="AD34">
-        <v>7.0524345154143958E-4</v>
+        <v>7.6334350349218847E-4</v>
       </c>
       <c r="AE34">
-        <v>7.4789339007903138E-4</v>
+        <v>7.304977004381235E-4</v>
       </c>
       <c r="AF34">
-        <v>7.6371479598301136E-4</v>
+        <v>7.6258973444780112E-4</v>
       </c>
       <c r="AG34">
-        <v>7.6198779319029762E-4</v>
+        <v>7.8032607517260688E-4</v>
       </c>
       <c r="AH34">
-        <v>7.6229310677184976E-4</v>
+        <v>7.7468465870992036E-4</v>
       </c>
       <c r="AI34">
-        <v>1.3621672254674972E-3</v>
+        <v>1.8016296230278061E-3</v>
       </c>
       <c r="AJ34">
-        <v>7.5635114519675853E-4</v>
+        <v>7.619871359811725E-4</v>
       </c>
       <c r="AK34">
-        <v>2.4859443049538802E-7</v>
+        <v>7.8507669918597756E-4</v>
       </c>
       <c r="AL34">
-        <v>2.5396689358757237E-5</v>
+        <v>3.427871302715449E-6</v>
       </c>
       <c r="AM34">
-        <v>-2.4094375958102191E-5</v>
+        <v>6.5494605512361531E-6</v>
       </c>
       <c r="AN34">
-        <v>3.786919055577545E-4</v>
+        <v>-3.7869437306830287E-5</v>
       </c>
       <c r="AO34">
-        <v>3.8213493631656992E-4</v>
+        <v>3.7735991052106324E-4</v>
       </c>
       <c r="AP34">
-        <v>1.5770781126099766E-4</v>
+        <v>4.1175410787381217E-4</v>
       </c>
       <c r="AQ34">
-        <v>-6.8489990643277507E-4</v>
+        <v>1.3726861762914934E-4</v>
+      </c>
+      <c r="AR34">
+        <v>-9.562720982900653E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35">
-        <v>0.30290679674202742</v>
+        <v>0.14214172942042017</v>
       </c>
       <c r="C35">
-        <v>1.8319910200220579E-5</v>
+        <v>5.3312940069351668E-5</v>
       </c>
       <c r="D35">
-        <v>1.039171354219037E-6</v>
+        <v>-2.5299981379242695E-6</v>
       </c>
       <c r="E35">
-        <v>-8.3040855574029317E-9</v>
+        <v>2.1232591831367259E-8</v>
       </c>
       <c r="F35">
-        <v>1.0343462939673212E-4</v>
+        <v>-7.77058651276689E-7</v>
       </c>
       <c r="G35">
-        <v>3.8272565510348187E-5</v>
+        <v>-1.1683834204389244E-5</v>
       </c>
       <c r="H35">
-        <v>6.730191365895337E-6</v>
+        <v>-5.1010582005930416E-5</v>
       </c>
       <c r="I35">
-        <v>4.3285807418830908E-5</v>
+        <v>-7.3542239003363062E-5</v>
       </c>
       <c r="J35">
-        <v>3.034005545389626E-5</v>
+        <v>-1.3041040500511906E-5</v>
       </c>
       <c r="K35">
-        <v>4.9603539928876354E-5</v>
+        <v>2.1697662720368714E-5</v>
       </c>
       <c r="L35">
-        <v>1.191605207341665E-5</v>
+        <v>-2.4792242733467145E-5</v>
       </c>
       <c r="M35">
-        <v>-4.4754407273300953E-5</v>
+        <v>-1.4333964618953388E-4</v>
       </c>
       <c r="N35">
-        <v>-6.8183650654414442E-5</v>
+        <v>-7.2163491999272628E-5</v>
       </c>
       <c r="O35">
-        <v>-4.9305930858366547E-5</v>
+        <v>-1.0169657660128924E-4</v>
       </c>
       <c r="P35">
-        <v>-1.0949375670773792E-5</v>
+        <v>-5.5562749301627453E-5</v>
       </c>
       <c r="Q35">
-        <v>-3.0873430161111322E-5</v>
+        <v>-4.3466662405800127E-5</v>
       </c>
       <c r="R35">
-        <v>9.827218876176016E-7</v>
+        <v>1.1023125334045581E-5</v>
       </c>
       <c r="S35">
-        <v>1.7837850240597375E-6</v>
+        <v>6.8205612843783312E-7</v>
       </c>
       <c r="T35">
-        <v>-6.1006798192369193E-5</v>
+        <v>1.2605742181323541E-6</v>
       </c>
       <c r="U35">
-        <v>-8.811828228040753E-5</v>
+        <v>-8.8887993567265792E-5</v>
       </c>
       <c r="V35">
-        <v>-3.7001550324961322E-5</v>
+        <v>-1.2687223334913883E-4</v>
       </c>
       <c r="W35">
-        <v>2.3376172638841456E-5</v>
+        <v>-1.2199498047994907E-4</v>
       </c>
       <c r="X35">
-        <v>1.1796023550697735E-5</v>
+        <v>-9.2062969685412452E-5</v>
       </c>
       <c r="Y35">
-        <v>3.5620091428164384E-5</v>
+        <v>1.0516298471858637E-5</v>
       </c>
       <c r="Z35">
-        <v>7.6416647815987719E-4</v>
+        <v>2.6462067046737145E-5</v>
       </c>
       <c r="AA35">
-        <v>7.7308254998453385E-4</v>
+        <v>7.5740690747393266E-4</v>
       </c>
       <c r="AB35">
-        <v>7.5115809429039909E-4</v>
+        <v>7.6199865744506655E-4</v>
       </c>
       <c r="AC35">
-        <v>7.5125005116909291E-4</v>
+        <v>7.3862701731531439E-4</v>
       </c>
       <c r="AD35">
-        <v>7.1722419945449212E-4</v>
+        <v>7.3200164795952634E-4</v>
       </c>
       <c r="AE35">
-        <v>7.5594023651026263E-4</v>
+        <v>7.0628929833827284E-4</v>
       </c>
       <c r="AF35">
-        <v>7.7476239923825099E-4</v>
+        <v>7.4835602265390787E-4</v>
       </c>
       <c r="AG35">
-        <v>7.7450408603590157E-4</v>
+        <v>7.640153842604989E-4</v>
       </c>
       <c r="AH35">
-        <v>7.8562042983484795E-4</v>
+        <v>7.623418688766033E-4</v>
       </c>
       <c r="AI35">
-        <v>7.5635114519675853E-4</v>
+        <v>7.619871359811725E-4</v>
       </c>
       <c r="AJ35">
-        <v>1.6537907546181033E-3</v>
+        <v>1.3639460348988091E-3</v>
       </c>
       <c r="AK35">
-        <v>-7.2282610919724162E-7</v>
+        <v>7.5670051519095578E-4</v>
       </c>
       <c r="AL35">
-        <v>2.6564275031928328E-5</v>
+        <v>2.2616295170416688E-7</v>
       </c>
       <c r="AM35">
-        <v>-3.1611184333235463E-5</v>
+        <v>2.5779376703687149E-5</v>
       </c>
       <c r="AN35">
-        <v>4.8275100182641046E-4</v>
+        <v>-2.3229238199700243E-5</v>
       </c>
       <c r="AO35">
-        <v>4.3972520854778573E-4</v>
+        <v>3.7615854293985635E-4</v>
       </c>
       <c r="AP35">
-        <v>1.8591249768122543E-4</v>
+        <v>3.8035158429987966E-4</v>
       </c>
       <c r="AQ35">
-        <v>-9.2595328166993453E-4</v>
+        <v>1.5798649814856403E-4</v>
+      </c>
+      <c r="AR35">
+        <v>-6.8254675729478528E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36">
-        <v>1.0357699272879675E-2</v>
+        <v>0.30323061554847663</v>
       </c>
       <c r="C36">
-        <v>7.8527576009741988E-7</v>
+        <v>1.8427642154406498E-5</v>
       </c>
       <c r="D36">
-        <v>-1.9472051545090359E-7</v>
+        <v>1.0314506632024591E-6</v>
       </c>
       <c r="E36">
-        <v>5.088119364487337E-10</v>
+        <v>-8.1013346839824349E-9</v>
       </c>
       <c r="F36">
-        <v>2.8372371979952678E-6</v>
+        <v>1.0245960372130385E-4</v>
       </c>
       <c r="G36">
-        <v>-2.6064669447825855E-6</v>
+        <v>3.7773138243759274E-5</v>
       </c>
       <c r="H36">
-        <v>5.3621916214791488E-6</v>
+        <v>6.5978064815258261E-6</v>
       </c>
       <c r="I36">
-        <v>-6.2117200108545933E-8</v>
+        <v>4.0725605605695177E-5</v>
       </c>
       <c r="J36">
-        <v>-3.2908818420419655E-6</v>
+        <v>3.0555407066694786E-5</v>
       </c>
       <c r="K36">
-        <v>9.6575497509544957E-7</v>
+        <v>4.9178265466384534E-5</v>
       </c>
       <c r="L36">
-        <v>2.4160640522381349E-6</v>
+        <v>1.0968483219124091E-5</v>
       </c>
       <c r="M36">
-        <v>-4.9393925643324691E-6</v>
+        <v>-3.0951248728201971E-5</v>
       </c>
       <c r="N36">
-        <v>-6.6941176230890715E-6</v>
+        <v>-7.1856500653891633E-5</v>
       </c>
       <c r="O36">
-        <v>-6.730334598509908E-7</v>
+        <v>-5.0857917144412029E-5</v>
       </c>
       <c r="P36">
-        <v>-3.3912605620616139E-7</v>
+        <v>-1.0432928073413338E-5</v>
       </c>
       <c r="Q36">
-        <v>3.7534158956152518E-6</v>
+        <v>-3.2141218011267882E-5</v>
       </c>
       <c r="R36">
-        <v>1.8334387705335062E-7</v>
+        <v>-4.254930286671401E-5</v>
       </c>
       <c r="S36">
-        <v>1.0507136979886374E-7</v>
+        <v>1.0021656004577799E-6</v>
       </c>
       <c r="T36">
-        <v>-1.5362920924603469E-6</v>
+        <v>1.7906963979163347E-6</v>
       </c>
       <c r="U36">
-        <v>-6.9776142869156437E-6</v>
+        <v>-6.6545579199711678E-5</v>
       </c>
       <c r="V36">
-        <v>-3.8931243886189371E-6</v>
+        <v>-9.2428188134873487E-5</v>
       </c>
       <c r="W36">
-        <v>-1.9996834611985036E-6</v>
+        <v>-4.114754127933928E-5</v>
       </c>
       <c r="X36">
-        <v>5.2102672916746735E-7</v>
+        <v>1.8790786895364923E-5</v>
       </c>
       <c r="Y36">
-        <v>-2.1800818275311565E-6</v>
+        <v>1.2162309662501373E-5</v>
       </c>
       <c r="Z36">
-        <v>-5.3300982779029104E-7</v>
+        <v>3.5530668842277339E-5</v>
       </c>
       <c r="AA36">
-        <v>8.5266355710639512E-6</v>
+        <v>7.6458640464500418E-4</v>
       </c>
       <c r="AB36">
-        <v>-1.234021170565662E-6</v>
+        <v>7.7307685019900618E-4</v>
       </c>
       <c r="AC36">
-        <v>-1.6351559695964983E-7</v>
+        <v>7.5124531691971551E-4</v>
       </c>
       <c r="AD36">
-        <v>5.0225066063042909E-6</v>
+        <v>7.5174049771818707E-4</v>
       </c>
       <c r="AE36">
-        <v>-1.8291446418301961E-6</v>
+        <v>7.1805345060567773E-4</v>
       </c>
       <c r="AF36">
-        <v>-3.0148453066589748E-7</v>
+        <v>7.5627131387999663E-4</v>
       </c>
       <c r="AG36">
-        <v>1.5609863016138864E-6</v>
+        <v>7.7484058353982708E-4</v>
       </c>
       <c r="AH36">
-        <v>3.4652889032663628E-6</v>
+        <v>7.747081412409389E-4</v>
       </c>
       <c r="AI36">
-        <v>2.4859443049538802E-7</v>
+        <v>7.8507669918597756E-4</v>
       </c>
       <c r="AJ36">
-        <v>-7.2282610919724162E-7</v>
+        <v>7.5670051519095578E-4</v>
       </c>
       <c r="AK36">
-        <v>5.3361304336867779E-6</v>
+        <v>1.6560383648621293E-3</v>
       </c>
       <c r="AL36">
-        <v>-2.6043434160854371E-5</v>
+        <v>-7.5976539995043478E-7</v>
       </c>
       <c r="AM36">
-        <v>-2.7909292836626391E-5</v>
+        <v>2.7164993129766073E-5</v>
       </c>
       <c r="AN36">
-        <v>1.0790087923448649E-5</v>
+        <v>-3.1215913866744152E-5</v>
       </c>
       <c r="AO36">
-        <v>1.2783271833306101E-5</v>
+        <v>4.8259748818672572E-4</v>
       </c>
       <c r="AP36">
-        <v>-4.6529424496661348E-6</v>
+        <v>4.3933374554840749E-4</v>
       </c>
       <c r="AQ36">
-        <v>-8.8602220955340196E-5</v>
+        <v>1.8553949492073132E-4</v>
+      </c>
+      <c r="AR36">
+        <v>-9.2277991864022539E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>49</v>
       </c>
       <c r="B37">
-        <v>1.8176840109713221E-2</v>
+        <v>1.0350338854848462E-2</v>
       </c>
       <c r="C37">
-        <v>2.9722505776107422E-6</v>
+        <v>7.5362715777955239E-7</v>
       </c>
       <c r="D37">
-        <v>-8.829787915970715E-7</v>
+        <v>-1.9882876856226541E-7</v>
       </c>
       <c r="E37">
-        <v>9.0022978437305863E-9</v>
+        <v>5.3733541348344549E-10</v>
       </c>
       <c r="F37">
-        <v>3.253522632420795E-5</v>
+        <v>2.8400966665832598E-6</v>
       </c>
       <c r="G37">
-        <v>1.4713503793644707E-5</v>
+        <v>-2.6637215720125339E-6</v>
       </c>
       <c r="H37">
-        <v>4.5088265248917055E-6</v>
+        <v>5.3837581896933056E-6</v>
       </c>
       <c r="I37">
-        <v>-8.3063578496506531E-6</v>
+        <v>8.9778289742622466E-8</v>
       </c>
       <c r="J37">
-        <v>5.595137262796995E-5</v>
+        <v>-3.250440209772427E-6</v>
       </c>
       <c r="K37">
-        <v>-2.297644490165617E-6</v>
+        <v>9.3443817916476104E-7</v>
       </c>
       <c r="L37">
-        <v>3.5064601021060789E-5</v>
+        <v>2.397146460787926E-6</v>
       </c>
       <c r="M37">
-        <v>4.5142387333377363E-6</v>
+        <v>-6.7743743791598887E-6</v>
       </c>
       <c r="N37">
-        <v>3.9497308044424595E-5</v>
+        <v>-7.027197181490915E-6</v>
       </c>
       <c r="O37">
-        <v>-4.5536945392413001E-6</v>
+        <v>-8.9471612672911954E-7</v>
       </c>
       <c r="P37">
-        <v>-2.2546113393746064E-5</v>
+        <v>-4.9773575722059652E-7</v>
       </c>
       <c r="Q37">
-        <v>-2.822320103721917E-5</v>
+        <v>3.6578289833164902E-6</v>
       </c>
       <c r="R37">
-        <v>4.3052011607947887E-7</v>
+        <v>2.802164331873797E-6</v>
       </c>
       <c r="S37">
-        <v>-2.7538131528380519E-7</v>
+        <v>1.8400954347317023E-7</v>
       </c>
       <c r="T37">
-        <v>-1.3783158448757709E-5</v>
+        <v>1.0436730982603765E-7</v>
       </c>
       <c r="U37">
-        <v>3.0288265024221649E-5</v>
+        <v>-2.3725656799221991E-6</v>
       </c>
       <c r="V37">
-        <v>9.3426894991103875E-6</v>
+        <v>-7.5960404032256732E-6</v>
       </c>
       <c r="W37">
-        <v>1.4045143057340732E-5</v>
+        <v>-4.4964108615656818E-6</v>
       </c>
       <c r="X37">
-        <v>2.5066950764934386E-6</v>
+        <v>-2.6795645298892043E-6</v>
       </c>
       <c r="Y37">
-        <v>2.013784791728501E-5</v>
+        <v>5.6828090318701979E-7</v>
       </c>
       <c r="Z37">
-        <v>1.3613920744783036E-5</v>
+        <v>-2.1875341033890164E-6</v>
       </c>
       <c r="AA37">
-        <v>3.8832066032320166E-7</v>
+        <v>-5.4463936303678453E-7</v>
       </c>
       <c r="AB37">
-        <v>6.41000841063366E-5</v>
+        <v>8.5446233084074294E-6</v>
       </c>
       <c r="AC37">
-        <v>3.9399127541021222E-5</v>
+        <v>-1.1778761042855737E-6</v>
       </c>
       <c r="AD37">
-        <v>2.4534194654435819E-5</v>
+        <v>-1.6518436540385309E-7</v>
       </c>
       <c r="AE37">
-        <v>3.8910220723055493E-5</v>
+        <v>5.031296807530376E-6</v>
       </c>
       <c r="AF37">
-        <v>1.4159230250619946E-5</v>
+        <v>-1.8529476941658E-6</v>
       </c>
       <c r="AG37">
-        <v>3.5655774030681425E-5</v>
+        <v>-3.281817522999517E-7</v>
       </c>
       <c r="AH37">
-        <v>4.9996074257602956E-6</v>
+        <v>1.5603041923077144E-6</v>
       </c>
       <c r="AI37">
-        <v>2.5396689358757237E-5</v>
+        <v>3.427871302715449E-6</v>
       </c>
       <c r="AJ37">
-        <v>2.6564275031928328E-5</v>
+        <v>2.2616295170416688E-7</v>
       </c>
       <c r="AK37">
-        <v>-2.6043434160854371E-5</v>
+        <v>-7.5976539995043478E-7</v>
       </c>
       <c r="AL37">
-        <v>1.030090913431336E-3</v>
+        <v>5.3376658944439942E-6</v>
       </c>
       <c r="AM37">
-        <v>1.3125959820653454E-4</v>
+        <v>-2.5995379457159424E-5</v>
       </c>
       <c r="AN37">
-        <v>-6.9239381469480047E-5</v>
+        <v>-2.7882556433901697E-5</v>
       </c>
       <c r="AO37">
-        <v>-4.4285602571714924E-5</v>
+        <v>1.0787249896904632E-5</v>
       </c>
       <c r="AP37">
-        <v>3.3859687520102402E-6</v>
+        <v>1.2684983280085367E-5</v>
       </c>
       <c r="AQ37">
-        <v>3.2797219291621349E-4</v>
+        <v>-4.6757211537094468E-6</v>
+      </c>
+      <c r="AR37">
+        <v>-8.7744047354038638E-5</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>50</v>
       </c>
       <c r="B38">
-        <v>-3.0870329180964724E-2</v>
+        <v>1.8033483807869375E-2</v>
       </c>
       <c r="C38">
-        <v>-6.6561361730082217E-6</v>
+        <v>2.7899555367540847E-6</v>
       </c>
       <c r="D38">
-        <v>-3.2583311215834349E-6</v>
+        <v>-1.0334561001571762E-6</v>
       </c>
       <c r="E38">
-        <v>2.954016607396414E-8</v>
+        <v>1.0532553549405659E-8</v>
       </c>
       <c r="F38">
-        <v>-1.1760968013646762E-5</v>
+        <v>3.2492339922331724E-5</v>
       </c>
       <c r="G38">
-        <v>2.2756918819256028E-5</v>
+        <v>1.5173013117684455E-5</v>
       </c>
       <c r="H38">
-        <v>-1.8791040016734084E-5</v>
+        <v>4.2793639545473446E-6</v>
       </c>
       <c r="I38">
-        <v>1.8376836389001638E-5</v>
+        <v>-9.8928125259052885E-6</v>
       </c>
       <c r="J38">
-        <v>4.6422348104345842E-5</v>
+        <v>5.6339776325737585E-5</v>
       </c>
       <c r="K38">
-        <v>8.0243595814496072E-6</v>
+        <v>-1.716200764187686E-6</v>
       </c>
       <c r="L38">
-        <v>2.5405246892678114E-5</v>
+        <v>3.5582490890898716E-5</v>
       </c>
       <c r="M38">
-        <v>3.0585834488922698E-5</v>
+        <v>3.8748218790004901E-5</v>
       </c>
       <c r="N38">
-        <v>4.076369953180751E-5</v>
+        <v>4.6269223299862366E-5</v>
       </c>
       <c r="O38">
-        <v>3.7495458104542818E-7</v>
+        <v>5.2819471929674983E-7</v>
       </c>
       <c r="P38">
-        <v>3.2506559709381887E-5</v>
+        <v>-2.1151042344867726E-5</v>
       </c>
       <c r="Q38">
-        <v>3.7413788626726276E-5</v>
+        <v>-2.6881329929756098E-5</v>
       </c>
       <c r="R38">
-        <v>1.6319100763837145E-6</v>
+        <v>-8.6828716712565845E-5</v>
       </c>
       <c r="S38">
-        <v>-8.443903227481615E-7</v>
+        <v>4.4041929045943611E-7</v>
       </c>
       <c r="T38">
-        <v>1.7382599122846092E-5</v>
+        <v>-2.8659827315869238E-7</v>
       </c>
       <c r="U38">
-        <v>5.3573246627997603E-5</v>
+        <v>-9.1963602796573968E-6</v>
       </c>
       <c r="V38">
-        <v>4.4047385844614743E-5</v>
+        <v>4.2481684031844217E-5</v>
       </c>
       <c r="W38">
-        <v>5.5298533649528712E-5</v>
+        <v>1.8654150972247834E-5</v>
       </c>
       <c r="X38">
-        <v>-1.811712004518766E-9</v>
+        <v>2.4052799086360171E-5</v>
       </c>
       <c r="Y38">
-        <v>8.652743137825871E-6</v>
+        <v>1.9961295204425745E-6</v>
       </c>
       <c r="Z38">
-        <v>-2.9360481021125929E-5</v>
+        <v>2.06451788935454E-5</v>
       </c>
       <c r="AA38">
-        <v>-3.8022033849529431E-5</v>
+        <v>1.4242220002960487E-5</v>
       </c>
       <c r="AB38">
-        <v>3.8413146181993756E-5</v>
+        <v>9.3419940192719544E-7</v>
       </c>
       <c r="AC38">
-        <v>-6.6095193044184543E-7</v>
+        <v>6.493873216813399E-5</v>
       </c>
       <c r="AD38">
-        <v>-1.6385837844701929E-5</v>
+        <v>3.9951759158020936E-5</v>
       </c>
       <c r="AE38">
-        <v>7.7361081896950722E-6</v>
+        <v>2.4448304518809874E-5</v>
       </c>
       <c r="AF38">
-        <v>-3.9086952848735432E-6</v>
+        <v>3.9382698627287582E-5</v>
       </c>
       <c r="AG38">
-        <v>4.8440844445902598E-6</v>
+        <v>1.5480316663018216E-5</v>
       </c>
       <c r="AH38">
-        <v>-3.9090438102937561E-5</v>
+        <v>3.6112915972027104E-5</v>
       </c>
       <c r="AI38">
-        <v>-2.4094375958102191E-5</v>
+        <v>6.5494605512361531E-6</v>
       </c>
       <c r="AJ38">
-        <v>-3.1611184333235463E-5</v>
+        <v>2.5779376703687149E-5</v>
       </c>
       <c r="AK38">
-        <v>-2.7909292836626391E-5</v>
+        <v>2.7164993129766073E-5</v>
       </c>
       <c r="AL38">
-        <v>1.3125959820653454E-4</v>
+        <v>-2.5995379457159424E-5</v>
       </c>
       <c r="AM38">
-        <v>1.1036402493871664E-3</v>
+        <v>1.0293595554383072E-3</v>
       </c>
       <c r="AN38">
-        <v>-1.0051472388101434E-4</v>
+        <v>1.305311523046843E-4</v>
       </c>
       <c r="AO38">
-        <v>-8.6293625798551348E-5</v>
+        <v>-6.7874303206288034E-5</v>
       </c>
       <c r="AP38">
-        <v>-2.3954656456203938E-5</v>
+        <v>-4.3032226993440914E-5</v>
       </c>
       <c r="AQ38">
-        <v>3.6478947468377836E-4</v>
+        <v>4.4356152654402337E-6</v>
+      </c>
+      <c r="AR38">
+        <v>3.194898591623417E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>51</v>
       </c>
       <c r="B39">
-        <v>0.15168590552598571</v>
+        <v>-3.0002152271783548E-2</v>
       </c>
       <c r="C39">
-        <v>-1.8539723440685585E-5</v>
+        <v>-6.0572978614861404E-6</v>
       </c>
       <c r="D39">
-        <v>2.89686766211284E-6</v>
+        <v>-3.3704414111874513E-6</v>
       </c>
       <c r="E39">
-        <v>-2.1345251528660415E-8</v>
+        <v>3.0504208080624811E-8</v>
       </c>
       <c r="F39">
-        <v>9.0706039357783656E-5</v>
+        <v>-1.150887113923727E-5</v>
       </c>
       <c r="G39">
-        <v>8.0026343163582615E-5</v>
+        <v>2.3607783540637679E-5</v>
       </c>
       <c r="H39">
-        <v>-5.8515461676648969E-5</v>
+        <v>-1.8879900017464195E-5</v>
       </c>
       <c r="I39">
-        <v>-3.6023502360054018E-5</v>
+        <v>1.7382693735625671E-5</v>
       </c>
       <c r="J39">
-        <v>-2.0722848788846002E-4</v>
+        <v>4.5915404099321059E-5</v>
       </c>
       <c r="K39">
-        <v>4.4279381699768459E-5</v>
+        <v>8.1523951257680819E-6</v>
       </c>
       <c r="L39">
-        <v>-8.5454281862489537E-5</v>
+        <v>2.5580868588570733E-5</v>
       </c>
       <c r="M39">
-        <v>-3.200603423451919E-4</v>
+        <v>5.2920032512073249E-5</v>
       </c>
       <c r="N39">
-        <v>-2.3554541100202344E-4</v>
+        <v>4.294686063254817E-5</v>
       </c>
       <c r="O39">
-        <v>-2.0511023347054877E-4</v>
+        <v>2.3039662703446028E-6</v>
       </c>
       <c r="P39">
-        <v>1.1901767475533589E-4</v>
+        <v>3.6959498596427942E-5</v>
       </c>
       <c r="Q39">
-        <v>5.7451431620964382E-5</v>
+        <v>4.0798407042487686E-5</v>
       </c>
       <c r="R39">
-        <v>4.2662222833033678E-6</v>
+        <v>-2.3798799603195429E-5</v>
       </c>
       <c r="S39">
-        <v>1.073758096602815E-6</v>
+        <v>1.6260607114634014E-6</v>
       </c>
       <c r="T39">
-        <v>-2.3319174777097114E-4</v>
+        <v>-8.246495457671037E-7</v>
       </c>
       <c r="U39">
-        <v>-2.775603322882704E-4</v>
+        <v>2.3016057492726588E-5</v>
       </c>
       <c r="V39">
-        <v>-2.4737388454350165E-4</v>
+        <v>5.7762560452753319E-5</v>
       </c>
       <c r="W39">
-        <v>-2.5659785109188166E-4</v>
+        <v>4.8755160941154545E-5</v>
       </c>
       <c r="X39">
-        <v>2.242080471791211E-5</v>
+        <v>6.1042891178117117E-5</v>
       </c>
       <c r="Y39">
-        <v>1.646339846512447E-5</v>
+        <v>-3.8753112466631331E-7</v>
       </c>
       <c r="Z39">
-        <v>4.0365629356841823E-4</v>
+        <v>9.1523291371155621E-6</v>
       </c>
       <c r="AA39">
-        <v>5.8979347552161137E-4</v>
+        <v>-2.8908515499029112E-5</v>
       </c>
       <c r="AB39">
-        <v>3.7078127527999437E-4</v>
+        <v>-3.8704430041460722E-5</v>
       </c>
       <c r="AC39">
-        <v>3.5577701878915496E-4</v>
+        <v>3.82326969437198E-5</v>
       </c>
       <c r="AD39">
-        <v>2.5194516600622716E-4</v>
+        <v>-5.2588613544814027E-7</v>
       </c>
       <c r="AE39">
-        <v>3.6283458477464394E-4</v>
+        <v>-1.6846050946496311E-5</v>
       </c>
       <c r="AF39">
-        <v>4.031385264726472E-4</v>
+        <v>7.805007192486377E-6</v>
       </c>
       <c r="AG39">
-        <v>4.1317050690739792E-4</v>
+        <v>-3.1962760641954713E-6</v>
       </c>
       <c r="AH39">
-        <v>3.7974521770316828E-4</v>
+        <v>4.8611499695481932E-6</v>
       </c>
       <c r="AI39">
-        <v>3.786919055577545E-4</v>
+        <v>-3.7869437306830287E-5</v>
       </c>
       <c r="AJ39">
-        <v>4.8275100182641046E-4</v>
+        <v>-2.3229238199700243E-5</v>
       </c>
       <c r="AK39">
-        <v>1.0790087923448649E-5</v>
+        <v>-3.1215913866744152E-5</v>
       </c>
       <c r="AL39">
-        <v>-6.9239381469480047E-5</v>
+        <v>-2.7882556433901697E-5</v>
       </c>
       <c r="AM39">
-        <v>-1.0051472388101434E-4</v>
+        <v>1.305311523046843E-4</v>
       </c>
       <c r="AN39">
-        <v>2.0236849481693455E-3</v>
+        <v>1.1016671918213923E-3</v>
       </c>
       <c r="AO39">
-        <v>1.8471926713625828E-4</v>
+        <v>-9.8994123775936774E-5</v>
       </c>
       <c r="AP39">
-        <v>1.9104235346903897E-4</v>
+        <v>-8.4424561077126481E-5</v>
       </c>
       <c r="AQ39">
-        <v>-7.9150724467695437E-4</v>
+        <v>-2.2199406239468601E-5</v>
+      </c>
+      <c r="AR39">
+        <v>3.5840604334615004E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>52</v>
       </c>
       <c r="B40">
-        <v>-8.7209085759077334E-2</v>
+        <v>0.14803921720790936</v>
       </c>
       <c r="C40">
-        <v>9.710421775690887E-5</v>
+        <v>-1.9208425160340764E-5</v>
       </c>
       <c r="D40">
-        <v>-2.7473720154348752E-6</v>
+        <v>2.5632093426097846E-6</v>
       </c>
       <c r="E40">
-        <v>7.0629170521029075E-9</v>
+        <v>-1.8978066609551009E-8</v>
       </c>
       <c r="F40">
-        <v>1.5386057604885089E-4</v>
+        <v>8.8099333403130311E-5</v>
       </c>
       <c r="G40">
-        <v>7.7999632797991154E-5</v>
+        <v>7.6671685962596917E-5</v>
       </c>
       <c r="H40">
-        <v>4.7719899226147261E-4</v>
+        <v>-5.909903294188602E-5</v>
       </c>
       <c r="I40">
-        <v>-3.3454447711108977E-4</v>
+        <v>-3.7244021950440405E-5</v>
       </c>
       <c r="J40">
-        <v>4.1730098122317314E-5</v>
+        <v>-2.0628212791292926E-4</v>
       </c>
       <c r="K40">
-        <v>2.8886901787732752E-5</v>
+        <v>4.2645198186014728E-5</v>
       </c>
       <c r="L40">
-        <v>-1.2942189627549643E-4</v>
+        <v>-9.167141801651303E-5</v>
       </c>
       <c r="M40">
-        <v>-1.722825983401787E-4</v>
+        <v>-2.5805846217603852E-4</v>
       </c>
       <c r="N40">
-        <v>-1.1478379244263959E-4</v>
+        <v>-2.5821785337472514E-4</v>
       </c>
       <c r="O40">
-        <v>3.1546564123223963E-5</v>
+        <v>-2.1930707834242724E-4</v>
       </c>
       <c r="P40">
-        <v>-5.869035117726453E-5</v>
+        <v>1.2773144809495276E-4</v>
       </c>
       <c r="Q40">
-        <v>-1.2516515398247423E-6</v>
+        <v>6.3268827136260056E-5</v>
       </c>
       <c r="R40">
-        <v>-3.1499113454875539E-6</v>
+        <v>-4.7291676796752815E-5</v>
       </c>
       <c r="S40">
-        <v>1.1364141862566055E-6</v>
+        <v>4.378581733912487E-6</v>
       </c>
       <c r="T40">
-        <v>-9.4160293775743755E-5</v>
+        <v>1.0863258192343018E-6</v>
       </c>
       <c r="U40">
-        <v>-1.7065811430583416E-4</v>
+        <v>-2.7490848896883897E-4</v>
       </c>
       <c r="V40">
-        <v>-2.2862497250114165E-4</v>
+        <v>-3.1403034863770884E-4</v>
       </c>
       <c r="W40">
-        <v>7.4148520867828641E-5</v>
+        <v>-2.8142333793042306E-4</v>
       </c>
       <c r="X40">
-        <v>1.1999638764810673E-5</v>
+        <v>-2.8940828298528831E-4</v>
       </c>
       <c r="Y40">
-        <v>5.5543807386748333E-5</v>
+        <v>2.5498506571355222E-5</v>
       </c>
       <c r="Z40">
-        <v>4.3801699276803418E-4</v>
+        <v>1.7944867047482212E-5</v>
       </c>
       <c r="AA40">
-        <v>3.592765088063606E-4</v>
+        <v>4.026188614934633E-4</v>
       </c>
       <c r="AB40">
-        <v>3.5922475752295929E-4</v>
+        <v>5.87445689839858E-4</v>
       </c>
       <c r="AC40">
-        <v>3.623765894293155E-4</v>
+        <v>3.7035832290054516E-4</v>
       </c>
       <c r="AD40">
-        <v>2.5536412099808742E-4</v>
+        <v>3.5411842352448485E-4</v>
       </c>
       <c r="AE40">
-        <v>3.7037320868375741E-4</v>
+        <v>2.5177474873515359E-4</v>
       </c>
       <c r="AF40">
-        <v>4.5382363650147382E-4</v>
+        <v>3.6214029100957267E-4</v>
       </c>
       <c r="AG40">
-        <v>4.2125340029787792E-4</v>
+        <v>4.0044559858913467E-4</v>
       </c>
       <c r="AH40">
-        <v>4.1354276603727661E-4</v>
+        <v>4.1191065967629377E-4</v>
       </c>
       <c r="AI40">
-        <v>3.8213493631656992E-4</v>
+        <v>3.7735991052106324E-4</v>
       </c>
       <c r="AJ40">
-        <v>4.3972520854778573E-4</v>
+        <v>3.7615854293985635E-4</v>
       </c>
       <c r="AK40">
-        <v>1.2783271833306101E-5</v>
+        <v>4.8259748818672572E-4</v>
       </c>
       <c r="AL40">
-        <v>-4.4285602571714924E-5</v>
+        <v>1.0787249896904632E-5</v>
       </c>
       <c r="AM40">
-        <v>-8.6293625798551348E-5</v>
+        <v>-6.7874303206288034E-5</v>
       </c>
       <c r="AN40">
-        <v>1.8471926713625828E-4</v>
+        <v>-9.8994123775936774E-5</v>
       </c>
       <c r="AO40">
-        <v>4.2055786013327004E-3</v>
+        <v>2.0278010360385949E-3</v>
       </c>
       <c r="AP40">
-        <v>1.371593282148413E-4</v>
+        <v>1.8484620374353296E-4</v>
       </c>
       <c r="AQ40">
-        <v>-4.6461468779139564E-4</v>
+        <v>1.8491956991039079E-4</v>
+      </c>
+      <c r="AR40">
+        <v>-7.5999238769450792E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>53</v>
       </c>
       <c r="B41">
-        <v>-3.173783483970876E-2</v>
+        <v>-8.7900576161723101E-2</v>
       </c>
       <c r="C41">
-        <v>-3.6166354192387116E-5</v>
+        <v>9.629450597452188E-5</v>
       </c>
       <c r="D41">
-        <v>2.2824532579531864E-6</v>
+        <v>-2.4660800694133118E-6</v>
       </c>
       <c r="E41">
-        <v>-1.4071416819641246E-8</v>
+        <v>4.8751495865864164E-9</v>
       </c>
       <c r="F41">
-        <v>5.2729231957937995E-4</v>
+        <v>1.5417843260810292E-4</v>
       </c>
       <c r="G41">
-        <v>-1.8521547443979276E-5</v>
+        <v>7.6617248480896627E-5</v>
       </c>
       <c r="H41">
-        <v>-8.7355630996347139E-6</v>
+        <v>4.7530690062067563E-4</v>
       </c>
       <c r="I41">
-        <v>-1.0238122483882363E-5</v>
+        <v>-3.3184969413944162E-4</v>
       </c>
       <c r="J41">
-        <v>-2.7236852486551275E-5</v>
+        <v>4.2277852227119104E-5</v>
       </c>
       <c r="K41">
-        <v>-3.9268400613410844E-5</v>
+        <v>2.8369072048134479E-5</v>
       </c>
       <c r="L41">
-        <v>-1.2099708312511239E-4</v>
+        <v>-1.2936524605460301E-4</v>
       </c>
       <c r="M41">
-        <v>8.6181194343178005E-5</v>
+        <v>-1.8484590998285141E-4</v>
       </c>
       <c r="N41">
-        <v>7.5340316913246697E-5</v>
+        <v>-1.0874516977415523E-4</v>
       </c>
       <c r="O41">
-        <v>-5.5606349597320476E-5</v>
+        <v>3.5521313264978954E-5</v>
       </c>
       <c r="P41">
-        <v>4.6271565935284006E-5</v>
+        <v>-5.7656337052169139E-5</v>
       </c>
       <c r="Q41">
-        <v>7.2041057755371378E-5</v>
+        <v>-1.4219726237313363E-6</v>
       </c>
       <c r="R41">
-        <v>1.6854425713366985E-6</v>
+        <v>4.6749325977003619E-6</v>
       </c>
       <c r="S41">
-        <v>4.4094739935862102E-7</v>
+        <v>-3.1479742465413821E-6</v>
       </c>
       <c r="T41">
-        <v>2.7555642063318924E-6</v>
+        <v>1.1393478751827723E-6</v>
       </c>
       <c r="U41">
-        <v>2.9604358400704266E-5</v>
+        <v>-8.7248140318261109E-5</v>
       </c>
       <c r="V41">
-        <v>1.7113101496331112E-5</v>
+        <v>-1.6312895012986591E-4</v>
       </c>
       <c r="W41">
-        <v>-1.728434469887237E-5</v>
+        <v>-2.2054997777696728E-4</v>
       </c>
       <c r="X41">
-        <v>1.8571486088071208E-5</v>
+        <v>8.07080910046832E-5</v>
       </c>
       <c r="Y41">
-        <v>4.3445861702619309E-6</v>
+        <v>1.1452309720167354E-5</v>
       </c>
       <c r="Z41">
-        <v>1.8372719529889965E-4</v>
+        <v>5.5692077909504099E-5</v>
       </c>
       <c r="AA41">
-        <v>1.9307276699712285E-4</v>
+        <v>4.3615326146382346E-4</v>
       </c>
       <c r="AB41">
-        <v>1.5082046462053201E-4</v>
+        <v>3.5801505068160425E-4</v>
       </c>
       <c r="AC41">
-        <v>1.5633072236814256E-4</v>
+        <v>3.5860028366845032E-4</v>
       </c>
       <c r="AD41">
-        <v>1.0386015992686073E-4</v>
+        <v>3.6104985962135577E-4</v>
       </c>
       <c r="AE41">
-        <v>8.1505091668721536E-5</v>
+        <v>2.5489463888757097E-4</v>
       </c>
       <c r="AF41">
-        <v>1.3906624210919763E-4</v>
+        <v>3.6865975118195818E-4</v>
       </c>
       <c r="AG41">
-        <v>1.679526220000058E-4</v>
+        <v>4.5247991152615218E-4</v>
       </c>
       <c r="AH41">
-        <v>1.3766436870969522E-4</v>
+        <v>4.1968965801691103E-4</v>
       </c>
       <c r="AI41">
-        <v>1.5770781126099766E-4</v>
+        <v>4.1175410787381217E-4</v>
       </c>
       <c r="AJ41">
-        <v>1.8591249768122543E-4</v>
+        <v>3.8035158429987966E-4</v>
       </c>
       <c r="AK41">
-        <v>-4.6529424496661348E-6</v>
+        <v>4.3933374554840749E-4</v>
       </c>
       <c r="AL41">
-        <v>3.3859687520102402E-6</v>
+        <v>1.2684983280085367E-5</v>
       </c>
       <c r="AM41">
-        <v>-2.3954656456203938E-5</v>
+        <v>-4.3032226993440914E-5</v>
       </c>
       <c r="AN41">
-        <v>1.9104235346903897E-4</v>
+        <v>-8.4424561077126481E-5</v>
       </c>
       <c r="AO41">
-        <v>1.371593282148413E-4</v>
+        <v>1.8484620374353296E-4</v>
       </c>
       <c r="AP41">
-        <v>2.4382516578593475E-3</v>
+        <v>4.1925737580163084E-3</v>
       </c>
       <c r="AQ41">
-        <v>-3.4105097352048002E-4</v>
+        <v>1.3380039810132407E-4</v>
+      </c>
+      <c r="AR41">
+        <v>-4.7657653650425914E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>54</v>
       </c>
       <c r="B42">
-        <v>-2.5865446472421207</v>
+        <v>-3.2656573120738122E-2</v>
       </c>
       <c r="C42">
-        <v>-1.0463361448894311E-4</v>
+        <v>-3.6166396130143145E-5</v>
       </c>
       <c r="D42">
-        <v>-1.496981184643576E-4</v>
+        <v>2.8769194255477449E-6</v>
       </c>
       <c r="E42">
-        <v>1.2922709265102534E-6</v>
+        <v>-1.9033125358466659E-8</v>
       </c>
       <c r="F42">
-        <v>-1.6940687462424716E-3</v>
+        <v>5.3598449500832359E-4</v>
       </c>
       <c r="G42">
-        <v>-7.4329922940483042E-4</v>
+        <v>-1.9991321342714908E-5</v>
       </c>
       <c r="H42">
-        <v>-9.2364851458757503E-4</v>
+        <v>-9.2991318796916496E-6</v>
       </c>
       <c r="I42">
-        <v>-1.2711840087198127E-3</v>
+        <v>-6.1691330145958805E-6</v>
       </c>
       <c r="J42">
-        <v>-8.9636741664410194E-4</v>
+        <v>-2.6325064785907192E-5</v>
       </c>
       <c r="K42">
-        <v>-1.3079474208521902E-3</v>
+        <v>-3.9325834437783079E-5</v>
       </c>
       <c r="L42">
-        <v>-1.414151135808499E-3</v>
+        <v>-1.184377992616742E-4</v>
       </c>
       <c r="M42">
-        <v>-1.8426557074204353E-3</v>
+        <v>-4.578124551861591E-5</v>
       </c>
       <c r="N42">
-        <v>-1.4157305479812121E-3</v>
+        <v>7.2319667593658845E-5</v>
       </c>
       <c r="O42">
-        <v>-9.3187609190677895E-4</v>
+        <v>-5.7559875845351915E-5</v>
       </c>
       <c r="P42">
-        <v>-3.9554637457496435E-4</v>
+        <v>3.125910408156593E-5</v>
       </c>
       <c r="Q42">
-        <v>-5.844187085943701E-4</v>
+        <v>5.9821689659732502E-5</v>
       </c>
       <c r="R42">
-        <v>-3.5939342340613359E-5</v>
+        <v>3.4084743905640205E-4</v>
       </c>
       <c r="S42">
-        <v>-3.7450627238493311E-5</v>
+        <v>1.6356103589936964E-6</v>
       </c>
       <c r="T42">
-        <v>-1.0251759642876408E-3</v>
+        <v>3.8065117494073738E-7</v>
       </c>
       <c r="U42">
-        <v>-1.1878898687438565E-3</v>
+        <v>-5.8642862670350707E-6</v>
       </c>
       <c r="V42">
-        <v>-1.3002500503034127E-3</v>
+        <v>2.5422342668913144E-5</v>
       </c>
       <c r="W42">
-        <v>-1.5115842393550773E-3</v>
+        <v>9.6960204878589239E-6</v>
       </c>
       <c r="X42">
-        <v>9.6714393400049241E-5</v>
+        <v>-2.836699554171915E-5</v>
       </c>
       <c r="Y42">
-        <v>-5.6131652601602737E-5</v>
+        <v>1.8842826737681332E-5</v>
       </c>
       <c r="Z42">
-        <v>-9.4485755885233996E-4</v>
+        <v>3.2697424771510218E-6</v>
       </c>
       <c r="AA42">
-        <v>-9.6631756788387508E-4</v>
+        <v>1.8289591655266461E-4</v>
       </c>
       <c r="AB42">
-        <v>-8.9756896550730958E-4</v>
+        <v>1.9368630981975431E-4</v>
       </c>
       <c r="AC42">
-        <v>-8.9412996349832042E-4</v>
+        <v>1.5240502166054474E-4</v>
       </c>
       <c r="AD42">
-        <v>-1.0671680372189051E-3</v>
+        <v>1.5708521729649401E-4</v>
       </c>
       <c r="AE42">
-        <v>-8.0569875164455593E-4</v>
+        <v>1.0507448715445149E-4</v>
       </c>
       <c r="AF42">
-        <v>-8.4645066631174439E-4</v>
+        <v>8.2628750884698016E-5</v>
       </c>
       <c r="AG42">
-        <v>-9.4795639767388602E-4</v>
+        <v>1.3885927297822763E-4</v>
       </c>
       <c r="AH42">
-        <v>-9.5311335697663034E-4</v>
+        <v>1.6842463336235261E-4</v>
       </c>
       <c r="AI42">
-        <v>-6.8489990643277507E-4</v>
+        <v>1.3726861762914934E-4</v>
       </c>
       <c r="AJ42">
-        <v>-9.2595328166993453E-4</v>
+        <v>1.5798649814856403E-4</v>
       </c>
       <c r="AK42">
-        <v>-8.8602220955340196E-5</v>
+        <v>1.8553949492073132E-4</v>
       </c>
       <c r="AL42">
-        <v>3.2797219291621349E-4</v>
+        <v>-4.6757211537094468E-6</v>
       </c>
       <c r="AM42">
-        <v>3.6478947468377836E-4</v>
+        <v>4.4356152654402337E-6</v>
       </c>
       <c r="AN42">
-        <v>-7.9150724467695437E-4</v>
+        <v>-2.2199406239468601E-5</v>
       </c>
       <c r="AO42">
-        <v>-4.6461468779139564E-4</v>
+        <v>1.8491956991039079E-4</v>
       </c>
       <c r="AP42">
-        <v>-3.4105097352048002E-4</v>
+        <v>1.3380039810132407E-4</v>
       </c>
       <c r="AQ42">
-        <v>1.2509939995914668E-2</v>
+        <v>2.4332131832502618E-3</v>
+      </c>
+      <c r="AR42">
+        <v>-3.3331822720655352E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43">
+        <v>-2.5697782758784133</v>
+      </c>
+      <c r="C43">
+        <v>-1.1197837044877331E-4</v>
+      </c>
+      <c r="D43">
+        <v>-1.5108751749055521E-4</v>
+      </c>
+      <c r="E43">
+        <v>1.3016074712162899E-6</v>
+      </c>
+      <c r="F43">
+        <v>-1.7041180280966313E-3</v>
+      </c>
+      <c r="G43">
+        <v>-7.4809789003865603E-4</v>
+      </c>
+      <c r="H43">
+        <v>-9.2332408612558398E-4</v>
+      </c>
+      <c r="I43">
+        <v>-1.2707421004932093E-3</v>
+      </c>
+      <c r="J43">
+        <v>-9.0258539961335794E-4</v>
+      </c>
+      <c r="K43">
+        <v>-1.3093890347538821E-3</v>
+      </c>
+      <c r="L43">
+        <v>-1.4224093550517488E-3</v>
+      </c>
+      <c r="M43">
+        <v>-1.8153576128611196E-3</v>
+      </c>
+      <c r="N43">
+        <v>-1.385178765190847E-3</v>
+      </c>
+      <c r="O43">
+        <v>-9.2926641202923429E-4</v>
+      </c>
+      <c r="P43">
+        <v>-3.8917987329987043E-4</v>
+      </c>
+      <c r="Q43">
+        <v>-5.7924486955479148E-4</v>
+      </c>
+      <c r="R43">
+        <v>-4.5208437257259295E-4</v>
+      </c>
+      <c r="S43">
+        <v>-3.5507447590695699E-5</v>
+      </c>
+      <c r="T43">
+        <v>-3.7219440850434456E-5</v>
+      </c>
+      <c r="U43">
+        <v>-1.0196715691800115E-3</v>
+      </c>
+      <c r="V43">
+        <v>-1.1834741592251807E-3</v>
+      </c>
+      <c r="W43">
+        <v>-1.302540809616962E-3</v>
+      </c>
+      <c r="X43">
+        <v>-1.510594346293435E-3</v>
+      </c>
+      <c r="Y43">
+        <v>9.7654341984000577E-5</v>
+      </c>
+      <c r="Z43">
+        <v>-5.4703025463282485E-5</v>
+      </c>
+      <c r="AA43">
+        <v>-9.4117145899835124E-4</v>
+      </c>
+      <c r="AB43">
+        <v>-9.5639080503178689E-4</v>
+      </c>
+      <c r="AC43">
+        <v>-8.8318060932463644E-4</v>
+      </c>
+      <c r="AD43">
+        <v>-8.8661189454627997E-4</v>
+      </c>
+      <c r="AE43">
+        <v>-1.0650679633729598E-3</v>
+      </c>
+      <c r="AF43">
+        <v>-8.0170506302705124E-4</v>
+      </c>
+      <c r="AG43">
+        <v>-8.3386719969538216E-4</v>
+      </c>
+      <c r="AH43">
+        <v>-9.3874486166108844E-4</v>
+      </c>
+      <c r="AI43">
+        <v>-9.562720982900653E-4</v>
+      </c>
+      <c r="AJ43">
+        <v>-6.8254675729478528E-4</v>
+      </c>
+      <c r="AK43">
+        <v>-9.2277991864022539E-4</v>
+      </c>
+      <c r="AL43">
+        <v>-8.7744047354038638E-5</v>
+      </c>
+      <c r="AM43">
+        <v>3.194898591623417E-4</v>
+      </c>
+      <c r="AN43">
+        <v>3.5840604334615004E-4</v>
+      </c>
+      <c r="AO43">
+        <v>-7.5999238769450792E-4</v>
+      </c>
+      <c r="AP43">
+        <v>-4.7657653650425914E-4</v>
+      </c>
+      <c r="AQ43">
+        <v>-3.3331822720655352E-4</v>
+      </c>
+      <c r="AR43">
+        <v>1.2495998650362846E-2</v>
       </c>
     </row>
   </sheetData>
